--- a/frontend/data/uk_election_predictions.xlsx
+++ b/frontend/data/uk_election_predictions.xlsx
@@ -47,30 +47,30 @@
     <t>aldridge-brownhills</t>
   </si>
   <si>
+    <t>Brexit Party/Reform UK</t>
+  </si>
+  <si>
+    <t>E14001064</t>
+  </si>
+  <si>
+    <t>altrincham and sale west</t>
+  </si>
+  <si>
+    <t>E14001065</t>
+  </si>
+  <si>
+    <t>amber valley</t>
+  </si>
+  <si>
+    <t>E14001066</t>
+  </si>
+  <si>
+    <t>arundel and south downs</t>
+  </si>
+  <si>
     <t>Conservative</t>
   </si>
   <si>
-    <t>E14001064</t>
-  </si>
-  <si>
-    <t>altrincham and sale west</t>
-  </si>
-  <si>
-    <t>E14001065</t>
-  </si>
-  <si>
-    <t>amber valley</t>
-  </si>
-  <si>
-    <t>Brexit Party/Reform UK</t>
-  </si>
-  <si>
-    <t>E14001066</t>
-  </si>
-  <si>
-    <t>arundel and south downs</t>
-  </si>
-  <si>
     <t>E14001067</t>
   </si>
   <si>
@@ -395,6 +395,9 @@
     <t>bradford west</t>
   </si>
   <si>
+    <t>Other</t>
+  </si>
+  <si>
     <t>E14001120</t>
   </si>
   <si>
@@ -1211,9 +1214,6 @@
     <t>great yarmouth</t>
   </si>
   <si>
-    <t>Other</t>
-  </si>
-  <si>
     <t>E14001256</t>
   </si>
   <si>
@@ -3815,6 +3815,9 @@
     <t>blaenau gwent and rhymney</t>
   </si>
   <si>
+    <t>Plaid Cymru</t>
+  </si>
+  <si>
     <t>W07000084</t>
   </si>
   <si>
@@ -3837,9 +3840,6 @@
   </si>
   <si>
     <t>caerphilly</t>
-  </si>
-  <si>
-    <t>Plaid Cymru</t>
   </si>
   <si>
     <t>W07000088</t>
@@ -4360,7 +4360,7 @@
         <v>6</v>
       </c>
       <c r="C2">
-        <v>0.2921991653506604</v>
+        <v>0.2925143604288105</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
@@ -4377,7 +4377,7 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>0.3620582229684139</v>
+        <v>0.3626930731865723</v>
       </c>
       <c r="D3" t="s">
         <v>7</v>
@@ -4394,7 +4394,7 @@
         <v>6</v>
       </c>
       <c r="C4">
-        <v>0.3995555485268464</v>
+        <v>0.3970787225281536</v>
       </c>
       <c r="D4" t="s">
         <v>7</v>
@@ -4408,27 +4408,27 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <v>0.3848951279804696</v>
+      </c>
+      <c r="D5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" t="s">
         <v>15</v>
-      </c>
-      <c r="C5">
-        <v>0.3811690257892728</v>
-      </c>
-      <c r="D5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
         <v>17</v>
       </c>
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
       <c r="C6">
-        <v>0.3684847428901259</v>
+        <v>0.363824286601389</v>
       </c>
       <c r="D6" t="s">
         <v>7</v>
@@ -4442,10 +4442,10 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C7">
-        <v>0.3311443216853283</v>
+        <v>0.3328634340280491</v>
       </c>
       <c r="D7" t="s">
         <v>7</v>
@@ -4459,10 +4459,10 @@
         <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C8">
-        <v>0.3318472403571271</v>
+        <v>0.3293939329544224</v>
       </c>
       <c r="D8" t="s">
         <v>7</v>
@@ -4476,10 +4476,10 @@
         <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C9">
-        <v>0.3246669678462067</v>
+        <v>0.324228857305032</v>
       </c>
       <c r="D9" t="s">
         <v>7</v>
@@ -4493,10 +4493,10 @@
         <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C10">
-        <v>0.3103760824726394</v>
+        <v>0.3139395134550744</v>
       </c>
       <c r="D10" t="s">
         <v>7</v>
@@ -4510,10 +4510,10 @@
         <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C11">
-        <v>0.210315600131295</v>
+        <v>0.20909881657508</v>
       </c>
       <c r="D11" t="s">
         <v>7</v>
@@ -4530,7 +4530,7 @@
         <v>6</v>
       </c>
       <c r="C12">
-        <v>0.3446388176222222</v>
+        <v>0.3458979408275309</v>
       </c>
       <c r="D12" t="s">
         <v>7</v>
@@ -4544,10 +4544,10 @@
         <v>31</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C13">
-        <v>0.3070256966130187</v>
+        <v>0.3101519003123441</v>
       </c>
       <c r="D13" t="s">
         <v>7</v>
@@ -4561,10 +4561,10 @@
         <v>33</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C14">
-        <v>0.4150893073671991</v>
+        <v>0.4163318212989995</v>
       </c>
       <c r="D14" t="s">
         <v>7</v>
@@ -4578,10 +4578,10 @@
         <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C15">
-        <v>0.3482344062586295</v>
+        <v>0.3449482259435828</v>
       </c>
       <c r="D15" t="s">
         <v>7</v>
@@ -4598,7 +4598,7 @@
         <v>6</v>
       </c>
       <c r="C16">
-        <v>0.3080646499211662</v>
+        <v>0.3108897071796079</v>
       </c>
       <c r="D16" t="s">
         <v>7</v>
@@ -4612,10 +4612,10 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C17">
-        <v>0.2583018345036134</v>
+        <v>0.2581652271289055</v>
       </c>
       <c r="D17" t="s">
         <v>7</v>
@@ -4629,10 +4629,10 @@
         <v>41</v>
       </c>
       <c r="B18" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C18">
-        <v>0.2988267729195434</v>
+        <v>0.2957086407508068</v>
       </c>
       <c r="D18" t="s">
         <v>7</v>
@@ -4649,7 +4649,7 @@
         <v>44</v>
       </c>
       <c r="C19">
-        <v>0.4300759456562349</v>
+        <v>0.4289327274080508</v>
       </c>
       <c r="D19" t="s">
         <v>7</v>
@@ -4666,7 +4666,7 @@
         <v>6</v>
       </c>
       <c r="C20">
-        <v>0.4468380138023574</v>
+        <v>0.446838337720757</v>
       </c>
       <c r="D20" t="s">
         <v>7</v>
@@ -4680,10 +4680,10 @@
         <v>48</v>
       </c>
       <c r="B21" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C21">
-        <v>0.3811650138673363</v>
+        <v>0.3821250188834537</v>
       </c>
       <c r="D21" t="s">
         <v>7</v>
@@ -4700,7 +4700,7 @@
         <v>6</v>
       </c>
       <c r="C22">
-        <v>0.3344251614978554</v>
+        <v>0.3382455525819016</v>
       </c>
       <c r="D22" t="s">
         <v>7</v>
@@ -4717,7 +4717,7 @@
         <v>6</v>
       </c>
       <c r="C23">
-        <v>0.4369161744909506</v>
+        <v>0.4361150861977534</v>
       </c>
       <c r="D23" t="s">
         <v>7</v>
@@ -4734,7 +4734,7 @@
         <v>6</v>
       </c>
       <c r="C24">
-        <v>0.3335312485975475</v>
+        <v>0.3356837839815848</v>
       </c>
       <c r="D24" t="s">
         <v>7</v>
@@ -4751,7 +4751,7 @@
         <v>6</v>
       </c>
       <c r="C25">
-        <v>0.6393188085384413</v>
+        <v>0.638494866249112</v>
       </c>
       <c r="D25" t="s">
         <v>7</v>
@@ -4765,10 +4765,10 @@
         <v>58</v>
       </c>
       <c r="B26" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C26">
-        <v>0.2806258847836097</v>
+        <v>0.2791133323496101</v>
       </c>
       <c r="D26" t="s">
         <v>7</v>
@@ -4782,10 +4782,10 @@
         <v>60</v>
       </c>
       <c r="B27" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C27">
-        <v>0.2805237413800937</v>
+        <v>0.2759558001858236</v>
       </c>
       <c r="D27" t="s">
         <v>7</v>
@@ -4802,7 +4802,7 @@
         <v>6</v>
       </c>
       <c r="C28">
-        <v>0.3117552186112074</v>
+        <v>0.3123659577083425</v>
       </c>
       <c r="D28" t="s">
         <v>7</v>
@@ -4819,7 +4819,7 @@
         <v>44</v>
       </c>
       <c r="C29">
-        <v>0.4387120842294758</v>
+        <v>0.4376414040888657</v>
       </c>
       <c r="D29" t="s">
         <v>7</v>
@@ -4836,7 +4836,7 @@
         <v>6</v>
       </c>
       <c r="C30">
-        <v>0.3456549751163897</v>
+        <v>0.3486317006826186</v>
       </c>
       <c r="D30" t="s">
         <v>7</v>
@@ -4853,7 +4853,7 @@
         <v>6</v>
       </c>
       <c r="C31">
-        <v>0.4427443295683027</v>
+        <v>0.447603545327402</v>
       </c>
       <c r="D31" t="s">
         <v>7</v>
@@ -4867,10 +4867,10 @@
         <v>70</v>
       </c>
       <c r="B32" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C32">
-        <v>0.4346084996832549</v>
+        <v>0.4358907906757701</v>
       </c>
       <c r="D32" t="s">
         <v>7</v>
@@ -4887,7 +4887,7 @@
         <v>6</v>
       </c>
       <c r="C33">
-        <v>0.3665579445188141</v>
+        <v>0.3568980809660334</v>
       </c>
       <c r="D33" t="s">
         <v>7</v>
@@ -4901,10 +4901,10 @@
         <v>74</v>
       </c>
       <c r="B34" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C34">
-        <v>0.3565914545167356</v>
+        <v>0.3494383799639729</v>
       </c>
       <c r="D34" t="s">
         <v>7</v>
@@ -4921,7 +4921,7 @@
         <v>6</v>
       </c>
       <c r="C35">
-        <v>0.5004724783831769</v>
+        <v>0.4857573951113609</v>
       </c>
       <c r="D35" t="s">
         <v>7</v>
@@ -4938,7 +4938,7 @@
         <v>79</v>
       </c>
       <c r="C36">
-        <v>0.2407580083141801</v>
+        <v>0.2433478816231222</v>
       </c>
       <c r="D36" t="s">
         <v>7</v>
@@ -4952,10 +4952,10 @@
         <v>81</v>
       </c>
       <c r="B37" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C37">
-        <v>0.2886931742968283</v>
+        <v>0.3384568809049596</v>
       </c>
       <c r="D37" t="s">
         <v>7</v>
@@ -4972,7 +4972,7 @@
         <v>6</v>
       </c>
       <c r="C38">
-        <v>0.3465307895553653</v>
+        <v>0.3432554876553289</v>
       </c>
       <c r="D38" t="s">
         <v>7</v>
@@ -4986,10 +4986,10 @@
         <v>85</v>
       </c>
       <c r="B39" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C39">
-        <v>0.3440065212015126</v>
+        <v>0.3334675603673717</v>
       </c>
       <c r="D39" t="s">
         <v>7</v>
@@ -5006,7 +5006,7 @@
         <v>6</v>
       </c>
       <c r="C40">
-        <v>0.481205082617963</v>
+        <v>0.4822723970273423</v>
       </c>
       <c r="D40" t="s">
         <v>7</v>
@@ -5020,10 +5020,10 @@
         <v>89</v>
       </c>
       <c r="B41" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C41">
-        <v>0.2561133802023802</v>
+        <v>0.2930887157838924</v>
       </c>
       <c r="D41" t="s">
         <v>7</v>
@@ -5040,7 +5040,7 @@
         <v>6</v>
       </c>
       <c r="C42">
-        <v>0.4969129698521282</v>
+        <v>0.498863344136383</v>
       </c>
       <c r="D42" t="s">
         <v>7</v>
@@ -5054,10 +5054,10 @@
         <v>93</v>
       </c>
       <c r="B43" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C43">
-        <v>0.4252489578233266</v>
+        <v>0.4273425732917904</v>
       </c>
       <c r="D43" t="s">
         <v>7</v>
@@ -5071,10 +5071,10 @@
         <v>95</v>
       </c>
       <c r="B44" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C44">
-        <v>0.4740149114278397</v>
+        <v>0.4740353805451992</v>
       </c>
       <c r="D44" t="s">
         <v>7</v>
@@ -5091,7 +5091,7 @@
         <v>6</v>
       </c>
       <c r="C45">
-        <v>0.3849560786555051</v>
+        <v>0.3838396867257516</v>
       </c>
       <c r="D45" t="s">
         <v>7</v>
@@ -5108,7 +5108,7 @@
         <v>6</v>
       </c>
       <c r="C46">
-        <v>0.3693749336005289</v>
+        <v>0.3698661397473352</v>
       </c>
       <c r="D46" t="s">
         <v>7</v>
@@ -5122,10 +5122,10 @@
         <v>101</v>
       </c>
       <c r="B47" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C47">
-        <v>0.2920714142176128</v>
+        <v>0.2926155663154248</v>
       </c>
       <c r="D47" t="s">
         <v>7</v>
@@ -5139,10 +5139,10 @@
         <v>103</v>
       </c>
       <c r="B48" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C48">
-        <v>0.4265334329802036</v>
+        <v>0.4314386278034156</v>
       </c>
       <c r="D48" t="s">
         <v>7</v>
@@ -5156,10 +5156,10 @@
         <v>105</v>
       </c>
       <c r="B49" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C49">
-        <v>0.3364877372600306</v>
+        <v>0.3383360290356556</v>
       </c>
       <c r="D49" t="s">
         <v>7</v>
@@ -5173,10 +5173,10 @@
         <v>107</v>
       </c>
       <c r="B50" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C50">
-        <v>0.3867552119515674</v>
+        <v>0.3818944245066954</v>
       </c>
       <c r="D50" t="s">
         <v>7</v>
@@ -5190,10 +5190,10 @@
         <v>109</v>
       </c>
       <c r="B51" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C51">
-        <v>0.3678840514918598</v>
+        <v>0.3684143421518599</v>
       </c>
       <c r="D51" t="s">
         <v>7</v>
@@ -5210,7 +5210,7 @@
         <v>6</v>
       </c>
       <c r="C52">
-        <v>0.4704246836604288</v>
+        <v>0.4712793494080896</v>
       </c>
       <c r="D52" t="s">
         <v>7</v>
@@ -5224,10 +5224,10 @@
         <v>113</v>
       </c>
       <c r="B53" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C53">
-        <v>0.4806178592821336</v>
+        <v>0.4919954255344806</v>
       </c>
       <c r="D53" t="s">
         <v>7</v>
@@ -5244,7 +5244,7 @@
         <v>6</v>
       </c>
       <c r="C54">
-        <v>0.3995489983749869</v>
+        <v>0.3960578057136706</v>
       </c>
       <c r="D54" t="s">
         <v>7</v>
@@ -5258,10 +5258,10 @@
         <v>117</v>
       </c>
       <c r="B55" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C55">
-        <v>0.2741123177500979</v>
+        <v>0.2799197406471978</v>
       </c>
       <c r="D55" t="s">
         <v>7</v>
@@ -5275,10 +5275,10 @@
         <v>119</v>
       </c>
       <c r="B56" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C56">
-        <v>0.3638145952545987</v>
+        <v>0.3658931322752896</v>
       </c>
       <c r="D56" t="s">
         <v>7</v>
@@ -5295,7 +5295,7 @@
         <v>6</v>
       </c>
       <c r="C57">
-        <v>0.5319788101052121</v>
+        <v>0.5187823295524883</v>
       </c>
       <c r="D57" t="s">
         <v>7</v>
@@ -5312,7 +5312,7 @@
         <v>6</v>
       </c>
       <c r="C58">
-        <v>0.3083017612380773</v>
+        <v>0.3040400193777805</v>
       </c>
       <c r="D58" t="s">
         <v>7</v>
@@ -5326,2322 +5326,2322 @@
         <v>125</v>
       </c>
       <c r="B59" t="s">
-        <v>6</v>
+        <v>126</v>
       </c>
       <c r="C59">
-        <v>0.3347488815515982</v>
+        <v>0.3201963569918908</v>
       </c>
       <c r="D59" t="s">
         <v>7</v>
       </c>
       <c r="E59" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B60" t="s">
         <v>6</v>
       </c>
       <c r="C60">
-        <v>0.3036369437365929</v>
+        <v>0.3024767425000124</v>
       </c>
       <c r="D60" t="s">
         <v>7</v>
       </c>
       <c r="E60" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B61" t="s">
         <v>6</v>
       </c>
       <c r="C61">
-        <v>0.3538406910978003</v>
+        <v>0.3531193143133521</v>
       </c>
       <c r="D61" t="s">
         <v>7</v>
       </c>
       <c r="E61" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B62" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C62">
-        <v>0.3580716268473747</v>
+        <v>0.3601202074000647</v>
       </c>
       <c r="D62" t="s">
         <v>7</v>
       </c>
       <c r="E62" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B63" t="s">
         <v>6</v>
       </c>
       <c r="C63">
-        <v>0.3669178613947036</v>
+        <v>0.3659968875225429</v>
       </c>
       <c r="D63" t="s">
         <v>7</v>
       </c>
       <c r="E63" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B64" t="s">
         <v>44</v>
       </c>
       <c r="C64">
-        <v>0.244563643964293</v>
+        <v>0.2440304167232492</v>
       </c>
       <c r="D64" t="s">
         <v>7</v>
       </c>
       <c r="E64" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B65" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C65">
-        <v>0.2927047656207103</v>
+        <v>0.2914454051695062</v>
       </c>
       <c r="D65" t="s">
         <v>7</v>
       </c>
       <c r="E65" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B66" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C66">
-        <v>0.3262550798218205</v>
+        <v>0.3260386117062041</v>
       </c>
       <c r="D66" t="s">
         <v>7</v>
       </c>
       <c r="E66" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B67" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C67">
-        <v>0.3199794067490914</v>
+        <v>0.3196585036978699</v>
       </c>
       <c r="D67" t="s">
         <v>7</v>
       </c>
       <c r="E67" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B68" t="s">
         <v>6</v>
       </c>
       <c r="C68">
-        <v>0.3017521905727124</v>
+        <v>0.3010796678811245</v>
       </c>
       <c r="D68" t="s">
         <v>7</v>
       </c>
       <c r="E68" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B69" t="s">
         <v>79</v>
       </c>
       <c r="C69">
-        <v>0.5856535643788792</v>
+        <v>0.592242385427759</v>
       </c>
       <c r="D69" t="s">
         <v>7</v>
       </c>
       <c r="E69" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B70" t="s">
         <v>79</v>
       </c>
       <c r="C70">
-        <v>0.5340226526388365</v>
+        <v>0.5472216243135631</v>
       </c>
       <c r="D70" t="s">
         <v>7</v>
       </c>
       <c r="E70" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B71" t="s">
         <v>6</v>
       </c>
       <c r="C71">
-        <v>0.4798087944649499</v>
+        <v>0.4793632230749952</v>
       </c>
       <c r="D71" t="s">
         <v>7</v>
       </c>
       <c r="E71" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B72" t="s">
         <v>6</v>
       </c>
       <c r="C72">
-        <v>0.3522959931195207</v>
+        <v>0.3515567252844493</v>
       </c>
       <c r="D72" t="s">
         <v>7</v>
       </c>
       <c r="E72" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B73" t="s">
         <v>6</v>
       </c>
       <c r="C73">
-        <v>0.4940470538723826</v>
+        <v>0.4942196691013788</v>
       </c>
       <c r="D73" t="s">
         <v>7</v>
       </c>
       <c r="E73" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B74" t="s">
         <v>6</v>
       </c>
       <c r="C74">
-        <v>0.4878993549571313</v>
+        <v>0.488527375412953</v>
       </c>
       <c r="D74" t="s">
         <v>7</v>
       </c>
       <c r="E74" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B75" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C75">
-        <v>0.2918148427745568</v>
+        <v>0.2888769563270372</v>
       </c>
       <c r="D75" t="s">
         <v>7</v>
       </c>
       <c r="E75" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B76" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C76">
-        <v>0.3343762850671849</v>
+        <v>0.3401010219475959</v>
       </c>
       <c r="D76" t="s">
         <v>7</v>
       </c>
       <c r="E76" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B77" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C77">
-        <v>0.3211176563077832</v>
+        <v>0.3183818513017188</v>
       </c>
       <c r="D77" t="s">
         <v>7</v>
       </c>
       <c r="E77" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B78" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C78">
-        <v>0.3920953723476018</v>
+        <v>0.3909068635244394</v>
       </c>
       <c r="D78" t="s">
         <v>7</v>
       </c>
       <c r="E78" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B79" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C79">
-        <v>0.2644905202227378</v>
+        <v>0.2673669172652001</v>
       </c>
       <c r="D79" t="s">
         <v>7</v>
       </c>
       <c r="E79" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B80" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C80">
-        <v>0.3489743856385542</v>
+        <v>0.3488704272221892</v>
       </c>
       <c r="D80" t="s">
         <v>7</v>
       </c>
       <c r="E80" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B81" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C81">
-        <v>0.3072023117881678</v>
+        <v>0.3085121172764843</v>
       </c>
       <c r="D81" t="s">
         <v>7</v>
       </c>
       <c r="E81" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B82" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C82">
-        <v>0.3992218291298309</v>
+        <v>0.3946946287986125</v>
       </c>
       <c r="D82" t="s">
         <v>7</v>
       </c>
       <c r="E82" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B83" t="s">
         <v>6</v>
       </c>
       <c r="C83">
-        <v>0.3937670638114268</v>
+        <v>0.3909511475356264</v>
       </c>
       <c r="D83" t="s">
         <v>7</v>
       </c>
       <c r="E83" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B84" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C84">
-        <v>0.2828139269268086</v>
+        <v>0.2827431797427498</v>
       </c>
       <c r="D84" t="s">
         <v>7</v>
       </c>
       <c r="E84" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B85" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C85">
-        <v>0.2852297690375062</v>
+        <v>0.282353492940456</v>
       </c>
       <c r="D85" t="s">
         <v>7</v>
       </c>
       <c r="E85" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B86" t="s">
         <v>6</v>
       </c>
       <c r="C86">
-        <v>0.3087853078661073</v>
+        <v>0.3092468361227959</v>
       </c>
       <c r="D86" t="s">
         <v>7</v>
       </c>
       <c r="E86" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B87" t="s">
         <v>6</v>
       </c>
       <c r="C87">
-        <v>0.2854338202612723</v>
+        <v>0.2887933829440511</v>
       </c>
       <c r="D87" t="s">
         <v>7</v>
       </c>
       <c r="E87" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B88" t="s">
         <v>79</v>
       </c>
       <c r="C88">
-        <v>0.3579655242378153</v>
+        <v>0.3572980482293691</v>
       </c>
       <c r="D88" t="s">
         <v>7</v>
       </c>
       <c r="E88" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B89" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C89">
-        <v>0.2851348145837937</v>
+        <v>0.2853063001903903</v>
       </c>
       <c r="D89" t="s">
         <v>7</v>
       </c>
       <c r="E89" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B90" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C90">
-        <v>0.2414708121845883</v>
+        <v>0.2503949629421727</v>
       </c>
       <c r="D90" t="s">
         <v>7</v>
       </c>
       <c r="E90" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B91" t="s">
         <v>6</v>
       </c>
       <c r="C91">
-        <v>0.2677147755765437</v>
+        <v>0.2674755569801305</v>
       </c>
       <c r="D91" t="s">
         <v>7</v>
       </c>
       <c r="E91" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B92" t="s">
         <v>44</v>
       </c>
       <c r="C92">
-        <v>0.2935569889326046</v>
+        <v>0.2886228192125692</v>
       </c>
       <c r="D92" t="s">
         <v>7</v>
       </c>
       <c r="E92" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B93" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C93">
-        <v>0.3605932715725296</v>
+        <v>0.3635514600838029</v>
       </c>
       <c r="D93" t="s">
         <v>7</v>
       </c>
       <c r="E93" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B94" t="s">
         <v>6</v>
       </c>
       <c r="C94">
-        <v>0.2890442235928335</v>
+        <v>0.2893000941609085</v>
       </c>
       <c r="D94" t="s">
         <v>7</v>
       </c>
       <c r="E94" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B95" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C95">
-        <v>0.2987433387062989</v>
+        <v>0.2975123980601787</v>
       </c>
       <c r="D95" t="s">
         <v>7</v>
       </c>
       <c r="E95" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B96" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C96">
-        <v>0.3424552014367637</v>
+        <v>0.3436806451202627</v>
       </c>
       <c r="D96" t="s">
         <v>7</v>
       </c>
       <c r="E96" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B97" t="s">
         <v>44</v>
       </c>
       <c r="C97">
-        <v>0.3559794383509119</v>
+        <v>0.3533079324588341</v>
       </c>
       <c r="D97" t="s">
         <v>7</v>
       </c>
       <c r="E97" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B98" t="s">
         <v>44</v>
       </c>
       <c r="C98">
-        <v>0.3397030098115803</v>
+        <v>0.3376263769226049</v>
       </c>
       <c r="D98" t="s">
         <v>7</v>
       </c>
       <c r="E98" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B99" t="s">
         <v>6</v>
       </c>
       <c r="C99">
-        <v>0.4446185732289417</v>
+        <v>0.44536282016692</v>
       </c>
       <c r="D99" t="s">
         <v>7</v>
       </c>
       <c r="E99" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B100" t="s">
         <v>44</v>
       </c>
       <c r="C100">
-        <v>0.3974913495724717</v>
+        <v>0.3951486967508427</v>
       </c>
       <c r="D100" t="s">
         <v>7</v>
       </c>
       <c r="E100" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B101" t="s">
         <v>44</v>
       </c>
       <c r="C101">
-        <v>0.3931654372200831</v>
+        <v>0.3938214985985315</v>
       </c>
       <c r="D101" t="s">
         <v>7</v>
       </c>
       <c r="E101" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B102" t="s">
         <v>6</v>
       </c>
       <c r="C102">
-        <v>0.4564197053321269</v>
+        <v>0.4550237420798823</v>
       </c>
       <c r="D102" t="s">
         <v>7</v>
       </c>
       <c r="E102" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B103" t="s">
         <v>6</v>
       </c>
       <c r="C103">
-        <v>0.3537297811005229</v>
+        <v>0.3551471138925335</v>
       </c>
       <c r="D103" t="s">
         <v>7</v>
       </c>
       <c r="E103" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B104" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C104">
-        <v>0.3808023629354426</v>
+        <v>0.3812464301244701</v>
       </c>
       <c r="D104" t="s">
         <v>7</v>
       </c>
       <c r="E104" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B105" t="s">
         <v>44</v>
       </c>
       <c r="C105">
-        <v>0.3290008695030662</v>
+        <v>0.3291430770208296</v>
       </c>
       <c r="D105" t="s">
         <v>7</v>
       </c>
       <c r="E105" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B106" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C106">
-        <v>0.3920809649314536</v>
+        <v>0.3940622702626701</v>
       </c>
       <c r="D106" t="s">
         <v>7</v>
       </c>
       <c r="E106" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B107" t="s">
         <v>44</v>
       </c>
       <c r="C107">
-        <v>0.327713517694682</v>
+        <v>0.3270945203524462</v>
       </c>
       <c r="D107" t="s">
         <v>7</v>
       </c>
       <c r="E107" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B108" t="s">
         <v>6</v>
       </c>
       <c r="C108">
-        <v>0.3864761824247066</v>
+        <v>0.3867254908843029</v>
       </c>
       <c r="D108" t="s">
         <v>7</v>
       </c>
       <c r="E108" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B109" t="s">
-        <v>15</v>
+        <v>126</v>
       </c>
       <c r="C109">
-        <v>0.2833898954005833</v>
+        <v>1</v>
       </c>
       <c r="D109" t="s">
         <v>7</v>
       </c>
       <c r="E109" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B110" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C110">
-        <v>0.2950948793362219</v>
+        <v>0.2972845950584908</v>
       </c>
       <c r="D110" t="s">
         <v>7</v>
       </c>
       <c r="E110" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B111" t="s">
         <v>6</v>
       </c>
       <c r="C111">
-        <v>0.4769129103255478</v>
+        <v>0.4771999738610122</v>
       </c>
       <c r="D111" t="s">
         <v>7</v>
       </c>
       <c r="E111" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B112" t="s">
         <v>6</v>
       </c>
       <c r="C112">
-        <v>0.3729929164405232</v>
+        <v>0.3729906675764873</v>
       </c>
       <c r="D112" t="s">
         <v>7</v>
       </c>
       <c r="E112" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B113" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C113">
-        <v>0.5605255387877255</v>
+        <v>0.555731945305225</v>
       </c>
       <c r="D113" t="s">
         <v>7</v>
       </c>
       <c r="E113" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B114" t="s">
         <v>6</v>
       </c>
       <c r="C114">
-        <v>0.6667298804091594</v>
+        <v>0.6659667778348437</v>
       </c>
       <c r="D114" t="s">
         <v>7</v>
       </c>
       <c r="E114" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B115" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C115">
-        <v>0.2784920479365197</v>
+        <v>0.2768347821194295</v>
       </c>
       <c r="D115" t="s">
         <v>7</v>
       </c>
       <c r="E115" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B116" t="s">
         <v>6</v>
       </c>
       <c r="C116">
-        <v>0.4024760881519272</v>
+        <v>0.3997881680543519</v>
       </c>
       <c r="D116" t="s">
         <v>7</v>
       </c>
       <c r="E116" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B117" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C117">
-        <v>0.2989845178222044</v>
+        <v>0.2962397305644639</v>
       </c>
       <c r="D117" t="s">
         <v>7</v>
       </c>
       <c r="E117" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B118" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C118">
-        <v>0.3373238006862117</v>
+        <v>0.3374449845105694</v>
       </c>
       <c r="D118" t="s">
         <v>7</v>
       </c>
       <c r="E118" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B119" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C119">
-        <v>0.3298929132259004</v>
+        <v>0.3352720028620672</v>
       </c>
       <c r="D119" t="s">
         <v>7</v>
       </c>
       <c r="E119" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B120" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C120">
-        <v>0.3487693206920428</v>
+        <v>0.355579565356543</v>
       </c>
       <c r="D120" t="s">
         <v>7</v>
       </c>
       <c r="E120" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B121" t="s">
-        <v>6</v>
+        <v>126</v>
       </c>
       <c r="C121">
-        <v>0.2574566673569203</v>
+        <v>0.3770199368628961</v>
       </c>
       <c r="D121" t="s">
         <v>7</v>
       </c>
       <c r="E121" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B122" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C122">
-        <v>0.2862082104888966</v>
+        <v>0.2857844437383169</v>
       </c>
       <c r="D122" t="s">
         <v>7</v>
       </c>
       <c r="E122" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B123" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C123">
-        <v>0.2704235690058107</v>
+        <v>0.2694823458263761</v>
       </c>
       <c r="D123" t="s">
         <v>7</v>
       </c>
       <c r="E123" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B124" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C124">
-        <v>0.4140585287426123</v>
+        <v>0.4123265126925549</v>
       </c>
       <c r="D124" t="s">
         <v>7</v>
       </c>
       <c r="E124" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B125" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C125">
-        <v>0.2821263473012712</v>
+        <v>0.2828872938194631</v>
       </c>
       <c r="D125" t="s">
         <v>7</v>
       </c>
       <c r="E125" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B126" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C126">
-        <v>0.3497165390554952</v>
+        <v>0.3532470731822582</v>
       </c>
       <c r="D126" t="s">
         <v>7</v>
       </c>
       <c r="E126" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B127" t="s">
         <v>6</v>
       </c>
       <c r="C127">
-        <v>0.4809359448377936</v>
+        <v>0.4870683297259988</v>
       </c>
       <c r="D127" t="s">
         <v>7</v>
       </c>
       <c r="E127" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B128" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C128">
-        <v>0.4435911329715011</v>
+        <v>0.4491606494833314</v>
       </c>
       <c r="D128" t="s">
         <v>7</v>
       </c>
       <c r="E128" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B129" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C129">
-        <v>0.3052144564718214</v>
+        <v>0.3066861899942552</v>
       </c>
       <c r="D129" t="s">
         <v>7</v>
       </c>
       <c r="E129" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B130" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C130">
-        <v>0.3869969270439754</v>
+        <v>0.3878220575552604</v>
       </c>
       <c r="D130" t="s">
         <v>7</v>
       </c>
       <c r="E130" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B131" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C131">
-        <v>0.2861871608886329</v>
+        <v>0.2880151062734182</v>
       </c>
       <c r="D131" t="s">
         <v>7</v>
       </c>
       <c r="E131" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B132" t="s">
         <v>6</v>
       </c>
       <c r="C132">
-        <v>0.3669835262558962</v>
+        <v>0.3672797590814171</v>
       </c>
       <c r="D132" t="s">
         <v>7</v>
       </c>
       <c r="E132" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B133" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C133">
-        <v>0.345282341657541</v>
+        <v>0.3406332207655233</v>
       </c>
       <c r="D133" t="s">
         <v>7</v>
       </c>
       <c r="E133" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B134" t="s">
         <v>6</v>
       </c>
       <c r="C134">
-        <v>0.355800140604979</v>
+        <v>0.3568433094036392</v>
       </c>
       <c r="D134" t="s">
         <v>7</v>
       </c>
       <c r="E134" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B135" t="s">
         <v>6</v>
       </c>
       <c r="C135">
-        <v>0.3123807731260665</v>
+        <v>0.3617114889705904</v>
       </c>
       <c r="D135" t="s">
         <v>7</v>
       </c>
       <c r="E135" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B136" t="s">
         <v>44</v>
       </c>
       <c r="C136">
-        <v>0.334364329807991</v>
+        <v>0.3341721369091715</v>
       </c>
       <c r="D136" t="s">
         <v>7</v>
       </c>
       <c r="E136" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B137" t="s">
         <v>6</v>
       </c>
       <c r="C137">
-        <v>0.3516396430065696</v>
+        <v>0.3511598470383787</v>
       </c>
       <c r="D137" t="s">
         <v>7</v>
       </c>
       <c r="E137" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B138" t="s">
         <v>6</v>
       </c>
       <c r="C138">
-        <v>0.308171797220926</v>
+        <v>0.3088599172841971</v>
       </c>
       <c r="D138" t="s">
         <v>7</v>
       </c>
       <c r="E138" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B139" t="s">
         <v>6</v>
       </c>
       <c r="C139">
-        <v>0.3672245053951412</v>
+        <v>0.3644054610151549</v>
       </c>
       <c r="D139" t="s">
         <v>7</v>
       </c>
       <c r="E139" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B140" t="s">
         <v>44</v>
       </c>
       <c r="C140">
-        <v>0.3968040388972082</v>
+        <v>0.3955092117466866</v>
       </c>
       <c r="D140" t="s">
         <v>7</v>
       </c>
       <c r="E140" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B141" t="s">
         <v>6</v>
       </c>
       <c r="C141">
-        <v>0.3095184538172543</v>
+        <v>0.3081976025038098</v>
       </c>
       <c r="D141" t="s">
         <v>7</v>
       </c>
       <c r="E141" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B142" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C142">
-        <v>0.3754337997479625</v>
+        <v>0.3717730305632392</v>
       </c>
       <c r="D142" t="s">
         <v>7</v>
       </c>
       <c r="E142" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B143" t="s">
         <v>6</v>
       </c>
       <c r="C143">
-        <v>0.3400972135387714</v>
+        <v>0.3444338121866022</v>
       </c>
       <c r="D143" t="s">
         <v>7</v>
       </c>
       <c r="E143" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B144" t="s">
         <v>6</v>
       </c>
       <c r="C144">
-        <v>0.6055543324596649</v>
+        <v>0.6092107871860075</v>
       </c>
       <c r="D144" t="s">
         <v>7</v>
       </c>
       <c r="E144" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B145" t="s">
         <v>6</v>
       </c>
       <c r="C145">
-        <v>0.2808261347713745</v>
+        <v>0.2833765684637191</v>
       </c>
       <c r="D145" t="s">
         <v>7</v>
       </c>
       <c r="E145" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B146" t="s">
         <v>6</v>
       </c>
       <c r="C146">
-        <v>0.3962566533995951</v>
+        <v>0.3985513110492952</v>
       </c>
       <c r="D146" t="s">
         <v>7</v>
       </c>
       <c r="E146" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B147" t="s">
         <v>6</v>
       </c>
       <c r="C147">
-        <v>0.4371991555069888</v>
+        <v>0.435307034407421</v>
       </c>
       <c r="D147" t="s">
         <v>7</v>
       </c>
       <c r="E147" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B148" t="s">
         <v>6</v>
       </c>
       <c r="C148">
-        <v>0.2890593589493095</v>
+        <v>0.2869961213560333</v>
       </c>
       <c r="D148" t="s">
         <v>7</v>
       </c>
       <c r="E148" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B149" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C149">
-        <v>0.3842961468522753</v>
+        <v>0.3870588230311317</v>
       </c>
       <c r="D149" t="s">
         <v>7</v>
       </c>
       <c r="E149" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B150" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C150">
-        <v>0.3397731911661288</v>
+        <v>0.340962439697909</v>
       </c>
       <c r="D150" t="s">
         <v>7</v>
       </c>
       <c r="E150" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="151" spans="1:5">
       <c r="A151" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B151" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C151">
-        <v>0.2653244764275514</v>
+        <v>0.2646327562853072</v>
       </c>
       <c r="D151" t="s">
         <v>7</v>
       </c>
       <c r="E151" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="152" spans="1:5">
       <c r="A152" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B152" t="s">
         <v>6</v>
       </c>
       <c r="C152">
-        <v>0.6755626876565314</v>
+        <v>0.6690191424990155</v>
       </c>
       <c r="D152" t="s">
         <v>7</v>
       </c>
       <c r="E152" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="153" spans="1:5">
       <c r="A153" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B153" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C153">
-        <v>0.3228764100506917</v>
+        <v>0.3210822240139956</v>
       </c>
       <c r="D153" t="s">
         <v>7</v>
       </c>
       <c r="E153" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="154" spans="1:5">
       <c r="A154" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B154" t="s">
         <v>44</v>
       </c>
       <c r="C154">
-        <v>0.3387535145651005</v>
+        <v>0.3387848585393599</v>
       </c>
       <c r="D154" t="s">
         <v>7</v>
       </c>
       <c r="E154" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="155" spans="1:5">
       <c r="A155" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B155" t="s">
         <v>6</v>
       </c>
       <c r="C155">
-        <v>0.2809421149956332</v>
+        <v>0.2840701677763426</v>
       </c>
       <c r="D155" t="s">
         <v>7</v>
       </c>
       <c r="E155" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="156" spans="1:5">
       <c r="A156" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B156" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C156">
-        <v>0.3331732564412097</v>
+        <v>0.3345106611457227</v>
       </c>
       <c r="D156" t="s">
         <v>7</v>
       </c>
       <c r="E156" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="157" spans="1:5">
       <c r="A157" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B157" t="s">
         <v>6</v>
       </c>
       <c r="C157">
-        <v>0.3685057239776969</v>
+        <v>0.3670776974715359</v>
       </c>
       <c r="D157" t="s">
         <v>7</v>
       </c>
       <c r="E157" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="158" spans="1:5">
       <c r="A158" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B158" t="s">
         <v>44</v>
       </c>
       <c r="C158">
-        <v>0.3679913768610194</v>
+        <v>0.3631099705891741</v>
       </c>
       <c r="D158" t="s">
         <v>7</v>
       </c>
       <c r="E158" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="159" spans="1:5">
       <c r="A159" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B159" t="s">
         <v>44</v>
       </c>
       <c r="C159">
-        <v>0.3691921790080616</v>
+        <v>0.3704918763257252</v>
       </c>
       <c r="D159" t="s">
         <v>7</v>
       </c>
       <c r="E159" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="160" spans="1:5">
       <c r="A160" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B160" t="s">
         <v>6</v>
       </c>
       <c r="C160">
-        <v>0.359561263663959</v>
+        <v>0.3594328573738069</v>
       </c>
       <c r="D160" t="s">
         <v>7</v>
       </c>
       <c r="E160" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="161" spans="1:5">
       <c r="A161" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B161" t="s">
         <v>6</v>
       </c>
       <c r="C161">
-        <v>0.393246599185926</v>
+        <v>0.3946661339567543</v>
       </c>
       <c r="D161" t="s">
         <v>7</v>
       </c>
       <c r="E161" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="162" spans="1:5">
       <c r="A162" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B162" t="s">
         <v>6</v>
       </c>
       <c r="C162">
-        <v>0.4666322446295757</v>
+        <v>0.4664992389012385</v>
       </c>
       <c r="D162" t="s">
         <v>7</v>
       </c>
       <c r="E162" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="163" spans="1:5">
       <c r="A163" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B163" t="s">
         <v>44</v>
       </c>
       <c r="C163">
-        <v>0.4318075042116055</v>
+        <v>0.430852800923761</v>
       </c>
       <c r="D163" t="s">
         <v>7</v>
       </c>
       <c r="E163" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="164" spans="1:5">
       <c r="A164" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B164" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C164">
-        <v>0.3514204192911553</v>
+        <v>0.3539578343370998</v>
       </c>
       <c r="D164" t="s">
         <v>7</v>
       </c>
       <c r="E164" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B165" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C165">
-        <v>0.3867842610373388</v>
+        <v>0.3821733234156131</v>
       </c>
       <c r="D165" t="s">
         <v>7</v>
       </c>
       <c r="E165" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="166" spans="1:5">
       <c r="A166" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B166" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="C166">
-        <v>0.3086873078598729</v>
+        <v>0.3072590194639022</v>
       </c>
       <c r="D166" t="s">
         <v>7</v>
       </c>
       <c r="E166" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B167" t="s">
         <v>6</v>
       </c>
       <c r="C167">
-        <v>0.3361521366704172</v>
+        <v>0.3387136525959499</v>
       </c>
       <c r="D167" t="s">
         <v>7</v>
       </c>
       <c r="E167" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="168" spans="1:5">
       <c r="A168" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B168" t="s">
         <v>6</v>
       </c>
       <c r="C168">
-        <v>0.5863252993968993</v>
+        <v>0.5853110533560778</v>
       </c>
       <c r="D168" t="s">
         <v>7</v>
       </c>
       <c r="E168" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="169" spans="1:5">
       <c r="A169" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B169" t="s">
         <v>44</v>
       </c>
       <c r="C169">
-        <v>0.3462259909316432</v>
+        <v>0.3421114553067905</v>
       </c>
       <c r="D169" t="s">
         <v>7</v>
       </c>
       <c r="E169" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="170" spans="1:5">
       <c r="A170" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B170" t="s">
         <v>6</v>
       </c>
       <c r="C170">
-        <v>0.3502261845457485</v>
+        <v>0.348549824087258</v>
       </c>
       <c r="D170" t="s">
         <v>7</v>
       </c>
       <c r="E170" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="171" spans="1:5">
       <c r="A171" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B171" t="s">
         <v>6</v>
       </c>
       <c r="C171">
-        <v>0.2503681598726717</v>
+        <v>0.2495387389544141</v>
       </c>
       <c r="D171" t="s">
         <v>7</v>
       </c>
       <c r="E171" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="172" spans="1:5">
       <c r="A172" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B172" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C172">
-        <v>0.4230784272125905</v>
+        <v>0.4277898523612557</v>
       </c>
       <c r="D172" t="s">
         <v>7</v>
       </c>
       <c r="E172" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="173" spans="1:5">
       <c r="A173" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B173" t="s">
         <v>44</v>
       </c>
       <c r="C173">
-        <v>0.3367016506150309</v>
+        <v>0.3372544272649038</v>
       </c>
       <c r="D173" t="s">
         <v>7</v>
       </c>
       <c r="E173" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="174" spans="1:5">
       <c r="A174" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B174" t="s">
         <v>6</v>
       </c>
       <c r="C174">
-        <v>0.304918596117592</v>
+        <v>0.3051511570226345</v>
       </c>
       <c r="D174" t="s">
         <v>7</v>
       </c>
       <c r="E174" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="175" spans="1:5">
       <c r="A175" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B175" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C175">
-        <v>0.2929417472252672</v>
+        <v>0.2909833372413856</v>
       </c>
       <c r="D175" t="s">
         <v>7</v>
       </c>
       <c r="E175" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="176" spans="1:5">
       <c r="A176" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B176" t="s">
         <v>6</v>
       </c>
       <c r="C176">
-        <v>0.3836672212571317</v>
+        <v>0.3823071449296032</v>
       </c>
       <c r="D176" t="s">
         <v>7</v>
       </c>
       <c r="E176" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="177" spans="1:5">
       <c r="A177" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B177" t="s">
         <v>6</v>
       </c>
       <c r="C177">
-        <v>0.5058048517553883</v>
+        <v>0.5058243918594832</v>
       </c>
       <c r="D177" t="s">
         <v>7</v>
       </c>
       <c r="E177" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="178" spans="1:5">
       <c r="A178" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B178" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C178">
-        <v>0.4145541336668475</v>
+        <v>0.4162481060384284</v>
       </c>
       <c r="D178" t="s">
         <v>7</v>
       </c>
       <c r="E178" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="179" spans="1:5">
       <c r="A179" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B179" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C179">
-        <v>0.2955419886526482</v>
+        <v>0.2975867169484162</v>
       </c>
       <c r="D179" t="s">
         <v>7</v>
       </c>
       <c r="E179" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="180" spans="1:5">
       <c r="A180" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B180" t="s">
         <v>44</v>
       </c>
       <c r="C180">
-        <v>0.3439909756407642</v>
+        <v>0.3424692034297692</v>
       </c>
       <c r="D180" t="s">
         <v>7</v>
       </c>
       <c r="E180" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="181" spans="1:5">
       <c r="A181" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B181" t="s">
         <v>6</v>
       </c>
       <c r="C181">
-        <v>0.3249581407628889</v>
+        <v>0.3216413627153308</v>
       </c>
       <c r="D181" t="s">
         <v>7</v>
       </c>
       <c r="E181" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="182" spans="1:5">
       <c r="A182" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B182" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C182">
-        <v>0.2741894557648799</v>
+        <v>0.2775288439984262</v>
       </c>
       <c r="D182" t="s">
         <v>7</v>
       </c>
       <c r="E182" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="183" spans="1:5">
       <c r="A183" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B183" t="s">
         <v>6</v>
       </c>
       <c r="C183">
-        <v>0.2836607553140028</v>
+        <v>0.2844407827723575</v>
       </c>
       <c r="D183" t="s">
         <v>7</v>
       </c>
       <c r="E183" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="184" spans="1:5">
       <c r="A184" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B184" t="s">
         <v>6</v>
       </c>
       <c r="C184">
-        <v>0.3329544459931558</v>
+        <v>0.3339360623652623</v>
       </c>
       <c r="D184" t="s">
         <v>7</v>
       </c>
       <c r="E184" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="185" spans="1:5">
       <c r="A185" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B185" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C185">
-        <v>0.339052071585564</v>
+        <v>0.340623867099085</v>
       </c>
       <c r="D185" t="s">
         <v>7</v>
       </c>
       <c r="E185" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="186" spans="1:5">
       <c r="A186" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B186" t="s">
         <v>44</v>
       </c>
       <c r="C186">
-        <v>0.3910043621192867</v>
+        <v>0.388904885438917</v>
       </c>
       <c r="D186" t="s">
         <v>7</v>
       </c>
       <c r="E186" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="187" spans="1:5">
       <c r="A187" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B187" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C187">
-        <v>0.2332321629007149</v>
+        <v>0.2366649143074912</v>
       </c>
       <c r="D187" t="s">
         <v>7</v>
       </c>
       <c r="E187" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="188" spans="1:5">
       <c r="A188" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B188" t="s">
         <v>44</v>
       </c>
       <c r="C188">
-        <v>0.4093423739111878</v>
+        <v>0.3974582634957153</v>
       </c>
       <c r="D188" t="s">
         <v>7</v>
       </c>
       <c r="E188" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="189" spans="1:5">
       <c r="A189" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B189" t="s">
         <v>6</v>
       </c>
       <c r="C189">
-        <v>0.3359072911395092</v>
+        <v>0.3356951634512588</v>
       </c>
       <c r="D189" t="s">
         <v>7</v>
       </c>
       <c r="E189" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="190" spans="1:5">
       <c r="A190" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B190" t="s">
-        <v>79</v>
+        <v>6</v>
       </c>
       <c r="C190">
-        <v>0.2744297490322425</v>
+        <v>0.2758487457971009</v>
       </c>
       <c r="D190" t="s">
         <v>7</v>
       </c>
       <c r="E190" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="191" spans="1:5">
       <c r="A191" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B191" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C191">
-        <v>0.3020907210945367</v>
+        <v>0.3015902439348378</v>
       </c>
       <c r="D191" t="s">
         <v>7</v>
       </c>
       <c r="E191" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="192" spans="1:5">
       <c r="A192" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B192" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C192">
-        <v>0.4115701728763535</v>
+        <v>0.4076350711005853</v>
       </c>
       <c r="D192" t="s">
         <v>7</v>
       </c>
       <c r="E192" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="193" spans="1:5">
       <c r="A193" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B193" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C193">
-        <v>0.4428401199135293</v>
+        <v>0.4515262743056659</v>
       </c>
       <c r="D193" t="s">
         <v>7</v>
       </c>
       <c r="E193" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="194" spans="1:5">
       <c r="A194" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B194" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C194">
-        <v>0.3865003143033541</v>
+        <v>0.3886890369964716</v>
       </c>
       <c r="D194" t="s">
         <v>7</v>
       </c>
       <c r="E194" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="195" spans="1:5">
       <c r="A195" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B195" t="s">
-        <v>398</v>
+        <v>126</v>
       </c>
       <c r="C195">
-        <v>0.4549443284067027</v>
+        <v>0.4589919238476373</v>
       </c>
       <c r="D195" t="s">
         <v>7</v>
@@ -7658,7 +7658,7 @@
         <v>6</v>
       </c>
       <c r="C196">
-        <v>0.3443292621696988</v>
+        <v>0.3477166912375113</v>
       </c>
       <c r="D196" t="s">
         <v>7</v>
@@ -7672,10 +7672,10 @@
         <v>402</v>
       </c>
       <c r="B197" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C197">
-        <v>0.2930588409272735</v>
+        <v>0.2954452219141319</v>
       </c>
       <c r="D197" t="s">
         <v>7</v>
@@ -7692,7 +7692,7 @@
         <v>6</v>
       </c>
       <c r="C198">
-        <v>0.5344580662610225</v>
+        <v>0.5355735883690182</v>
       </c>
       <c r="D198" t="s">
         <v>7</v>
@@ -7709,7 +7709,7 @@
         <v>6</v>
       </c>
       <c r="C199">
-        <v>0.629113066002929</v>
+        <v>0.6287542918572999</v>
       </c>
       <c r="D199" t="s">
         <v>7</v>
@@ -7723,10 +7723,10 @@
         <v>408</v>
       </c>
       <c r="B200" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C200">
-        <v>0.3195683816803292</v>
+        <v>0.3251134354981137</v>
       </c>
       <c r="D200" t="s">
         <v>7</v>
@@ -7740,10 +7740,10 @@
         <v>410</v>
       </c>
       <c r="B201" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C201">
-        <v>0.3192857967151713</v>
+        <v>0.3189914791871748</v>
       </c>
       <c r="D201" t="s">
         <v>7</v>
@@ -7757,10 +7757,10 @@
         <v>412</v>
       </c>
       <c r="B202" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C202">
-        <v>0.3291643078941876</v>
+        <v>0.3300963852963707</v>
       </c>
       <c r="D202" t="s">
         <v>7</v>
@@ -7777,7 +7777,7 @@
         <v>6</v>
       </c>
       <c r="C203">
-        <v>0.5177961370822138</v>
+        <v>0.5184238743487551</v>
       </c>
       <c r="D203" t="s">
         <v>7</v>
@@ -7794,7 +7794,7 @@
         <v>6</v>
       </c>
       <c r="C204">
-        <v>0.4561112205063635</v>
+        <v>0.4617220182580419</v>
       </c>
       <c r="D204" t="s">
         <v>7</v>
@@ -7808,10 +7808,10 @@
         <v>418</v>
       </c>
       <c r="B205" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C205">
-        <v>0.4079175475677814</v>
+        <v>0.4091656312840194</v>
       </c>
       <c r="D205" t="s">
         <v>7</v>
@@ -7825,10 +7825,10 @@
         <v>420</v>
       </c>
       <c r="B206" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C206">
-        <v>0.3434163154931731</v>
+        <v>0.3466370229237181</v>
       </c>
       <c r="D206" t="s">
         <v>7</v>
@@ -7845,7 +7845,7 @@
         <v>44</v>
       </c>
       <c r="C207">
-        <v>0.5436441484152249</v>
+        <v>0.5461969990871027</v>
       </c>
       <c r="D207" t="s">
         <v>7</v>
@@ -7862,7 +7862,7 @@
         <v>44</v>
       </c>
       <c r="C208">
-        <v>0.3690633107991113</v>
+        <v>0.3659307755746065</v>
       </c>
       <c r="D208" t="s">
         <v>7</v>
@@ -7876,10 +7876,10 @@
         <v>426</v>
       </c>
       <c r="B209" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C209">
-        <v>0.5106720427606812</v>
+        <v>0.510842235462775</v>
       </c>
       <c r="D209" t="s">
         <v>7</v>
@@ -7896,7 +7896,7 @@
         <v>6</v>
       </c>
       <c r="C210">
-        <v>0.415225678600413</v>
+        <v>0.4128309149062205</v>
       </c>
       <c r="D210" t="s">
         <v>7</v>
@@ -7910,10 +7910,10 @@
         <v>430</v>
       </c>
       <c r="B211" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C211">
-        <v>0.4812546121620567</v>
+        <v>0.4839220255328627</v>
       </c>
       <c r="D211" t="s">
         <v>7</v>
@@ -7927,10 +7927,10 @@
         <v>432</v>
       </c>
       <c r="B212" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C212">
-        <v>0.2740411196793159</v>
+        <v>0.2734059637147231</v>
       </c>
       <c r="D212" t="s">
         <v>7</v>
@@ -7944,10 +7944,10 @@
         <v>434</v>
       </c>
       <c r="B213" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C213">
-        <v>0.2987699568264576</v>
+        <v>0.2957071347127823</v>
       </c>
       <c r="D213" t="s">
         <v>7</v>
@@ -7961,10 +7961,10 @@
         <v>436</v>
       </c>
       <c r="B214" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C214">
-        <v>0.3907595033680481</v>
+        <v>0.3944261136750927</v>
       </c>
       <c r="D214" t="s">
         <v>7</v>
@@ -7978,10 +7978,10 @@
         <v>438</v>
       </c>
       <c r="B215" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C215">
-        <v>0.5077798010650122</v>
+        <v>0.5050764304076868</v>
       </c>
       <c r="D215" t="s">
         <v>7</v>
@@ -7995,10 +7995,10 @@
         <v>440</v>
       </c>
       <c r="B216" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C216">
-        <v>0.3194781254836031</v>
+        <v>0.3195768378055955</v>
       </c>
       <c r="D216" t="s">
         <v>7</v>
@@ -8012,10 +8012,10 @@
         <v>442</v>
       </c>
       <c r="B217" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C217">
-        <v>0.2825607979693605</v>
+        <v>0.2823549538351468</v>
       </c>
       <c r="D217" t="s">
         <v>7</v>
@@ -8029,10 +8029,10 @@
         <v>444</v>
       </c>
       <c r="B218" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C218">
-        <v>0.3504032277776228</v>
+        <v>0.3558318811932435</v>
       </c>
       <c r="D218" t="s">
         <v>7</v>
@@ -8049,7 +8049,7 @@
         <v>44</v>
       </c>
       <c r="C219">
-        <v>0.4750194776397262</v>
+        <v>0.4758415570361427</v>
       </c>
       <c r="D219" t="s">
         <v>7</v>
@@ -8063,10 +8063,10 @@
         <v>448</v>
       </c>
       <c r="B220" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C220">
-        <v>0.2901533228937584</v>
+        <v>0.2889032533528874</v>
       </c>
       <c r="D220" t="s">
         <v>7</v>
@@ -8080,10 +8080,10 @@
         <v>450</v>
       </c>
       <c r="B221" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C221">
-        <v>0.3800488520372624</v>
+        <v>0.3826628209683341</v>
       </c>
       <c r="D221" t="s">
         <v>7</v>
@@ -8097,10 +8097,10 @@
         <v>452</v>
       </c>
       <c r="B222" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C222">
-        <v>0.301306258600507</v>
+        <v>0.3053449840447459</v>
       </c>
       <c r="D222" t="s">
         <v>7</v>
@@ -8114,10 +8114,10 @@
         <v>454</v>
       </c>
       <c r="B223" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C223">
-        <v>0.4673671634957003</v>
+        <v>0.4696148379494077</v>
       </c>
       <c r="D223" t="s">
         <v>7</v>
@@ -8131,10 +8131,10 @@
         <v>456</v>
       </c>
       <c r="B224" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C224">
-        <v>0.3001242015268992</v>
+        <v>0.2950372649806424</v>
       </c>
       <c r="D224" t="s">
         <v>7</v>
@@ -8148,10 +8148,10 @@
         <v>458</v>
       </c>
       <c r="B225" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C225">
-        <v>0.3785504608721839</v>
+        <v>0.373692714158223</v>
       </c>
       <c r="D225" t="s">
         <v>7</v>
@@ -8168,7 +8168,7 @@
         <v>6</v>
       </c>
       <c r="C226">
-        <v>0.4768849252751304</v>
+        <v>0.477449290351352</v>
       </c>
       <c r="D226" t="s">
         <v>7</v>
@@ -8182,10 +8182,10 @@
         <v>462</v>
       </c>
       <c r="B227" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C227">
-        <v>0.3006433116273651</v>
+        <v>0.3018248370107985</v>
       </c>
       <c r="D227" t="s">
         <v>7</v>
@@ -8202,7 +8202,7 @@
         <v>6</v>
       </c>
       <c r="C228">
-        <v>0.4912376382546738</v>
+        <v>0.4923041299285724</v>
       </c>
       <c r="D228" t="s">
         <v>7</v>
@@ -8219,7 +8219,7 @@
         <v>6</v>
       </c>
       <c r="C229">
-        <v>0.5669713358912335</v>
+        <v>0.5665509611286522</v>
       </c>
       <c r="D229" t="s">
         <v>7</v>
@@ -8236,7 +8236,7 @@
         <v>44</v>
       </c>
       <c r="C230">
-        <v>0.3499431062482737</v>
+        <v>0.3528321139960491</v>
       </c>
       <c r="D230" t="s">
         <v>7</v>
@@ -8253,7 +8253,7 @@
         <v>6</v>
       </c>
       <c r="C231">
-        <v>0.3086904630362478</v>
+        <v>0.3101063147744256</v>
       </c>
       <c r="D231" t="s">
         <v>7</v>
@@ -8270,7 +8270,7 @@
         <v>6</v>
       </c>
       <c r="C232">
-        <v>0.5887437076897095</v>
+        <v>0.5938350308911474</v>
       </c>
       <c r="D232" t="s">
         <v>7</v>
@@ -8287,7 +8287,7 @@
         <v>44</v>
       </c>
       <c r="C233">
-        <v>0.3954667969377052</v>
+        <v>0.3954303818976487</v>
       </c>
       <c r="D233" t="s">
         <v>7</v>
@@ -8304,7 +8304,7 @@
         <v>6</v>
       </c>
       <c r="C234">
-        <v>0.4046821404113183</v>
+        <v>0.4065859799851749</v>
       </c>
       <c r="D234" t="s">
         <v>7</v>
@@ -8321,7 +8321,7 @@
         <v>6</v>
       </c>
       <c r="C235">
-        <v>0.4955811611249114</v>
+        <v>0.4941107002461808</v>
       </c>
       <c r="D235" t="s">
         <v>7</v>
@@ -8338,7 +8338,7 @@
         <v>6</v>
       </c>
       <c r="C236">
-        <v>0.2777203185596439</v>
+        <v>0.2781950929071519</v>
       </c>
       <c r="D236" t="s">
         <v>7</v>
@@ -8355,7 +8355,7 @@
         <v>6</v>
       </c>
       <c r="C237">
-        <v>0.3044926828850151</v>
+        <v>0.3049216612924652</v>
       </c>
       <c r="D237" t="s">
         <v>7</v>
@@ -8372,7 +8372,7 @@
         <v>6</v>
       </c>
       <c r="C238">
-        <v>0.3400442298129109</v>
+        <v>0.3477416144168453</v>
       </c>
       <c r="D238" t="s">
         <v>7</v>
@@ -8389,7 +8389,7 @@
         <v>6</v>
       </c>
       <c r="C239">
-        <v>0.4296521223182578</v>
+        <v>0.4272691027460807</v>
       </c>
       <c r="D239" t="s">
         <v>7</v>
@@ -8403,10 +8403,10 @@
         <v>488</v>
       </c>
       <c r="B240" t="s">
-        <v>398</v>
+        <v>126</v>
       </c>
       <c r="C240">
-        <v>0.4170226172489271</v>
+        <v>0.4347607488907044</v>
       </c>
       <c r="D240" t="s">
         <v>7</v>
@@ -8420,10 +8420,10 @@
         <v>490</v>
       </c>
       <c r="B241" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C241">
-        <v>0.2305993089710209</v>
+        <v>0.2334882528914666</v>
       </c>
       <c r="D241" t="s">
         <v>7</v>
@@ -8437,10 +8437,10 @@
         <v>492</v>
       </c>
       <c r="B242" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C242">
-        <v>0.3115119537994323</v>
+        <v>0.3128888290613531</v>
       </c>
       <c r="D242" t="s">
         <v>7</v>
@@ -8454,10 +8454,10 @@
         <v>494</v>
       </c>
       <c r="B243" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C243">
-        <v>0.5219048980197921</v>
+        <v>0.5218553490607608</v>
       </c>
       <c r="D243" t="s">
         <v>7</v>
@@ -8471,10 +8471,10 @@
         <v>496</v>
       </c>
       <c r="B244" t="s">
-        <v>398</v>
+        <v>126</v>
       </c>
       <c r="C244">
-        <v>0.4046486739417333</v>
+        <v>0.4448958175868111</v>
       </c>
       <c r="D244" t="s">
         <v>7</v>
@@ -8491,7 +8491,7 @@
         <v>6</v>
       </c>
       <c r="C245">
-        <v>0.6135414167870159</v>
+        <v>0.6154564953603902</v>
       </c>
       <c r="D245" t="s">
         <v>7</v>
@@ -8508,7 +8508,7 @@
         <v>6</v>
       </c>
       <c r="C246">
-        <v>0.4080557191398699</v>
+        <v>0.4084357694977033</v>
       </c>
       <c r="D246" t="s">
         <v>7</v>
@@ -8525,7 +8525,7 @@
         <v>6</v>
       </c>
       <c r="C247">
-        <v>0.401312405853469</v>
+        <v>0.401688163585029</v>
       </c>
       <c r="D247" t="s">
         <v>7</v>
@@ -8539,10 +8539,10 @@
         <v>504</v>
       </c>
       <c r="B248" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C248">
-        <v>0.3062065616491785</v>
+        <v>0.303738667513013</v>
       </c>
       <c r="D248" t="s">
         <v>7</v>
@@ -8559,7 +8559,7 @@
         <v>6</v>
       </c>
       <c r="C249">
-        <v>0.419536537697268</v>
+        <v>0.4206245291755838</v>
       </c>
       <c r="D249" t="s">
         <v>7</v>
@@ -8573,10 +8573,10 @@
         <v>508</v>
       </c>
       <c r="B250" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C250">
-        <v>0.2960347002073471</v>
+        <v>0.294753895305112</v>
       </c>
       <c r="D250" t="s">
         <v>7</v>
@@ -8593,7 +8593,7 @@
         <v>44</v>
       </c>
       <c r="C251">
-        <v>0.433314741065681</v>
+        <v>0.4901194882770973</v>
       </c>
       <c r="D251" t="s">
         <v>7</v>
@@ -8610,7 +8610,7 @@
         <v>6</v>
       </c>
       <c r="C252">
-        <v>0.3697803361875929</v>
+        <v>0.3700099594971057</v>
       </c>
       <c r="D252" t="s">
         <v>7</v>
@@ -8627,7 +8627,7 @@
         <v>6</v>
       </c>
       <c r="C253">
-        <v>0.3303125629506041</v>
+        <v>0.330546251343952</v>
       </c>
       <c r="D253" t="s">
         <v>7</v>
@@ -8644,7 +8644,7 @@
         <v>6</v>
       </c>
       <c r="C254">
-        <v>0.4680323988723611</v>
+        <v>0.4680618251149123</v>
       </c>
       <c r="D254" t="s">
         <v>7</v>
@@ -8658,10 +8658,10 @@
         <v>518</v>
       </c>
       <c r="B255" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C255">
-        <v>0.477889526365873</v>
+        <v>0.4778316099310007</v>
       </c>
       <c r="D255" t="s">
         <v>7</v>
@@ -8678,7 +8678,7 @@
         <v>6</v>
       </c>
       <c r="C256">
-        <v>0.5866366809190557</v>
+        <v>0.5869314304506835</v>
       </c>
       <c r="D256" t="s">
         <v>7</v>
@@ -8695,7 +8695,7 @@
         <v>6</v>
       </c>
       <c r="C257">
-        <v>0.3848416641249937</v>
+        <v>0.3845433365935728</v>
       </c>
       <c r="D257" t="s">
         <v>7</v>
@@ -8712,7 +8712,7 @@
         <v>6</v>
       </c>
       <c r="C258">
-        <v>0.4830052026743175</v>
+        <v>0.4857713555955565</v>
       </c>
       <c r="D258" t="s">
         <v>7</v>
@@ -8726,10 +8726,10 @@
         <v>526</v>
       </c>
       <c r="B259" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C259">
-        <v>0.3007542253781241</v>
+        <v>0.3014763423330936</v>
       </c>
       <c r="D259" t="s">
         <v>7</v>
@@ -8746,7 +8746,7 @@
         <v>6</v>
       </c>
       <c r="C260">
-        <v>0.4166448640457767</v>
+        <v>0.4154480628594182</v>
       </c>
       <c r="D260" t="s">
         <v>7</v>
@@ -8763,7 +8763,7 @@
         <v>6</v>
       </c>
       <c r="C261">
-        <v>0.4682065749420462</v>
+        <v>0.4664717649825334</v>
       </c>
       <c r="D261" t="s">
         <v>7</v>
@@ -8780,7 +8780,7 @@
         <v>6</v>
       </c>
       <c r="C262">
-        <v>0.4150442831294344</v>
+        <v>0.4143603629621579</v>
       </c>
       <c r="D262" t="s">
         <v>7</v>
@@ -8797,7 +8797,7 @@
         <v>6</v>
       </c>
       <c r="C263">
-        <v>0.4377757118902053</v>
+        <v>0.4375057259717712</v>
       </c>
       <c r="D263" t="s">
         <v>7</v>
@@ -8814,7 +8814,7 @@
         <v>6</v>
       </c>
       <c r="C264">
-        <v>0.4160383935771113</v>
+        <v>0.4153529789177671</v>
       </c>
       <c r="D264" t="s">
         <v>7</v>
@@ -8831,7 +8831,7 @@
         <v>6</v>
       </c>
       <c r="C265">
-        <v>0.3345888275510537</v>
+        <v>0.3287516391891646</v>
       </c>
       <c r="D265" t="s">
         <v>7</v>
@@ -8845,10 +8845,10 @@
         <v>540</v>
       </c>
       <c r="B266" t="s">
-        <v>398</v>
+        <v>6</v>
       </c>
       <c r="C266">
-        <v>0.3365319403334371</v>
+        <v>0.3628686972194654</v>
       </c>
       <c r="D266" t="s">
         <v>7</v>
@@ -8865,7 +8865,7 @@
         <v>6</v>
       </c>
       <c r="C267">
-        <v>0.247789531357906</v>
+        <v>0.2498743183649366</v>
       </c>
       <c r="D267" t="s">
         <v>7</v>
@@ -8882,7 +8882,7 @@
         <v>6</v>
       </c>
       <c r="C268">
-        <v>0.4179020363943559</v>
+        <v>0.4176244865813888</v>
       </c>
       <c r="D268" t="s">
         <v>7</v>
@@ -8899,7 +8899,7 @@
         <v>44</v>
       </c>
       <c r="C269">
-        <v>0.375574299916195</v>
+        <v>0.3717419941545167</v>
       </c>
       <c r="D269" t="s">
         <v>7</v>
@@ -8916,7 +8916,7 @@
         <v>6</v>
       </c>
       <c r="C270">
-        <v>0.520019534372709</v>
+        <v>0.5198557021059653</v>
       </c>
       <c r="D270" t="s">
         <v>7</v>
@@ -8933,7 +8933,7 @@
         <v>6</v>
       </c>
       <c r="C271">
-        <v>0.5491246911824519</v>
+        <v>0.5506138635607348</v>
       </c>
       <c r="D271" t="s">
         <v>7</v>
@@ -8950,7 +8950,7 @@
         <v>6</v>
       </c>
       <c r="C272">
-        <v>0.3468949489959254</v>
+        <v>0.3456008845730008</v>
       </c>
       <c r="D272" t="s">
         <v>7</v>
@@ -8967,7 +8967,7 @@
         <v>6</v>
       </c>
       <c r="C273">
-        <v>0.5054616836120924</v>
+        <v>0.5047872520486726</v>
       </c>
       <c r="D273" t="s">
         <v>7</v>
@@ -8981,10 +8981,10 @@
         <v>556</v>
       </c>
       <c r="B274" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C274">
-        <v>0.3598188358932274</v>
+        <v>0.3609825988105117</v>
       </c>
       <c r="D274" t="s">
         <v>7</v>
@@ -8998,10 +8998,10 @@
         <v>558</v>
       </c>
       <c r="B275" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C275">
-        <v>0.2443687701253149</v>
+        <v>0.2471938644485852</v>
       </c>
       <c r="D275" t="s">
         <v>7</v>
@@ -9018,7 +9018,7 @@
         <v>6</v>
       </c>
       <c r="C276">
-        <v>0.316327755570034</v>
+        <v>0.315276623299826</v>
       </c>
       <c r="D276" t="s">
         <v>7</v>
@@ -9035,7 +9035,7 @@
         <v>79</v>
       </c>
       <c r="C277">
-        <v>0.4282773759922051</v>
+        <v>0.4310931270753286</v>
       </c>
       <c r="D277" t="s">
         <v>7</v>
@@ -9052,7 +9052,7 @@
         <v>6</v>
       </c>
       <c r="C278">
-        <v>0.398598266889279</v>
+        <v>0.3982732736784659</v>
       </c>
       <c r="D278" t="s">
         <v>7</v>
@@ -9069,7 +9069,7 @@
         <v>6</v>
       </c>
       <c r="C279">
-        <v>0.5341468703342348</v>
+        <v>0.533584518793604</v>
       </c>
       <c r="D279" t="s">
         <v>7</v>
@@ -9086,7 +9086,7 @@
         <v>6</v>
       </c>
       <c r="C280">
-        <v>0.4701272082142793</v>
+        <v>0.4737056730530078</v>
       </c>
       <c r="D280" t="s">
         <v>7</v>
@@ -9103,7 +9103,7 @@
         <v>6</v>
       </c>
       <c r="C281">
-        <v>0.3870985325902513</v>
+        <v>0.3867319597409787</v>
       </c>
       <c r="D281" t="s">
         <v>7</v>
@@ -9117,10 +9117,10 @@
         <v>572</v>
       </c>
       <c r="B282" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C282">
-        <v>0.3846473436400294</v>
+        <v>0.385273914294723</v>
       </c>
       <c r="D282" t="s">
         <v>7</v>
@@ -9134,10 +9134,10 @@
         <v>574</v>
       </c>
       <c r="B283" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C283">
-        <v>0.35803083506319</v>
+        <v>0.3617437170941228</v>
       </c>
       <c r="D283" t="s">
         <v>7</v>
@@ -9154,7 +9154,7 @@
         <v>6</v>
       </c>
       <c r="C284">
-        <v>0.3223710029122165</v>
+        <v>0.3217035281941626</v>
       </c>
       <c r="D284" t="s">
         <v>7</v>
@@ -9168,10 +9168,10 @@
         <v>578</v>
       </c>
       <c r="B285" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C285">
-        <v>0.2454919078310039</v>
+        <v>0.2368714964975877</v>
       </c>
       <c r="D285" t="s">
         <v>7</v>
@@ -9188,7 +9188,7 @@
         <v>6</v>
       </c>
       <c r="C286">
-        <v>0.2891222769499245</v>
+        <v>0.2891015214108358</v>
       </c>
       <c r="D286" t="s">
         <v>7</v>
@@ -9205,7 +9205,7 @@
         <v>44</v>
       </c>
       <c r="C287">
-        <v>0.4828251243341666</v>
+        <v>0.4819933495265971</v>
       </c>
       <c r="D287" t="s">
         <v>7</v>
@@ -9222,7 +9222,7 @@
         <v>6</v>
       </c>
       <c r="C288">
-        <v>0.2552557059150746</v>
+        <v>0.2544269851430639</v>
       </c>
       <c r="D288" t="s">
         <v>7</v>
@@ -9239,7 +9239,7 @@
         <v>6</v>
       </c>
       <c r="C289">
-        <v>0.3437066760549945</v>
+        <v>0.344477059943197</v>
       </c>
       <c r="D289" t="s">
         <v>7</v>
@@ -9253,10 +9253,10 @@
         <v>588</v>
       </c>
       <c r="B290" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C290">
-        <v>0.3062045757964451</v>
+        <v>0.3068820765488964</v>
       </c>
       <c r="D290" t="s">
         <v>7</v>
@@ -9273,7 +9273,7 @@
         <v>6</v>
       </c>
       <c r="C291">
-        <v>0.4312123992135999</v>
+        <v>0.43454832795702</v>
       </c>
       <c r="D291" t="s">
         <v>7</v>
@@ -9290,7 +9290,7 @@
         <v>79</v>
       </c>
       <c r="C292">
-        <v>0.4864381058779144</v>
+        <v>0.4852450899255945</v>
       </c>
       <c r="D292" t="s">
         <v>7</v>
@@ -9307,7 +9307,7 @@
         <v>6</v>
       </c>
       <c r="C293">
-        <v>0.604916915168056</v>
+        <v>0.6065921239979619</v>
       </c>
       <c r="D293" t="s">
         <v>7</v>
@@ -9321,10 +9321,10 @@
         <v>596</v>
       </c>
       <c r="B294" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C294">
-        <v>0.4211652256419892</v>
+        <v>0.4249526031032193</v>
       </c>
       <c r="D294" t="s">
         <v>7</v>
@@ -9338,10 +9338,10 @@
         <v>598</v>
       </c>
       <c r="B295" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C295">
-        <v>0.3069009169411765</v>
+        <v>0.3062291185111508</v>
       </c>
       <c r="D295" t="s">
         <v>7</v>
@@ -9355,10 +9355,10 @@
         <v>600</v>
       </c>
       <c r="B296" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C296">
-        <v>0.3010460388156279</v>
+        <v>0.2995599492379087</v>
       </c>
       <c r="D296" t="s">
         <v>7</v>
@@ -9372,10 +9372,10 @@
         <v>602</v>
       </c>
       <c r="B297" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C297">
-        <v>0.4141629679932161</v>
+        <v>0.4120705429776052</v>
       </c>
       <c r="D297" t="s">
         <v>7</v>
@@ -9389,10 +9389,10 @@
         <v>604</v>
       </c>
       <c r="B298" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C298">
-        <v>0.358731656628555</v>
+        <v>0.3582941781481896</v>
       </c>
       <c r="D298" t="s">
         <v>7</v>
@@ -9409,7 +9409,7 @@
         <v>44</v>
       </c>
       <c r="C299">
-        <v>0.2835994131889271</v>
+        <v>0.2861549308586899</v>
       </c>
       <c r="D299" t="s">
         <v>7</v>
@@ -9423,10 +9423,10 @@
         <v>608</v>
       </c>
       <c r="B300" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C300">
-        <v>0.3216776475382147</v>
+        <v>0.3227362685329092</v>
       </c>
       <c r="D300" t="s">
         <v>7</v>
@@ -9443,7 +9443,7 @@
         <v>6</v>
       </c>
       <c r="C301">
-        <v>0.3443689246791146</v>
+        <v>0.3437267914930859</v>
       </c>
       <c r="D301" t="s">
         <v>7</v>
@@ -9460,7 +9460,7 @@
         <v>44</v>
       </c>
       <c r="C302">
-        <v>0.4670440621007423</v>
+        <v>0.4674832079199708</v>
       </c>
       <c r="D302" t="s">
         <v>7</v>
@@ -9474,10 +9474,10 @@
         <v>614</v>
       </c>
       <c r="B303" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C303">
-        <v>0.3059623768788805</v>
+        <v>0.3068253780039805</v>
       </c>
       <c r="D303" t="s">
         <v>7</v>
@@ -9491,10 +9491,10 @@
         <v>616</v>
       </c>
       <c r="B304" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C304">
-        <v>0.2843269335399105</v>
+        <v>0.2841211686297654</v>
       </c>
       <c r="D304" t="s">
         <v>7</v>
@@ -9511,7 +9511,7 @@
         <v>44</v>
       </c>
       <c r="C305">
-        <v>0.4009919178664613</v>
+        <v>0.3972044998980188</v>
       </c>
       <c r="D305" t="s">
         <v>7</v>
@@ -9525,10 +9525,10 @@
         <v>620</v>
       </c>
       <c r="B306" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C306">
-        <v>0.4840465553028163</v>
+        <v>0.4900783257037527</v>
       </c>
       <c r="D306" t="s">
         <v>7</v>
@@ -9545,7 +9545,7 @@
         <v>6</v>
       </c>
       <c r="C307">
-        <v>0.424547975696667</v>
+        <v>0.4290848121071581</v>
       </c>
       <c r="D307" t="s">
         <v>7</v>
@@ -9562,7 +9562,7 @@
         <v>6</v>
       </c>
       <c r="C308">
-        <v>0.3806296530873151</v>
+        <v>0.3812892264106097</v>
       </c>
       <c r="D308" t="s">
         <v>7</v>
@@ -9579,7 +9579,7 @@
         <v>6</v>
       </c>
       <c r="C309">
-        <v>0.2726257769587213</v>
+        <v>0.2729348839328355</v>
       </c>
       <c r="D309" t="s">
         <v>7</v>
@@ -9596,7 +9596,7 @@
         <v>6</v>
       </c>
       <c r="C310">
-        <v>0.3932069355296702</v>
+        <v>0.3924817248870033</v>
       </c>
       <c r="D310" t="s">
         <v>7</v>
@@ -9610,10 +9610,10 @@
         <v>630</v>
       </c>
       <c r="B311" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C311">
-        <v>0.364159210338386</v>
+        <v>0.3649826564721951</v>
       </c>
       <c r="D311" t="s">
         <v>7</v>
@@ -9627,10 +9627,10 @@
         <v>632</v>
       </c>
       <c r="B312" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C312">
-        <v>0.2524974966116469</v>
+        <v>0.2525512797727946</v>
       </c>
       <c r="D312" t="s">
         <v>7</v>
@@ -9647,7 +9647,7 @@
         <v>44</v>
       </c>
       <c r="C313">
-        <v>0.3258762713066557</v>
+        <v>0.3273223810051179</v>
       </c>
       <c r="D313" t="s">
         <v>7</v>
@@ -9661,10 +9661,10 @@
         <v>636</v>
       </c>
       <c r="B314" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C314">
-        <v>0.2986298184181888</v>
+        <v>0.2937165267147964</v>
       </c>
       <c r="D314" t="s">
         <v>7</v>
@@ -9681,7 +9681,7 @@
         <v>44</v>
       </c>
       <c r="C315">
-        <v>0.4952010648019043</v>
+        <v>0.4942634895910673</v>
       </c>
       <c r="D315" t="s">
         <v>7</v>
@@ -9698,7 +9698,7 @@
         <v>6</v>
       </c>
       <c r="C316">
-        <v>0.3533714903186627</v>
+        <v>0.3504492670981796</v>
       </c>
       <c r="D316" t="s">
         <v>7</v>
@@ -9715,7 +9715,7 @@
         <v>6</v>
       </c>
       <c r="C317">
-        <v>0.4959795081136854</v>
+        <v>0.4936853486780529</v>
       </c>
       <c r="D317" t="s">
         <v>7</v>
@@ -9732,7 +9732,7 @@
         <v>6</v>
       </c>
       <c r="C318">
-        <v>0.5253449753091858</v>
+        <v>0.5251042912253109</v>
       </c>
       <c r="D318" t="s">
         <v>7</v>
@@ -9749,7 +9749,7 @@
         <v>6</v>
       </c>
       <c r="C319">
-        <v>0.3289386361167404</v>
+        <v>0.3305651522249652</v>
       </c>
       <c r="D319" t="s">
         <v>7</v>
@@ -9763,10 +9763,10 @@
         <v>648</v>
       </c>
       <c r="B320" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C320">
-        <v>0.2669759412281325</v>
+        <v>0.2654949543906793</v>
       </c>
       <c r="D320" t="s">
         <v>7</v>
@@ -9783,7 +9783,7 @@
         <v>6</v>
       </c>
       <c r="C321">
-        <v>0.339161058707651</v>
+        <v>0.3395079146313663</v>
       </c>
       <c r="D321" t="s">
         <v>7</v>
@@ -9800,7 +9800,7 @@
         <v>6</v>
       </c>
       <c r="C322">
-        <v>0.3482581487247646</v>
+        <v>0.3485061586486588</v>
       </c>
       <c r="D322" t="s">
         <v>7</v>
@@ -9814,10 +9814,10 @@
         <v>654</v>
       </c>
       <c r="B323" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C323">
-        <v>0.3059737545760831</v>
+        <v>0.3038495525059894</v>
       </c>
       <c r="D323" t="s">
         <v>7</v>
@@ -9834,7 +9834,7 @@
         <v>44</v>
       </c>
       <c r="C324">
-        <v>0.3969839837483555</v>
+        <v>0.3959497031438496</v>
       </c>
       <c r="D324" t="s">
         <v>7</v>
@@ -9851,7 +9851,7 @@
         <v>44</v>
       </c>
       <c r="C325">
-        <v>0.2358621138248448</v>
+        <v>0.2367742231131662</v>
       </c>
       <c r="D325" t="s">
         <v>7</v>
@@ -9868,7 +9868,7 @@
         <v>44</v>
       </c>
       <c r="C326">
-        <v>0.3761525230906156</v>
+        <v>0.3750311137141048</v>
       </c>
       <c r="D326" t="s">
         <v>7</v>
@@ -9885,7 +9885,7 @@
         <v>44</v>
       </c>
       <c r="C327">
-        <v>0.3359121476702498</v>
+        <v>0.3368313100919328</v>
       </c>
       <c r="D327" t="s">
         <v>7</v>
@@ -9899,10 +9899,10 @@
         <v>664</v>
       </c>
       <c r="B328" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C328">
-        <v>0.2717990922248174</v>
+        <v>0.2704430253201534</v>
       </c>
       <c r="D328" t="s">
         <v>7</v>
@@ -9916,10 +9916,10 @@
         <v>666</v>
       </c>
       <c r="B329" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C329">
-        <v>0.2835656865256266</v>
+        <v>0.2841047544583576</v>
       </c>
       <c r="D329" t="s">
         <v>7</v>
@@ -9933,10 +9933,10 @@
         <v>668</v>
       </c>
       <c r="B330" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C330">
-        <v>0.3163342332753378</v>
+        <v>0.3208474343204666</v>
       </c>
       <c r="D330" t="s">
         <v>7</v>
@@ -9950,10 +9950,10 @@
         <v>670</v>
       </c>
       <c r="B331" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C331">
-        <v>0.3669257421726532</v>
+        <v>0.3656023360617762</v>
       </c>
       <c r="D331" t="s">
         <v>7</v>
@@ -9967,10 +9967,10 @@
         <v>672</v>
       </c>
       <c r="B332" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C332">
-        <v>0.3334186559323681</v>
+        <v>0.331252045483267</v>
       </c>
       <c r="D332" t="s">
         <v>7</v>
@@ -9987,7 +9987,7 @@
         <v>6</v>
       </c>
       <c r="C333">
-        <v>0.4618271624517494</v>
+        <v>0.4617084331013162</v>
       </c>
       <c r="D333" t="s">
         <v>7</v>
@@ -10001,10 +10001,10 @@
         <v>676</v>
       </c>
       <c r="B334" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="C334">
-        <v>0.2594764140073977</v>
+        <v>0.2559891553923031</v>
       </c>
       <c r="D334" t="s">
         <v>7</v>
@@ -10018,10 +10018,10 @@
         <v>678</v>
       </c>
       <c r="B335" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C335">
-        <v>0.3564463839932533</v>
+        <v>0.357592846573205</v>
       </c>
       <c r="D335" t="s">
         <v>7</v>
@@ -10035,10 +10035,10 @@
         <v>680</v>
       </c>
       <c r="B336" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C336">
-        <v>0.3088241745099614</v>
+        <v>0.3055676064747564</v>
       </c>
       <c r="D336" t="s">
         <v>7</v>
@@ -10055,7 +10055,7 @@
         <v>44</v>
       </c>
       <c r="C337">
-        <v>0.4131056078987515</v>
+        <v>0.4118050910011717</v>
       </c>
       <c r="D337" t="s">
         <v>7</v>
@@ -10072,7 +10072,7 @@
         <v>6</v>
       </c>
       <c r="C338">
-        <v>0.2845452612687152</v>
+        <v>0.284482982717028</v>
       </c>
       <c r="D338" t="s">
         <v>7</v>
@@ -10086,10 +10086,10 @@
         <v>686</v>
       </c>
       <c r="B339" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C339">
-        <v>0.4681795328122594</v>
+        <v>0.4729884323719991</v>
       </c>
       <c r="D339" t="s">
         <v>7</v>
@@ -10103,10 +10103,10 @@
         <v>688</v>
       </c>
       <c r="B340" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C340">
-        <v>0.2805055267969355</v>
+        <v>0.2795109317370509</v>
       </c>
       <c r="D340" t="s">
         <v>7</v>
@@ -10123,7 +10123,7 @@
         <v>6</v>
       </c>
       <c r="C341">
-        <v>0.3059104900998462</v>
+        <v>0.2980229680464076</v>
       </c>
       <c r="D341" t="s">
         <v>7</v>
@@ -10137,10 +10137,10 @@
         <v>692</v>
       </c>
       <c r="B342" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C342">
-        <v>0.2705092591486839</v>
+        <v>0.269644962292767</v>
       </c>
       <c r="D342" t="s">
         <v>7</v>
@@ -10154,10 +10154,10 @@
         <v>694</v>
       </c>
       <c r="B343" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C343">
-        <v>0.3589703528427646</v>
+        <v>0.3558535325266513</v>
       </c>
       <c r="D343" t="s">
         <v>7</v>
@@ -10171,10 +10171,10 @@
         <v>696</v>
       </c>
       <c r="B344" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C344">
-        <v>0.2408117657065297</v>
+        <v>0.2418088927725526</v>
       </c>
       <c r="D344" t="s">
         <v>7</v>
@@ -10191,7 +10191,7 @@
         <v>6</v>
       </c>
       <c r="C345">
-        <v>0.3419811946370188</v>
+        <v>0.342866044645609</v>
       </c>
       <c r="D345" t="s">
         <v>7</v>
@@ -10205,10 +10205,10 @@
         <v>700</v>
       </c>
       <c r="B346" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C346">
-        <v>0.3199839588363672</v>
+        <v>0.3226637100034135</v>
       </c>
       <c r="D346" t="s">
         <v>7</v>
@@ -10222,10 +10222,10 @@
         <v>702</v>
       </c>
       <c r="B347" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C347">
-        <v>0.3532141526285706</v>
+        <v>0.3561518313583903</v>
       </c>
       <c r="D347" t="s">
         <v>7</v>
@@ -10242,7 +10242,7 @@
         <v>6</v>
       </c>
       <c r="C348">
-        <v>0.3224982750839737</v>
+        <v>0.3240661650475435</v>
       </c>
       <c r="D348" t="s">
         <v>7</v>
@@ -10259,7 +10259,7 @@
         <v>6</v>
       </c>
       <c r="C349">
-        <v>0.5061458555470948</v>
+        <v>0.5087688673501838</v>
       </c>
       <c r="D349" t="s">
         <v>7</v>
@@ -10273,10 +10273,10 @@
         <v>708</v>
       </c>
       <c r="B350" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C350">
-        <v>0.3659446588643471</v>
+        <v>0.3680436522539374</v>
       </c>
       <c r="D350" t="s">
         <v>7</v>
@@ -10293,7 +10293,7 @@
         <v>79</v>
       </c>
       <c r="C351">
-        <v>0.2976562086702949</v>
+        <v>0.2983734046938649</v>
       </c>
       <c r="D351" t="s">
         <v>7</v>
@@ -10307,10 +10307,10 @@
         <v>712</v>
       </c>
       <c r="B352" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C352">
-        <v>0.4063702310346625</v>
+        <v>0.4056922131568523</v>
       </c>
       <c r="D352" t="s">
         <v>7</v>
@@ -10324,10 +10324,10 @@
         <v>714</v>
       </c>
       <c r="B353" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C353">
-        <v>0.3546267675666195</v>
+        <v>0.3545692344163664</v>
       </c>
       <c r="D353" t="s">
         <v>7</v>
@@ -10344,7 +10344,7 @@
         <v>6</v>
       </c>
       <c r="C354">
-        <v>0.2891862892311041</v>
+        <v>0.2855240063532514</v>
       </c>
       <c r="D354" t="s">
         <v>7</v>
@@ -10361,7 +10361,7 @@
         <v>6</v>
       </c>
       <c r="C355">
-        <v>0.3499225439840264</v>
+        <v>0.3410497998986727</v>
       </c>
       <c r="D355" t="s">
         <v>7</v>
@@ -10378,7 +10378,7 @@
         <v>6</v>
       </c>
       <c r="C356">
-        <v>0.3119035427438974</v>
+        <v>0.3132144786174916</v>
       </c>
       <c r="D356" t="s">
         <v>7</v>
@@ -10395,7 +10395,7 @@
         <v>6</v>
       </c>
       <c r="C357">
-        <v>0.3832723824503916</v>
+        <v>0.3815512926309224</v>
       </c>
       <c r="D357" t="s">
         <v>7</v>
@@ -10412,7 +10412,7 @@
         <v>79</v>
       </c>
       <c r="C358">
-        <v>0.3506419458853889</v>
+        <v>0.342873169221634</v>
       </c>
       <c r="D358" t="s">
         <v>7</v>
@@ -10429,7 +10429,7 @@
         <v>44</v>
       </c>
       <c r="C359">
-        <v>0.4600930980942639</v>
+        <v>0.4602245178497633</v>
       </c>
       <c r="D359" t="s">
         <v>7</v>
@@ -10446,7 +10446,7 @@
         <v>6</v>
       </c>
       <c r="C360">
-        <v>0.4924515376028096</v>
+        <v>0.4925601697322087</v>
       </c>
       <c r="D360" t="s">
         <v>7</v>
@@ -10460,10 +10460,10 @@
         <v>730</v>
       </c>
       <c r="B361" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C361">
-        <v>0.3105794641995573</v>
+        <v>0.3087103819321343</v>
       </c>
       <c r="D361" t="s">
         <v>7</v>
@@ -10480,7 +10480,7 @@
         <v>6</v>
       </c>
       <c r="C362">
-        <v>0.3573677650166904</v>
+        <v>0.3598741143582589</v>
       </c>
       <c r="D362" t="s">
         <v>7</v>
@@ -10497,7 +10497,7 @@
         <v>6</v>
       </c>
       <c r="C363">
-        <v>0.2836208023075129</v>
+        <v>0.2848037642357048</v>
       </c>
       <c r="D363" t="s">
         <v>7</v>
@@ -10511,10 +10511,10 @@
         <v>736</v>
       </c>
       <c r="B364" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C364">
-        <v>0.2901466149201132</v>
+        <v>0.2853645223374569</v>
       </c>
       <c r="D364" t="s">
         <v>7</v>
@@ -10528,10 +10528,10 @@
         <v>738</v>
       </c>
       <c r="B365" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C365">
-        <v>0.3118400842106001</v>
+        <v>0.3161323413993479</v>
       </c>
       <c r="D365" t="s">
         <v>7</v>
@@ -10545,10 +10545,10 @@
         <v>740</v>
       </c>
       <c r="B366" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C366">
-        <v>0.2458874717622704</v>
+        <v>0.2477619373291138</v>
       </c>
       <c r="D366" t="s">
         <v>7</v>
@@ -10565,7 +10565,7 @@
         <v>6</v>
       </c>
       <c r="C367">
-        <v>0.3233679184261398</v>
+        <v>0.3260859479095397</v>
       </c>
       <c r="D367" t="s">
         <v>7</v>
@@ -10579,10 +10579,10 @@
         <v>744</v>
       </c>
       <c r="B368" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C368">
-        <v>0.3588114040660749</v>
+        <v>0.3577851294245041</v>
       </c>
       <c r="D368" t="s">
         <v>7</v>
@@ -10599,7 +10599,7 @@
         <v>6</v>
       </c>
       <c r="C369">
-        <v>0.5648381672171651</v>
+        <v>0.5672330199771578</v>
       </c>
       <c r="D369" t="s">
         <v>7</v>
@@ -10613,10 +10613,10 @@
         <v>748</v>
       </c>
       <c r="B370" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C370">
-        <v>0.3259383407559205</v>
+        <v>0.3288845142900242</v>
       </c>
       <c r="D370" t="s">
         <v>7</v>
@@ -10633,7 +10633,7 @@
         <v>6</v>
       </c>
       <c r="C371">
-        <v>0.4575639429774609</v>
+        <v>0.4566596311109102</v>
       </c>
       <c r="D371" t="s">
         <v>7</v>
@@ -10650,7 +10650,7 @@
         <v>6</v>
       </c>
       <c r="C372">
-        <v>0.363696991657278</v>
+        <v>0.3539196912358694</v>
       </c>
       <c r="D372" t="s">
         <v>7</v>
@@ -10667,7 +10667,7 @@
         <v>6</v>
       </c>
       <c r="C373">
-        <v>0.4271521854965857</v>
+        <v>0.4268975275884578</v>
       </c>
       <c r="D373" t="s">
         <v>7</v>
@@ -10684,7 +10684,7 @@
         <v>6</v>
       </c>
       <c r="C374">
-        <v>0.4784935137299111</v>
+        <v>0.4850532774202961</v>
       </c>
       <c r="D374" t="s">
         <v>7</v>
@@ -10701,7 +10701,7 @@
         <v>6</v>
       </c>
       <c r="C375">
-        <v>0.4455378624790778</v>
+        <v>0.4444634647490701</v>
       </c>
       <c r="D375" t="s">
         <v>7</v>
@@ -10715,10 +10715,10 @@
         <v>760</v>
       </c>
       <c r="B376" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C376">
-        <v>0.3483790141030403</v>
+        <v>0.3494424720929362</v>
       </c>
       <c r="D376" t="s">
         <v>7</v>
@@ -10735,7 +10735,7 @@
         <v>6</v>
       </c>
       <c r="C377">
-        <v>0.4634980718267991</v>
+        <v>0.4710131461362481</v>
       </c>
       <c r="D377" t="s">
         <v>7</v>
@@ -10752,7 +10752,7 @@
         <v>6</v>
       </c>
       <c r="C378">
-        <v>0.3096989067221528</v>
+        <v>0.310140419008588</v>
       </c>
       <c r="D378" t="s">
         <v>7</v>
@@ -10769,7 +10769,7 @@
         <v>6</v>
       </c>
       <c r="C379">
-        <v>0.3293949032250943</v>
+        <v>0.3335932425756207</v>
       </c>
       <c r="D379" t="s">
         <v>7</v>
@@ -10786,7 +10786,7 @@
         <v>6</v>
       </c>
       <c r="C380">
-        <v>0.3646281361402508</v>
+        <v>0.363408017239023</v>
       </c>
       <c r="D380" t="s">
         <v>7</v>
@@ -10800,10 +10800,10 @@
         <v>770</v>
       </c>
       <c r="B381" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C381">
-        <v>0.4309996603088106</v>
+        <v>0.433604350585675</v>
       </c>
       <c r="D381" t="s">
         <v>7</v>
@@ -10820,7 +10820,7 @@
         <v>6</v>
       </c>
       <c r="C382">
-        <v>0.335418129570762</v>
+        <v>0.3365710917997811</v>
       </c>
       <c r="D382" t="s">
         <v>7</v>
@@ -10834,10 +10834,10 @@
         <v>774</v>
       </c>
       <c r="B383" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C383">
-        <v>0.3482181433357228</v>
+        <v>0.3488751556788903</v>
       </c>
       <c r="D383" t="s">
         <v>7</v>
@@ -10854,7 +10854,7 @@
         <v>44</v>
       </c>
       <c r="C384">
-        <v>0.4594197993612531</v>
+        <v>0.4588479214627305</v>
       </c>
       <c r="D384" t="s">
         <v>7</v>
@@ -10871,7 +10871,7 @@
         <v>6</v>
       </c>
       <c r="C385">
-        <v>0.4029045065374681</v>
+        <v>0.3896002672044507</v>
       </c>
       <c r="D385" t="s">
         <v>7</v>
@@ -10885,10 +10885,10 @@
         <v>780</v>
       </c>
       <c r="B386" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C386">
-        <v>0.2835868989118119</v>
+        <v>0.2844276955118172</v>
       </c>
       <c r="D386" t="s">
         <v>7</v>
@@ -10902,10 +10902,10 @@
         <v>782</v>
       </c>
       <c r="B387" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C387">
-        <v>0.3991757515153388</v>
+        <v>0.396761053256302</v>
       </c>
       <c r="D387" t="s">
         <v>7</v>
@@ -10922,7 +10922,7 @@
         <v>44</v>
       </c>
       <c r="C388">
-        <v>0.3074431001040871</v>
+        <v>0.3078682319556003</v>
       </c>
       <c r="D388" t="s">
         <v>7</v>
@@ -10939,7 +10939,7 @@
         <v>6</v>
       </c>
       <c r="C389">
-        <v>0.3504352249841114</v>
+        <v>0.3508316156744308</v>
       </c>
       <c r="D389" t="s">
         <v>7</v>
@@ -10953,10 +10953,10 @@
         <v>788</v>
       </c>
       <c r="B390" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C390">
-        <v>0.335348634777815</v>
+        <v>0.338306166971486</v>
       </c>
       <c r="D390" t="s">
         <v>7</v>
@@ -10970,10 +10970,10 @@
         <v>790</v>
       </c>
       <c r="B391" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C391">
-        <v>0.3779248597477655</v>
+        <v>0.3771037625274989</v>
       </c>
       <c r="D391" t="s">
         <v>7</v>
@@ -10987,10 +10987,10 @@
         <v>792</v>
       </c>
       <c r="B392" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C392">
-        <v>0.3144642375744883</v>
+        <v>0.3164240918241739</v>
       </c>
       <c r="D392" t="s">
         <v>7</v>
@@ -11004,10 +11004,10 @@
         <v>794</v>
       </c>
       <c r="B393" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C393">
-        <v>0.3798119627755119</v>
+        <v>0.3788850492005276</v>
       </c>
       <c r="D393" t="s">
         <v>7</v>
@@ -11021,10 +11021,10 @@
         <v>796</v>
       </c>
       <c r="B394" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C394">
-        <v>0.3739804061966772</v>
+        <v>0.3784855630043354</v>
       </c>
       <c r="D394" t="s">
         <v>7</v>
@@ -11038,10 +11038,10 @@
         <v>798</v>
       </c>
       <c r="B395" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C395">
-        <v>0.4091182911648155</v>
+        <v>0.4122815173360852</v>
       </c>
       <c r="D395" t="s">
         <v>7</v>
@@ -11058,7 +11058,7 @@
         <v>6</v>
       </c>
       <c r="C396">
-        <v>0.3739525408855695</v>
+        <v>0.3728690296861203</v>
       </c>
       <c r="D396" t="s">
         <v>7</v>
@@ -11072,10 +11072,10 @@
         <v>802</v>
       </c>
       <c r="B397" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C397">
-        <v>0.3372896636937475</v>
+        <v>0.3362966528046027</v>
       </c>
       <c r="D397" t="s">
         <v>7</v>
@@ -11092,7 +11092,7 @@
         <v>6</v>
       </c>
       <c r="C398">
-        <v>0.5001311493484526</v>
+        <v>0.5009763496460983</v>
       </c>
       <c r="D398" t="s">
         <v>7</v>
@@ -11106,10 +11106,10 @@
         <v>806</v>
       </c>
       <c r="B399" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C399">
-        <v>0.3626897583710657</v>
+        <v>0.3620657187242247</v>
       </c>
       <c r="D399" t="s">
         <v>7</v>
@@ -11126,7 +11126,7 @@
         <v>6</v>
       </c>
       <c r="C400">
-        <v>0.341173779414662</v>
+        <v>0.3396357613486796</v>
       </c>
       <c r="D400" t="s">
         <v>7</v>
@@ -11140,10 +11140,10 @@
         <v>810</v>
       </c>
       <c r="B401" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C401">
-        <v>0.4770265951591228</v>
+        <v>0.4820023246090103</v>
       </c>
       <c r="D401" t="s">
         <v>7</v>
@@ -11160,7 +11160,7 @@
         <v>6</v>
       </c>
       <c r="C402">
-        <v>0.393517634145109</v>
+        <v>0.3910028028063164</v>
       </c>
       <c r="D402" t="s">
         <v>7</v>
@@ -11177,7 +11177,7 @@
         <v>6</v>
       </c>
       <c r="C403">
-        <v>0.292951329249466</v>
+        <v>0.2961928965264862</v>
       </c>
       <c r="D403" t="s">
         <v>7</v>
@@ -11191,10 +11191,10 @@
         <v>816</v>
       </c>
       <c r="B404" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C404">
-        <v>0.3003731540710914</v>
+        <v>0.2971490462965958</v>
       </c>
       <c r="D404" t="s">
         <v>7</v>
@@ -11211,7 +11211,7 @@
         <v>6</v>
       </c>
       <c r="C405">
-        <v>0.38712910972343</v>
+        <v>0.3838538386670843</v>
       </c>
       <c r="D405" t="s">
         <v>7</v>
@@ -11228,7 +11228,7 @@
         <v>79</v>
       </c>
       <c r="C406">
-        <v>0.5418973798758684</v>
+        <v>0.5416980967921755</v>
       </c>
       <c r="D406" t="s">
         <v>7</v>
@@ -11245,7 +11245,7 @@
         <v>6</v>
       </c>
       <c r="C407">
-        <v>0.3923760571027656</v>
+        <v>0.3932251129578064</v>
       </c>
       <c r="D407" t="s">
         <v>7</v>
@@ -11262,7 +11262,7 @@
         <v>6</v>
       </c>
       <c r="C408">
-        <v>0.4398680599367746</v>
+        <v>0.4424052106040023</v>
       </c>
       <c r="D408" t="s">
         <v>7</v>
@@ -11279,7 +11279,7 @@
         <v>6</v>
       </c>
       <c r="C409">
-        <v>0.4580369439291966</v>
+        <v>0.4542310031991851</v>
       </c>
       <c r="D409" t="s">
         <v>7</v>
@@ -11293,10 +11293,10 @@
         <v>828</v>
       </c>
       <c r="B410" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C410">
-        <v>0.2786077243831897</v>
+        <v>0.2790983578207493</v>
       </c>
       <c r="D410" t="s">
         <v>7</v>
@@ -11313,7 +11313,7 @@
         <v>6</v>
       </c>
       <c r="C411">
-        <v>0.3207314107068708</v>
+        <v>0.3192450134463625</v>
       </c>
       <c r="D411" t="s">
         <v>7</v>
@@ -11330,7 +11330,7 @@
         <v>6</v>
       </c>
       <c r="C412">
-        <v>0.4236192011380492</v>
+        <v>0.422680526668655</v>
       </c>
       <c r="D412" t="s">
         <v>7</v>
@@ -11347,7 +11347,7 @@
         <v>6</v>
       </c>
       <c r="C413">
-        <v>0.2588990231482534</v>
+        <v>0.258230034666867</v>
       </c>
       <c r="D413" t="s">
         <v>7</v>
@@ -11361,10 +11361,10 @@
         <v>836</v>
       </c>
       <c r="B414" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C414">
-        <v>0.3017382893388351</v>
+        <v>0.3009033100177761</v>
       </c>
       <c r="D414" t="s">
         <v>7</v>
@@ -11378,10 +11378,10 @@
         <v>838</v>
       </c>
       <c r="B415" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C415">
-        <v>0.3627212495420229</v>
+        <v>0.3619303870260741</v>
       </c>
       <c r="D415" t="s">
         <v>7</v>
@@ -11395,10 +11395,10 @@
         <v>840</v>
       </c>
       <c r="B416" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C416">
-        <v>0.525631494284742</v>
+        <v>0.5063094728120429</v>
       </c>
       <c r="D416" t="s">
         <v>7</v>
@@ -11415,7 +11415,7 @@
         <v>6</v>
       </c>
       <c r="C417">
-        <v>0.2561816099369306</v>
+        <v>0.2567839408648351</v>
       </c>
       <c r="D417" t="s">
         <v>7</v>
@@ -11429,10 +11429,10 @@
         <v>844</v>
       </c>
       <c r="B418" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C418">
-        <v>0.3049293381272613</v>
+        <v>0.3058852199465608</v>
       </c>
       <c r="D418" t="s">
         <v>7</v>
@@ -11446,10 +11446,10 @@
         <v>846</v>
       </c>
       <c r="B419" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C419">
-        <v>0.4104889067410642</v>
+        <v>0.4133713594007117</v>
       </c>
       <c r="D419" t="s">
         <v>7</v>
@@ -11466,7 +11466,7 @@
         <v>44</v>
       </c>
       <c r="C420">
-        <v>0.4506730194029844</v>
+        <v>0.4524716067654568</v>
       </c>
       <c r="D420" t="s">
         <v>7</v>
@@ -11483,7 +11483,7 @@
         <v>44</v>
       </c>
       <c r="C421">
-        <v>0.4421748176112514</v>
+        <v>0.4404432447642156</v>
       </c>
       <c r="D421" t="s">
         <v>7</v>
@@ -11500,7 +11500,7 @@
         <v>6</v>
       </c>
       <c r="C422">
-        <v>0.3678494985582489</v>
+        <v>0.3665066022372021</v>
       </c>
       <c r="D422" t="s">
         <v>7</v>
@@ -11517,7 +11517,7 @@
         <v>44</v>
       </c>
       <c r="C423">
-        <v>0.4121667744141146</v>
+        <v>0.4122987824947921</v>
       </c>
       <c r="D423" t="s">
         <v>7</v>
@@ -11531,10 +11531,10 @@
         <v>856</v>
       </c>
       <c r="B424" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C424">
-        <v>0.3159362714232383</v>
+        <v>0.3146575291347722</v>
       </c>
       <c r="D424" t="s">
         <v>7</v>
@@ -11551,7 +11551,7 @@
         <v>6</v>
       </c>
       <c r="C425">
-        <v>0.3540572606631477</v>
+        <v>0.3560042436738198</v>
       </c>
       <c r="D425" t="s">
         <v>7</v>
@@ -11565,10 +11565,10 @@
         <v>860</v>
       </c>
       <c r="B426" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C426">
-        <v>0.3777921251551525</v>
+        <v>0.3766156647437505</v>
       </c>
       <c r="D426" t="s">
         <v>7</v>
@@ -11585,7 +11585,7 @@
         <v>6</v>
       </c>
       <c r="C427">
-        <v>0.2762399824442439</v>
+        <v>0.2759649959292526</v>
       </c>
       <c r="D427" t="s">
         <v>7</v>
@@ -11602,7 +11602,7 @@
         <v>6</v>
       </c>
       <c r="C428">
-        <v>0.2724413031135646</v>
+        <v>0.2711563901759526</v>
       </c>
       <c r="D428" t="s">
         <v>7</v>
@@ -11616,10 +11616,10 @@
         <v>866</v>
       </c>
       <c r="B429" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C429">
-        <v>0.3483203211127535</v>
+        <v>0.3477066871250877</v>
       </c>
       <c r="D429" t="s">
         <v>7</v>
@@ -11636,7 +11636,7 @@
         <v>6</v>
       </c>
       <c r="C430">
-        <v>0.3559505319503517</v>
+        <v>0.3554148903527548</v>
       </c>
       <c r="D430" t="s">
         <v>7</v>
@@ -11650,10 +11650,10 @@
         <v>870</v>
       </c>
       <c r="B431" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C431">
-        <v>0.2971929277480729</v>
+        <v>0.3022742048057931</v>
       </c>
       <c r="D431" t="s">
         <v>7</v>
@@ -11667,10 +11667,10 @@
         <v>872</v>
       </c>
       <c r="B432" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C432">
-        <v>0.3490113139386439</v>
+        <v>0.3505370911227951</v>
       </c>
       <c r="D432" t="s">
         <v>7</v>
@@ -11687,7 +11687,7 @@
         <v>6</v>
       </c>
       <c r="C433">
-        <v>0.2775467946912031</v>
+        <v>0.2776179001344524</v>
       </c>
       <c r="D433" t="s">
         <v>7</v>
@@ -11701,10 +11701,10 @@
         <v>876</v>
       </c>
       <c r="B434" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C434">
-        <v>0.3697659381924875</v>
+        <v>0.3681350968957232</v>
       </c>
       <c r="D434" t="s">
         <v>7</v>
@@ -11718,10 +11718,10 @@
         <v>878</v>
       </c>
       <c r="B435" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C435">
-        <v>0.3752236316801415</v>
+        <v>0.3757332899507906</v>
       </c>
       <c r="D435" t="s">
         <v>7</v>
@@ -11735,10 +11735,10 @@
         <v>880</v>
       </c>
       <c r="B436" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C436">
-        <v>0.3888404358279803</v>
+        <v>0.3831125452076493</v>
       </c>
       <c r="D436" t="s">
         <v>7</v>
@@ -11752,10 +11752,10 @@
         <v>882</v>
       </c>
       <c r="B437" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C437">
-        <v>0.3014258886074584</v>
+        <v>0.302465437125774</v>
       </c>
       <c r="D437" t="s">
         <v>7</v>
@@ -11769,10 +11769,10 @@
         <v>884</v>
       </c>
       <c r="B438" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C438">
-        <v>0.3501317928912035</v>
+        <v>0.3516669602011376</v>
       </c>
       <c r="D438" t="s">
         <v>7</v>
@@ -11789,7 +11789,7 @@
         <v>6</v>
       </c>
       <c r="C439">
-        <v>0.3689590388931338</v>
+        <v>0.3714763885109734</v>
       </c>
       <c r="D439" t="s">
         <v>7</v>
@@ -11803,10 +11803,10 @@
         <v>888</v>
       </c>
       <c r="B440" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C440">
-        <v>0.2930582762369733</v>
+        <v>0.2951361234837089</v>
       </c>
       <c r="D440" t="s">
         <v>7</v>
@@ -11823,7 +11823,7 @@
         <v>6</v>
       </c>
       <c r="C441">
-        <v>0.3116676562556502</v>
+        <v>0.3112936177655987</v>
       </c>
       <c r="D441" t="s">
         <v>7</v>
@@ -11840,7 +11840,7 @@
         <v>6</v>
       </c>
       <c r="C442">
-        <v>0.2969005781438252</v>
+        <v>0.2988182896881045</v>
       </c>
       <c r="D442" t="s">
         <v>7</v>
@@ -11854,10 +11854,10 @@
         <v>894</v>
       </c>
       <c r="B443" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C443">
-        <v>0.3083605159381835</v>
+        <v>0.3062494453903968</v>
       </c>
       <c r="D443" t="s">
         <v>7</v>
@@ -11871,10 +11871,10 @@
         <v>896</v>
       </c>
       <c r="B444" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C444">
-        <v>0.3227810303908513</v>
+        <v>0.3270908830392907</v>
       </c>
       <c r="D444" t="s">
         <v>7</v>
@@ -11891,7 +11891,7 @@
         <v>6</v>
       </c>
       <c r="C445">
-        <v>0.3563314084418838</v>
+        <v>0.3559760366502255</v>
       </c>
       <c r="D445" t="s">
         <v>7</v>
@@ -11908,7 +11908,7 @@
         <v>44</v>
       </c>
       <c r="C446">
-        <v>0.3694424729466998</v>
+        <v>0.3664006381454172</v>
       </c>
       <c r="D446" t="s">
         <v>7</v>
@@ -11925,7 +11925,7 @@
         <v>6</v>
       </c>
       <c r="C447">
-        <v>0.2806430760319418</v>
+        <v>0.2807451881966995</v>
       </c>
       <c r="D447" t="s">
         <v>7</v>
@@ -11942,7 +11942,7 @@
         <v>6</v>
       </c>
       <c r="C448">
-        <v>0.3604206852756249</v>
+        <v>0.3605143953364514</v>
       </c>
       <c r="D448" t="s">
         <v>7</v>
@@ -11959,7 +11959,7 @@
         <v>6</v>
       </c>
       <c r="C449">
-        <v>0.4060916451498125</v>
+        <v>0.4010407789354055</v>
       </c>
       <c r="D449" t="s">
         <v>7</v>
@@ -11976,7 +11976,7 @@
         <v>44</v>
       </c>
       <c r="C450">
-        <v>0.3980950870130865</v>
+        <v>0.3976583710245067</v>
       </c>
       <c r="D450" t="s">
         <v>7</v>
@@ -11993,7 +11993,7 @@
         <v>44</v>
       </c>
       <c r="C451">
-        <v>0.3953312885675174</v>
+        <v>0.3949459448058157</v>
       </c>
       <c r="D451" t="s">
         <v>7</v>
@@ -12010,7 +12010,7 @@
         <v>6</v>
       </c>
       <c r="C452">
-        <v>0.3291187825672548</v>
+        <v>0.3296522588143242</v>
       </c>
       <c r="D452" t="s">
         <v>7</v>
@@ -12024,10 +12024,10 @@
         <v>914</v>
       </c>
       <c r="B453" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C453">
-        <v>0.3431028842488534</v>
+        <v>0.3364263731265571</v>
       </c>
       <c r="D453" t="s">
         <v>7</v>
@@ -12041,10 +12041,10 @@
         <v>916</v>
       </c>
       <c r="B454" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C454">
-        <v>0.2713591109586055</v>
+        <v>0.2712284409837693</v>
       </c>
       <c r="D454" t="s">
         <v>7</v>
@@ -12058,10 +12058,10 @@
         <v>918</v>
       </c>
       <c r="B455" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C455">
-        <v>0.3259339906510607</v>
+        <v>0.3247769369056187</v>
       </c>
       <c r="D455" t="s">
         <v>7</v>
@@ -12078,7 +12078,7 @@
         <v>6</v>
       </c>
       <c r="C456">
-        <v>0.3645010712733379</v>
+        <v>0.3638382506970495</v>
       </c>
       <c r="D456" t="s">
         <v>7</v>
@@ -12092,10 +12092,10 @@
         <v>922</v>
       </c>
       <c r="B457" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C457">
-        <v>0.3797831800082372</v>
+        <v>0.3858887135142025</v>
       </c>
       <c r="D457" t="s">
         <v>7</v>
@@ -12112,7 +12112,7 @@
         <v>6</v>
       </c>
       <c r="C458">
-        <v>0.3537153660591556</v>
+        <v>0.3533328791342177</v>
       </c>
       <c r="D458" t="s">
         <v>7</v>
@@ -12129,7 +12129,7 @@
         <v>6</v>
       </c>
       <c r="C459">
-        <v>0.3810775666593174</v>
+        <v>0.3794987996991459</v>
       </c>
       <c r="D459" t="s">
         <v>7</v>
@@ -12146,7 +12146,7 @@
         <v>6</v>
       </c>
       <c r="C460">
-        <v>0.3264051630049449</v>
+        <v>0.3292128459409154</v>
       </c>
       <c r="D460" t="s">
         <v>7</v>
@@ -12160,10 +12160,10 @@
         <v>930</v>
       </c>
       <c r="B461" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C461">
-        <v>0.3085337868681475</v>
+        <v>0.3073710470772348</v>
       </c>
       <c r="D461" t="s">
         <v>7</v>
@@ -12180,7 +12180,7 @@
         <v>6</v>
       </c>
       <c r="C462">
-        <v>0.3321565992012373</v>
+        <v>0.3345165652421457</v>
       </c>
       <c r="D462" t="s">
         <v>7</v>
@@ -12197,7 +12197,7 @@
         <v>10</v>
       </c>
       <c r="C463">
-        <v>0.2927588619458896</v>
+        <v>0.2850815106846945</v>
       </c>
       <c r="D463" t="s">
         <v>7</v>
@@ -12214,7 +12214,7 @@
         <v>6</v>
       </c>
       <c r="C464">
-        <v>0.4182129517500688</v>
+        <v>0.4188817037512355</v>
       </c>
       <c r="D464" t="s">
         <v>7</v>
@@ -12231,7 +12231,7 @@
         <v>44</v>
       </c>
       <c r="C465">
-        <v>0.3674907519996055</v>
+        <v>0.3694609199986665</v>
       </c>
       <c r="D465" t="s">
         <v>7</v>
@@ -12248,7 +12248,7 @@
         <v>6</v>
       </c>
       <c r="C466">
-        <v>0.5246757970000753</v>
+        <v>0.5242685523091681</v>
       </c>
       <c r="D466" t="s">
         <v>7</v>
@@ -12265,7 +12265,7 @@
         <v>6</v>
       </c>
       <c r="C467">
-        <v>0.4783115422743723</v>
+        <v>0.4734774178726135</v>
       </c>
       <c r="D467" t="s">
         <v>7</v>
@@ -12282,7 +12282,7 @@
         <v>6</v>
       </c>
       <c r="C468">
-        <v>0.3800880824484475</v>
+        <v>0.3801905906000626</v>
       </c>
       <c r="D468" t="s">
         <v>7</v>
@@ -12296,10 +12296,10 @@
         <v>946</v>
       </c>
       <c r="B469" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C469">
-        <v>0.2968609930543137</v>
+        <v>0.2973104049059154</v>
       </c>
       <c r="D469" t="s">
         <v>7</v>
@@ -12313,10 +12313,10 @@
         <v>948</v>
       </c>
       <c r="B470" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C470">
-        <v>0.2974576783175921</v>
+        <v>0.298809584383551</v>
       </c>
       <c r="D470" t="s">
         <v>7</v>
@@ -12333,7 +12333,7 @@
         <v>44</v>
       </c>
       <c r="C471">
-        <v>0.3279314632944729</v>
+        <v>0.3260353372043116</v>
       </c>
       <c r="D471" t="s">
         <v>7</v>
@@ -12347,10 +12347,10 @@
         <v>952</v>
       </c>
       <c r="B472" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C472">
-        <v>0.296697067658223</v>
+        <v>0.2977871160427352</v>
       </c>
       <c r="D472" t="s">
         <v>7</v>
@@ -12367,7 +12367,7 @@
         <v>44</v>
       </c>
       <c r="C473">
-        <v>0.3345713272221548</v>
+        <v>0.329778170039945</v>
       </c>
       <c r="D473" t="s">
         <v>7</v>
@@ -12381,10 +12381,10 @@
         <v>956</v>
       </c>
       <c r="B474" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C474">
-        <v>0.3574215046228389</v>
+        <v>0.3597215530982563</v>
       </c>
       <c r="D474" t="s">
         <v>7</v>
@@ -12401,7 +12401,7 @@
         <v>6</v>
       </c>
       <c r="C475">
-        <v>0.3400839489426426</v>
+        <v>0.3398763520268112</v>
       </c>
       <c r="D475" t="s">
         <v>7</v>
@@ -12418,7 +12418,7 @@
         <v>6</v>
       </c>
       <c r="C476">
-        <v>0.3096863661806615</v>
+        <v>0.3116494411541115</v>
       </c>
       <c r="D476" t="s">
         <v>7</v>
@@ -12432,10 +12432,10 @@
         <v>962</v>
       </c>
       <c r="B477" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C477">
-        <v>0.318887200890589</v>
+        <v>0.3090026825727349</v>
       </c>
       <c r="D477" t="s">
         <v>7</v>
@@ -12452,7 +12452,7 @@
         <v>6</v>
       </c>
       <c r="C478">
-        <v>0.4092417819197193</v>
+        <v>0.4080606813631315</v>
       </c>
       <c r="D478" t="s">
         <v>7</v>
@@ -12469,7 +12469,7 @@
         <v>44</v>
       </c>
       <c r="C479">
-        <v>0.3983101414364557</v>
+        <v>0.3945755275291037</v>
       </c>
       <c r="D479" t="s">
         <v>7</v>
@@ -12486,7 +12486,7 @@
         <v>6</v>
       </c>
       <c r="C480">
-        <v>0.4568728428192342</v>
+        <v>0.4553207431636923</v>
       </c>
       <c r="D480" t="s">
         <v>7</v>
@@ -12503,7 +12503,7 @@
         <v>44</v>
       </c>
       <c r="C481">
-        <v>0.372837088044393</v>
+        <v>0.3727767211496779</v>
       </c>
       <c r="D481" t="s">
         <v>7</v>
@@ -12517,10 +12517,10 @@
         <v>972</v>
       </c>
       <c r="B482" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="C482">
-        <v>0.2657827255839919</v>
+        <v>0.2662843770559931</v>
       </c>
       <c r="D482" t="s">
         <v>7</v>
@@ -12534,10 +12534,10 @@
         <v>974</v>
       </c>
       <c r="B483" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C483">
-        <v>0.2858425503064123</v>
+        <v>0.2841855467470946</v>
       </c>
       <c r="D483" t="s">
         <v>7</v>
@@ -12554,7 +12554,7 @@
         <v>44</v>
       </c>
       <c r="C484">
-        <v>0.3616489562466889</v>
+        <v>0.3613090399168942</v>
       </c>
       <c r="D484" t="s">
         <v>7</v>
@@ -12568,10 +12568,10 @@
         <v>978</v>
       </c>
       <c r="B485" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C485">
-        <v>0.3716030731674089</v>
+        <v>0.3715838513821805</v>
       </c>
       <c r="D485" t="s">
         <v>7</v>
@@ -12585,10 +12585,10 @@
         <v>980</v>
       </c>
       <c r="B486" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C486">
-        <v>0.4357799044220196</v>
+        <v>0.4425234522183656</v>
       </c>
       <c r="D486" t="s">
         <v>7</v>
@@ -12605,7 +12605,7 @@
         <v>44</v>
       </c>
       <c r="C487">
-        <v>0.4260028284976772</v>
+        <v>0.4265372960827504</v>
       </c>
       <c r="D487" t="s">
         <v>7</v>
@@ -12619,10 +12619,10 @@
         <v>984</v>
       </c>
       <c r="B488" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C488">
-        <v>0.2795992879904622</v>
+        <v>0.2750918140181081</v>
       </c>
       <c r="D488" t="s">
         <v>7</v>
@@ -12639,7 +12639,7 @@
         <v>6</v>
       </c>
       <c r="C489">
-        <v>0.5087391511785967</v>
+        <v>0.5095122301415167</v>
       </c>
       <c r="D489" t="s">
         <v>7</v>
@@ -12653,10 +12653,10 @@
         <v>988</v>
       </c>
       <c r="B490" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C490">
-        <v>0.3243946367688255</v>
+        <v>0.3256047817306831</v>
       </c>
       <c r="D490" t="s">
         <v>7</v>
@@ -12673,7 +12673,7 @@
         <v>6</v>
       </c>
       <c r="C491">
-        <v>0.2911841510234984</v>
+        <v>0.2905798766685286</v>
       </c>
       <c r="D491" t="s">
         <v>7</v>
@@ -12690,7 +12690,7 @@
         <v>6</v>
       </c>
       <c r="C492">
-        <v>0.5171945681509194</v>
+        <v>0.5177817250278671</v>
       </c>
       <c r="D492" t="s">
         <v>7</v>
@@ -12707,7 +12707,7 @@
         <v>6</v>
       </c>
       <c r="C493">
-        <v>0.3007306569725106</v>
+        <v>0.3003064761658628</v>
       </c>
       <c r="D493" t="s">
         <v>7</v>
@@ -12724,7 +12724,7 @@
         <v>44</v>
       </c>
       <c r="C494">
-        <v>0.2985147889650148</v>
+        <v>0.2953646868102617</v>
       </c>
       <c r="D494" t="s">
         <v>7</v>
@@ -12741,7 +12741,7 @@
         <v>44</v>
       </c>
       <c r="C495">
-        <v>0.5203301607401026</v>
+        <v>0.5183411412022323</v>
       </c>
       <c r="D495" t="s">
         <v>7</v>
@@ -12758,7 +12758,7 @@
         <v>6</v>
       </c>
       <c r="C496">
-        <v>0.484666647928404</v>
+        <v>0.4852176310066227</v>
       </c>
       <c r="D496" t="s">
         <v>7</v>
@@ -12772,10 +12772,10 @@
         <v>1002</v>
       </c>
       <c r="B497" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C497">
-        <v>0.3530878231771015</v>
+        <v>0.357668126086904</v>
       </c>
       <c r="D497" t="s">
         <v>7</v>
@@ -12792,7 +12792,7 @@
         <v>6</v>
       </c>
       <c r="C498">
-        <v>0.6895469281742609</v>
+        <v>0.6890456821002725</v>
       </c>
       <c r="D498" t="s">
         <v>7</v>
@@ -12806,10 +12806,10 @@
         <v>1006</v>
       </c>
       <c r="B499" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C499">
-        <v>0.3486834828542944</v>
+        <v>0.3473363146281323</v>
       </c>
       <c r="D499" t="s">
         <v>7</v>
@@ -12826,7 +12826,7 @@
         <v>6</v>
       </c>
       <c r="C500">
-        <v>0.4112276850676133</v>
+        <v>0.4092536484552595</v>
       </c>
       <c r="D500" t="s">
         <v>7</v>
@@ -12840,10 +12840,10 @@
         <v>1010</v>
       </c>
       <c r="B501" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C501">
-        <v>0.4601981222354937</v>
+        <v>0.4559208647188595</v>
       </c>
       <c r="D501" t="s">
         <v>7</v>
@@ -12860,7 +12860,7 @@
         <v>6</v>
       </c>
       <c r="C502">
-        <v>0.5836054112018614</v>
+        <v>0.5859153361517387</v>
       </c>
       <c r="D502" t="s">
         <v>7</v>
@@ -12874,10 +12874,10 @@
         <v>1014</v>
       </c>
       <c r="B503" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C503">
-        <v>0.365176899009903</v>
+        <v>0.3655756452781949</v>
       </c>
       <c r="D503" t="s">
         <v>7</v>
@@ -12891,10 +12891,10 @@
         <v>1016</v>
       </c>
       <c r="B504" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C504">
-        <v>0.3264336112518306</v>
+        <v>0.3259139402802484</v>
       </c>
       <c r="D504" t="s">
         <v>7</v>
@@ -12911,7 +12911,7 @@
         <v>6</v>
       </c>
       <c r="C505">
-        <v>0.4429187318397071</v>
+        <v>0.4421371198487041</v>
       </c>
       <c r="D505" t="s">
         <v>7</v>
@@ -12925,10 +12925,10 @@
         <v>1020</v>
       </c>
       <c r="B506" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C506">
-        <v>0.5368300089996419</v>
+        <v>0.5415265344275999</v>
       </c>
       <c r="D506" t="s">
         <v>7</v>
@@ -12945,7 +12945,7 @@
         <v>6</v>
       </c>
       <c r="C507">
-        <v>0.3288672015113308</v>
+        <v>0.3271961855419739</v>
       </c>
       <c r="D507" t="s">
         <v>7</v>
@@ -12959,10 +12959,10 @@
         <v>1024</v>
       </c>
       <c r="B508" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C508">
-        <v>0.3051134955150344</v>
+        <v>0.3002024932735842</v>
       </c>
       <c r="D508" t="s">
         <v>7</v>
@@ -12976,10 +12976,10 @@
         <v>1026</v>
       </c>
       <c r="B509" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C509">
-        <v>0.4376606598543472</v>
+        <v>0.4314932619870074</v>
       </c>
       <c r="D509" t="s">
         <v>7</v>
@@ -12993,10 +12993,10 @@
         <v>1028</v>
       </c>
       <c r="B510" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C510">
-        <v>0.34707765017382</v>
+        <v>0.3427363849589825</v>
       </c>
       <c r="D510" t="s">
         <v>7</v>
@@ -13013,7 +13013,7 @@
         <v>44</v>
       </c>
       <c r="C511">
-        <v>0.3569368441463345</v>
+        <v>0.3535673995779168</v>
       </c>
       <c r="D511" t="s">
         <v>7</v>
@@ -13030,7 +13030,7 @@
         <v>6</v>
       </c>
       <c r="C512">
-        <v>0.2969789205590913</v>
+        <v>0.3002673907898285</v>
       </c>
       <c r="D512" t="s">
         <v>7</v>
@@ -13047,7 +13047,7 @@
         <v>6</v>
       </c>
       <c r="C513">
-        <v>0.34057393711725</v>
+        <v>0.3413723231438398</v>
       </c>
       <c r="D513" t="s">
         <v>7</v>
@@ -13064,7 +13064,7 @@
         <v>44</v>
       </c>
       <c r="C514">
-        <v>0.3971411582633853</v>
+        <v>0.3993981488048282</v>
       </c>
       <c r="D514" t="s">
         <v>7</v>
@@ -13081,7 +13081,7 @@
         <v>6</v>
       </c>
       <c r="C515">
-        <v>0.4917310945405247</v>
+        <v>0.4946350041080018</v>
       </c>
       <c r="D515" t="s">
         <v>7</v>
@@ -13095,10 +13095,10 @@
         <v>1040</v>
       </c>
       <c r="B516" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C516">
-        <v>0.3136582803182621</v>
+        <v>0.313344543960601</v>
       </c>
       <c r="D516" t="s">
         <v>7</v>
@@ -13112,10 +13112,10 @@
         <v>1042</v>
       </c>
       <c r="B517" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C517">
-        <v>0.3503131220087068</v>
+        <v>0.3494282893047542</v>
       </c>
       <c r="D517" t="s">
         <v>7</v>
@@ -13129,10 +13129,10 @@
         <v>1044</v>
       </c>
       <c r="B518" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C518">
-        <v>0.2940497908881016</v>
+        <v>0.2894352457172066</v>
       </c>
       <c r="D518" t="s">
         <v>7</v>
@@ -13149,7 +13149,7 @@
         <v>44</v>
       </c>
       <c r="C519">
-        <v>0.5047022096912473</v>
+        <v>0.5045656618302092</v>
       </c>
       <c r="D519" t="s">
         <v>7</v>
@@ -13163,10 +13163,10 @@
         <v>1048</v>
       </c>
       <c r="B520" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C520">
-        <v>0.3216992008616841</v>
+        <v>0.3226996103351161</v>
       </c>
       <c r="D520" t="s">
         <v>7</v>
@@ -13180,10 +13180,10 @@
         <v>1050</v>
       </c>
       <c r="B521" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C521">
-        <v>0.310527825753201</v>
+        <v>0.3092775133576188</v>
       </c>
       <c r="D521" t="s">
         <v>7</v>
@@ -13197,10 +13197,10 @@
         <v>1052</v>
       </c>
       <c r="B522" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C522">
-        <v>0.3564247909780286</v>
+        <v>0.3603891710480687</v>
       </c>
       <c r="D522" t="s">
         <v>7</v>
@@ -13217,7 +13217,7 @@
         <v>6</v>
       </c>
       <c r="C523">
-        <v>0.4198122536664113</v>
+        <v>0.4216905500519827</v>
       </c>
       <c r="D523" t="s">
         <v>7</v>
@@ -13234,7 +13234,7 @@
         <v>6</v>
       </c>
       <c r="C524">
-        <v>0.2813070831821995</v>
+        <v>0.2801995045975289</v>
       </c>
       <c r="D524" t="s">
         <v>7</v>
@@ -13251,7 +13251,7 @@
         <v>44</v>
       </c>
       <c r="C525">
-        <v>0.3983722144391702</v>
+        <v>0.3987948290483855</v>
       </c>
       <c r="D525" t="s">
         <v>7</v>
@@ -13268,7 +13268,7 @@
         <v>44</v>
       </c>
       <c r="C526">
-        <v>0.4721857952407336</v>
+        <v>0.4725154894524636</v>
       </c>
       <c r="D526" t="s">
         <v>7</v>
@@ -13282,10 +13282,10 @@
         <v>1062</v>
       </c>
       <c r="B527" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C527">
-        <v>0.3775557651091793</v>
+        <v>0.3828456881772203</v>
       </c>
       <c r="D527" t="s">
         <v>7</v>
@@ -13302,7 +13302,7 @@
         <v>6</v>
       </c>
       <c r="C528">
-        <v>0.440987956824349</v>
+        <v>0.4407892123357277</v>
       </c>
       <c r="D528" t="s">
         <v>7</v>
@@ -13316,10 +13316,10 @@
         <v>1066</v>
       </c>
       <c r="B529" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C529">
-        <v>0.3108516095748026</v>
+        <v>0.3099299548219754</v>
       </c>
       <c r="D529" t="s">
         <v>7</v>
@@ -13336,7 +13336,7 @@
         <v>44</v>
       </c>
       <c r="C530">
-        <v>0.487862554668997</v>
+        <v>0.4855798583865336</v>
       </c>
       <c r="D530" t="s">
         <v>7</v>
@@ -13353,7 +13353,7 @@
         <v>44</v>
       </c>
       <c r="C531">
-        <v>0.5275553520207631</v>
+        <v>0.5237103317289084</v>
       </c>
       <c r="D531" t="s">
         <v>7</v>
@@ -13367,10 +13367,10 @@
         <v>1072</v>
       </c>
       <c r="B532" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C532">
-        <v>0.2840763969193159</v>
+        <v>0.2842505801227574</v>
       </c>
       <c r="D532" t="s">
         <v>7</v>
@@ -13384,10 +13384,10 @@
         <v>1074</v>
       </c>
       <c r="B533" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C533">
-        <v>0.4818803662081564</v>
+        <v>0.4938399360550284</v>
       </c>
       <c r="D533" t="s">
         <v>7</v>
@@ -13401,10 +13401,10 @@
         <v>1076</v>
       </c>
       <c r="B534" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C534">
-        <v>0.3321191635331257</v>
+        <v>0.3363267941904955</v>
       </c>
       <c r="D534" t="s">
         <v>7</v>
@@ -13421,7 +13421,7 @@
         <v>6</v>
       </c>
       <c r="C535">
-        <v>0.3024789581456784</v>
+        <v>0.3025759772614587</v>
       </c>
       <c r="D535" t="s">
         <v>7</v>
@@ -13435,10 +13435,10 @@
         <v>1080</v>
       </c>
       <c r="B536" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C536">
-        <v>0.3041959921400835</v>
+        <v>0.3037834462919964</v>
       </c>
       <c r="D536" t="s">
         <v>7</v>
@@ -13455,7 +13455,7 @@
         <v>6</v>
       </c>
       <c r="C537">
-        <v>0.3668614860704464</v>
+        <v>0.3655065498237841</v>
       </c>
       <c r="D537" t="s">
         <v>7</v>
@@ -13469,10 +13469,10 @@
         <v>1084</v>
       </c>
       <c r="B538" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C538">
-        <v>0.2836312125611357</v>
+        <v>0.2837305469161654</v>
       </c>
       <c r="D538" t="s">
         <v>7</v>
@@ -13489,7 +13489,7 @@
         <v>6</v>
       </c>
       <c r="C539">
-        <v>0.299266095890961</v>
+        <v>0.2938396228527492</v>
       </c>
       <c r="D539" t="s">
         <v>7</v>
@@ -13503,10 +13503,10 @@
         <v>1088</v>
       </c>
       <c r="B540" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C540">
-        <v>0.2642925258742722</v>
+        <v>0.2650870010674514</v>
       </c>
       <c r="D540" t="s">
         <v>7</v>
@@ -13523,7 +13523,7 @@
         <v>6</v>
       </c>
       <c r="C541">
-        <v>0.3948372122047223</v>
+        <v>0.396539798281041</v>
       </c>
       <c r="D541" t="s">
         <v>7</v>
@@ -13540,7 +13540,7 @@
         <v>44</v>
       </c>
       <c r="C542">
-        <v>0.3647680623669811</v>
+        <v>0.363629798273096</v>
       </c>
       <c r="D542" t="s">
         <v>7</v>
@@ -13557,7 +13557,7 @@
         <v>6</v>
       </c>
       <c r="C543">
-        <v>0.3928040106299726</v>
+        <v>0.3929996676849817</v>
       </c>
       <c r="D543" t="s">
         <v>7</v>
@@ -13574,7 +13574,7 @@
         <v>6</v>
       </c>
       <c r="C544">
-        <v>0.3879714548887081</v>
+        <v>0.3883015089791447</v>
       </c>
       <c r="D544" t="s">
         <v>7</v>
@@ -13843,7 +13843,7 @@
         <v>1143</v>
       </c>
       <c r="C563">
-        <v>0.2803984501131189</v>
+        <v>0.2864704823337463</v>
       </c>
       <c r="D563" t="s">
         <v>1144</v>
@@ -13860,7 +13860,7 @@
         <v>1143</v>
       </c>
       <c r="C564">
-        <v>0.3092805950009559</v>
+        <v>0.3258036828282375</v>
       </c>
       <c r="D564" t="s">
         <v>1144</v>
@@ -13877,7 +13877,7 @@
         <v>1143</v>
       </c>
       <c r="C565">
-        <v>0.256921405594602</v>
+        <v>0.2802473464546237</v>
       </c>
       <c r="D565" t="s">
         <v>1144</v>
@@ -13894,7 +13894,7 @@
         <v>1143</v>
       </c>
       <c r="C566">
-        <v>0.3368119958880676</v>
+        <v>0.3414880232722243</v>
       </c>
       <c r="D566" t="s">
         <v>1144</v>
@@ -13911,7 +13911,7 @@
         <v>1143</v>
       </c>
       <c r="C567">
-        <v>0.3716357228389356</v>
+        <v>0.38457179624773</v>
       </c>
       <c r="D567" t="s">
         <v>1144</v>
@@ -13928,7 +13928,7 @@
         <v>1143</v>
       </c>
       <c r="C568">
-        <v>0.3904385591676873</v>
+        <v>0.3986569939196357</v>
       </c>
       <c r="D568" t="s">
         <v>1144</v>
@@ -13945,7 +13945,7 @@
         <v>1143</v>
       </c>
       <c r="C569">
-        <v>0.2607309313619816</v>
+        <v>0.2780028687651764</v>
       </c>
       <c r="D569" t="s">
         <v>1144</v>
@@ -13962,7 +13962,7 @@
         <v>1143</v>
       </c>
       <c r="C570">
-        <v>0.3004020790986021</v>
+        <v>0.2979173536637857</v>
       </c>
       <c r="D570" t="s">
         <v>1144</v>
@@ -13979,7 +13979,7 @@
         <v>1143</v>
       </c>
       <c r="C571">
-        <v>0.2859597753547766</v>
+        <v>0.289328318799762</v>
       </c>
       <c r="D571" t="s">
         <v>1144</v>
@@ -13996,7 +13996,7 @@
         <v>6</v>
       </c>
       <c r="C572">
-        <v>0.2841602866421246</v>
+        <v>0.2689528970444114</v>
       </c>
       <c r="D572" t="s">
         <v>1144</v>
@@ -14013,7 +14013,7 @@
         <v>1143</v>
       </c>
       <c r="C573">
-        <v>0.325259877481746</v>
+        <v>0.3310679927158143</v>
       </c>
       <c r="D573" t="s">
         <v>1144</v>
@@ -14030,7 +14030,7 @@
         <v>44</v>
       </c>
       <c r="C574">
-        <v>0.3537319654279315</v>
+        <v>0.3745233055121229</v>
       </c>
       <c r="D574" t="s">
         <v>1144</v>
@@ -14047,7 +14047,7 @@
         <v>1143</v>
       </c>
       <c r="C575">
-        <v>0.3552317448314531</v>
+        <v>0.3609503931535211</v>
       </c>
       <c r="D575" t="s">
         <v>1144</v>
@@ -14064,7 +14064,7 @@
         <v>1143</v>
       </c>
       <c r="C576">
-        <v>0.3455273416874772</v>
+        <v>0.3614134210710114</v>
       </c>
       <c r="D576" t="s">
         <v>1144</v>
@@ -14081,7 +14081,7 @@
         <v>6</v>
       </c>
       <c r="C577">
-        <v>0.3362610396367837</v>
+        <v>0.3547044166050438</v>
       </c>
       <c r="D577" t="s">
         <v>1144</v>
@@ -14098,7 +14098,7 @@
         <v>1143</v>
       </c>
       <c r="C578">
-        <v>0.3775852748406982</v>
+        <v>0.3860022077826153</v>
       </c>
       <c r="D578" t="s">
         <v>1144</v>
@@ -14115,7 +14115,7 @@
         <v>1143</v>
       </c>
       <c r="C579">
-        <v>0.3384994274145131</v>
+        <v>0.348853621382039</v>
       </c>
       <c r="D579" t="s">
         <v>1144</v>
@@ -14129,10 +14129,10 @@
         <v>1178</v>
       </c>
       <c r="B580" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C580">
-        <v>0.3346548992088073</v>
+        <v>0.3082028561276396</v>
       </c>
       <c r="D580" t="s">
         <v>1144</v>
@@ -14149,7 +14149,7 @@
         <v>1143</v>
       </c>
       <c r="C581">
-        <v>0.4416044964795715</v>
+        <v>0.4507354408416883</v>
       </c>
       <c r="D581" t="s">
         <v>1144</v>
@@ -14166,7 +14166,7 @@
         <v>1143</v>
       </c>
       <c r="C582">
-        <v>0.302683507961262</v>
+        <v>0.3111926056353069</v>
       </c>
       <c r="D582" t="s">
         <v>1144</v>
@@ -14183,7 +14183,7 @@
         <v>1143</v>
       </c>
       <c r="C583">
-        <v>0.3664093077371354</v>
+        <v>0.3760716036414755</v>
       </c>
       <c r="D583" t="s">
         <v>1144</v>
@@ -14200,7 +14200,7 @@
         <v>1143</v>
       </c>
       <c r="C584">
-        <v>0.2892883416050688</v>
+        <v>0.3054729845603847</v>
       </c>
       <c r="D584" t="s">
         <v>1144</v>
@@ -14217,7 +14217,7 @@
         <v>1143</v>
       </c>
       <c r="C585">
-        <v>0.3947646890973808</v>
+        <v>0.4213316524519853</v>
       </c>
       <c r="D585" t="s">
         <v>1144</v>
@@ -14234,7 +14234,7 @@
         <v>1143</v>
       </c>
       <c r="C586">
-        <v>0.2900716192888082</v>
+        <v>0.2866332683638242</v>
       </c>
       <c r="D586" t="s">
         <v>1144</v>
@@ -14251,7 +14251,7 @@
         <v>6</v>
       </c>
       <c r="C587">
-        <v>0.27675764322906</v>
+        <v>0.2806803719891457</v>
       </c>
       <c r="D587" t="s">
         <v>1144</v>
@@ -14268,7 +14268,7 @@
         <v>1143</v>
       </c>
       <c r="C588">
-        <v>0.3069050695091165</v>
+        <v>0.3083120608557081</v>
       </c>
       <c r="D588" t="s">
         <v>1144</v>
@@ -14285,7 +14285,7 @@
         <v>44</v>
       </c>
       <c r="C589">
-        <v>0.3562167389466532</v>
+        <v>0.3832589754029783</v>
       </c>
       <c r="D589" t="s">
         <v>1144</v>
@@ -14302,7 +14302,7 @@
         <v>6</v>
       </c>
       <c r="C590">
-        <v>0.4090849047517601</v>
+        <v>0.3560520258445286</v>
       </c>
       <c r="D590" t="s">
         <v>1144</v>
@@ -14319,7 +14319,7 @@
         <v>1143</v>
       </c>
       <c r="C591">
-        <v>0.5023077918955595</v>
+        <v>0.5146076658102717</v>
       </c>
       <c r="D591" t="s">
         <v>1144</v>
@@ -14336,7 +14336,7 @@
         <v>1143</v>
       </c>
       <c r="C592">
-        <v>0.3747668557508136</v>
+        <v>0.3556858223917162</v>
       </c>
       <c r="D592" t="s">
         <v>1144</v>
@@ -14353,7 +14353,7 @@
         <v>1143</v>
       </c>
       <c r="C593">
-        <v>0.6469595193403909</v>
+        <v>0.6490499622100746</v>
       </c>
       <c r="D593" t="s">
         <v>1144</v>
@@ -14370,7 +14370,7 @@
         <v>1143</v>
       </c>
       <c r="C594">
-        <v>0.4135152757137049</v>
+        <v>0.4378732857975119</v>
       </c>
       <c r="D594" t="s">
         <v>1144</v>
@@ -14387,7 +14387,7 @@
         <v>6</v>
       </c>
       <c r="C595">
-        <v>0.3443778027926068</v>
+        <v>0.2942098408724645</v>
       </c>
       <c r="D595" t="s">
         <v>1144</v>
@@ -14404,7 +14404,7 @@
         <v>1143</v>
       </c>
       <c r="C596">
-        <v>0.4181541506198702</v>
+        <v>0.430622158920845</v>
       </c>
       <c r="D596" t="s">
         <v>1144</v>
@@ -14421,7 +14421,7 @@
         <v>6</v>
       </c>
       <c r="C597">
-        <v>0.3371137441489442</v>
+        <v>0.3303272811547263</v>
       </c>
       <c r="D597" t="s">
         <v>1144</v>
@@ -14435,10 +14435,10 @@
         <v>1214</v>
       </c>
       <c r="B598" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C598">
-        <v>0.2819373793752624</v>
+        <v>0.2577889525169242</v>
       </c>
       <c r="D598" t="s">
         <v>1144</v>
@@ -14455,7 +14455,7 @@
         <v>1143</v>
       </c>
       <c r="C599">
-        <v>0.2552408607343494</v>
+        <v>0.2579959382769951</v>
       </c>
       <c r="D599" t="s">
         <v>1144</v>
@@ -14472,7 +14472,7 @@
         <v>1143</v>
       </c>
       <c r="C600">
-        <v>0.2719958055063219</v>
+        <v>0.3016416697033701</v>
       </c>
       <c r="D600" t="s">
         <v>1144</v>
@@ -14486,10 +14486,10 @@
         <v>1220</v>
       </c>
       <c r="B601" t="s">
-        <v>44</v>
+        <v>1143</v>
       </c>
       <c r="C601">
-        <v>0.2939756134445283</v>
+        <v>0.2676406225064724</v>
       </c>
       <c r="D601" t="s">
         <v>1144</v>
@@ -14506,7 +14506,7 @@
         <v>1143</v>
       </c>
       <c r="C602">
-        <v>0.3409790867645696</v>
+        <v>0.3545593487111702</v>
       </c>
       <c r="D602" t="s">
         <v>1144</v>
@@ -14523,7 +14523,7 @@
         <v>1143</v>
       </c>
       <c r="C603">
-        <v>0.2718135376803398</v>
+        <v>0.2835193350593359</v>
       </c>
       <c r="D603" t="s">
         <v>1144</v>
@@ -14540,7 +14540,7 @@
         <v>6</v>
       </c>
       <c r="C604">
-        <v>0.3147277535135263</v>
+        <v>0.3114415183577908</v>
       </c>
       <c r="D604" t="s">
         <v>1144</v>
@@ -14557,7 +14557,7 @@
         <v>44</v>
       </c>
       <c r="C605">
-        <v>0.3213334863754314</v>
+        <v>0.2814751866609839</v>
       </c>
       <c r="D605" t="s">
         <v>1144</v>
@@ -14574,7 +14574,7 @@
         <v>6</v>
       </c>
       <c r="C606">
-        <v>0.3290302583714077</v>
+        <v>0.334552042583307</v>
       </c>
       <c r="D606" t="s">
         <v>1144</v>
@@ -14588,10 +14588,10 @@
         <v>1232</v>
       </c>
       <c r="B607" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C607">
-        <v>0.3096853313312492</v>
+        <v>0.3444961238169109</v>
       </c>
       <c r="D607" t="s">
         <v>1144</v>
@@ -14608,7 +14608,7 @@
         <v>6</v>
       </c>
       <c r="C608">
-        <v>0.3018577569089774</v>
+        <v>0.3026401795431786</v>
       </c>
       <c r="D608" t="s">
         <v>1144</v>
@@ -14622,10 +14622,10 @@
         <v>1236</v>
       </c>
       <c r="B609" t="s">
-        <v>1143</v>
+        <v>6</v>
       </c>
       <c r="C609">
-        <v>0.2549025660212396</v>
+        <v>0.3426008937160536</v>
       </c>
       <c r="D609" t="s">
         <v>1144</v>
@@ -14639,10 +14639,10 @@
         <v>1238</v>
       </c>
       <c r="B610" t="s">
-        <v>6</v>
+        <v>1143</v>
       </c>
       <c r="C610">
-        <v>0.2639519734251855</v>
+        <v>0.2742726267087609</v>
       </c>
       <c r="D610" t="s">
         <v>1144</v>
@@ -14659,7 +14659,7 @@
         <v>44</v>
       </c>
       <c r="C611">
-        <v>0.4933001374964287</v>
+        <v>0.5058837969616241</v>
       </c>
       <c r="D611" t="s">
         <v>1144</v>
@@ -14676,7 +14676,7 @@
         <v>44</v>
       </c>
       <c r="C612">
-        <v>0.3520445191535814</v>
+        <v>0.3881136385797994</v>
       </c>
       <c r="D612" t="s">
         <v>1144</v>
@@ -14693,7 +14693,7 @@
         <v>1143</v>
       </c>
       <c r="C613">
-        <v>0.3193394794373632</v>
+        <v>0.3396631312405216</v>
       </c>
       <c r="D613" t="s">
         <v>1144</v>
@@ -14710,7 +14710,7 @@
         <v>1143</v>
       </c>
       <c r="C614">
-        <v>0.4104896303327592</v>
+        <v>0.4226724022552727</v>
       </c>
       <c r="D614" t="s">
         <v>1144</v>
@@ -14724,10 +14724,10 @@
         <v>1248</v>
       </c>
       <c r="B615" t="s">
-        <v>1143</v>
+        <v>17</v>
       </c>
       <c r="C615">
-        <v>0.3257694865057319</v>
+        <v>0.3534305838872275</v>
       </c>
       <c r="D615" t="s">
         <v>1144</v>
@@ -14744,7 +14744,7 @@
         <v>1143</v>
       </c>
       <c r="C616">
-        <v>0.3997286652450292</v>
+        <v>0.4004570094405502</v>
       </c>
       <c r="D616" t="s">
         <v>1144</v>
@@ -14761,7 +14761,7 @@
         <v>1143</v>
       </c>
       <c r="C617">
-        <v>0.3164903933280043</v>
+        <v>0.3346711187907207</v>
       </c>
       <c r="D617" t="s">
         <v>1144</v>
@@ -14775,10 +14775,10 @@
         <v>1254</v>
       </c>
       <c r="B618" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C618">
-        <v>0.3550674746761407</v>
+        <v>0.3427179215581034</v>
       </c>
       <c r="D618" t="s">
         <v>1144</v>
@@ -14795,7 +14795,7 @@
         <v>1143</v>
       </c>
       <c r="C619">
-        <v>0.4240259759058843</v>
+        <v>0.4080337399457341</v>
       </c>
       <c r="D619" t="s">
         <v>1144</v>
@@ -14809,10 +14809,10 @@
         <v>1258</v>
       </c>
       <c r="B620" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C620">
-        <v>0.3106325173216741</v>
+        <v>0.3176749237790665</v>
       </c>
       <c r="D620" t="s">
         <v>1259</v>
@@ -14826,10 +14826,10 @@
         <v>1261</v>
       </c>
       <c r="B621" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C621">
-        <v>0.3402506294431389</v>
+        <v>0.3898875927790148</v>
       </c>
       <c r="D621" t="s">
         <v>1259</v>
@@ -14843,10 +14843,10 @@
         <v>1263</v>
       </c>
       <c r="B622" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C622">
-        <v>0.2637580919092145</v>
+        <v>0.281484563416065</v>
       </c>
       <c r="D622" t="s">
         <v>1259</v>
@@ -14860,78 +14860,78 @@
         <v>1265</v>
       </c>
       <c r="B623" t="s">
-        <v>15</v>
+        <v>1266</v>
       </c>
       <c r="C623">
-        <v>0.2167691682035335</v>
+        <v>0.2591063611341231</v>
       </c>
       <c r="D623" t="s">
         <v>1259</v>
       </c>
       <c r="E623" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="624" spans="1:5">
       <c r="A624" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="B624" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C624">
-        <v>0.2875202091305907</v>
+        <v>0.2652711631454605</v>
       </c>
       <c r="D624" t="s">
         <v>1259</v>
       </c>
       <c r="E624" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="625" spans="1:5">
       <c r="A625" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="B625" t="s">
-        <v>10</v>
+        <v>1266</v>
       </c>
       <c r="C625">
-        <v>0.2384834338184541</v>
+        <v>0.2552321976063709</v>
       </c>
       <c r="D625" t="s">
         <v>1259</v>
       </c>
       <c r="E625" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="626" spans="1:5">
       <c r="A626" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="B626" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C626">
-        <v>0.3311244110486929</v>
+        <v>0.340685697596409</v>
       </c>
       <c r="D626" t="s">
         <v>1259</v>
       </c>
       <c r="E626" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="627" spans="1:5">
       <c r="A627" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="B627" t="s">
-        <v>1274</v>
+        <v>1266</v>
       </c>
       <c r="C627">
-        <v>0.2464065981917523</v>
+        <v>0.340384197342984</v>
       </c>
       <c r="D627" t="s">
         <v>1259</v>
@@ -14945,10 +14945,10 @@
         <v>1276</v>
       </c>
       <c r="B628" t="s">
-        <v>6</v>
+        <v>1266</v>
       </c>
       <c r="C628">
-        <v>0.2378883648181562</v>
+        <v>0.2527012084086105</v>
       </c>
       <c r="D628" t="s">
         <v>1259</v>
@@ -14962,10 +14962,10 @@
         <v>1278</v>
       </c>
       <c r="B629" t="s">
-        <v>6</v>
+        <v>1266</v>
       </c>
       <c r="C629">
-        <v>0.2680686809974087</v>
+        <v>0.254551825902422</v>
       </c>
       <c r="D629" t="s">
         <v>1259</v>
@@ -14979,10 +14979,10 @@
         <v>1280</v>
       </c>
       <c r="B630" t="s">
-        <v>1274</v>
+        <v>79</v>
       </c>
       <c r="C630">
-        <v>0.3390367028653101</v>
+        <v>0.3800981562024544</v>
       </c>
       <c r="D630" t="s">
         <v>1259</v>
@@ -14996,10 +14996,10 @@
         <v>1282</v>
       </c>
       <c r="B631" t="s">
-        <v>1274</v>
+        <v>1266</v>
       </c>
       <c r="C631">
-        <v>0.3136100690536355</v>
+        <v>0.3504948428899604</v>
       </c>
       <c r="D631" t="s">
         <v>1259</v>
@@ -15013,10 +15013,10 @@
         <v>1284</v>
       </c>
       <c r="B632" t="s">
-        <v>1274</v>
+        <v>1266</v>
       </c>
       <c r="C632">
-        <v>0.3598350111353313</v>
+        <v>0.3820029269959446</v>
       </c>
       <c r="D632" t="s">
         <v>1259</v>
@@ -15030,10 +15030,10 @@
         <v>1286</v>
       </c>
       <c r="B633" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C633">
-        <v>0.266914550822311</v>
+        <v>0.2664997068169506</v>
       </c>
       <c r="D633" t="s">
         <v>1259</v>
@@ -15047,10 +15047,10 @@
         <v>1288</v>
       </c>
       <c r="B634" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C634">
-        <v>0.4038390827828977</v>
+        <v>0.4352193923397861</v>
       </c>
       <c r="D634" t="s">
         <v>1259</v>
@@ -15064,10 +15064,10 @@
         <v>1290</v>
       </c>
       <c r="B635" t="s">
-        <v>1274</v>
+        <v>1266</v>
       </c>
       <c r="C635">
-        <v>0.4318090063306752</v>
+        <v>0.4256090970699435</v>
       </c>
       <c r="D635" t="s">
         <v>1259</v>
@@ -15084,7 +15084,7 @@
         <v>6</v>
       </c>
       <c r="C636">
-        <v>0.3777084470536536</v>
+        <v>0.2143974739034276</v>
       </c>
       <c r="D636" t="s">
         <v>1259</v>
@@ -15098,10 +15098,10 @@
         <v>1294</v>
       </c>
       <c r="B637" t="s">
-        <v>1274</v>
+        <v>10</v>
       </c>
       <c r="C637">
-        <v>0.2893100648345865</v>
+        <v>0.3240619832987795</v>
       </c>
       <c r="D637" t="s">
         <v>1259</v>
@@ -15115,10 +15115,10 @@
         <v>1296</v>
       </c>
       <c r="B638" t="s">
-        <v>1274</v>
+        <v>1266</v>
       </c>
       <c r="C638">
-        <v>0.4219910253724234</v>
+        <v>0.5155898349987399</v>
       </c>
       <c r="D638" t="s">
         <v>1259</v>
@@ -15135,7 +15135,7 @@
         <v>10</v>
       </c>
       <c r="C639">
-        <v>0.3339393036395892</v>
+        <v>0.3168641342733758</v>
       </c>
       <c r="D639" t="s">
         <v>1259</v>
@@ -15149,10 +15149,10 @@
         <v>1300</v>
       </c>
       <c r="B640" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C640">
-        <v>0.2944888790848084</v>
+        <v>0.3172043456001913</v>
       </c>
       <c r="D640" t="s">
         <v>1259</v>
@@ -15166,10 +15166,10 @@
         <v>1302</v>
       </c>
       <c r="B641" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C641">
-        <v>0.2537462915413167</v>
+        <v>0.2746078490612653</v>
       </c>
       <c r="D641" t="s">
         <v>1259</v>
@@ -15183,10 +15183,10 @@
         <v>1304</v>
       </c>
       <c r="B642" t="s">
-        <v>1274</v>
+        <v>1266</v>
       </c>
       <c r="C642">
-        <v>0.2828784524231167</v>
+        <v>0.3151792714617053</v>
       </c>
       <c r="D642" t="s">
         <v>1259</v>
@@ -15200,10 +15200,10 @@
         <v>1306</v>
       </c>
       <c r="B643" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C643">
-        <v>0.3280054383401928</v>
+        <v>0.34295009322101</v>
       </c>
       <c r="D643" t="s">
         <v>1259</v>
@@ -15217,10 +15217,10 @@
         <v>1308</v>
       </c>
       <c r="B644" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C644">
-        <v>0.2792961236893269</v>
+        <v>0.3013268602348379</v>
       </c>
       <c r="D644" t="s">
         <v>1259</v>
@@ -15234,10 +15234,10 @@
         <v>1310</v>
       </c>
       <c r="B645" t="s">
-        <v>15</v>
+        <v>1266</v>
       </c>
       <c r="C645">
-        <v>0.2519659452945653</v>
+        <v>0.2537664187195656</v>
       </c>
       <c r="D645" t="s">
         <v>1259</v>
@@ -15251,10 +15251,10 @@
         <v>1312</v>
       </c>
       <c r="B646" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C646">
-        <v>0.3486354291654009</v>
+        <v>0.4133748809203024</v>
       </c>
       <c r="D646" t="s">
         <v>1259</v>
@@ -15268,10 +15268,10 @@
         <v>1314</v>
       </c>
       <c r="B647" t="s">
-        <v>6</v>
+        <v>1266</v>
       </c>
       <c r="C647">
-        <v>0.2953960648232236</v>
+        <v>0.2736903771873888</v>
       </c>
       <c r="D647" t="s">
         <v>1259</v>
@@ -15285,10 +15285,10 @@
         <v>1316</v>
       </c>
       <c r="B648" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C648">
-        <v>0.2949517727973148</v>
+        <v>0.3345951658160509</v>
       </c>
       <c r="D648" t="s">
         <v>1259</v>
@@ -15302,10 +15302,10 @@
         <v>1318</v>
       </c>
       <c r="B649" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C649">
-        <v>0.3393039821027033</v>
+        <v>0.3586998441438936</v>
       </c>
       <c r="D649" t="s">
         <v>1259</v>
@@ -15319,10 +15319,10 @@
         <v>1320</v>
       </c>
       <c r="B650" t="s">
-        <v>6</v>
+        <v>1266</v>
       </c>
       <c r="C650">
-        <v>0.2713212016688576</v>
+        <v>0.2737113174241471</v>
       </c>
       <c r="D650" t="s">
         <v>1259</v>
@@ -15336,10 +15336,10 @@
         <v>1322</v>
       </c>
       <c r="B651" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C651">
-        <v>0.3209404141003637</v>
+        <v>0.333872735611434</v>
       </c>
       <c r="D651" t="s">
         <v>1259</v>
@@ -15368,18 +15368,18 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B2">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B3">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -15387,7 +15387,7 @@
         <v>79</v>
       </c>
       <c r="B4">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -15395,7 +15395,7 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>245</v>
+        <v>240</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -15403,23 +15403,23 @@
         <v>44</v>
       </c>
       <c r="B6">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>398</v>
+        <v>126</v>
       </c>
       <c r="B7">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>1274</v>
+        <v>1266</v>
       </c>
       <c r="B8">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:2">

--- a/frontend/data/uk_election_predictions.xlsx
+++ b/frontend/data/uk_election_predictions.xlsx
@@ -47,30 +47,30 @@
     <t>aldridge-brownhills</t>
   </si>
   <si>
+    <t>Conservative</t>
+  </si>
+  <si>
+    <t>E14001064</t>
+  </si>
+  <si>
+    <t>altrincham and sale west</t>
+  </si>
+  <si>
+    <t>E14001065</t>
+  </si>
+  <si>
+    <t>amber valley</t>
+  </si>
+  <si>
     <t>Brexit Party/Reform UK</t>
   </si>
   <si>
-    <t>E14001064</t>
-  </si>
-  <si>
-    <t>altrincham and sale west</t>
-  </si>
-  <si>
-    <t>E14001065</t>
-  </si>
-  <si>
-    <t>amber valley</t>
-  </si>
-  <si>
     <t>E14001066</t>
   </si>
   <si>
     <t>arundel and south downs</t>
   </si>
   <si>
-    <t>Conservative</t>
-  </si>
-  <si>
     <t>E14001067</t>
   </si>
   <si>
@@ -254,448 +254,448 @@
     <t>birmingham northfield</t>
   </si>
   <si>
+    <t>E14001097</t>
+  </si>
+  <si>
+    <t>birmingham perry barr</t>
+  </si>
+  <si>
+    <t>E14001098</t>
+  </si>
+  <si>
+    <t>birmingham selly oak</t>
+  </si>
+  <si>
+    <t>E14001099</t>
+  </si>
+  <si>
+    <t>birmingham yardley</t>
+  </si>
+  <si>
+    <t>E14001100</t>
+  </si>
+  <si>
+    <t>bishop auckland</t>
+  </si>
+  <si>
+    <t>E14001101</t>
+  </si>
+  <si>
+    <t>blackburn</t>
+  </si>
+  <si>
+    <t>E14001102</t>
+  </si>
+  <si>
+    <t>blackley and middleton south</t>
+  </si>
+  <si>
+    <t>E14001103</t>
+  </si>
+  <si>
+    <t>blackpool north and fleetwood</t>
+  </si>
+  <si>
+    <t>E14001104</t>
+  </si>
+  <si>
+    <t>blackpool south</t>
+  </si>
+  <si>
+    <t>E14001105</t>
+  </si>
+  <si>
+    <t>blaydon and consett</t>
+  </si>
+  <si>
+    <t>E14001106</t>
+  </si>
+  <si>
+    <t>blyth and ashington</t>
+  </si>
+  <si>
+    <t>E14001107</t>
+  </si>
+  <si>
+    <t>bognor regis and littlehampton</t>
+  </si>
+  <si>
+    <t>E14001108</t>
+  </si>
+  <si>
+    <t>bolsover</t>
+  </si>
+  <si>
+    <t>E14001109</t>
+  </si>
+  <si>
+    <t>bolton north east</t>
+  </si>
+  <si>
+    <t>E14001110</t>
+  </si>
+  <si>
+    <t>bolton south and walkden</t>
+  </si>
+  <si>
+    <t>E14001111</t>
+  </si>
+  <si>
+    <t>bolton west</t>
+  </si>
+  <si>
+    <t>E14001112</t>
+  </si>
+  <si>
+    <t>bootle</t>
+  </si>
+  <si>
+    <t>E14001113</t>
+  </si>
+  <si>
+    <t>boston and skegness</t>
+  </si>
+  <si>
+    <t>E14001114</t>
+  </si>
+  <si>
+    <t>bournemouth east</t>
+  </si>
+  <si>
+    <t>E14001115</t>
+  </si>
+  <si>
+    <t>bournemouth west</t>
+  </si>
+  <si>
+    <t>E14001116</t>
+  </si>
+  <si>
+    <t>bracknell</t>
+  </si>
+  <si>
+    <t>E14001117</t>
+  </si>
+  <si>
+    <t>bradford east</t>
+  </si>
+  <si>
+    <t>E14001118</t>
+  </si>
+  <si>
+    <t>bradford south</t>
+  </si>
+  <si>
+    <t>E14001119</t>
+  </si>
+  <si>
+    <t>bradford west</t>
+  </si>
+  <si>
+    <t>E14001120</t>
+  </si>
+  <si>
+    <t>braintree</t>
+  </si>
+  <si>
+    <t>E14001121</t>
+  </si>
+  <si>
+    <t>brent east</t>
+  </si>
+  <si>
+    <t>E14001122</t>
+  </si>
+  <si>
+    <t>brent west</t>
+  </si>
+  <si>
+    <t>E14001123</t>
+  </si>
+  <si>
+    <t>brentford and isleworth</t>
+  </si>
+  <si>
+    <t>E14001124</t>
+  </si>
+  <si>
+    <t>brentwood and ongar</t>
+  </si>
+  <si>
+    <t>E14001125</t>
+  </si>
+  <si>
+    <t>bridgwater</t>
+  </si>
+  <si>
+    <t>E14001126</t>
+  </si>
+  <si>
+    <t>bridlington and the wolds</t>
+  </si>
+  <si>
+    <t>E14001127</t>
+  </si>
+  <si>
+    <t>brigg and immingham</t>
+  </si>
+  <si>
+    <t>E14001128</t>
+  </si>
+  <si>
+    <t>brighton kemptown and peacehaven</t>
+  </si>
+  <si>
+    <t>E14001129</t>
+  </si>
+  <si>
+    <t>brighton pavilion</t>
+  </si>
+  <si>
     <t>Green Party</t>
   </si>
   <si>
-    <t>E14001097</t>
-  </si>
-  <si>
-    <t>birmingham perry barr</t>
-  </si>
-  <si>
-    <t>E14001098</t>
-  </si>
-  <si>
-    <t>birmingham selly oak</t>
-  </si>
-  <si>
-    <t>E14001099</t>
-  </si>
-  <si>
-    <t>birmingham yardley</t>
-  </si>
-  <si>
-    <t>E14001100</t>
-  </si>
-  <si>
-    <t>bishop auckland</t>
-  </si>
-  <si>
-    <t>E14001101</t>
-  </si>
-  <si>
-    <t>blackburn</t>
-  </si>
-  <si>
-    <t>E14001102</t>
-  </si>
-  <si>
-    <t>blackley and middleton south</t>
-  </si>
-  <si>
-    <t>E14001103</t>
-  </si>
-  <si>
-    <t>blackpool north and fleetwood</t>
-  </si>
-  <si>
-    <t>E14001104</t>
-  </si>
-  <si>
-    <t>blackpool south</t>
-  </si>
-  <si>
-    <t>E14001105</t>
-  </si>
-  <si>
-    <t>blaydon and consett</t>
-  </si>
-  <si>
-    <t>E14001106</t>
-  </si>
-  <si>
-    <t>blyth and ashington</t>
-  </si>
-  <si>
-    <t>E14001107</t>
-  </si>
-  <si>
-    <t>bognor regis and littlehampton</t>
-  </si>
-  <si>
-    <t>E14001108</t>
-  </si>
-  <si>
-    <t>bolsover</t>
-  </si>
-  <si>
-    <t>E14001109</t>
-  </si>
-  <si>
-    <t>bolton north east</t>
-  </si>
-  <si>
-    <t>E14001110</t>
-  </si>
-  <si>
-    <t>bolton south and walkden</t>
-  </si>
-  <si>
-    <t>E14001111</t>
-  </si>
-  <si>
-    <t>bolton west</t>
-  </si>
-  <si>
-    <t>E14001112</t>
-  </si>
-  <si>
-    <t>bootle</t>
-  </si>
-  <si>
-    <t>E14001113</t>
-  </si>
-  <si>
-    <t>boston and skegness</t>
-  </si>
-  <si>
-    <t>E14001114</t>
-  </si>
-  <si>
-    <t>bournemouth east</t>
-  </si>
-  <si>
-    <t>E14001115</t>
-  </si>
-  <si>
-    <t>bournemouth west</t>
-  </si>
-  <si>
-    <t>E14001116</t>
-  </si>
-  <si>
-    <t>bracknell</t>
-  </si>
-  <si>
-    <t>E14001117</t>
-  </si>
-  <si>
-    <t>bradford east</t>
-  </si>
-  <si>
-    <t>E14001118</t>
-  </si>
-  <si>
-    <t>bradford south</t>
-  </si>
-  <si>
-    <t>E14001119</t>
-  </si>
-  <si>
-    <t>bradford west</t>
+    <t>E14001130</t>
+  </si>
+  <si>
+    <t>bristol central</t>
+  </si>
+  <si>
+    <t>E14001131</t>
+  </si>
+  <si>
+    <t>bristol east</t>
+  </si>
+  <si>
+    <t>E14001132</t>
+  </si>
+  <si>
+    <t>bristol north east</t>
+  </si>
+  <si>
+    <t>E14001133</t>
+  </si>
+  <si>
+    <t>bristol north west</t>
+  </si>
+  <si>
+    <t>E14001134</t>
+  </si>
+  <si>
+    <t>bristol south</t>
+  </si>
+  <si>
+    <t>E14001135</t>
+  </si>
+  <si>
+    <t>broadland and fakenham</t>
+  </si>
+  <si>
+    <t>E14001136</t>
+  </si>
+  <si>
+    <t>bromley and biggin hill</t>
+  </si>
+  <si>
+    <t>E14001137</t>
+  </si>
+  <si>
+    <t>bromsgrove</t>
+  </si>
+  <si>
+    <t>E14001138</t>
+  </si>
+  <si>
+    <t>broxbourne</t>
+  </si>
+  <si>
+    <t>E14001139</t>
+  </si>
+  <si>
+    <t>broxtowe</t>
+  </si>
+  <si>
+    <t>E14001140</t>
+  </si>
+  <si>
+    <t>buckingham and bletchley</t>
+  </si>
+  <si>
+    <t>E14001141</t>
+  </si>
+  <si>
+    <t>burnley</t>
+  </si>
+  <si>
+    <t>E14001142</t>
+  </si>
+  <si>
+    <t>burton and uttoxeter</t>
+  </si>
+  <si>
+    <t>E14001143</t>
+  </si>
+  <si>
+    <t>bury north</t>
+  </si>
+  <si>
+    <t>E14001144</t>
+  </si>
+  <si>
+    <t>bury south</t>
+  </si>
+  <si>
+    <t>E14001145</t>
+  </si>
+  <si>
+    <t>bury st edmunds and stowmarket</t>
+  </si>
+  <si>
+    <t>E14001146</t>
+  </si>
+  <si>
+    <t>calder valley</t>
+  </si>
+  <si>
+    <t>E14001147</t>
+  </si>
+  <si>
+    <t>camborne and redruth</t>
+  </si>
+  <si>
+    <t>E14001148</t>
+  </si>
+  <si>
+    <t>cambridge</t>
+  </si>
+  <si>
+    <t>E14001149</t>
+  </si>
+  <si>
+    <t>cannock chase</t>
+  </si>
+  <si>
+    <t>E14001150</t>
+  </si>
+  <si>
+    <t>canterbury</t>
+  </si>
+  <si>
+    <t>E14001151</t>
+  </si>
+  <si>
+    <t>carlisle</t>
+  </si>
+  <si>
+    <t>E14001152</t>
+  </si>
+  <si>
+    <t>carshalton and wallington</t>
+  </si>
+  <si>
+    <t>E14001153</t>
+  </si>
+  <si>
+    <t>castle point</t>
+  </si>
+  <si>
+    <t>E14001154</t>
+  </si>
+  <si>
+    <t>central devon</t>
+  </si>
+  <si>
+    <t>E14001155</t>
+  </si>
+  <si>
+    <t>central suffolk and north ipswich</t>
+  </si>
+  <si>
+    <t>E14001156</t>
+  </si>
+  <si>
+    <t>chatham and aylesford</t>
+  </si>
+  <si>
+    <t>E14001157</t>
+  </si>
+  <si>
+    <t>cheadle</t>
+  </si>
+  <si>
+    <t>E14001158</t>
+  </si>
+  <si>
+    <t>chelmsford</t>
+  </si>
+  <si>
+    <t>E14001159</t>
+  </si>
+  <si>
+    <t>chelsea and fulham</t>
+  </si>
+  <si>
+    <t>E14001160</t>
+  </si>
+  <si>
+    <t>cheltenham</t>
+  </si>
+  <si>
+    <t>E14001161</t>
+  </si>
+  <si>
+    <t>chesham and amersham</t>
+  </si>
+  <si>
+    <t>E14001162</t>
+  </si>
+  <si>
+    <t>chester north and neston</t>
+  </si>
+  <si>
+    <t>E14001163</t>
+  </si>
+  <si>
+    <t>chester south and eddisbury</t>
+  </si>
+  <si>
+    <t>E14001164</t>
+  </si>
+  <si>
+    <t>chesterfield</t>
+  </si>
+  <si>
+    <t>E14001165</t>
+  </si>
+  <si>
+    <t>chichester</t>
+  </si>
+  <si>
+    <t>E14001166</t>
+  </si>
+  <si>
+    <t>chingford and woodford green</t>
+  </si>
+  <si>
+    <t>E14001167</t>
+  </si>
+  <si>
+    <t>chippenham</t>
+  </si>
+  <si>
+    <t>E14001168</t>
+  </si>
+  <si>
+    <t>chipping barnet</t>
+  </si>
+  <si>
+    <t>E14001169</t>
+  </si>
+  <si>
+    <t>chorley</t>
   </si>
   <si>
     <t>Other</t>
-  </si>
-  <si>
-    <t>E14001120</t>
-  </si>
-  <si>
-    <t>braintree</t>
-  </si>
-  <si>
-    <t>E14001121</t>
-  </si>
-  <si>
-    <t>brent east</t>
-  </si>
-  <si>
-    <t>E14001122</t>
-  </si>
-  <si>
-    <t>brent west</t>
-  </si>
-  <si>
-    <t>E14001123</t>
-  </si>
-  <si>
-    <t>brentford and isleworth</t>
-  </si>
-  <si>
-    <t>E14001124</t>
-  </si>
-  <si>
-    <t>brentwood and ongar</t>
-  </si>
-  <si>
-    <t>E14001125</t>
-  </si>
-  <si>
-    <t>bridgwater</t>
-  </si>
-  <si>
-    <t>E14001126</t>
-  </si>
-  <si>
-    <t>bridlington and the wolds</t>
-  </si>
-  <si>
-    <t>E14001127</t>
-  </si>
-  <si>
-    <t>brigg and immingham</t>
-  </si>
-  <si>
-    <t>E14001128</t>
-  </si>
-  <si>
-    <t>brighton kemptown and peacehaven</t>
-  </si>
-  <si>
-    <t>E14001129</t>
-  </si>
-  <si>
-    <t>brighton pavilion</t>
-  </si>
-  <si>
-    <t>E14001130</t>
-  </si>
-  <si>
-    <t>bristol central</t>
-  </si>
-  <si>
-    <t>E14001131</t>
-  </si>
-  <si>
-    <t>bristol east</t>
-  </si>
-  <si>
-    <t>E14001132</t>
-  </si>
-  <si>
-    <t>bristol north east</t>
-  </si>
-  <si>
-    <t>E14001133</t>
-  </si>
-  <si>
-    <t>bristol north west</t>
-  </si>
-  <si>
-    <t>E14001134</t>
-  </si>
-  <si>
-    <t>bristol south</t>
-  </si>
-  <si>
-    <t>E14001135</t>
-  </si>
-  <si>
-    <t>broadland and fakenham</t>
-  </si>
-  <si>
-    <t>E14001136</t>
-  </si>
-  <si>
-    <t>bromley and biggin hill</t>
-  </si>
-  <si>
-    <t>E14001137</t>
-  </si>
-  <si>
-    <t>bromsgrove</t>
-  </si>
-  <si>
-    <t>E14001138</t>
-  </si>
-  <si>
-    <t>broxbourne</t>
-  </si>
-  <si>
-    <t>E14001139</t>
-  </si>
-  <si>
-    <t>broxtowe</t>
-  </si>
-  <si>
-    <t>E14001140</t>
-  </si>
-  <si>
-    <t>buckingham and bletchley</t>
-  </si>
-  <si>
-    <t>E14001141</t>
-  </si>
-  <si>
-    <t>burnley</t>
-  </si>
-  <si>
-    <t>E14001142</t>
-  </si>
-  <si>
-    <t>burton and uttoxeter</t>
-  </si>
-  <si>
-    <t>E14001143</t>
-  </si>
-  <si>
-    <t>bury north</t>
-  </si>
-  <si>
-    <t>E14001144</t>
-  </si>
-  <si>
-    <t>bury south</t>
-  </si>
-  <si>
-    <t>E14001145</t>
-  </si>
-  <si>
-    <t>bury st edmunds and stowmarket</t>
-  </si>
-  <si>
-    <t>E14001146</t>
-  </si>
-  <si>
-    <t>calder valley</t>
-  </si>
-  <si>
-    <t>E14001147</t>
-  </si>
-  <si>
-    <t>camborne and redruth</t>
-  </si>
-  <si>
-    <t>E14001148</t>
-  </si>
-  <si>
-    <t>cambridge</t>
-  </si>
-  <si>
-    <t>E14001149</t>
-  </si>
-  <si>
-    <t>cannock chase</t>
-  </si>
-  <si>
-    <t>E14001150</t>
-  </si>
-  <si>
-    <t>canterbury</t>
-  </si>
-  <si>
-    <t>E14001151</t>
-  </si>
-  <si>
-    <t>carlisle</t>
-  </si>
-  <si>
-    <t>E14001152</t>
-  </si>
-  <si>
-    <t>carshalton and wallington</t>
-  </si>
-  <si>
-    <t>E14001153</t>
-  </si>
-  <si>
-    <t>castle point</t>
-  </si>
-  <si>
-    <t>E14001154</t>
-  </si>
-  <si>
-    <t>central devon</t>
-  </si>
-  <si>
-    <t>E14001155</t>
-  </si>
-  <si>
-    <t>central suffolk and north ipswich</t>
-  </si>
-  <si>
-    <t>E14001156</t>
-  </si>
-  <si>
-    <t>chatham and aylesford</t>
-  </si>
-  <si>
-    <t>E14001157</t>
-  </si>
-  <si>
-    <t>cheadle</t>
-  </si>
-  <si>
-    <t>E14001158</t>
-  </si>
-  <si>
-    <t>chelmsford</t>
-  </si>
-  <si>
-    <t>E14001159</t>
-  </si>
-  <si>
-    <t>chelsea and fulham</t>
-  </si>
-  <si>
-    <t>E14001160</t>
-  </si>
-  <si>
-    <t>cheltenham</t>
-  </si>
-  <si>
-    <t>E14001161</t>
-  </si>
-  <si>
-    <t>chesham and amersham</t>
-  </si>
-  <si>
-    <t>E14001162</t>
-  </si>
-  <si>
-    <t>chester north and neston</t>
-  </si>
-  <si>
-    <t>E14001163</t>
-  </si>
-  <si>
-    <t>chester south and eddisbury</t>
-  </si>
-  <si>
-    <t>E14001164</t>
-  </si>
-  <si>
-    <t>chesterfield</t>
-  </si>
-  <si>
-    <t>E14001165</t>
-  </si>
-  <si>
-    <t>chichester</t>
-  </si>
-  <si>
-    <t>E14001166</t>
-  </si>
-  <si>
-    <t>chingford and woodford green</t>
-  </si>
-  <si>
-    <t>E14001167</t>
-  </si>
-  <si>
-    <t>chippenham</t>
-  </si>
-  <si>
-    <t>E14001168</t>
-  </si>
-  <si>
-    <t>chipping barnet</t>
-  </si>
-  <si>
-    <t>E14001169</t>
-  </si>
-  <si>
-    <t>chorley</t>
   </si>
   <si>
     <t>E14001170</t>
@@ -4360,7 +4360,7 @@
         <v>6</v>
       </c>
       <c r="C2">
-        <v>0.2925143604288105</v>
+        <v>0.3002962226851348</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
@@ -4377,7 +4377,7 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>0.3626930731865723</v>
+        <v>0.3989348122084349</v>
       </c>
       <c r="D3" t="s">
         <v>7</v>
@@ -4394,7 +4394,7 @@
         <v>6</v>
       </c>
       <c r="C4">
-        <v>0.3970787225281536</v>
+        <v>0.3980742653381755</v>
       </c>
       <c r="D4" t="s">
         <v>7</v>
@@ -4408,27 +4408,27 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C5">
-        <v>0.3848951279804696</v>
+        <v>0.3814936246259302</v>
       </c>
       <c r="D5" t="s">
         <v>7</v>
       </c>
       <c r="E5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C6">
-        <v>0.363824286601389</v>
+        <v>0.3772759839072296</v>
       </c>
       <c r="D6" t="s">
         <v>7</v>
@@ -4442,10 +4442,10 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C7">
-        <v>0.3328634340280491</v>
+        <v>0.318406540325769</v>
       </c>
       <c r="D7" t="s">
         <v>7</v>
@@ -4459,10 +4459,10 @@
         <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C8">
-        <v>0.3293939329544224</v>
+        <v>0.3431227614901878</v>
       </c>
       <c r="D8" t="s">
         <v>7</v>
@@ -4476,10 +4476,10 @@
         <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C9">
-        <v>0.324228857305032</v>
+        <v>0.3180994384531466</v>
       </c>
       <c r="D9" t="s">
         <v>7</v>
@@ -4493,10 +4493,10 @@
         <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C10">
-        <v>0.3139395134550744</v>
+        <v>0.3214139942662587</v>
       </c>
       <c r="D10" t="s">
         <v>7</v>
@@ -4510,10 +4510,10 @@
         <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C11">
-        <v>0.20909881657508</v>
+        <v>0.2353194530314209</v>
       </c>
       <c r="D11" t="s">
         <v>7</v>
@@ -4530,7 +4530,7 @@
         <v>6</v>
       </c>
       <c r="C12">
-        <v>0.3458979408275309</v>
+        <v>0.3964912353346211</v>
       </c>
       <c r="D12" t="s">
         <v>7</v>
@@ -4544,10 +4544,10 @@
         <v>31</v>
       </c>
       <c r="B13" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C13">
-        <v>0.3101519003123441</v>
+        <v>0.3009475130199061</v>
       </c>
       <c r="D13" t="s">
         <v>7</v>
@@ -4561,10 +4561,10 @@
         <v>33</v>
       </c>
       <c r="B14" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C14">
-        <v>0.4163318212989995</v>
+        <v>0.3856685315090146</v>
       </c>
       <c r="D14" t="s">
         <v>7</v>
@@ -4578,10 +4578,10 @@
         <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C15">
-        <v>0.3449482259435828</v>
+        <v>0.3519008435379434</v>
       </c>
       <c r="D15" t="s">
         <v>7</v>
@@ -4598,7 +4598,7 @@
         <v>6</v>
       </c>
       <c r="C16">
-        <v>0.3108897071796079</v>
+        <v>0.3369790465850339</v>
       </c>
       <c r="D16" t="s">
         <v>7</v>
@@ -4612,10 +4612,10 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C17">
-        <v>0.2581652271289055</v>
+        <v>0.2802172007067437</v>
       </c>
       <c r="D17" t="s">
         <v>7</v>
@@ -4629,10 +4629,10 @@
         <v>41</v>
       </c>
       <c r="B18" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C18">
-        <v>0.2957086407508068</v>
+        <v>0.3095092411044063</v>
       </c>
       <c r="D18" t="s">
         <v>7</v>
@@ -4649,7 +4649,7 @@
         <v>44</v>
       </c>
       <c r="C19">
-        <v>0.4289327274080508</v>
+        <v>0.4343178921057265</v>
       </c>
       <c r="D19" t="s">
         <v>7</v>
@@ -4666,7 +4666,7 @@
         <v>6</v>
       </c>
       <c r="C20">
-        <v>0.446838337720757</v>
+        <v>0.4483731014269515</v>
       </c>
       <c r="D20" t="s">
         <v>7</v>
@@ -4680,10 +4680,10 @@
         <v>48</v>
       </c>
       <c r="B21" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C21">
-        <v>0.3821250188834537</v>
+        <v>0.388804940006443</v>
       </c>
       <c r="D21" t="s">
         <v>7</v>
@@ -4700,7 +4700,7 @@
         <v>6</v>
       </c>
       <c r="C22">
-        <v>0.3382455525819016</v>
+        <v>0.3612691945836911</v>
       </c>
       <c r="D22" t="s">
         <v>7</v>
@@ -4717,7 +4717,7 @@
         <v>6</v>
       </c>
       <c r="C23">
-        <v>0.4361150861977534</v>
+        <v>0.4578224991226191</v>
       </c>
       <c r="D23" t="s">
         <v>7</v>
@@ -4734,7 +4734,7 @@
         <v>6</v>
       </c>
       <c r="C24">
-        <v>0.3356837839815848</v>
+        <v>0.3414169536271225</v>
       </c>
       <c r="D24" t="s">
         <v>7</v>
@@ -4751,7 +4751,7 @@
         <v>6</v>
       </c>
       <c r="C25">
-        <v>0.638494866249112</v>
+        <v>0.6109098336275681</v>
       </c>
       <c r="D25" t="s">
         <v>7</v>
@@ -4765,10 +4765,10 @@
         <v>58</v>
       </c>
       <c r="B26" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C26">
-        <v>0.2791133323496101</v>
+        <v>0.2964336672472846</v>
       </c>
       <c r="D26" t="s">
         <v>7</v>
@@ -4782,10 +4782,10 @@
         <v>60</v>
       </c>
       <c r="B27" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C27">
-        <v>0.2759558001858236</v>
+        <v>0.2783797087325597</v>
       </c>
       <c r="D27" t="s">
         <v>7</v>
@@ -4802,7 +4802,7 @@
         <v>6</v>
       </c>
       <c r="C28">
-        <v>0.3123659577083425</v>
+        <v>0.3196052925396836</v>
       </c>
       <c r="D28" t="s">
         <v>7</v>
@@ -4819,7 +4819,7 @@
         <v>44</v>
       </c>
       <c r="C29">
-        <v>0.4376414040888657</v>
+        <v>0.4350980786145996</v>
       </c>
       <c r="D29" t="s">
         <v>7</v>
@@ -4836,7 +4836,7 @@
         <v>6</v>
       </c>
       <c r="C30">
-        <v>0.3486317006826186</v>
+        <v>0.3764963133352794</v>
       </c>
       <c r="D30" t="s">
         <v>7</v>
@@ -4853,7 +4853,7 @@
         <v>6</v>
       </c>
       <c r="C31">
-        <v>0.447603545327402</v>
+        <v>0.4546350624711464</v>
       </c>
       <c r="D31" t="s">
         <v>7</v>
@@ -4867,10 +4867,10 @@
         <v>70</v>
       </c>
       <c r="B32" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C32">
-        <v>0.4358907906757701</v>
+        <v>0.4129129265094403</v>
       </c>
       <c r="D32" t="s">
         <v>7</v>
@@ -4887,7 +4887,7 @@
         <v>6</v>
       </c>
       <c r="C33">
-        <v>0.3568980809660334</v>
+        <v>0.404690972781568</v>
       </c>
       <c r="D33" t="s">
         <v>7</v>
@@ -4901,10 +4901,10 @@
         <v>74</v>
       </c>
       <c r="B34" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C34">
-        <v>0.3494383799639729</v>
+        <v>0.3323184531036122</v>
       </c>
       <c r="D34" t="s">
         <v>7</v>
@@ -4921,7 +4921,7 @@
         <v>6</v>
       </c>
       <c r="C35">
-        <v>0.4857573951113609</v>
+        <v>0.4533586195021107</v>
       </c>
       <c r="D35" t="s">
         <v>7</v>
@@ -4935,1248 +4935,1248 @@
         <v>78</v>
       </c>
       <c r="B36" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36">
+        <v>0.2459615220445875</v>
+      </c>
+      <c r="D36" t="s">
+        <v>7</v>
+      </c>
+      <c r="E36" t="s">
         <v>79</v>
-      </c>
-      <c r="C36">
-        <v>0.2433478816231222</v>
-      </c>
-      <c r="D36" t="s">
-        <v>7</v>
-      </c>
-      <c r="E36" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
+        <v>80</v>
+      </c>
+      <c r="B37" t="s">
+        <v>15</v>
+      </c>
+      <c r="C37">
+        <v>0.322498172682082</v>
+      </c>
+      <c r="D37" t="s">
+        <v>7</v>
+      </c>
+      <c r="E37" t="s">
         <v>81</v>
-      </c>
-      <c r="B37" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37">
-        <v>0.3384568809049596</v>
-      </c>
-      <c r="D37" t="s">
-        <v>7</v>
-      </c>
-      <c r="E37" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
+        <v>82</v>
+      </c>
+      <c r="B38" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38">
+        <v>0.340201226698975</v>
+      </c>
+      <c r="D38" t="s">
+        <v>7</v>
+      </c>
+      <c r="E38" t="s">
         <v>83</v>
-      </c>
-      <c r="B38" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38">
-        <v>0.3432554876553289</v>
-      </c>
-      <c r="D38" t="s">
-        <v>7</v>
-      </c>
-      <c r="E38" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
+        <v>84</v>
+      </c>
+      <c r="B39" t="s">
+        <v>15</v>
+      </c>
+      <c r="C39">
+        <v>0.3151173381253176</v>
+      </c>
+      <c r="D39" t="s">
+        <v>7</v>
+      </c>
+      <c r="E39" t="s">
         <v>85</v>
-      </c>
-      <c r="B39" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39">
-        <v>0.3334675603673717</v>
-      </c>
-      <c r="D39" t="s">
-        <v>7</v>
-      </c>
-      <c r="E39" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
+        <v>86</v>
+      </c>
+      <c r="B40" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40">
+        <v>0.4891317449919983</v>
+      </c>
+      <c r="D40" t="s">
+        <v>7</v>
+      </c>
+      <c r="E40" t="s">
         <v>87</v>
-      </c>
-      <c r="B40" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40">
-        <v>0.4822723970273423</v>
-      </c>
-      <c r="D40" t="s">
-        <v>7</v>
-      </c>
-      <c r="E40" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" t="s">
+        <v>88</v>
+      </c>
+      <c r="B41" t="s">
+        <v>15</v>
+      </c>
+      <c r="C41">
+        <v>0.2925719630911905</v>
+      </c>
+      <c r="D41" t="s">
+        <v>7</v>
+      </c>
+      <c r="E41" t="s">
         <v>89</v>
-      </c>
-      <c r="B41" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41">
-        <v>0.2930887157838924</v>
-      </c>
-      <c r="D41" t="s">
-        <v>7</v>
-      </c>
-      <c r="E41" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" t="s">
+        <v>90</v>
+      </c>
+      <c r="B42" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42">
+        <v>0.5229940888378336</v>
+      </c>
+      <c r="D42" t="s">
+        <v>7</v>
+      </c>
+      <c r="E42" t="s">
         <v>91</v>
-      </c>
-      <c r="B42" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42">
-        <v>0.498863344136383</v>
-      </c>
-      <c r="D42" t="s">
-        <v>7</v>
-      </c>
-      <c r="E42" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" t="s">
+        <v>92</v>
+      </c>
+      <c r="B43" t="s">
+        <v>15</v>
+      </c>
+      <c r="C43">
+        <v>0.4035177225469865</v>
+      </c>
+      <c r="D43" t="s">
+        <v>7</v>
+      </c>
+      <c r="E43" t="s">
         <v>93</v>
-      </c>
-      <c r="B43" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43">
-        <v>0.4273425732917904</v>
-      </c>
-      <c r="D43" t="s">
-        <v>7</v>
-      </c>
-      <c r="E43" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" t="s">
+        <v>94</v>
+      </c>
+      <c r="B44" t="s">
+        <v>15</v>
+      </c>
+      <c r="C44">
+        <v>0.4391638333122718</v>
+      </c>
+      <c r="D44" t="s">
+        <v>7</v>
+      </c>
+      <c r="E44" t="s">
         <v>95</v>
-      </c>
-      <c r="B44" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44">
-        <v>0.4740353805451992</v>
-      </c>
-      <c r="D44" t="s">
-        <v>7</v>
-      </c>
-      <c r="E44" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" t="s">
+        <v>96</v>
+      </c>
+      <c r="B45" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45">
+        <v>0.4114668141323106</v>
+      </c>
+      <c r="D45" t="s">
+        <v>7</v>
+      </c>
+      <c r="E45" t="s">
         <v>97</v>
-      </c>
-      <c r="B45" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45">
-        <v>0.3838396867257516</v>
-      </c>
-      <c r="D45" t="s">
-        <v>7</v>
-      </c>
-      <c r="E45" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" t="s">
+        <v>98</v>
+      </c>
+      <c r="B46" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46">
+        <v>0.4016794669200297</v>
+      </c>
+      <c r="D46" t="s">
+        <v>7</v>
+      </c>
+      <c r="E46" t="s">
         <v>99</v>
-      </c>
-      <c r="B46" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46">
-        <v>0.3698661397473352</v>
-      </c>
-      <c r="D46" t="s">
-        <v>7</v>
-      </c>
-      <c r="E46" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" t="s">
+        <v>100</v>
+      </c>
+      <c r="B47" t="s">
+        <v>15</v>
+      </c>
+      <c r="C47">
+        <v>0.2984322803310926</v>
+      </c>
+      <c r="D47" t="s">
+        <v>7</v>
+      </c>
+      <c r="E47" t="s">
         <v>101</v>
-      </c>
-      <c r="B47" t="s">
-        <v>10</v>
-      </c>
-      <c r="C47">
-        <v>0.2926155663154248</v>
-      </c>
-      <c r="D47" t="s">
-        <v>7</v>
-      </c>
-      <c r="E47" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" t="s">
+        <v>102</v>
+      </c>
+      <c r="B48" t="s">
+        <v>15</v>
+      </c>
+      <c r="C48">
+        <v>0.4184649805694353</v>
+      </c>
+      <c r="D48" t="s">
+        <v>7</v>
+      </c>
+      <c r="E48" t="s">
         <v>103</v>
-      </c>
-      <c r="B48" t="s">
-        <v>10</v>
-      </c>
-      <c r="C48">
-        <v>0.4314386278034156</v>
-      </c>
-      <c r="D48" t="s">
-        <v>7</v>
-      </c>
-      <c r="E48" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" t="s">
+        <v>104</v>
+      </c>
+      <c r="B49" t="s">
+        <v>15</v>
+      </c>
+      <c r="C49">
+        <v>0.3284198078522778</v>
+      </c>
+      <c r="D49" t="s">
+        <v>7</v>
+      </c>
+      <c r="E49" t="s">
         <v>105</v>
-      </c>
-      <c r="B49" t="s">
-        <v>10</v>
-      </c>
-      <c r="C49">
-        <v>0.3383360290356556</v>
-      </c>
-      <c r="D49" t="s">
-        <v>7</v>
-      </c>
-      <c r="E49" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" t="s">
+        <v>106</v>
+      </c>
+      <c r="B50" t="s">
+        <v>15</v>
+      </c>
+      <c r="C50">
+        <v>0.3683957327026833</v>
+      </c>
+      <c r="D50" t="s">
+        <v>7</v>
+      </c>
+      <c r="E50" t="s">
         <v>107</v>
-      </c>
-      <c r="B50" t="s">
-        <v>10</v>
-      </c>
-      <c r="C50">
-        <v>0.3818944245066954</v>
-      </c>
-      <c r="D50" t="s">
-        <v>7</v>
-      </c>
-      <c r="E50" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" t="s">
+        <v>108</v>
+      </c>
+      <c r="B51" t="s">
+        <v>15</v>
+      </c>
+      <c r="C51">
+        <v>0.3542038261771873</v>
+      </c>
+      <c r="D51" t="s">
+        <v>7</v>
+      </c>
+      <c r="E51" t="s">
         <v>109</v>
-      </c>
-      <c r="B51" t="s">
-        <v>10</v>
-      </c>
-      <c r="C51">
-        <v>0.3684143421518599</v>
-      </c>
-      <c r="D51" t="s">
-        <v>7</v>
-      </c>
-      <c r="E51" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" t="s">
+        <v>110</v>
+      </c>
+      <c r="B52" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52">
+        <v>0.5103199961921103</v>
+      </c>
+      <c r="D52" t="s">
+        <v>7</v>
+      </c>
+      <c r="E52" t="s">
         <v>111</v>
-      </c>
-      <c r="B52" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52">
-        <v>0.4712793494080896</v>
-      </c>
-      <c r="D52" t="s">
-        <v>7</v>
-      </c>
-      <c r="E52" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" t="s">
+        <v>112</v>
+      </c>
+      <c r="B53" t="s">
+        <v>15</v>
+      </c>
+      <c r="C53">
+        <v>0.450848055858213</v>
+      </c>
+      <c r="D53" t="s">
+        <v>7</v>
+      </c>
+      <c r="E53" t="s">
         <v>113</v>
-      </c>
-      <c r="B53" t="s">
-        <v>10</v>
-      </c>
-      <c r="C53">
-        <v>0.4919954255344806</v>
-      </c>
-      <c r="D53" t="s">
-        <v>7</v>
-      </c>
-      <c r="E53" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" t="s">
+        <v>114</v>
+      </c>
+      <c r="B54" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54">
+        <v>0.4099391428166435</v>
+      </c>
+      <c r="D54" t="s">
+        <v>7</v>
+      </c>
+      <c r="E54" t="s">
         <v>115</v>
-      </c>
-      <c r="B54" t="s">
-        <v>6</v>
-      </c>
-      <c r="C54">
-        <v>0.3960578057136706</v>
-      </c>
-      <c r="D54" t="s">
-        <v>7</v>
-      </c>
-      <c r="E54" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" t="s">
+        <v>116</v>
+      </c>
+      <c r="B55" t="s">
+        <v>10</v>
+      </c>
+      <c r="C55">
+        <v>0.2805987164695691</v>
+      </c>
+      <c r="D55" t="s">
+        <v>7</v>
+      </c>
+      <c r="E55" t="s">
         <v>117</v>
-      </c>
-      <c r="B55" t="s">
-        <v>17</v>
-      </c>
-      <c r="C55">
-        <v>0.2799197406471978</v>
-      </c>
-      <c r="D55" t="s">
-        <v>7</v>
-      </c>
-      <c r="E55" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" t="s">
+        <v>118</v>
+      </c>
+      <c r="B56" t="s">
+        <v>10</v>
+      </c>
+      <c r="C56">
+        <v>0.3743231313460855</v>
+      </c>
+      <c r="D56" t="s">
+        <v>7</v>
+      </c>
+      <c r="E56" t="s">
         <v>119</v>
-      </c>
-      <c r="B56" t="s">
-        <v>17</v>
-      </c>
-      <c r="C56">
-        <v>0.3658931322752896</v>
-      </c>
-      <c r="D56" t="s">
-        <v>7</v>
-      </c>
-      <c r="E56" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" t="s">
+        <v>120</v>
+      </c>
+      <c r="B57" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57">
+        <v>0.549497453963136</v>
+      </c>
+      <c r="D57" t="s">
+        <v>7</v>
+      </c>
+      <c r="E57" t="s">
         <v>121</v>
-      </c>
-      <c r="B57" t="s">
-        <v>6</v>
-      </c>
-      <c r="C57">
-        <v>0.5187823295524883</v>
-      </c>
-      <c r="D57" t="s">
-        <v>7</v>
-      </c>
-      <c r="E57" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" t="s">
+        <v>122</v>
+      </c>
+      <c r="B58" t="s">
+        <v>6</v>
+      </c>
+      <c r="C58">
+        <v>0.3267277430665724</v>
+      </c>
+      <c r="D58" t="s">
+        <v>7</v>
+      </c>
+      <c r="E58" t="s">
         <v>123</v>
-      </c>
-      <c r="B58" t="s">
-        <v>6</v>
-      </c>
-      <c r="C58">
-        <v>0.3040400193777805</v>
-      </c>
-      <c r="D58" t="s">
-        <v>7</v>
-      </c>
-      <c r="E58" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" t="s">
+        <v>124</v>
+      </c>
+      <c r="B59" t="s">
+        <v>6</v>
+      </c>
+      <c r="C59">
+        <v>0.3666813415149887</v>
+      </c>
+      <c r="D59" t="s">
+        <v>7</v>
+      </c>
+      <c r="E59" t="s">
         <v>125</v>
-      </c>
-      <c r="B59" t="s">
-        <v>126</v>
-      </c>
-      <c r="C59">
-        <v>0.3201963569918908</v>
-      </c>
-      <c r="D59" t="s">
-        <v>7</v>
-      </c>
-      <c r="E59" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B60" t="s">
         <v>6</v>
       </c>
       <c r="C60">
-        <v>0.3024767425000124</v>
+        <v>0.3165721826892021</v>
       </c>
       <c r="D60" t="s">
         <v>7</v>
       </c>
       <c r="E60" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B61" t="s">
         <v>6</v>
       </c>
       <c r="C61">
-        <v>0.3531193143133521</v>
+        <v>0.3788749124073311</v>
       </c>
       <c r="D61" t="s">
         <v>7</v>
       </c>
       <c r="E61" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B62" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C62">
-        <v>0.3601202074000647</v>
+        <v>0.3575576311099624</v>
       </c>
       <c r="D62" t="s">
         <v>7</v>
       </c>
       <c r="E62" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B63" t="s">
         <v>6</v>
       </c>
       <c r="C63">
-        <v>0.3659968875225429</v>
+        <v>0.3781634780995647</v>
       </c>
       <c r="D63" t="s">
         <v>7</v>
       </c>
       <c r="E63" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B64" t="s">
         <v>44</v>
       </c>
       <c r="C64">
-        <v>0.2440304167232492</v>
+        <v>0.2382639085572628</v>
       </c>
       <c r="D64" t="s">
         <v>7</v>
       </c>
       <c r="E64" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B65" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C65">
-        <v>0.2914454051695062</v>
+        <v>0.3095694828066517</v>
       </c>
       <c r="D65" t="s">
         <v>7</v>
       </c>
       <c r="E65" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B66" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C66">
-        <v>0.3260386117062041</v>
+        <v>0.3229724193607359</v>
       </c>
       <c r="D66" t="s">
         <v>7</v>
       </c>
       <c r="E66" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B67" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C67">
-        <v>0.3196585036978699</v>
+        <v>0.3422753340231358</v>
       </c>
       <c r="D67" t="s">
         <v>7</v>
       </c>
       <c r="E67" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B68" t="s">
         <v>6</v>
       </c>
       <c r="C68">
-        <v>0.3010796678811245</v>
+        <v>0.3187585501733449</v>
       </c>
       <c r="D68" t="s">
         <v>7</v>
       </c>
       <c r="E68" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" t="s">
+        <v>144</v>
+      </c>
+      <c r="B69" t="s">
+        <v>145</v>
+      </c>
+      <c r="C69">
+        <v>0.5078273401668283</v>
+      </c>
+      <c r="D69" t="s">
+        <v>7</v>
+      </c>
+      <c r="E69" t="s">
         <v>146</v>
-      </c>
-      <c r="B69" t="s">
-        <v>79</v>
-      </c>
-      <c r="C69">
-        <v>0.592242385427759</v>
-      </c>
-      <c r="D69" t="s">
-        <v>7</v>
-      </c>
-      <c r="E69" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" t="s">
+        <v>147</v>
+      </c>
+      <c r="B70" t="s">
+        <v>145</v>
+      </c>
+      <c r="C70">
+        <v>0.4616473895475012</v>
+      </c>
+      <c r="D70" t="s">
+        <v>7</v>
+      </c>
+      <c r="E70" t="s">
         <v>148</v>
-      </c>
-      <c r="B70" t="s">
-        <v>79</v>
-      </c>
-      <c r="C70">
-        <v>0.5472216243135631</v>
-      </c>
-      <c r="D70" t="s">
-        <v>7</v>
-      </c>
-      <c r="E70" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" t="s">
+        <v>149</v>
+      </c>
+      <c r="B71" t="s">
+        <v>6</v>
+      </c>
+      <c r="C71">
+        <v>0.4864179164293944</v>
+      </c>
+      <c r="D71" t="s">
+        <v>7</v>
+      </c>
+      <c r="E71" t="s">
         <v>150</v>
-      </c>
-      <c r="B71" t="s">
-        <v>6</v>
-      </c>
-      <c r="C71">
-        <v>0.4793632230749952</v>
-      </c>
-      <c r="D71" t="s">
-        <v>7</v>
-      </c>
-      <c r="E71" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" t="s">
+        <v>151</v>
+      </c>
+      <c r="B72" t="s">
+        <v>6</v>
+      </c>
+      <c r="C72">
+        <v>0.3819526433667775</v>
+      </c>
+      <c r="D72" t="s">
+        <v>7</v>
+      </c>
+      <c r="E72" t="s">
         <v>152</v>
-      </c>
-      <c r="B72" t="s">
-        <v>6</v>
-      </c>
-      <c r="C72">
-        <v>0.3515567252844493</v>
-      </c>
-      <c r="D72" t="s">
-        <v>7</v>
-      </c>
-      <c r="E72" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" t="s">
+        <v>153</v>
+      </c>
+      <c r="B73" t="s">
+        <v>6</v>
+      </c>
+      <c r="C73">
+        <v>0.5164770252214986</v>
+      </c>
+      <c r="D73" t="s">
+        <v>7</v>
+      </c>
+      <c r="E73" t="s">
         <v>154</v>
-      </c>
-      <c r="B73" t="s">
-        <v>6</v>
-      </c>
-      <c r="C73">
-        <v>0.4942196691013788</v>
-      </c>
-      <c r="D73" t="s">
-        <v>7</v>
-      </c>
-      <c r="E73" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" t="s">
+        <v>155</v>
+      </c>
+      <c r="B74" t="s">
+        <v>6</v>
+      </c>
+      <c r="C74">
+        <v>0.5032246133194256</v>
+      </c>
+      <c r="D74" t="s">
+        <v>7</v>
+      </c>
+      <c r="E74" t="s">
         <v>156</v>
-      </c>
-      <c r="B74" t="s">
-        <v>6</v>
-      </c>
-      <c r="C74">
-        <v>0.488527375412953</v>
-      </c>
-      <c r="D74" t="s">
-        <v>7</v>
-      </c>
-      <c r="E74" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" t="s">
+        <v>157</v>
+      </c>
+      <c r="B75" t="s">
+        <v>10</v>
+      </c>
+      <c r="C75">
+        <v>0.2993000090958812</v>
+      </c>
+      <c r="D75" t="s">
+        <v>7</v>
+      </c>
+      <c r="E75" t="s">
         <v>158</v>
-      </c>
-      <c r="B75" t="s">
-        <v>17</v>
-      </c>
-      <c r="C75">
-        <v>0.2888769563270372</v>
-      </c>
-      <c r="D75" t="s">
-        <v>7</v>
-      </c>
-      <c r="E75" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" t="s">
+        <v>159</v>
+      </c>
+      <c r="B76" t="s">
+        <v>10</v>
+      </c>
+      <c r="C76">
+        <v>0.3400497221985563</v>
+      </c>
+      <c r="D76" t="s">
+        <v>7</v>
+      </c>
+      <c r="E76" t="s">
         <v>160</v>
-      </c>
-      <c r="B76" t="s">
-        <v>17</v>
-      </c>
-      <c r="C76">
-        <v>0.3401010219475959</v>
-      </c>
-      <c r="D76" t="s">
-        <v>7</v>
-      </c>
-      <c r="E76" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" t="s">
+        <v>161</v>
+      </c>
+      <c r="B77" t="s">
+        <v>10</v>
+      </c>
+      <c r="C77">
+        <v>0.3265129379870993</v>
+      </c>
+      <c r="D77" t="s">
+        <v>7</v>
+      </c>
+      <c r="E77" t="s">
         <v>162</v>
-      </c>
-      <c r="B77" t="s">
-        <v>17</v>
-      </c>
-      <c r="C77">
-        <v>0.3183818513017188</v>
-      </c>
-      <c r="D77" t="s">
-        <v>7</v>
-      </c>
-      <c r="E77" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" t="s">
+        <v>163</v>
+      </c>
+      <c r="B78" t="s">
+        <v>10</v>
+      </c>
+      <c r="C78">
+        <v>0.4349493680507749</v>
+      </c>
+      <c r="D78" t="s">
+        <v>7</v>
+      </c>
+      <c r="E78" t="s">
         <v>164</v>
-      </c>
-      <c r="B78" t="s">
-        <v>17</v>
-      </c>
-      <c r="C78">
-        <v>0.3909068635244394</v>
-      </c>
-      <c r="D78" t="s">
-        <v>7</v>
-      </c>
-      <c r="E78" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" t="s">
+        <v>165</v>
+      </c>
+      <c r="B79" t="s">
+        <v>15</v>
+      </c>
+      <c r="C79">
+        <v>0.2679351381437652</v>
+      </c>
+      <c r="D79" t="s">
+        <v>7</v>
+      </c>
+      <c r="E79" t="s">
         <v>166</v>
-      </c>
-      <c r="B79" t="s">
-        <v>17</v>
-      </c>
-      <c r="C79">
-        <v>0.2673669172652001</v>
-      </c>
-      <c r="D79" t="s">
-        <v>7</v>
-      </c>
-      <c r="E79" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" t="s">
+        <v>167</v>
+      </c>
+      <c r="B80" t="s">
+        <v>10</v>
+      </c>
+      <c r="C80">
+        <v>0.3674058478769018</v>
+      </c>
+      <c r="D80" t="s">
+        <v>7</v>
+      </c>
+      <c r="E80" t="s">
         <v>168</v>
-      </c>
-      <c r="B80" t="s">
-        <v>17</v>
-      </c>
-      <c r="C80">
-        <v>0.3488704272221892</v>
-      </c>
-      <c r="D80" t="s">
-        <v>7</v>
-      </c>
-      <c r="E80" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" t="s">
+        <v>169</v>
+      </c>
+      <c r="B81" t="s">
+        <v>15</v>
+      </c>
+      <c r="C81">
+        <v>0.2971075835112787</v>
+      </c>
+      <c r="D81" t="s">
+        <v>7</v>
+      </c>
+      <c r="E81" t="s">
         <v>170</v>
-      </c>
-      <c r="B81" t="s">
-        <v>10</v>
-      </c>
-      <c r="C81">
-        <v>0.3085121172764843</v>
-      </c>
-      <c r="D81" t="s">
-        <v>7</v>
-      </c>
-      <c r="E81" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" t="s">
+        <v>171</v>
+      </c>
+      <c r="B82" t="s">
+        <v>10</v>
+      </c>
+      <c r="C82">
+        <v>0.4305090506742372</v>
+      </c>
+      <c r="D82" t="s">
+        <v>7</v>
+      </c>
+      <c r="E82" t="s">
         <v>172</v>
-      </c>
-      <c r="B82" t="s">
-        <v>17</v>
-      </c>
-      <c r="C82">
-        <v>0.3946946287986125</v>
-      </c>
-      <c r="D82" t="s">
-        <v>7</v>
-      </c>
-      <c r="E82" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" t="s">
+        <v>173</v>
+      </c>
+      <c r="B83" t="s">
+        <v>6</v>
+      </c>
+      <c r="C83">
+        <v>0.4063087628671082</v>
+      </c>
+      <c r="D83" t="s">
+        <v>7</v>
+      </c>
+      <c r="E83" t="s">
         <v>174</v>
-      </c>
-      <c r="B83" t="s">
-        <v>6</v>
-      </c>
-      <c r="C83">
-        <v>0.3909511475356264</v>
-      </c>
-      <c r="D83" t="s">
-        <v>7</v>
-      </c>
-      <c r="E83" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" t="s">
+        <v>175</v>
+      </c>
+      <c r="B84" t="s">
+        <v>10</v>
+      </c>
+      <c r="C84">
+        <v>0.2906061728833929</v>
+      </c>
+      <c r="D84" t="s">
+        <v>7</v>
+      </c>
+      <c r="E84" t="s">
         <v>176</v>
-      </c>
-      <c r="B84" t="s">
-        <v>17</v>
-      </c>
-      <c r="C84">
-        <v>0.2827431797427498</v>
-      </c>
-      <c r="D84" t="s">
-        <v>7</v>
-      </c>
-      <c r="E84" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" t="s">
+        <v>177</v>
+      </c>
+      <c r="B85" t="s">
+        <v>15</v>
+      </c>
+      <c r="C85">
+        <v>0.3007345872638664</v>
+      </c>
+      <c r="D85" t="s">
+        <v>7</v>
+      </c>
+      <c r="E85" t="s">
         <v>178</v>
-      </c>
-      <c r="B85" t="s">
-        <v>10</v>
-      </c>
-      <c r="C85">
-        <v>0.282353492940456</v>
-      </c>
-      <c r="D85" t="s">
-        <v>7</v>
-      </c>
-      <c r="E85" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" t="s">
+        <v>179</v>
+      </c>
+      <c r="B86" t="s">
+        <v>6</v>
+      </c>
+      <c r="C86">
+        <v>0.3237343282314755</v>
+      </c>
+      <c r="D86" t="s">
+        <v>7</v>
+      </c>
+      <c r="E86" t="s">
         <v>180</v>
-      </c>
-      <c r="B86" t="s">
-        <v>6</v>
-      </c>
-      <c r="C86">
-        <v>0.3092468361227959</v>
-      </c>
-      <c r="D86" t="s">
-        <v>7</v>
-      </c>
-      <c r="E86" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" t="s">
+        <v>181</v>
+      </c>
+      <c r="B87" t="s">
+        <v>6</v>
+      </c>
+      <c r="C87">
+        <v>0.29834314125855</v>
+      </c>
+      <c r="D87" t="s">
+        <v>7</v>
+      </c>
+      <c r="E87" t="s">
         <v>182</v>
-      </c>
-      <c r="B87" t="s">
-        <v>6</v>
-      </c>
-      <c r="C87">
-        <v>0.2887933829440511</v>
-      </c>
-      <c r="D87" t="s">
-        <v>7</v>
-      </c>
-      <c r="E87" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" t="s">
+        <v>183</v>
+      </c>
+      <c r="B88" t="s">
+        <v>145</v>
+      </c>
+      <c r="C88">
+        <v>0.2882411988975978</v>
+      </c>
+      <c r="D88" t="s">
+        <v>7</v>
+      </c>
+      <c r="E88" t="s">
         <v>184</v>
-      </c>
-      <c r="B88" t="s">
-        <v>79</v>
-      </c>
-      <c r="C88">
-        <v>0.3572980482293691</v>
-      </c>
-      <c r="D88" t="s">
-        <v>7</v>
-      </c>
-      <c r="E88" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" t="s">
+        <v>185</v>
+      </c>
+      <c r="B89" t="s">
+        <v>10</v>
+      </c>
+      <c r="C89">
+        <v>0.2921006793610279</v>
+      </c>
+      <c r="D89" t="s">
+        <v>7</v>
+      </c>
+      <c r="E89" t="s">
         <v>186</v>
-      </c>
-      <c r="B89" t="s">
-        <v>6</v>
-      </c>
-      <c r="C89">
-        <v>0.2853063001903903</v>
-      </c>
-      <c r="D89" t="s">
-        <v>7</v>
-      </c>
-      <c r="E89" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" t="s">
+        <v>187</v>
+      </c>
+      <c r="B90" t="s">
+        <v>10</v>
+      </c>
+      <c r="C90">
+        <v>0.254588620561127</v>
+      </c>
+      <c r="D90" t="s">
+        <v>7</v>
+      </c>
+      <c r="E90" t="s">
         <v>188</v>
-      </c>
-      <c r="B90" t="s">
-        <v>17</v>
-      </c>
-      <c r="C90">
-        <v>0.2503949629421727</v>
-      </c>
-      <c r="D90" t="s">
-        <v>7</v>
-      </c>
-      <c r="E90" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" t="s">
+        <v>189</v>
+      </c>
+      <c r="B91" t="s">
+        <v>6</v>
+      </c>
+      <c r="C91">
+        <v>0.2698122518268143</v>
+      </c>
+      <c r="D91" t="s">
+        <v>7</v>
+      </c>
+      <c r="E91" t="s">
         <v>190</v>
-      </c>
-      <c r="B91" t="s">
-        <v>6</v>
-      </c>
-      <c r="C91">
-        <v>0.2674755569801305</v>
-      </c>
-      <c r="D91" t="s">
-        <v>7</v>
-      </c>
-      <c r="E91" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B92" t="s">
         <v>44</v>
       </c>
       <c r="C92">
-        <v>0.2886228192125692</v>
+        <v>0.2878086011921501</v>
       </c>
       <c r="D92" t="s">
         <v>7</v>
       </c>
       <c r="E92" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" t="s">
+        <v>193</v>
+      </c>
+      <c r="B93" t="s">
+        <v>15</v>
+      </c>
+      <c r="C93">
+        <v>0.3614313350310794</v>
+      </c>
+      <c r="D93" t="s">
+        <v>7</v>
+      </c>
+      <c r="E93" t="s">
         <v>194</v>
-      </c>
-      <c r="B93" t="s">
-        <v>10</v>
-      </c>
-      <c r="C93">
-        <v>0.3635514600838029</v>
-      </c>
-      <c r="D93" t="s">
-        <v>7</v>
-      </c>
-      <c r="E93" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" t="s">
+        <v>195</v>
+      </c>
+      <c r="B94" t="s">
+        <v>6</v>
+      </c>
+      <c r="C94">
+        <v>0.3028125920358366</v>
+      </c>
+      <c r="D94" t="s">
+        <v>7</v>
+      </c>
+      <c r="E94" t="s">
         <v>196</v>
-      </c>
-      <c r="B94" t="s">
-        <v>6</v>
-      </c>
-      <c r="C94">
-        <v>0.2893000941609085</v>
-      </c>
-      <c r="D94" t="s">
-        <v>7</v>
-      </c>
-      <c r="E94" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" t="s">
+        <v>197</v>
+      </c>
+      <c r="B95" t="s">
+        <v>15</v>
+      </c>
+      <c r="C95">
+        <v>0.3229139035645419</v>
+      </c>
+      <c r="D95" t="s">
+        <v>7</v>
+      </c>
+      <c r="E95" t="s">
         <v>198</v>
-      </c>
-      <c r="B95" t="s">
-        <v>10</v>
-      </c>
-      <c r="C95">
-        <v>0.2975123980601787</v>
-      </c>
-      <c r="D95" t="s">
-        <v>7</v>
-      </c>
-      <c r="E95" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" t="s">
+        <v>199</v>
+      </c>
+      <c r="B96" t="s">
+        <v>15</v>
+      </c>
+      <c r="C96">
+        <v>0.3359856925161489</v>
+      </c>
+      <c r="D96" t="s">
+        <v>7</v>
+      </c>
+      <c r="E96" t="s">
         <v>200</v>
-      </c>
-      <c r="B96" t="s">
-        <v>10</v>
-      </c>
-      <c r="C96">
-        <v>0.3436806451202627</v>
-      </c>
-      <c r="D96" t="s">
-        <v>7</v>
-      </c>
-      <c r="E96" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B97" t="s">
         <v>44</v>
       </c>
       <c r="C97">
-        <v>0.3533079324588341</v>
+        <v>0.3313369896101837</v>
       </c>
       <c r="D97" t="s">
         <v>7</v>
       </c>
       <c r="E97" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B98" t="s">
         <v>44</v>
       </c>
       <c r="C98">
-        <v>0.3376263769226049</v>
+        <v>0.3278473180106534</v>
       </c>
       <c r="D98" t="s">
         <v>7</v>
       </c>
       <c r="E98" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" t="s">
+        <v>205</v>
+      </c>
+      <c r="B99" t="s">
+        <v>6</v>
+      </c>
+      <c r="C99">
+        <v>0.4479166310528179</v>
+      </c>
+      <c r="D99" t="s">
+        <v>7</v>
+      </c>
+      <c r="E99" t="s">
         <v>206</v>
-      </c>
-      <c r="B99" t="s">
-        <v>6</v>
-      </c>
-      <c r="C99">
-        <v>0.44536282016692</v>
-      </c>
-      <c r="D99" t="s">
-        <v>7</v>
-      </c>
-      <c r="E99" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B100" t="s">
         <v>44</v>
       </c>
       <c r="C100">
-        <v>0.3951486967508427</v>
+        <v>0.3951710061802141</v>
       </c>
       <c r="D100" t="s">
         <v>7</v>
       </c>
       <c r="E100" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B101" t="s">
         <v>44</v>
       </c>
       <c r="C101">
-        <v>0.3938214985985315</v>
+        <v>0.3830851469969022</v>
       </c>
       <c r="D101" t="s">
         <v>7</v>
       </c>
       <c r="E101" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" t="s">
+        <v>211</v>
+      </c>
+      <c r="B102" t="s">
+        <v>6</v>
+      </c>
+      <c r="C102">
+        <v>0.4773530103256327</v>
+      </c>
+      <c r="D102" t="s">
+        <v>7</v>
+      </c>
+      <c r="E102" t="s">
         <v>212</v>
-      </c>
-      <c r="B102" t="s">
-        <v>6</v>
-      </c>
-      <c r="C102">
-        <v>0.4550237420798823</v>
-      </c>
-      <c r="D102" t="s">
-        <v>7</v>
-      </c>
-      <c r="E102" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" t="s">
+        <v>213</v>
+      </c>
+      <c r="B103" t="s">
+        <v>6</v>
+      </c>
+      <c r="C103">
+        <v>0.3586449919421741</v>
+      </c>
+      <c r="D103" t="s">
+        <v>7</v>
+      </c>
+      <c r="E103" t="s">
         <v>214</v>
-      </c>
-      <c r="B103" t="s">
-        <v>6</v>
-      </c>
-      <c r="C103">
-        <v>0.3551471138925335</v>
-      </c>
-      <c r="D103" t="s">
-        <v>7</v>
-      </c>
-      <c r="E103" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" t="s">
+        <v>215</v>
+      </c>
+      <c r="B104" t="s">
+        <v>15</v>
+      </c>
+      <c r="C104">
+        <v>0.3820716306341245</v>
+      </c>
+      <c r="D104" t="s">
+        <v>7</v>
+      </c>
+      <c r="E104" t="s">
         <v>216</v>
-      </c>
-      <c r="B104" t="s">
-        <v>10</v>
-      </c>
-      <c r="C104">
-        <v>0.3812464301244701</v>
-      </c>
-      <c r="D104" t="s">
-        <v>7</v>
-      </c>
-      <c r="E104" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B105" t="s">
         <v>44</v>
       </c>
       <c r="C105">
-        <v>0.3291430770208296</v>
+        <v>0.3253083367409038</v>
       </c>
       <c r="D105" t="s">
         <v>7</v>
       </c>
       <c r="E105" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" t="s">
+        <v>219</v>
+      </c>
+      <c r="B106" t="s">
+        <v>10</v>
+      </c>
+      <c r="C106">
+        <v>0.3887183210787193</v>
+      </c>
+      <c r="D106" t="s">
+        <v>7</v>
+      </c>
+      <c r="E106" t="s">
         <v>220</v>
-      </c>
-      <c r="B106" t="s">
-        <v>17</v>
-      </c>
-      <c r="C106">
-        <v>0.3940622702626701</v>
-      </c>
-      <c r="D106" t="s">
-        <v>7</v>
-      </c>
-      <c r="E106" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B107" t="s">
         <v>44</v>
       </c>
       <c r="C107">
-        <v>0.3270945203524462</v>
+        <v>0.3177137331713519</v>
       </c>
       <c r="D107" t="s">
         <v>7</v>
       </c>
       <c r="E107" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" t="s">
+        <v>223</v>
+      </c>
+      <c r="B108" t="s">
+        <v>6</v>
+      </c>
+      <c r="C108">
+        <v>0.3974702534980666</v>
+      </c>
+      <c r="D108" t="s">
+        <v>7</v>
+      </c>
+      <c r="E108" t="s">
         <v>224</v>
-      </c>
-      <c r="B108" t="s">
-        <v>6</v>
-      </c>
-      <c r="C108">
-        <v>0.3867254908843029</v>
-      </c>
-      <c r="D108" t="s">
-        <v>7</v>
-      </c>
-      <c r="E108" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" t="s">
+        <v>225</v>
+      </c>
+      <c r="B109" t="s">
         <v>226</v>
-      </c>
-      <c r="B109" t="s">
-        <v>126</v>
       </c>
       <c r="C109">
         <v>1</v>
@@ -6193,10 +6193,10 @@
         <v>228</v>
       </c>
       <c r="B110" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C110">
-        <v>0.2972845950584908</v>
+        <v>0.2985187471312225</v>
       </c>
       <c r="D110" t="s">
         <v>7</v>
@@ -6213,7 +6213,7 @@
         <v>6</v>
       </c>
       <c r="C111">
-        <v>0.4771999738610122</v>
+        <v>0.4920506420456521</v>
       </c>
       <c r="D111" t="s">
         <v>7</v>
@@ -6230,7 +6230,7 @@
         <v>6</v>
       </c>
       <c r="C112">
-        <v>0.3729906675764873</v>
+        <v>0.39997932654015</v>
       </c>
       <c r="D112" t="s">
         <v>7</v>
@@ -6244,10 +6244,10 @@
         <v>234</v>
       </c>
       <c r="B113" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C113">
-        <v>0.555731945305225</v>
+        <v>0.4986369722137559</v>
       </c>
       <c r="D113" t="s">
         <v>7</v>
@@ -6264,7 +6264,7 @@
         <v>6</v>
       </c>
       <c r="C114">
-        <v>0.6659667778348437</v>
+        <v>0.6277789202831435</v>
       </c>
       <c r="D114" t="s">
         <v>7</v>
@@ -6278,10 +6278,10 @@
         <v>238</v>
       </c>
       <c r="B115" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C115">
-        <v>0.2768347821194295</v>
+        <v>0.2917936640563258</v>
       </c>
       <c r="D115" t="s">
         <v>7</v>
@@ -6298,7 +6298,7 @@
         <v>6</v>
       </c>
       <c r="C116">
-        <v>0.3997881680543519</v>
+        <v>0.418192410588658</v>
       </c>
       <c r="D116" t="s">
         <v>7</v>
@@ -6312,10 +6312,10 @@
         <v>242</v>
       </c>
       <c r="B117" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C117">
-        <v>0.2962397305644639</v>
+        <v>0.300415631379341</v>
       </c>
       <c r="D117" t="s">
         <v>7</v>
@@ -6329,10 +6329,10 @@
         <v>244</v>
       </c>
       <c r="B118" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C118">
-        <v>0.3374449845105694</v>
+        <v>0.3565574634589235</v>
       </c>
       <c r="D118" t="s">
         <v>7</v>
@@ -6346,10 +6346,10 @@
         <v>246</v>
       </c>
       <c r="B119" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C119">
-        <v>0.3352720028620672</v>
+        <v>0.3011536142885618</v>
       </c>
       <c r="D119" t="s">
         <v>7</v>
@@ -6363,10 +6363,10 @@
         <v>248</v>
       </c>
       <c r="B120" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C120">
-        <v>0.355579565356543</v>
+        <v>0.3733885376468294</v>
       </c>
       <c r="D120" t="s">
         <v>7</v>
@@ -6380,10 +6380,10 @@
         <v>250</v>
       </c>
       <c r="B121" t="s">
-        <v>126</v>
+        <v>226</v>
       </c>
       <c r="C121">
-        <v>0.3770199368628961</v>
+        <v>0.3979065107076647</v>
       </c>
       <c r="D121" t="s">
         <v>7</v>
@@ -6397,10 +6397,10 @@
         <v>252</v>
       </c>
       <c r="B122" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C122">
-        <v>0.2857844437383169</v>
+        <v>0.3003930689963263</v>
       </c>
       <c r="D122" t="s">
         <v>7</v>
@@ -6414,10 +6414,10 @@
         <v>254</v>
       </c>
       <c r="B123" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C123">
-        <v>0.2694823458263761</v>
+        <v>0.2802168186595491</v>
       </c>
       <c r="D123" t="s">
         <v>7</v>
@@ -6431,10 +6431,10 @@
         <v>256</v>
       </c>
       <c r="B124" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C124">
-        <v>0.4123265126925549</v>
+        <v>0.4045558547319171</v>
       </c>
       <c r="D124" t="s">
         <v>7</v>
@@ -6448,10 +6448,10 @@
         <v>258</v>
       </c>
       <c r="B125" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C125">
-        <v>0.2828872938194631</v>
+        <v>0.2845308528777176</v>
       </c>
       <c r="D125" t="s">
         <v>7</v>
@@ -6465,10 +6465,10 @@
         <v>260</v>
       </c>
       <c r="B126" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C126">
-        <v>0.3532470731822582</v>
+        <v>0.342726595330417</v>
       </c>
       <c r="D126" t="s">
         <v>7</v>
@@ -6485,7 +6485,7 @@
         <v>6</v>
       </c>
       <c r="C127">
-        <v>0.4870683297259988</v>
+        <v>0.4930329258209397</v>
       </c>
       <c r="D127" t="s">
         <v>7</v>
@@ -6499,10 +6499,10 @@
         <v>264</v>
       </c>
       <c r="B128" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C128">
-        <v>0.4491606494833314</v>
+        <v>0.4285953891799711</v>
       </c>
       <c r="D128" t="s">
         <v>7</v>
@@ -6516,10 +6516,10 @@
         <v>266</v>
       </c>
       <c r="B129" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C129">
-        <v>0.3066861899942552</v>
+        <v>0.3032739017712001</v>
       </c>
       <c r="D129" t="s">
         <v>7</v>
@@ -6533,10 +6533,10 @@
         <v>268</v>
       </c>
       <c r="B130" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C130">
-        <v>0.3878220575552604</v>
+        <v>0.3803789681409016</v>
       </c>
       <c r="D130" t="s">
         <v>7</v>
@@ -6550,10 +6550,10 @@
         <v>270</v>
       </c>
       <c r="B131" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C131">
-        <v>0.2880151062734182</v>
+        <v>0.2923789351386583</v>
       </c>
       <c r="D131" t="s">
         <v>7</v>
@@ -6570,7 +6570,7 @@
         <v>6</v>
       </c>
       <c r="C132">
-        <v>0.3672797590814171</v>
+        <v>0.3825902003395259</v>
       </c>
       <c r="D132" t="s">
         <v>7</v>
@@ -6584,10 +6584,10 @@
         <v>274</v>
       </c>
       <c r="B133" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C133">
-        <v>0.3406332207655233</v>
+        <v>0.3318967353138298</v>
       </c>
       <c r="D133" t="s">
         <v>7</v>
@@ -6604,7 +6604,7 @@
         <v>6</v>
       </c>
       <c r="C134">
-        <v>0.3568433094036392</v>
+        <v>0.3710089639585467</v>
       </c>
       <c r="D134" t="s">
         <v>7</v>
@@ -6621,7 +6621,7 @@
         <v>6</v>
       </c>
       <c r="C135">
-        <v>0.3617114889705904</v>
+        <v>0.3956344284408497</v>
       </c>
       <c r="D135" t="s">
         <v>7</v>
@@ -6638,7 +6638,7 @@
         <v>44</v>
       </c>
       <c r="C136">
-        <v>0.3341721369091715</v>
+        <v>0.3300583768548642</v>
       </c>
       <c r="D136" t="s">
         <v>7</v>
@@ -6655,7 +6655,7 @@
         <v>6</v>
       </c>
       <c r="C137">
-        <v>0.3511598470383787</v>
+        <v>0.3831631586042276</v>
       </c>
       <c r="D137" t="s">
         <v>7</v>
@@ -6672,7 +6672,7 @@
         <v>6</v>
       </c>
       <c r="C138">
-        <v>0.3088599172841971</v>
+        <v>0.3151561321771282</v>
       </c>
       <c r="D138" t="s">
         <v>7</v>
@@ -6689,7 +6689,7 @@
         <v>6</v>
       </c>
       <c r="C139">
-        <v>0.3644054610151549</v>
+        <v>0.4030833363612665</v>
       </c>
       <c r="D139" t="s">
         <v>7</v>
@@ -6706,7 +6706,7 @@
         <v>44</v>
       </c>
       <c r="C140">
-        <v>0.3955092117466866</v>
+        <v>0.3962241535500782</v>
       </c>
       <c r="D140" t="s">
         <v>7</v>
@@ -6723,7 +6723,7 @@
         <v>6</v>
       </c>
       <c r="C141">
-        <v>0.3081976025038098</v>
+        <v>0.3221745241627366</v>
       </c>
       <c r="D141" t="s">
         <v>7</v>
@@ -6737,10 +6737,10 @@
         <v>292</v>
       </c>
       <c r="B142" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C142">
-        <v>0.3717730305632392</v>
+        <v>0.3922322476550797</v>
       </c>
       <c r="D142" t="s">
         <v>7</v>
@@ -6757,7 +6757,7 @@
         <v>6</v>
       </c>
       <c r="C143">
-        <v>0.3444338121866022</v>
+        <v>0.3587754753702972</v>
       </c>
       <c r="D143" t="s">
         <v>7</v>
@@ -6774,7 +6774,7 @@
         <v>6</v>
       </c>
       <c r="C144">
-        <v>0.6092107871860075</v>
+        <v>0.6037434288266073</v>
       </c>
       <c r="D144" t="s">
         <v>7</v>
@@ -6791,7 +6791,7 @@
         <v>6</v>
       </c>
       <c r="C145">
-        <v>0.2833765684637191</v>
+        <v>0.2920174908574525</v>
       </c>
       <c r="D145" t="s">
         <v>7</v>
@@ -6808,7 +6808,7 @@
         <v>6</v>
       </c>
       <c r="C146">
-        <v>0.3985513110492952</v>
+        <v>0.4092681654141022</v>
       </c>
       <c r="D146" t="s">
         <v>7</v>
@@ -6825,7 +6825,7 @@
         <v>6</v>
       </c>
       <c r="C147">
-        <v>0.435307034407421</v>
+        <v>0.4569896275696877</v>
       </c>
       <c r="D147" t="s">
         <v>7</v>
@@ -6842,7 +6842,7 @@
         <v>6</v>
       </c>
       <c r="C148">
-        <v>0.2869961213560333</v>
+        <v>0.2993671482301161</v>
       </c>
       <c r="D148" t="s">
         <v>7</v>
@@ -6856,10 +6856,10 @@
         <v>306</v>
       </c>
       <c r="B149" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C149">
-        <v>0.3870588230311317</v>
+        <v>0.3897167386417176</v>
       </c>
       <c r="D149" t="s">
         <v>7</v>
@@ -6873,10 +6873,10 @@
         <v>308</v>
       </c>
       <c r="B150" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C150">
-        <v>0.340962439697909</v>
+        <v>0.3587988759724908</v>
       </c>
       <c r="D150" t="s">
         <v>7</v>
@@ -6890,10 +6890,10 @@
         <v>310</v>
       </c>
       <c r="B151" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C151">
-        <v>0.2646327562853072</v>
+        <v>0.2656390058748325</v>
       </c>
       <c r="D151" t="s">
         <v>7</v>
@@ -6910,7 +6910,7 @@
         <v>6</v>
       </c>
       <c r="C152">
-        <v>0.6690191424990155</v>
+        <v>0.669101392745868</v>
       </c>
       <c r="D152" t="s">
         <v>7</v>
@@ -6924,10 +6924,10 @@
         <v>314</v>
       </c>
       <c r="B153" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C153">
-        <v>0.3210822240139956</v>
+        <v>0.3302663083196633</v>
       </c>
       <c r="D153" t="s">
         <v>7</v>
@@ -6944,7 +6944,7 @@
         <v>44</v>
       </c>
       <c r="C154">
-        <v>0.3387848585393599</v>
+        <v>0.3260404161258039</v>
       </c>
       <c r="D154" t="s">
         <v>7</v>
@@ -6961,7 +6961,7 @@
         <v>6</v>
       </c>
       <c r="C155">
-        <v>0.2840701677763426</v>
+        <v>0.3007304444506452</v>
       </c>
       <c r="D155" t="s">
         <v>7</v>
@@ -6975,10 +6975,10 @@
         <v>320</v>
       </c>
       <c r="B156" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C156">
-        <v>0.3345106611457227</v>
+        <v>0.3392578219412783</v>
       </c>
       <c r="D156" t="s">
         <v>7</v>
@@ -6995,7 +6995,7 @@
         <v>6</v>
       </c>
       <c r="C157">
-        <v>0.3670776974715359</v>
+        <v>0.3902641004488228</v>
       </c>
       <c r="D157" t="s">
         <v>7</v>
@@ -7012,7 +7012,7 @@
         <v>44</v>
       </c>
       <c r="C158">
-        <v>0.3631099705891741</v>
+        <v>0.3717849917944823</v>
       </c>
       <c r="D158" t="s">
         <v>7</v>
@@ -7029,7 +7029,7 @@
         <v>44</v>
       </c>
       <c r="C159">
-        <v>0.3704918763257252</v>
+        <v>0.3772329486419598</v>
       </c>
       <c r="D159" t="s">
         <v>7</v>
@@ -7046,7 +7046,7 @@
         <v>6</v>
       </c>
       <c r="C160">
-        <v>0.3594328573738069</v>
+        <v>0.3788918787033055</v>
       </c>
       <c r="D160" t="s">
         <v>7</v>
@@ -7063,7 +7063,7 @@
         <v>6</v>
       </c>
       <c r="C161">
-        <v>0.3946661339567543</v>
+        <v>0.4155464552821093</v>
       </c>
       <c r="D161" t="s">
         <v>7</v>
@@ -7080,7 +7080,7 @@
         <v>6</v>
       </c>
       <c r="C162">
-        <v>0.4664992389012385</v>
+        <v>0.4746319607183628</v>
       </c>
       <c r="D162" t="s">
         <v>7</v>
@@ -7097,7 +7097,7 @@
         <v>44</v>
       </c>
       <c r="C163">
-        <v>0.430852800923761</v>
+        <v>0.437333373353116</v>
       </c>
       <c r="D163" t="s">
         <v>7</v>
@@ -7111,10 +7111,10 @@
         <v>336</v>
       </c>
       <c r="B164" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C164">
-        <v>0.3539578343370998</v>
+        <v>0.3502424764164641</v>
       </c>
       <c r="D164" t="s">
         <v>7</v>
@@ -7128,10 +7128,10 @@
         <v>338</v>
       </c>
       <c r="B165" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C165">
-        <v>0.3821733234156131</v>
+        <v>0.4001705675708802</v>
       </c>
       <c r="D165" t="s">
         <v>7</v>
@@ -7145,10 +7145,10 @@
         <v>340</v>
       </c>
       <c r="B166" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C166">
-        <v>0.3072590194639022</v>
+        <v>0.2975380378601613</v>
       </c>
       <c r="D166" t="s">
         <v>7</v>
@@ -7165,7 +7165,7 @@
         <v>6</v>
       </c>
       <c r="C167">
-        <v>0.3387136525959499</v>
+        <v>0.3595491322031325</v>
       </c>
       <c r="D167" t="s">
         <v>7</v>
@@ -7182,7 +7182,7 @@
         <v>6</v>
       </c>
       <c r="C168">
-        <v>0.5853110533560778</v>
+        <v>0.6014939225985809</v>
       </c>
       <c r="D168" t="s">
         <v>7</v>
@@ -7199,7 +7199,7 @@
         <v>44</v>
       </c>
       <c r="C169">
-        <v>0.3421114553067905</v>
+        <v>0.3241449429878185</v>
       </c>
       <c r="D169" t="s">
         <v>7</v>
@@ -7216,7 +7216,7 @@
         <v>6</v>
       </c>
       <c r="C170">
-        <v>0.348549824087258</v>
+        <v>0.3807567384711282</v>
       </c>
       <c r="D170" t="s">
         <v>7</v>
@@ -7233,7 +7233,7 @@
         <v>6</v>
       </c>
       <c r="C171">
-        <v>0.2495387389544141</v>
+        <v>0.2546623000129131</v>
       </c>
       <c r="D171" t="s">
         <v>7</v>
@@ -7250,7 +7250,7 @@
         <v>10</v>
       </c>
       <c r="C172">
-        <v>0.4277898523612557</v>
+        <v>0.4070515817297399</v>
       </c>
       <c r="D172" t="s">
         <v>7</v>
@@ -7267,7 +7267,7 @@
         <v>44</v>
       </c>
       <c r="C173">
-        <v>0.3372544272649038</v>
+        <v>0.315260977941936</v>
       </c>
       <c r="D173" t="s">
         <v>7</v>
@@ -7284,7 +7284,7 @@
         <v>6</v>
       </c>
       <c r="C174">
-        <v>0.3051511570226345</v>
+        <v>0.3068921397766141</v>
       </c>
       <c r="D174" t="s">
         <v>7</v>
@@ -7298,10 +7298,10 @@
         <v>358</v>
       </c>
       <c r="B175" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C175">
-        <v>0.2909833372413856</v>
+        <v>0.2991817610435577</v>
       </c>
       <c r="D175" t="s">
         <v>7</v>
@@ -7318,7 +7318,7 @@
         <v>6</v>
       </c>
       <c r="C176">
-        <v>0.3823071449296032</v>
+        <v>0.4109100496534059</v>
       </c>
       <c r="D176" t="s">
         <v>7</v>
@@ -7335,7 +7335,7 @@
         <v>6</v>
       </c>
       <c r="C177">
-        <v>0.5058243918594832</v>
+        <v>0.5081521526070965</v>
       </c>
       <c r="D177" t="s">
         <v>7</v>
@@ -7349,10 +7349,10 @@
         <v>364</v>
       </c>
       <c r="B178" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C178">
-        <v>0.4162481060384284</v>
+        <v>0.3990032422549026</v>
       </c>
       <c r="D178" t="s">
         <v>7</v>
@@ -7366,10 +7366,10 @@
         <v>366</v>
       </c>
       <c r="B179" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C179">
-        <v>0.2975867169484162</v>
+        <v>0.3052088167911217</v>
       </c>
       <c r="D179" t="s">
         <v>7</v>
@@ -7386,7 +7386,7 @@
         <v>44</v>
       </c>
       <c r="C180">
-        <v>0.3424692034297692</v>
+        <v>0.3347566358036256</v>
       </c>
       <c r="D180" t="s">
         <v>7</v>
@@ -7403,7 +7403,7 @@
         <v>6</v>
       </c>
       <c r="C181">
-        <v>0.3216413627153308</v>
+        <v>0.3234626293076278</v>
       </c>
       <c r="D181" t="s">
         <v>7</v>
@@ -7417,10 +7417,10 @@
         <v>372</v>
       </c>
       <c r="B182" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C182">
-        <v>0.2775288439984262</v>
+        <v>0.2914165832595993</v>
       </c>
       <c r="D182" t="s">
         <v>7</v>
@@ -7437,7 +7437,7 @@
         <v>6</v>
       </c>
       <c r="C183">
-        <v>0.2844407827723575</v>
+        <v>0.310505530470617</v>
       </c>
       <c r="D183" t="s">
         <v>7</v>
@@ -7454,7 +7454,7 @@
         <v>6</v>
       </c>
       <c r="C184">
-        <v>0.3339360623652623</v>
+        <v>0.3519089282631613</v>
       </c>
       <c r="D184" t="s">
         <v>7</v>
@@ -7471,7 +7471,7 @@
         <v>10</v>
       </c>
       <c r="C185">
-        <v>0.340623867099085</v>
+        <v>0.3550755189546099</v>
       </c>
       <c r="D185" t="s">
         <v>7</v>
@@ -7488,7 +7488,7 @@
         <v>44</v>
       </c>
       <c r="C186">
-        <v>0.388904885438917</v>
+        <v>0.3905876208464197</v>
       </c>
       <c r="D186" t="s">
         <v>7</v>
@@ -7502,10 +7502,10 @@
         <v>382</v>
       </c>
       <c r="B187" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C187">
-        <v>0.2366649143074912</v>
+        <v>0.2418665624514982</v>
       </c>
       <c r="D187" t="s">
         <v>7</v>
@@ -7522,7 +7522,7 @@
         <v>44</v>
       </c>
       <c r="C188">
-        <v>0.3974582634957153</v>
+        <v>0.3833658964704665</v>
       </c>
       <c r="D188" t="s">
         <v>7</v>
@@ -7539,7 +7539,7 @@
         <v>6</v>
       </c>
       <c r="C189">
-        <v>0.3356951634512588</v>
+        <v>0.3299834992216931</v>
       </c>
       <c r="D189" t="s">
         <v>7</v>
@@ -7556,7 +7556,7 @@
         <v>6</v>
       </c>
       <c r="C190">
-        <v>0.2758487457971009</v>
+        <v>0.3068010559662859</v>
       </c>
       <c r="D190" t="s">
         <v>7</v>
@@ -7570,10 +7570,10 @@
         <v>390</v>
       </c>
       <c r="B191" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C191">
-        <v>0.3015902439348378</v>
+        <v>0.3245536067617779</v>
       </c>
       <c r="D191" t="s">
         <v>7</v>
@@ -7587,10 +7587,10 @@
         <v>392</v>
       </c>
       <c r="B192" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C192">
-        <v>0.4076350711005853</v>
+        <v>0.3996110396852516</v>
       </c>
       <c r="D192" t="s">
         <v>7</v>
@@ -7604,10 +7604,10 @@
         <v>394</v>
       </c>
       <c r="B193" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C193">
-        <v>0.4515262743056659</v>
+        <v>0.4269156485061978</v>
       </c>
       <c r="D193" t="s">
         <v>7</v>
@@ -7621,10 +7621,10 @@
         <v>396</v>
       </c>
       <c r="B194" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C194">
-        <v>0.3886890369964716</v>
+        <v>0.3666473929467334</v>
       </c>
       <c r="D194" t="s">
         <v>7</v>
@@ -7638,10 +7638,10 @@
         <v>398</v>
       </c>
       <c r="B195" t="s">
-        <v>126</v>
+        <v>226</v>
       </c>
       <c r="C195">
-        <v>0.4589919238476373</v>
+        <v>0.4893148158248171</v>
       </c>
       <c r="D195" t="s">
         <v>7</v>
@@ -7658,7 +7658,7 @@
         <v>6</v>
       </c>
       <c r="C196">
-        <v>0.3477166912375113</v>
+        <v>0.3740493236206467</v>
       </c>
       <c r="D196" t="s">
         <v>7</v>
@@ -7672,10 +7672,10 @@
         <v>402</v>
       </c>
       <c r="B197" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C197">
-        <v>0.2954452219141319</v>
+        <v>0.3043670344438727</v>
       </c>
       <c r="D197" t="s">
         <v>7</v>
@@ -7692,7 +7692,7 @@
         <v>6</v>
       </c>
       <c r="C198">
-        <v>0.5355735883690182</v>
+        <v>0.515960181493341</v>
       </c>
       <c r="D198" t="s">
         <v>7</v>
@@ -7709,7 +7709,7 @@
         <v>6</v>
       </c>
       <c r="C199">
-        <v>0.6287542918572999</v>
+        <v>0.5985523022331036</v>
       </c>
       <c r="D199" t="s">
         <v>7</v>
@@ -7723,10 +7723,10 @@
         <v>408</v>
       </c>
       <c r="B200" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C200">
-        <v>0.3251134354981137</v>
+        <v>0.3207343094594806</v>
       </c>
       <c r="D200" t="s">
         <v>7</v>
@@ -7740,10 +7740,10 @@
         <v>410</v>
       </c>
       <c r="B201" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C201">
-        <v>0.3189914791871748</v>
+        <v>0.3128304518200635</v>
       </c>
       <c r="D201" t="s">
         <v>7</v>
@@ -7757,10 +7757,10 @@
         <v>412</v>
       </c>
       <c r="B202" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C202">
-        <v>0.3300963852963707</v>
+        <v>0.344763369465294</v>
       </c>
       <c r="D202" t="s">
         <v>7</v>
@@ -7777,7 +7777,7 @@
         <v>6</v>
       </c>
       <c r="C203">
-        <v>0.5184238743487551</v>
+        <v>0.5389872030786965</v>
       </c>
       <c r="D203" t="s">
         <v>7</v>
@@ -7794,7 +7794,7 @@
         <v>6</v>
       </c>
       <c r="C204">
-        <v>0.4617220182580419</v>
+        <v>0.4780070444482749</v>
       </c>
       <c r="D204" t="s">
         <v>7</v>
@@ -7808,10 +7808,10 @@
         <v>418</v>
       </c>
       <c r="B205" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C205">
-        <v>0.4091656312840194</v>
+        <v>0.4291432086975526</v>
       </c>
       <c r="D205" t="s">
         <v>7</v>
@@ -7825,10 +7825,10 @@
         <v>420</v>
       </c>
       <c r="B206" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C206">
-        <v>0.3466370229237181</v>
+        <v>0.3486419298180785</v>
       </c>
       <c r="D206" t="s">
         <v>7</v>
@@ -7845,7 +7845,7 @@
         <v>44</v>
       </c>
       <c r="C207">
-        <v>0.5461969990871027</v>
+        <v>0.5342254465460607</v>
       </c>
       <c r="D207" t="s">
         <v>7</v>
@@ -7862,7 +7862,7 @@
         <v>44</v>
       </c>
       <c r="C208">
-        <v>0.3659307755746065</v>
+        <v>0.3637723143870945</v>
       </c>
       <c r="D208" t="s">
         <v>7</v>
@@ -7876,10 +7876,10 @@
         <v>426</v>
       </c>
       <c r="B209" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C209">
-        <v>0.510842235462775</v>
+        <v>0.5360691498455966</v>
       </c>
       <c r="D209" t="s">
         <v>7</v>
@@ -7896,7 +7896,7 @@
         <v>6</v>
       </c>
       <c r="C210">
-        <v>0.4128309149062205</v>
+        <v>0.425815792585612</v>
       </c>
       <c r="D210" t="s">
         <v>7</v>
@@ -7910,10 +7910,10 @@
         <v>430</v>
       </c>
       <c r="B211" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C211">
-        <v>0.4839220255328627</v>
+        <v>0.469228159972165</v>
       </c>
       <c r="D211" t="s">
         <v>7</v>
@@ -7927,10 +7927,10 @@
         <v>432</v>
       </c>
       <c r="B212" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C212">
-        <v>0.2734059637147231</v>
+        <v>0.2865841405127169</v>
       </c>
       <c r="D212" t="s">
         <v>7</v>
@@ -7944,10 +7944,10 @@
         <v>434</v>
       </c>
       <c r="B213" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C213">
-        <v>0.2957071347127823</v>
+        <v>0.3085231099321432</v>
       </c>
       <c r="D213" t="s">
         <v>7</v>
@@ -7961,10 +7961,10 @@
         <v>436</v>
       </c>
       <c r="B214" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C214">
-        <v>0.3944261136750927</v>
+        <v>0.3754605116908143</v>
       </c>
       <c r="D214" t="s">
         <v>7</v>
@@ -7978,10 +7978,10 @@
         <v>438</v>
       </c>
       <c r="B215" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C215">
-        <v>0.5050764304076868</v>
+        <v>0.510461569852468</v>
       </c>
       <c r="D215" t="s">
         <v>7</v>
@@ -7995,10 +7995,10 @@
         <v>440</v>
       </c>
       <c r="B216" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C216">
-        <v>0.3195768378055955</v>
+        <v>0.3307735696332388</v>
       </c>
       <c r="D216" t="s">
         <v>7</v>
@@ -8012,10 +8012,10 @@
         <v>442</v>
       </c>
       <c r="B217" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C217">
-        <v>0.2823549538351468</v>
+        <v>0.3015613459644056</v>
       </c>
       <c r="D217" t="s">
         <v>7</v>
@@ -8029,10 +8029,10 @@
         <v>444</v>
       </c>
       <c r="B218" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C218">
-        <v>0.3558318811932435</v>
+        <v>0.3452070806974275</v>
       </c>
       <c r="D218" t="s">
         <v>7</v>
@@ -8049,7 +8049,7 @@
         <v>44</v>
       </c>
       <c r="C219">
-        <v>0.4758415570361427</v>
+        <v>0.4756972760410768</v>
       </c>
       <c r="D219" t="s">
         <v>7</v>
@@ -8063,10 +8063,10 @@
         <v>448</v>
       </c>
       <c r="B220" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C220">
-        <v>0.2889032533528874</v>
+        <v>0.3003480853462688</v>
       </c>
       <c r="D220" t="s">
         <v>7</v>
@@ -8080,10 +8080,10 @@
         <v>450</v>
       </c>
       <c r="B221" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C221">
-        <v>0.3826628209683341</v>
+        <v>0.3768374928585538</v>
       </c>
       <c r="D221" t="s">
         <v>7</v>
@@ -8097,10 +8097,10 @@
         <v>452</v>
       </c>
       <c r="B222" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="C222">
-        <v>0.3053449840447459</v>
+        <v>0.3010235109699173</v>
       </c>
       <c r="D222" t="s">
         <v>7</v>
@@ -8114,10 +8114,10 @@
         <v>454</v>
       </c>
       <c r="B223" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C223">
-        <v>0.4696148379494077</v>
+        <v>0.4765094957880461</v>
       </c>
       <c r="D223" t="s">
         <v>7</v>
@@ -8131,10 +8131,10 @@
         <v>456</v>
       </c>
       <c r="B224" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C224">
-        <v>0.2950372649806424</v>
+        <v>0.294228593697671</v>
       </c>
       <c r="D224" t="s">
         <v>7</v>
@@ -8148,10 +8148,10 @@
         <v>458</v>
       </c>
       <c r="B225" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C225">
-        <v>0.373692714158223</v>
+        <v>0.357277166938235</v>
       </c>
       <c r="D225" t="s">
         <v>7</v>
@@ -8168,7 +8168,7 @@
         <v>6</v>
       </c>
       <c r="C226">
-        <v>0.477449290351352</v>
+        <v>0.4948153973721272</v>
       </c>
       <c r="D226" t="s">
         <v>7</v>
@@ -8182,10 +8182,10 @@
         <v>462</v>
       </c>
       <c r="B227" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C227">
-        <v>0.3018248370107985</v>
+        <v>0.3139757246352484</v>
       </c>
       <c r="D227" t="s">
         <v>7</v>
@@ -8202,7 +8202,7 @@
         <v>6</v>
       </c>
       <c r="C228">
-        <v>0.4923041299285724</v>
+        <v>0.4900836559484408</v>
       </c>
       <c r="D228" t="s">
         <v>7</v>
@@ -8219,7 +8219,7 @@
         <v>6</v>
       </c>
       <c r="C229">
-        <v>0.5665509611286522</v>
+        <v>0.5629967857282343</v>
       </c>
       <c r="D229" t="s">
         <v>7</v>
@@ -8236,7 +8236,7 @@
         <v>44</v>
       </c>
       <c r="C230">
-        <v>0.3528321139960491</v>
+        <v>0.3414861291283385</v>
       </c>
       <c r="D230" t="s">
         <v>7</v>
@@ -8253,7 +8253,7 @@
         <v>6</v>
       </c>
       <c r="C231">
-        <v>0.3101063147744256</v>
+        <v>0.3169369374019304</v>
       </c>
       <c r="D231" t="s">
         <v>7</v>
@@ -8270,7 +8270,7 @@
         <v>6</v>
       </c>
       <c r="C232">
-        <v>0.5938350308911474</v>
+        <v>0.5928719926402432</v>
       </c>
       <c r="D232" t="s">
         <v>7</v>
@@ -8287,7 +8287,7 @@
         <v>44</v>
       </c>
       <c r="C233">
-        <v>0.3954303818976487</v>
+        <v>0.4058206781830309</v>
       </c>
       <c r="D233" t="s">
         <v>7</v>
@@ -8304,7 +8304,7 @@
         <v>6</v>
       </c>
       <c r="C234">
-        <v>0.4065859799851749</v>
+        <v>0.4355186943093656</v>
       </c>
       <c r="D234" t="s">
         <v>7</v>
@@ -8321,7 +8321,7 @@
         <v>6</v>
       </c>
       <c r="C235">
-        <v>0.4941107002461808</v>
+        <v>0.5049695909821283</v>
       </c>
       <c r="D235" t="s">
         <v>7</v>
@@ -8338,7 +8338,7 @@
         <v>6</v>
       </c>
       <c r="C236">
-        <v>0.2781950929071519</v>
+        <v>0.2910555541220295</v>
       </c>
       <c r="D236" t="s">
         <v>7</v>
@@ -8355,7 +8355,7 @@
         <v>6</v>
       </c>
       <c r="C237">
-        <v>0.3049216612924652</v>
+        <v>0.3095878954993169</v>
       </c>
       <c r="D237" t="s">
         <v>7</v>
@@ -8372,7 +8372,7 @@
         <v>6</v>
       </c>
       <c r="C238">
-        <v>0.3477416144168453</v>
+        <v>0.3633863693589875</v>
       </c>
       <c r="D238" t="s">
         <v>7</v>
@@ -8389,7 +8389,7 @@
         <v>6</v>
       </c>
       <c r="C239">
-        <v>0.4272691027460807</v>
+        <v>0.4470480239178109</v>
       </c>
       <c r="D239" t="s">
         <v>7</v>
@@ -8403,10 +8403,10 @@
         <v>488</v>
       </c>
       <c r="B240" t="s">
-        <v>126</v>
+        <v>226</v>
       </c>
       <c r="C240">
-        <v>0.4347607488907044</v>
+        <v>0.3435980414546606</v>
       </c>
       <c r="D240" t="s">
         <v>7</v>
@@ -8420,10 +8420,10 @@
         <v>490</v>
       </c>
       <c r="B241" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C241">
-        <v>0.2334882528914666</v>
+        <v>0.2418084406263513</v>
       </c>
       <c r="D241" t="s">
         <v>7</v>
@@ -8437,10 +8437,10 @@
         <v>492</v>
       </c>
       <c r="B242" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C242">
-        <v>0.3128888290613531</v>
+        <v>0.3254633788769889</v>
       </c>
       <c r="D242" t="s">
         <v>7</v>
@@ -8454,10 +8454,10 @@
         <v>494</v>
       </c>
       <c r="B243" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C243">
-        <v>0.5218553490607608</v>
+        <v>0.4985677903177679</v>
       </c>
       <c r="D243" t="s">
         <v>7</v>
@@ -8471,10 +8471,10 @@
         <v>496</v>
       </c>
       <c r="B244" t="s">
-        <v>126</v>
+        <v>226</v>
       </c>
       <c r="C244">
-        <v>0.4448958175868111</v>
+        <v>0.4739853917103896</v>
       </c>
       <c r="D244" t="s">
         <v>7</v>
@@ -8491,7 +8491,7 @@
         <v>6</v>
       </c>
       <c r="C245">
-        <v>0.6154564953603902</v>
+        <v>0.630875927650298</v>
       </c>
       <c r="D245" t="s">
         <v>7</v>
@@ -8508,7 +8508,7 @@
         <v>6</v>
       </c>
       <c r="C246">
-        <v>0.4084357694977033</v>
+        <v>0.4500539226364544</v>
       </c>
       <c r="D246" t="s">
         <v>7</v>
@@ -8525,7 +8525,7 @@
         <v>6</v>
       </c>
       <c r="C247">
-        <v>0.401688163585029</v>
+        <v>0.406860206884375</v>
       </c>
       <c r="D247" t="s">
         <v>7</v>
@@ -8539,10 +8539,10 @@
         <v>504</v>
       </c>
       <c r="B248" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C248">
-        <v>0.303738667513013</v>
+        <v>0.3038899271040585</v>
       </c>
       <c r="D248" t="s">
         <v>7</v>
@@ -8559,7 +8559,7 @@
         <v>6</v>
       </c>
       <c r="C249">
-        <v>0.4206245291755838</v>
+        <v>0.4313281847867615</v>
       </c>
       <c r="D249" t="s">
         <v>7</v>
@@ -8573,10 +8573,10 @@
         <v>508</v>
       </c>
       <c r="B250" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C250">
-        <v>0.294753895305112</v>
+        <v>0.3144152454635587</v>
       </c>
       <c r="D250" t="s">
         <v>7</v>
@@ -8593,7 +8593,7 @@
         <v>44</v>
       </c>
       <c r="C251">
-        <v>0.4901194882770973</v>
+        <v>0.4956648060980605</v>
       </c>
       <c r="D251" t="s">
         <v>7</v>
@@ -8610,7 +8610,7 @@
         <v>6</v>
       </c>
       <c r="C252">
-        <v>0.3700099594971057</v>
+        <v>0.412613287327262</v>
       </c>
       <c r="D252" t="s">
         <v>7</v>
@@ -8627,7 +8627,7 @@
         <v>6</v>
       </c>
       <c r="C253">
-        <v>0.330546251343952</v>
+        <v>0.3640125533911438</v>
       </c>
       <c r="D253" t="s">
         <v>7</v>
@@ -8644,7 +8644,7 @@
         <v>6</v>
       </c>
       <c r="C254">
-        <v>0.4680618251149123</v>
+        <v>0.4952444340995464</v>
       </c>
       <c r="D254" t="s">
         <v>7</v>
@@ -8658,10 +8658,10 @@
         <v>518</v>
       </c>
       <c r="B255" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C255">
-        <v>0.4778316099310007</v>
+        <v>0.4477480114328528</v>
       </c>
       <c r="D255" t="s">
         <v>7</v>
@@ -8678,7 +8678,7 @@
         <v>6</v>
       </c>
       <c r="C256">
-        <v>0.5869314304506835</v>
+        <v>0.5998794761109332</v>
       </c>
       <c r="D256" t="s">
         <v>7</v>
@@ -8695,7 +8695,7 @@
         <v>6</v>
       </c>
       <c r="C257">
-        <v>0.3845433365935728</v>
+        <v>0.4083044809684342</v>
       </c>
       <c r="D257" t="s">
         <v>7</v>
@@ -8712,7 +8712,7 @@
         <v>6</v>
       </c>
       <c r="C258">
-        <v>0.4857713555955565</v>
+        <v>0.5038548175019024</v>
       </c>
       <c r="D258" t="s">
         <v>7</v>
@@ -8726,10 +8726,10 @@
         <v>526</v>
       </c>
       <c r="B259" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C259">
-        <v>0.3014763423330936</v>
+        <v>0.298309960583961</v>
       </c>
       <c r="D259" t="s">
         <v>7</v>
@@ -8746,7 +8746,7 @@
         <v>6</v>
       </c>
       <c r="C260">
-        <v>0.4154480628594182</v>
+        <v>0.4380693008040051</v>
       </c>
       <c r="D260" t="s">
         <v>7</v>
@@ -8763,7 +8763,7 @@
         <v>6</v>
       </c>
       <c r="C261">
-        <v>0.4664717649825334</v>
+        <v>0.4864763997171652</v>
       </c>
       <c r="D261" t="s">
         <v>7</v>
@@ -8780,7 +8780,7 @@
         <v>6</v>
       </c>
       <c r="C262">
-        <v>0.4143603629621579</v>
+        <v>0.4287235228623805</v>
       </c>
       <c r="D262" t="s">
         <v>7</v>
@@ -8797,7 +8797,7 @@
         <v>6</v>
       </c>
       <c r="C263">
-        <v>0.4375057259717712</v>
+        <v>0.4641700467578964</v>
       </c>
       <c r="D263" t="s">
         <v>7</v>
@@ -8814,7 +8814,7 @@
         <v>6</v>
       </c>
       <c r="C264">
-        <v>0.4153529789177671</v>
+        <v>0.4459811716922109</v>
       </c>
       <c r="D264" t="s">
         <v>7</v>
@@ -8831,7 +8831,7 @@
         <v>6</v>
       </c>
       <c r="C265">
-        <v>0.3287516391891646</v>
+        <v>0.3460140349583291</v>
       </c>
       <c r="D265" t="s">
         <v>7</v>
@@ -8848,7 +8848,7 @@
         <v>6</v>
       </c>
       <c r="C266">
-        <v>0.3628686972194654</v>
+        <v>0.4001543853618537</v>
       </c>
       <c r="D266" t="s">
         <v>7</v>
@@ -8865,7 +8865,7 @@
         <v>6</v>
       </c>
       <c r="C267">
-        <v>0.2498743183649366</v>
+        <v>0.27489883096257</v>
       </c>
       <c r="D267" t="s">
         <v>7</v>
@@ -8882,7 +8882,7 @@
         <v>6</v>
       </c>
       <c r="C268">
-        <v>0.4176244865813888</v>
+        <v>0.4522097145691867</v>
       </c>
       <c r="D268" t="s">
         <v>7</v>
@@ -8899,7 +8899,7 @@
         <v>44</v>
       </c>
       <c r="C269">
-        <v>0.3717419941545167</v>
+        <v>0.3742069161109122</v>
       </c>
       <c r="D269" t="s">
         <v>7</v>
@@ -8916,7 +8916,7 @@
         <v>6</v>
       </c>
       <c r="C270">
-        <v>0.5198557021059653</v>
+        <v>0.5360106206282612</v>
       </c>
       <c r="D270" t="s">
         <v>7</v>
@@ -8933,7 +8933,7 @@
         <v>6</v>
       </c>
       <c r="C271">
-        <v>0.5506138635607348</v>
+        <v>0.545025541322165</v>
       </c>
       <c r="D271" t="s">
         <v>7</v>
@@ -8950,7 +8950,7 @@
         <v>6</v>
       </c>
       <c r="C272">
-        <v>0.3456008845730008</v>
+        <v>0.3836762635762402</v>
       </c>
       <c r="D272" t="s">
         <v>7</v>
@@ -8967,7 +8967,7 @@
         <v>6</v>
       </c>
       <c r="C273">
-        <v>0.5047872520486726</v>
+        <v>0.5318173437997095</v>
       </c>
       <c r="D273" t="s">
         <v>7</v>
@@ -8981,10 +8981,10 @@
         <v>556</v>
       </c>
       <c r="B274" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C274">
-        <v>0.3609825988105117</v>
+        <v>0.3538248437096296</v>
       </c>
       <c r="D274" t="s">
         <v>7</v>
@@ -8998,10 +8998,10 @@
         <v>558</v>
       </c>
       <c r="B275" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C275">
-        <v>0.2471938644485852</v>
+        <v>0.2470521541805436</v>
       </c>
       <c r="D275" t="s">
         <v>7</v>
@@ -9018,7 +9018,7 @@
         <v>6</v>
       </c>
       <c r="C276">
-        <v>0.315276623299826</v>
+        <v>0.3205862798227412</v>
       </c>
       <c r="D276" t="s">
         <v>7</v>
@@ -9032,10 +9032,10 @@
         <v>562</v>
       </c>
       <c r="B277" t="s">
-        <v>79</v>
+        <v>6</v>
       </c>
       <c r="C277">
-        <v>0.4310931270753286</v>
+        <v>0.3775952015336524</v>
       </c>
       <c r="D277" t="s">
         <v>7</v>
@@ -9052,7 +9052,7 @@
         <v>6</v>
       </c>
       <c r="C278">
-        <v>0.3982732736784659</v>
+        <v>0.4472552011613439</v>
       </c>
       <c r="D278" t="s">
         <v>7</v>
@@ -9069,7 +9069,7 @@
         <v>6</v>
       </c>
       <c r="C279">
-        <v>0.533584518793604</v>
+        <v>0.5470272584789674</v>
       </c>
       <c r="D279" t="s">
         <v>7</v>
@@ -9086,7 +9086,7 @@
         <v>6</v>
       </c>
       <c r="C280">
-        <v>0.4737056730530078</v>
+        <v>0.4957217443707417</v>
       </c>
       <c r="D280" t="s">
         <v>7</v>
@@ -9103,7 +9103,7 @@
         <v>6</v>
       </c>
       <c r="C281">
-        <v>0.3867319597409787</v>
+        <v>0.3982901030774012</v>
       </c>
       <c r="D281" t="s">
         <v>7</v>
@@ -9117,10 +9117,10 @@
         <v>572</v>
       </c>
       <c r="B282" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C282">
-        <v>0.385273914294723</v>
+        <v>0.3652230944510147</v>
       </c>
       <c r="D282" t="s">
         <v>7</v>
@@ -9134,10 +9134,10 @@
         <v>574</v>
       </c>
       <c r="B283" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C283">
-        <v>0.3617437170941228</v>
+        <v>0.3511290221596897</v>
       </c>
       <c r="D283" t="s">
         <v>7</v>
@@ -9154,7 +9154,7 @@
         <v>6</v>
       </c>
       <c r="C284">
-        <v>0.3217035281941626</v>
+        <v>0.3311349468320045</v>
       </c>
       <c r="D284" t="s">
         <v>7</v>
@@ -9168,10 +9168,10 @@
         <v>578</v>
       </c>
       <c r="B285" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C285">
-        <v>0.2368714964975877</v>
+        <v>0.2471130291645466</v>
       </c>
       <c r="D285" t="s">
         <v>7</v>
@@ -9188,7 +9188,7 @@
         <v>6</v>
       </c>
       <c r="C286">
-        <v>0.2891015214108358</v>
+        <v>0.2982945753434204</v>
       </c>
       <c r="D286" t="s">
         <v>7</v>
@@ -9205,7 +9205,7 @@
         <v>44</v>
       </c>
       <c r="C287">
-        <v>0.4819933495265971</v>
+        <v>0.4707537629897592</v>
       </c>
       <c r="D287" t="s">
         <v>7</v>
@@ -9222,7 +9222,7 @@
         <v>6</v>
       </c>
       <c r="C288">
-        <v>0.2544269851430639</v>
+        <v>0.2732692304410334</v>
       </c>
       <c r="D288" t="s">
         <v>7</v>
@@ -9239,7 +9239,7 @@
         <v>6</v>
       </c>
       <c r="C289">
-        <v>0.344477059943197</v>
+        <v>0.3715527343026447</v>
       </c>
       <c r="D289" t="s">
         <v>7</v>
@@ -9253,10 +9253,10 @@
         <v>588</v>
       </c>
       <c r="B290" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C290">
-        <v>0.3068820765488964</v>
+        <v>0.3157416106838649</v>
       </c>
       <c r="D290" t="s">
         <v>7</v>
@@ -9273,7 +9273,7 @@
         <v>6</v>
       </c>
       <c r="C291">
-        <v>0.43454832795702</v>
+        <v>0.4326806216142559</v>
       </c>
       <c r="D291" t="s">
         <v>7</v>
@@ -9287,10 +9287,10 @@
         <v>592</v>
       </c>
       <c r="B292" t="s">
-        <v>79</v>
+        <v>145</v>
       </c>
       <c r="C292">
-        <v>0.4852450899255945</v>
+        <v>0.4348878100797352</v>
       </c>
       <c r="D292" t="s">
         <v>7</v>
@@ -9307,7 +9307,7 @@
         <v>6</v>
       </c>
       <c r="C293">
-        <v>0.6065921239979619</v>
+        <v>0.6096690182428608</v>
       </c>
       <c r="D293" t="s">
         <v>7</v>
@@ -9321,10 +9321,10 @@
         <v>596</v>
       </c>
       <c r="B294" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C294">
-        <v>0.4249526031032193</v>
+        <v>0.4072351746972967</v>
       </c>
       <c r="D294" t="s">
         <v>7</v>
@@ -9338,10 +9338,10 @@
         <v>598</v>
       </c>
       <c r="B295" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C295">
-        <v>0.3062291185111508</v>
+        <v>0.3258689965924915</v>
       </c>
       <c r="D295" t="s">
         <v>7</v>
@@ -9355,10 +9355,10 @@
         <v>600</v>
       </c>
       <c r="B296" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C296">
-        <v>0.2995599492379087</v>
+        <v>0.3107578013810601</v>
       </c>
       <c r="D296" t="s">
         <v>7</v>
@@ -9372,10 +9372,10 @@
         <v>602</v>
       </c>
       <c r="B297" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C297">
-        <v>0.4120705429776052</v>
+        <v>0.4586725376093624</v>
       </c>
       <c r="D297" t="s">
         <v>7</v>
@@ -9389,10 +9389,10 @@
         <v>604</v>
       </c>
       <c r="B298" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C298">
-        <v>0.3582941781481896</v>
+        <v>0.3929279416878534</v>
       </c>
       <c r="D298" t="s">
         <v>7</v>
@@ -9409,7 +9409,7 @@
         <v>44</v>
       </c>
       <c r="C299">
-        <v>0.2861549308586899</v>
+        <v>0.2724267678915268</v>
       </c>
       <c r="D299" t="s">
         <v>7</v>
@@ -9423,10 +9423,10 @@
         <v>608</v>
       </c>
       <c r="B300" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C300">
-        <v>0.3227362685329092</v>
+        <v>0.3237046944611848</v>
       </c>
       <c r="D300" t="s">
         <v>7</v>
@@ -9443,7 +9443,7 @@
         <v>6</v>
       </c>
       <c r="C301">
-        <v>0.3437267914930859</v>
+        <v>0.3594218945460432</v>
       </c>
       <c r="D301" t="s">
         <v>7</v>
@@ -9460,7 +9460,7 @@
         <v>44</v>
       </c>
       <c r="C302">
-        <v>0.4674832079199708</v>
+        <v>0.4692241628957253</v>
       </c>
       <c r="D302" t="s">
         <v>7</v>
@@ -9474,10 +9474,10 @@
         <v>614</v>
       </c>
       <c r="B303" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C303">
-        <v>0.3068253780039805</v>
+        <v>0.3113951720533466</v>
       </c>
       <c r="D303" t="s">
         <v>7</v>
@@ -9491,10 +9491,10 @@
         <v>616</v>
       </c>
       <c r="B304" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C304">
-        <v>0.2841211686297654</v>
+        <v>0.2960098879222638</v>
       </c>
       <c r="D304" t="s">
         <v>7</v>
@@ -9511,7 +9511,7 @@
         <v>44</v>
       </c>
       <c r="C305">
-        <v>0.3972044998980188</v>
+        <v>0.4023084222755631</v>
       </c>
       <c r="D305" t="s">
         <v>7</v>
@@ -9525,10 +9525,10 @@
         <v>620</v>
       </c>
       <c r="B306" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C306">
-        <v>0.4900783257037527</v>
+        <v>0.4317027411156236</v>
       </c>
       <c r="D306" t="s">
         <v>7</v>
@@ -9545,7 +9545,7 @@
         <v>6</v>
       </c>
       <c r="C307">
-        <v>0.4290848121071581</v>
+        <v>0.4258750280921418</v>
       </c>
       <c r="D307" t="s">
         <v>7</v>
@@ -9562,7 +9562,7 @@
         <v>6</v>
       </c>
       <c r="C308">
-        <v>0.3812892264106097</v>
+        <v>0.3956219004151964</v>
       </c>
       <c r="D308" t="s">
         <v>7</v>
@@ -9579,7 +9579,7 @@
         <v>6</v>
       </c>
       <c r="C309">
-        <v>0.2729348839328355</v>
+        <v>0.2765356806492457</v>
       </c>
       <c r="D309" t="s">
         <v>7</v>
@@ -9596,7 +9596,7 @@
         <v>6</v>
       </c>
       <c r="C310">
-        <v>0.3924817248870033</v>
+        <v>0.4106840097620228</v>
       </c>
       <c r="D310" t="s">
         <v>7</v>
@@ -9610,10 +9610,10 @@
         <v>630</v>
       </c>
       <c r="B311" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C311">
-        <v>0.3649826564721951</v>
+        <v>0.3497578615105849</v>
       </c>
       <c r="D311" t="s">
         <v>7</v>
@@ -9627,10 +9627,10 @@
         <v>632</v>
       </c>
       <c r="B312" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C312">
-        <v>0.2525512797727946</v>
+        <v>0.2716780196777767</v>
       </c>
       <c r="D312" t="s">
         <v>7</v>
@@ -9647,7 +9647,7 @@
         <v>44</v>
       </c>
       <c r="C313">
-        <v>0.3273223810051179</v>
+        <v>0.3144619068046991</v>
       </c>
       <c r="D313" t="s">
         <v>7</v>
@@ -9661,10 +9661,10 @@
         <v>636</v>
       </c>
       <c r="B314" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C314">
-        <v>0.2937165267147964</v>
+        <v>0.2995171261039128</v>
       </c>
       <c r="D314" t="s">
         <v>7</v>
@@ -9681,7 +9681,7 @@
         <v>44</v>
       </c>
       <c r="C315">
-        <v>0.4942634895910673</v>
+        <v>0.5030119793598046</v>
       </c>
       <c r="D315" t="s">
         <v>7</v>
@@ -9698,7 +9698,7 @@
         <v>6</v>
       </c>
       <c r="C316">
-        <v>0.3504492670981796</v>
+        <v>0.3882333791138319</v>
       </c>
       <c r="D316" t="s">
         <v>7</v>
@@ -9715,7 +9715,7 @@
         <v>6</v>
       </c>
       <c r="C317">
-        <v>0.4936853486780529</v>
+        <v>0.5312937698599693</v>
       </c>
       <c r="D317" t="s">
         <v>7</v>
@@ -9732,7 +9732,7 @@
         <v>6</v>
       </c>
       <c r="C318">
-        <v>0.5251042912253109</v>
+        <v>0.5585781178314113</v>
       </c>
       <c r="D318" t="s">
         <v>7</v>
@@ -9749,7 +9749,7 @@
         <v>6</v>
       </c>
       <c r="C319">
-        <v>0.3305651522249652</v>
+        <v>0.34658658720485</v>
       </c>
       <c r="D319" t="s">
         <v>7</v>
@@ -9763,10 +9763,10 @@
         <v>648</v>
       </c>
       <c r="B320" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C320">
-        <v>0.2654949543906793</v>
+        <v>0.2807207142330665</v>
       </c>
       <c r="D320" t="s">
         <v>7</v>
@@ -9783,7 +9783,7 @@
         <v>6</v>
       </c>
       <c r="C321">
-        <v>0.3395079146313663</v>
+        <v>0.3529537752677362</v>
       </c>
       <c r="D321" t="s">
         <v>7</v>
@@ -9800,7 +9800,7 @@
         <v>6</v>
       </c>
       <c r="C322">
-        <v>0.3485061586486588</v>
+        <v>0.3777685342998616</v>
       </c>
       <c r="D322" t="s">
         <v>7</v>
@@ -9814,10 +9814,10 @@
         <v>654</v>
       </c>
       <c r="B323" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C323">
-        <v>0.3038495525059894</v>
+        <v>0.3178933526716169</v>
       </c>
       <c r="D323" t="s">
         <v>7</v>
@@ -9834,7 +9834,7 @@
         <v>44</v>
       </c>
       <c r="C324">
-        <v>0.3959497031438496</v>
+        <v>0.4064018787656126</v>
       </c>
       <c r="D324" t="s">
         <v>7</v>
@@ -9848,10 +9848,10 @@
         <v>658</v>
       </c>
       <c r="B325" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="C325">
-        <v>0.2367742231131662</v>
+        <v>0.220257006478951</v>
       </c>
       <c r="D325" t="s">
         <v>7</v>
@@ -9868,7 +9868,7 @@
         <v>44</v>
       </c>
       <c r="C326">
-        <v>0.3750311137141048</v>
+        <v>0.3670231080288204</v>
       </c>
       <c r="D326" t="s">
         <v>7</v>
@@ -9885,7 +9885,7 @@
         <v>44</v>
       </c>
       <c r="C327">
-        <v>0.3368313100919328</v>
+        <v>0.3257836925848742</v>
       </c>
       <c r="D327" t="s">
         <v>7</v>
@@ -9899,10 +9899,10 @@
         <v>664</v>
       </c>
       <c r="B328" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C328">
-        <v>0.2704430253201534</v>
+        <v>0.2788693950164571</v>
       </c>
       <c r="D328" t="s">
         <v>7</v>
@@ -9916,10 +9916,10 @@
         <v>666</v>
       </c>
       <c r="B329" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C329">
-        <v>0.2841047544583576</v>
+        <v>0.3001956267066369</v>
       </c>
       <c r="D329" t="s">
         <v>7</v>
@@ -9933,10 +9933,10 @@
         <v>668</v>
       </c>
       <c r="B330" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C330">
-        <v>0.3208474343204666</v>
+        <v>0.3165332827973709</v>
       </c>
       <c r="D330" t="s">
         <v>7</v>
@@ -9953,7 +9953,7 @@
         <v>10</v>
       </c>
       <c r="C331">
-        <v>0.3656023360617762</v>
+        <v>0.3591439584070425</v>
       </c>
       <c r="D331" t="s">
         <v>7</v>
@@ -9967,10 +9967,10 @@
         <v>672</v>
       </c>
       <c r="B332" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C332">
-        <v>0.331252045483267</v>
+        <v>0.3446512731069328</v>
       </c>
       <c r="D332" t="s">
         <v>7</v>
@@ -9987,7 +9987,7 @@
         <v>6</v>
       </c>
       <c r="C333">
-        <v>0.4617084331013162</v>
+        <v>0.4795055885624363</v>
       </c>
       <c r="D333" t="s">
         <v>7</v>
@@ -10001,10 +10001,10 @@
         <v>676</v>
       </c>
       <c r="B334" t="s">
-        <v>79</v>
+        <v>15</v>
       </c>
       <c r="C334">
-        <v>0.2559891553923031</v>
+        <v>0.3047915206114759</v>
       </c>
       <c r="D334" t="s">
         <v>7</v>
@@ -10018,10 +10018,10 @@
         <v>678</v>
       </c>
       <c r="B335" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C335">
-        <v>0.357592846573205</v>
+        <v>0.3521803938942047</v>
       </c>
       <c r="D335" t="s">
         <v>7</v>
@@ -10035,10 +10035,10 @@
         <v>680</v>
       </c>
       <c r="B336" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C336">
-        <v>0.3055676064747564</v>
+        <v>0.313448716369143</v>
       </c>
       <c r="D336" t="s">
         <v>7</v>
@@ -10055,7 +10055,7 @@
         <v>44</v>
       </c>
       <c r="C337">
-        <v>0.4118050910011717</v>
+        <v>0.4349343024479565</v>
       </c>
       <c r="D337" t="s">
         <v>7</v>
@@ -10072,7 +10072,7 @@
         <v>6</v>
       </c>
       <c r="C338">
-        <v>0.284482982717028</v>
+        <v>0.2854852829759107</v>
       </c>
       <c r="D338" t="s">
         <v>7</v>
@@ -10086,10 +10086,10 @@
         <v>686</v>
       </c>
       <c r="B339" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C339">
-        <v>0.4729884323719991</v>
+        <v>0.4458043344323856</v>
       </c>
       <c r="D339" t="s">
         <v>7</v>
@@ -10103,10 +10103,10 @@
         <v>688</v>
       </c>
       <c r="B340" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C340">
-        <v>0.2795109317370509</v>
+        <v>0.3047709792065275</v>
       </c>
       <c r="D340" t="s">
         <v>7</v>
@@ -10123,7 +10123,7 @@
         <v>6</v>
       </c>
       <c r="C341">
-        <v>0.2980229680464076</v>
+        <v>0.2990813877334996</v>
       </c>
       <c r="D341" t="s">
         <v>7</v>
@@ -10137,10 +10137,10 @@
         <v>692</v>
       </c>
       <c r="B342" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C342">
-        <v>0.269644962292767</v>
+        <v>0.2721560871503791</v>
       </c>
       <c r="D342" t="s">
         <v>7</v>
@@ -10154,10 +10154,10 @@
         <v>694</v>
       </c>
       <c r="B343" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C343">
-        <v>0.3558535325266513</v>
+        <v>0.3794909387912558</v>
       </c>
       <c r="D343" t="s">
         <v>7</v>
@@ -10171,10 +10171,10 @@
         <v>696</v>
       </c>
       <c r="B344" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C344">
-        <v>0.2418088927725526</v>
+        <v>0.2588774413122668</v>
       </c>
       <c r="D344" t="s">
         <v>7</v>
@@ -10191,7 +10191,7 @@
         <v>6</v>
       </c>
       <c r="C345">
-        <v>0.342866044645609</v>
+        <v>0.3726174277736634</v>
       </c>
       <c r="D345" t="s">
         <v>7</v>
@@ -10205,10 +10205,10 @@
         <v>700</v>
       </c>
       <c r="B346" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C346">
-        <v>0.3226637100034135</v>
+        <v>0.3232982652366989</v>
       </c>
       <c r="D346" t="s">
         <v>7</v>
@@ -10222,10 +10222,10 @@
         <v>702</v>
       </c>
       <c r="B347" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C347">
-        <v>0.3561518313583903</v>
+        <v>0.3486952262558319</v>
       </c>
       <c r="D347" t="s">
         <v>7</v>
@@ -10242,7 +10242,7 @@
         <v>6</v>
       </c>
       <c r="C348">
-        <v>0.3240661650475435</v>
+        <v>0.3530073020373877</v>
       </c>
       <c r="D348" t="s">
         <v>7</v>
@@ -10259,7 +10259,7 @@
         <v>6</v>
       </c>
       <c r="C349">
-        <v>0.5087688673501838</v>
+        <v>0.4980031414894597</v>
       </c>
       <c r="D349" t="s">
         <v>7</v>
@@ -10273,10 +10273,10 @@
         <v>708</v>
       </c>
       <c r="B350" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C350">
-        <v>0.3680436522539374</v>
+        <v>0.3555779640253525</v>
       </c>
       <c r="D350" t="s">
         <v>7</v>
@@ -10290,10 +10290,10 @@
         <v>710</v>
       </c>
       <c r="B351" t="s">
-        <v>79</v>
+        <v>145</v>
       </c>
       <c r="C351">
-        <v>0.2983734046938649</v>
+        <v>0.2389293229611857</v>
       </c>
       <c r="D351" t="s">
         <v>7</v>
@@ -10307,10 +10307,10 @@
         <v>712</v>
       </c>
       <c r="B352" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C352">
-        <v>0.4056922131568523</v>
+        <v>0.3990660858335938</v>
       </c>
       <c r="D352" t="s">
         <v>7</v>
@@ -10324,10 +10324,10 @@
         <v>714</v>
       </c>
       <c r="B353" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C353">
-        <v>0.3545692344163664</v>
+        <v>0.3721755721657349</v>
       </c>
       <c r="D353" t="s">
         <v>7</v>
@@ -10344,7 +10344,7 @@
         <v>6</v>
       </c>
       <c r="C354">
-        <v>0.2855240063532514</v>
+        <v>0.2903983149070718</v>
       </c>
       <c r="D354" t="s">
         <v>7</v>
@@ -10361,7 +10361,7 @@
         <v>6</v>
       </c>
       <c r="C355">
-        <v>0.3410497998986727</v>
+        <v>0.3819562470991175</v>
       </c>
       <c r="D355" t="s">
         <v>7</v>
@@ -10378,7 +10378,7 @@
         <v>6</v>
       </c>
       <c r="C356">
-        <v>0.3132144786174916</v>
+        <v>0.3227839113560097</v>
       </c>
       <c r="D356" t="s">
         <v>7</v>
@@ -10395,7 +10395,7 @@
         <v>6</v>
       </c>
       <c r="C357">
-        <v>0.3815512926309224</v>
+        <v>0.4084791249552997</v>
       </c>
       <c r="D357" t="s">
         <v>7</v>
@@ -10409,10 +10409,10 @@
         <v>724</v>
       </c>
       <c r="B358" t="s">
-        <v>79</v>
+        <v>6</v>
       </c>
       <c r="C358">
-        <v>0.342873169221634</v>
+        <v>0.3458304139432658</v>
       </c>
       <c r="D358" t="s">
         <v>7</v>
@@ -10429,7 +10429,7 @@
         <v>44</v>
       </c>
       <c r="C359">
-        <v>0.4602245178497633</v>
+        <v>0.4528335956850251</v>
       </c>
       <c r="D359" t="s">
         <v>7</v>
@@ -10446,7 +10446,7 @@
         <v>6</v>
       </c>
       <c r="C360">
-        <v>0.4925601697322087</v>
+        <v>0.4877784654609692</v>
       </c>
       <c r="D360" t="s">
         <v>7</v>
@@ -10460,10 +10460,10 @@
         <v>730</v>
       </c>
       <c r="B361" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C361">
-        <v>0.3087103819321343</v>
+        <v>0.3057092016594836</v>
       </c>
       <c r="D361" t="s">
         <v>7</v>
@@ -10480,7 +10480,7 @@
         <v>6</v>
       </c>
       <c r="C362">
-        <v>0.3598741143582589</v>
+        <v>0.3678651736383626</v>
       </c>
       <c r="D362" t="s">
         <v>7</v>
@@ -10497,7 +10497,7 @@
         <v>6</v>
       </c>
       <c r="C363">
-        <v>0.2848037642357048</v>
+        <v>0.2896491248062164</v>
       </c>
       <c r="D363" t="s">
         <v>7</v>
@@ -10511,10 +10511,10 @@
         <v>736</v>
       </c>
       <c r="B364" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C364">
-        <v>0.2853645223374569</v>
+        <v>0.3062765197452864</v>
       </c>
       <c r="D364" t="s">
         <v>7</v>
@@ -10528,10 +10528,10 @@
         <v>738</v>
       </c>
       <c r="B365" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C365">
-        <v>0.3161323413993479</v>
+        <v>0.3191356235027803</v>
       </c>
       <c r="D365" t="s">
         <v>7</v>
@@ -10545,10 +10545,10 @@
         <v>740</v>
       </c>
       <c r="B366" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C366">
-        <v>0.2477619373291138</v>
+        <v>0.2721207579711444</v>
       </c>
       <c r="D366" t="s">
         <v>7</v>
@@ -10565,7 +10565,7 @@
         <v>6</v>
       </c>
       <c r="C367">
-        <v>0.3260859479095397</v>
+        <v>0.3570953578617954</v>
       </c>
       <c r="D367" t="s">
         <v>7</v>
@@ -10579,10 +10579,10 @@
         <v>744</v>
       </c>
       <c r="B368" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C368">
-        <v>0.3577851294245041</v>
+        <v>0.3568299810265756</v>
       </c>
       <c r="D368" t="s">
         <v>7</v>
@@ -10599,7 +10599,7 @@
         <v>6</v>
       </c>
       <c r="C369">
-        <v>0.5672330199771578</v>
+        <v>0.5365589787463735</v>
       </c>
       <c r="D369" t="s">
         <v>7</v>
@@ -10613,10 +10613,10 @@
         <v>748</v>
       </c>
       <c r="B370" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C370">
-        <v>0.3288845142900242</v>
+        <v>0.3416768851249381</v>
       </c>
       <c r="D370" t="s">
         <v>7</v>
@@ -10633,7 +10633,7 @@
         <v>6</v>
       </c>
       <c r="C371">
-        <v>0.4566596311109102</v>
+        <v>0.475330483179788</v>
       </c>
       <c r="D371" t="s">
         <v>7</v>
@@ -10650,7 +10650,7 @@
         <v>6</v>
       </c>
       <c r="C372">
-        <v>0.3539196912358694</v>
+        <v>0.3836238396119306</v>
       </c>
       <c r="D372" t="s">
         <v>7</v>
@@ -10667,7 +10667,7 @@
         <v>6</v>
       </c>
       <c r="C373">
-        <v>0.4268975275884578</v>
+        <v>0.4459139234820456</v>
       </c>
       <c r="D373" t="s">
         <v>7</v>
@@ -10684,7 +10684,7 @@
         <v>6</v>
       </c>
       <c r="C374">
-        <v>0.4850532774202961</v>
+        <v>0.5007435441542931</v>
       </c>
       <c r="D374" t="s">
         <v>7</v>
@@ -10701,7 +10701,7 @@
         <v>6</v>
       </c>
       <c r="C375">
-        <v>0.4444634647490701</v>
+        <v>0.4805282975018298</v>
       </c>
       <c r="D375" t="s">
         <v>7</v>
@@ -10715,10 +10715,10 @@
         <v>760</v>
       </c>
       <c r="B376" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C376">
-        <v>0.3494424720929362</v>
+        <v>0.3547355265524255</v>
       </c>
       <c r="D376" t="s">
         <v>7</v>
@@ -10735,7 +10735,7 @@
         <v>6</v>
       </c>
       <c r="C377">
-        <v>0.4710131461362481</v>
+        <v>0.4890450285563663</v>
       </c>
       <c r="D377" t="s">
         <v>7</v>
@@ -10752,7 +10752,7 @@
         <v>6</v>
       </c>
       <c r="C378">
-        <v>0.310140419008588</v>
+        <v>0.3189023059272294</v>
       </c>
       <c r="D378" t="s">
         <v>7</v>
@@ -10769,7 +10769,7 @@
         <v>6</v>
       </c>
       <c r="C379">
-        <v>0.3335932425756207</v>
+        <v>0.33193303184139</v>
       </c>
       <c r="D379" t="s">
         <v>7</v>
@@ -10786,7 +10786,7 @@
         <v>6</v>
       </c>
       <c r="C380">
-        <v>0.363408017239023</v>
+        <v>0.380505937209123</v>
       </c>
       <c r="D380" t="s">
         <v>7</v>
@@ -10800,10 +10800,10 @@
         <v>770</v>
       </c>
       <c r="B381" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C381">
-        <v>0.433604350585675</v>
+        <v>0.4688006910022827</v>
       </c>
       <c r="D381" t="s">
         <v>7</v>
@@ -10820,7 +10820,7 @@
         <v>6</v>
       </c>
       <c r="C382">
-        <v>0.3365710917997811</v>
+        <v>0.3382818743965192</v>
       </c>
       <c r="D382" t="s">
         <v>7</v>
@@ -10834,10 +10834,10 @@
         <v>774</v>
       </c>
       <c r="B383" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C383">
-        <v>0.3488751556788903</v>
+        <v>0.3689678404919182</v>
       </c>
       <c r="D383" t="s">
         <v>7</v>
@@ -10854,7 +10854,7 @@
         <v>44</v>
       </c>
       <c r="C384">
-        <v>0.4588479214627305</v>
+        <v>0.4358004397927337</v>
       </c>
       <c r="D384" t="s">
         <v>7</v>
@@ -10871,7 +10871,7 @@
         <v>6</v>
       </c>
       <c r="C385">
-        <v>0.3896002672044507</v>
+        <v>0.4109915775745731</v>
       </c>
       <c r="D385" t="s">
         <v>7</v>
@@ -10885,10 +10885,10 @@
         <v>780</v>
       </c>
       <c r="B386" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C386">
-        <v>0.2844276955118172</v>
+        <v>0.3022559536176835</v>
       </c>
       <c r="D386" t="s">
         <v>7</v>
@@ -10902,10 +10902,10 @@
         <v>782</v>
       </c>
       <c r="B387" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C387">
-        <v>0.396761053256302</v>
+        <v>0.4187939811953572</v>
       </c>
       <c r="D387" t="s">
         <v>7</v>
@@ -10922,7 +10922,7 @@
         <v>44</v>
       </c>
       <c r="C388">
-        <v>0.3078682319556003</v>
+        <v>0.2896212500113542</v>
       </c>
       <c r="D388" t="s">
         <v>7</v>
@@ -10939,7 +10939,7 @@
         <v>6</v>
       </c>
       <c r="C389">
-        <v>0.3508316156744308</v>
+        <v>0.3671986447706274</v>
       </c>
       <c r="D389" t="s">
         <v>7</v>
@@ -10953,10 +10953,10 @@
         <v>788</v>
       </c>
       <c r="B390" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C390">
-        <v>0.338306166971486</v>
+        <v>0.3346569449653552</v>
       </c>
       <c r="D390" t="s">
         <v>7</v>
@@ -10970,10 +10970,10 @@
         <v>790</v>
       </c>
       <c r="B391" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C391">
-        <v>0.3771037625274989</v>
+        <v>0.3458973998735382</v>
       </c>
       <c r="D391" t="s">
         <v>7</v>
@@ -10987,10 +10987,10 @@
         <v>792</v>
       </c>
       <c r="B392" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C392">
-        <v>0.3164240918241739</v>
+        <v>0.3225934970983097</v>
       </c>
       <c r="D392" t="s">
         <v>7</v>
@@ -11004,10 +11004,10 @@
         <v>794</v>
       </c>
       <c r="B393" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C393">
-        <v>0.3788850492005276</v>
+        <v>0.3787321103203632</v>
       </c>
       <c r="D393" t="s">
         <v>7</v>
@@ -11021,10 +11021,10 @@
         <v>796</v>
       </c>
       <c r="B394" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C394">
-        <v>0.3784855630043354</v>
+        <v>0.3688174300211956</v>
       </c>
       <c r="D394" t="s">
         <v>7</v>
@@ -11038,10 +11038,10 @@
         <v>798</v>
       </c>
       <c r="B395" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C395">
-        <v>0.4122815173360852</v>
+        <v>0.4159781236541838</v>
       </c>
       <c r="D395" t="s">
         <v>7</v>
@@ -11058,7 +11058,7 @@
         <v>6</v>
       </c>
       <c r="C396">
-        <v>0.3728690296861203</v>
+        <v>0.3935152201867761</v>
       </c>
       <c r="D396" t="s">
         <v>7</v>
@@ -11072,10 +11072,10 @@
         <v>802</v>
       </c>
       <c r="B397" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C397">
-        <v>0.3362966528046027</v>
+        <v>0.3378939523612386</v>
       </c>
       <c r="D397" t="s">
         <v>7</v>
@@ -11092,7 +11092,7 @@
         <v>6</v>
       </c>
       <c r="C398">
-        <v>0.5009763496460983</v>
+        <v>0.5011520367850562</v>
       </c>
       <c r="D398" t="s">
         <v>7</v>
@@ -11106,10 +11106,10 @@
         <v>806</v>
       </c>
       <c r="B399" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C399">
-        <v>0.3620657187242247</v>
+        <v>0.3532540386337862</v>
       </c>
       <c r="D399" t="s">
         <v>7</v>
@@ -11126,7 +11126,7 @@
         <v>6</v>
       </c>
       <c r="C400">
-        <v>0.3396357613486796</v>
+        <v>0.3420977947133838</v>
       </c>
       <c r="D400" t="s">
         <v>7</v>
@@ -11140,10 +11140,10 @@
         <v>810</v>
       </c>
       <c r="B401" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C401">
-        <v>0.4820023246090103</v>
+        <v>0.4471594489038782</v>
       </c>
       <c r="D401" t="s">
         <v>7</v>
@@ -11160,7 +11160,7 @@
         <v>6</v>
       </c>
       <c r="C402">
-        <v>0.3910028028063164</v>
+        <v>0.4014000649469068</v>
       </c>
       <c r="D402" t="s">
         <v>7</v>
@@ -11177,7 +11177,7 @@
         <v>6</v>
       </c>
       <c r="C403">
-        <v>0.2961928965264862</v>
+        <v>0.3058075027467035</v>
       </c>
       <c r="D403" t="s">
         <v>7</v>
@@ -11191,10 +11191,10 @@
         <v>816</v>
       </c>
       <c r="B404" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C404">
-        <v>0.2971490462965958</v>
+        <v>0.3158274266041715</v>
       </c>
       <c r="D404" t="s">
         <v>7</v>
@@ -11211,7 +11211,7 @@
         <v>6</v>
       </c>
       <c r="C405">
-        <v>0.3838538386670843</v>
+        <v>0.4324767824202079</v>
       </c>
       <c r="D405" t="s">
         <v>7</v>
@@ -11225,10 +11225,10 @@
         <v>820</v>
       </c>
       <c r="B406" t="s">
-        <v>79</v>
+        <v>145</v>
       </c>
       <c r="C406">
-        <v>0.5416980967921755</v>
+        <v>0.4426453668142301</v>
       </c>
       <c r="D406" t="s">
         <v>7</v>
@@ -11245,7 +11245,7 @@
         <v>6</v>
       </c>
       <c r="C407">
-        <v>0.3932251129578064</v>
+        <v>0.4003194386949274</v>
       </c>
       <c r="D407" t="s">
         <v>7</v>
@@ -11262,7 +11262,7 @@
         <v>6</v>
       </c>
       <c r="C408">
-        <v>0.4424052106040023</v>
+        <v>0.4720842580342541</v>
       </c>
       <c r="D408" t="s">
         <v>7</v>
@@ -11279,7 +11279,7 @@
         <v>6</v>
       </c>
       <c r="C409">
-        <v>0.4542310031991851</v>
+        <v>0.4901439022654028</v>
       </c>
       <c r="D409" t="s">
         <v>7</v>
@@ -11293,10 +11293,10 @@
         <v>828</v>
       </c>
       <c r="B410" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C410">
-        <v>0.2790983578207493</v>
+        <v>0.291621864859898</v>
       </c>
       <c r="D410" t="s">
         <v>7</v>
@@ -11313,7 +11313,7 @@
         <v>6</v>
       </c>
       <c r="C411">
-        <v>0.3192450134463625</v>
+        <v>0.3294956562050057</v>
       </c>
       <c r="D411" t="s">
         <v>7</v>
@@ -11330,7 +11330,7 @@
         <v>6</v>
       </c>
       <c r="C412">
-        <v>0.422680526668655</v>
+        <v>0.4351081568229256</v>
       </c>
       <c r="D412" t="s">
         <v>7</v>
@@ -11347,7 +11347,7 @@
         <v>6</v>
       </c>
       <c r="C413">
-        <v>0.258230034666867</v>
+        <v>0.2673210815794937</v>
       </c>
       <c r="D413" t="s">
         <v>7</v>
@@ -11361,10 +11361,10 @@
         <v>836</v>
       </c>
       <c r="B414" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C414">
-        <v>0.3009033100177761</v>
+        <v>0.3138955462049966</v>
       </c>
       <c r="D414" t="s">
         <v>7</v>
@@ -11378,10 +11378,10 @@
         <v>838</v>
       </c>
       <c r="B415" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C415">
-        <v>0.3619303870260741</v>
+        <v>0.3605865147753164</v>
       </c>
       <c r="D415" t="s">
         <v>7</v>
@@ -11395,10 +11395,10 @@
         <v>840</v>
       </c>
       <c r="B416" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C416">
-        <v>0.5063094728120429</v>
+        <v>0.4332518953556057</v>
       </c>
       <c r="D416" t="s">
         <v>7</v>
@@ -11415,7 +11415,7 @@
         <v>6</v>
       </c>
       <c r="C417">
-        <v>0.2567839408648351</v>
+        <v>0.2803713428289135</v>
       </c>
       <c r="D417" t="s">
         <v>7</v>
@@ -11429,10 +11429,10 @@
         <v>844</v>
       </c>
       <c r="B418" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C418">
-        <v>0.3058852199465608</v>
+        <v>0.3067393179949134</v>
       </c>
       <c r="D418" t="s">
         <v>7</v>
@@ -11446,10 +11446,10 @@
         <v>846</v>
       </c>
       <c r="B419" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C419">
-        <v>0.4133713594007117</v>
+        <v>0.3959844363271829</v>
       </c>
       <c r="D419" t="s">
         <v>7</v>
@@ -11466,7 +11466,7 @@
         <v>44</v>
       </c>
       <c r="C420">
-        <v>0.4524716067654568</v>
+        <v>0.447330818536044</v>
       </c>
       <c r="D420" t="s">
         <v>7</v>
@@ -11483,7 +11483,7 @@
         <v>44</v>
       </c>
       <c r="C421">
-        <v>0.4404432447642156</v>
+        <v>0.4538082877403036</v>
       </c>
       <c r="D421" t="s">
         <v>7</v>
@@ -11500,7 +11500,7 @@
         <v>6</v>
       </c>
       <c r="C422">
-        <v>0.3665066022372021</v>
+        <v>0.3748418256784402</v>
       </c>
       <c r="D422" t="s">
         <v>7</v>
@@ -11517,7 +11517,7 @@
         <v>44</v>
       </c>
       <c r="C423">
-        <v>0.4122987824947921</v>
+        <v>0.4318944883799044</v>
       </c>
       <c r="D423" t="s">
         <v>7</v>
@@ -11531,10 +11531,10 @@
         <v>856</v>
       </c>
       <c r="B424" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C424">
-        <v>0.3146575291347722</v>
+        <v>0.3349120276540628</v>
       </c>
       <c r="D424" t="s">
         <v>7</v>
@@ -11551,7 +11551,7 @@
         <v>6</v>
       </c>
       <c r="C425">
-        <v>0.3560042436738198</v>
+        <v>0.3742515358759995</v>
       </c>
       <c r="D425" t="s">
         <v>7</v>
@@ -11565,10 +11565,10 @@
         <v>860</v>
       </c>
       <c r="B426" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C426">
-        <v>0.3766156647437505</v>
+        <v>0.3570308188952453</v>
       </c>
       <c r="D426" t="s">
         <v>7</v>
@@ -11585,7 +11585,7 @@
         <v>6</v>
       </c>
       <c r="C427">
-        <v>0.2759649959292526</v>
+        <v>0.2886549423145098</v>
       </c>
       <c r="D427" t="s">
         <v>7</v>
@@ -11602,7 +11602,7 @@
         <v>6</v>
       </c>
       <c r="C428">
-        <v>0.2711563901759526</v>
+        <v>0.2791660997950676</v>
       </c>
       <c r="D428" t="s">
         <v>7</v>
@@ -11616,10 +11616,10 @@
         <v>866</v>
       </c>
       <c r="B429" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C429">
-        <v>0.3477066871250877</v>
+        <v>0.3479244417855497</v>
       </c>
       <c r="D429" t="s">
         <v>7</v>
@@ -11636,7 +11636,7 @@
         <v>6</v>
       </c>
       <c r="C430">
-        <v>0.3554148903527548</v>
+        <v>0.3716433297355806</v>
       </c>
       <c r="D430" t="s">
         <v>7</v>
@@ -11650,10 +11650,10 @@
         <v>870</v>
       </c>
       <c r="B431" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C431">
-        <v>0.3022742048057931</v>
+        <v>0.2980584775335986</v>
       </c>
       <c r="D431" t="s">
         <v>7</v>
@@ -11667,10 +11667,10 @@
         <v>872</v>
       </c>
       <c r="B432" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C432">
-        <v>0.3505370911227951</v>
+        <v>0.3507934942317557</v>
       </c>
       <c r="D432" t="s">
         <v>7</v>
@@ -11687,7 +11687,7 @@
         <v>6</v>
       </c>
       <c r="C433">
-        <v>0.2776179001344524</v>
+        <v>0.2791596617722182</v>
       </c>
       <c r="D433" t="s">
         <v>7</v>
@@ -11701,10 +11701,10 @@
         <v>876</v>
       </c>
       <c r="B434" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C434">
-        <v>0.3681350968957232</v>
+        <v>0.3620775136718439</v>
       </c>
       <c r="D434" t="s">
         <v>7</v>
@@ -11718,10 +11718,10 @@
         <v>878</v>
       </c>
       <c r="B435" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C435">
-        <v>0.3757332899507906</v>
+        <v>0.3880874102587367</v>
       </c>
       <c r="D435" t="s">
         <v>7</v>
@@ -11735,10 +11735,10 @@
         <v>880</v>
       </c>
       <c r="B436" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C436">
-        <v>0.3831125452076493</v>
+        <v>0.3552901274643998</v>
       </c>
       <c r="D436" t="s">
         <v>7</v>
@@ -11752,10 +11752,10 @@
         <v>882</v>
       </c>
       <c r="B437" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C437">
-        <v>0.302465437125774</v>
+        <v>0.3163147040792227</v>
       </c>
       <c r="D437" t="s">
         <v>7</v>
@@ -11769,10 +11769,10 @@
         <v>884</v>
       </c>
       <c r="B438" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C438">
-        <v>0.3516669602011376</v>
+        <v>0.3587563341285492</v>
       </c>
       <c r="D438" t="s">
         <v>7</v>
@@ -11789,7 +11789,7 @@
         <v>6</v>
       </c>
       <c r="C439">
-        <v>0.3714763885109734</v>
+        <v>0.3972896727883712</v>
       </c>
       <c r="D439" t="s">
         <v>7</v>
@@ -11803,10 +11803,10 @@
         <v>888</v>
       </c>
       <c r="B440" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C440">
-        <v>0.2951361234837089</v>
+        <v>0.3098597459587893</v>
       </c>
       <c r="D440" t="s">
         <v>7</v>
@@ -11823,7 +11823,7 @@
         <v>6</v>
       </c>
       <c r="C441">
-        <v>0.3112936177655987</v>
+        <v>0.341887936914513</v>
       </c>
       <c r="D441" t="s">
         <v>7</v>
@@ -11840,7 +11840,7 @@
         <v>6</v>
       </c>
       <c r="C442">
-        <v>0.2988182896881045</v>
+        <v>0.3156378680298125</v>
       </c>
       <c r="D442" t="s">
         <v>7</v>
@@ -11854,10 +11854,10 @@
         <v>894</v>
       </c>
       <c r="B443" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C443">
-        <v>0.3062494453903968</v>
+        <v>0.3046258556223034</v>
       </c>
       <c r="D443" t="s">
         <v>7</v>
@@ -11871,10 +11871,10 @@
         <v>896</v>
       </c>
       <c r="B444" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C444">
-        <v>0.3270908830392907</v>
+        <v>0.3383851475886783</v>
       </c>
       <c r="D444" t="s">
         <v>7</v>
@@ -11891,7 +11891,7 @@
         <v>6</v>
       </c>
       <c r="C445">
-        <v>0.3559760366502255</v>
+        <v>0.3738418813937043</v>
       </c>
       <c r="D445" t="s">
         <v>7</v>
@@ -11908,7 +11908,7 @@
         <v>44</v>
       </c>
       <c r="C446">
-        <v>0.3664006381454172</v>
+        <v>0.3442356020405257</v>
       </c>
       <c r="D446" t="s">
         <v>7</v>
@@ -11925,7 +11925,7 @@
         <v>6</v>
       </c>
       <c r="C447">
-        <v>0.2807451881966995</v>
+        <v>0.2794578278247444</v>
       </c>
       <c r="D447" t="s">
         <v>7</v>
@@ -11942,7 +11942,7 @@
         <v>6</v>
       </c>
       <c r="C448">
-        <v>0.3605143953364514</v>
+        <v>0.3826953050286061</v>
       </c>
       <c r="D448" t="s">
         <v>7</v>
@@ -11959,7 +11959,7 @@
         <v>6</v>
       </c>
       <c r="C449">
-        <v>0.4010407789354055</v>
+        <v>0.4149093458369522</v>
       </c>
       <c r="D449" t="s">
         <v>7</v>
@@ -11976,7 +11976,7 @@
         <v>44</v>
       </c>
       <c r="C450">
-        <v>0.3976583710245067</v>
+        <v>0.4136677566652305</v>
       </c>
       <c r="D450" t="s">
         <v>7</v>
@@ -11993,7 +11993,7 @@
         <v>44</v>
       </c>
       <c r="C451">
-        <v>0.3949459448058157</v>
+        <v>0.3894726335765242</v>
       </c>
       <c r="D451" t="s">
         <v>7</v>
@@ -12010,7 +12010,7 @@
         <v>6</v>
       </c>
       <c r="C452">
-        <v>0.3296522588143242</v>
+        <v>0.3459605576029035</v>
       </c>
       <c r="D452" t="s">
         <v>7</v>
@@ -12024,10 +12024,10 @@
         <v>914</v>
       </c>
       <c r="B453" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C453">
-        <v>0.3364263731265571</v>
+        <v>0.3575547628139507</v>
       </c>
       <c r="D453" t="s">
         <v>7</v>
@@ -12041,10 +12041,10 @@
         <v>916</v>
       </c>
       <c r="B454" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C454">
-        <v>0.2712284409837693</v>
+        <v>0.2877432326703628</v>
       </c>
       <c r="D454" t="s">
         <v>7</v>
@@ -12058,10 +12058,10 @@
         <v>918</v>
       </c>
       <c r="B455" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C455">
-        <v>0.3247769369056187</v>
+        <v>0.3514013764125104</v>
       </c>
       <c r="D455" t="s">
         <v>7</v>
@@ -12078,7 +12078,7 @@
         <v>6</v>
       </c>
       <c r="C456">
-        <v>0.3638382506970495</v>
+        <v>0.3879417717042475</v>
       </c>
       <c r="D456" t="s">
         <v>7</v>
@@ -12092,10 +12092,10 @@
         <v>922</v>
       </c>
       <c r="B457" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C457">
-        <v>0.3858887135142025</v>
+        <v>0.3624980622041154</v>
       </c>
       <c r="D457" t="s">
         <v>7</v>
@@ -12112,7 +12112,7 @@
         <v>6</v>
       </c>
       <c r="C458">
-        <v>0.3533328791342177</v>
+        <v>0.3536023349663245</v>
       </c>
       <c r="D458" t="s">
         <v>7</v>
@@ -12129,7 +12129,7 @@
         <v>6</v>
       </c>
       <c r="C459">
-        <v>0.3794987996991459</v>
+        <v>0.4007336565953506</v>
       </c>
       <c r="D459" t="s">
         <v>7</v>
@@ -12146,7 +12146,7 @@
         <v>6</v>
       </c>
       <c r="C460">
-        <v>0.3292128459409154</v>
+        <v>0.3545024537920187</v>
       </c>
       <c r="D460" t="s">
         <v>7</v>
@@ -12160,10 +12160,10 @@
         <v>930</v>
       </c>
       <c r="B461" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C461">
-        <v>0.3073710470772348</v>
+        <v>0.3099913501502077</v>
       </c>
       <c r="D461" t="s">
         <v>7</v>
@@ -12180,7 +12180,7 @@
         <v>6</v>
       </c>
       <c r="C462">
-        <v>0.3345165652421457</v>
+        <v>0.3384865851067231</v>
       </c>
       <c r="D462" t="s">
         <v>7</v>
@@ -12197,7 +12197,7 @@
         <v>10</v>
       </c>
       <c r="C463">
-        <v>0.2850815106846945</v>
+        <v>0.3015419834462581</v>
       </c>
       <c r="D463" t="s">
         <v>7</v>
@@ -12214,7 +12214,7 @@
         <v>6</v>
       </c>
       <c r="C464">
-        <v>0.4188817037512355</v>
+        <v>0.4246555222786241</v>
       </c>
       <c r="D464" t="s">
         <v>7</v>
@@ -12231,7 +12231,7 @@
         <v>44</v>
       </c>
       <c r="C465">
-        <v>0.3694609199986665</v>
+        <v>0.3529578053281249</v>
       </c>
       <c r="D465" t="s">
         <v>7</v>
@@ -12248,7 +12248,7 @@
         <v>6</v>
       </c>
       <c r="C466">
-        <v>0.5242685523091681</v>
+        <v>0.542544008563014</v>
       </c>
       <c r="D466" t="s">
         <v>7</v>
@@ -12265,7 +12265,7 @@
         <v>6</v>
       </c>
       <c r="C467">
-        <v>0.4734774178726135</v>
+        <v>0.4942027841325637</v>
       </c>
       <c r="D467" t="s">
         <v>7</v>
@@ -12282,7 +12282,7 @@
         <v>6</v>
       </c>
       <c r="C468">
-        <v>0.3801905906000626</v>
+        <v>0.3950346489054566</v>
       </c>
       <c r="D468" t="s">
         <v>7</v>
@@ -12296,10 +12296,10 @@
         <v>946</v>
       </c>
       <c r="B469" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C469">
-        <v>0.2973104049059154</v>
+        <v>0.2983889476254387</v>
       </c>
       <c r="D469" t="s">
         <v>7</v>
@@ -12313,10 +12313,10 @@
         <v>948</v>
       </c>
       <c r="B470" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C470">
-        <v>0.298809584383551</v>
+        <v>0.3037758010873418</v>
       </c>
       <c r="D470" t="s">
         <v>7</v>
@@ -12333,7 +12333,7 @@
         <v>44</v>
       </c>
       <c r="C471">
-        <v>0.3260353372043116</v>
+        <v>0.3228972402686213</v>
       </c>
       <c r="D471" t="s">
         <v>7</v>
@@ -12347,10 +12347,10 @@
         <v>952</v>
       </c>
       <c r="B472" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C472">
-        <v>0.2977871160427352</v>
+        <v>0.3127220280896493</v>
       </c>
       <c r="D472" t="s">
         <v>7</v>
@@ -12367,7 +12367,7 @@
         <v>44</v>
       </c>
       <c r="C473">
-        <v>0.329778170039945</v>
+        <v>0.3202838469322625</v>
       </c>
       <c r="D473" t="s">
         <v>7</v>
@@ -12381,10 +12381,10 @@
         <v>956</v>
       </c>
       <c r="B474" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C474">
-        <v>0.3597215530982563</v>
+        <v>0.3494433483903207</v>
       </c>
       <c r="D474" t="s">
         <v>7</v>
@@ -12401,7 +12401,7 @@
         <v>6</v>
       </c>
       <c r="C475">
-        <v>0.3398763520268112</v>
+        <v>0.3434517949521806</v>
       </c>
       <c r="D475" t="s">
         <v>7</v>
@@ -12418,7 +12418,7 @@
         <v>6</v>
       </c>
       <c r="C476">
-        <v>0.3116494411541115</v>
+        <v>0.337206297584071</v>
       </c>
       <c r="D476" t="s">
         <v>7</v>
@@ -12432,10 +12432,10 @@
         <v>962</v>
       </c>
       <c r="B477" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C477">
-        <v>0.3090026825727349</v>
+        <v>0.3270215241099507</v>
       </c>
       <c r="D477" t="s">
         <v>7</v>
@@ -12452,7 +12452,7 @@
         <v>6</v>
       </c>
       <c r="C478">
-        <v>0.4080606813631315</v>
+        <v>0.405071732243402</v>
       </c>
       <c r="D478" t="s">
         <v>7</v>
@@ -12469,7 +12469,7 @@
         <v>44</v>
       </c>
       <c r="C479">
-        <v>0.3945755275291037</v>
+        <v>0.4109620591806651</v>
       </c>
       <c r="D479" t="s">
         <v>7</v>
@@ -12486,7 +12486,7 @@
         <v>6</v>
       </c>
       <c r="C480">
-        <v>0.4553207431636923</v>
+        <v>0.4808227091051544</v>
       </c>
       <c r="D480" t="s">
         <v>7</v>
@@ -12503,7 +12503,7 @@
         <v>44</v>
       </c>
       <c r="C481">
-        <v>0.3727767211496779</v>
+        <v>0.3686951874359896</v>
       </c>
       <c r="D481" t="s">
         <v>7</v>
@@ -12517,10 +12517,10 @@
         <v>972</v>
       </c>
       <c r="B482" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C482">
-        <v>0.2662843770559931</v>
+        <v>0.2709165948126885</v>
       </c>
       <c r="D482" t="s">
         <v>7</v>
@@ -12534,10 +12534,10 @@
         <v>974</v>
       </c>
       <c r="B483" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C483">
-        <v>0.2841855467470946</v>
+        <v>0.2993317919729756</v>
       </c>
       <c r="D483" t="s">
         <v>7</v>
@@ -12554,7 +12554,7 @@
         <v>44</v>
       </c>
       <c r="C484">
-        <v>0.3613090399168942</v>
+        <v>0.3676077360374654</v>
       </c>
       <c r="D484" t="s">
         <v>7</v>
@@ -12568,10 +12568,10 @@
         <v>978</v>
       </c>
       <c r="B485" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C485">
-        <v>0.3715838513821805</v>
+        <v>0.3683273013909316</v>
       </c>
       <c r="D485" t="s">
         <v>7</v>
@@ -12585,10 +12585,10 @@
         <v>980</v>
       </c>
       <c r="B486" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C486">
-        <v>0.4425234522183656</v>
+        <v>0.4035427152113107</v>
       </c>
       <c r="D486" t="s">
         <v>7</v>
@@ -12605,7 +12605,7 @@
         <v>44</v>
       </c>
       <c r="C487">
-        <v>0.4265372960827504</v>
+        <v>0.4379266744042156</v>
       </c>
       <c r="D487" t="s">
         <v>7</v>
@@ -12619,10 +12619,10 @@
         <v>984</v>
       </c>
       <c r="B488" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C488">
-        <v>0.2750918140181081</v>
+        <v>0.2826432057992881</v>
       </c>
       <c r="D488" t="s">
         <v>7</v>
@@ -12639,7 +12639,7 @@
         <v>6</v>
       </c>
       <c r="C489">
-        <v>0.5095122301415167</v>
+        <v>0.5075651937315832</v>
       </c>
       <c r="D489" t="s">
         <v>7</v>
@@ -12653,10 +12653,10 @@
         <v>988</v>
       </c>
       <c r="B490" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C490">
-        <v>0.3256047817306831</v>
+        <v>0.3338428305686082</v>
       </c>
       <c r="D490" t="s">
         <v>7</v>
@@ -12673,7 +12673,7 @@
         <v>6</v>
       </c>
       <c r="C491">
-        <v>0.2905798766685286</v>
+        <v>0.2997076834470001</v>
       </c>
       <c r="D491" t="s">
         <v>7</v>
@@ -12690,7 +12690,7 @@
         <v>6</v>
       </c>
       <c r="C492">
-        <v>0.5177817250278671</v>
+        <v>0.4957566264239316</v>
       </c>
       <c r="D492" t="s">
         <v>7</v>
@@ -12707,7 +12707,7 @@
         <v>6</v>
       </c>
       <c r="C493">
-        <v>0.3003064761658628</v>
+        <v>0.305747439749195</v>
       </c>
       <c r="D493" t="s">
         <v>7</v>
@@ -12721,10 +12721,10 @@
         <v>996</v>
       </c>
       <c r="B494" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="C494">
-        <v>0.2953646868102617</v>
+        <v>0.3010034441280779</v>
       </c>
       <c r="D494" t="s">
         <v>7</v>
@@ -12741,7 +12741,7 @@
         <v>44</v>
       </c>
       <c r="C495">
-        <v>0.5183411412022323</v>
+        <v>0.5030255975690348</v>
       </c>
       <c r="D495" t="s">
         <v>7</v>
@@ -12758,7 +12758,7 @@
         <v>6</v>
       </c>
       <c r="C496">
-        <v>0.4852176310066227</v>
+        <v>0.5044357580421969</v>
       </c>
       <c r="D496" t="s">
         <v>7</v>
@@ -12772,10 +12772,10 @@
         <v>1002</v>
       </c>
       <c r="B497" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C497">
-        <v>0.357668126086904</v>
+        <v>0.3561471966020757</v>
       </c>
       <c r="D497" t="s">
         <v>7</v>
@@ -12792,7 +12792,7 @@
         <v>6</v>
       </c>
       <c r="C498">
-        <v>0.6890456821002725</v>
+        <v>0.6641151591104736</v>
       </c>
       <c r="D498" t="s">
         <v>7</v>
@@ -12806,10 +12806,10 @@
         <v>1006</v>
       </c>
       <c r="B499" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C499">
-        <v>0.3473363146281323</v>
+        <v>0.3420264589923934</v>
       </c>
       <c r="D499" t="s">
         <v>7</v>
@@ -12826,7 +12826,7 @@
         <v>6</v>
       </c>
       <c r="C500">
-        <v>0.4092536484552595</v>
+        <v>0.4456510712762181</v>
       </c>
       <c r="D500" t="s">
         <v>7</v>
@@ -12840,10 +12840,10 @@
         <v>1010</v>
       </c>
       <c r="B501" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C501">
-        <v>0.4559208647188595</v>
+        <v>0.4195982987048805</v>
       </c>
       <c r="D501" t="s">
         <v>7</v>
@@ -12860,7 +12860,7 @@
         <v>6</v>
       </c>
       <c r="C502">
-        <v>0.5859153361517387</v>
+        <v>0.5875752046940469</v>
       </c>
       <c r="D502" t="s">
         <v>7</v>
@@ -12874,10 +12874,10 @@
         <v>1014</v>
       </c>
       <c r="B503" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C503">
-        <v>0.3655756452781949</v>
+        <v>0.3594496959489215</v>
       </c>
       <c r="D503" t="s">
         <v>7</v>
@@ -12891,10 +12891,10 @@
         <v>1016</v>
       </c>
       <c r="B504" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C504">
-        <v>0.3259139402802484</v>
+        <v>0.3277265957844223</v>
       </c>
       <c r="D504" t="s">
         <v>7</v>
@@ -12911,7 +12911,7 @@
         <v>6</v>
       </c>
       <c r="C505">
-        <v>0.4421371198487041</v>
+        <v>0.4580781695857361</v>
       </c>
       <c r="D505" t="s">
         <v>7</v>
@@ -12925,10 +12925,10 @@
         <v>1020</v>
       </c>
       <c r="B506" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C506">
-        <v>0.5415265344275999</v>
+        <v>0.4930719869370004</v>
       </c>
       <c r="D506" t="s">
         <v>7</v>
@@ -12945,7 +12945,7 @@
         <v>6</v>
       </c>
       <c r="C507">
-        <v>0.3271961855419739</v>
+        <v>0.3376352302293694</v>
       </c>
       <c r="D507" t="s">
         <v>7</v>
@@ -12959,10 +12959,10 @@
         <v>1024</v>
       </c>
       <c r="B508" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C508">
-        <v>0.3002024932735842</v>
+        <v>0.3284281027431424</v>
       </c>
       <c r="D508" t="s">
         <v>7</v>
@@ -12976,10 +12976,10 @@
         <v>1026</v>
       </c>
       <c r="B509" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C509">
-        <v>0.4314932619870074</v>
+        <v>0.4772774711861864</v>
       </c>
       <c r="D509" t="s">
         <v>7</v>
@@ -12993,10 +12993,10 @@
         <v>1028</v>
       </c>
       <c r="B510" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C510">
-        <v>0.3427363849589825</v>
+        <v>0.3606271061475856</v>
       </c>
       <c r="D510" t="s">
         <v>7</v>
@@ -13013,7 +13013,7 @@
         <v>44</v>
       </c>
       <c r="C511">
-        <v>0.3535673995779168</v>
+        <v>0.3453696411624043</v>
       </c>
       <c r="D511" t="s">
         <v>7</v>
@@ -13030,7 +13030,7 @@
         <v>6</v>
       </c>
       <c r="C512">
-        <v>0.3002673907898285</v>
+        <v>0.3083007206030108</v>
       </c>
       <c r="D512" t="s">
         <v>7</v>
@@ -13047,7 +13047,7 @@
         <v>6</v>
       </c>
       <c r="C513">
-        <v>0.3413723231438398</v>
+        <v>0.3759547259521832</v>
       </c>
       <c r="D513" t="s">
         <v>7</v>
@@ -13064,7 +13064,7 @@
         <v>44</v>
       </c>
       <c r="C514">
-        <v>0.3993981488048282</v>
+        <v>0.3959987156399142</v>
       </c>
       <c r="D514" t="s">
         <v>7</v>
@@ -13081,7 +13081,7 @@
         <v>6</v>
       </c>
       <c r="C515">
-        <v>0.4946350041080018</v>
+        <v>0.5093243738329343</v>
       </c>
       <c r="D515" t="s">
         <v>7</v>
@@ -13095,10 +13095,10 @@
         <v>1040</v>
       </c>
       <c r="B516" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C516">
-        <v>0.313344543960601</v>
+        <v>0.3130640474108625</v>
       </c>
       <c r="D516" t="s">
         <v>7</v>
@@ -13112,10 +13112,10 @@
         <v>1042</v>
       </c>
       <c r="B517" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C517">
-        <v>0.3494282893047542</v>
+        <v>0.3486601615829156</v>
       </c>
       <c r="D517" t="s">
         <v>7</v>
@@ -13129,10 +13129,10 @@
         <v>1044</v>
       </c>
       <c r="B518" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C518">
-        <v>0.2894352457172066</v>
+        <v>0.3118796817646081</v>
       </c>
       <c r="D518" t="s">
         <v>7</v>
@@ -13149,7 +13149,7 @@
         <v>44</v>
       </c>
       <c r="C519">
-        <v>0.5045656618302092</v>
+        <v>0.5042723888541051</v>
       </c>
       <c r="D519" t="s">
         <v>7</v>
@@ -13163,10 +13163,10 @@
         <v>1048</v>
       </c>
       <c r="B520" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C520">
-        <v>0.3226996103351161</v>
+        <v>0.3311721517529383</v>
       </c>
       <c r="D520" t="s">
         <v>7</v>
@@ -13180,10 +13180,10 @@
         <v>1050</v>
       </c>
       <c r="B521" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C521">
-        <v>0.3092775133576188</v>
+        <v>0.3085715968839398</v>
       </c>
       <c r="D521" t="s">
         <v>7</v>
@@ -13197,10 +13197,10 @@
         <v>1052</v>
       </c>
       <c r="B522" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C522">
-        <v>0.3603891710480687</v>
+        <v>0.3487518278696923</v>
       </c>
       <c r="D522" t="s">
         <v>7</v>
@@ -13217,7 +13217,7 @@
         <v>6</v>
       </c>
       <c r="C523">
-        <v>0.4216905500519827</v>
+        <v>0.4521774738487041</v>
       </c>
       <c r="D523" t="s">
         <v>7</v>
@@ -13234,7 +13234,7 @@
         <v>6</v>
       </c>
       <c r="C524">
-        <v>0.2801995045975289</v>
+        <v>0.3050251115314274</v>
       </c>
       <c r="D524" t="s">
         <v>7</v>
@@ -13251,7 +13251,7 @@
         <v>44</v>
       </c>
       <c r="C525">
-        <v>0.3987948290483855</v>
+        <v>0.3897822889160966</v>
       </c>
       <c r="D525" t="s">
         <v>7</v>
@@ -13268,7 +13268,7 @@
         <v>44</v>
       </c>
       <c r="C526">
-        <v>0.4725154894524636</v>
+        <v>0.4932142715392414</v>
       </c>
       <c r="D526" t="s">
         <v>7</v>
@@ -13282,10 +13282,10 @@
         <v>1062</v>
       </c>
       <c r="B527" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C527">
-        <v>0.3828456881772203</v>
+        <v>0.3864893225464031</v>
       </c>
       <c r="D527" t="s">
         <v>7</v>
@@ -13302,7 +13302,7 @@
         <v>6</v>
       </c>
       <c r="C528">
-        <v>0.4407892123357277</v>
+        <v>0.4576004183460236</v>
       </c>
       <c r="D528" t="s">
         <v>7</v>
@@ -13316,10 +13316,10 @@
         <v>1066</v>
       </c>
       <c r="B529" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C529">
-        <v>0.3099299548219754</v>
+        <v>0.3215609784122469</v>
       </c>
       <c r="D529" t="s">
         <v>7</v>
@@ -13336,7 +13336,7 @@
         <v>44</v>
       </c>
       <c r="C530">
-        <v>0.4855798583865336</v>
+        <v>0.4983623706272305</v>
       </c>
       <c r="D530" t="s">
         <v>7</v>
@@ -13353,7 +13353,7 @@
         <v>44</v>
       </c>
       <c r="C531">
-        <v>0.5237103317289084</v>
+        <v>0.5286307202732964</v>
       </c>
       <c r="D531" t="s">
         <v>7</v>
@@ -13367,10 +13367,10 @@
         <v>1072</v>
       </c>
       <c r="B532" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C532">
-        <v>0.2842505801227574</v>
+        <v>0.2778038804523806</v>
       </c>
       <c r="D532" t="s">
         <v>7</v>
@@ -13384,10 +13384,10 @@
         <v>1074</v>
       </c>
       <c r="B533" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C533">
-        <v>0.4938399360550284</v>
+        <v>0.4838850462707051</v>
       </c>
       <c r="D533" t="s">
         <v>7</v>
@@ -13401,10 +13401,10 @@
         <v>1076</v>
       </c>
       <c r="B534" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C534">
-        <v>0.3363267941904955</v>
+        <v>0.3321921653170519</v>
       </c>
       <c r="D534" t="s">
         <v>7</v>
@@ -13421,7 +13421,7 @@
         <v>6</v>
       </c>
       <c r="C535">
-        <v>0.3025759772614587</v>
+        <v>0.3195099650166262</v>
       </c>
       <c r="D535" t="s">
         <v>7</v>
@@ -13435,10 +13435,10 @@
         <v>1080</v>
       </c>
       <c r="B536" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C536">
-        <v>0.3037834462919964</v>
+        <v>0.3212892829272065</v>
       </c>
       <c r="D536" t="s">
         <v>7</v>
@@ -13455,7 +13455,7 @@
         <v>6</v>
       </c>
       <c r="C537">
-        <v>0.3655065498237841</v>
+        <v>0.3938710264174453</v>
       </c>
       <c r="D537" t="s">
         <v>7</v>
@@ -13469,10 +13469,10 @@
         <v>1084</v>
       </c>
       <c r="B538" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C538">
-        <v>0.2837305469161654</v>
+        <v>0.2909602188089097</v>
       </c>
       <c r="D538" t="s">
         <v>7</v>
@@ -13489,7 +13489,7 @@
         <v>6</v>
       </c>
       <c r="C539">
-        <v>0.2938396228527492</v>
+        <v>0.3052957612300293</v>
       </c>
       <c r="D539" t="s">
         <v>7</v>
@@ -13503,10 +13503,10 @@
         <v>1088</v>
       </c>
       <c r="B540" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C540">
-        <v>0.2650870010674514</v>
+        <v>0.2682805740824088</v>
       </c>
       <c r="D540" t="s">
         <v>7</v>
@@ -13523,7 +13523,7 @@
         <v>6</v>
       </c>
       <c r="C541">
-        <v>0.396539798281041</v>
+        <v>0.4227015532990956</v>
       </c>
       <c r="D541" t="s">
         <v>7</v>
@@ -13540,7 +13540,7 @@
         <v>44</v>
       </c>
       <c r="C542">
-        <v>0.363629798273096</v>
+        <v>0.3727070857923098</v>
       </c>
       <c r="D542" t="s">
         <v>7</v>
@@ -13557,7 +13557,7 @@
         <v>6</v>
       </c>
       <c r="C543">
-        <v>0.3929996676849817</v>
+        <v>0.4245315093262037</v>
       </c>
       <c r="D543" t="s">
         <v>7</v>
@@ -13574,7 +13574,7 @@
         <v>6</v>
       </c>
       <c r="C544">
-        <v>0.3883015089791447</v>
+        <v>0.4078635454308713</v>
       </c>
       <c r="D544" t="s">
         <v>7</v>
@@ -13843,7 +13843,7 @@
         <v>1143</v>
       </c>
       <c r="C563">
-        <v>0.2864704823337463</v>
+        <v>0.2805793477961462</v>
       </c>
       <c r="D563" t="s">
         <v>1144</v>
@@ -13860,7 +13860,7 @@
         <v>1143</v>
       </c>
       <c r="C564">
-        <v>0.3258036828282375</v>
+        <v>0.3226886015185672</v>
       </c>
       <c r="D564" t="s">
         <v>1144</v>
@@ -13877,7 +13877,7 @@
         <v>1143</v>
       </c>
       <c r="C565">
-        <v>0.2802473464546237</v>
+        <v>0.2735351765318364</v>
       </c>
       <c r="D565" t="s">
         <v>1144</v>
@@ -13894,7 +13894,7 @@
         <v>1143</v>
       </c>
       <c r="C566">
-        <v>0.3414880232722243</v>
+        <v>0.3414690873982061</v>
       </c>
       <c r="D566" t="s">
         <v>1144</v>
@@ -13911,7 +13911,7 @@
         <v>1143</v>
       </c>
       <c r="C567">
-        <v>0.38457179624773</v>
+        <v>0.3956732205486582</v>
       </c>
       <c r="D567" t="s">
         <v>1144</v>
@@ -13928,7 +13928,7 @@
         <v>1143</v>
       </c>
       <c r="C568">
-        <v>0.3986569939196357</v>
+        <v>0.4057781108554573</v>
       </c>
       <c r="D568" t="s">
         <v>1144</v>
@@ -13945,7 +13945,7 @@
         <v>1143</v>
       </c>
       <c r="C569">
-        <v>0.2780028687651764</v>
+        <v>0.2699343584469736</v>
       </c>
       <c r="D569" t="s">
         <v>1144</v>
@@ -13962,7 +13962,7 @@
         <v>1143</v>
       </c>
       <c r="C570">
-        <v>0.2979173536637857</v>
+        <v>0.2927710349495408</v>
       </c>
       <c r="D570" t="s">
         <v>1144</v>
@@ -13979,7 +13979,7 @@
         <v>1143</v>
       </c>
       <c r="C571">
-        <v>0.289328318799762</v>
+        <v>0.290648248460051</v>
       </c>
       <c r="D571" t="s">
         <v>1144</v>
@@ -13996,7 +13996,7 @@
         <v>6</v>
       </c>
       <c r="C572">
-        <v>0.2689528970444114</v>
+        <v>0.3022814677171713</v>
       </c>
       <c r="D572" t="s">
         <v>1144</v>
@@ -14013,7 +14013,7 @@
         <v>1143</v>
       </c>
       <c r="C573">
-        <v>0.3310679927158143</v>
+        <v>0.3372318552626489</v>
       </c>
       <c r="D573" t="s">
         <v>1144</v>
@@ -14030,7 +14030,7 @@
         <v>44</v>
       </c>
       <c r="C574">
-        <v>0.3745233055121229</v>
+        <v>0.3775549555757317</v>
       </c>
       <c r="D574" t="s">
         <v>1144</v>
@@ -14047,7 +14047,7 @@
         <v>1143</v>
       </c>
       <c r="C575">
-        <v>0.3609503931535211</v>
+        <v>0.3574920420765598</v>
       </c>
       <c r="D575" t="s">
         <v>1144</v>
@@ -14064,7 +14064,7 @@
         <v>1143</v>
       </c>
       <c r="C576">
-        <v>0.3614134210710114</v>
+        <v>0.3568132423250981</v>
       </c>
       <c r="D576" t="s">
         <v>1144</v>
@@ -14081,7 +14081,7 @@
         <v>6</v>
       </c>
       <c r="C577">
-        <v>0.3547044166050438</v>
+        <v>0.3615887940632187</v>
       </c>
       <c r="D577" t="s">
         <v>1144</v>
@@ -14098,7 +14098,7 @@
         <v>1143</v>
       </c>
       <c r="C578">
-        <v>0.3860022077826153</v>
+        <v>0.4079216583092571</v>
       </c>
       <c r="D578" t="s">
         <v>1144</v>
@@ -14115,7 +14115,7 @@
         <v>1143</v>
       </c>
       <c r="C579">
-        <v>0.348853621382039</v>
+        <v>0.3592432676170801</v>
       </c>
       <c r="D579" t="s">
         <v>1144</v>
@@ -14129,10 +14129,10 @@
         <v>1178</v>
       </c>
       <c r="B580" t="s">
-        <v>17</v>
+        <v>1143</v>
       </c>
       <c r="C580">
-        <v>0.3082028561276396</v>
+        <v>0.2855633197430203</v>
       </c>
       <c r="D580" t="s">
         <v>1144</v>
@@ -14149,7 +14149,7 @@
         <v>1143</v>
       </c>
       <c r="C581">
-        <v>0.4507354408416883</v>
+        <v>0.4590984710226226</v>
       </c>
       <c r="D581" t="s">
         <v>1144</v>
@@ -14166,7 +14166,7 @@
         <v>1143</v>
       </c>
       <c r="C582">
-        <v>0.3111926056353069</v>
+        <v>0.3073904002761048</v>
       </c>
       <c r="D582" t="s">
         <v>1144</v>
@@ -14183,7 +14183,7 @@
         <v>1143</v>
       </c>
       <c r="C583">
-        <v>0.3760716036414755</v>
+        <v>0.3857194928848706</v>
       </c>
       <c r="D583" t="s">
         <v>1144</v>
@@ -14200,7 +14200,7 @@
         <v>1143</v>
       </c>
       <c r="C584">
-        <v>0.3054729845603847</v>
+        <v>0.3072132309375001</v>
       </c>
       <c r="D584" t="s">
         <v>1144</v>
@@ -14217,7 +14217,7 @@
         <v>1143</v>
       </c>
       <c r="C585">
-        <v>0.4213316524519853</v>
+        <v>0.4129209703516483</v>
       </c>
       <c r="D585" t="s">
         <v>1144</v>
@@ -14234,7 +14234,7 @@
         <v>1143</v>
       </c>
       <c r="C586">
-        <v>0.2866332683638242</v>
+        <v>0.2922727161975859</v>
       </c>
       <c r="D586" t="s">
         <v>1144</v>
@@ -14251,7 +14251,7 @@
         <v>6</v>
       </c>
       <c r="C587">
-        <v>0.2806803719891457</v>
+        <v>0.3185620061034763</v>
       </c>
       <c r="D587" t="s">
         <v>1144</v>
@@ -14268,7 +14268,7 @@
         <v>1143</v>
       </c>
       <c r="C588">
-        <v>0.3083120608557081</v>
+        <v>0.3202880134151589</v>
       </c>
       <c r="D588" t="s">
         <v>1144</v>
@@ -14285,7 +14285,7 @@
         <v>44</v>
       </c>
       <c r="C589">
-        <v>0.3832589754029783</v>
+        <v>0.3954747404431621</v>
       </c>
       <c r="D589" t="s">
         <v>1144</v>
@@ -14302,7 +14302,7 @@
         <v>6</v>
       </c>
       <c r="C590">
-        <v>0.3560520258445286</v>
+        <v>0.4218210913926099</v>
       </c>
       <c r="D590" t="s">
         <v>1144</v>
@@ -14319,7 +14319,7 @@
         <v>1143</v>
       </c>
       <c r="C591">
-        <v>0.5146076658102717</v>
+        <v>0.5055260582908665</v>
       </c>
       <c r="D591" t="s">
         <v>1144</v>
@@ -14336,7 +14336,7 @@
         <v>1143</v>
       </c>
       <c r="C592">
-        <v>0.3556858223917162</v>
+        <v>0.365673310209782</v>
       </c>
       <c r="D592" t="s">
         <v>1144</v>
@@ -14353,7 +14353,7 @@
         <v>1143</v>
       </c>
       <c r="C593">
-        <v>0.6490499622100746</v>
+        <v>0.6401762238910994</v>
       </c>
       <c r="D593" t="s">
         <v>1144</v>
@@ -14370,7 +14370,7 @@
         <v>1143</v>
       </c>
       <c r="C594">
-        <v>0.4378732857975119</v>
+        <v>0.4436973462294086</v>
       </c>
       <c r="D594" t="s">
         <v>1144</v>
@@ -14387,7 +14387,7 @@
         <v>6</v>
       </c>
       <c r="C595">
-        <v>0.2942098408724645</v>
+        <v>0.3269430634555045</v>
       </c>
       <c r="D595" t="s">
         <v>1144</v>
@@ -14404,7 +14404,7 @@
         <v>1143</v>
       </c>
       <c r="C596">
-        <v>0.430622158920845</v>
+        <v>0.4327550014237833</v>
       </c>
       <c r="D596" t="s">
         <v>1144</v>
@@ -14421,7 +14421,7 @@
         <v>6</v>
       </c>
       <c r="C597">
-        <v>0.3303272811547263</v>
+        <v>0.3308150620577314</v>
       </c>
       <c r="D597" t="s">
         <v>1144</v>
@@ -14435,10 +14435,10 @@
         <v>1214</v>
       </c>
       <c r="B598" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C598">
-        <v>0.2577889525169242</v>
+        <v>0.2367616074960175</v>
       </c>
       <c r="D598" t="s">
         <v>1144</v>
@@ -14455,7 +14455,7 @@
         <v>1143</v>
       </c>
       <c r="C599">
-        <v>0.2579959382769951</v>
+        <v>0.2526013000338156</v>
       </c>
       <c r="D599" t="s">
         <v>1144</v>
@@ -14472,7 +14472,7 @@
         <v>1143</v>
       </c>
       <c r="C600">
-        <v>0.3016416697033701</v>
+        <v>0.2776339863292266</v>
       </c>
       <c r="D600" t="s">
         <v>1144</v>
@@ -14489,7 +14489,7 @@
         <v>1143</v>
       </c>
       <c r="C601">
-        <v>0.2676406225064724</v>
+        <v>0.2634075432664323</v>
       </c>
       <c r="D601" t="s">
         <v>1144</v>
@@ -14506,7 +14506,7 @@
         <v>1143</v>
       </c>
       <c r="C602">
-        <v>0.3545593487111702</v>
+        <v>0.3577424260993998</v>
       </c>
       <c r="D602" t="s">
         <v>1144</v>
@@ -14523,7 +14523,7 @@
         <v>1143</v>
       </c>
       <c r="C603">
-        <v>0.2835193350593359</v>
+        <v>0.2883954952829639</v>
       </c>
       <c r="D603" t="s">
         <v>1144</v>
@@ -14540,7 +14540,7 @@
         <v>6</v>
       </c>
       <c r="C604">
-        <v>0.3114415183577908</v>
+        <v>0.3367664588901789</v>
       </c>
       <c r="D604" t="s">
         <v>1144</v>
@@ -14557,7 +14557,7 @@
         <v>44</v>
       </c>
       <c r="C605">
-        <v>0.2814751866609839</v>
+        <v>0.2841136840544377</v>
       </c>
       <c r="D605" t="s">
         <v>1144</v>
@@ -14574,7 +14574,7 @@
         <v>6</v>
       </c>
       <c r="C606">
-        <v>0.334552042583307</v>
+        <v>0.334797708980002</v>
       </c>
       <c r="D606" t="s">
         <v>1144</v>
@@ -14588,10 +14588,10 @@
         <v>1232</v>
       </c>
       <c r="B607" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C607">
-        <v>0.3444961238169109</v>
+        <v>0.3062364447840163</v>
       </c>
       <c r="D607" t="s">
         <v>1144</v>
@@ -14608,7 +14608,7 @@
         <v>6</v>
       </c>
       <c r="C608">
-        <v>0.3026401795431786</v>
+        <v>0.316493316642598</v>
       </c>
       <c r="D608" t="s">
         <v>1144</v>
@@ -14625,7 +14625,7 @@
         <v>6</v>
       </c>
       <c r="C609">
-        <v>0.3426008937160536</v>
+        <v>0.3312592535947746</v>
       </c>
       <c r="D609" t="s">
         <v>1144</v>
@@ -14642,7 +14642,7 @@
         <v>1143</v>
       </c>
       <c r="C610">
-        <v>0.2742726267087609</v>
+        <v>0.2641594966463437</v>
       </c>
       <c r="D610" t="s">
         <v>1144</v>
@@ -14659,7 +14659,7 @@
         <v>44</v>
       </c>
       <c r="C611">
-        <v>0.5058837969616241</v>
+        <v>0.5372130385996471</v>
       </c>
       <c r="D611" t="s">
         <v>1144</v>
@@ -14676,7 +14676,7 @@
         <v>44</v>
       </c>
       <c r="C612">
-        <v>0.3881136385797994</v>
+        <v>0.3809873455544808</v>
       </c>
       <c r="D612" t="s">
         <v>1144</v>
@@ -14693,7 +14693,7 @@
         <v>1143</v>
       </c>
       <c r="C613">
-        <v>0.3396631312405216</v>
+        <v>0.3320218097910265</v>
       </c>
       <c r="D613" t="s">
         <v>1144</v>
@@ -14710,7 +14710,7 @@
         <v>1143</v>
       </c>
       <c r="C614">
-        <v>0.4226724022552727</v>
+        <v>0.4355269863930907</v>
       </c>
       <c r="D614" t="s">
         <v>1144</v>
@@ -14724,10 +14724,10 @@
         <v>1248</v>
       </c>
       <c r="B615" t="s">
-        <v>17</v>
+        <v>1143</v>
       </c>
       <c r="C615">
-        <v>0.3534305838872275</v>
+        <v>0.337248592140817</v>
       </c>
       <c r="D615" t="s">
         <v>1144</v>
@@ -14744,7 +14744,7 @@
         <v>1143</v>
       </c>
       <c r="C616">
-        <v>0.4004570094405502</v>
+        <v>0.4215982454230516</v>
       </c>
       <c r="D616" t="s">
         <v>1144</v>
@@ -14761,7 +14761,7 @@
         <v>1143</v>
       </c>
       <c r="C617">
-        <v>0.3346711187907207</v>
+        <v>0.3488178018243955</v>
       </c>
       <c r="D617" t="s">
         <v>1144</v>
@@ -14775,10 +14775,10 @@
         <v>1254</v>
       </c>
       <c r="B618" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C618">
-        <v>0.3427179215581034</v>
+        <v>0.33842893991552</v>
       </c>
       <c r="D618" t="s">
         <v>1144</v>
@@ -14795,7 +14795,7 @@
         <v>1143</v>
       </c>
       <c r="C619">
-        <v>0.4080337399457341</v>
+        <v>0.4396673522786895</v>
       </c>
       <c r="D619" t="s">
         <v>1144</v>
@@ -14809,10 +14809,10 @@
         <v>1258</v>
       </c>
       <c r="B620" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C620">
-        <v>0.3176749237790665</v>
+        <v>0.3208740786197954</v>
       </c>
       <c r="D620" t="s">
         <v>1259</v>
@@ -14826,10 +14826,10 @@
         <v>1261</v>
       </c>
       <c r="B621" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C621">
-        <v>0.3898875927790148</v>
+        <v>0.2849908240552963</v>
       </c>
       <c r="D621" t="s">
         <v>1259</v>
@@ -14843,10 +14843,10 @@
         <v>1263</v>
       </c>
       <c r="B622" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C622">
-        <v>0.281484563416065</v>
+        <v>0.2689692625739072</v>
       </c>
       <c r="D622" t="s">
         <v>1259</v>
@@ -14863,7 +14863,7 @@
         <v>1266</v>
       </c>
       <c r="C623">
-        <v>0.2591063611341231</v>
+        <v>0.2506124707651516</v>
       </c>
       <c r="D623" t="s">
         <v>1259</v>
@@ -14877,10 +14877,10 @@
         <v>1268</v>
       </c>
       <c r="B624" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C624">
-        <v>0.2652711631454605</v>
+        <v>0.32873480287471</v>
       </c>
       <c r="D624" t="s">
         <v>1259</v>
@@ -14894,10 +14894,10 @@
         <v>1270</v>
       </c>
       <c r="B625" t="s">
-        <v>1266</v>
+        <v>10</v>
       </c>
       <c r="C625">
-        <v>0.2552321976063709</v>
+        <v>0.2714908099689861</v>
       </c>
       <c r="D625" t="s">
         <v>1259</v>
@@ -14914,7 +14914,7 @@
         <v>10</v>
       </c>
       <c r="C626">
-        <v>0.340685697596409</v>
+        <v>0.2883791463376097</v>
       </c>
       <c r="D626" t="s">
         <v>1259</v>
@@ -14931,7 +14931,7 @@
         <v>1266</v>
       </c>
       <c r="C627">
-        <v>0.340384197342984</v>
+        <v>0.3216437950931499</v>
       </c>
       <c r="D627" t="s">
         <v>1259</v>
@@ -14948,7 +14948,7 @@
         <v>1266</v>
       </c>
       <c r="C628">
-        <v>0.2527012084086105</v>
+        <v>0.2495800351792938</v>
       </c>
       <c r="D628" t="s">
         <v>1259</v>
@@ -14962,10 +14962,10 @@
         <v>1278</v>
       </c>
       <c r="B629" t="s">
-        <v>1266</v>
+        <v>6</v>
       </c>
       <c r="C629">
-        <v>0.254551825902422</v>
+        <v>0.2592465372568677</v>
       </c>
       <c r="D629" t="s">
         <v>1259</v>
@@ -14979,10 +14979,10 @@
         <v>1280</v>
       </c>
       <c r="B630" t="s">
-        <v>79</v>
+        <v>1266</v>
       </c>
       <c r="C630">
-        <v>0.3800981562024544</v>
+        <v>0.3544400377676947</v>
       </c>
       <c r="D630" t="s">
         <v>1259</v>
@@ -14999,7 +14999,7 @@
         <v>1266</v>
       </c>
       <c r="C631">
-        <v>0.3504948428899604</v>
+        <v>0.3410032757419665</v>
       </c>
       <c r="D631" t="s">
         <v>1259</v>
@@ -15016,7 +15016,7 @@
         <v>1266</v>
       </c>
       <c r="C632">
-        <v>0.3820029269959446</v>
+        <v>0.4392612962612498</v>
       </c>
       <c r="D632" t="s">
         <v>1259</v>
@@ -15033,7 +15033,7 @@
         <v>10</v>
       </c>
       <c r="C633">
-        <v>0.2664997068169506</v>
+        <v>0.263016991224886</v>
       </c>
       <c r="D633" t="s">
         <v>1259</v>
@@ -15047,10 +15047,10 @@
         <v>1288</v>
       </c>
       <c r="B634" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C634">
-        <v>0.4352193923397861</v>
+        <v>0.356576973165613</v>
       </c>
       <c r="D634" t="s">
         <v>1259</v>
@@ -15067,7 +15067,7 @@
         <v>1266</v>
       </c>
       <c r="C635">
-        <v>0.4256090970699435</v>
+        <v>0.4975052542390138</v>
       </c>
       <c r="D635" t="s">
         <v>1259</v>
@@ -15084,7 +15084,7 @@
         <v>6</v>
       </c>
       <c r="C636">
-        <v>0.2143974739034276</v>
+        <v>0.3661746535485418</v>
       </c>
       <c r="D636" t="s">
         <v>1259</v>
@@ -15098,10 +15098,10 @@
         <v>1294</v>
       </c>
       <c r="B637" t="s">
-        <v>10</v>
+        <v>1266</v>
       </c>
       <c r="C637">
-        <v>0.3240619832987795</v>
+        <v>0.2859552120957903</v>
       </c>
       <c r="D637" t="s">
         <v>1259</v>
@@ -15118,7 +15118,7 @@
         <v>1266</v>
       </c>
       <c r="C638">
-        <v>0.5155898349987399</v>
+        <v>0.4472031298499361</v>
       </c>
       <c r="D638" t="s">
         <v>1259</v>
@@ -15135,7 +15135,7 @@
         <v>10</v>
       </c>
       <c r="C639">
-        <v>0.3168641342733758</v>
+        <v>0.3728624558060826</v>
       </c>
       <c r="D639" t="s">
         <v>1259</v>
@@ -15149,10 +15149,10 @@
         <v>1300</v>
       </c>
       <c r="B640" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C640">
-        <v>0.3172043456001913</v>
+        <v>0.331998191773518</v>
       </c>
       <c r="D640" t="s">
         <v>1259</v>
@@ -15166,10 +15166,10 @@
         <v>1302</v>
       </c>
       <c r="B641" t="s">
-        <v>10</v>
+        <v>1266</v>
       </c>
       <c r="C641">
-        <v>0.2746078490612653</v>
+        <v>0.2407356937882281</v>
       </c>
       <c r="D641" t="s">
         <v>1259</v>
@@ -15186,7 +15186,7 @@
         <v>1266</v>
       </c>
       <c r="C642">
-        <v>0.3151792714617053</v>
+        <v>0.3250894978954148</v>
       </c>
       <c r="D642" t="s">
         <v>1259</v>
@@ -15200,10 +15200,10 @@
         <v>1306</v>
       </c>
       <c r="B643" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C643">
-        <v>0.34295009322101</v>
+        <v>0.2720783336877807</v>
       </c>
       <c r="D643" t="s">
         <v>1259</v>
@@ -15217,10 +15217,10 @@
         <v>1308</v>
       </c>
       <c r="B644" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C644">
-        <v>0.3013268602348379</v>
+        <v>0.2268079677148513</v>
       </c>
       <c r="D644" t="s">
         <v>1259</v>
@@ -15234,10 +15234,10 @@
         <v>1310</v>
       </c>
       <c r="B645" t="s">
-        <v>1266</v>
+        <v>10</v>
       </c>
       <c r="C645">
-        <v>0.2537664187195656</v>
+        <v>0.2559367048804051</v>
       </c>
       <c r="D645" t="s">
         <v>1259</v>
@@ -15251,10 +15251,10 @@
         <v>1312</v>
       </c>
       <c r="B646" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C646">
-        <v>0.4133748809203024</v>
+        <v>0.302340233593975</v>
       </c>
       <c r="D646" t="s">
         <v>1259</v>
@@ -15268,10 +15268,10 @@
         <v>1314</v>
       </c>
       <c r="B647" t="s">
-        <v>1266</v>
+        <v>6</v>
       </c>
       <c r="C647">
-        <v>0.2736903771873888</v>
+        <v>0.2908053135072795</v>
       </c>
       <c r="D647" t="s">
         <v>1259</v>
@@ -15285,10 +15285,10 @@
         <v>1316</v>
       </c>
       <c r="B648" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C648">
-        <v>0.3345951658160509</v>
+        <v>0.2425098874253842</v>
       </c>
       <c r="D648" t="s">
         <v>1259</v>
@@ -15302,10 +15302,10 @@
         <v>1318</v>
       </c>
       <c r="B649" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C649">
-        <v>0.3586998441438936</v>
+        <v>0.2847068048881836</v>
       </c>
       <c r="D649" t="s">
         <v>1259</v>
@@ -15319,10 +15319,10 @@
         <v>1320</v>
       </c>
       <c r="B650" t="s">
-        <v>1266</v>
+        <v>6</v>
       </c>
       <c r="C650">
-        <v>0.2737113174241471</v>
+        <v>0.2724851214034243</v>
       </c>
       <c r="D650" t="s">
         <v>1259</v>
@@ -15336,10 +15336,10 @@
         <v>1322</v>
       </c>
       <c r="B651" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C651">
-        <v>0.333872735611434</v>
+        <v>0.2623149712659195</v>
       </c>
       <c r="D651" t="s">
         <v>1259</v>
@@ -15368,26 +15368,26 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B2">
-        <v>151</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B3">
-        <v>104</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>79</v>
+        <v>145</v>
       </c>
       <c r="B4">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -15395,7 +15395,7 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>240</v>
+        <v>254</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -15403,15 +15403,15 @@
         <v>44</v>
       </c>
       <c r="B6">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>126</v>
+        <v>226</v>
       </c>
       <c r="B7">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -15419,7 +15419,7 @@
         <v>1266</v>
       </c>
       <c r="B8">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -15427,7 +15427,7 @@
         <v>1143</v>
       </c>
       <c r="B9">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:2">

--- a/frontend/data/uk_election_predictions.xlsx
+++ b/frontend/data/uk_election_predictions.xlsx
@@ -4360,7 +4360,7 @@
         <v>6</v>
       </c>
       <c r="C2">
-        <v>0.3002962226851348</v>
+        <v>0.3060309584275397</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
@@ -4377,7 +4377,7 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>0.3989348122084349</v>
+        <v>0.3957556692270089</v>
       </c>
       <c r="D3" t="s">
         <v>7</v>
@@ -4394,7 +4394,7 @@
         <v>6</v>
       </c>
       <c r="C4">
-        <v>0.3980742653381755</v>
+        <v>0.4030104674074728</v>
       </c>
       <c r="D4" t="s">
         <v>7</v>
@@ -4411,7 +4411,7 @@
         <v>15</v>
       </c>
       <c r="C5">
-        <v>0.3814936246259302</v>
+        <v>0.3838990466812431</v>
       </c>
       <c r="D5" t="s">
         <v>7</v>
@@ -4428,7 +4428,7 @@
         <v>10</v>
       </c>
       <c r="C6">
-        <v>0.3772759839072296</v>
+        <v>0.3752755969253125</v>
       </c>
       <c r="D6" t="s">
         <v>7</v>
@@ -4445,7 +4445,7 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>0.318406540325769</v>
+        <v>0.3231907475654792</v>
       </c>
       <c r="D7" t="s">
         <v>7</v>
@@ -4462,7 +4462,7 @@
         <v>15</v>
       </c>
       <c r="C8">
-        <v>0.3431227614901878</v>
+        <v>0.3455262606011146</v>
       </c>
       <c r="D8" t="s">
         <v>7</v>
@@ -4479,7 +4479,7 @@
         <v>15</v>
       </c>
       <c r="C9">
-        <v>0.3180994384531466</v>
+        <v>0.3204416180128751</v>
       </c>
       <c r="D9" t="s">
         <v>7</v>
@@ -4496,7 +4496,7 @@
         <v>10</v>
       </c>
       <c r="C10">
-        <v>0.3214139942662587</v>
+        <v>0.3178487526243371</v>
       </c>
       <c r="D10" t="s">
         <v>7</v>
@@ -4513,7 +4513,7 @@
         <v>15</v>
       </c>
       <c r="C11">
-        <v>0.2353194530314209</v>
+        <v>0.2372055438901787</v>
       </c>
       <c r="D11" t="s">
         <v>7</v>
@@ -4530,7 +4530,7 @@
         <v>6</v>
       </c>
       <c r="C12">
-        <v>0.3964912353346211</v>
+        <v>0.4011389575056979</v>
       </c>
       <c r="D12" t="s">
         <v>7</v>
@@ -4547,7 +4547,7 @@
         <v>15</v>
       </c>
       <c r="C13">
-        <v>0.3009475130199061</v>
+        <v>0.3031744857568566</v>
       </c>
       <c r="D13" t="s">
         <v>7</v>
@@ -4564,7 +4564,7 @@
         <v>15</v>
       </c>
       <c r="C14">
-        <v>0.3856685315090146</v>
+        <v>0.3880295833579075</v>
       </c>
       <c r="D14" t="s">
         <v>7</v>
@@ -4581,7 +4581,7 @@
         <v>10</v>
       </c>
       <c r="C15">
-        <v>0.3519008435379434</v>
+        <v>0.3486478518205304</v>
       </c>
       <c r="D15" t="s">
         <v>7</v>
@@ -4598,7 +4598,7 @@
         <v>6</v>
       </c>
       <c r="C16">
-        <v>0.3369790465850339</v>
+        <v>0.3417171146966719</v>
       </c>
       <c r="D16" t="s">
         <v>7</v>
@@ -4615,7 +4615,7 @@
         <v>15</v>
       </c>
       <c r="C17">
-        <v>0.2802172007067437</v>
+        <v>0.282513605191444</v>
       </c>
       <c r="D17" t="s">
         <v>7</v>
@@ -4632,7 +4632,7 @@
         <v>10</v>
       </c>
       <c r="C18">
-        <v>0.3095092411044063</v>
+        <v>0.3062923276582313</v>
       </c>
       <c r="D18" t="s">
         <v>7</v>
@@ -4649,7 +4649,7 @@
         <v>44</v>
       </c>
       <c r="C19">
-        <v>0.4343178921057265</v>
+        <v>0.4349264065203161</v>
       </c>
       <c r="D19" t="s">
         <v>7</v>
@@ -4666,7 +4666,7 @@
         <v>6</v>
       </c>
       <c r="C20">
-        <v>0.4483731014269515</v>
+        <v>0.4554178588071641</v>
       </c>
       <c r="D20" t="s">
         <v>7</v>
@@ -4683,7 +4683,7 @@
         <v>10</v>
       </c>
       <c r="C21">
-        <v>0.388804940006443</v>
+        <v>0.3868551572114342</v>
       </c>
       <c r="D21" t="s">
         <v>7</v>
@@ -4700,7 +4700,7 @@
         <v>6</v>
       </c>
       <c r="C22">
-        <v>0.3612691945836911</v>
+        <v>0.3667239870621659</v>
       </c>
       <c r="D22" t="s">
         <v>7</v>
@@ -4717,7 +4717,7 @@
         <v>6</v>
       </c>
       <c r="C23">
-        <v>0.4578224991226191</v>
+        <v>0.4636145169103582</v>
       </c>
       <c r="D23" t="s">
         <v>7</v>
@@ -4734,7 +4734,7 @@
         <v>6</v>
       </c>
       <c r="C24">
-        <v>0.3414169536271225</v>
+        <v>0.3484756503290099</v>
       </c>
       <c r="D24" t="s">
         <v>7</v>
@@ -4751,7 +4751,7 @@
         <v>6</v>
       </c>
       <c r="C25">
-        <v>0.6109098336275681</v>
+        <v>0.6169287386930266</v>
       </c>
       <c r="D25" t="s">
         <v>7</v>
@@ -4768,7 +4768,7 @@
         <v>15</v>
       </c>
       <c r="C26">
-        <v>0.2964336672472846</v>
+        <v>0.2991613937499235</v>
       </c>
       <c r="D26" t="s">
         <v>7</v>
@@ -4782,10 +4782,10 @@
         <v>60</v>
       </c>
       <c r="B27" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C27">
-        <v>0.2783797087325597</v>
+        <v>0.2772926426349963</v>
       </c>
       <c r="D27" t="s">
         <v>7</v>
@@ -4802,7 +4802,7 @@
         <v>6</v>
       </c>
       <c r="C28">
-        <v>0.3196052925396836</v>
+        <v>0.325959105287959</v>
       </c>
       <c r="D28" t="s">
         <v>7</v>
@@ -4819,7 +4819,7 @@
         <v>44</v>
       </c>
       <c r="C29">
-        <v>0.4350980786145996</v>
+        <v>0.4347777777250297</v>
       </c>
       <c r="D29" t="s">
         <v>7</v>
@@ -4836,7 +4836,7 @@
         <v>6</v>
       </c>
       <c r="C30">
-        <v>0.3764963133352794</v>
+        <v>0.3820536567114865</v>
       </c>
       <c r="D30" t="s">
         <v>7</v>
@@ -4853,7 +4853,7 @@
         <v>6</v>
       </c>
       <c r="C31">
-        <v>0.4546350624711464</v>
+        <v>0.4585655804911234</v>
       </c>
       <c r="D31" t="s">
         <v>7</v>
@@ -4870,7 +4870,7 @@
         <v>15</v>
       </c>
       <c r="C32">
-        <v>0.4129129265094403</v>
+        <v>0.4150520994089015</v>
       </c>
       <c r="D32" t="s">
         <v>7</v>
@@ -4887,7 +4887,7 @@
         <v>6</v>
       </c>
       <c r="C33">
-        <v>0.404690972781568</v>
+        <v>0.4087628301333632</v>
       </c>
       <c r="D33" t="s">
         <v>7</v>
@@ -4904,7 +4904,7 @@
         <v>15</v>
       </c>
       <c r="C34">
-        <v>0.3323184531036122</v>
+        <v>0.3343513143965691</v>
       </c>
       <c r="D34" t="s">
         <v>7</v>
@@ -4921,7 +4921,7 @@
         <v>6</v>
       </c>
       <c r="C35">
-        <v>0.4533586195021107</v>
+        <v>0.4581950768969518</v>
       </c>
       <c r="D35" t="s">
         <v>7</v>
@@ -4938,7 +4938,7 @@
         <v>6</v>
       </c>
       <c r="C36">
-        <v>0.2459615220445875</v>
+        <v>0.2520640415434271</v>
       </c>
       <c r="D36" t="s">
         <v>7</v>
@@ -4955,7 +4955,7 @@
         <v>15</v>
       </c>
       <c r="C37">
-        <v>0.322498172682082</v>
+        <v>0.3247833370830005</v>
       </c>
       <c r="D37" t="s">
         <v>7</v>
@@ -4972,7 +4972,7 @@
         <v>6</v>
       </c>
       <c r="C38">
-        <v>0.340201226698975</v>
+        <v>0.3468887734947915</v>
       </c>
       <c r="D38" t="s">
         <v>7</v>
@@ -4989,7 +4989,7 @@
         <v>15</v>
       </c>
       <c r="C39">
-        <v>0.3151173381253176</v>
+        <v>0.3175509996091644</v>
       </c>
       <c r="D39" t="s">
         <v>7</v>
@@ -5006,7 +5006,7 @@
         <v>6</v>
       </c>
       <c r="C40">
-        <v>0.4891317449919983</v>
+        <v>0.4938631157699417</v>
       </c>
       <c r="D40" t="s">
         <v>7</v>
@@ -5023,7 +5023,7 @@
         <v>15</v>
       </c>
       <c r="C41">
-        <v>0.2925719630911905</v>
+        <v>0.2947780220363082</v>
       </c>
       <c r="D41" t="s">
         <v>7</v>
@@ -5040,7 +5040,7 @@
         <v>6</v>
       </c>
       <c r="C42">
-        <v>0.5229940888378336</v>
+        <v>0.5268952148894968</v>
       </c>
       <c r="D42" t="s">
         <v>7</v>
@@ -5057,7 +5057,7 @@
         <v>15</v>
       </c>
       <c r="C43">
-        <v>0.4035177225469865</v>
+        <v>0.4065686124091875</v>
       </c>
       <c r="D43" t="s">
         <v>7</v>
@@ -5074,7 +5074,7 @@
         <v>15</v>
       </c>
       <c r="C44">
-        <v>0.4391638333122718</v>
+        <v>0.4414753387388314</v>
       </c>
       <c r="D44" t="s">
         <v>7</v>
@@ -5091,7 +5091,7 @@
         <v>6</v>
       </c>
       <c r="C45">
-        <v>0.4114668141323106</v>
+        <v>0.416756964843691</v>
       </c>
       <c r="D45" t="s">
         <v>7</v>
@@ -5108,7 +5108,7 @@
         <v>6</v>
       </c>
       <c r="C46">
-        <v>0.4016794669200297</v>
+        <v>0.4070351367661855</v>
       </c>
       <c r="D46" t="s">
         <v>7</v>
@@ -5125,7 +5125,7 @@
         <v>15</v>
       </c>
       <c r="C47">
-        <v>0.2984322803310926</v>
+        <v>0.3008956437630479</v>
       </c>
       <c r="D47" t="s">
         <v>7</v>
@@ -5142,7 +5142,7 @@
         <v>15</v>
       </c>
       <c r="C48">
-        <v>0.4184649805694353</v>
+        <v>0.4207763067518052</v>
       </c>
       <c r="D48" t="s">
         <v>7</v>
@@ -5159,7 +5159,7 @@
         <v>15</v>
       </c>
       <c r="C49">
-        <v>0.3284198078522778</v>
+        <v>0.3306828217545445</v>
       </c>
       <c r="D49" t="s">
         <v>7</v>
@@ -5176,7 +5176,7 @@
         <v>15</v>
       </c>
       <c r="C50">
-        <v>0.3683957327026833</v>
+        <v>0.3707510674288791</v>
       </c>
       <c r="D50" t="s">
         <v>7</v>
@@ -5193,7 +5193,7 @@
         <v>15</v>
       </c>
       <c r="C51">
-        <v>0.3542038261771873</v>
+        <v>0.3567057381332023</v>
       </c>
       <c r="D51" t="s">
         <v>7</v>
@@ -5210,7 +5210,7 @@
         <v>6</v>
       </c>
       <c r="C52">
-        <v>0.5103199961921103</v>
+        <v>0.5150335653613047</v>
       </c>
       <c r="D52" t="s">
         <v>7</v>
@@ -5227,7 +5227,7 @@
         <v>15</v>
       </c>
       <c r="C53">
-        <v>0.450848055858213</v>
+        <v>0.4531665166474279</v>
       </c>
       <c r="D53" t="s">
         <v>7</v>
@@ -5244,7 +5244,7 @@
         <v>6</v>
       </c>
       <c r="C54">
-        <v>0.4099391428166435</v>
+        <v>0.4159676567098612</v>
       </c>
       <c r="D54" t="s">
         <v>7</v>
@@ -5261,7 +5261,7 @@
         <v>10</v>
       </c>
       <c r="C55">
-        <v>0.2805987164695691</v>
+        <v>0.2776998290661505</v>
       </c>
       <c r="D55" t="s">
         <v>7</v>
@@ -5278,7 +5278,7 @@
         <v>10</v>
       </c>
       <c r="C56">
-        <v>0.3743231313460855</v>
+        <v>0.3707699901950717</v>
       </c>
       <c r="D56" t="s">
         <v>7</v>
@@ -5295,7 +5295,7 @@
         <v>6</v>
       </c>
       <c r="C57">
-        <v>0.549497453963136</v>
+        <v>0.5539828770309629</v>
       </c>
       <c r="D57" t="s">
         <v>7</v>
@@ -5312,7 +5312,7 @@
         <v>6</v>
       </c>
       <c r="C58">
-        <v>0.3267277430665724</v>
+        <v>0.3323884840829821</v>
       </c>
       <c r="D58" t="s">
         <v>7</v>
@@ -5329,7 +5329,7 @@
         <v>6</v>
       </c>
       <c r="C59">
-        <v>0.3666813415149887</v>
+        <v>0.3712069502541631</v>
       </c>
       <c r="D59" t="s">
         <v>7</v>
@@ -5346,7 +5346,7 @@
         <v>6</v>
       </c>
       <c r="C60">
-        <v>0.3165721826892021</v>
+        <v>0.3223665613447457</v>
       </c>
       <c r="D60" t="s">
         <v>7</v>
@@ -5363,7 +5363,7 @@
         <v>6</v>
       </c>
       <c r="C61">
-        <v>0.3788749124073311</v>
+        <v>0.38351999584113</v>
       </c>
       <c r="D61" t="s">
         <v>7</v>
@@ -5380,7 +5380,7 @@
         <v>10</v>
       </c>
       <c r="C62">
-        <v>0.3575576311099624</v>
+        <v>0.3555285864604376</v>
       </c>
       <c r="D62" t="s">
         <v>7</v>
@@ -5397,7 +5397,7 @@
         <v>6</v>
       </c>
       <c r="C63">
-        <v>0.3781634780995647</v>
+        <v>0.3835274046881488</v>
       </c>
       <c r="D63" t="s">
         <v>7</v>
@@ -5414,7 +5414,7 @@
         <v>44</v>
       </c>
       <c r="C64">
-        <v>0.2382639085572628</v>
+        <v>0.2375773460100436</v>
       </c>
       <c r="D64" t="s">
         <v>7</v>
@@ -5431,7 +5431,7 @@
         <v>10</v>
       </c>
       <c r="C65">
-        <v>0.3095694828066517</v>
+        <v>0.3057722132204313</v>
       </c>
       <c r="D65" t="s">
         <v>7</v>
@@ -5448,7 +5448,7 @@
         <v>15</v>
       </c>
       <c r="C66">
-        <v>0.3229724193607359</v>
+        <v>0.3253298259184371</v>
       </c>
       <c r="D66" t="s">
         <v>7</v>
@@ -5465,7 +5465,7 @@
         <v>15</v>
       </c>
       <c r="C67">
-        <v>0.3422753340231358</v>
+        <v>0.3448097254675754</v>
       </c>
       <c r="D67" t="s">
         <v>7</v>
@@ -5482,7 +5482,7 @@
         <v>6</v>
       </c>
       <c r="C68">
-        <v>0.3187585501733449</v>
+        <v>0.3249597366443409</v>
       </c>
       <c r="D68" t="s">
         <v>7</v>
@@ -5499,7 +5499,7 @@
         <v>145</v>
       </c>
       <c r="C69">
-        <v>0.5078273401668283</v>
+        <v>0.5044675834685887</v>
       </c>
       <c r="D69" t="s">
         <v>7</v>
@@ -5516,7 +5516,7 @@
         <v>145</v>
       </c>
       <c r="C70">
-        <v>0.4616473895475012</v>
+        <v>0.4581726181570005</v>
       </c>
       <c r="D70" t="s">
         <v>7</v>
@@ -5533,7 +5533,7 @@
         <v>6</v>
       </c>
       <c r="C71">
-        <v>0.4864179164293944</v>
+        <v>0.4932794201000744</v>
       </c>
       <c r="D71" t="s">
         <v>7</v>
@@ -5550,7 +5550,7 @@
         <v>6</v>
       </c>
       <c r="C72">
-        <v>0.3819526433667775</v>
+        <v>0.389010643532808</v>
       </c>
       <c r="D72" t="s">
         <v>7</v>
@@ -5567,7 +5567,7 @@
         <v>6</v>
       </c>
       <c r="C73">
-        <v>0.5164770252214986</v>
+        <v>0.5227529357192899</v>
       </c>
       <c r="D73" t="s">
         <v>7</v>
@@ -5584,7 +5584,7 @@
         <v>6</v>
       </c>
       <c r="C74">
-        <v>0.5032246133194256</v>
+        <v>0.5090842108023957</v>
       </c>
       <c r="D74" t="s">
         <v>7</v>
@@ -5601,7 +5601,7 @@
         <v>10</v>
       </c>
       <c r="C75">
-        <v>0.2993000090958812</v>
+        <v>0.2956894178949458</v>
       </c>
       <c r="D75" t="s">
         <v>7</v>
@@ -5618,7 +5618,7 @@
         <v>10</v>
       </c>
       <c r="C76">
-        <v>0.3400497221985563</v>
+        <v>0.3367479626332665</v>
       </c>
       <c r="D76" t="s">
         <v>7</v>
@@ -5635,7 +5635,7 @@
         <v>10</v>
       </c>
       <c r="C77">
-        <v>0.3265129379870993</v>
+        <v>0.3229656946496388</v>
       </c>
       <c r="D77" t="s">
         <v>7</v>
@@ -5652,7 +5652,7 @@
         <v>10</v>
       </c>
       <c r="C78">
-        <v>0.4349493680507749</v>
+        <v>0.4313887686762239</v>
       </c>
       <c r="D78" t="s">
         <v>7</v>
@@ -5669,7 +5669,7 @@
         <v>15</v>
       </c>
       <c r="C79">
-        <v>0.2679351381437652</v>
+        <v>0.270154237920041</v>
       </c>
       <c r="D79" t="s">
         <v>7</v>
@@ -5686,7 +5686,7 @@
         <v>10</v>
       </c>
       <c r="C80">
-        <v>0.3674058478769018</v>
+        <v>0.3640193417162574</v>
       </c>
       <c r="D80" t="s">
         <v>7</v>
@@ -5703,7 +5703,7 @@
         <v>15</v>
       </c>
       <c r="C81">
-        <v>0.2971075835112787</v>
+        <v>0.29933853630601</v>
       </c>
       <c r="D81" t="s">
         <v>7</v>
@@ -5720,7 +5720,7 @@
         <v>10</v>
       </c>
       <c r="C82">
-        <v>0.4305090506742372</v>
+        <v>0.4269646138289054</v>
       </c>
       <c r="D82" t="s">
         <v>7</v>
@@ -5737,7 +5737,7 @@
         <v>6</v>
       </c>
       <c r="C83">
-        <v>0.4063087628671082</v>
+        <v>0.4117439644091261</v>
       </c>
       <c r="D83" t="s">
         <v>7</v>
@@ -5751,10 +5751,10 @@
         <v>175</v>
       </c>
       <c r="B84" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C84">
-        <v>0.2906061728833929</v>
+        <v>0.2917206404748828</v>
       </c>
       <c r="D84" t="s">
         <v>7</v>
@@ -5771,7 +5771,7 @@
         <v>15</v>
       </c>
       <c r="C85">
-        <v>0.3007345872638664</v>
+        <v>0.3032221404275506</v>
       </c>
       <c r="D85" t="s">
         <v>7</v>
@@ -5788,7 +5788,7 @@
         <v>6</v>
       </c>
       <c r="C86">
-        <v>0.3237343282314755</v>
+        <v>0.3294248686257662</v>
       </c>
       <c r="D86" t="s">
         <v>7</v>
@@ -5805,7 +5805,7 @@
         <v>6</v>
       </c>
       <c r="C87">
-        <v>0.29834314125855</v>
+        <v>0.3031815878656347</v>
       </c>
       <c r="D87" t="s">
         <v>7</v>
@@ -5822,7 +5822,7 @@
         <v>145</v>
       </c>
       <c r="C88">
-        <v>0.2882411988975978</v>
+        <v>0.282396732303714</v>
       </c>
       <c r="D88" t="s">
         <v>7</v>
@@ -5836,10 +5836,10 @@
         <v>185</v>
       </c>
       <c r="B89" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C89">
-        <v>0.2921006793610279</v>
+        <v>0.294104921631926</v>
       </c>
       <c r="D89" t="s">
         <v>7</v>
@@ -5856,7 +5856,7 @@
         <v>10</v>
       </c>
       <c r="C90">
-        <v>0.254588620561127</v>
+        <v>0.2511079021211545</v>
       </c>
       <c r="D90" t="s">
         <v>7</v>
@@ -5873,7 +5873,7 @@
         <v>6</v>
       </c>
       <c r="C91">
-        <v>0.2698122518268143</v>
+        <v>0.2754941604050063</v>
       </c>
       <c r="D91" t="s">
         <v>7</v>
@@ -5890,7 +5890,7 @@
         <v>44</v>
       </c>
       <c r="C92">
-        <v>0.2878086011921501</v>
+        <v>0.2868382116065973</v>
       </c>
       <c r="D92" t="s">
         <v>7</v>
@@ -5907,7 +5907,7 @@
         <v>15</v>
       </c>
       <c r="C93">
-        <v>0.3614313350310794</v>
+        <v>0.3639209521356697</v>
       </c>
       <c r="D93" t="s">
         <v>7</v>
@@ -5924,7 +5924,7 @@
         <v>6</v>
       </c>
       <c r="C94">
-        <v>0.3028125920358366</v>
+        <v>0.3087462667177674</v>
       </c>
       <c r="D94" t="s">
         <v>7</v>
@@ -5941,7 +5941,7 @@
         <v>15</v>
       </c>
       <c r="C95">
-        <v>0.3229139035645419</v>
+        <v>0.3252812573717014</v>
       </c>
       <c r="D95" t="s">
         <v>7</v>
@@ -5958,7 +5958,7 @@
         <v>15</v>
       </c>
       <c r="C96">
-        <v>0.3359856925161489</v>
+        <v>0.3382356908072282</v>
       </c>
       <c r="D96" t="s">
         <v>7</v>
@@ -5975,7 +5975,7 @@
         <v>44</v>
       </c>
       <c r="C97">
-        <v>0.3313369896101837</v>
+        <v>0.3305678687056897</v>
       </c>
       <c r="D97" t="s">
         <v>7</v>
@@ -5992,7 +5992,7 @@
         <v>44</v>
       </c>
       <c r="C98">
-        <v>0.3278473180106534</v>
+        <v>0.3276376859957902</v>
       </c>
       <c r="D98" t="s">
         <v>7</v>
@@ -6009,7 +6009,7 @@
         <v>6</v>
       </c>
       <c r="C99">
-        <v>0.4479166310528179</v>
+        <v>0.4541313481577624</v>
       </c>
       <c r="D99" t="s">
         <v>7</v>
@@ -6026,7 +6026,7 @@
         <v>44</v>
       </c>
       <c r="C100">
-        <v>0.3951710061802141</v>
+        <v>0.395449429937289</v>
       </c>
       <c r="D100" t="s">
         <v>7</v>
@@ -6043,7 +6043,7 @@
         <v>44</v>
       </c>
       <c r="C101">
-        <v>0.3830851469969022</v>
+        <v>0.3828025310366773</v>
       </c>
       <c r="D101" t="s">
         <v>7</v>
@@ -6060,7 +6060,7 @@
         <v>6</v>
       </c>
       <c r="C102">
-        <v>0.4773530103256327</v>
+        <v>0.482969791571925</v>
       </c>
       <c r="D102" t="s">
         <v>7</v>
@@ -6077,7 +6077,7 @@
         <v>6</v>
       </c>
       <c r="C103">
-        <v>0.3586449919421741</v>
+        <v>0.3631762227304923</v>
       </c>
       <c r="D103" t="s">
         <v>7</v>
@@ -6094,7 +6094,7 @@
         <v>15</v>
       </c>
       <c r="C104">
-        <v>0.3820716306341245</v>
+        <v>0.3845834002554279</v>
       </c>
       <c r="D104" t="s">
         <v>7</v>
@@ -6111,7 +6111,7 @@
         <v>44</v>
       </c>
       <c r="C105">
-        <v>0.3253083367409038</v>
+        <v>0.3245703724110675</v>
       </c>
       <c r="D105" t="s">
         <v>7</v>
@@ -6128,7 +6128,7 @@
         <v>10</v>
       </c>
       <c r="C106">
-        <v>0.3887183210787193</v>
+        <v>0.3860873413174603</v>
       </c>
       <c r="D106" t="s">
         <v>7</v>
@@ -6145,7 +6145,7 @@
         <v>44</v>
       </c>
       <c r="C107">
-        <v>0.3177137331713519</v>
+        <v>0.3174397436809532</v>
       </c>
       <c r="D107" t="s">
         <v>7</v>
@@ -6162,7 +6162,7 @@
         <v>6</v>
       </c>
       <c r="C108">
-        <v>0.3974702534980666</v>
+        <v>0.402746885651706</v>
       </c>
       <c r="D108" t="s">
         <v>7</v>
@@ -6196,7 +6196,7 @@
         <v>15</v>
       </c>
       <c r="C110">
-        <v>0.2985187471312225</v>
+        <v>0.3008681905351897</v>
       </c>
       <c r="D110" t="s">
         <v>7</v>
@@ -6213,7 +6213,7 @@
         <v>6</v>
       </c>
       <c r="C111">
-        <v>0.4920506420456521</v>
+        <v>0.4972155201343991</v>
       </c>
       <c r="D111" t="s">
         <v>7</v>
@@ -6230,7 +6230,7 @@
         <v>6</v>
       </c>
       <c r="C112">
-        <v>0.39997932654015</v>
+        <v>0.405655010241315</v>
       </c>
       <c r="D112" t="s">
         <v>7</v>
@@ -6247,7 +6247,7 @@
         <v>15</v>
       </c>
       <c r="C113">
-        <v>0.4986369722137559</v>
+        <v>0.5005576013108168</v>
       </c>
       <c r="D113" t="s">
         <v>7</v>
@@ -6264,7 +6264,7 @@
         <v>6</v>
       </c>
       <c r="C114">
-        <v>0.6277789202831435</v>
+        <v>0.6336033546599277</v>
       </c>
       <c r="D114" t="s">
         <v>7</v>
@@ -6278,10 +6278,10 @@
         <v>238</v>
       </c>
       <c r="B115" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C115">
-        <v>0.2917936640563258</v>
+        <v>0.2974879192974573</v>
       </c>
       <c r="D115" t="s">
         <v>7</v>
@@ -6298,7 +6298,7 @@
         <v>6</v>
       </c>
       <c r="C116">
-        <v>0.418192410588658</v>
+        <v>0.423568825437536</v>
       </c>
       <c r="D116" t="s">
         <v>7</v>
@@ -6315,7 +6315,7 @@
         <v>10</v>
       </c>
       <c r="C117">
-        <v>0.300415631379341</v>
+        <v>0.2971856148577491</v>
       </c>
       <c r="D117" t="s">
         <v>7</v>
@@ -6332,7 +6332,7 @@
         <v>10</v>
       </c>
       <c r="C118">
-        <v>0.3565574634589235</v>
+        <v>0.3527694761004676</v>
       </c>
       <c r="D118" t="s">
         <v>7</v>
@@ -6346,10 +6346,10 @@
         <v>246</v>
       </c>
       <c r="B119" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C119">
-        <v>0.3011536142885618</v>
+        <v>0.3039966159201843</v>
       </c>
       <c r="D119" t="s">
         <v>7</v>
@@ -6366,7 +6366,7 @@
         <v>10</v>
       </c>
       <c r="C120">
-        <v>0.3733885376468294</v>
+        <v>0.3697162949817061</v>
       </c>
       <c r="D120" t="s">
         <v>7</v>
@@ -6383,7 +6383,7 @@
         <v>226</v>
       </c>
       <c r="C121">
-        <v>0.3979065107076647</v>
+        <v>0.399880578695231</v>
       </c>
       <c r="D121" t="s">
         <v>7</v>
@@ -6400,7 +6400,7 @@
         <v>15</v>
       </c>
       <c r="C122">
-        <v>0.3003930689963263</v>
+        <v>0.3027050333461117</v>
       </c>
       <c r="D122" t="s">
         <v>7</v>
@@ -6417,7 +6417,7 @@
         <v>15</v>
       </c>
       <c r="C123">
-        <v>0.2802168186595491</v>
+        <v>0.2824930083861395</v>
       </c>
       <c r="D123" t="s">
         <v>7</v>
@@ -6434,7 +6434,7 @@
         <v>15</v>
       </c>
       <c r="C124">
-        <v>0.4045558547319171</v>
+        <v>0.4071060299989792</v>
       </c>
       <c r="D124" t="s">
         <v>7</v>
@@ -6448,10 +6448,10 @@
         <v>258</v>
       </c>
       <c r="B125" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C125">
-        <v>0.2845308528777176</v>
+        <v>0.2844688904006356</v>
       </c>
       <c r="D125" t="s">
         <v>7</v>
@@ -6468,7 +6468,7 @@
         <v>10</v>
       </c>
       <c r="C126">
-        <v>0.342726595330417</v>
+        <v>0.3401837502560929</v>
       </c>
       <c r="D126" t="s">
         <v>7</v>
@@ -6485,7 +6485,7 @@
         <v>6</v>
       </c>
       <c r="C127">
-        <v>0.4930329258209397</v>
+        <v>0.4988200563513577</v>
       </c>
       <c r="D127" t="s">
         <v>7</v>
@@ -6502,7 +6502,7 @@
         <v>15</v>
       </c>
       <c r="C128">
-        <v>0.4285953891799711</v>
+        <v>0.4306230764915597</v>
       </c>
       <c r="D128" t="s">
         <v>7</v>
@@ -6519,7 +6519,7 @@
         <v>15</v>
       </c>
       <c r="C129">
-        <v>0.3032739017712001</v>
+        <v>0.3054608467497341</v>
       </c>
       <c r="D129" t="s">
         <v>7</v>
@@ -6536,7 +6536,7 @@
         <v>15</v>
       </c>
       <c r="C130">
-        <v>0.3803789681409016</v>
+        <v>0.3825930486347683</v>
       </c>
       <c r="D130" t="s">
         <v>7</v>
@@ -6553,7 +6553,7 @@
         <v>10</v>
       </c>
       <c r="C131">
-        <v>0.2923789351386583</v>
+        <v>0.2888172384237931</v>
       </c>
       <c r="D131" t="s">
         <v>7</v>
@@ -6570,7 +6570,7 @@
         <v>6</v>
       </c>
       <c r="C132">
-        <v>0.3825902003395259</v>
+        <v>0.3890378069861455</v>
       </c>
       <c r="D132" t="s">
         <v>7</v>
@@ -6587,7 +6587,7 @@
         <v>15</v>
       </c>
       <c r="C133">
-        <v>0.3318967353138298</v>
+        <v>0.334266920510691</v>
       </c>
       <c r="D133" t="s">
         <v>7</v>
@@ -6604,7 +6604,7 @@
         <v>6</v>
       </c>
       <c r="C134">
-        <v>0.3710089639585467</v>
+        <v>0.3766801802996115</v>
       </c>
       <c r="D134" t="s">
         <v>7</v>
@@ -6621,7 +6621,7 @@
         <v>6</v>
       </c>
       <c r="C135">
-        <v>0.3956344284408497</v>
+        <v>0.4009608455977919</v>
       </c>
       <c r="D135" t="s">
         <v>7</v>
@@ -6638,7 +6638,7 @@
         <v>44</v>
       </c>
       <c r="C136">
-        <v>0.3300583768548642</v>
+        <v>0.3291097762416505</v>
       </c>
       <c r="D136" t="s">
         <v>7</v>
@@ -6655,7 +6655,7 @@
         <v>6</v>
       </c>
       <c r="C137">
-        <v>0.3831631586042276</v>
+        <v>0.3888999312564402</v>
       </c>
       <c r="D137" t="s">
         <v>7</v>
@@ -6672,7 +6672,7 @@
         <v>6</v>
       </c>
       <c r="C138">
-        <v>0.3151561321771282</v>
+        <v>0.3206937686042245</v>
       </c>
       <c r="D138" t="s">
         <v>7</v>
@@ -6689,7 +6689,7 @@
         <v>6</v>
       </c>
       <c r="C139">
-        <v>0.4030833363612665</v>
+        <v>0.4082679517336641</v>
       </c>
       <c r="D139" t="s">
         <v>7</v>
@@ -6706,7 +6706,7 @@
         <v>44</v>
       </c>
       <c r="C140">
-        <v>0.3962241535500782</v>
+        <v>0.3961174753635202</v>
       </c>
       <c r="D140" t="s">
         <v>7</v>
@@ -6723,7 +6723,7 @@
         <v>6</v>
       </c>
       <c r="C141">
-        <v>0.3221745241627366</v>
+        <v>0.3278167103440045</v>
       </c>
       <c r="D141" t="s">
         <v>7</v>
@@ -6740,7 +6740,7 @@
         <v>10</v>
       </c>
       <c r="C142">
-        <v>0.3922322476550797</v>
+        <v>0.3893300734409071</v>
       </c>
       <c r="D142" t="s">
         <v>7</v>
@@ -6757,7 +6757,7 @@
         <v>6</v>
       </c>
       <c r="C143">
-        <v>0.3587754753702972</v>
+        <v>0.3646819150123399</v>
       </c>
       <c r="D143" t="s">
         <v>7</v>
@@ -6774,7 +6774,7 @@
         <v>6</v>
       </c>
       <c r="C144">
-        <v>0.6037434288266073</v>
+        <v>0.6098237967893969</v>
       </c>
       <c r="D144" t="s">
         <v>7</v>
@@ -6791,7 +6791,7 @@
         <v>6</v>
       </c>
       <c r="C145">
-        <v>0.2920174908574525</v>
+        <v>0.2978221665932609</v>
       </c>
       <c r="D145" t="s">
         <v>7</v>
@@ -6808,7 +6808,7 @@
         <v>6</v>
       </c>
       <c r="C146">
-        <v>0.4092681654141022</v>
+        <v>0.4142142555885948</v>
       </c>
       <c r="D146" t="s">
         <v>7</v>
@@ -6825,7 +6825,7 @@
         <v>6</v>
       </c>
       <c r="C147">
-        <v>0.4569896275696877</v>
+        <v>0.4623674361292716</v>
       </c>
       <c r="D147" t="s">
         <v>7</v>
@@ -6842,7 +6842,7 @@
         <v>6</v>
       </c>
       <c r="C148">
-        <v>0.2993671482301161</v>
+        <v>0.305624885873213</v>
       </c>
       <c r="D148" t="s">
         <v>7</v>
@@ -6859,7 +6859,7 @@
         <v>10</v>
       </c>
       <c r="C149">
-        <v>0.3897167386417176</v>
+        <v>0.3874278895491353</v>
       </c>
       <c r="D149" t="s">
         <v>7</v>
@@ -6876,7 +6876,7 @@
         <v>6</v>
       </c>
       <c r="C150">
-        <v>0.3587988759724908</v>
+        <v>0.3636534847960338</v>
       </c>
       <c r="D150" t="s">
         <v>7</v>
@@ -6893,7 +6893,7 @@
         <v>10</v>
       </c>
       <c r="C151">
-        <v>0.2656390058748325</v>
+        <v>0.2624286390941708</v>
       </c>
       <c r="D151" t="s">
         <v>7</v>
@@ -6910,7 +6910,7 @@
         <v>6</v>
       </c>
       <c r="C152">
-        <v>0.669101392745868</v>
+        <v>0.6746825626293217</v>
       </c>
       <c r="D152" t="s">
         <v>7</v>
@@ -6927,7 +6927,7 @@
         <v>10</v>
       </c>
       <c r="C153">
-        <v>0.3302663083196633</v>
+        <v>0.3276255260762391</v>
       </c>
       <c r="D153" t="s">
         <v>7</v>
@@ -6944,7 +6944,7 @@
         <v>44</v>
       </c>
       <c r="C154">
-        <v>0.3260404161258039</v>
+        <v>0.325430706481897</v>
       </c>
       <c r="D154" t="s">
         <v>7</v>
@@ -6961,7 +6961,7 @@
         <v>6</v>
       </c>
       <c r="C155">
-        <v>0.3007304444506452</v>
+        <v>0.3062276111644893</v>
       </c>
       <c r="D155" t="s">
         <v>7</v>
@@ -6978,7 +6978,7 @@
         <v>10</v>
       </c>
       <c r="C156">
-        <v>0.3392578219412783</v>
+        <v>0.3360404049357503</v>
       </c>
       <c r="D156" t="s">
         <v>7</v>
@@ -6995,7 +6995,7 @@
         <v>6</v>
       </c>
       <c r="C157">
-        <v>0.3902641004488228</v>
+        <v>0.3961316452093933</v>
       </c>
       <c r="D157" t="s">
         <v>7</v>
@@ -7012,7 +7012,7 @@
         <v>44</v>
       </c>
       <c r="C158">
-        <v>0.3717849917944823</v>
+        <v>0.3706646084995573</v>
       </c>
       <c r="D158" t="s">
         <v>7</v>
@@ -7029,7 +7029,7 @@
         <v>44</v>
       </c>
       <c r="C159">
-        <v>0.3772329486419598</v>
+        <v>0.3762856813571452</v>
       </c>
       <c r="D159" t="s">
         <v>7</v>
@@ -7046,7 +7046,7 @@
         <v>6</v>
       </c>
       <c r="C160">
-        <v>0.3788918787033055</v>
+        <v>0.384222619614028</v>
       </c>
       <c r="D160" t="s">
         <v>7</v>
@@ -7063,7 +7063,7 @@
         <v>6</v>
       </c>
       <c r="C161">
-        <v>0.4155464552821093</v>
+        <v>0.4212809318090024</v>
       </c>
       <c r="D161" t="s">
         <v>7</v>
@@ -7080,7 +7080,7 @@
         <v>6</v>
       </c>
       <c r="C162">
-        <v>0.4746319607183628</v>
+        <v>0.4791642629521437</v>
       </c>
       <c r="D162" t="s">
         <v>7</v>
@@ -7097,7 +7097,7 @@
         <v>44</v>
       </c>
       <c r="C163">
-        <v>0.437333373353116</v>
+        <v>0.4367674395103602</v>
       </c>
       <c r="D163" t="s">
         <v>7</v>
@@ -7114,7 +7114,7 @@
         <v>10</v>
       </c>
       <c r="C164">
-        <v>0.3502424764164641</v>
+        <v>0.3468184636066912</v>
       </c>
       <c r="D164" t="s">
         <v>7</v>
@@ -7131,7 +7131,7 @@
         <v>10</v>
       </c>
       <c r="C165">
-        <v>0.4001705675708802</v>
+        <v>0.3966200508436361</v>
       </c>
       <c r="D165" t="s">
         <v>7</v>
@@ -7148,7 +7148,7 @@
         <v>10</v>
       </c>
       <c r="C166">
-        <v>0.2975380378601613</v>
+        <v>0.2949169890103672</v>
       </c>
       <c r="D166" t="s">
         <v>7</v>
@@ -7165,7 +7165,7 @@
         <v>6</v>
       </c>
       <c r="C167">
-        <v>0.3595491322031325</v>
+        <v>0.3649751222663535</v>
       </c>
       <c r="D167" t="s">
         <v>7</v>
@@ -7182,7 +7182,7 @@
         <v>6</v>
       </c>
       <c r="C168">
-        <v>0.6014939225985809</v>
+        <v>0.6067376617554322</v>
       </c>
       <c r="D168" t="s">
         <v>7</v>
@@ -7199,7 +7199,7 @@
         <v>44</v>
       </c>
       <c r="C169">
-        <v>0.3241449429878185</v>
+        <v>0.3235648468642274</v>
       </c>
       <c r="D169" t="s">
         <v>7</v>
@@ -7216,7 +7216,7 @@
         <v>6</v>
       </c>
       <c r="C170">
-        <v>0.3807567384711282</v>
+        <v>0.3877323272982944</v>
       </c>
       <c r="D170" t="s">
         <v>7</v>
@@ -7233,7 +7233,7 @@
         <v>6</v>
       </c>
       <c r="C171">
-        <v>0.2546623000129131</v>
+        <v>0.2604460445775562</v>
       </c>
       <c r="D171" t="s">
         <v>7</v>
@@ -7247,10 +7247,10 @@
         <v>352</v>
       </c>
       <c r="B172" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C172">
-        <v>0.4070515817297399</v>
+        <v>0.4087579181999978</v>
       </c>
       <c r="D172" t="s">
         <v>7</v>
@@ -7267,7 +7267,7 @@
         <v>44</v>
       </c>
       <c r="C173">
-        <v>0.315260977941936</v>
+        <v>0.3142888641016721</v>
       </c>
       <c r="D173" t="s">
         <v>7</v>
@@ -7284,7 +7284,7 @@
         <v>6</v>
       </c>
       <c r="C174">
-        <v>0.3068921397766141</v>
+        <v>0.312472452168804</v>
       </c>
       <c r="D174" t="s">
         <v>7</v>
@@ -7301,7 +7301,7 @@
         <v>15</v>
       </c>
       <c r="C175">
-        <v>0.2991817610435577</v>
+        <v>0.3013773191346147</v>
       </c>
       <c r="D175" t="s">
         <v>7</v>
@@ -7318,7 +7318,7 @@
         <v>6</v>
       </c>
       <c r="C176">
-        <v>0.4109100496534059</v>
+        <v>0.4173452547585265</v>
       </c>
       <c r="D176" t="s">
         <v>7</v>
@@ -7335,7 +7335,7 @@
         <v>6</v>
       </c>
       <c r="C177">
-        <v>0.5081521526070965</v>
+        <v>0.5133345583611484</v>
       </c>
       <c r="D177" t="s">
         <v>7</v>
@@ -7352,7 +7352,7 @@
         <v>15</v>
       </c>
       <c r="C178">
-        <v>0.3990032422549026</v>
+        <v>0.4012495895474747</v>
       </c>
       <c r="D178" t="s">
         <v>7</v>
@@ -7369,7 +7369,7 @@
         <v>15</v>
       </c>
       <c r="C179">
-        <v>0.3052088167911217</v>
+        <v>0.3074359373757005</v>
       </c>
       <c r="D179" t="s">
         <v>7</v>
@@ -7386,7 +7386,7 @@
         <v>44</v>
       </c>
       <c r="C180">
-        <v>0.3347566358036256</v>
+        <v>0.3338581484546305</v>
       </c>
       <c r="D180" t="s">
         <v>7</v>
@@ -7403,7 +7403,7 @@
         <v>6</v>
       </c>
       <c r="C181">
-        <v>0.3234626293076278</v>
+        <v>0.3289056709976607</v>
       </c>
       <c r="D181" t="s">
         <v>7</v>
@@ -7420,7 +7420,7 @@
         <v>10</v>
       </c>
       <c r="C182">
-        <v>0.2914165832595993</v>
+        <v>0.2876880646307309</v>
       </c>
       <c r="D182" t="s">
         <v>7</v>
@@ -7437,7 +7437,7 @@
         <v>6</v>
       </c>
       <c r="C183">
-        <v>0.310505530470617</v>
+        <v>0.316284639358597</v>
       </c>
       <c r="D183" t="s">
         <v>7</v>
@@ -7454,7 +7454,7 @@
         <v>6</v>
       </c>
       <c r="C184">
-        <v>0.3519089282631613</v>
+        <v>0.3577086741564074</v>
       </c>
       <c r="D184" t="s">
         <v>7</v>
@@ -7471,7 +7471,7 @@
         <v>10</v>
       </c>
       <c r="C185">
-        <v>0.3550755189546099</v>
+        <v>0.3509228344916561</v>
       </c>
       <c r="D185" t="s">
         <v>7</v>
@@ -7488,7 +7488,7 @@
         <v>44</v>
       </c>
       <c r="C186">
-        <v>0.3905876208464197</v>
+        <v>0.3896994534361884</v>
       </c>
       <c r="D186" t="s">
         <v>7</v>
@@ -7505,7 +7505,7 @@
         <v>15</v>
       </c>
       <c r="C187">
-        <v>0.2418665624514982</v>
+        <v>0.2439290897721322</v>
       </c>
       <c r="D187" t="s">
         <v>7</v>
@@ -7522,7 +7522,7 @@
         <v>44</v>
       </c>
       <c r="C188">
-        <v>0.3833658964704665</v>
+        <v>0.3831918509439612</v>
       </c>
       <c r="D188" t="s">
         <v>7</v>
@@ -7539,7 +7539,7 @@
         <v>6</v>
       </c>
       <c r="C189">
-        <v>0.3299834992216931</v>
+        <v>0.3354155950937601</v>
       </c>
       <c r="D189" t="s">
         <v>7</v>
@@ -7556,7 +7556,7 @@
         <v>6</v>
       </c>
       <c r="C190">
-        <v>0.3068010559662859</v>
+        <v>0.312356644899441</v>
       </c>
       <c r="D190" t="s">
         <v>7</v>
@@ -7573,7 +7573,7 @@
         <v>10</v>
       </c>
       <c r="C191">
-        <v>0.3245536067617779</v>
+        <v>0.3208483650316469</v>
       </c>
       <c r="D191" t="s">
         <v>7</v>
@@ -7590,7 +7590,7 @@
         <v>15</v>
       </c>
       <c r="C192">
-        <v>0.3996110396852516</v>
+        <v>0.4021949580633546</v>
       </c>
       <c r="D192" t="s">
         <v>7</v>
@@ -7607,7 +7607,7 @@
         <v>15</v>
       </c>
       <c r="C193">
-        <v>0.4269156485061978</v>
+        <v>0.4288410233187454</v>
       </c>
       <c r="D193" t="s">
         <v>7</v>
@@ -7624,7 +7624,7 @@
         <v>15</v>
       </c>
       <c r="C194">
-        <v>0.3666473929467334</v>
+        <v>0.3690759847520541</v>
       </c>
       <c r="D194" t="s">
         <v>7</v>
@@ -7641,7 +7641,7 @@
         <v>226</v>
       </c>
       <c r="C195">
-        <v>0.4893148158248171</v>
+        <v>0.489447647821338</v>
       </c>
       <c r="D195" t="s">
         <v>7</v>
@@ -7658,7 +7658,7 @@
         <v>6</v>
       </c>
       <c r="C196">
-        <v>0.3740493236206467</v>
+        <v>0.3805493599211855</v>
       </c>
       <c r="D196" t="s">
         <v>7</v>
@@ -7675,7 +7675,7 @@
         <v>10</v>
       </c>
       <c r="C197">
-        <v>0.3043670344438727</v>
+        <v>0.3011530385429229</v>
       </c>
       <c r="D197" t="s">
         <v>7</v>
@@ -7692,7 +7692,7 @@
         <v>6</v>
       </c>
       <c r="C198">
-        <v>0.515960181493341</v>
+        <v>0.52126385275278</v>
       </c>
       <c r="D198" t="s">
         <v>7</v>
@@ -7709,7 +7709,7 @@
         <v>6</v>
       </c>
       <c r="C199">
-        <v>0.5985523022331036</v>
+        <v>0.6043219680366082</v>
       </c>
       <c r="D199" t="s">
         <v>7</v>
@@ -7726,7 +7726,7 @@
         <v>15</v>
       </c>
       <c r="C200">
-        <v>0.3207343094594806</v>
+        <v>0.3231213950474332</v>
       </c>
       <c r="D200" t="s">
         <v>7</v>
@@ -7743,7 +7743,7 @@
         <v>15</v>
       </c>
       <c r="C201">
-        <v>0.3128304518200635</v>
+        <v>0.3150268093184416</v>
       </c>
       <c r="D201" t="s">
         <v>7</v>
@@ -7760,7 +7760,7 @@
         <v>10</v>
       </c>
       <c r="C202">
-        <v>0.344763369465294</v>
+        <v>0.3413596981322196</v>
       </c>
       <c r="D202" t="s">
         <v>7</v>
@@ -7777,7 +7777,7 @@
         <v>6</v>
       </c>
       <c r="C203">
-        <v>0.5389872030786965</v>
+        <v>0.5453988276229358</v>
       </c>
       <c r="D203" t="s">
         <v>7</v>
@@ -7794,7 +7794,7 @@
         <v>6</v>
       </c>
       <c r="C204">
-        <v>0.4780070444482749</v>
+        <v>0.4836161525443174</v>
       </c>
       <c r="D204" t="s">
         <v>7</v>
@@ -7811,7 +7811,7 @@
         <v>10</v>
       </c>
       <c r="C205">
-        <v>0.4291432086975526</v>
+        <v>0.4264429686502</v>
       </c>
       <c r="D205" t="s">
         <v>7</v>
@@ -7828,7 +7828,7 @@
         <v>15</v>
       </c>
       <c r="C206">
-        <v>0.3486419298180785</v>
+        <v>0.3510537013660929</v>
       </c>
       <c r="D206" t="s">
         <v>7</v>
@@ -7845,7 +7845,7 @@
         <v>44</v>
       </c>
       <c r="C207">
-        <v>0.5342254465460607</v>
+        <v>0.5337628968295718</v>
       </c>
       <c r="D207" t="s">
         <v>7</v>
@@ -7862,7 +7862,7 @@
         <v>44</v>
       </c>
       <c r="C208">
-        <v>0.3637723143870945</v>
+        <v>0.3635545537221573</v>
       </c>
       <c r="D208" t="s">
         <v>7</v>
@@ -7879,7 +7879,7 @@
         <v>10</v>
       </c>
       <c r="C209">
-        <v>0.5360691498455966</v>
+        <v>0.5339411286017559</v>
       </c>
       <c r="D209" t="s">
         <v>7</v>
@@ -7896,7 +7896,7 @@
         <v>6</v>
       </c>
       <c r="C210">
-        <v>0.425815792585612</v>
+        <v>0.4322784645104548</v>
       </c>
       <c r="D210" t="s">
         <v>7</v>
@@ -7913,7 +7913,7 @@
         <v>15</v>
       </c>
       <c r="C211">
-        <v>0.469228159972165</v>
+        <v>0.4714194753912632</v>
       </c>
       <c r="D211" t="s">
         <v>7</v>
@@ -7930,7 +7930,7 @@
         <v>15</v>
       </c>
       <c r="C212">
-        <v>0.2865841405127169</v>
+        <v>0.2889622851475213</v>
       </c>
       <c r="D212" t="s">
         <v>7</v>
@@ -7947,7 +7947,7 @@
         <v>15</v>
       </c>
       <c r="C213">
-        <v>0.3085231099321432</v>
+        <v>0.3108304323310289</v>
       </c>
       <c r="D213" t="s">
         <v>7</v>
@@ -7964,7 +7964,7 @@
         <v>15</v>
       </c>
       <c r="C214">
-        <v>0.3754605116908143</v>
+        <v>0.3776539389672126</v>
       </c>
       <c r="D214" t="s">
         <v>7</v>
@@ -7981,7 +7981,7 @@
         <v>10</v>
       </c>
       <c r="C215">
-        <v>0.510461569852468</v>
+        <v>0.5076527304590179</v>
       </c>
       <c r="D215" t="s">
         <v>7</v>
@@ -7998,7 +7998,7 @@
         <v>15</v>
       </c>
       <c r="C216">
-        <v>0.3307735696332388</v>
+        <v>0.3334192410131651</v>
       </c>
       <c r="D216" t="s">
         <v>7</v>
@@ -8015,7 +8015,7 @@
         <v>10</v>
       </c>
       <c r="C217">
-        <v>0.3015613459644056</v>
+        <v>0.2979445272096424</v>
       </c>
       <c r="D217" t="s">
         <v>7</v>
@@ -8029,10 +8029,10 @@
         <v>444</v>
       </c>
       <c r="B218" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C218">
-        <v>0.3452070806974275</v>
+        <v>0.3452761211705379</v>
       </c>
       <c r="D218" t="s">
         <v>7</v>
@@ -8049,7 +8049,7 @@
         <v>44</v>
       </c>
       <c r="C219">
-        <v>0.4756972760410768</v>
+        <v>0.475823819747024</v>
       </c>
       <c r="D219" t="s">
         <v>7</v>
@@ -8066,7 +8066,7 @@
         <v>15</v>
       </c>
       <c r="C220">
-        <v>0.3003480853462688</v>
+        <v>0.3027993908223574</v>
       </c>
       <c r="D220" t="s">
         <v>7</v>
@@ -8083,7 +8083,7 @@
         <v>15</v>
       </c>
       <c r="C221">
-        <v>0.3768374928585538</v>
+        <v>0.379252803068657</v>
       </c>
       <c r="D221" t="s">
         <v>7</v>
@@ -8100,7 +8100,7 @@
         <v>6</v>
       </c>
       <c r="C222">
-        <v>0.3010235109699173</v>
+        <v>0.307365002291224</v>
       </c>
       <c r="D222" t="s">
         <v>7</v>
@@ -8117,7 +8117,7 @@
         <v>10</v>
       </c>
       <c r="C223">
-        <v>0.4765094957880461</v>
+        <v>0.4736986655938657</v>
       </c>
       <c r="D223" t="s">
         <v>7</v>
@@ -8134,7 +8134,7 @@
         <v>10</v>
       </c>
       <c r="C224">
-        <v>0.294228593697671</v>
+        <v>0.2906639522398441</v>
       </c>
       <c r="D224" t="s">
         <v>7</v>
@@ -8151,7 +8151,7 @@
         <v>15</v>
       </c>
       <c r="C225">
-        <v>0.357277166938235</v>
+        <v>0.359792004793746</v>
       </c>
       <c r="D225" t="s">
         <v>7</v>
@@ -8168,7 +8168,7 @@
         <v>6</v>
       </c>
       <c r="C226">
-        <v>0.4948153973721272</v>
+        <v>0.5003732689855046</v>
       </c>
       <c r="D226" t="s">
         <v>7</v>
@@ -8185,7 +8185,7 @@
         <v>10</v>
       </c>
       <c r="C227">
-        <v>0.3139757246352484</v>
+        <v>0.3104592871868451</v>
       </c>
       <c r="D227" t="s">
         <v>7</v>
@@ -8202,7 +8202,7 @@
         <v>6</v>
       </c>
       <c r="C228">
-        <v>0.4900836559484408</v>
+        <v>0.4948909213788268</v>
       </c>
       <c r="D228" t="s">
         <v>7</v>
@@ -8219,7 +8219,7 @@
         <v>6</v>
       </c>
       <c r="C229">
-        <v>0.5629967857282343</v>
+        <v>0.5692849052666057</v>
       </c>
       <c r="D229" t="s">
         <v>7</v>
@@ -8236,7 +8236,7 @@
         <v>44</v>
       </c>
       <c r="C230">
-        <v>0.3414861291283385</v>
+        <v>0.3410400182973143</v>
       </c>
       <c r="D230" t="s">
         <v>7</v>
@@ -8253,7 +8253,7 @@
         <v>6</v>
       </c>
       <c r="C231">
-        <v>0.3169369374019304</v>
+        <v>0.323117789613182</v>
       </c>
       <c r="D231" t="s">
         <v>7</v>
@@ -8270,7 +8270,7 @@
         <v>6</v>
       </c>
       <c r="C232">
-        <v>0.5928719926402432</v>
+        <v>0.5981603193611746</v>
       </c>
       <c r="D232" t="s">
         <v>7</v>
@@ -8287,7 +8287,7 @@
         <v>44</v>
       </c>
       <c r="C233">
-        <v>0.4058206781830309</v>
+        <v>0.4052469218373108</v>
       </c>
       <c r="D233" t="s">
         <v>7</v>
@@ -8304,7 +8304,7 @@
         <v>6</v>
       </c>
       <c r="C234">
-        <v>0.4355186943093656</v>
+        <v>0.44022433354806</v>
       </c>
       <c r="D234" t="s">
         <v>7</v>
@@ -8321,7 +8321,7 @@
         <v>6</v>
       </c>
       <c r="C235">
-        <v>0.5049695909821283</v>
+        <v>0.5107491903191065</v>
       </c>
       <c r="D235" t="s">
         <v>7</v>
@@ -8338,7 +8338,7 @@
         <v>6</v>
       </c>
       <c r="C236">
-        <v>0.2910555541220295</v>
+        <v>0.2971960396306566</v>
       </c>
       <c r="D236" t="s">
         <v>7</v>
@@ -8355,7 +8355,7 @@
         <v>6</v>
       </c>
       <c r="C237">
-        <v>0.3095878954993169</v>
+        <v>0.3152333927614711</v>
       </c>
       <c r="D237" t="s">
         <v>7</v>
@@ -8372,7 +8372,7 @@
         <v>6</v>
       </c>
       <c r="C238">
-        <v>0.3633863693589875</v>
+        <v>0.368008514435983</v>
       </c>
       <c r="D238" t="s">
         <v>7</v>
@@ -8389,7 +8389,7 @@
         <v>6</v>
       </c>
       <c r="C239">
-        <v>0.4470480239178109</v>
+        <v>0.4528708710536115</v>
       </c>
       <c r="D239" t="s">
         <v>7</v>
@@ -8406,7 +8406,7 @@
         <v>226</v>
       </c>
       <c r="C240">
-        <v>0.3435980414546606</v>
+        <v>0.3462385711789149</v>
       </c>
       <c r="D240" t="s">
         <v>7</v>
@@ -8423,7 +8423,7 @@
         <v>10</v>
       </c>
       <c r="C241">
-        <v>0.2418084406263513</v>
+        <v>0.2383877973681386</v>
       </c>
       <c r="D241" t="s">
         <v>7</v>
@@ -8440,7 +8440,7 @@
         <v>6</v>
       </c>
       <c r="C242">
-        <v>0.3254633788769889</v>
+        <v>0.3312884553726934</v>
       </c>
       <c r="D242" t="s">
         <v>7</v>
@@ -8457,7 +8457,7 @@
         <v>15</v>
       </c>
       <c r="C243">
-        <v>0.4985677903177679</v>
+        <v>0.500853992723043</v>
       </c>
       <c r="D243" t="s">
         <v>7</v>
@@ -8474,7 +8474,7 @@
         <v>226</v>
       </c>
       <c r="C244">
-        <v>0.4739853917103896</v>
+        <v>0.4753122467841381</v>
       </c>
       <c r="D244" t="s">
         <v>7</v>
@@ -8491,7 +8491,7 @@
         <v>6</v>
       </c>
       <c r="C245">
-        <v>0.630875927650298</v>
+        <v>0.6365938941068338</v>
       </c>
       <c r="D245" t="s">
         <v>7</v>
@@ -8508,7 +8508,7 @@
         <v>6</v>
       </c>
       <c r="C246">
-        <v>0.4500539226364544</v>
+        <v>0.4552354679532494</v>
       </c>
       <c r="D246" t="s">
         <v>7</v>
@@ -8525,7 +8525,7 @@
         <v>6</v>
       </c>
       <c r="C247">
-        <v>0.406860206884375</v>
+        <v>0.4130480424882629</v>
       </c>
       <c r="D247" t="s">
         <v>7</v>
@@ -8542,7 +8542,7 @@
         <v>10</v>
       </c>
       <c r="C248">
-        <v>0.3038899271040585</v>
+        <v>0.3007608966771927</v>
       </c>
       <c r="D248" t="s">
         <v>7</v>
@@ -8559,7 +8559,7 @@
         <v>6</v>
       </c>
       <c r="C249">
-        <v>0.4313281847867615</v>
+        <v>0.4372008493822402</v>
       </c>
       <c r="D249" t="s">
         <v>7</v>
@@ -8576,7 +8576,7 @@
         <v>15</v>
       </c>
       <c r="C250">
-        <v>0.3144152454635587</v>
+        <v>0.3167809468931533</v>
       </c>
       <c r="D250" t="s">
         <v>7</v>
@@ -8593,7 +8593,7 @@
         <v>44</v>
       </c>
       <c r="C251">
-        <v>0.4956648060980605</v>
+        <v>0.4960981945480177</v>
       </c>
       <c r="D251" t="s">
         <v>7</v>
@@ -8610,7 +8610,7 @@
         <v>6</v>
       </c>
       <c r="C252">
-        <v>0.412613287327262</v>
+        <v>0.4175548364995839</v>
       </c>
       <c r="D252" t="s">
         <v>7</v>
@@ -8627,7 +8627,7 @@
         <v>6</v>
       </c>
       <c r="C253">
-        <v>0.3640125533911438</v>
+        <v>0.3695709556916547</v>
       </c>
       <c r="D253" t="s">
         <v>7</v>
@@ -8644,7 +8644,7 @@
         <v>6</v>
       </c>
       <c r="C254">
-        <v>0.4952444340995464</v>
+        <v>0.5005025990617649</v>
       </c>
       <c r="D254" t="s">
         <v>7</v>
@@ -8661,7 +8661,7 @@
         <v>15</v>
       </c>
       <c r="C255">
-        <v>0.4477480114328528</v>
+        <v>0.4504237061036552</v>
       </c>
       <c r="D255" t="s">
         <v>7</v>
@@ -8678,7 +8678,7 @@
         <v>6</v>
       </c>
       <c r="C256">
-        <v>0.5998794761109332</v>
+        <v>0.603918347216904</v>
       </c>
       <c r="D256" t="s">
         <v>7</v>
@@ -8695,7 +8695,7 @@
         <v>6</v>
       </c>
       <c r="C257">
-        <v>0.4083044809684342</v>
+        <v>0.4142189500065502</v>
       </c>
       <c r="D257" t="s">
         <v>7</v>
@@ -8712,7 +8712,7 @@
         <v>6</v>
       </c>
       <c r="C258">
-        <v>0.5038548175019024</v>
+        <v>0.510519316454962</v>
       </c>
       <c r="D258" t="s">
         <v>7</v>
@@ -8729,7 +8729,7 @@
         <v>15</v>
       </c>
       <c r="C259">
-        <v>0.298309960583961</v>
+        <v>0.3004134595234022</v>
       </c>
       <c r="D259" t="s">
         <v>7</v>
@@ -8746,7 +8746,7 @@
         <v>6</v>
       </c>
       <c r="C260">
-        <v>0.4380693008040051</v>
+        <v>0.4438626218174644</v>
       </c>
       <c r="D260" t="s">
         <v>7</v>
@@ -8763,7 +8763,7 @@
         <v>6</v>
       </c>
       <c r="C261">
-        <v>0.4864763997171652</v>
+        <v>0.4924575402663876</v>
       </c>
       <c r="D261" t="s">
         <v>7</v>
@@ -8780,7 +8780,7 @@
         <v>6</v>
       </c>
       <c r="C262">
-        <v>0.4287235228623805</v>
+        <v>0.4344632757592707</v>
       </c>
       <c r="D262" t="s">
         <v>7</v>
@@ -8797,7 +8797,7 @@
         <v>6</v>
       </c>
       <c r="C263">
-        <v>0.4641700467578964</v>
+        <v>0.4695565420413191</v>
       </c>
       <c r="D263" t="s">
         <v>7</v>
@@ -8814,7 +8814,7 @@
         <v>6</v>
       </c>
       <c r="C264">
-        <v>0.4459811716922109</v>
+        <v>0.4516797344587705</v>
       </c>
       <c r="D264" t="s">
         <v>7</v>
@@ -8831,7 +8831,7 @@
         <v>6</v>
       </c>
       <c r="C265">
-        <v>0.3460140349583291</v>
+        <v>0.3517538244124224</v>
       </c>
       <c r="D265" t="s">
         <v>7</v>
@@ -8848,7 +8848,7 @@
         <v>6</v>
       </c>
       <c r="C266">
-        <v>0.4001543853618537</v>
+        <v>0.4049663634664883</v>
       </c>
       <c r="D266" t="s">
         <v>7</v>
@@ -8865,7 +8865,7 @@
         <v>6</v>
       </c>
       <c r="C267">
-        <v>0.27489883096257</v>
+        <v>0.2801316938369079</v>
       </c>
       <c r="D267" t="s">
         <v>7</v>
@@ -8882,7 +8882,7 @@
         <v>6</v>
       </c>
       <c r="C268">
-        <v>0.4522097145691867</v>
+        <v>0.4571165799744631</v>
       </c>
       <c r="D268" t="s">
         <v>7</v>
@@ -8899,7 +8899,7 @@
         <v>44</v>
       </c>
       <c r="C269">
-        <v>0.3742069161109122</v>
+        <v>0.3729116193046573</v>
       </c>
       <c r="D269" t="s">
         <v>7</v>
@@ -8916,7 +8916,7 @@
         <v>6</v>
       </c>
       <c r="C270">
-        <v>0.5360106206282612</v>
+        <v>0.5427927211304929</v>
       </c>
       <c r="D270" t="s">
         <v>7</v>
@@ -8933,7 +8933,7 @@
         <v>6</v>
       </c>
       <c r="C271">
-        <v>0.545025541322165</v>
+        <v>0.5514165812903913</v>
       </c>
       <c r="D271" t="s">
         <v>7</v>
@@ -8950,7 +8950,7 @@
         <v>6</v>
       </c>
       <c r="C272">
-        <v>0.3836762635762402</v>
+        <v>0.3903289525358814</v>
       </c>
       <c r="D272" t="s">
         <v>7</v>
@@ -8967,7 +8967,7 @@
         <v>6</v>
       </c>
       <c r="C273">
-        <v>0.5318173437997095</v>
+        <v>0.537893289925253</v>
       </c>
       <c r="D273" t="s">
         <v>7</v>
@@ -8984,7 +8984,7 @@
         <v>15</v>
       </c>
       <c r="C274">
-        <v>0.3538248437096296</v>
+        <v>0.3567795579988073</v>
       </c>
       <c r="D274" t="s">
         <v>7</v>
@@ -9001,7 +9001,7 @@
         <v>10</v>
       </c>
       <c r="C275">
-        <v>0.2470521541805436</v>
+        <v>0.2434975618392645</v>
       </c>
       <c r="D275" t="s">
         <v>7</v>
@@ -9018,7 +9018,7 @@
         <v>6</v>
       </c>
       <c r="C276">
-        <v>0.3205862798227412</v>
+        <v>0.3248643751286648</v>
       </c>
       <c r="D276" t="s">
         <v>7</v>
@@ -9035,7 +9035,7 @@
         <v>6</v>
       </c>
       <c r="C277">
-        <v>0.3775952015336524</v>
+        <v>0.382998336426568</v>
       </c>
       <c r="D277" t="s">
         <v>7</v>
@@ -9052,7 +9052,7 @@
         <v>6</v>
       </c>
       <c r="C278">
-        <v>0.4472552011613439</v>
+        <v>0.4516882737181834</v>
       </c>
       <c r="D278" t="s">
         <v>7</v>
@@ -9069,7 +9069,7 @@
         <v>6</v>
       </c>
       <c r="C279">
-        <v>0.5470272584789674</v>
+        <v>0.553225481550041</v>
       </c>
       <c r="D279" t="s">
         <v>7</v>
@@ -9086,7 +9086,7 @@
         <v>6</v>
       </c>
       <c r="C280">
-        <v>0.4957217443707417</v>
+        <v>0.4996390636210539</v>
       </c>
       <c r="D280" t="s">
         <v>7</v>
@@ -9103,7 +9103,7 @@
         <v>6</v>
       </c>
       <c r="C281">
-        <v>0.3982901030774012</v>
+        <v>0.4042351114621328</v>
       </c>
       <c r="D281" t="s">
         <v>7</v>
@@ -9120,7 +9120,7 @@
         <v>15</v>
       </c>
       <c r="C282">
-        <v>0.3652230944510147</v>
+        <v>0.3676843630447438</v>
       </c>
       <c r="D282" t="s">
         <v>7</v>
@@ -9137,7 +9137,7 @@
         <v>6</v>
       </c>
       <c r="C283">
-        <v>0.3511290221596897</v>
+        <v>0.3564393111361292</v>
       </c>
       <c r="D283" t="s">
         <v>7</v>
@@ -9154,7 +9154,7 @@
         <v>6</v>
       </c>
       <c r="C284">
-        <v>0.3311349468320045</v>
+        <v>0.3373427095624622</v>
       </c>
       <c r="D284" t="s">
         <v>7</v>
@@ -9171,7 +9171,7 @@
         <v>15</v>
       </c>
       <c r="C285">
-        <v>0.2471130291645466</v>
+        <v>0.2490284621728504</v>
       </c>
       <c r="D285" t="s">
         <v>7</v>
@@ -9188,7 +9188,7 @@
         <v>6</v>
       </c>
       <c r="C286">
-        <v>0.2982945753434204</v>
+        <v>0.3040129186173865</v>
       </c>
       <c r="D286" t="s">
         <v>7</v>
@@ -9205,7 +9205,7 @@
         <v>44</v>
       </c>
       <c r="C287">
-        <v>0.4707537629897592</v>
+        <v>0.4705097458337114</v>
       </c>
       <c r="D287" t="s">
         <v>7</v>
@@ -9222,7 +9222,7 @@
         <v>6</v>
       </c>
       <c r="C288">
-        <v>0.2732692304410334</v>
+        <v>0.2795602509827043</v>
       </c>
       <c r="D288" t="s">
         <v>7</v>
@@ -9239,7 +9239,7 @@
         <v>6</v>
       </c>
       <c r="C289">
-        <v>0.3715527343026447</v>
+        <v>0.3766442752442883</v>
       </c>
       <c r="D289" t="s">
         <v>7</v>
@@ -9256,7 +9256,7 @@
         <v>15</v>
       </c>
       <c r="C290">
-        <v>0.3157416106838649</v>
+        <v>0.3181579336124398</v>
       </c>
       <c r="D290" t="s">
         <v>7</v>
@@ -9273,7 +9273,7 @@
         <v>6</v>
       </c>
       <c r="C291">
-        <v>0.4326806216142559</v>
+        <v>0.4382329848431203</v>
       </c>
       <c r="D291" t="s">
         <v>7</v>
@@ -9290,7 +9290,7 @@
         <v>145</v>
       </c>
       <c r="C292">
-        <v>0.4348878100797352</v>
+        <v>0.4297622545883468</v>
       </c>
       <c r="D292" t="s">
         <v>7</v>
@@ -9307,7 +9307,7 @@
         <v>6</v>
       </c>
       <c r="C293">
-        <v>0.6096690182428608</v>
+        <v>0.6155363651541489</v>
       </c>
       <c r="D293" t="s">
         <v>7</v>
@@ -9324,7 +9324,7 @@
         <v>15</v>
       </c>
       <c r="C294">
-        <v>0.4072351746972967</v>
+        <v>0.4095128402444583</v>
       </c>
       <c r="D294" t="s">
         <v>7</v>
@@ -9341,7 +9341,7 @@
         <v>10</v>
       </c>
       <c r="C295">
-        <v>0.3258689965924915</v>
+        <v>0.3227167310804794</v>
       </c>
       <c r="D295" t="s">
         <v>7</v>
@@ -9358,7 +9358,7 @@
         <v>15</v>
       </c>
       <c r="C296">
-        <v>0.3107578013810601</v>
+        <v>0.3132479825330827</v>
       </c>
       <c r="D296" t="s">
         <v>7</v>
@@ -9375,7 +9375,7 @@
         <v>10</v>
       </c>
       <c r="C297">
-        <v>0.4586725376093624</v>
+        <v>0.4553235217563223</v>
       </c>
       <c r="D297" t="s">
         <v>7</v>
@@ -9392,7 +9392,7 @@
         <v>10</v>
       </c>
       <c r="C298">
-        <v>0.3929279416878534</v>
+        <v>0.3902692949045607</v>
       </c>
       <c r="D298" t="s">
         <v>7</v>
@@ -9409,7 +9409,7 @@
         <v>44</v>
       </c>
       <c r="C299">
-        <v>0.2724267678915268</v>
+        <v>0.2724901601169842</v>
       </c>
       <c r="D299" t="s">
         <v>7</v>
@@ -9426,7 +9426,7 @@
         <v>10</v>
       </c>
       <c r="C300">
-        <v>0.3237046944611848</v>
+        <v>0.3201020247933296</v>
       </c>
       <c r="D300" t="s">
         <v>7</v>
@@ -9443,7 +9443,7 @@
         <v>6</v>
       </c>
       <c r="C301">
-        <v>0.3594218945460432</v>
+        <v>0.3651338896500385</v>
       </c>
       <c r="D301" t="s">
         <v>7</v>
@@ -9460,7 +9460,7 @@
         <v>44</v>
       </c>
       <c r="C302">
-        <v>0.4692241628957253</v>
+        <v>0.469269289582411</v>
       </c>
       <c r="D302" t="s">
         <v>7</v>
@@ -9477,7 +9477,7 @@
         <v>10</v>
       </c>
       <c r="C303">
-        <v>0.3113951720533466</v>
+        <v>0.3078793870613528</v>
       </c>
       <c r="D303" t="s">
         <v>7</v>
@@ -9494,7 +9494,7 @@
         <v>10</v>
       </c>
       <c r="C304">
-        <v>0.2960098879222638</v>
+        <v>0.2922127448047602</v>
       </c>
       <c r="D304" t="s">
         <v>7</v>
@@ -9511,7 +9511,7 @@
         <v>44</v>
       </c>
       <c r="C305">
-        <v>0.4023084222755631</v>
+        <v>0.4014516423990678</v>
       </c>
       <c r="D305" t="s">
         <v>7</v>
@@ -9528,7 +9528,7 @@
         <v>15</v>
       </c>
       <c r="C306">
-        <v>0.4317027411156236</v>
+        <v>0.4336396208735654</v>
       </c>
       <c r="D306" t="s">
         <v>7</v>
@@ -9545,7 +9545,7 @@
         <v>6</v>
       </c>
       <c r="C307">
-        <v>0.4258750280921418</v>
+        <v>0.4315152699243084</v>
       </c>
       <c r="D307" t="s">
         <v>7</v>
@@ -9562,7 +9562,7 @@
         <v>6</v>
       </c>
       <c r="C308">
-        <v>0.3956219004151964</v>
+        <v>0.4010190658672029</v>
       </c>
       <c r="D308" t="s">
         <v>7</v>
@@ -9579,7 +9579,7 @@
         <v>6</v>
       </c>
       <c r="C309">
-        <v>0.2765356806492457</v>
+        <v>0.2818819195593599</v>
       </c>
       <c r="D309" t="s">
         <v>7</v>
@@ -9596,7 +9596,7 @@
         <v>6</v>
       </c>
       <c r="C310">
-        <v>0.4106840097620228</v>
+        <v>0.4171369853569546</v>
       </c>
       <c r="D310" t="s">
         <v>7</v>
@@ -9613,7 +9613,7 @@
         <v>15</v>
       </c>
       <c r="C311">
-        <v>0.3497578615105849</v>
+        <v>0.3521207583112989</v>
       </c>
       <c r="D311" t="s">
         <v>7</v>
@@ -9630,7 +9630,7 @@
         <v>15</v>
       </c>
       <c r="C312">
-        <v>0.2716780196777767</v>
+        <v>0.273993763704012</v>
       </c>
       <c r="D312" t="s">
         <v>7</v>
@@ -9647,7 +9647,7 @@
         <v>44</v>
       </c>
       <c r="C313">
-        <v>0.3144619068046991</v>
+        <v>0.3131184977063728</v>
       </c>
       <c r="D313" t="s">
         <v>7</v>
@@ -9664,7 +9664,7 @@
         <v>10</v>
       </c>
       <c r="C314">
-        <v>0.2995171261039128</v>
+        <v>0.2959684667614155</v>
       </c>
       <c r="D314" t="s">
         <v>7</v>
@@ -9681,7 +9681,7 @@
         <v>44</v>
       </c>
       <c r="C315">
-        <v>0.5030119793598046</v>
+        <v>0.5030080066804039</v>
       </c>
       <c r="D315" t="s">
         <v>7</v>
@@ -9698,7 +9698,7 @@
         <v>6</v>
       </c>
       <c r="C316">
-        <v>0.3882333791138319</v>
+        <v>0.3938794177574184</v>
       </c>
       <c r="D316" t="s">
         <v>7</v>
@@ -9715,7 +9715,7 @@
         <v>6</v>
       </c>
       <c r="C317">
-        <v>0.5312937698599693</v>
+        <v>0.536670990458005</v>
       </c>
       <c r="D317" t="s">
         <v>7</v>
@@ -9732,7 +9732,7 @@
         <v>6</v>
       </c>
       <c r="C318">
-        <v>0.5585781178314113</v>
+        <v>0.5644807092272125</v>
       </c>
       <c r="D318" t="s">
         <v>7</v>
@@ -9749,7 +9749,7 @@
         <v>6</v>
       </c>
       <c r="C319">
-        <v>0.34658658720485</v>
+        <v>0.3521754100600347</v>
       </c>
       <c r="D319" t="s">
         <v>7</v>
@@ -9766,7 +9766,7 @@
         <v>15</v>
       </c>
       <c r="C320">
-        <v>0.2807207142330665</v>
+        <v>0.2830514329557617</v>
       </c>
       <c r="D320" t="s">
         <v>7</v>
@@ -9783,7 +9783,7 @@
         <v>6</v>
       </c>
       <c r="C321">
-        <v>0.3529537752677362</v>
+        <v>0.3581545778631968</v>
       </c>
       <c r="D321" t="s">
         <v>7</v>
@@ -9800,7 +9800,7 @@
         <v>6</v>
       </c>
       <c r="C322">
-        <v>0.3777685342998616</v>
+        <v>0.3830340452151103</v>
       </c>
       <c r="D322" t="s">
         <v>7</v>
@@ -9817,7 +9817,7 @@
         <v>10</v>
       </c>
       <c r="C323">
-        <v>0.3178933526716169</v>
+        <v>0.3143354062858941</v>
       </c>
       <c r="D323" t="s">
         <v>7</v>
@@ -9834,7 +9834,7 @@
         <v>44</v>
       </c>
       <c r="C324">
-        <v>0.4064018787656126</v>
+        <v>0.4052216368277862</v>
       </c>
       <c r="D324" t="s">
         <v>7</v>
@@ -9848,10 +9848,10 @@
         <v>658</v>
       </c>
       <c r="B325" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C325">
-        <v>0.220257006478951</v>
+        <v>0.2245497039222527</v>
       </c>
       <c r="D325" t="s">
         <v>7</v>
@@ -9868,7 +9868,7 @@
         <v>44</v>
       </c>
       <c r="C326">
-        <v>0.3670231080288204</v>
+        <v>0.36622687022017</v>
       </c>
       <c r="D326" t="s">
         <v>7</v>
@@ -9885,7 +9885,7 @@
         <v>44</v>
       </c>
       <c r="C327">
-        <v>0.3257836925848742</v>
+        <v>0.3252648880141185</v>
       </c>
       <c r="D327" t="s">
         <v>7</v>
@@ -9902,7 +9902,7 @@
         <v>15</v>
       </c>
       <c r="C328">
-        <v>0.2788693950164571</v>
+        <v>0.28124459137469</v>
       </c>
       <c r="D328" t="s">
         <v>7</v>
@@ -9919,7 +9919,7 @@
         <v>15</v>
       </c>
       <c r="C329">
-        <v>0.3001956267066369</v>
+        <v>0.302368758040183</v>
       </c>
       <c r="D329" t="s">
         <v>7</v>
@@ -9936,7 +9936,7 @@
         <v>15</v>
       </c>
       <c r="C330">
-        <v>0.3165332827973709</v>
+        <v>0.3189276527375555</v>
       </c>
       <c r="D330" t="s">
         <v>7</v>
@@ -9950,10 +9950,10 @@
         <v>670</v>
       </c>
       <c r="B331" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C331">
-        <v>0.3591439584070425</v>
+        <v>0.3574593112131789</v>
       </c>
       <c r="D331" t="s">
         <v>7</v>
@@ -9970,7 +9970,7 @@
         <v>10</v>
       </c>
       <c r="C332">
-        <v>0.3446512731069328</v>
+        <v>0.3414726310091031</v>
       </c>
       <c r="D332" t="s">
         <v>7</v>
@@ -9987,7 +9987,7 @@
         <v>6</v>
       </c>
       <c r="C333">
-        <v>0.4795055885624363</v>
+        <v>0.4860361099471424</v>
       </c>
       <c r="D333" t="s">
         <v>7</v>
@@ -10004,7 +10004,7 @@
         <v>15</v>
       </c>
       <c r="C334">
-        <v>0.3047915206114759</v>
+        <v>0.3069554386544092</v>
       </c>
       <c r="D334" t="s">
         <v>7</v>
@@ -10021,7 +10021,7 @@
         <v>15</v>
       </c>
       <c r="C335">
-        <v>0.3521803938942047</v>
+        <v>0.3549319077345647</v>
       </c>
       <c r="D335" t="s">
         <v>7</v>
@@ -10038,7 +10038,7 @@
         <v>10</v>
       </c>
       <c r="C336">
-        <v>0.313448716369143</v>
+        <v>0.3095574546765317</v>
       </c>
       <c r="D336" t="s">
         <v>7</v>
@@ -10055,7 +10055,7 @@
         <v>44</v>
       </c>
       <c r="C337">
-        <v>0.4349343024479565</v>
+        <v>0.4339861658202007</v>
       </c>
       <c r="D337" t="s">
         <v>7</v>
@@ -10072,7 +10072,7 @@
         <v>6</v>
       </c>
       <c r="C338">
-        <v>0.2854852829759107</v>
+        <v>0.2914939545742061</v>
       </c>
       <c r="D338" t="s">
         <v>7</v>
@@ -10089,7 +10089,7 @@
         <v>15</v>
       </c>
       <c r="C339">
-        <v>0.4458043344323856</v>
+        <v>0.4479716548515007</v>
       </c>
       <c r="D339" t="s">
         <v>7</v>
@@ -10106,7 +10106,7 @@
         <v>15</v>
       </c>
       <c r="C340">
-        <v>0.3047709792065275</v>
+        <v>0.306975379904933</v>
       </c>
       <c r="D340" t="s">
         <v>7</v>
@@ -10123,7 +10123,7 @@
         <v>6</v>
       </c>
       <c r="C341">
-        <v>0.2990813877334996</v>
+        <v>0.3051432759499521</v>
       </c>
       <c r="D341" t="s">
         <v>7</v>
@@ -10140,7 +10140,7 @@
         <v>10</v>
       </c>
       <c r="C342">
-        <v>0.2721560871503791</v>
+        <v>0.2692457810055402</v>
       </c>
       <c r="D342" t="s">
         <v>7</v>
@@ -10157,7 +10157,7 @@
         <v>10</v>
       </c>
       <c r="C343">
-        <v>0.3794909387912558</v>
+        <v>0.3757685007328178</v>
       </c>
       <c r="D343" t="s">
         <v>7</v>
@@ -10174,7 +10174,7 @@
         <v>15</v>
       </c>
       <c r="C344">
-        <v>0.2588774413122668</v>
+        <v>0.2611178404158734</v>
       </c>
       <c r="D344" t="s">
         <v>7</v>
@@ -10191,7 +10191,7 @@
         <v>6</v>
       </c>
       <c r="C345">
-        <v>0.3726174277736634</v>
+        <v>0.3782166625769434</v>
       </c>
       <c r="D345" t="s">
         <v>7</v>
@@ -10208,7 +10208,7 @@
         <v>10</v>
       </c>
       <c r="C346">
-        <v>0.3232982652366989</v>
+        <v>0.3201396791318229</v>
       </c>
       <c r="D346" t="s">
         <v>7</v>
@@ -10225,7 +10225,7 @@
         <v>15</v>
       </c>
       <c r="C347">
-        <v>0.3486952262558319</v>
+        <v>0.3511372116355303</v>
       </c>
       <c r="D347" t="s">
         <v>7</v>
@@ -10242,7 +10242,7 @@
         <v>6</v>
       </c>
       <c r="C348">
-        <v>0.3530073020373877</v>
+        <v>0.3592010554715729</v>
       </c>
       <c r="D348" t="s">
         <v>7</v>
@@ -10259,7 +10259,7 @@
         <v>6</v>
       </c>
       <c r="C349">
-        <v>0.4980031414894597</v>
+        <v>0.5048517696564034</v>
       </c>
       <c r="D349" t="s">
         <v>7</v>
@@ -10276,7 +10276,7 @@
         <v>15</v>
       </c>
       <c r="C350">
-        <v>0.3555779640253525</v>
+        <v>0.357783323728112</v>
       </c>
       <c r="D350" t="s">
         <v>7</v>
@@ -10293,7 +10293,7 @@
         <v>145</v>
       </c>
       <c r="C351">
-        <v>0.2389293229611857</v>
+        <v>0.2317129685538366</v>
       </c>
       <c r="D351" t="s">
         <v>7</v>
@@ -10310,7 +10310,7 @@
         <v>15</v>
       </c>
       <c r="C352">
-        <v>0.3990660858335938</v>
+        <v>0.4015317335891016</v>
       </c>
       <c r="D352" t="s">
         <v>7</v>
@@ -10327,7 +10327,7 @@
         <v>10</v>
       </c>
       <c r="C353">
-        <v>0.3721755721657349</v>
+        <v>0.3688327690175873</v>
       </c>
       <c r="D353" t="s">
         <v>7</v>
@@ -10344,7 +10344,7 @@
         <v>6</v>
       </c>
       <c r="C354">
-        <v>0.2903983149070718</v>
+        <v>0.2954905467717648</v>
       </c>
       <c r="D354" t="s">
         <v>7</v>
@@ -10361,7 +10361,7 @@
         <v>6</v>
       </c>
       <c r="C355">
-        <v>0.3819562470991175</v>
+        <v>0.3877022305355358</v>
       </c>
       <c r="D355" t="s">
         <v>7</v>
@@ -10378,7 +10378,7 @@
         <v>6</v>
       </c>
       <c r="C356">
-        <v>0.3227839113560097</v>
+        <v>0.3285480777230912</v>
       </c>
       <c r="D356" t="s">
         <v>7</v>
@@ -10395,7 +10395,7 @@
         <v>6</v>
       </c>
       <c r="C357">
-        <v>0.4084791249552997</v>
+        <v>0.4140400507950224</v>
       </c>
       <c r="D357" t="s">
         <v>7</v>
@@ -10412,7 +10412,7 @@
         <v>6</v>
       </c>
       <c r="C358">
-        <v>0.3458304139432658</v>
+        <v>0.352261832944315</v>
       </c>
       <c r="D358" t="s">
         <v>7</v>
@@ -10429,7 +10429,7 @@
         <v>44</v>
       </c>
       <c r="C359">
-        <v>0.4528335956850251</v>
+        <v>0.4526094476176031</v>
       </c>
       <c r="D359" t="s">
         <v>7</v>
@@ -10446,7 +10446,7 @@
         <v>6</v>
       </c>
       <c r="C360">
-        <v>0.4877784654609692</v>
+        <v>0.4942814791324469</v>
       </c>
       <c r="D360" t="s">
         <v>7</v>
@@ -10463,7 +10463,7 @@
         <v>15</v>
       </c>
       <c r="C361">
-        <v>0.3057092016594836</v>
+        <v>0.3081114178097432</v>
       </c>
       <c r="D361" t="s">
         <v>7</v>
@@ -10480,7 +10480,7 @@
         <v>6</v>
       </c>
       <c r="C362">
-        <v>0.3678651736383626</v>
+        <v>0.3731618005408188</v>
       </c>
       <c r="D362" t="s">
         <v>7</v>
@@ -10497,7 +10497,7 @@
         <v>6</v>
       </c>
       <c r="C363">
-        <v>0.2896491248062164</v>
+        <v>0.295387126912032</v>
       </c>
       <c r="D363" t="s">
         <v>7</v>
@@ -10514,7 +10514,7 @@
         <v>10</v>
       </c>
       <c r="C364">
-        <v>0.3062765197452864</v>
+        <v>0.3028986610426423</v>
       </c>
       <c r="D364" t="s">
         <v>7</v>
@@ -10531,7 +10531,7 @@
         <v>15</v>
       </c>
       <c r="C365">
-        <v>0.3191356235027803</v>
+        <v>0.3215993689221526</v>
       </c>
       <c r="D365" t="s">
         <v>7</v>
@@ -10548,7 +10548,7 @@
         <v>15</v>
       </c>
       <c r="C366">
-        <v>0.2721207579711444</v>
+        <v>0.2741762177091143</v>
       </c>
       <c r="D366" t="s">
         <v>7</v>
@@ -10565,7 +10565,7 @@
         <v>6</v>
       </c>
       <c r="C367">
-        <v>0.3570953578617954</v>
+        <v>0.3622082336770255</v>
       </c>
       <c r="D367" t="s">
         <v>7</v>
@@ -10582,7 +10582,7 @@
         <v>15</v>
       </c>
       <c r="C368">
-        <v>0.3568299810265756</v>
+        <v>0.3598930666679192</v>
       </c>
       <c r="D368" t="s">
         <v>7</v>
@@ -10599,7 +10599,7 @@
         <v>6</v>
       </c>
       <c r="C369">
-        <v>0.5365589787463735</v>
+        <v>0.5418386999243436</v>
       </c>
       <c r="D369" t="s">
         <v>7</v>
@@ -10616,7 +10616,7 @@
         <v>15</v>
       </c>
       <c r="C370">
-        <v>0.3416768851249381</v>
+        <v>0.3440573871828592</v>
       </c>
       <c r="D370" t="s">
         <v>7</v>
@@ -10633,7 +10633,7 @@
         <v>6</v>
       </c>
       <c r="C371">
-        <v>0.475330483179788</v>
+        <v>0.4818037603512438</v>
       </c>
       <c r="D371" t="s">
         <v>7</v>
@@ -10650,7 +10650,7 @@
         <v>6</v>
       </c>
       <c r="C372">
-        <v>0.3836238396119306</v>
+        <v>0.3886589767347233</v>
       </c>
       <c r="D372" t="s">
         <v>7</v>
@@ -10667,7 +10667,7 @@
         <v>6</v>
       </c>
       <c r="C373">
-        <v>0.4459139234820456</v>
+        <v>0.4518321029746044</v>
       </c>
       <c r="D373" t="s">
         <v>7</v>
@@ -10684,7 +10684,7 @@
         <v>6</v>
       </c>
       <c r="C374">
-        <v>0.5007435441542931</v>
+        <v>0.5062674642545448</v>
       </c>
       <c r="D374" t="s">
         <v>7</v>
@@ -10701,7 +10701,7 @@
         <v>6</v>
       </c>
       <c r="C375">
-        <v>0.4805282975018298</v>
+        <v>0.4859244773702881</v>
       </c>
       <c r="D375" t="s">
         <v>7</v>
@@ -10718,7 +10718,7 @@
         <v>15</v>
       </c>
       <c r="C376">
-        <v>0.3547355265524255</v>
+        <v>0.3576926675708865</v>
       </c>
       <c r="D376" t="s">
         <v>7</v>
@@ -10735,7 +10735,7 @@
         <v>6</v>
       </c>
       <c r="C377">
-        <v>0.4890450285563663</v>
+        <v>0.4945111800165009</v>
       </c>
       <c r="D377" t="s">
         <v>7</v>
@@ -10752,7 +10752,7 @@
         <v>6</v>
       </c>
       <c r="C378">
-        <v>0.3189023059272294</v>
+        <v>0.3244654939888216</v>
       </c>
       <c r="D378" t="s">
         <v>7</v>
@@ -10769,7 +10769,7 @@
         <v>6</v>
       </c>
       <c r="C379">
-        <v>0.33193303184139</v>
+        <v>0.3374096663353172</v>
       </c>
       <c r="D379" t="s">
         <v>7</v>
@@ -10786,7 +10786,7 @@
         <v>6</v>
       </c>
       <c r="C380">
-        <v>0.380505937209123</v>
+        <v>0.386169028271969</v>
       </c>
       <c r="D380" t="s">
         <v>7</v>
@@ -10803,7 +10803,7 @@
         <v>10</v>
       </c>
       <c r="C381">
-        <v>0.4688006910022827</v>
+        <v>0.4668044274490474</v>
       </c>
       <c r="D381" t="s">
         <v>7</v>
@@ -10820,7 +10820,7 @@
         <v>6</v>
       </c>
       <c r="C382">
-        <v>0.3382818743965192</v>
+        <v>0.343120021702196</v>
       </c>
       <c r="D382" t="s">
         <v>7</v>
@@ -10837,7 +10837,7 @@
         <v>10</v>
       </c>
       <c r="C383">
-        <v>0.3689678404919182</v>
+        <v>0.365330114928362</v>
       </c>
       <c r="D383" t="s">
         <v>7</v>
@@ -10854,7 +10854,7 @@
         <v>44</v>
       </c>
       <c r="C384">
-        <v>0.4358004397927337</v>
+        <v>0.4354180412702172</v>
       </c>
       <c r="D384" t="s">
         <v>7</v>
@@ -10871,7 +10871,7 @@
         <v>6</v>
       </c>
       <c r="C385">
-        <v>0.4109915775745731</v>
+        <v>0.4158802813897221</v>
       </c>
       <c r="D385" t="s">
         <v>7</v>
@@ -10888,7 +10888,7 @@
         <v>15</v>
       </c>
       <c r="C386">
-        <v>0.3022559536176835</v>
+        <v>0.3044891669632954</v>
       </c>
       <c r="D386" t="s">
         <v>7</v>
@@ -10905,7 +10905,7 @@
         <v>10</v>
       </c>
       <c r="C387">
-        <v>0.4187939811953572</v>
+        <v>0.4153650693102153</v>
       </c>
       <c r="D387" t="s">
         <v>7</v>
@@ -10922,7 +10922,7 @@
         <v>44</v>
       </c>
       <c r="C388">
-        <v>0.2896212500113542</v>
+        <v>0.2884540648339964</v>
       </c>
       <c r="D388" t="s">
         <v>7</v>
@@ -10939,7 +10939,7 @@
         <v>6</v>
       </c>
       <c r="C389">
-        <v>0.3671986447706274</v>
+        <v>0.3727434049091187</v>
       </c>
       <c r="D389" t="s">
         <v>7</v>
@@ -10956,7 +10956,7 @@
         <v>15</v>
       </c>
       <c r="C390">
-        <v>0.3346569449653552</v>
+        <v>0.3370397198087378</v>
       </c>
       <c r="D390" t="s">
         <v>7</v>
@@ -10973,7 +10973,7 @@
         <v>15</v>
       </c>
       <c r="C391">
-        <v>0.3458973998735382</v>
+        <v>0.348335816847116</v>
       </c>
       <c r="D391" t="s">
         <v>7</v>
@@ -10990,7 +10990,7 @@
         <v>10</v>
       </c>
       <c r="C392">
-        <v>0.3225934970983097</v>
+        <v>0.3189712555498261</v>
       </c>
       <c r="D392" t="s">
         <v>7</v>
@@ -11007,7 +11007,7 @@
         <v>10</v>
       </c>
       <c r="C393">
-        <v>0.3787321103203632</v>
+        <v>0.3762388376142077</v>
       </c>
       <c r="D393" t="s">
         <v>7</v>
@@ -11024,7 +11024,7 @@
         <v>15</v>
       </c>
       <c r="C394">
-        <v>0.3688174300211956</v>
+        <v>0.3711857404365056</v>
       </c>
       <c r="D394" t="s">
         <v>7</v>
@@ -11041,7 +11041,7 @@
         <v>10</v>
       </c>
       <c r="C395">
-        <v>0.4159781236541838</v>
+        <v>0.4133186450137529</v>
       </c>
       <c r="D395" t="s">
         <v>7</v>
@@ -11058,7 +11058,7 @@
         <v>6</v>
       </c>
       <c r="C396">
-        <v>0.3935152201867761</v>
+        <v>0.3994779645348568</v>
       </c>
       <c r="D396" t="s">
         <v>7</v>
@@ -11075,7 +11075,7 @@
         <v>10</v>
       </c>
       <c r="C397">
-        <v>0.3378939523612386</v>
+        <v>0.3350895289733127</v>
       </c>
       <c r="D397" t="s">
         <v>7</v>
@@ -11092,7 +11092,7 @@
         <v>6</v>
       </c>
       <c r="C398">
-        <v>0.5011520367850562</v>
+        <v>0.5080860633779676</v>
       </c>
       <c r="D398" t="s">
         <v>7</v>
@@ -11109,7 +11109,7 @@
         <v>15</v>
       </c>
       <c r="C399">
-        <v>0.3532540386337862</v>
+        <v>0.3556828227419039</v>
       </c>
       <c r="D399" t="s">
         <v>7</v>
@@ -11126,7 +11126,7 @@
         <v>6</v>
       </c>
       <c r="C400">
-        <v>0.3420977947133838</v>
+        <v>0.3475036864733208</v>
       </c>
       <c r="D400" t="s">
         <v>7</v>
@@ -11143,7 +11143,7 @@
         <v>15</v>
       </c>
       <c r="C401">
-        <v>0.4471594489038782</v>
+        <v>0.449109235710471</v>
       </c>
       <c r="D401" t="s">
         <v>7</v>
@@ -11160,7 +11160,7 @@
         <v>6</v>
       </c>
       <c r="C402">
-        <v>0.4014000649469068</v>
+        <v>0.4064389586456107</v>
       </c>
       <c r="D402" t="s">
         <v>7</v>
@@ -11177,7 +11177,7 @@
         <v>6</v>
       </c>
       <c r="C403">
-        <v>0.3058075027467035</v>
+        <v>0.3108524135580112</v>
       </c>
       <c r="D403" t="s">
         <v>7</v>
@@ -11194,7 +11194,7 @@
         <v>10</v>
       </c>
       <c r="C404">
-        <v>0.3158274266041715</v>
+        <v>0.312755983879567</v>
       </c>
       <c r="D404" t="s">
         <v>7</v>
@@ -11211,7 +11211,7 @@
         <v>6</v>
       </c>
       <c r="C405">
-        <v>0.4324767824202079</v>
+        <v>0.4366612087653646</v>
       </c>
       <c r="D405" t="s">
         <v>7</v>
@@ -11228,7 +11228,7 @@
         <v>145</v>
       </c>
       <c r="C406">
-        <v>0.4426453668142301</v>
+        <v>0.4392642458249147</v>
       </c>
       <c r="D406" t="s">
         <v>7</v>
@@ -11245,7 +11245,7 @@
         <v>6</v>
       </c>
       <c r="C407">
-        <v>0.4003194386949274</v>
+        <v>0.4058144270289831</v>
       </c>
       <c r="D407" t="s">
         <v>7</v>
@@ -11262,7 +11262,7 @@
         <v>6</v>
       </c>
       <c r="C408">
-        <v>0.4720842580342541</v>
+        <v>0.4774752439140311</v>
       </c>
       <c r="D408" t="s">
         <v>7</v>
@@ -11279,7 +11279,7 @@
         <v>6</v>
       </c>
       <c r="C409">
-        <v>0.4901439022654028</v>
+        <v>0.4942635917637561</v>
       </c>
       <c r="D409" t="s">
         <v>7</v>
@@ -11296,7 +11296,7 @@
         <v>15</v>
       </c>
       <c r="C410">
-        <v>0.291621864859898</v>
+        <v>0.2939096575701667</v>
       </c>
       <c r="D410" t="s">
         <v>7</v>
@@ -11313,7 +11313,7 @@
         <v>6</v>
       </c>
       <c r="C411">
-        <v>0.3294956562050057</v>
+        <v>0.3352539520638984</v>
       </c>
       <c r="D411" t="s">
         <v>7</v>
@@ -11330,7 +11330,7 @@
         <v>6</v>
       </c>
       <c r="C412">
-        <v>0.4351081568229256</v>
+        <v>0.4407379943137761</v>
       </c>
       <c r="D412" t="s">
         <v>7</v>
@@ -11347,7 +11347,7 @@
         <v>6</v>
       </c>
       <c r="C413">
-        <v>0.2673210815794937</v>
+        <v>0.2726444865450189</v>
       </c>
       <c r="D413" t="s">
         <v>7</v>
@@ -11364,7 +11364,7 @@
         <v>15</v>
       </c>
       <c r="C414">
-        <v>0.3138955462049966</v>
+        <v>0.3164442829452042</v>
       </c>
       <c r="D414" t="s">
         <v>7</v>
@@ -11381,7 +11381,7 @@
         <v>15</v>
       </c>
       <c r="C415">
-        <v>0.3605865147753164</v>
+        <v>0.3629341202340278</v>
       </c>
       <c r="D415" t="s">
         <v>7</v>
@@ -11398,7 +11398,7 @@
         <v>15</v>
       </c>
       <c r="C416">
-        <v>0.4332518953556057</v>
+        <v>0.4373037212662835</v>
       </c>
       <c r="D416" t="s">
         <v>7</v>
@@ -11415,7 +11415,7 @@
         <v>6</v>
       </c>
       <c r="C417">
-        <v>0.2803713428289135</v>
+        <v>0.2861117393675225</v>
       </c>
       <c r="D417" t="s">
         <v>7</v>
@@ -11432,7 +11432,7 @@
         <v>10</v>
       </c>
       <c r="C418">
-        <v>0.3067393179949134</v>
+        <v>0.303990089573389</v>
       </c>
       <c r="D418" t="s">
         <v>7</v>
@@ -11449,7 +11449,7 @@
         <v>15</v>
       </c>
       <c r="C419">
-        <v>0.3959844363271829</v>
+        <v>0.3984390346354085</v>
       </c>
       <c r="D419" t="s">
         <v>7</v>
@@ -11466,7 +11466,7 @@
         <v>44</v>
       </c>
       <c r="C420">
-        <v>0.447330818536044</v>
+        <v>0.4473658487040756</v>
       </c>
       <c r="D420" t="s">
         <v>7</v>
@@ -11483,7 +11483,7 @@
         <v>44</v>
       </c>
       <c r="C421">
-        <v>0.4538082877403036</v>
+        <v>0.4532891708419397</v>
       </c>
       <c r="D421" t="s">
         <v>7</v>
@@ -11500,7 +11500,7 @@
         <v>6</v>
       </c>
       <c r="C422">
-        <v>0.3748418256784402</v>
+        <v>0.38053112902339</v>
       </c>
       <c r="D422" t="s">
         <v>7</v>
@@ -11517,7 +11517,7 @@
         <v>44</v>
       </c>
       <c r="C423">
-        <v>0.4318944883799044</v>
+        <v>0.4308436271537863</v>
       </c>
       <c r="D423" t="s">
         <v>7</v>
@@ -11534,7 +11534,7 @@
         <v>10</v>
       </c>
       <c r="C424">
-        <v>0.3349120276540628</v>
+        <v>0.3316939687775155</v>
       </c>
       <c r="D424" t="s">
         <v>7</v>
@@ -11551,7 +11551,7 @@
         <v>6</v>
       </c>
       <c r="C425">
-        <v>0.3742515358759995</v>
+        <v>0.3795525355636375</v>
       </c>
       <c r="D425" t="s">
         <v>7</v>
@@ -11568,7 +11568,7 @@
         <v>15</v>
       </c>
       <c r="C426">
-        <v>0.3570308188952453</v>
+        <v>0.3593202438134249</v>
       </c>
       <c r="D426" t="s">
         <v>7</v>
@@ -11585,7 +11585,7 @@
         <v>6</v>
       </c>
       <c r="C427">
-        <v>0.2886549423145098</v>
+        <v>0.2945977653518862</v>
       </c>
       <c r="D427" t="s">
         <v>7</v>
@@ -11602,7 +11602,7 @@
         <v>6</v>
       </c>
       <c r="C428">
-        <v>0.2791660997950676</v>
+        <v>0.2846372477456875</v>
       </c>
       <c r="D428" t="s">
         <v>7</v>
@@ -11619,7 +11619,7 @@
         <v>10</v>
       </c>
       <c r="C429">
-        <v>0.3479244417855497</v>
+        <v>0.344617895774117</v>
       </c>
       <c r="D429" t="s">
         <v>7</v>
@@ -11636,7 +11636,7 @@
         <v>6</v>
       </c>
       <c r="C430">
-        <v>0.3716433297355806</v>
+        <v>0.3779046512281166</v>
       </c>
       <c r="D430" t="s">
         <v>7</v>
@@ -11653,7 +11653,7 @@
         <v>6</v>
       </c>
       <c r="C431">
-        <v>0.2980584775335986</v>
+        <v>0.3030108440764399</v>
       </c>
       <c r="D431" t="s">
         <v>7</v>
@@ -11670,7 +11670,7 @@
         <v>15</v>
       </c>
       <c r="C432">
-        <v>0.3507934942317557</v>
+        <v>0.3533676140125941</v>
       </c>
       <c r="D432" t="s">
         <v>7</v>
@@ -11687,7 +11687,7 @@
         <v>6</v>
       </c>
       <c r="C433">
-        <v>0.2791596617722182</v>
+        <v>0.2846103921442354</v>
       </c>
       <c r="D433" t="s">
         <v>7</v>
@@ -11704,7 +11704,7 @@
         <v>15</v>
       </c>
       <c r="C434">
-        <v>0.3620775136718439</v>
+        <v>0.3646730696323053</v>
       </c>
       <c r="D434" t="s">
         <v>7</v>
@@ -11721,7 +11721,7 @@
         <v>10</v>
       </c>
       <c r="C435">
-        <v>0.3880874102587367</v>
+        <v>0.3849090642413376</v>
       </c>
       <c r="D435" t="s">
         <v>7</v>
@@ -11738,7 +11738,7 @@
         <v>15</v>
       </c>
       <c r="C436">
-        <v>0.3552901274643998</v>
+        <v>0.3576074616665251</v>
       </c>
       <c r="D436" t="s">
         <v>7</v>
@@ -11755,7 +11755,7 @@
         <v>10</v>
       </c>
       <c r="C437">
-        <v>0.3163147040792227</v>
+        <v>0.3126611413958739</v>
       </c>
       <c r="D437" t="s">
         <v>7</v>
@@ -11772,7 +11772,7 @@
         <v>15</v>
       </c>
       <c r="C438">
-        <v>0.3587563341285492</v>
+        <v>0.3613105407581528</v>
       </c>
       <c r="D438" t="s">
         <v>7</v>
@@ -11789,7 +11789,7 @@
         <v>6</v>
       </c>
       <c r="C439">
-        <v>0.3972896727883712</v>
+        <v>0.4036115166037405</v>
       </c>
       <c r="D439" t="s">
         <v>7</v>
@@ -11806,7 +11806,7 @@
         <v>10</v>
       </c>
       <c r="C440">
-        <v>0.3098597459587893</v>
+        <v>0.3062283012271882</v>
       </c>
       <c r="D440" t="s">
         <v>7</v>
@@ -11823,7 +11823,7 @@
         <v>6</v>
       </c>
       <c r="C441">
-        <v>0.341887936914513</v>
+        <v>0.3487674068611831</v>
       </c>
       <c r="D441" t="s">
         <v>7</v>
@@ -11840,7 +11840,7 @@
         <v>6</v>
       </c>
       <c r="C442">
-        <v>0.3156378680298125</v>
+        <v>0.3216017006219055</v>
       </c>
       <c r="D442" t="s">
         <v>7</v>
@@ -11857,7 +11857,7 @@
         <v>15</v>
       </c>
       <c r="C443">
-        <v>0.3046258556223034</v>
+        <v>0.3070972861866177</v>
       </c>
       <c r="D443" t="s">
         <v>7</v>
@@ -11874,7 +11874,7 @@
         <v>10</v>
       </c>
       <c r="C444">
-        <v>0.3383851475886783</v>
+        <v>0.3355704920167318</v>
       </c>
       <c r="D444" t="s">
         <v>7</v>
@@ -11891,7 +11891,7 @@
         <v>6</v>
       </c>
       <c r="C445">
-        <v>0.3738418813937043</v>
+        <v>0.3796182485996014</v>
       </c>
       <c r="D445" t="s">
         <v>7</v>
@@ -11908,7 +11908,7 @@
         <v>44</v>
       </c>
       <c r="C446">
-        <v>0.3442356020405257</v>
+        <v>0.3438515825475766</v>
       </c>
       <c r="D446" t="s">
         <v>7</v>
@@ -11925,7 +11925,7 @@
         <v>6</v>
       </c>
       <c r="C447">
-        <v>0.2794578278247444</v>
+        <v>0.2855020007596275</v>
       </c>
       <c r="D447" t="s">
         <v>7</v>
@@ -11942,7 +11942,7 @@
         <v>6</v>
       </c>
       <c r="C448">
-        <v>0.3826953050286061</v>
+        <v>0.3884933866693064</v>
       </c>
       <c r="D448" t="s">
         <v>7</v>
@@ -11959,7 +11959,7 @@
         <v>6</v>
       </c>
       <c r="C449">
-        <v>0.4149093458369522</v>
+        <v>0.4200759325105389</v>
       </c>
       <c r="D449" t="s">
         <v>7</v>
@@ -11976,7 +11976,7 @@
         <v>44</v>
       </c>
       <c r="C450">
-        <v>0.4136677566652305</v>
+        <v>0.4127447292786718</v>
       </c>
       <c r="D450" t="s">
         <v>7</v>
@@ -11993,7 +11993,7 @@
         <v>44</v>
       </c>
       <c r="C451">
-        <v>0.3894726335765242</v>
+        <v>0.3893795870510624</v>
       </c>
       <c r="D451" t="s">
         <v>7</v>
@@ -12010,7 +12010,7 @@
         <v>6</v>
       </c>
       <c r="C452">
-        <v>0.3459605576029035</v>
+        <v>0.3516806434100651</v>
       </c>
       <c r="D452" t="s">
         <v>7</v>
@@ -12027,7 +12027,7 @@
         <v>10</v>
       </c>
       <c r="C453">
-        <v>0.3575547628139507</v>
+        <v>0.3538455900535299</v>
       </c>
       <c r="D453" t="s">
         <v>7</v>
@@ -12044,7 +12044,7 @@
         <v>15</v>
       </c>
       <c r="C454">
-        <v>0.2877432326703628</v>
+        <v>0.2898429874741598</v>
       </c>
       <c r="D454" t="s">
         <v>7</v>
@@ -12061,7 +12061,7 @@
         <v>10</v>
       </c>
       <c r="C455">
-        <v>0.3514013764125104</v>
+        <v>0.3476485071191834</v>
       </c>
       <c r="D455" t="s">
         <v>7</v>
@@ -12078,7 +12078,7 @@
         <v>6</v>
       </c>
       <c r="C456">
-        <v>0.3879417717042475</v>
+        <v>0.3950207462160221</v>
       </c>
       <c r="D456" t="s">
         <v>7</v>
@@ -12095,7 +12095,7 @@
         <v>15</v>
       </c>
       <c r="C457">
-        <v>0.3624980622041154</v>
+        <v>0.3645748676244241</v>
       </c>
       <c r="D457" t="s">
         <v>7</v>
@@ -12112,7 +12112,7 @@
         <v>6</v>
       </c>
       <c r="C458">
-        <v>0.3536023349663245</v>
+        <v>0.3594844704147667</v>
       </c>
       <c r="D458" t="s">
         <v>7</v>
@@ -12129,7 +12129,7 @@
         <v>6</v>
       </c>
       <c r="C459">
-        <v>0.4007336565953506</v>
+        <v>0.4067511184980228</v>
       </c>
       <c r="D459" t="s">
         <v>7</v>
@@ -12146,7 +12146,7 @@
         <v>6</v>
       </c>
       <c r="C460">
-        <v>0.3545024537920187</v>
+        <v>0.3597587044429388</v>
       </c>
       <c r="D460" t="s">
         <v>7</v>
@@ -12163,7 +12163,7 @@
         <v>10</v>
       </c>
       <c r="C461">
-        <v>0.3099913501502077</v>
+        <v>0.3060810710376915</v>
       </c>
       <c r="D461" t="s">
         <v>7</v>
@@ -12180,7 +12180,7 @@
         <v>6</v>
       </c>
       <c r="C462">
-        <v>0.3384865851067231</v>
+        <v>0.3442955372881455</v>
       </c>
       <c r="D462" t="s">
         <v>7</v>
@@ -12197,7 +12197,7 @@
         <v>10</v>
       </c>
       <c r="C463">
-        <v>0.3015419834462581</v>
+        <v>0.2976647035277822</v>
       </c>
       <c r="D463" t="s">
         <v>7</v>
@@ -12214,7 +12214,7 @@
         <v>6</v>
       </c>
       <c r="C464">
-        <v>0.4246555222786241</v>
+        <v>0.4320728280331821</v>
       </c>
       <c r="D464" t="s">
         <v>7</v>
@@ -12231,7 +12231,7 @@
         <v>44</v>
       </c>
       <c r="C465">
-        <v>0.3529578053281249</v>
+        <v>0.3525267466167537</v>
       </c>
       <c r="D465" t="s">
         <v>7</v>
@@ -12248,7 +12248,7 @@
         <v>6</v>
       </c>
       <c r="C466">
-        <v>0.542544008563014</v>
+        <v>0.5490993672664753</v>
       </c>
       <c r="D466" t="s">
         <v>7</v>
@@ -12265,7 +12265,7 @@
         <v>6</v>
       </c>
       <c r="C467">
-        <v>0.4942027841325637</v>
+        <v>0.4993198117769058</v>
       </c>
       <c r="D467" t="s">
         <v>7</v>
@@ -12282,7 +12282,7 @@
         <v>6</v>
       </c>
       <c r="C468">
-        <v>0.3950346489054566</v>
+        <v>0.4013384611867765</v>
       </c>
       <c r="D468" t="s">
         <v>7</v>
@@ -12299,7 +12299,7 @@
         <v>15</v>
       </c>
       <c r="C469">
-        <v>0.2983889476254387</v>
+        <v>0.3009372241005837</v>
       </c>
       <c r="D469" t="s">
         <v>7</v>
@@ -12316,7 +12316,7 @@
         <v>15</v>
       </c>
       <c r="C470">
-        <v>0.3037758010873418</v>
+        <v>0.3061219875564219</v>
       </c>
       <c r="D470" t="s">
         <v>7</v>
@@ -12333,7 +12333,7 @@
         <v>44</v>
       </c>
       <c r="C471">
-        <v>0.3228972402686213</v>
+        <v>0.3219928343149802</v>
       </c>
       <c r="D471" t="s">
         <v>7</v>
@@ -12350,7 +12350,7 @@
         <v>15</v>
       </c>
       <c r="C472">
-        <v>0.3127220280896493</v>
+        <v>0.3151888073756525</v>
       </c>
       <c r="D472" t="s">
         <v>7</v>
@@ -12367,7 +12367,7 @@
         <v>44</v>
       </c>
       <c r="C473">
-        <v>0.3202838469322625</v>
+        <v>0.3201202066452111</v>
       </c>
       <c r="D473" t="s">
         <v>7</v>
@@ -12384,7 +12384,7 @@
         <v>10</v>
       </c>
       <c r="C474">
-        <v>0.3494433483903207</v>
+        <v>0.3462894162097644</v>
       </c>
       <c r="D474" t="s">
         <v>7</v>
@@ -12401,7 +12401,7 @@
         <v>6</v>
       </c>
       <c r="C475">
-        <v>0.3434517949521806</v>
+        <v>0.3496438575996575</v>
       </c>
       <c r="D475" t="s">
         <v>7</v>
@@ -12418,7 +12418,7 @@
         <v>6</v>
       </c>
       <c r="C476">
-        <v>0.337206297584071</v>
+        <v>0.3428834552358128</v>
       </c>
       <c r="D476" t="s">
         <v>7</v>
@@ -12435,7 +12435,7 @@
         <v>10</v>
       </c>
       <c r="C477">
-        <v>0.3270215241099507</v>
+        <v>0.323048849224911</v>
       </c>
       <c r="D477" t="s">
         <v>7</v>
@@ -12452,7 +12452,7 @@
         <v>6</v>
       </c>
       <c r="C478">
-        <v>0.405071732243402</v>
+        <v>0.4098019833550145</v>
       </c>
       <c r="D478" t="s">
         <v>7</v>
@@ -12469,7 +12469,7 @@
         <v>44</v>
       </c>
       <c r="C479">
-        <v>0.4109620591806651</v>
+        <v>0.4103970402236649</v>
       </c>
       <c r="D479" t="s">
         <v>7</v>
@@ -12486,7 +12486,7 @@
         <v>6</v>
       </c>
       <c r="C480">
-        <v>0.4808227091051544</v>
+        <v>0.486092022445386</v>
       </c>
       <c r="D480" t="s">
         <v>7</v>
@@ -12503,7 +12503,7 @@
         <v>44</v>
       </c>
       <c r="C481">
-        <v>0.3686951874359896</v>
+        <v>0.368572774156839</v>
       </c>
       <c r="D481" t="s">
         <v>7</v>
@@ -12517,10 +12517,10 @@
         <v>972</v>
       </c>
       <c r="B482" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C482">
-        <v>0.2709165948126885</v>
+        <v>0.2729357947018041</v>
       </c>
       <c r="D482" t="s">
         <v>7</v>
@@ -12537,7 +12537,7 @@
         <v>10</v>
       </c>
       <c r="C483">
-        <v>0.2993317919729756</v>
+        <v>0.2956875703180566</v>
       </c>
       <c r="D483" t="s">
         <v>7</v>
@@ -12554,7 +12554,7 @@
         <v>44</v>
       </c>
       <c r="C484">
-        <v>0.3676077360374654</v>
+        <v>0.3668432457276088</v>
       </c>
       <c r="D484" t="s">
         <v>7</v>
@@ -12571,7 +12571,7 @@
         <v>15</v>
       </c>
       <c r="C485">
-        <v>0.3683273013909316</v>
+        <v>0.3707803644857839</v>
       </c>
       <c r="D485" t="s">
         <v>7</v>
@@ -12588,7 +12588,7 @@
         <v>15</v>
       </c>
       <c r="C486">
-        <v>0.4035427152113107</v>
+        <v>0.4056535128660276</v>
       </c>
       <c r="D486" t="s">
         <v>7</v>
@@ -12605,7 +12605,7 @@
         <v>44</v>
       </c>
       <c r="C487">
-        <v>0.4379266744042156</v>
+        <v>0.4378168085919965</v>
       </c>
       <c r="D487" t="s">
         <v>7</v>
@@ -12622,7 +12622,7 @@
         <v>10</v>
       </c>
       <c r="C488">
-        <v>0.2826432057992881</v>
+        <v>0.279142195659259</v>
       </c>
       <c r="D488" t="s">
         <v>7</v>
@@ -12639,7 +12639,7 @@
         <v>6</v>
       </c>
       <c r="C489">
-        <v>0.5075651937315832</v>
+        <v>0.5143663148910238</v>
       </c>
       <c r="D489" t="s">
         <v>7</v>
@@ -12656,7 +12656,7 @@
         <v>15</v>
       </c>
       <c r="C490">
-        <v>0.3338428305686082</v>
+        <v>0.336425818773508</v>
       </c>
       <c r="D490" t="s">
         <v>7</v>
@@ -12673,7 +12673,7 @@
         <v>6</v>
       </c>
       <c r="C491">
-        <v>0.2997076834470001</v>
+        <v>0.3053067887332611</v>
       </c>
       <c r="D491" t="s">
         <v>7</v>
@@ -12690,7 +12690,7 @@
         <v>6</v>
       </c>
       <c r="C492">
-        <v>0.4957566264239316</v>
+        <v>0.501867033266777</v>
       </c>
       <c r="D492" t="s">
         <v>7</v>
@@ -12707,7 +12707,7 @@
         <v>6</v>
       </c>
       <c r="C493">
-        <v>0.305747439749195</v>
+        <v>0.311945885317772</v>
       </c>
       <c r="D493" t="s">
         <v>7</v>
@@ -12724,7 +12724,7 @@
         <v>10</v>
       </c>
       <c r="C494">
-        <v>0.3010034441280779</v>
+        <v>0.2980270941299217</v>
       </c>
       <c r="D494" t="s">
         <v>7</v>
@@ -12741,7 +12741,7 @@
         <v>44</v>
       </c>
       <c r="C495">
-        <v>0.5030255975690348</v>
+        <v>0.5030032899208954</v>
       </c>
       <c r="D495" t="s">
         <v>7</v>
@@ -12758,7 +12758,7 @@
         <v>6</v>
       </c>
       <c r="C496">
-        <v>0.5044357580421969</v>
+        <v>0.5089858724634819</v>
       </c>
       <c r="D496" t="s">
         <v>7</v>
@@ -12775,7 +12775,7 @@
         <v>10</v>
       </c>
       <c r="C497">
-        <v>0.3561471966020757</v>
+        <v>0.3527857158034807</v>
       </c>
       <c r="D497" t="s">
         <v>7</v>
@@ -12792,7 +12792,7 @@
         <v>6</v>
       </c>
       <c r="C498">
-        <v>0.6641151591104736</v>
+        <v>0.6695383317942755</v>
       </c>
       <c r="D498" t="s">
         <v>7</v>
@@ -12809,7 +12809,7 @@
         <v>15</v>
       </c>
       <c r="C499">
-        <v>0.3420264589923934</v>
+        <v>0.3446121378870369</v>
       </c>
       <c r="D499" t="s">
         <v>7</v>
@@ -12826,7 +12826,7 @@
         <v>6</v>
       </c>
       <c r="C500">
-        <v>0.4456510712762181</v>
+        <v>0.4514427572057305</v>
       </c>
       <c r="D500" t="s">
         <v>7</v>
@@ -12843,7 +12843,7 @@
         <v>15</v>
       </c>
       <c r="C501">
-        <v>0.4195982987048805</v>
+        <v>0.4217077243969311</v>
       </c>
       <c r="D501" t="s">
         <v>7</v>
@@ -12860,7 +12860,7 @@
         <v>6</v>
       </c>
       <c r="C502">
-        <v>0.5875752046940469</v>
+        <v>0.5918399585207635</v>
       </c>
       <c r="D502" t="s">
         <v>7</v>
@@ -12877,7 +12877,7 @@
         <v>15</v>
       </c>
       <c r="C503">
-        <v>0.3594496959489215</v>
+        <v>0.3619648655297907</v>
       </c>
       <c r="D503" t="s">
         <v>7</v>
@@ -12894,7 +12894,7 @@
         <v>15</v>
       </c>
       <c r="C504">
-        <v>0.3277265957844223</v>
+        <v>0.3301698473845137</v>
       </c>
       <c r="D504" t="s">
         <v>7</v>
@@ -12911,7 +12911,7 @@
         <v>6</v>
       </c>
       <c r="C505">
-        <v>0.4580781695857361</v>
+        <v>0.4633196054288258</v>
       </c>
       <c r="D505" t="s">
         <v>7</v>
@@ -12928,7 +12928,7 @@
         <v>15</v>
       </c>
       <c r="C506">
-        <v>0.4930719869370004</v>
+        <v>0.4949437653422113</v>
       </c>
       <c r="D506" t="s">
         <v>7</v>
@@ -12945,7 +12945,7 @@
         <v>6</v>
       </c>
       <c r="C507">
-        <v>0.3376352302293694</v>
+        <v>0.3436856149775744</v>
       </c>
       <c r="D507" t="s">
         <v>7</v>
@@ -12962,7 +12962,7 @@
         <v>15</v>
       </c>
       <c r="C508">
-        <v>0.3284281027431424</v>
+        <v>0.3305577369364911</v>
       </c>
       <c r="D508" t="s">
         <v>7</v>
@@ -12979,7 +12979,7 @@
         <v>10</v>
       </c>
       <c r="C509">
-        <v>0.4772774711861864</v>
+        <v>0.4738067417067568</v>
       </c>
       <c r="D509" t="s">
         <v>7</v>
@@ -12996,7 +12996,7 @@
         <v>10</v>
       </c>
       <c r="C510">
-        <v>0.3606271061475856</v>
+        <v>0.3567517384182431</v>
       </c>
       <c r="D510" t="s">
         <v>7</v>
@@ -13013,7 +13013,7 @@
         <v>44</v>
       </c>
       <c r="C511">
-        <v>0.3453696411624043</v>
+        <v>0.3439636144449801</v>
       </c>
       <c r="D511" t="s">
         <v>7</v>
@@ -13030,7 +13030,7 @@
         <v>6</v>
       </c>
       <c r="C512">
-        <v>0.3083007206030108</v>
+        <v>0.3135169645387443</v>
       </c>
       <c r="D512" t="s">
         <v>7</v>
@@ -13047,7 +13047,7 @@
         <v>6</v>
       </c>
       <c r="C513">
-        <v>0.3759547259521832</v>
+        <v>0.3820465069050213</v>
       </c>
       <c r="D513" t="s">
         <v>7</v>
@@ -13064,7 +13064,7 @@
         <v>44</v>
       </c>
       <c r="C514">
-        <v>0.3959987156399142</v>
+        <v>0.3948820853399574</v>
       </c>
       <c r="D514" t="s">
         <v>7</v>
@@ -13081,7 +13081,7 @@
         <v>6</v>
       </c>
       <c r="C515">
-        <v>0.5093243738329343</v>
+        <v>0.5163065173556722</v>
       </c>
       <c r="D515" t="s">
         <v>7</v>
@@ -13098,7 +13098,7 @@
         <v>15</v>
       </c>
       <c r="C516">
-        <v>0.3130640474108625</v>
+        <v>0.3155808600342381</v>
       </c>
       <c r="D516" t="s">
         <v>7</v>
@@ -13115,7 +13115,7 @@
         <v>15</v>
       </c>
       <c r="C517">
-        <v>0.3486601615829156</v>
+        <v>0.3511461134944553</v>
       </c>
       <c r="D517" t="s">
         <v>7</v>
@@ -13132,7 +13132,7 @@
         <v>10</v>
       </c>
       <c r="C518">
-        <v>0.3118796817646081</v>
+        <v>0.3083680559609567</v>
       </c>
       <c r="D518" t="s">
         <v>7</v>
@@ -13149,7 +13149,7 @@
         <v>44</v>
       </c>
       <c r="C519">
-        <v>0.5042723888541051</v>
+        <v>0.5044870779999142</v>
       </c>
       <c r="D519" t="s">
         <v>7</v>
@@ -13166,7 +13166,7 @@
         <v>15</v>
       </c>
       <c r="C520">
-        <v>0.3311721517529383</v>
+        <v>0.3335748896183803</v>
       </c>
       <c r="D520" t="s">
         <v>7</v>
@@ -13183,7 +13183,7 @@
         <v>10</v>
       </c>
       <c r="C521">
-        <v>0.3085715968839398</v>
+        <v>0.3051630097965268</v>
       </c>
       <c r="D521" t="s">
         <v>7</v>
@@ -13200,7 +13200,7 @@
         <v>15</v>
       </c>
       <c r="C522">
-        <v>0.3487518278696923</v>
+        <v>0.351134088103789</v>
       </c>
       <c r="D522" t="s">
         <v>7</v>
@@ -13217,7 +13217,7 @@
         <v>6</v>
       </c>
       <c r="C523">
-        <v>0.4521774738487041</v>
+        <v>0.4564942987577268</v>
       </c>
       <c r="D523" t="s">
         <v>7</v>
@@ -13234,7 +13234,7 @@
         <v>6</v>
       </c>
       <c r="C524">
-        <v>0.3050251115314274</v>
+        <v>0.3106424373176639</v>
       </c>
       <c r="D524" t="s">
         <v>7</v>
@@ -13251,7 +13251,7 @@
         <v>44</v>
       </c>
       <c r="C525">
-        <v>0.3897822889160966</v>
+        <v>0.3895854153835558</v>
       </c>
       <c r="D525" t="s">
         <v>7</v>
@@ -13268,7 +13268,7 @@
         <v>44</v>
       </c>
       <c r="C526">
-        <v>0.4932142715392414</v>
+        <v>0.4926813029054473</v>
       </c>
       <c r="D526" t="s">
         <v>7</v>
@@ -13285,7 +13285,7 @@
         <v>10</v>
       </c>
       <c r="C527">
-        <v>0.3864893225464031</v>
+        <v>0.3828934815847183</v>
       </c>
       <c r="D527" t="s">
         <v>7</v>
@@ -13302,7 +13302,7 @@
         <v>6</v>
       </c>
       <c r="C528">
-        <v>0.4576004183460236</v>
+        <v>0.4638222900968532</v>
       </c>
       <c r="D528" t="s">
         <v>7</v>
@@ -13319,7 +13319,7 @@
         <v>10</v>
       </c>
       <c r="C529">
-        <v>0.3215609784122469</v>
+        <v>0.3180985252452098</v>
       </c>
       <c r="D529" t="s">
         <v>7</v>
@@ -13336,7 +13336,7 @@
         <v>44</v>
       </c>
       <c r="C530">
-        <v>0.4983623706272305</v>
+        <v>0.4985454879130852</v>
       </c>
       <c r="D530" t="s">
         <v>7</v>
@@ -13353,7 +13353,7 @@
         <v>44</v>
       </c>
       <c r="C531">
-        <v>0.5286307202732964</v>
+        <v>0.5290168824408702</v>
       </c>
       <c r="D531" t="s">
         <v>7</v>
@@ -13370,7 +13370,7 @@
         <v>10</v>
       </c>
       <c r="C532">
-        <v>0.2778038804523806</v>
+        <v>0.2750165799870084</v>
       </c>
       <c r="D532" t="s">
         <v>7</v>
@@ -13387,7 +13387,7 @@
         <v>15</v>
       </c>
       <c r="C533">
-        <v>0.4838850462707051</v>
+        <v>0.4858357765086512</v>
       </c>
       <c r="D533" t="s">
         <v>7</v>
@@ -13404,7 +13404,7 @@
         <v>15</v>
       </c>
       <c r="C534">
-        <v>0.3321921653170519</v>
+        <v>0.3345964354423055</v>
       </c>
       <c r="D534" t="s">
         <v>7</v>
@@ -13421,7 +13421,7 @@
         <v>6</v>
       </c>
       <c r="C535">
-        <v>0.3195099650166262</v>
+        <v>0.3249625081240264</v>
       </c>
       <c r="D535" t="s">
         <v>7</v>
@@ -13438,7 +13438,7 @@
         <v>6</v>
       </c>
       <c r="C536">
-        <v>0.3212892829272065</v>
+        <v>0.3272526722983137</v>
       </c>
       <c r="D536" t="s">
         <v>7</v>
@@ -13455,7 +13455,7 @@
         <v>6</v>
       </c>
       <c r="C537">
-        <v>0.3938710264174453</v>
+        <v>0.3998050112308191</v>
       </c>
       <c r="D537" t="s">
         <v>7</v>
@@ -13472,7 +13472,7 @@
         <v>15</v>
       </c>
       <c r="C538">
-        <v>0.2909602188089097</v>
+        <v>0.293323083844064</v>
       </c>
       <c r="D538" t="s">
         <v>7</v>
@@ -13489,7 +13489,7 @@
         <v>6</v>
       </c>
       <c r="C539">
-        <v>0.3052957612300293</v>
+        <v>0.3111131217512075</v>
       </c>
       <c r="D539" t="s">
         <v>7</v>
@@ -13506,7 +13506,7 @@
         <v>15</v>
       </c>
       <c r="C540">
-        <v>0.2682805740824088</v>
+        <v>0.2704941391778484</v>
       </c>
       <c r="D540" t="s">
         <v>7</v>
@@ -13523,7 +13523,7 @@
         <v>6</v>
       </c>
       <c r="C541">
-        <v>0.4227015532990956</v>
+        <v>0.4274418418957602</v>
       </c>
       <c r="D541" t="s">
         <v>7</v>
@@ -13540,7 +13540,7 @@
         <v>44</v>
       </c>
       <c r="C542">
-        <v>0.3727070857923098</v>
+        <v>0.3718594706334718</v>
       </c>
       <c r="D542" t="s">
         <v>7</v>
@@ -13557,7 +13557,7 @@
         <v>6</v>
       </c>
       <c r="C543">
-        <v>0.4245315093262037</v>
+        <v>0.4319448756113557</v>
       </c>
       <c r="D543" t="s">
         <v>7</v>
@@ -13574,7 +13574,7 @@
         <v>6</v>
       </c>
       <c r="C544">
-        <v>0.4078635454308713</v>
+        <v>0.4141164910707301</v>
       </c>
       <c r="D544" t="s">
         <v>7</v>
@@ -15379,7 +15379,7 @@
         <v>10</v>
       </c>
       <c r="B3">
-        <v>111</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -15395,7 +15395,7 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>254</v>
+        <v>262</v>
       </c>
     </row>
     <row r="6" spans="1:2">

--- a/frontend/data/uk_election_predictions.xlsx
+++ b/frontend/data/uk_election_predictions.xlsx
@@ -4360,7 +4360,7 @@
         <v>6</v>
       </c>
       <c r="C2">
-        <v>0.3060309584275397</v>
+        <v>0.3177513979729616</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
@@ -4377,7 +4377,7 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>0.3957556692270089</v>
+        <v>0.3822886088806316</v>
       </c>
       <c r="D3" t="s">
         <v>7</v>
@@ -4394,7 +4394,7 @@
         <v>6</v>
       </c>
       <c r="C4">
-        <v>0.4030104674074728</v>
+        <v>0.4137669402890238</v>
       </c>
       <c r="D4" t="s">
         <v>7</v>
@@ -4411,7 +4411,7 @@
         <v>15</v>
       </c>
       <c r="C5">
-        <v>0.3838990466812431</v>
+        <v>0.3850388772697</v>
       </c>
       <c r="D5" t="s">
         <v>7</v>
@@ -4428,7 +4428,7 @@
         <v>10</v>
       </c>
       <c r="C6">
-        <v>0.3752755969253125</v>
+        <v>0.369139315511929</v>
       </c>
       <c r="D6" t="s">
         <v>7</v>
@@ -4445,7 +4445,7 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>0.3231907475654792</v>
+        <v>0.331339904195997</v>
       </c>
       <c r="D7" t="s">
         <v>7</v>
@@ -4462,7 +4462,7 @@
         <v>15</v>
       </c>
       <c r="C8">
-        <v>0.3455262606011146</v>
+        <v>0.3485156812299325</v>
       </c>
       <c r="D8" t="s">
         <v>7</v>
@@ -4479,7 +4479,7 @@
         <v>15</v>
       </c>
       <c r="C9">
-        <v>0.3204416180128751</v>
+        <v>0.3219436675263968</v>
       </c>
       <c r="D9" t="s">
         <v>7</v>
@@ -4496,7 +4496,7 @@
         <v>10</v>
       </c>
       <c r="C10">
-        <v>0.3178487526243371</v>
+        <v>0.3065732495472183</v>
       </c>
       <c r="D10" t="s">
         <v>7</v>
@@ -4513,7 +4513,7 @@
         <v>15</v>
       </c>
       <c r="C11">
-        <v>0.2372055438901787</v>
+        <v>0.2390731334221285</v>
       </c>
       <c r="D11" t="s">
         <v>7</v>
@@ -4530,7 +4530,7 @@
         <v>6</v>
       </c>
       <c r="C12">
-        <v>0.4011389575056979</v>
+        <v>0.4055858717063986</v>
       </c>
       <c r="D12" t="s">
         <v>7</v>
@@ -4547,7 +4547,7 @@
         <v>15</v>
       </c>
       <c r="C13">
-        <v>0.3031744857568566</v>
+        <v>0.3042740836874898</v>
       </c>
       <c r="D13" t="s">
         <v>7</v>
@@ -4564,7 +4564,7 @@
         <v>15</v>
       </c>
       <c r="C14">
-        <v>0.3880295833579075</v>
+        <v>0.3893338233574824</v>
       </c>
       <c r="D14" t="s">
         <v>7</v>
@@ -4581,7 +4581,7 @@
         <v>10</v>
       </c>
       <c r="C15">
-        <v>0.3486478518205304</v>
+        <v>0.3367846366770625</v>
       </c>
       <c r="D15" t="s">
         <v>7</v>
@@ -4598,7 +4598,7 @@
         <v>6</v>
       </c>
       <c r="C16">
-        <v>0.3417171146966719</v>
+        <v>0.3521276997982936</v>
       </c>
       <c r="D16" t="s">
         <v>7</v>
@@ -4615,7 +4615,7 @@
         <v>15</v>
       </c>
       <c r="C17">
-        <v>0.282513605191444</v>
+        <v>0.2848509169148288</v>
       </c>
       <c r="D17" t="s">
         <v>7</v>
@@ -4632,7 +4632,7 @@
         <v>10</v>
       </c>
       <c r="C18">
-        <v>0.3062923276582313</v>
+        <v>0.2954495075615227</v>
       </c>
       <c r="D18" t="s">
         <v>7</v>
@@ -4649,7 +4649,7 @@
         <v>44</v>
       </c>
       <c r="C19">
-        <v>0.4349264065203161</v>
+        <v>0.4266081040175916</v>
       </c>
       <c r="D19" t="s">
         <v>7</v>
@@ -4666,7 +4666,7 @@
         <v>6</v>
       </c>
       <c r="C20">
-        <v>0.4554178588071641</v>
+        <v>0.4685072603721165</v>
       </c>
       <c r="D20" t="s">
         <v>7</v>
@@ -4683,7 +4683,7 @@
         <v>10</v>
       </c>
       <c r="C21">
-        <v>0.3868551572114342</v>
+        <v>0.3834230492516509</v>
       </c>
       <c r="D21" t="s">
         <v>7</v>
@@ -4700,7 +4700,7 @@
         <v>6</v>
       </c>
       <c r="C22">
-        <v>0.3667239870621659</v>
+        <v>0.3779259080982248</v>
       </c>
       <c r="D22" t="s">
         <v>7</v>
@@ -4717,7 +4717,7 @@
         <v>6</v>
       </c>
       <c r="C23">
-        <v>0.4636145169103582</v>
+        <v>0.478089320108933</v>
       </c>
       <c r="D23" t="s">
         <v>7</v>
@@ -4734,7 +4734,7 @@
         <v>6</v>
       </c>
       <c r="C24">
-        <v>0.3484756503290099</v>
+        <v>0.361556768086219</v>
       </c>
       <c r="D24" t="s">
         <v>7</v>
@@ -4751,7 +4751,7 @@
         <v>6</v>
       </c>
       <c r="C25">
-        <v>0.6169287386930266</v>
+        <v>0.6250156488544485</v>
       </c>
       <c r="D25" t="s">
         <v>7</v>
@@ -4768,7 +4768,7 @@
         <v>15</v>
       </c>
       <c r="C26">
-        <v>0.2991613937499235</v>
+        <v>0.3017749185340396</v>
       </c>
       <c r="D26" t="s">
         <v>7</v>
@@ -4785,7 +4785,7 @@
         <v>6</v>
       </c>
       <c r="C27">
-        <v>0.2772926426349963</v>
+        <v>0.2888142944367904</v>
       </c>
       <c r="D27" t="s">
         <v>7</v>
@@ -4802,7 +4802,7 @@
         <v>6</v>
       </c>
       <c r="C28">
-        <v>0.325959105287959</v>
+        <v>0.3395525933544372</v>
       </c>
       <c r="D28" t="s">
         <v>7</v>
@@ -4819,7 +4819,7 @@
         <v>44</v>
       </c>
       <c r="C29">
-        <v>0.4347777777250297</v>
+        <v>0.4280611996691047</v>
       </c>
       <c r="D29" t="s">
         <v>7</v>
@@ -4836,7 +4836,7 @@
         <v>6</v>
       </c>
       <c r="C30">
-        <v>0.3820536567114865</v>
+        <v>0.3897713621363565</v>
       </c>
       <c r="D30" t="s">
         <v>7</v>
@@ -4853,7 +4853,7 @@
         <v>6</v>
       </c>
       <c r="C31">
-        <v>0.4585655804911234</v>
+        <v>0.4667570003921129</v>
       </c>
       <c r="D31" t="s">
         <v>7</v>
@@ -4870,7 +4870,7 @@
         <v>15</v>
       </c>
       <c r="C32">
-        <v>0.4150520994089015</v>
+        <v>0.4150797994520152</v>
       </c>
       <c r="D32" t="s">
         <v>7</v>
@@ -4887,7 +4887,7 @@
         <v>6</v>
       </c>
       <c r="C33">
-        <v>0.4087628301333632</v>
+        <v>0.4166813184098438</v>
       </c>
       <c r="D33" t="s">
         <v>7</v>
@@ -4904,7 +4904,7 @@
         <v>15</v>
       </c>
       <c r="C34">
-        <v>0.3343513143965691</v>
+        <v>0.3339177740814324</v>
       </c>
       <c r="D34" t="s">
         <v>7</v>
@@ -4921,7 +4921,7 @@
         <v>6</v>
       </c>
       <c r="C35">
-        <v>0.4581950768969518</v>
+        <v>0.4645671632420837</v>
       </c>
       <c r="D35" t="s">
         <v>7</v>
@@ -4938,7 +4938,7 @@
         <v>6</v>
       </c>
       <c r="C36">
-        <v>0.2520640415434271</v>
+        <v>0.2610495202782282</v>
       </c>
       <c r="D36" t="s">
         <v>7</v>
@@ -4955,7 +4955,7 @@
         <v>15</v>
       </c>
       <c r="C37">
-        <v>0.3247833370830005</v>
+        <v>0.324733415137741</v>
       </c>
       <c r="D37" t="s">
         <v>7</v>
@@ -4972,7 +4972,7 @@
         <v>6</v>
       </c>
       <c r="C38">
-        <v>0.3468887734947915</v>
+        <v>0.3576997206119941</v>
       </c>
       <c r="D38" t="s">
         <v>7</v>
@@ -4986,10 +4986,10 @@
         <v>84</v>
       </c>
       <c r="B39" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C39">
-        <v>0.3175509996091644</v>
+        <v>0.3268810936023725</v>
       </c>
       <c r="D39" t="s">
         <v>7</v>
@@ -5006,7 +5006,7 @@
         <v>6</v>
       </c>
       <c r="C40">
-        <v>0.4938631157699417</v>
+        <v>0.5044391390868795</v>
       </c>
       <c r="D40" t="s">
         <v>7</v>
@@ -5023,7 +5023,7 @@
         <v>15</v>
       </c>
       <c r="C41">
-        <v>0.2947780220363082</v>
+        <v>0.2953775000898723</v>
       </c>
       <c r="D41" t="s">
         <v>7</v>
@@ -5040,7 +5040,7 @@
         <v>6</v>
       </c>
       <c r="C42">
-        <v>0.5268952148894968</v>
+        <v>0.5329197933876577</v>
       </c>
       <c r="D42" t="s">
         <v>7</v>
@@ -5057,7 +5057,7 @@
         <v>15</v>
       </c>
       <c r="C43">
-        <v>0.4065686124091875</v>
+        <v>0.4099366288116458</v>
       </c>
       <c r="D43" t="s">
         <v>7</v>
@@ -5074,7 +5074,7 @@
         <v>15</v>
       </c>
       <c r="C44">
-        <v>0.4414753387388314</v>
+        <v>0.4414358167626309</v>
       </c>
       <c r="D44" t="s">
         <v>7</v>
@@ -5091,7 +5091,7 @@
         <v>6</v>
       </c>
       <c r="C45">
-        <v>0.416756964843691</v>
+        <v>0.4273475191209967</v>
       </c>
       <c r="D45" t="s">
         <v>7</v>
@@ -5108,7 +5108,7 @@
         <v>6</v>
       </c>
       <c r="C46">
-        <v>0.4070351367661855</v>
+        <v>0.4170379215983832</v>
       </c>
       <c r="D46" t="s">
         <v>7</v>
@@ -5125,7 +5125,7 @@
         <v>15</v>
       </c>
       <c r="C47">
-        <v>0.3008956437630479</v>
+        <v>0.3036730784295011</v>
       </c>
       <c r="D47" t="s">
         <v>7</v>
@@ -5142,7 +5142,7 @@
         <v>15</v>
       </c>
       <c r="C48">
-        <v>0.4207763067518052</v>
+        <v>0.4211371320304504</v>
       </c>
       <c r="D48" t="s">
         <v>7</v>
@@ -5159,7 +5159,7 @@
         <v>15</v>
       </c>
       <c r="C49">
-        <v>0.3306828217545445</v>
+        <v>0.332672869972364</v>
       </c>
       <c r="D49" t="s">
         <v>7</v>
@@ -5176,7 +5176,7 @@
         <v>15</v>
       </c>
       <c r="C50">
-        <v>0.3707510674288791</v>
+        <v>0.3723946640151131</v>
       </c>
       <c r="D50" t="s">
         <v>7</v>
@@ -5193,7 +5193,7 @@
         <v>15</v>
       </c>
       <c r="C51">
-        <v>0.3567057381332023</v>
+        <v>0.3586566036047759</v>
       </c>
       <c r="D51" t="s">
         <v>7</v>
@@ -5210,7 +5210,7 @@
         <v>6</v>
       </c>
       <c r="C52">
-        <v>0.5150335653613047</v>
+        <v>0.5225519150334679</v>
       </c>
       <c r="D52" t="s">
         <v>7</v>
@@ -5227,7 +5227,7 @@
         <v>15</v>
       </c>
       <c r="C53">
-        <v>0.4531665166474279</v>
+        <v>0.4553504960372634</v>
       </c>
       <c r="D53" t="s">
         <v>7</v>
@@ -5244,7 +5244,7 @@
         <v>6</v>
       </c>
       <c r="C54">
-        <v>0.4159676567098612</v>
+        <v>0.429698151116335</v>
       </c>
       <c r="D54" t="s">
         <v>7</v>
@@ -5261,7 +5261,7 @@
         <v>10</v>
       </c>
       <c r="C55">
-        <v>0.2776998290661505</v>
+        <v>0.2674720836440906</v>
       </c>
       <c r="D55" t="s">
         <v>7</v>
@@ -5278,7 +5278,7 @@
         <v>10</v>
       </c>
       <c r="C56">
-        <v>0.3707699901950717</v>
+        <v>0.3588373758523407</v>
       </c>
       <c r="D56" t="s">
         <v>7</v>
@@ -5295,7 +5295,7 @@
         <v>6</v>
       </c>
       <c r="C57">
-        <v>0.5539828770309629</v>
+        <v>0.5630588465036649</v>
       </c>
       <c r="D57" t="s">
         <v>7</v>
@@ -5312,7 +5312,7 @@
         <v>6</v>
       </c>
       <c r="C58">
-        <v>0.3323884840829821</v>
+        <v>0.3405618819979059</v>
       </c>
       <c r="D58" t="s">
         <v>7</v>
@@ -5329,7 +5329,7 @@
         <v>6</v>
       </c>
       <c r="C59">
-        <v>0.3712069502541631</v>
+        <v>0.3770830623050745</v>
       </c>
       <c r="D59" t="s">
         <v>7</v>
@@ -5346,7 +5346,7 @@
         <v>6</v>
       </c>
       <c r="C60">
-        <v>0.3223665613447457</v>
+        <v>0.3335419468111263</v>
       </c>
       <c r="D60" t="s">
         <v>7</v>
@@ -5363,7 +5363,7 @@
         <v>6</v>
       </c>
       <c r="C61">
-        <v>0.38351999584113</v>
+        <v>0.3931710623309639</v>
       </c>
       <c r="D61" t="s">
         <v>7</v>
@@ -5380,7 +5380,7 @@
         <v>10</v>
       </c>
       <c r="C62">
-        <v>0.3555285864604376</v>
+        <v>0.34567084856782</v>
       </c>
       <c r="D62" t="s">
         <v>7</v>
@@ -5397,7 +5397,7 @@
         <v>6</v>
       </c>
       <c r="C63">
-        <v>0.3835274046881488</v>
+        <v>0.3934626543689259</v>
       </c>
       <c r="D63" t="s">
         <v>7</v>
@@ -5414,7 +5414,7 @@
         <v>44</v>
       </c>
       <c r="C64">
-        <v>0.2375773460100436</v>
+        <v>0.2251742171408301</v>
       </c>
       <c r="D64" t="s">
         <v>7</v>
@@ -5428,10 +5428,10 @@
         <v>136</v>
       </c>
       <c r="B65" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C65">
-        <v>0.3057722132204313</v>
+        <v>0.2942482472951895</v>
       </c>
       <c r="D65" t="s">
         <v>7</v>
@@ -5448,7 +5448,7 @@
         <v>15</v>
       </c>
       <c r="C66">
-        <v>0.3253298259184371</v>
+        <v>0.3280505731616938</v>
       </c>
       <c r="D66" t="s">
         <v>7</v>
@@ -5465,7 +5465,7 @@
         <v>15</v>
       </c>
       <c r="C67">
-        <v>0.3448097254675754</v>
+        <v>0.3483205437453036</v>
       </c>
       <c r="D67" t="s">
         <v>7</v>
@@ -5482,7 +5482,7 @@
         <v>6</v>
       </c>
       <c r="C68">
-        <v>0.3249597366443409</v>
+        <v>0.3353712974152576</v>
       </c>
       <c r="D68" t="s">
         <v>7</v>
@@ -5499,7 +5499,7 @@
         <v>145</v>
       </c>
       <c r="C69">
-        <v>0.5044675834685887</v>
+        <v>0.5099338211860865</v>
       </c>
       <c r="D69" t="s">
         <v>7</v>
@@ -5516,7 +5516,7 @@
         <v>145</v>
       </c>
       <c r="C70">
-        <v>0.4581726181570005</v>
+        <v>0.4624613446015777</v>
       </c>
       <c r="D70" t="s">
         <v>7</v>
@@ -5533,7 +5533,7 @@
         <v>6</v>
       </c>
       <c r="C71">
-        <v>0.4932794201000744</v>
+        <v>0.5027631421569684</v>
       </c>
       <c r="D71" t="s">
         <v>7</v>
@@ -5550,7 +5550,7 @@
         <v>6</v>
       </c>
       <c r="C72">
-        <v>0.389010643532808</v>
+        <v>0.4009667907789304</v>
       </c>
       <c r="D72" t="s">
         <v>7</v>
@@ -5567,7 +5567,7 @@
         <v>6</v>
       </c>
       <c r="C73">
-        <v>0.5227529357192899</v>
+        <v>0.5353513871718116</v>
       </c>
       <c r="D73" t="s">
         <v>7</v>
@@ -5584,7 +5584,7 @@
         <v>6</v>
       </c>
       <c r="C74">
-        <v>0.5090842108023957</v>
+        <v>0.5181991891948154</v>
       </c>
       <c r="D74" t="s">
         <v>7</v>
@@ -5601,7 +5601,7 @@
         <v>10</v>
       </c>
       <c r="C75">
-        <v>0.2956894178949458</v>
+        <v>0.2846022320059888</v>
       </c>
       <c r="D75" t="s">
         <v>7</v>
@@ -5618,7 +5618,7 @@
         <v>10</v>
       </c>
       <c r="C76">
-        <v>0.3367479626332665</v>
+        <v>0.3249482004824814</v>
       </c>
       <c r="D76" t="s">
         <v>7</v>
@@ -5635,7 +5635,7 @@
         <v>10</v>
       </c>
       <c r="C77">
-        <v>0.3229656946496388</v>
+        <v>0.3120826786182517</v>
       </c>
       <c r="D77" t="s">
         <v>7</v>
@@ -5652,7 +5652,7 @@
         <v>10</v>
       </c>
       <c r="C78">
-        <v>0.4313887686762239</v>
+        <v>0.4204544375090389</v>
       </c>
       <c r="D78" t="s">
         <v>7</v>
@@ -5666,10 +5666,10 @@
         <v>165</v>
       </c>
       <c r="B79" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C79">
-        <v>0.270154237920041</v>
+        <v>0.2740414878838242</v>
       </c>
       <c r="D79" t="s">
         <v>7</v>
@@ -5686,7 +5686,7 @@
         <v>10</v>
       </c>
       <c r="C80">
-        <v>0.3640193417162574</v>
+        <v>0.3533033205049024</v>
       </c>
       <c r="D80" t="s">
         <v>7</v>
@@ -5703,7 +5703,7 @@
         <v>15</v>
       </c>
       <c r="C81">
-        <v>0.29933853630601</v>
+        <v>0.3005895488572687</v>
       </c>
       <c r="D81" t="s">
         <v>7</v>
@@ -5720,7 +5720,7 @@
         <v>10</v>
       </c>
       <c r="C82">
-        <v>0.4269646138289054</v>
+        <v>0.414837313563022</v>
       </c>
       <c r="D82" t="s">
         <v>7</v>
@@ -5737,7 +5737,7 @@
         <v>6</v>
       </c>
       <c r="C83">
-        <v>0.4117439644091261</v>
+        <v>0.4229069046608408</v>
       </c>
       <c r="D83" t="s">
         <v>7</v>
@@ -5754,7 +5754,7 @@
         <v>15</v>
       </c>
       <c r="C84">
-        <v>0.2917206404748828</v>
+        <v>0.2941939288809385</v>
       </c>
       <c r="D84" t="s">
         <v>7</v>
@@ -5771,7 +5771,7 @@
         <v>15</v>
       </c>
       <c r="C85">
-        <v>0.3032221404275506</v>
+        <v>0.306730940958134</v>
       </c>
       <c r="D85" t="s">
         <v>7</v>
@@ -5788,7 +5788,7 @@
         <v>6</v>
       </c>
       <c r="C86">
-        <v>0.3294248686257662</v>
+        <v>0.3406293251035752</v>
       </c>
       <c r="D86" t="s">
         <v>7</v>
@@ -5805,7 +5805,7 @@
         <v>6</v>
       </c>
       <c r="C87">
-        <v>0.3031815878656347</v>
+        <v>0.3124293931316601</v>
       </c>
       <c r="D87" t="s">
         <v>7</v>
@@ -5819,10 +5819,10 @@
         <v>183</v>
       </c>
       <c r="B88" t="s">
-        <v>145</v>
+        <v>6</v>
       </c>
       <c r="C88">
-        <v>0.282396732303714</v>
+        <v>0.2944485797123317</v>
       </c>
       <c r="D88" t="s">
         <v>7</v>
@@ -5839,7 +5839,7 @@
         <v>6</v>
       </c>
       <c r="C89">
-        <v>0.294104921631926</v>
+        <v>0.3050371186895044</v>
       </c>
       <c r="D89" t="s">
         <v>7</v>
@@ -5856,7 +5856,7 @@
         <v>10</v>
       </c>
       <c r="C90">
-        <v>0.2511079021211545</v>
+        <v>0.2389255510983078</v>
       </c>
       <c r="D90" t="s">
         <v>7</v>
@@ -5873,7 +5873,7 @@
         <v>6</v>
       </c>
       <c r="C91">
-        <v>0.2754941604050063</v>
+        <v>0.2870329309210982</v>
       </c>
       <c r="D91" t="s">
         <v>7</v>
@@ -5887,10 +5887,10 @@
         <v>191</v>
       </c>
       <c r="B92" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="C92">
-        <v>0.2868382116065973</v>
+        <v>0.2846769468156784</v>
       </c>
       <c r="D92" t="s">
         <v>7</v>
@@ -5907,7 +5907,7 @@
         <v>15</v>
       </c>
       <c r="C93">
-        <v>0.3639209521356697</v>
+        <v>0.3662967803745927</v>
       </c>
       <c r="D93" t="s">
         <v>7</v>
@@ -5924,7 +5924,7 @@
         <v>6</v>
       </c>
       <c r="C94">
-        <v>0.3087462667177674</v>
+        <v>0.32130490892417</v>
       </c>
       <c r="D94" t="s">
         <v>7</v>
@@ -5941,7 +5941,7 @@
         <v>15</v>
       </c>
       <c r="C95">
-        <v>0.3252812573717014</v>
+        <v>0.3283365869324532</v>
       </c>
       <c r="D95" t="s">
         <v>7</v>
@@ -5958,7 +5958,7 @@
         <v>15</v>
       </c>
       <c r="C96">
-        <v>0.3382356908072282</v>
+        <v>0.3381753039610108</v>
       </c>
       <c r="D96" t="s">
         <v>7</v>
@@ -5975,7 +5975,7 @@
         <v>44</v>
       </c>
       <c r="C97">
-        <v>0.3305678687056897</v>
+        <v>0.3192041741053191</v>
       </c>
       <c r="D97" t="s">
         <v>7</v>
@@ -5992,7 +5992,7 @@
         <v>44</v>
       </c>
       <c r="C98">
-        <v>0.3276376859957902</v>
+        <v>0.3169082187984161</v>
       </c>
       <c r="D98" t="s">
         <v>7</v>
@@ -6009,7 +6009,7 @@
         <v>6</v>
       </c>
       <c r="C99">
-        <v>0.4541313481577624</v>
+        <v>0.4684943365759415</v>
       </c>
       <c r="D99" t="s">
         <v>7</v>
@@ -6026,7 +6026,7 @@
         <v>44</v>
       </c>
       <c r="C100">
-        <v>0.395449429937289</v>
+        <v>0.3883177966375701</v>
       </c>
       <c r="D100" t="s">
         <v>7</v>
@@ -6043,7 +6043,7 @@
         <v>44</v>
       </c>
       <c r="C101">
-        <v>0.3828025310366773</v>
+        <v>0.3765801580972891</v>
       </c>
       <c r="D101" t="s">
         <v>7</v>
@@ -6060,7 +6060,7 @@
         <v>6</v>
       </c>
       <c r="C102">
-        <v>0.482969791571925</v>
+        <v>0.4943945950765775</v>
       </c>
       <c r="D102" t="s">
         <v>7</v>
@@ -6077,7 +6077,7 @@
         <v>6</v>
       </c>
       <c r="C103">
-        <v>0.3631762227304923</v>
+        <v>0.3737724968675789</v>
       </c>
       <c r="D103" t="s">
         <v>7</v>
@@ -6094,7 +6094,7 @@
         <v>15</v>
       </c>
       <c r="C104">
-        <v>0.3845834002554279</v>
+        <v>0.3867741018758274</v>
       </c>
       <c r="D104" t="s">
         <v>7</v>
@@ -6111,7 +6111,7 @@
         <v>44</v>
       </c>
       <c r="C105">
-        <v>0.3245703724110675</v>
+        <v>0.3148237138688294</v>
       </c>
       <c r="D105" t="s">
         <v>7</v>
@@ -6128,7 +6128,7 @@
         <v>10</v>
       </c>
       <c r="C106">
-        <v>0.3860873413174603</v>
+        <v>0.376287075335497</v>
       </c>
       <c r="D106" t="s">
         <v>7</v>
@@ -6145,7 +6145,7 @@
         <v>44</v>
       </c>
       <c r="C107">
-        <v>0.3174397436809532</v>
+        <v>0.3096826262045743</v>
       </c>
       <c r="D107" t="s">
         <v>7</v>
@@ -6162,7 +6162,7 @@
         <v>6</v>
       </c>
       <c r="C108">
-        <v>0.402746885651706</v>
+        <v>0.4140143513231161</v>
       </c>
       <c r="D108" t="s">
         <v>7</v>
@@ -6196,7 +6196,7 @@
         <v>15</v>
       </c>
       <c r="C110">
-        <v>0.3008681905351897</v>
+        <v>0.303822970275554</v>
       </c>
       <c r="D110" t="s">
         <v>7</v>
@@ -6213,7 +6213,7 @@
         <v>6</v>
       </c>
       <c r="C111">
-        <v>0.4972155201343991</v>
+        <v>0.5115797017547364</v>
       </c>
       <c r="D111" t="s">
         <v>7</v>
@@ -6230,7 +6230,7 @@
         <v>6</v>
       </c>
       <c r="C112">
-        <v>0.405655010241315</v>
+        <v>0.4175684350127324</v>
       </c>
       <c r="D112" t="s">
         <v>7</v>
@@ -6247,7 +6247,7 @@
         <v>15</v>
       </c>
       <c r="C113">
-        <v>0.5005576013108168</v>
+        <v>0.5003901328474587</v>
       </c>
       <c r="D113" t="s">
         <v>7</v>
@@ -6264,7 +6264,7 @@
         <v>6</v>
       </c>
       <c r="C114">
-        <v>0.6336033546599277</v>
+        <v>0.6421153357630042</v>
       </c>
       <c r="D114" t="s">
         <v>7</v>
@@ -6281,7 +6281,7 @@
         <v>6</v>
       </c>
       <c r="C115">
-        <v>0.2974879192974573</v>
+        <v>0.3092666554854256</v>
       </c>
       <c r="D115" t="s">
         <v>7</v>
@@ -6298,7 +6298,7 @@
         <v>6</v>
       </c>
       <c r="C116">
-        <v>0.423568825437536</v>
+        <v>0.4348713223213781</v>
       </c>
       <c r="D116" t="s">
         <v>7</v>
@@ -6315,7 +6315,7 @@
         <v>10</v>
       </c>
       <c r="C117">
-        <v>0.2971856148577491</v>
+        <v>0.2875513573273098</v>
       </c>
       <c r="D117" t="s">
         <v>7</v>
@@ -6332,7 +6332,7 @@
         <v>10</v>
       </c>
       <c r="C118">
-        <v>0.3527694761004676</v>
+        <v>0.3382072798096959</v>
       </c>
       <c r="D118" t="s">
         <v>7</v>
@@ -6349,7 +6349,7 @@
         <v>6</v>
       </c>
       <c r="C119">
-        <v>0.3039966159201843</v>
+        <v>0.3107844297630665</v>
       </c>
       <c r="D119" t="s">
         <v>7</v>
@@ -6366,7 +6366,7 @@
         <v>10</v>
       </c>
       <c r="C120">
-        <v>0.3697162949817061</v>
+        <v>0.3572798416672965</v>
       </c>
       <c r="D120" t="s">
         <v>7</v>
@@ -6383,7 +6383,7 @@
         <v>226</v>
       </c>
       <c r="C121">
-        <v>0.399880578695231</v>
+        <v>0.4048284965792949</v>
       </c>
       <c r="D121" t="s">
         <v>7</v>
@@ -6400,7 +6400,7 @@
         <v>15</v>
       </c>
       <c r="C122">
-        <v>0.3027050333461117</v>
+        <v>0.3046279190528884</v>
       </c>
       <c r="D122" t="s">
         <v>7</v>
@@ -6417,7 +6417,7 @@
         <v>15</v>
       </c>
       <c r="C123">
-        <v>0.2824930083861395</v>
+        <v>0.2845936181567129</v>
       </c>
       <c r="D123" t="s">
         <v>7</v>
@@ -6434,7 +6434,7 @@
         <v>15</v>
       </c>
       <c r="C124">
-        <v>0.4071060299989792</v>
+        <v>0.4082541664942054</v>
       </c>
       <c r="D124" t="s">
         <v>7</v>
@@ -6451,7 +6451,7 @@
         <v>6</v>
       </c>
       <c r="C125">
-        <v>0.2844688904006356</v>
+        <v>0.2959417105482513</v>
       </c>
       <c r="D125" t="s">
         <v>7</v>
@@ -6465,10 +6465,10 @@
         <v>260</v>
       </c>
       <c r="B126" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C126">
-        <v>0.3401837502560929</v>
+        <v>0.3386205879591305</v>
       </c>
       <c r="D126" t="s">
         <v>7</v>
@@ -6485,7 +6485,7 @@
         <v>6</v>
       </c>
       <c r="C127">
-        <v>0.4988200563513577</v>
+        <v>0.5113549568973127</v>
       </c>
       <c r="D127" t="s">
         <v>7</v>
@@ -6502,7 +6502,7 @@
         <v>15</v>
       </c>
       <c r="C128">
-        <v>0.4306230764915597</v>
+        <v>0.4290813396586111</v>
       </c>
       <c r="D128" t="s">
         <v>7</v>
@@ -6519,7 +6519,7 @@
         <v>15</v>
       </c>
       <c r="C129">
-        <v>0.3054608467497341</v>
+        <v>0.3055911094442256</v>
       </c>
       <c r="D129" t="s">
         <v>7</v>
@@ -6536,7 +6536,7 @@
         <v>15</v>
       </c>
       <c r="C130">
-        <v>0.3825930486347683</v>
+        <v>0.3828352180975345</v>
       </c>
       <c r="D130" t="s">
         <v>7</v>
@@ -6553,7 +6553,7 @@
         <v>10</v>
       </c>
       <c r="C131">
-        <v>0.2888172384237931</v>
+        <v>0.2770284333725027</v>
       </c>
       <c r="D131" t="s">
         <v>7</v>
@@ -6570,7 +6570,7 @@
         <v>6</v>
       </c>
       <c r="C132">
-        <v>0.3890378069861455</v>
+        <v>0.4021724122612851</v>
       </c>
       <c r="D132" t="s">
         <v>7</v>
@@ -6587,7 +6587,7 @@
         <v>15</v>
       </c>
       <c r="C133">
-        <v>0.334266920510691</v>
+        <v>0.3364521188805053</v>
       </c>
       <c r="D133" t="s">
         <v>7</v>
@@ -6604,7 +6604,7 @@
         <v>6</v>
       </c>
       <c r="C134">
-        <v>0.3766801802996115</v>
+        <v>0.3914624631820178</v>
       </c>
       <c r="D134" t="s">
         <v>7</v>
@@ -6621,7 +6621,7 @@
         <v>6</v>
       </c>
       <c r="C135">
-        <v>0.4009608455977919</v>
+        <v>0.4114796982456557</v>
       </c>
       <c r="D135" t="s">
         <v>7</v>
@@ -6638,7 +6638,7 @@
         <v>44</v>
       </c>
       <c r="C136">
-        <v>0.3291097762416505</v>
+        <v>0.3166184396374957</v>
       </c>
       <c r="D136" t="s">
         <v>7</v>
@@ -6655,7 +6655,7 @@
         <v>6</v>
       </c>
       <c r="C137">
-        <v>0.3888999312564402</v>
+        <v>0.3980871829605155</v>
       </c>
       <c r="D137" t="s">
         <v>7</v>
@@ -6672,7 +6672,7 @@
         <v>6</v>
       </c>
       <c r="C138">
-        <v>0.3206937686042245</v>
+        <v>0.3320418601882254</v>
       </c>
       <c r="D138" t="s">
         <v>7</v>
@@ -6689,7 +6689,7 @@
         <v>6</v>
       </c>
       <c r="C139">
-        <v>0.4082679517336641</v>
+        <v>0.4182490808040034</v>
       </c>
       <c r="D139" t="s">
         <v>7</v>
@@ -6706,7 +6706,7 @@
         <v>44</v>
       </c>
       <c r="C140">
-        <v>0.3961174753635202</v>
+        <v>0.3906918434655675</v>
       </c>
       <c r="D140" t="s">
         <v>7</v>
@@ -6723,7 +6723,7 @@
         <v>6</v>
       </c>
       <c r="C141">
-        <v>0.3278167103440045</v>
+        <v>0.3394030309081547</v>
       </c>
       <c r="D141" t="s">
         <v>7</v>
@@ -6740,7 +6740,7 @@
         <v>10</v>
       </c>
       <c r="C142">
-        <v>0.3893300734409071</v>
+        <v>0.3818599159088267</v>
       </c>
       <c r="D142" t="s">
         <v>7</v>
@@ -6757,7 +6757,7 @@
         <v>6</v>
       </c>
       <c r="C143">
-        <v>0.3646819150123399</v>
+        <v>0.3744531260966947</v>
       </c>
       <c r="D143" t="s">
         <v>7</v>
@@ -6774,7 +6774,7 @@
         <v>6</v>
       </c>
       <c r="C144">
-        <v>0.6098237967893969</v>
+        <v>0.6177557817988265</v>
       </c>
       <c r="D144" t="s">
         <v>7</v>
@@ -6791,7 +6791,7 @@
         <v>6</v>
       </c>
       <c r="C145">
-        <v>0.2978221665932609</v>
+        <v>0.3085202191613176</v>
       </c>
       <c r="D145" t="s">
         <v>7</v>
@@ -6808,7 +6808,7 @@
         <v>6</v>
       </c>
       <c r="C146">
-        <v>0.4142142555885948</v>
+        <v>0.4254187313468136</v>
       </c>
       <c r="D146" t="s">
         <v>7</v>
@@ -6825,7 +6825,7 @@
         <v>6</v>
       </c>
       <c r="C147">
-        <v>0.4623674361292716</v>
+        <v>0.4739806979672494</v>
       </c>
       <c r="D147" t="s">
         <v>7</v>
@@ -6842,7 +6842,7 @@
         <v>6</v>
       </c>
       <c r="C148">
-        <v>0.305624885873213</v>
+        <v>0.3168482097594877</v>
       </c>
       <c r="D148" t="s">
         <v>7</v>
@@ -6859,7 +6859,7 @@
         <v>10</v>
       </c>
       <c r="C149">
-        <v>0.3874278895491353</v>
+        <v>0.3773518676769389</v>
       </c>
       <c r="D149" t="s">
         <v>7</v>
@@ -6876,7 +6876,7 @@
         <v>6</v>
       </c>
       <c r="C150">
-        <v>0.3636534847960338</v>
+        <v>0.3719862901818265</v>
       </c>
       <c r="D150" t="s">
         <v>7</v>
@@ -6893,7 +6893,7 @@
         <v>10</v>
       </c>
       <c r="C151">
-        <v>0.2624286390941708</v>
+        <v>0.2513699073921489</v>
       </c>
       <c r="D151" t="s">
         <v>7</v>
@@ -6910,7 +6910,7 @@
         <v>6</v>
       </c>
       <c r="C152">
-        <v>0.6746825626293217</v>
+        <v>0.6822032151879841</v>
       </c>
       <c r="D152" t="s">
         <v>7</v>
@@ -6927,7 +6927,7 @@
         <v>10</v>
       </c>
       <c r="C153">
-        <v>0.3276255260762391</v>
+        <v>0.3219643299205065</v>
       </c>
       <c r="D153" t="s">
         <v>7</v>
@@ -6944,7 +6944,7 @@
         <v>44</v>
       </c>
       <c r="C154">
-        <v>0.325430706481897</v>
+        <v>0.3157355539161525</v>
       </c>
       <c r="D154" t="s">
         <v>7</v>
@@ -6961,7 +6961,7 @@
         <v>6</v>
       </c>
       <c r="C155">
-        <v>0.3062276111644893</v>
+        <v>0.3158143589548416</v>
       </c>
       <c r="D155" t="s">
         <v>7</v>
@@ -6978,7 +6978,7 @@
         <v>10</v>
       </c>
       <c r="C156">
-        <v>0.3360404049357503</v>
+        <v>0.3272434704953649</v>
       </c>
       <c r="D156" t="s">
         <v>7</v>
@@ -6995,7 +6995,7 @@
         <v>6</v>
       </c>
       <c r="C157">
-        <v>0.3961316452093933</v>
+        <v>0.4072142892427044</v>
       </c>
       <c r="D157" t="s">
         <v>7</v>
@@ -7012,7 +7012,7 @@
         <v>44</v>
       </c>
       <c r="C158">
-        <v>0.3706646084995573</v>
+        <v>0.3601013160075043</v>
       </c>
       <c r="D158" t="s">
         <v>7</v>
@@ -7029,7 +7029,7 @@
         <v>44</v>
       </c>
       <c r="C159">
-        <v>0.3762856813571452</v>
+        <v>0.3650535693323411</v>
       </c>
       <c r="D159" t="s">
         <v>7</v>
@@ -7046,7 +7046,7 @@
         <v>6</v>
       </c>
       <c r="C160">
-        <v>0.384222619614028</v>
+        <v>0.3949632887230734</v>
       </c>
       <c r="D160" t="s">
         <v>7</v>
@@ -7063,7 +7063,7 @@
         <v>6</v>
       </c>
       <c r="C161">
-        <v>0.4212809318090024</v>
+        <v>0.4329949319204694</v>
       </c>
       <c r="D161" t="s">
         <v>7</v>
@@ -7080,7 +7080,7 @@
         <v>6</v>
       </c>
       <c r="C162">
-        <v>0.4791642629521437</v>
+        <v>0.4897276408028025</v>
       </c>
       <c r="D162" t="s">
         <v>7</v>
@@ -7097,7 +7097,7 @@
         <v>44</v>
       </c>
       <c r="C163">
-        <v>0.4367674395103602</v>
+        <v>0.4262015870734005</v>
       </c>
       <c r="D163" t="s">
         <v>7</v>
@@ -7114,7 +7114,7 @@
         <v>10</v>
       </c>
       <c r="C164">
-        <v>0.3468184636066912</v>
+        <v>0.3331506870166411</v>
       </c>
       <c r="D164" t="s">
         <v>7</v>
@@ -7131,7 +7131,7 @@
         <v>10</v>
       </c>
       <c r="C165">
-        <v>0.3966200508436361</v>
+        <v>0.3836779244800037</v>
       </c>
       <c r="D165" t="s">
         <v>7</v>
@@ -7148,7 +7148,7 @@
         <v>10</v>
       </c>
       <c r="C166">
-        <v>0.2949169890103672</v>
+        <v>0.2877130334392995</v>
       </c>
       <c r="D166" t="s">
         <v>7</v>
@@ -7165,7 +7165,7 @@
         <v>6</v>
       </c>
       <c r="C167">
-        <v>0.3649751222663535</v>
+        <v>0.3764108886808609</v>
       </c>
       <c r="D167" t="s">
         <v>7</v>
@@ -7182,7 +7182,7 @@
         <v>6</v>
       </c>
       <c r="C168">
-        <v>0.6067376617554322</v>
+        <v>0.6177969729671817</v>
       </c>
       <c r="D168" t="s">
         <v>7</v>
@@ -7199,7 +7199,7 @@
         <v>44</v>
       </c>
       <c r="C169">
-        <v>0.3235648468642274</v>
+        <v>0.3153492975298122</v>
       </c>
       <c r="D169" t="s">
         <v>7</v>
@@ -7216,7 +7216,7 @@
         <v>6</v>
       </c>
       <c r="C170">
-        <v>0.3877323272982944</v>
+        <v>0.401317873824064</v>
       </c>
       <c r="D170" t="s">
         <v>7</v>
@@ -7233,7 +7233,7 @@
         <v>6</v>
       </c>
       <c r="C171">
-        <v>0.2604460445775562</v>
+        <v>0.2724642343405217</v>
       </c>
       <c r="D171" t="s">
         <v>7</v>
@@ -7250,7 +7250,7 @@
         <v>15</v>
       </c>
       <c r="C172">
-        <v>0.4087579181999978</v>
+        <v>0.415866582904903</v>
       </c>
       <c r="D172" t="s">
         <v>7</v>
@@ -7267,7 +7267,7 @@
         <v>44</v>
       </c>
       <c r="C173">
-        <v>0.3142888641016721</v>
+        <v>0.3035205145367715</v>
       </c>
       <c r="D173" t="s">
         <v>7</v>
@@ -7284,7 +7284,7 @@
         <v>6</v>
       </c>
       <c r="C174">
-        <v>0.312472452168804</v>
+        <v>0.3245760785718852</v>
       </c>
       <c r="D174" t="s">
         <v>7</v>
@@ -7301,7 +7301,7 @@
         <v>15</v>
       </c>
       <c r="C175">
-        <v>0.3013773191346147</v>
+        <v>0.303135478480608</v>
       </c>
       <c r="D175" t="s">
         <v>7</v>
@@ -7318,7 +7318,7 @@
         <v>6</v>
       </c>
       <c r="C176">
-        <v>0.4173452547585265</v>
+        <v>0.4307307974385401</v>
       </c>
       <c r="D176" t="s">
         <v>7</v>
@@ -7335,7 +7335,7 @@
         <v>6</v>
       </c>
       <c r="C177">
-        <v>0.5133345583611484</v>
+        <v>0.5271747731254864</v>
       </c>
       <c r="D177" t="s">
         <v>7</v>
@@ -7352,7 +7352,7 @@
         <v>15</v>
       </c>
       <c r="C178">
-        <v>0.4012495895474747</v>
+        <v>0.4016327007184258</v>
       </c>
       <c r="D178" t="s">
         <v>7</v>
@@ -7369,7 +7369,7 @@
         <v>15</v>
       </c>
       <c r="C179">
-        <v>0.3074359373757005</v>
+        <v>0.3095684621960773</v>
       </c>
       <c r="D179" t="s">
         <v>7</v>
@@ -7386,7 +7386,7 @@
         <v>44</v>
       </c>
       <c r="C180">
-        <v>0.3338581484546305</v>
+        <v>0.3224676143293874</v>
       </c>
       <c r="D180" t="s">
         <v>7</v>
@@ -7403,7 +7403,7 @@
         <v>6</v>
       </c>
       <c r="C181">
-        <v>0.3289056709976607</v>
+        <v>0.3405057323282793</v>
       </c>
       <c r="D181" t="s">
         <v>7</v>
@@ -7417,10 +7417,10 @@
         <v>372</v>
       </c>
       <c r="B182" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C182">
-        <v>0.2876880646307309</v>
+        <v>0.2810305532600089</v>
       </c>
       <c r="D182" t="s">
         <v>7</v>
@@ -7437,7 +7437,7 @@
         <v>6</v>
       </c>
       <c r="C183">
-        <v>0.316284639358597</v>
+        <v>0.326870159390351</v>
       </c>
       <c r="D183" t="s">
         <v>7</v>
@@ -7454,7 +7454,7 @@
         <v>6</v>
       </c>
       <c r="C184">
-        <v>0.3577086741564074</v>
+        <v>0.3694114175357649</v>
       </c>
       <c r="D184" t="s">
         <v>7</v>
@@ -7468,10 +7468,10 @@
         <v>378</v>
       </c>
       <c r="B185" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C185">
-        <v>0.3509228344916561</v>
+        <v>0.3367474205751546</v>
       </c>
       <c r="D185" t="s">
         <v>7</v>
@@ -7488,7 +7488,7 @@
         <v>44</v>
       </c>
       <c r="C186">
-        <v>0.3896994534361884</v>
+        <v>0.3802798823873389</v>
       </c>
       <c r="D186" t="s">
         <v>7</v>
@@ -7505,7 +7505,7 @@
         <v>15</v>
       </c>
       <c r="C187">
-        <v>0.2439290897721322</v>
+        <v>0.2461859225994922</v>
       </c>
       <c r="D187" t="s">
         <v>7</v>
@@ -7522,7 +7522,7 @@
         <v>44</v>
       </c>
       <c r="C188">
-        <v>0.3831918509439612</v>
+        <v>0.3780185907557829</v>
       </c>
       <c r="D188" t="s">
         <v>7</v>
@@ -7539,7 +7539,7 @@
         <v>6</v>
       </c>
       <c r="C189">
-        <v>0.3354155950937601</v>
+        <v>0.3475952887549523</v>
       </c>
       <c r="D189" t="s">
         <v>7</v>
@@ -7556,7 +7556,7 @@
         <v>6</v>
       </c>
       <c r="C190">
-        <v>0.312356644899441</v>
+        <v>0.3180228111410904</v>
       </c>
       <c r="D190" t="s">
         <v>7</v>
@@ -7573,7 +7573,7 @@
         <v>10</v>
       </c>
       <c r="C191">
-        <v>0.3208483650316469</v>
+        <v>0.309428755408372</v>
       </c>
       <c r="D191" t="s">
         <v>7</v>
@@ -7590,7 +7590,7 @@
         <v>15</v>
       </c>
       <c r="C192">
-        <v>0.4021949580633546</v>
+        <v>0.4057802189475063</v>
       </c>
       <c r="D192" t="s">
         <v>7</v>
@@ -7607,7 +7607,7 @@
         <v>15</v>
       </c>
       <c r="C193">
-        <v>0.4288410233187454</v>
+        <v>0.4285209953712673</v>
       </c>
       <c r="D193" t="s">
         <v>7</v>
@@ -7624,7 +7624,7 @@
         <v>15</v>
       </c>
       <c r="C194">
-        <v>0.3690759847520541</v>
+        <v>0.3686609637516772</v>
       </c>
       <c r="D194" t="s">
         <v>7</v>
@@ -7641,7 +7641,7 @@
         <v>226</v>
       </c>
       <c r="C195">
-        <v>0.489447647821338</v>
+        <v>0.4940064828599474</v>
       </c>
       <c r="D195" t="s">
         <v>7</v>
@@ -7658,7 +7658,7 @@
         <v>6</v>
       </c>
       <c r="C196">
-        <v>0.3805493599211855</v>
+        <v>0.3918014892957586</v>
       </c>
       <c r="D196" t="s">
         <v>7</v>
@@ -7675,7 +7675,7 @@
         <v>10</v>
       </c>
       <c r="C197">
-        <v>0.3011530385429229</v>
+        <v>0.2917913163421734</v>
       </c>
       <c r="D197" t="s">
         <v>7</v>
@@ -7692,7 +7692,7 @@
         <v>6</v>
       </c>
       <c r="C198">
-        <v>0.52126385275278</v>
+        <v>0.5256327350992031</v>
       </c>
       <c r="D198" t="s">
         <v>7</v>
@@ -7709,7 +7709,7 @@
         <v>6</v>
       </c>
       <c r="C199">
-        <v>0.6043219680366082</v>
+        <v>0.6115906448939207</v>
       </c>
       <c r="D199" t="s">
         <v>7</v>
@@ -7726,7 +7726,7 @@
         <v>15</v>
       </c>
       <c r="C200">
-        <v>0.3231213950474332</v>
+        <v>0.3253947992303289</v>
       </c>
       <c r="D200" t="s">
         <v>7</v>
@@ -7743,7 +7743,7 @@
         <v>15</v>
       </c>
       <c r="C201">
-        <v>0.3150268093184416</v>
+        <v>0.3164486756910976</v>
       </c>
       <c r="D201" t="s">
         <v>7</v>
@@ -7760,7 +7760,7 @@
         <v>10</v>
       </c>
       <c r="C202">
-        <v>0.3413596981322196</v>
+        <v>0.3314031218730466</v>
       </c>
       <c r="D202" t="s">
         <v>7</v>
@@ -7777,7 +7777,7 @@
         <v>6</v>
       </c>
       <c r="C203">
-        <v>0.5453988276229358</v>
+        <v>0.5569423179388862</v>
       </c>
       <c r="D203" t="s">
         <v>7</v>
@@ -7794,7 +7794,7 @@
         <v>6</v>
       </c>
       <c r="C204">
-        <v>0.4836161525443174</v>
+        <v>0.4940017422872954</v>
       </c>
       <c r="D204" t="s">
         <v>7</v>
@@ -7811,7 +7811,7 @@
         <v>10</v>
       </c>
       <c r="C205">
-        <v>0.4264429686502</v>
+        <v>0.4193690743303607</v>
       </c>
       <c r="D205" t="s">
         <v>7</v>
@@ -7828,7 +7828,7 @@
         <v>15</v>
       </c>
       <c r="C206">
-        <v>0.3510537013660929</v>
+        <v>0.3529230057255753</v>
       </c>
       <c r="D206" t="s">
         <v>7</v>
@@ -7845,7 +7845,7 @@
         <v>44</v>
       </c>
       <c r="C207">
-        <v>0.5337628968295718</v>
+        <v>0.5282577329304537</v>
       </c>
       <c r="D207" t="s">
         <v>7</v>
@@ -7862,7 +7862,7 @@
         <v>44</v>
       </c>
       <c r="C208">
-        <v>0.3635545537221573</v>
+        <v>0.3572759760765802</v>
       </c>
       <c r="D208" t="s">
         <v>7</v>
@@ -7879,7 +7879,7 @@
         <v>10</v>
       </c>
       <c r="C209">
-        <v>0.5339411286017559</v>
+        <v>0.5259310527921848</v>
       </c>
       <c r="D209" t="s">
         <v>7</v>
@@ -7896,7 +7896,7 @@
         <v>6</v>
       </c>
       <c r="C210">
-        <v>0.4322784645104548</v>
+        <v>0.4466958233959494</v>
       </c>
       <c r="D210" t="s">
         <v>7</v>
@@ -7913,7 +7913,7 @@
         <v>15</v>
       </c>
       <c r="C211">
-        <v>0.4714194753912632</v>
+        <v>0.4714768015058112</v>
       </c>
       <c r="D211" t="s">
         <v>7</v>
@@ -7930,7 +7930,7 @@
         <v>15</v>
       </c>
       <c r="C212">
-        <v>0.2889622851475213</v>
+        <v>0.2917362467853614</v>
       </c>
       <c r="D212" t="s">
         <v>7</v>
@@ -7947,7 +7947,7 @@
         <v>15</v>
       </c>
       <c r="C213">
-        <v>0.3108304323310289</v>
+        <v>0.3133788435937771</v>
       </c>
       <c r="D213" t="s">
         <v>7</v>
@@ -7964,7 +7964,7 @@
         <v>15</v>
       </c>
       <c r="C214">
-        <v>0.3776539389672126</v>
+        <v>0.3781438197087224</v>
       </c>
       <c r="D214" t="s">
         <v>7</v>
@@ -7981,7 +7981,7 @@
         <v>10</v>
       </c>
       <c r="C215">
-        <v>0.5076527304590179</v>
+        <v>0.495149041724007</v>
       </c>
       <c r="D215" t="s">
         <v>7</v>
@@ -7998,7 +7998,7 @@
         <v>15</v>
       </c>
       <c r="C216">
-        <v>0.3334192410131651</v>
+        <v>0.338315915425655</v>
       </c>
       <c r="D216" t="s">
         <v>7</v>
@@ -8012,10 +8012,10 @@
         <v>442</v>
       </c>
       <c r="B217" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C217">
-        <v>0.2979445272096424</v>
+        <v>0.2930836282664133</v>
       </c>
       <c r="D217" t="s">
         <v>7</v>
@@ -8032,7 +8032,7 @@
         <v>6</v>
       </c>
       <c r="C218">
-        <v>0.3452761211705379</v>
+        <v>0.3587380409352858</v>
       </c>
       <c r="D218" t="s">
         <v>7</v>
@@ -8049,7 +8049,7 @@
         <v>44</v>
       </c>
       <c r="C219">
-        <v>0.475823819747024</v>
+        <v>0.4726411646955317</v>
       </c>
       <c r="D219" t="s">
         <v>7</v>
@@ -8066,7 +8066,7 @@
         <v>15</v>
       </c>
       <c r="C220">
-        <v>0.3027993908223574</v>
+        <v>0.3058139042412027</v>
       </c>
       <c r="D220" t="s">
         <v>7</v>
@@ -8083,7 +8083,7 @@
         <v>15</v>
       </c>
       <c r="C221">
-        <v>0.379252803068657</v>
+        <v>0.3823375173213545</v>
       </c>
       <c r="D221" t="s">
         <v>7</v>
@@ -8100,7 +8100,7 @@
         <v>6</v>
       </c>
       <c r="C222">
-        <v>0.307365002291224</v>
+        <v>0.3202899837374809</v>
       </c>
       <c r="D222" t="s">
         <v>7</v>
@@ -8117,7 +8117,7 @@
         <v>10</v>
       </c>
       <c r="C223">
-        <v>0.4736986655938657</v>
+        <v>0.4647425536398484</v>
       </c>
       <c r="D223" t="s">
         <v>7</v>
@@ -8134,7 +8134,7 @@
         <v>10</v>
       </c>
       <c r="C224">
-        <v>0.2906639522398441</v>
+        <v>0.2789032247660559</v>
       </c>
       <c r="D224" t="s">
         <v>7</v>
@@ -8151,7 +8151,7 @@
         <v>15</v>
       </c>
       <c r="C225">
-        <v>0.359792004793746</v>
+        <v>0.361512320193079</v>
       </c>
       <c r="D225" t="s">
         <v>7</v>
@@ -8168,7 +8168,7 @@
         <v>6</v>
       </c>
       <c r="C226">
-        <v>0.5003732689855046</v>
+        <v>0.5116396741165794</v>
       </c>
       <c r="D226" t="s">
         <v>7</v>
@@ -8185,7 +8185,7 @@
         <v>10</v>
       </c>
       <c r="C227">
-        <v>0.3104592871868451</v>
+        <v>0.2996521498530782</v>
       </c>
       <c r="D227" t="s">
         <v>7</v>
@@ -8202,7 +8202,7 @@
         <v>6</v>
       </c>
       <c r="C228">
-        <v>0.4948909213788268</v>
+        <v>0.5088798597204086</v>
       </c>
       <c r="D228" t="s">
         <v>7</v>
@@ -8219,7 +8219,7 @@
         <v>6</v>
       </c>
       <c r="C229">
-        <v>0.5692849052666057</v>
+        <v>0.5793449328941894</v>
       </c>
       <c r="D229" t="s">
         <v>7</v>
@@ -8236,7 +8236,7 @@
         <v>44</v>
       </c>
       <c r="C230">
-        <v>0.3410400182973143</v>
+        <v>0.3317428947097051</v>
       </c>
       <c r="D230" t="s">
         <v>7</v>
@@ -8253,7 +8253,7 @@
         <v>6</v>
       </c>
       <c r="C231">
-        <v>0.323117789613182</v>
+        <v>0.3363027572203622</v>
       </c>
       <c r="D231" t="s">
         <v>7</v>
@@ -8270,7 +8270,7 @@
         <v>6</v>
       </c>
       <c r="C232">
-        <v>0.5981603193611746</v>
+        <v>0.6099239196103653</v>
       </c>
       <c r="D232" t="s">
         <v>7</v>
@@ -8287,7 +8287,7 @@
         <v>44</v>
       </c>
       <c r="C233">
-        <v>0.4052469218373108</v>
+        <v>0.3962686908673368</v>
       </c>
       <c r="D233" t="s">
         <v>7</v>
@@ -8304,7 +8304,7 @@
         <v>6</v>
       </c>
       <c r="C234">
-        <v>0.44022433354806</v>
+        <v>0.4489134774039293</v>
       </c>
       <c r="D234" t="s">
         <v>7</v>
@@ -8321,7 +8321,7 @@
         <v>6</v>
       </c>
       <c r="C235">
-        <v>0.5107491903191065</v>
+        <v>0.5203567356573355</v>
       </c>
       <c r="D235" t="s">
         <v>7</v>
@@ -8338,7 +8338,7 @@
         <v>6</v>
       </c>
       <c r="C236">
-        <v>0.2971960396306566</v>
+        <v>0.308221623413592</v>
       </c>
       <c r="D236" t="s">
         <v>7</v>
@@ -8355,7 +8355,7 @@
         <v>6</v>
       </c>
       <c r="C237">
-        <v>0.3152333927614711</v>
+        <v>0.3281612415324567</v>
       </c>
       <c r="D237" t="s">
         <v>7</v>
@@ -8372,7 +8372,7 @@
         <v>6</v>
       </c>
       <c r="C238">
-        <v>0.368008514435983</v>
+        <v>0.376065400153703</v>
       </c>
       <c r="D238" t="s">
         <v>7</v>
@@ -8389,7 +8389,7 @@
         <v>6</v>
       </c>
       <c r="C239">
-        <v>0.4528708710536115</v>
+        <v>0.4666542902291647</v>
       </c>
       <c r="D239" t="s">
         <v>7</v>
@@ -8406,7 +8406,7 @@
         <v>226</v>
       </c>
       <c r="C240">
-        <v>0.3462385711789149</v>
+        <v>0.3522967028147929</v>
       </c>
       <c r="D240" t="s">
         <v>7</v>
@@ -8420,10 +8420,10 @@
         <v>490</v>
       </c>
       <c r="B241" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C241">
-        <v>0.2383877973681386</v>
+        <v>0.2323183949910056</v>
       </c>
       <c r="D241" t="s">
         <v>7</v>
@@ -8440,7 +8440,7 @@
         <v>6</v>
       </c>
       <c r="C242">
-        <v>0.3312884553726934</v>
+        <v>0.3419814192782404</v>
       </c>
       <c r="D242" t="s">
         <v>7</v>
@@ -8457,7 +8457,7 @@
         <v>15</v>
       </c>
       <c r="C243">
-        <v>0.500853992723043</v>
+        <v>0.5006799575697565</v>
       </c>
       <c r="D243" t="s">
         <v>7</v>
@@ -8474,7 +8474,7 @@
         <v>226</v>
       </c>
       <c r="C244">
-        <v>0.4753122467841381</v>
+        <v>0.4771018800278814</v>
       </c>
       <c r="D244" t="s">
         <v>7</v>
@@ -8491,7 +8491,7 @@
         <v>6</v>
       </c>
       <c r="C245">
-        <v>0.6365938941068338</v>
+        <v>0.6452899008851005</v>
       </c>
       <c r="D245" t="s">
         <v>7</v>
@@ -8508,7 +8508,7 @@
         <v>6</v>
       </c>
       <c r="C246">
-        <v>0.4552354679532494</v>
+        <v>0.4636217166248545</v>
       </c>
       <c r="D246" t="s">
         <v>7</v>
@@ -8525,7 +8525,7 @@
         <v>6</v>
       </c>
       <c r="C247">
-        <v>0.4130480424882629</v>
+        <v>0.4263025802786948</v>
       </c>
       <c r="D247" t="s">
         <v>7</v>
@@ -8542,7 +8542,7 @@
         <v>10</v>
       </c>
       <c r="C248">
-        <v>0.3007608966771927</v>
+        <v>0.2911544830091955</v>
       </c>
       <c r="D248" t="s">
         <v>7</v>
@@ -8559,7 +8559,7 @@
         <v>6</v>
       </c>
       <c r="C249">
-        <v>0.4372008493822402</v>
+        <v>0.4490593135708703</v>
       </c>
       <c r="D249" t="s">
         <v>7</v>
@@ -8576,7 +8576,7 @@
         <v>15</v>
       </c>
       <c r="C250">
-        <v>0.3167809468931533</v>
+        <v>0.3193572902584206</v>
       </c>
       <c r="D250" t="s">
         <v>7</v>
@@ -8593,7 +8593,7 @@
         <v>44</v>
       </c>
       <c r="C251">
-        <v>0.4960981945480177</v>
+        <v>0.4920765672140364</v>
       </c>
       <c r="D251" t="s">
         <v>7</v>
@@ -8610,7 +8610,7 @@
         <v>6</v>
       </c>
       <c r="C252">
-        <v>0.4175548364995839</v>
+        <v>0.4295100346662291</v>
       </c>
       <c r="D252" t="s">
         <v>7</v>
@@ -8627,7 +8627,7 @@
         <v>6</v>
       </c>
       <c r="C253">
-        <v>0.3695709556916547</v>
+        <v>0.3797643571126112</v>
       </c>
       <c r="D253" t="s">
         <v>7</v>
@@ -8644,7 +8644,7 @@
         <v>6</v>
       </c>
       <c r="C254">
-        <v>0.5005025990617649</v>
+        <v>0.5130304667892039</v>
       </c>
       <c r="D254" t="s">
         <v>7</v>
@@ -8661,7 +8661,7 @@
         <v>15</v>
       </c>
       <c r="C255">
-        <v>0.4504237061036552</v>
+        <v>0.4526973403610122</v>
       </c>
       <c r="D255" t="s">
         <v>7</v>
@@ -8678,7 +8678,7 @@
         <v>6</v>
       </c>
       <c r="C256">
-        <v>0.603918347216904</v>
+        <v>0.6102906084632975</v>
       </c>
       <c r="D256" t="s">
         <v>7</v>
@@ -8695,7 +8695,7 @@
         <v>6</v>
       </c>
       <c r="C257">
-        <v>0.4142189500065502</v>
+        <v>0.4252869864910019</v>
       </c>
       <c r="D257" t="s">
         <v>7</v>
@@ -8712,7 +8712,7 @@
         <v>6</v>
       </c>
       <c r="C258">
-        <v>0.510519316454962</v>
+        <v>0.5207193197792143</v>
       </c>
       <c r="D258" t="s">
         <v>7</v>
@@ -8729,7 +8729,7 @@
         <v>15</v>
       </c>
       <c r="C259">
-        <v>0.3004134595234022</v>
+        <v>0.2999551002181531</v>
       </c>
       <c r="D259" t="s">
         <v>7</v>
@@ -8746,7 +8746,7 @@
         <v>6</v>
       </c>
       <c r="C260">
-        <v>0.4438626218174644</v>
+        <v>0.4551250714572553</v>
       </c>
       <c r="D260" t="s">
         <v>7</v>
@@ -8763,7 +8763,7 @@
         <v>6</v>
       </c>
       <c r="C261">
-        <v>0.4924575402663876</v>
+        <v>0.5042220771703753</v>
       </c>
       <c r="D261" t="s">
         <v>7</v>
@@ -8780,7 +8780,7 @@
         <v>6</v>
       </c>
       <c r="C262">
-        <v>0.4344632757592707</v>
+        <v>0.4430022555391789</v>
       </c>
       <c r="D262" t="s">
         <v>7</v>
@@ -8797,7 +8797,7 @@
         <v>6</v>
       </c>
       <c r="C263">
-        <v>0.4695565420413191</v>
+        <v>0.4794056890398446</v>
       </c>
       <c r="D263" t="s">
         <v>7</v>
@@ -8814,7 +8814,7 @@
         <v>6</v>
       </c>
       <c r="C264">
-        <v>0.4516797344587705</v>
+        <v>0.4612502472942309</v>
       </c>
       <c r="D264" t="s">
         <v>7</v>
@@ -8831,7 +8831,7 @@
         <v>6</v>
       </c>
       <c r="C265">
-        <v>0.3517538244124224</v>
+        <v>0.3606790444548494</v>
       </c>
       <c r="D265" t="s">
         <v>7</v>
@@ -8848,7 +8848,7 @@
         <v>6</v>
       </c>
       <c r="C266">
-        <v>0.4049663634664883</v>
+        <v>0.413266941272524</v>
       </c>
       <c r="D266" t="s">
         <v>7</v>
@@ -8865,7 +8865,7 @@
         <v>6</v>
       </c>
       <c r="C267">
-        <v>0.2801316938369079</v>
+        <v>0.2898857341600403</v>
       </c>
       <c r="D267" t="s">
         <v>7</v>
@@ -8882,7 +8882,7 @@
         <v>6</v>
       </c>
       <c r="C268">
-        <v>0.4571165799744631</v>
+        <v>0.4677622630388396</v>
       </c>
       <c r="D268" t="s">
         <v>7</v>
@@ -8899,7 +8899,7 @@
         <v>44</v>
       </c>
       <c r="C269">
-        <v>0.3729116193046573</v>
+        <v>0.3608027024625819</v>
       </c>
       <c r="D269" t="s">
         <v>7</v>
@@ -8916,7 +8916,7 @@
         <v>6</v>
       </c>
       <c r="C270">
-        <v>0.5427927211304929</v>
+        <v>0.5532464640751245</v>
       </c>
       <c r="D270" t="s">
         <v>7</v>
@@ -8933,7 +8933,7 @@
         <v>6</v>
       </c>
       <c r="C271">
-        <v>0.5514165812903913</v>
+        <v>0.5606967991198075</v>
       </c>
       <c r="D271" t="s">
         <v>7</v>
@@ -8950,7 +8950,7 @@
         <v>6</v>
       </c>
       <c r="C272">
-        <v>0.3903289525358814</v>
+        <v>0.4015826491170143</v>
       </c>
       <c r="D272" t="s">
         <v>7</v>
@@ -8967,7 +8967,7 @@
         <v>6</v>
       </c>
       <c r="C273">
-        <v>0.537893289925253</v>
+        <v>0.5499409857298471</v>
       </c>
       <c r="D273" t="s">
         <v>7</v>
@@ -8984,7 +8984,7 @@
         <v>15</v>
       </c>
       <c r="C274">
-        <v>0.3567795579988073</v>
+        <v>0.3623086791294109</v>
       </c>
       <c r="D274" t="s">
         <v>7</v>
@@ -8998,10 +8998,10 @@
         <v>558</v>
       </c>
       <c r="B275" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C275">
-        <v>0.2434975618392645</v>
+        <v>0.2430331853213277</v>
       </c>
       <c r="D275" t="s">
         <v>7</v>
@@ -9018,7 +9018,7 @@
         <v>6</v>
       </c>
       <c r="C276">
-        <v>0.3248643751286648</v>
+        <v>0.3338660101859057</v>
       </c>
       <c r="D276" t="s">
         <v>7</v>
@@ -9035,7 +9035,7 @@
         <v>6</v>
       </c>
       <c r="C277">
-        <v>0.382998336426568</v>
+        <v>0.3906582368052031</v>
       </c>
       <c r="D277" t="s">
         <v>7</v>
@@ -9052,7 +9052,7 @@
         <v>6</v>
       </c>
       <c r="C278">
-        <v>0.4516882737181834</v>
+        <v>0.4568775256297566</v>
       </c>
       <c r="D278" t="s">
         <v>7</v>
@@ -9069,7 +9069,7 @@
         <v>6</v>
       </c>
       <c r="C279">
-        <v>0.553225481550041</v>
+        <v>0.5639298152217527</v>
       </c>
       <c r="D279" t="s">
         <v>7</v>
@@ -9086,7 +9086,7 @@
         <v>6</v>
       </c>
       <c r="C280">
-        <v>0.4996390636210539</v>
+        <v>0.5062276776398805</v>
       </c>
       <c r="D280" t="s">
         <v>7</v>
@@ -9103,7 +9103,7 @@
         <v>6</v>
       </c>
       <c r="C281">
-        <v>0.4042351114621328</v>
+        <v>0.4181681675248892</v>
       </c>
       <c r="D281" t="s">
         <v>7</v>
@@ -9120,7 +9120,7 @@
         <v>15</v>
       </c>
       <c r="C282">
-        <v>0.3676843630447438</v>
+        <v>0.3703709320976004</v>
       </c>
       <c r="D282" t="s">
         <v>7</v>
@@ -9137,7 +9137,7 @@
         <v>6</v>
       </c>
       <c r="C283">
-        <v>0.3564393111361292</v>
+        <v>0.3655257933063339</v>
       </c>
       <c r="D283" t="s">
         <v>7</v>
@@ -9154,7 +9154,7 @@
         <v>6</v>
       </c>
       <c r="C284">
-        <v>0.3373427095624622</v>
+        <v>0.3489132415633993</v>
       </c>
       <c r="D284" t="s">
         <v>7</v>
@@ -9171,7 +9171,7 @@
         <v>15</v>
       </c>
       <c r="C285">
-        <v>0.2490284621728504</v>
+        <v>0.2503689210790596</v>
       </c>
       <c r="D285" t="s">
         <v>7</v>
@@ -9188,7 +9188,7 @@
         <v>6</v>
       </c>
       <c r="C286">
-        <v>0.3040129186173865</v>
+        <v>0.3146019568205206</v>
       </c>
       <c r="D286" t="s">
         <v>7</v>
@@ -9205,7 +9205,7 @@
         <v>44</v>
       </c>
       <c r="C287">
-        <v>0.4705097458337114</v>
+        <v>0.4658178817547965</v>
       </c>
       <c r="D287" t="s">
         <v>7</v>
@@ -9222,7 +9222,7 @@
         <v>6</v>
       </c>
       <c r="C288">
-        <v>0.2795602509827043</v>
+        <v>0.2915861578446677</v>
       </c>
       <c r="D288" t="s">
         <v>7</v>
@@ -9239,7 +9239,7 @@
         <v>6</v>
       </c>
       <c r="C289">
-        <v>0.3766442752442883</v>
+        <v>0.3868899424053717</v>
       </c>
       <c r="D289" t="s">
         <v>7</v>
@@ -9256,7 +9256,7 @@
         <v>15</v>
       </c>
       <c r="C290">
-        <v>0.3181579336124398</v>
+        <v>0.3214170076002224</v>
       </c>
       <c r="D290" t="s">
         <v>7</v>
@@ -9273,7 +9273,7 @@
         <v>6</v>
       </c>
       <c r="C291">
-        <v>0.4382329848431203</v>
+        <v>0.4470887575383654</v>
       </c>
       <c r="D291" t="s">
         <v>7</v>
@@ -9290,7 +9290,7 @@
         <v>145</v>
       </c>
       <c r="C292">
-        <v>0.4297622545883468</v>
+        <v>0.4317491058314316</v>
       </c>
       <c r="D292" t="s">
         <v>7</v>
@@ -9307,7 +9307,7 @@
         <v>6</v>
       </c>
       <c r="C293">
-        <v>0.6155363651541489</v>
+        <v>0.6244506001415259</v>
       </c>
       <c r="D293" t="s">
         <v>7</v>
@@ -9324,7 +9324,7 @@
         <v>15</v>
       </c>
       <c r="C294">
-        <v>0.4095128402444583</v>
+        <v>0.4089960194674507</v>
       </c>
       <c r="D294" t="s">
         <v>7</v>
@@ -9341,7 +9341,7 @@
         <v>10</v>
       </c>
       <c r="C295">
-        <v>0.3227167310804794</v>
+        <v>0.3145493860791583</v>
       </c>
       <c r="D295" t="s">
         <v>7</v>
@@ -9358,7 +9358,7 @@
         <v>15</v>
       </c>
       <c r="C296">
-        <v>0.3132479825330827</v>
+        <v>0.31647002386855</v>
       </c>
       <c r="D296" t="s">
         <v>7</v>
@@ -9375,7 +9375,7 @@
         <v>10</v>
       </c>
       <c r="C297">
-        <v>0.4553235217563223</v>
+        <v>0.4461867059106271</v>
       </c>
       <c r="D297" t="s">
         <v>7</v>
@@ -9392,7 +9392,7 @@
         <v>10</v>
       </c>
       <c r="C298">
-        <v>0.3902692949045607</v>
+        <v>0.3786389595772517</v>
       </c>
       <c r="D298" t="s">
         <v>7</v>
@@ -9409,7 +9409,7 @@
         <v>44</v>
       </c>
       <c r="C299">
-        <v>0.2724901601169842</v>
+        <v>0.2614565070052689</v>
       </c>
       <c r="D299" t="s">
         <v>7</v>
@@ -9426,7 +9426,7 @@
         <v>10</v>
       </c>
       <c r="C300">
-        <v>0.3201020247933296</v>
+        <v>0.3069831753375744</v>
       </c>
       <c r="D300" t="s">
         <v>7</v>
@@ -9443,7 +9443,7 @@
         <v>6</v>
       </c>
       <c r="C301">
-        <v>0.3651338896500385</v>
+        <v>0.3772454891940416</v>
       </c>
       <c r="D301" t="s">
         <v>7</v>
@@ -9460,7 +9460,7 @@
         <v>44</v>
       </c>
       <c r="C302">
-        <v>0.469269289582411</v>
+        <v>0.4647148423079107</v>
       </c>
       <c r="D302" t="s">
         <v>7</v>
@@ -9477,7 +9477,7 @@
         <v>10</v>
       </c>
       <c r="C303">
-        <v>0.3078793870613528</v>
+        <v>0.297020710519695</v>
       </c>
       <c r="D303" t="s">
         <v>7</v>
@@ -9491,10 +9491,10 @@
         <v>616</v>
       </c>
       <c r="B304" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C304">
-        <v>0.2922127448047602</v>
+        <v>0.2845574363802308</v>
       </c>
       <c r="D304" t="s">
         <v>7</v>
@@ -9511,7 +9511,7 @@
         <v>44</v>
       </c>
       <c r="C305">
-        <v>0.4014516423990678</v>
+        <v>0.3920697688182801</v>
       </c>
       <c r="D305" t="s">
         <v>7</v>
@@ -9528,7 +9528,7 @@
         <v>15</v>
       </c>
       <c r="C306">
-        <v>0.4336396208735654</v>
+        <v>0.4327029435863228</v>
       </c>
       <c r="D306" t="s">
         <v>7</v>
@@ -9545,7 +9545,7 @@
         <v>6</v>
       </c>
       <c r="C307">
-        <v>0.4315152699243084</v>
+        <v>0.4448386609192092</v>
       </c>
       <c r="D307" t="s">
         <v>7</v>
@@ -9562,7 +9562,7 @@
         <v>6</v>
       </c>
       <c r="C308">
-        <v>0.4010190658672029</v>
+        <v>0.411670927673743</v>
       </c>
       <c r="D308" t="s">
         <v>7</v>
@@ -9579,7 +9579,7 @@
         <v>6</v>
       </c>
       <c r="C309">
-        <v>0.2818819195593599</v>
+        <v>0.2937885960814636</v>
       </c>
       <c r="D309" t="s">
         <v>7</v>
@@ -9596,7 +9596,7 @@
         <v>6</v>
       </c>
       <c r="C310">
-        <v>0.4171369853569546</v>
+        <v>0.4315434292576864</v>
       </c>
       <c r="D310" t="s">
         <v>7</v>
@@ -9613,7 +9613,7 @@
         <v>15</v>
       </c>
       <c r="C311">
-        <v>0.3521207583112989</v>
+        <v>0.3540259463510645</v>
       </c>
       <c r="D311" t="s">
         <v>7</v>
@@ -9630,7 +9630,7 @@
         <v>15</v>
       </c>
       <c r="C312">
-        <v>0.273993763704012</v>
+        <v>0.2768119430270821</v>
       </c>
       <c r="D312" t="s">
         <v>7</v>
@@ -9647,7 +9647,7 @@
         <v>44</v>
       </c>
       <c r="C313">
-        <v>0.3131184977063728</v>
+        <v>0.3012457618750705</v>
       </c>
       <c r="D313" t="s">
         <v>7</v>
@@ -9661,10 +9661,10 @@
         <v>636</v>
       </c>
       <c r="B314" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C314">
-        <v>0.2959684667614155</v>
+        <v>0.2995085983059964</v>
       </c>
       <c r="D314" t="s">
         <v>7</v>
@@ -9681,7 +9681,7 @@
         <v>44</v>
       </c>
       <c r="C315">
-        <v>0.5030080066804039</v>
+        <v>0.4962980691585901</v>
       </c>
       <c r="D315" t="s">
         <v>7</v>
@@ -9698,7 +9698,7 @@
         <v>6</v>
       </c>
       <c r="C316">
-        <v>0.3938794177574184</v>
+        <v>0.4037849190072293</v>
       </c>
       <c r="D316" t="s">
         <v>7</v>
@@ -9715,7 +9715,7 @@
         <v>6</v>
       </c>
       <c r="C317">
-        <v>0.536670990458005</v>
+        <v>0.5463630362204773</v>
       </c>
       <c r="D317" t="s">
         <v>7</v>
@@ -9732,7 +9732,7 @@
         <v>6</v>
       </c>
       <c r="C318">
-        <v>0.5644807092272125</v>
+        <v>0.5759136010683347</v>
       </c>
       <c r="D318" t="s">
         <v>7</v>
@@ -9749,7 +9749,7 @@
         <v>6</v>
       </c>
       <c r="C319">
-        <v>0.3521754100600347</v>
+        <v>0.363716438702583</v>
       </c>
       <c r="D319" t="s">
         <v>7</v>
@@ -9766,7 +9766,7 @@
         <v>15</v>
       </c>
       <c r="C320">
-        <v>0.2830514329557617</v>
+        <v>0.2863753170948884</v>
       </c>
       <c r="D320" t="s">
         <v>7</v>
@@ -9783,7 +9783,7 @@
         <v>6</v>
       </c>
       <c r="C321">
-        <v>0.3581545778631968</v>
+        <v>0.3686780475055504</v>
       </c>
       <c r="D321" t="s">
         <v>7</v>
@@ -9800,7 +9800,7 @@
         <v>6</v>
       </c>
       <c r="C322">
-        <v>0.3830340452151103</v>
+        <v>0.3930228852079471</v>
       </c>
       <c r="D322" t="s">
         <v>7</v>
@@ -9817,7 +9817,7 @@
         <v>10</v>
       </c>
       <c r="C323">
-        <v>0.3143354062858941</v>
+        <v>0.3032407914181701</v>
       </c>
       <c r="D323" t="s">
         <v>7</v>
@@ -9834,7 +9834,7 @@
         <v>44</v>
       </c>
       <c r="C324">
-        <v>0.4052216368277862</v>
+        <v>0.3945970107533279</v>
       </c>
       <c r="D324" t="s">
         <v>7</v>
@@ -9851,7 +9851,7 @@
         <v>6</v>
       </c>
       <c r="C325">
-        <v>0.2245497039222527</v>
+        <v>0.2353620251354855</v>
       </c>
       <c r="D325" t="s">
         <v>7</v>
@@ -9868,7 +9868,7 @@
         <v>44</v>
       </c>
       <c r="C326">
-        <v>0.36622687022017</v>
+        <v>0.3568842267624615</v>
       </c>
       <c r="D326" t="s">
         <v>7</v>
@@ -9885,7 +9885,7 @@
         <v>44</v>
       </c>
       <c r="C327">
-        <v>0.3252648880141185</v>
+        <v>0.3159347296001412</v>
       </c>
       <c r="D327" t="s">
         <v>7</v>
@@ -9899,10 +9899,10 @@
         <v>664</v>
       </c>
       <c r="B328" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C328">
-        <v>0.28124459137469</v>
+        <v>0.2895979869722479</v>
       </c>
       <c r="D328" t="s">
         <v>7</v>
@@ -9919,7 +9919,7 @@
         <v>15</v>
       </c>
       <c r="C329">
-        <v>0.302368758040183</v>
+        <v>0.3050517502872068</v>
       </c>
       <c r="D329" t="s">
         <v>7</v>
@@ -9936,7 +9936,7 @@
         <v>15</v>
       </c>
       <c r="C330">
-        <v>0.3189276527375555</v>
+        <v>0.3207628518523722</v>
       </c>
       <c r="D330" t="s">
         <v>7</v>
@@ -9953,7 +9953,7 @@
         <v>15</v>
       </c>
       <c r="C331">
-        <v>0.3574593112131789</v>
+        <v>0.3625476441132194</v>
       </c>
       <c r="D331" t="s">
         <v>7</v>
@@ -9970,7 +9970,7 @@
         <v>10</v>
       </c>
       <c r="C332">
-        <v>0.3414726310091031</v>
+        <v>0.3314768216021105</v>
       </c>
       <c r="D332" t="s">
         <v>7</v>
@@ -9987,7 +9987,7 @@
         <v>6</v>
       </c>
       <c r="C333">
-        <v>0.4860361099471424</v>
+        <v>0.498785131249303</v>
       </c>
       <c r="D333" t="s">
         <v>7</v>
@@ -10004,7 +10004,7 @@
         <v>15</v>
       </c>
       <c r="C334">
-        <v>0.3069554386544092</v>
+        <v>0.3109644642924358</v>
       </c>
       <c r="D334" t="s">
         <v>7</v>
@@ -10021,7 +10021,7 @@
         <v>15</v>
       </c>
       <c r="C335">
-        <v>0.3549319077345647</v>
+        <v>0.3602587934751963</v>
       </c>
       <c r="D335" t="s">
         <v>7</v>
@@ -10038,7 +10038,7 @@
         <v>10</v>
       </c>
       <c r="C336">
-        <v>0.3095574546765317</v>
+        <v>0.2964386002610418</v>
       </c>
       <c r="D336" t="s">
         <v>7</v>
@@ -10055,7 +10055,7 @@
         <v>44</v>
       </c>
       <c r="C337">
-        <v>0.4339861658202007</v>
+        <v>0.4241081538787879</v>
       </c>
       <c r="D337" t="s">
         <v>7</v>
@@ -10072,7 +10072,7 @@
         <v>6</v>
       </c>
       <c r="C338">
-        <v>0.2914939545742061</v>
+        <v>0.3059839463585597</v>
       </c>
       <c r="D338" t="s">
         <v>7</v>
@@ -10089,7 +10089,7 @@
         <v>15</v>
       </c>
       <c r="C339">
-        <v>0.4479716548515007</v>
+        <v>0.4488125767406623</v>
       </c>
       <c r="D339" t="s">
         <v>7</v>
@@ -10106,7 +10106,7 @@
         <v>15</v>
       </c>
       <c r="C340">
-        <v>0.306975379904933</v>
+        <v>0.3092850089601737</v>
       </c>
       <c r="D340" t="s">
         <v>7</v>
@@ -10123,7 +10123,7 @@
         <v>6</v>
       </c>
       <c r="C341">
-        <v>0.3051432759499521</v>
+        <v>0.3199619604131295</v>
       </c>
       <c r="D341" t="s">
         <v>7</v>
@@ -10140,7 +10140,7 @@
         <v>10</v>
       </c>
       <c r="C342">
-        <v>0.2692457810055402</v>
+        <v>0.2599200427163789</v>
       </c>
       <c r="D342" t="s">
         <v>7</v>
@@ -10157,7 +10157,7 @@
         <v>10</v>
       </c>
       <c r="C343">
-        <v>0.3757685007328178</v>
+        <v>0.3626864552144133</v>
       </c>
       <c r="D343" t="s">
         <v>7</v>
@@ -10174,7 +10174,7 @@
         <v>15</v>
       </c>
       <c r="C344">
-        <v>0.2611178404158734</v>
+        <v>0.2636954719468262</v>
       </c>
       <c r="D344" t="s">
         <v>7</v>
@@ -10191,7 +10191,7 @@
         <v>6</v>
       </c>
       <c r="C345">
-        <v>0.3782166625769434</v>
+        <v>0.388883225275534</v>
       </c>
       <c r="D345" t="s">
         <v>7</v>
@@ -10205,10 +10205,10 @@
         <v>700</v>
       </c>
       <c r="B346" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C346">
-        <v>0.3201396791318229</v>
+        <v>0.309315977886474</v>
       </c>
       <c r="D346" t="s">
         <v>7</v>
@@ -10225,7 +10225,7 @@
         <v>15</v>
       </c>
       <c r="C347">
-        <v>0.3511372116355303</v>
+        <v>0.353117337830763</v>
       </c>
       <c r="D347" t="s">
         <v>7</v>
@@ -10242,7 +10242,7 @@
         <v>6</v>
       </c>
       <c r="C348">
-        <v>0.3592010554715729</v>
+        <v>0.3696405409763551</v>
       </c>
       <c r="D348" t="s">
         <v>7</v>
@@ -10259,7 +10259,7 @@
         <v>6</v>
       </c>
       <c r="C349">
-        <v>0.5048517696564034</v>
+        <v>0.513983737280778</v>
       </c>
       <c r="D349" t="s">
         <v>7</v>
@@ -10276,7 +10276,7 @@
         <v>15</v>
       </c>
       <c r="C350">
-        <v>0.357783323728112</v>
+        <v>0.3576146477649211</v>
       </c>
       <c r="D350" t="s">
         <v>7</v>
@@ -10293,7 +10293,7 @@
         <v>145</v>
       </c>
       <c r="C351">
-        <v>0.2317129685538366</v>
+        <v>0.235790518634051</v>
       </c>
       <c r="D351" t="s">
         <v>7</v>
@@ -10310,7 +10310,7 @@
         <v>15</v>
       </c>
       <c r="C352">
-        <v>0.4015317335891016</v>
+        <v>0.4040108579419713</v>
       </c>
       <c r="D352" t="s">
         <v>7</v>
@@ -10327,7 +10327,7 @@
         <v>10</v>
       </c>
       <c r="C353">
-        <v>0.3688327690175873</v>
+        <v>0.3581954370321566</v>
       </c>
       <c r="D353" t="s">
         <v>7</v>
@@ -10344,7 +10344,7 @@
         <v>6</v>
       </c>
       <c r="C354">
-        <v>0.2954905467717648</v>
+        <v>0.3049797225403081</v>
       </c>
       <c r="D354" t="s">
         <v>7</v>
@@ -10361,7 +10361,7 @@
         <v>6</v>
       </c>
       <c r="C355">
-        <v>0.3877022305355358</v>
+        <v>0.3969309993503536</v>
       </c>
       <c r="D355" t="s">
         <v>7</v>
@@ -10378,7 +10378,7 @@
         <v>6</v>
       </c>
       <c r="C356">
-        <v>0.3285480777230912</v>
+        <v>0.3407877361791164</v>
       </c>
       <c r="D356" t="s">
         <v>7</v>
@@ -10395,7 +10395,7 @@
         <v>6</v>
       </c>
       <c r="C357">
-        <v>0.4140400507950224</v>
+        <v>0.4255386120104166</v>
       </c>
       <c r="D357" t="s">
         <v>7</v>
@@ -10412,7 +10412,7 @@
         <v>6</v>
       </c>
       <c r="C358">
-        <v>0.352261832944315</v>
+        <v>0.3629317565929992</v>
       </c>
       <c r="D358" t="s">
         <v>7</v>
@@ -10429,7 +10429,7 @@
         <v>44</v>
       </c>
       <c r="C359">
-        <v>0.4526094476176031</v>
+        <v>0.4462201855437908</v>
       </c>
       <c r="D359" t="s">
         <v>7</v>
@@ -10446,7 +10446,7 @@
         <v>6</v>
       </c>
       <c r="C360">
-        <v>0.4942814791324469</v>
+        <v>0.5033708441126752</v>
       </c>
       <c r="D360" t="s">
         <v>7</v>
@@ -10463,7 +10463,7 @@
         <v>15</v>
       </c>
       <c r="C361">
-        <v>0.3081114178097432</v>
+        <v>0.3103602430659022</v>
       </c>
       <c r="D361" t="s">
         <v>7</v>
@@ -10480,7 +10480,7 @@
         <v>6</v>
       </c>
       <c r="C362">
-        <v>0.3731618005408188</v>
+        <v>0.3852494574372063</v>
       </c>
       <c r="D362" t="s">
         <v>7</v>
@@ -10497,7 +10497,7 @@
         <v>6</v>
       </c>
       <c r="C363">
-        <v>0.295387126912032</v>
+        <v>0.3070595943506313</v>
       </c>
       <c r="D363" t="s">
         <v>7</v>
@@ -10514,7 +10514,7 @@
         <v>10</v>
       </c>
       <c r="C364">
-        <v>0.3028986610426423</v>
+        <v>0.2898821486936167</v>
       </c>
       <c r="D364" t="s">
         <v>7</v>
@@ -10531,7 +10531,7 @@
         <v>15</v>
       </c>
       <c r="C365">
-        <v>0.3215993689221526</v>
+        <v>0.3239092996795535</v>
       </c>
       <c r="D365" t="s">
         <v>7</v>
@@ -10548,7 +10548,7 @@
         <v>15</v>
       </c>
       <c r="C366">
-        <v>0.2741762177091143</v>
+        <v>0.2760018428062074</v>
       </c>
       <c r="D366" t="s">
         <v>7</v>
@@ -10565,7 +10565,7 @@
         <v>6</v>
       </c>
       <c r="C367">
-        <v>0.3622082336770255</v>
+        <v>0.3701468544137403</v>
       </c>
       <c r="D367" t="s">
         <v>7</v>
@@ -10582,7 +10582,7 @@
         <v>15</v>
       </c>
       <c r="C368">
-        <v>0.3598930666679192</v>
+        <v>0.3657060461591357</v>
       </c>
       <c r="D368" t="s">
         <v>7</v>
@@ -10599,7 +10599,7 @@
         <v>6</v>
       </c>
       <c r="C369">
-        <v>0.5418386999243436</v>
+        <v>0.5508193368647804</v>
       </c>
       <c r="D369" t="s">
         <v>7</v>
@@ -10616,7 +10616,7 @@
         <v>15</v>
       </c>
       <c r="C370">
-        <v>0.3440573871828592</v>
+        <v>0.346873274461757</v>
       </c>
       <c r="D370" t="s">
         <v>7</v>
@@ -10633,7 +10633,7 @@
         <v>6</v>
       </c>
       <c r="C371">
-        <v>0.4818037603512438</v>
+        <v>0.4953715652262097</v>
       </c>
       <c r="D371" t="s">
         <v>7</v>
@@ -10650,7 +10650,7 @@
         <v>6</v>
       </c>
       <c r="C372">
-        <v>0.3886589767347233</v>
+        <v>0.3980059874345931</v>
       </c>
       <c r="D372" t="s">
         <v>7</v>
@@ -10667,7 +10667,7 @@
         <v>6</v>
       </c>
       <c r="C373">
-        <v>0.4518321029746044</v>
+        <v>0.4663199570988534</v>
       </c>
       <c r="D373" t="s">
         <v>7</v>
@@ -10684,7 +10684,7 @@
         <v>6</v>
       </c>
       <c r="C374">
-        <v>0.5062674642545448</v>
+        <v>0.5158360648798389</v>
       </c>
       <c r="D374" t="s">
         <v>7</v>
@@ -10701,7 +10701,7 @@
         <v>6</v>
       </c>
       <c r="C375">
-        <v>0.4859244773702881</v>
+        <v>0.4955184215924993</v>
       </c>
       <c r="D375" t="s">
         <v>7</v>
@@ -10718,7 +10718,7 @@
         <v>15</v>
       </c>
       <c r="C376">
-        <v>0.3576926675708865</v>
+        <v>0.3633245181856611</v>
       </c>
       <c r="D376" t="s">
         <v>7</v>
@@ -10735,7 +10735,7 @@
         <v>6</v>
       </c>
       <c r="C377">
-        <v>0.4945111800165009</v>
+        <v>0.5056865726655022</v>
       </c>
       <c r="D377" t="s">
         <v>7</v>
@@ -10752,7 +10752,7 @@
         <v>6</v>
       </c>
       <c r="C378">
-        <v>0.3244654939888216</v>
+        <v>0.3363320361311882</v>
       </c>
       <c r="D378" t="s">
         <v>7</v>
@@ -10769,7 +10769,7 @@
         <v>6</v>
       </c>
       <c r="C379">
-        <v>0.3374096663353172</v>
+        <v>0.348918908483048</v>
       </c>
       <c r="D379" t="s">
         <v>7</v>
@@ -10786,7 +10786,7 @@
         <v>6</v>
       </c>
       <c r="C380">
-        <v>0.386169028271969</v>
+        <v>0.3983738653560592</v>
       </c>
       <c r="D380" t="s">
         <v>7</v>
@@ -10803,7 +10803,7 @@
         <v>10</v>
       </c>
       <c r="C381">
-        <v>0.4668044274490474</v>
+        <v>0.4594241133485151</v>
       </c>
       <c r="D381" t="s">
         <v>7</v>
@@ -10820,7 +10820,7 @@
         <v>6</v>
       </c>
       <c r="C382">
-        <v>0.343120021702196</v>
+        <v>0.3536359205544146</v>
       </c>
       <c r="D382" t="s">
         <v>7</v>
@@ -10837,7 +10837,7 @@
         <v>10</v>
       </c>
       <c r="C383">
-        <v>0.365330114928362</v>
+        <v>0.3532667150252892</v>
       </c>
       <c r="D383" t="s">
         <v>7</v>
@@ -10854,7 +10854,7 @@
         <v>44</v>
       </c>
       <c r="C384">
-        <v>0.4354180412702172</v>
+        <v>0.4290164798473723</v>
       </c>
       <c r="D384" t="s">
         <v>7</v>
@@ -10871,7 +10871,7 @@
         <v>6</v>
       </c>
       <c r="C385">
-        <v>0.4158802813897221</v>
+        <v>0.426095480826498</v>
       </c>
       <c r="D385" t="s">
         <v>7</v>
@@ -10888,7 +10888,7 @@
         <v>15</v>
       </c>
       <c r="C386">
-        <v>0.3044891669632954</v>
+        <v>0.3065141044439668</v>
       </c>
       <c r="D386" t="s">
         <v>7</v>
@@ -10905,7 +10905,7 @@
         <v>10</v>
       </c>
       <c r="C387">
-        <v>0.4153650693102153</v>
+        <v>0.402668245199555</v>
       </c>
       <c r="D387" t="s">
         <v>7</v>
@@ -10922,7 +10922,7 @@
         <v>44</v>
       </c>
       <c r="C388">
-        <v>0.2884540648339964</v>
+        <v>0.2774931476960985</v>
       </c>
       <c r="D388" t="s">
         <v>7</v>
@@ -10939,7 +10939,7 @@
         <v>6</v>
       </c>
       <c r="C389">
-        <v>0.3727434049091187</v>
+        <v>0.3839907038671397</v>
       </c>
       <c r="D389" t="s">
         <v>7</v>
@@ -10956,7 +10956,7 @@
         <v>15</v>
       </c>
       <c r="C390">
-        <v>0.3370397198087378</v>
+        <v>0.3390748354355828</v>
       </c>
       <c r="D390" t="s">
         <v>7</v>
@@ -10973,7 +10973,7 @@
         <v>15</v>
       </c>
       <c r="C391">
-        <v>0.348335816847116</v>
+        <v>0.349082384357114</v>
       </c>
       <c r="D391" t="s">
         <v>7</v>
@@ -10990,7 +10990,7 @@
         <v>10</v>
       </c>
       <c r="C392">
-        <v>0.3189712555498261</v>
+        <v>0.3068823898419369</v>
       </c>
       <c r="D392" t="s">
         <v>7</v>
@@ -11007,7 +11007,7 @@
         <v>10</v>
       </c>
       <c r="C393">
-        <v>0.3762388376142077</v>
+        <v>0.3704367171497558</v>
       </c>
       <c r="D393" t="s">
         <v>7</v>
@@ -11024,7 +11024,7 @@
         <v>15</v>
       </c>
       <c r="C394">
-        <v>0.3711857404365056</v>
+        <v>0.3728561045939273</v>
       </c>
       <c r="D394" t="s">
         <v>7</v>
@@ -11041,7 +11041,7 @@
         <v>10</v>
       </c>
       <c r="C395">
-        <v>0.4133186450137529</v>
+        <v>0.4052078357104421</v>
       </c>
       <c r="D395" t="s">
         <v>7</v>
@@ -11058,7 +11058,7 @@
         <v>6</v>
       </c>
       <c r="C396">
-        <v>0.3994779645348568</v>
+        <v>0.4142476926055175</v>
       </c>
       <c r="D396" t="s">
         <v>7</v>
@@ -11075,7 +11075,7 @@
         <v>10</v>
       </c>
       <c r="C397">
-        <v>0.3350895289733127</v>
+        <v>0.3265848531495993</v>
       </c>
       <c r="D397" t="s">
         <v>7</v>
@@ -11092,7 +11092,7 @@
         <v>6</v>
       </c>
       <c r="C398">
-        <v>0.5080860633779676</v>
+        <v>0.5171753097355651</v>
       </c>
       <c r="D398" t="s">
         <v>7</v>
@@ -11109,7 +11109,7 @@
         <v>15</v>
       </c>
       <c r="C399">
-        <v>0.3556828227419039</v>
+        <v>0.359110174201243</v>
       </c>
       <c r="D399" t="s">
         <v>7</v>
@@ -11126,7 +11126,7 @@
         <v>6</v>
       </c>
       <c r="C400">
-        <v>0.3475036864733208</v>
+        <v>0.3595376531454739</v>
       </c>
       <c r="D400" t="s">
         <v>7</v>
@@ -11143,7 +11143,7 @@
         <v>15</v>
       </c>
       <c r="C401">
-        <v>0.449109235710471</v>
+        <v>0.4491970303849152</v>
       </c>
       <c r="D401" t="s">
         <v>7</v>
@@ -11160,7 +11160,7 @@
         <v>6</v>
       </c>
       <c r="C402">
-        <v>0.4064389586456107</v>
+        <v>0.4184848925417775</v>
       </c>
       <c r="D402" t="s">
         <v>7</v>
@@ -11177,7 +11177,7 @@
         <v>6</v>
       </c>
       <c r="C403">
-        <v>0.3108524135580112</v>
+        <v>0.3209324868781458</v>
       </c>
       <c r="D403" t="s">
         <v>7</v>
@@ -11194,7 +11194,7 @@
         <v>10</v>
       </c>
       <c r="C404">
-        <v>0.312755983879567</v>
+        <v>0.3039870382240839</v>
       </c>
       <c r="D404" t="s">
         <v>7</v>
@@ -11211,7 +11211,7 @@
         <v>6</v>
       </c>
       <c r="C405">
-        <v>0.4366612087653646</v>
+        <v>0.4425219944794893</v>
       </c>
       <c r="D405" t="s">
         <v>7</v>
@@ -11228,7 +11228,7 @@
         <v>145</v>
       </c>
       <c r="C406">
-        <v>0.4392642458249147</v>
+        <v>0.441771558854837</v>
       </c>
       <c r="D406" t="s">
         <v>7</v>
@@ -11245,7 +11245,7 @@
         <v>6</v>
       </c>
       <c r="C407">
-        <v>0.4058144270289831</v>
+        <v>0.4208688108277057</v>
       </c>
       <c r="D407" t="s">
         <v>7</v>
@@ -11262,7 +11262,7 @@
         <v>6</v>
       </c>
       <c r="C408">
-        <v>0.4774752439140311</v>
+        <v>0.4869595497511841</v>
       </c>
       <c r="D408" t="s">
         <v>7</v>
@@ -11279,7 +11279,7 @@
         <v>6</v>
       </c>
       <c r="C409">
-        <v>0.4942635917637561</v>
+        <v>0.5030077508215334</v>
       </c>
       <c r="D409" t="s">
         <v>7</v>
@@ -11296,7 +11296,7 @@
         <v>15</v>
       </c>
       <c r="C410">
-        <v>0.2939096575701667</v>
+        <v>0.2960414899254465</v>
       </c>
       <c r="D410" t="s">
         <v>7</v>
@@ -11313,7 +11313,7 @@
         <v>6</v>
       </c>
       <c r="C411">
-        <v>0.3352539520638984</v>
+        <v>0.3465222906359068</v>
       </c>
       <c r="D411" t="s">
         <v>7</v>
@@ -11330,7 +11330,7 @@
         <v>6</v>
       </c>
       <c r="C412">
-        <v>0.4407379943137761</v>
+        <v>0.4556504430586393</v>
       </c>
       <c r="D412" t="s">
         <v>7</v>
@@ -11347,7 +11347,7 @@
         <v>6</v>
       </c>
       <c r="C413">
-        <v>0.2726444865450189</v>
+        <v>0.2827496322710187</v>
       </c>
       <c r="D413" t="s">
         <v>7</v>
@@ -11364,7 +11364,7 @@
         <v>15</v>
       </c>
       <c r="C414">
-        <v>0.3164442829452042</v>
+        <v>0.3201252396396334</v>
       </c>
       <c r="D414" t="s">
         <v>7</v>
@@ -11381,7 +11381,7 @@
         <v>15</v>
       </c>
       <c r="C415">
-        <v>0.3629341202340278</v>
+        <v>0.3662716461415004</v>
       </c>
       <c r="D415" t="s">
         <v>7</v>
@@ -11398,7 +11398,7 @@
         <v>15</v>
       </c>
       <c r="C416">
-        <v>0.4373037212662835</v>
+        <v>0.4422239922013177</v>
       </c>
       <c r="D416" t="s">
         <v>7</v>
@@ -11415,7 +11415,7 @@
         <v>6</v>
       </c>
       <c r="C417">
-        <v>0.2861117393675225</v>
+        <v>0.2953305560228429</v>
       </c>
       <c r="D417" t="s">
         <v>7</v>
@@ -11432,7 +11432,7 @@
         <v>10</v>
       </c>
       <c r="C418">
-        <v>0.303990089573389</v>
+        <v>0.2968244345907722</v>
       </c>
       <c r="D418" t="s">
         <v>7</v>
@@ -11449,7 +11449,7 @@
         <v>15</v>
       </c>
       <c r="C419">
-        <v>0.3984390346354085</v>
+        <v>0.4006120447094201</v>
       </c>
       <c r="D419" t="s">
         <v>7</v>
@@ -11466,7 +11466,7 @@
         <v>44</v>
       </c>
       <c r="C420">
-        <v>0.4473658487040756</v>
+        <v>0.4437514962128905</v>
       </c>
       <c r="D420" t="s">
         <v>7</v>
@@ -11483,7 +11483,7 @@
         <v>44</v>
       </c>
       <c r="C421">
-        <v>0.4532891708419397</v>
+        <v>0.4449266095234198</v>
       </c>
       <c r="D421" t="s">
         <v>7</v>
@@ -11500,7 +11500,7 @@
         <v>6</v>
       </c>
       <c r="C422">
-        <v>0.38053112902339</v>
+        <v>0.3932800364445031</v>
       </c>
       <c r="D422" t="s">
         <v>7</v>
@@ -11517,7 +11517,7 @@
         <v>44</v>
       </c>
       <c r="C423">
-        <v>0.4308436271537863</v>
+        <v>0.4209390073629534</v>
       </c>
       <c r="D423" t="s">
         <v>7</v>
@@ -11534,7 +11534,7 @@
         <v>10</v>
       </c>
       <c r="C424">
-        <v>0.3316939687775155</v>
+        <v>0.3224082792125115</v>
       </c>
       <c r="D424" t="s">
         <v>7</v>
@@ -11551,7 +11551,7 @@
         <v>6</v>
       </c>
       <c r="C425">
-        <v>0.3795525355636375</v>
+        <v>0.3908717988792995</v>
       </c>
       <c r="D425" t="s">
         <v>7</v>
@@ -11568,7 +11568,7 @@
         <v>15</v>
       </c>
       <c r="C426">
-        <v>0.3593202438134249</v>
+        <v>0.3619722950799887</v>
       </c>
       <c r="D426" t="s">
         <v>7</v>
@@ -11585,7 +11585,7 @@
         <v>6</v>
       </c>
       <c r="C427">
-        <v>0.2945977653518862</v>
+        <v>0.307206403941885</v>
       </c>
       <c r="D427" t="s">
         <v>7</v>
@@ -11602,7 +11602,7 @@
         <v>6</v>
       </c>
       <c r="C428">
-        <v>0.2846372477456875</v>
+        <v>0.296362979653009</v>
       </c>
       <c r="D428" t="s">
         <v>7</v>
@@ -11619,7 +11619,7 @@
         <v>10</v>
       </c>
       <c r="C429">
-        <v>0.344617895774117</v>
+        <v>0.3325154492541166</v>
       </c>
       <c r="D429" t="s">
         <v>7</v>
@@ -11636,7 +11636,7 @@
         <v>6</v>
       </c>
       <c r="C430">
-        <v>0.3779046512281166</v>
+        <v>0.390773548704821</v>
       </c>
       <c r="D430" t="s">
         <v>7</v>
@@ -11653,7 +11653,7 @@
         <v>6</v>
       </c>
       <c r="C431">
-        <v>0.3030108440764399</v>
+        <v>0.3103960866508857</v>
       </c>
       <c r="D431" t="s">
         <v>7</v>
@@ -11670,7 +11670,7 @@
         <v>15</v>
       </c>
       <c r="C432">
-        <v>0.3533676140125941</v>
+        <v>0.3573173998451919</v>
       </c>
       <c r="D432" t="s">
         <v>7</v>
@@ -11687,7 +11687,7 @@
         <v>6</v>
       </c>
       <c r="C433">
-        <v>0.2846103921442354</v>
+        <v>0.2969301393877559</v>
       </c>
       <c r="D433" t="s">
         <v>7</v>
@@ -11704,7 +11704,7 @@
         <v>15</v>
       </c>
       <c r="C434">
-        <v>0.3646730696323053</v>
+        <v>0.3682493745097581</v>
       </c>
       <c r="D434" t="s">
         <v>7</v>
@@ -11721,7 +11721,7 @@
         <v>10</v>
       </c>
       <c r="C435">
-        <v>0.3849090642413376</v>
+        <v>0.375552548115118</v>
       </c>
       <c r="D435" t="s">
         <v>7</v>
@@ -11738,7 +11738,7 @@
         <v>15</v>
       </c>
       <c r="C436">
-        <v>0.3576074616665251</v>
+        <v>0.3595062455578177</v>
       </c>
       <c r="D436" t="s">
         <v>7</v>
@@ -11755,7 +11755,7 @@
         <v>10</v>
       </c>
       <c r="C437">
-        <v>0.3126611413958739</v>
+        <v>0.3012345560384321</v>
       </c>
       <c r="D437" t="s">
         <v>7</v>
@@ -11772,7 +11772,7 @@
         <v>15</v>
       </c>
       <c r="C438">
-        <v>0.3613105407581528</v>
+        <v>0.3631267311904203</v>
       </c>
       <c r="D438" t="s">
         <v>7</v>
@@ -11789,7 +11789,7 @@
         <v>6</v>
       </c>
       <c r="C439">
-        <v>0.4036115166037405</v>
+        <v>0.4139142331339077</v>
       </c>
       <c r="D439" t="s">
         <v>7</v>
@@ -11806,7 +11806,7 @@
         <v>10</v>
       </c>
       <c r="C440">
-        <v>0.3062283012271882</v>
+        <v>0.2934081499320107</v>
       </c>
       <c r="D440" t="s">
         <v>7</v>
@@ -11823,7 +11823,7 @@
         <v>6</v>
       </c>
       <c r="C441">
-        <v>0.3487674068611831</v>
+        <v>0.3620322565712872</v>
       </c>
       <c r="D441" t="s">
         <v>7</v>
@@ -11840,7 +11840,7 @@
         <v>6</v>
       </c>
       <c r="C442">
-        <v>0.3216017006219055</v>
+        <v>0.3315831097365082</v>
       </c>
       <c r="D442" t="s">
         <v>7</v>
@@ -11857,7 +11857,7 @@
         <v>15</v>
       </c>
       <c r="C443">
-        <v>0.3070972861866177</v>
+        <v>0.3095803180311477</v>
       </c>
       <c r="D443" t="s">
         <v>7</v>
@@ -11874,7 +11874,7 @@
         <v>10</v>
       </c>
       <c r="C444">
-        <v>0.3355704920167318</v>
+        <v>0.3288333500761927</v>
       </c>
       <c r="D444" t="s">
         <v>7</v>
@@ -11891,7 +11891,7 @@
         <v>6</v>
       </c>
       <c r="C445">
-        <v>0.3796182485996014</v>
+        <v>0.3903356790911203</v>
       </c>
       <c r="D445" t="s">
         <v>7</v>
@@ -11908,7 +11908,7 @@
         <v>44</v>
       </c>
       <c r="C446">
-        <v>0.3438515825475766</v>
+        <v>0.3341611918108894</v>
       </c>
       <c r="D446" t="s">
         <v>7</v>
@@ -11925,7 +11925,7 @@
         <v>6</v>
       </c>
       <c r="C447">
-        <v>0.2855020007596275</v>
+        <v>0.2992231081618633</v>
       </c>
       <c r="D447" t="s">
         <v>7</v>
@@ -11942,7 +11942,7 @@
         <v>6</v>
       </c>
       <c r="C448">
-        <v>0.3884933866693064</v>
+        <v>0.3996519121181489</v>
       </c>
       <c r="D448" t="s">
         <v>7</v>
@@ -11959,7 +11959,7 @@
         <v>6</v>
       </c>
       <c r="C449">
-        <v>0.4200759325105389</v>
+        <v>0.4323291385311515</v>
       </c>
       <c r="D449" t="s">
         <v>7</v>
@@ -11976,7 +11976,7 @@
         <v>44</v>
       </c>
       <c r="C450">
-        <v>0.4127447292786718</v>
+        <v>0.4032082821877489</v>
       </c>
       <c r="D450" t="s">
         <v>7</v>
@@ -11993,7 +11993,7 @@
         <v>44</v>
       </c>
       <c r="C451">
-        <v>0.3893795870510624</v>
+        <v>0.3808793891628075</v>
       </c>
       <c r="D451" t="s">
         <v>7</v>
@@ -12010,7 +12010,7 @@
         <v>6</v>
       </c>
       <c r="C452">
-        <v>0.3516806434100651</v>
+        <v>0.3634855491286965</v>
       </c>
       <c r="D452" t="s">
         <v>7</v>
@@ -12027,7 +12027,7 @@
         <v>10</v>
       </c>
       <c r="C453">
-        <v>0.3538455900535299</v>
+        <v>0.3420707709748624</v>
       </c>
       <c r="D453" t="s">
         <v>7</v>
@@ -12044,7 +12044,7 @@
         <v>15</v>
       </c>
       <c r="C454">
-        <v>0.2898429874741598</v>
+        <v>0.2914084827944642</v>
       </c>
       <c r="D454" t="s">
         <v>7</v>
@@ -12061,7 +12061,7 @@
         <v>10</v>
       </c>
       <c r="C455">
-        <v>0.3476485071191834</v>
+        <v>0.3351227682972485</v>
       </c>
       <c r="D455" t="s">
         <v>7</v>
@@ -12078,7 +12078,7 @@
         <v>6</v>
       </c>
       <c r="C456">
-        <v>0.3950207462160221</v>
+        <v>0.4062710307165586</v>
       </c>
       <c r="D456" t="s">
         <v>7</v>
@@ -12095,7 +12095,7 @@
         <v>15</v>
       </c>
       <c r="C457">
-        <v>0.3645748676244241</v>
+        <v>0.3641079581717803</v>
       </c>
       <c r="D457" t="s">
         <v>7</v>
@@ -12112,7 +12112,7 @@
         <v>6</v>
       </c>
       <c r="C458">
-        <v>0.3594844704147667</v>
+        <v>0.3716892279439142</v>
       </c>
       <c r="D458" t="s">
         <v>7</v>
@@ -12129,7 +12129,7 @@
         <v>6</v>
       </c>
       <c r="C459">
-        <v>0.4067511184980228</v>
+        <v>0.4176856972719337</v>
       </c>
       <c r="D459" t="s">
         <v>7</v>
@@ -12146,7 +12146,7 @@
         <v>6</v>
       </c>
       <c r="C460">
-        <v>0.3597587044429388</v>
+        <v>0.3680824014179211</v>
       </c>
       <c r="D460" t="s">
         <v>7</v>
@@ -12160,10 +12160,10 @@
         <v>930</v>
       </c>
       <c r="B461" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C461">
-        <v>0.3060810710376915</v>
+        <v>0.315961238965417</v>
       </c>
       <c r="D461" t="s">
         <v>7</v>
@@ -12180,7 +12180,7 @@
         <v>6</v>
       </c>
       <c r="C462">
-        <v>0.3442955372881455</v>
+        <v>0.3587641331431747</v>
       </c>
       <c r="D462" t="s">
         <v>7</v>
@@ -12194,10 +12194,10 @@
         <v>934</v>
       </c>
       <c r="B463" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C463">
-        <v>0.2976647035277822</v>
+        <v>0.2959525900253683</v>
       </c>
       <c r="D463" t="s">
         <v>7</v>
@@ -12214,7 +12214,7 @@
         <v>6</v>
       </c>
       <c r="C464">
-        <v>0.4320728280331821</v>
+        <v>0.4441405108262563</v>
       </c>
       <c r="D464" t="s">
         <v>7</v>
@@ -12231,7 +12231,7 @@
         <v>44</v>
       </c>
       <c r="C465">
-        <v>0.3525267466167537</v>
+        <v>0.3451045785823223</v>
       </c>
       <c r="D465" t="s">
         <v>7</v>
@@ -12248,7 +12248,7 @@
         <v>6</v>
       </c>
       <c r="C466">
-        <v>0.5490993672664753</v>
+        <v>0.559954498053082</v>
       </c>
       <c r="D466" t="s">
         <v>7</v>
@@ -12265,7 +12265,7 @@
         <v>6</v>
       </c>
       <c r="C467">
-        <v>0.4993198117769058</v>
+        <v>0.5070579214647533</v>
       </c>
       <c r="D467" t="s">
         <v>7</v>
@@ -12282,7 +12282,7 @@
         <v>6</v>
       </c>
       <c r="C468">
-        <v>0.4013384611867765</v>
+        <v>0.4160871566845558</v>
       </c>
       <c r="D468" t="s">
         <v>7</v>
@@ -12299,7 +12299,7 @@
         <v>15</v>
       </c>
       <c r="C469">
-        <v>0.3009372241005837</v>
+        <v>0.3036936235714265</v>
       </c>
       <c r="D469" t="s">
         <v>7</v>
@@ -12313,10 +12313,10 @@
         <v>948</v>
       </c>
       <c r="B470" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C470">
-        <v>0.3061219875564219</v>
+        <v>0.310824669641773</v>
       </c>
       <c r="D470" t="s">
         <v>7</v>
@@ -12333,7 +12333,7 @@
         <v>44</v>
       </c>
       <c r="C471">
-        <v>0.3219928343149802</v>
+        <v>0.3110792519122317</v>
       </c>
       <c r="D471" t="s">
         <v>7</v>
@@ -12350,7 +12350,7 @@
         <v>15</v>
       </c>
       <c r="C472">
-        <v>0.3151888073756525</v>
+        <v>0.319101540077665</v>
       </c>
       <c r="D472" t="s">
         <v>7</v>
@@ -12367,7 +12367,7 @@
         <v>44</v>
       </c>
       <c r="C473">
-        <v>0.3201202066452111</v>
+        <v>0.3116884750881828</v>
       </c>
       <c r="D473" t="s">
         <v>7</v>
@@ -12381,10 +12381,10 @@
         <v>956</v>
       </c>
       <c r="B474" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C474">
-        <v>0.3462894162097644</v>
+        <v>0.3389900555740918</v>
       </c>
       <c r="D474" t="s">
         <v>7</v>
@@ -12401,7 +12401,7 @@
         <v>6</v>
       </c>
       <c r="C475">
-        <v>0.3496438575996575</v>
+        <v>0.3623250780778673</v>
       </c>
       <c r="D475" t="s">
         <v>7</v>
@@ -12418,7 +12418,7 @@
         <v>6</v>
       </c>
       <c r="C476">
-        <v>0.3428834552358128</v>
+        <v>0.3538805413162479</v>
       </c>
       <c r="D476" t="s">
         <v>7</v>
@@ -12432,10 +12432,10 @@
         <v>962</v>
       </c>
       <c r="B477" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C477">
-        <v>0.323048849224911</v>
+        <v>0.312372702103771</v>
       </c>
       <c r="D477" t="s">
         <v>7</v>
@@ -12452,7 +12452,7 @@
         <v>6</v>
       </c>
       <c r="C478">
-        <v>0.4098019833550145</v>
+        <v>0.4215618165511976</v>
       </c>
       <c r="D478" t="s">
         <v>7</v>
@@ -12469,7 +12469,7 @@
         <v>44</v>
       </c>
       <c r="C479">
-        <v>0.4103970402236649</v>
+        <v>0.4001566778067346</v>
       </c>
       <c r="D479" t="s">
         <v>7</v>
@@ -12486,7 +12486,7 @@
         <v>6</v>
       </c>
       <c r="C480">
-        <v>0.486092022445386</v>
+        <v>0.4975446464462833</v>
       </c>
       <c r="D480" t="s">
         <v>7</v>
@@ -12503,7 +12503,7 @@
         <v>44</v>
       </c>
       <c r="C481">
-        <v>0.368572774156839</v>
+        <v>0.3623025914536655</v>
       </c>
       <c r="D481" t="s">
         <v>7</v>
@@ -12520,7 +12520,7 @@
         <v>6</v>
       </c>
       <c r="C482">
-        <v>0.2729357947018041</v>
+        <v>0.2845303846344786</v>
       </c>
       <c r="D482" t="s">
         <v>7</v>
@@ -12534,10 +12534,10 @@
         <v>974</v>
       </c>
       <c r="B483" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C483">
-        <v>0.2956875703180566</v>
+        <v>0.2944433573754238</v>
       </c>
       <c r="D483" t="s">
         <v>7</v>
@@ -12554,7 +12554,7 @@
         <v>44</v>
       </c>
       <c r="C484">
-        <v>0.3668432457276088</v>
+        <v>0.3568733055987396</v>
       </c>
       <c r="D484" t="s">
         <v>7</v>
@@ -12571,7 +12571,7 @@
         <v>15</v>
       </c>
       <c r="C485">
-        <v>0.3707803644857839</v>
+        <v>0.3722099840685633</v>
       </c>
       <c r="D485" t="s">
         <v>7</v>
@@ -12588,7 +12588,7 @@
         <v>15</v>
       </c>
       <c r="C486">
-        <v>0.4056535128660276</v>
+        <v>0.404991989599352</v>
       </c>
       <c r="D486" t="s">
         <v>7</v>
@@ -12605,7 +12605,7 @@
         <v>44</v>
       </c>
       <c r="C487">
-        <v>0.4378168085919965</v>
+        <v>0.4323359345254725</v>
       </c>
       <c r="D487" t="s">
         <v>7</v>
@@ -12622,7 +12622,7 @@
         <v>10</v>
       </c>
       <c r="C488">
-        <v>0.279142195659259</v>
+        <v>0.2664462343663797</v>
       </c>
       <c r="D488" t="s">
         <v>7</v>
@@ -12639,7 +12639,7 @@
         <v>6</v>
       </c>
       <c r="C489">
-        <v>0.5143663148910238</v>
+        <v>0.5257863903256648</v>
       </c>
       <c r="D489" t="s">
         <v>7</v>
@@ -12656,7 +12656,7 @@
         <v>15</v>
       </c>
       <c r="C490">
-        <v>0.336425818773508</v>
+        <v>0.3406787846767886</v>
       </c>
       <c r="D490" t="s">
         <v>7</v>
@@ -12673,7 +12673,7 @@
         <v>6</v>
       </c>
       <c r="C491">
-        <v>0.3053067887332611</v>
+        <v>0.3179583450362559</v>
       </c>
       <c r="D491" t="s">
         <v>7</v>
@@ -12690,7 +12690,7 @@
         <v>6</v>
       </c>
       <c r="C492">
-        <v>0.501867033266777</v>
+        <v>0.5090904117163787</v>
       </c>
       <c r="D492" t="s">
         <v>7</v>
@@ -12707,7 +12707,7 @@
         <v>6</v>
       </c>
       <c r="C493">
-        <v>0.311945885317772</v>
+        <v>0.3266215192789174</v>
       </c>
       <c r="D493" t="s">
         <v>7</v>
@@ -12724,7 +12724,7 @@
         <v>10</v>
       </c>
       <c r="C494">
-        <v>0.2980270941299217</v>
+        <v>0.2893575723489397</v>
       </c>
       <c r="D494" t="s">
         <v>7</v>
@@ -12741,7 +12741,7 @@
         <v>44</v>
       </c>
       <c r="C495">
-        <v>0.5030032899208954</v>
+        <v>0.4987870886747073</v>
       </c>
       <c r="D495" t="s">
         <v>7</v>
@@ -12758,7 +12758,7 @@
         <v>6</v>
       </c>
       <c r="C496">
-        <v>0.5089858724634819</v>
+        <v>0.519834632376928</v>
       </c>
       <c r="D496" t="s">
         <v>7</v>
@@ -12775,7 +12775,7 @@
         <v>10</v>
       </c>
       <c r="C497">
-        <v>0.3527857158034807</v>
+        <v>0.3396803814981904</v>
       </c>
       <c r="D497" t="s">
         <v>7</v>
@@ -12792,7 +12792,7 @@
         <v>6</v>
       </c>
       <c r="C498">
-        <v>0.6695383317942755</v>
+        <v>0.6761671687299718</v>
       </c>
       <c r="D498" t="s">
         <v>7</v>
@@ -12809,7 +12809,7 @@
         <v>15</v>
       </c>
       <c r="C499">
-        <v>0.3446121378870369</v>
+        <v>0.3473675714186414</v>
       </c>
       <c r="D499" t="s">
         <v>7</v>
@@ -12826,7 +12826,7 @@
         <v>6</v>
       </c>
       <c r="C500">
-        <v>0.4514427572057305</v>
+        <v>0.4617075998454622</v>
       </c>
       <c r="D500" t="s">
         <v>7</v>
@@ -12843,7 +12843,7 @@
         <v>15</v>
       </c>
       <c r="C501">
-        <v>0.4217077243969311</v>
+        <v>0.4215186073404895</v>
       </c>
       <c r="D501" t="s">
         <v>7</v>
@@ -12860,7 +12860,7 @@
         <v>6</v>
       </c>
       <c r="C502">
-        <v>0.5918399585207635</v>
+        <v>0.5974032914677929</v>
       </c>
       <c r="D502" t="s">
         <v>7</v>
@@ -12877,7 +12877,7 @@
         <v>15</v>
       </c>
       <c r="C503">
-        <v>0.3619648655297907</v>
+        <v>0.3632921331179927</v>
       </c>
       <c r="D503" t="s">
         <v>7</v>
@@ -12894,7 +12894,7 @@
         <v>15</v>
       </c>
       <c r="C504">
-        <v>0.3301698473845137</v>
+        <v>0.3323556895979893</v>
       </c>
       <c r="D504" t="s">
         <v>7</v>
@@ -12911,7 +12911,7 @@
         <v>6</v>
       </c>
       <c r="C505">
-        <v>0.4633196054288258</v>
+        <v>0.4742675728342634</v>
       </c>
       <c r="D505" t="s">
         <v>7</v>
@@ -12928,7 +12928,7 @@
         <v>15</v>
       </c>
       <c r="C506">
-        <v>0.4949437653422113</v>
+        <v>0.4938964731857792</v>
       </c>
       <c r="D506" t="s">
         <v>7</v>
@@ -12945,7 +12945,7 @@
         <v>6</v>
       </c>
       <c r="C507">
-        <v>0.3436856149775744</v>
+        <v>0.3578671454418533</v>
       </c>
       <c r="D507" t="s">
         <v>7</v>
@@ -12962,7 +12962,7 @@
         <v>15</v>
       </c>
       <c r="C508">
-        <v>0.3305577369364911</v>
+        <v>0.3327277441120651</v>
       </c>
       <c r="D508" t="s">
         <v>7</v>
@@ -12979,7 +12979,7 @@
         <v>10</v>
       </c>
       <c r="C509">
-        <v>0.4738067417067568</v>
+        <v>0.4636850741696669</v>
       </c>
       <c r="D509" t="s">
         <v>7</v>
@@ -12996,7 +12996,7 @@
         <v>10</v>
       </c>
       <c r="C510">
-        <v>0.3567517384182431</v>
+        <v>0.3434269996685428</v>
       </c>
       <c r="D510" t="s">
         <v>7</v>
@@ -13013,7 +13013,7 @@
         <v>44</v>
       </c>
       <c r="C511">
-        <v>0.3439636144449801</v>
+        <v>0.3318059001258545</v>
       </c>
       <c r="D511" t="s">
         <v>7</v>
@@ -13030,7 +13030,7 @@
         <v>6</v>
       </c>
       <c r="C512">
-        <v>0.3135169645387443</v>
+        <v>0.3245033109525624</v>
       </c>
       <c r="D512" t="s">
         <v>7</v>
@@ -13047,7 +13047,7 @@
         <v>6</v>
       </c>
       <c r="C513">
-        <v>0.3820465069050213</v>
+        <v>0.3928126810720414</v>
       </c>
       <c r="D513" t="s">
         <v>7</v>
@@ -13064,7 +13064,7 @@
         <v>44</v>
       </c>
       <c r="C514">
-        <v>0.3948820853399574</v>
+        <v>0.3851928333215255</v>
       </c>
       <c r="D514" t="s">
         <v>7</v>
@@ -13081,7 +13081,7 @@
         <v>6</v>
       </c>
       <c r="C515">
-        <v>0.5163065173556722</v>
+        <v>0.5255465895838465</v>
       </c>
       <c r="D515" t="s">
         <v>7</v>
@@ -13095,10 +13095,10 @@
         <v>1040</v>
       </c>
       <c r="B516" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C516">
-        <v>0.3155808600342381</v>
+        <v>0.3183298173721873</v>
       </c>
       <c r="D516" t="s">
         <v>7</v>
@@ -13115,7 +13115,7 @@
         <v>15</v>
       </c>
       <c r="C517">
-        <v>0.3511461134944553</v>
+        <v>0.3538022752668876</v>
       </c>
       <c r="D517" t="s">
         <v>7</v>
@@ -13132,7 +13132,7 @@
         <v>10</v>
       </c>
       <c r="C518">
-        <v>0.3083680559609567</v>
+        <v>0.2972484167886799</v>
       </c>
       <c r="D518" t="s">
         <v>7</v>
@@ -13149,7 +13149,7 @@
         <v>44</v>
       </c>
       <c r="C519">
-        <v>0.5044870779999142</v>
+        <v>0.5024211308031022</v>
       </c>
       <c r="D519" t="s">
         <v>7</v>
@@ -13166,7 +13166,7 @@
         <v>15</v>
       </c>
       <c r="C520">
-        <v>0.3335748896183803</v>
+        <v>0.335990314202335</v>
       </c>
       <c r="D520" t="s">
         <v>7</v>
@@ -13183,7 +13183,7 @@
         <v>10</v>
       </c>
       <c r="C521">
-        <v>0.3051630097965268</v>
+        <v>0.2929376359647182</v>
       </c>
       <c r="D521" t="s">
         <v>7</v>
@@ -13200,7 +13200,7 @@
         <v>15</v>
       </c>
       <c r="C522">
-        <v>0.351134088103789</v>
+        <v>0.3524487252497951</v>
       </c>
       <c r="D522" t="s">
         <v>7</v>
@@ -13217,7 +13217,7 @@
         <v>6</v>
       </c>
       <c r="C523">
-        <v>0.4564942987577268</v>
+        <v>0.465531796365688</v>
       </c>
       <c r="D523" t="s">
         <v>7</v>
@@ -13234,7 +13234,7 @@
         <v>6</v>
       </c>
       <c r="C524">
-        <v>0.3106424373176639</v>
+        <v>0.3195929657248891</v>
       </c>
       <c r="D524" t="s">
         <v>7</v>
@@ -13251,7 +13251,7 @@
         <v>44</v>
       </c>
       <c r="C525">
-        <v>0.3895854153835558</v>
+        <v>0.3786037708033582</v>
       </c>
       <c r="D525" t="s">
         <v>7</v>
@@ -13268,7 +13268,7 @@
         <v>44</v>
       </c>
       <c r="C526">
-        <v>0.4926813029054473</v>
+        <v>0.4851178902837471</v>
       </c>
       <c r="D526" t="s">
         <v>7</v>
@@ -13285,7 +13285,7 @@
         <v>10</v>
       </c>
       <c r="C527">
-        <v>0.3828934815847183</v>
+        <v>0.3704970276092567</v>
       </c>
       <c r="D527" t="s">
         <v>7</v>
@@ -13302,7 +13302,7 @@
         <v>6</v>
       </c>
       <c r="C528">
-        <v>0.4638222900968532</v>
+        <v>0.4773208460689147</v>
       </c>
       <c r="D528" t="s">
         <v>7</v>
@@ -13319,7 +13319,7 @@
         <v>10</v>
       </c>
       <c r="C529">
-        <v>0.3180985252452098</v>
+        <v>0.3073714743039998</v>
       </c>
       <c r="D529" t="s">
         <v>7</v>
@@ -13336,7 +13336,7 @@
         <v>44</v>
       </c>
       <c r="C530">
-        <v>0.4985454879130852</v>
+        <v>0.4948554555083374</v>
       </c>
       <c r="D530" t="s">
         <v>7</v>
@@ -13353,7 +13353,7 @@
         <v>44</v>
       </c>
       <c r="C531">
-        <v>0.5290168824408702</v>
+        <v>0.5276301795658149</v>
       </c>
       <c r="D531" t="s">
         <v>7</v>
@@ -13370,7 +13370,7 @@
         <v>10</v>
       </c>
       <c r="C532">
-        <v>0.2750165799870084</v>
+        <v>0.2669254770600861</v>
       </c>
       <c r="D532" t="s">
         <v>7</v>
@@ -13387,7 +13387,7 @@
         <v>15</v>
       </c>
       <c r="C533">
-        <v>0.4858357765086512</v>
+        <v>0.4851203837319838</v>
       </c>
       <c r="D533" t="s">
         <v>7</v>
@@ -13404,7 +13404,7 @@
         <v>15</v>
       </c>
       <c r="C534">
-        <v>0.3345964354423055</v>
+        <v>0.3349284041750403</v>
       </c>
       <c r="D534" t="s">
         <v>7</v>
@@ -13421,7 +13421,7 @@
         <v>6</v>
       </c>
       <c r="C535">
-        <v>0.3249625081240264</v>
+        <v>0.3362937749854033</v>
       </c>
       <c r="D535" t="s">
         <v>7</v>
@@ -13438,7 +13438,7 @@
         <v>6</v>
       </c>
       <c r="C536">
-        <v>0.3272526722983137</v>
+        <v>0.3391245663853532</v>
       </c>
       <c r="D536" t="s">
         <v>7</v>
@@ -13455,7 +13455,7 @@
         <v>6</v>
       </c>
       <c r="C537">
-        <v>0.3998050112308191</v>
+        <v>0.4105024521454541</v>
       </c>
       <c r="D537" t="s">
         <v>7</v>
@@ -13472,7 +13472,7 @@
         <v>15</v>
       </c>
       <c r="C538">
-        <v>0.293323083844064</v>
+        <v>0.2957197802619093</v>
       </c>
       <c r="D538" t="s">
         <v>7</v>
@@ -13489,7 +13489,7 @@
         <v>6</v>
       </c>
       <c r="C539">
-        <v>0.3111131217512075</v>
+        <v>0.3223440885510908</v>
       </c>
       <c r="D539" t="s">
         <v>7</v>
@@ -13506,7 +13506,7 @@
         <v>15</v>
       </c>
       <c r="C540">
-        <v>0.2704941391778484</v>
+        <v>0.2723726852424826</v>
       </c>
       <c r="D540" t="s">
         <v>7</v>
@@ -13523,7 +13523,7 @@
         <v>6</v>
       </c>
       <c r="C541">
-        <v>0.4274418418957602</v>
+        <v>0.4359240499389753</v>
       </c>
       <c r="D541" t="s">
         <v>7</v>
@@ -13540,7 +13540,7 @@
         <v>44</v>
       </c>
       <c r="C542">
-        <v>0.3718594706334718</v>
+        <v>0.3619748762818268</v>
       </c>
       <c r="D542" t="s">
         <v>7</v>
@@ -13557,7 +13557,7 @@
         <v>6</v>
       </c>
       <c r="C543">
-        <v>0.4319448756113557</v>
+        <v>0.443636510935222</v>
       </c>
       <c r="D543" t="s">
         <v>7</v>
@@ -13574,7 +13574,7 @@
         <v>6</v>
       </c>
       <c r="C544">
-        <v>0.4141164910707301</v>
+        <v>0.4289519883795928</v>
       </c>
       <c r="D544" t="s">
         <v>7</v>
@@ -14812,7 +14812,7 @@
         <v>6</v>
       </c>
       <c r="C620">
-        <v>0.3208740786197954</v>
+        <v>0.3319525456876453</v>
       </c>
       <c r="D620" t="s">
         <v>1259</v>
@@ -14829,7 +14829,7 @@
         <v>15</v>
       </c>
       <c r="C621">
-        <v>0.2849908240552963</v>
+        <v>0.3504011928859856</v>
       </c>
       <c r="D621" t="s">
         <v>1259</v>
@@ -14846,7 +14846,7 @@
         <v>6</v>
       </c>
       <c r="C622">
-        <v>0.2689692625739072</v>
+        <v>0.2805348231654675</v>
       </c>
       <c r="D622" t="s">
         <v>1259</v>
@@ -14863,7 +14863,7 @@
         <v>1266</v>
       </c>
       <c r="C623">
-        <v>0.2506124707651516</v>
+        <v>0.2144867233283977</v>
       </c>
       <c r="D623" t="s">
         <v>1259</v>
@@ -14880,7 +14880,7 @@
         <v>10</v>
       </c>
       <c r="C624">
-        <v>0.32873480287471</v>
+        <v>0.3068739601967791</v>
       </c>
       <c r="D624" t="s">
         <v>1259</v>
@@ -14897,7 +14897,7 @@
         <v>10</v>
       </c>
       <c r="C625">
-        <v>0.2714908099689861</v>
+        <v>0.2541124991815008</v>
       </c>
       <c r="D625" t="s">
         <v>1259</v>
@@ -14911,10 +14911,10 @@
         <v>1272</v>
       </c>
       <c r="B626" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C626">
-        <v>0.2883791463376097</v>
+        <v>0.355596308414829</v>
       </c>
       <c r="D626" t="s">
         <v>1259</v>
@@ -14931,7 +14931,7 @@
         <v>1266</v>
       </c>
       <c r="C627">
-        <v>0.3216437950931499</v>
+        <v>0.2815415376198599</v>
       </c>
       <c r="D627" t="s">
         <v>1259</v>
@@ -14945,10 +14945,10 @@
         <v>1276</v>
       </c>
       <c r="B628" t="s">
-        <v>1266</v>
+        <v>6</v>
       </c>
       <c r="C628">
-        <v>0.2495800351792938</v>
+        <v>0.237864130896577</v>
       </c>
       <c r="D628" t="s">
         <v>1259</v>
@@ -14965,7 +14965,7 @@
         <v>6</v>
       </c>
       <c r="C629">
-        <v>0.2592465372568677</v>
+        <v>0.2761093716323665</v>
       </c>
       <c r="D629" t="s">
         <v>1259</v>
@@ -14982,7 +14982,7 @@
         <v>1266</v>
       </c>
       <c r="C630">
-        <v>0.3544400377676947</v>
+        <v>0.3045400551210535</v>
       </c>
       <c r="D630" t="s">
         <v>1259</v>
@@ -14999,7 +14999,7 @@
         <v>1266</v>
       </c>
       <c r="C631">
-        <v>0.3410032757419665</v>
+        <v>0.3023629207555387</v>
       </c>
       <c r="D631" t="s">
         <v>1259</v>
@@ -15016,7 +15016,7 @@
         <v>1266</v>
       </c>
       <c r="C632">
-        <v>0.4392612962612498</v>
+        <v>0.3924141789197788</v>
       </c>
       <c r="D632" t="s">
         <v>1259</v>
@@ -15030,10 +15030,10 @@
         <v>1286</v>
       </c>
       <c r="B633" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C633">
-        <v>0.263016991224886</v>
+        <v>0.266199210429178</v>
       </c>
       <c r="D633" t="s">
         <v>1259</v>
@@ -15050,7 +15050,7 @@
         <v>15</v>
       </c>
       <c r="C634">
-        <v>0.356576973165613</v>
+        <v>0.4193210875139612</v>
       </c>
       <c r="D634" t="s">
         <v>1259</v>
@@ -15067,7 +15067,7 @@
         <v>1266</v>
       </c>
       <c r="C635">
-        <v>0.4975052542390138</v>
+        <v>0.4572059829506785</v>
       </c>
       <c r="D635" t="s">
         <v>1259</v>
@@ -15084,7 +15084,7 @@
         <v>6</v>
       </c>
       <c r="C636">
-        <v>0.3661746535485418</v>
+        <v>0.3777014908825693</v>
       </c>
       <c r="D636" t="s">
         <v>1259</v>
@@ -15098,10 +15098,10 @@
         <v>1294</v>
       </c>
       <c r="B637" t="s">
-        <v>1266</v>
+        <v>15</v>
       </c>
       <c r="C637">
-        <v>0.2859552120957903</v>
+        <v>0.2959923307669016</v>
       </c>
       <c r="D637" t="s">
         <v>1259</v>
@@ -15118,7 +15118,7 @@
         <v>1266</v>
       </c>
       <c r="C638">
-        <v>0.4472031298499361</v>
+        <v>0.4226175453429617</v>
       </c>
       <c r="D638" t="s">
         <v>1259</v>
@@ -15135,7 +15135,7 @@
         <v>10</v>
       </c>
       <c r="C639">
-        <v>0.3728624558060826</v>
+        <v>0.3489875328904459</v>
       </c>
       <c r="D639" t="s">
         <v>1259</v>
@@ -15152,7 +15152,7 @@
         <v>10</v>
       </c>
       <c r="C640">
-        <v>0.331998191773518</v>
+        <v>0.3169804919734888</v>
       </c>
       <c r="D640" t="s">
         <v>1259</v>
@@ -15166,10 +15166,10 @@
         <v>1302</v>
       </c>
       <c r="B641" t="s">
-        <v>1266</v>
+        <v>15</v>
       </c>
       <c r="C641">
-        <v>0.2407356937882281</v>
+        <v>0.271411162011699</v>
       </c>
       <c r="D641" t="s">
         <v>1259</v>
@@ -15186,7 +15186,7 @@
         <v>1266</v>
       </c>
       <c r="C642">
-        <v>0.3250894978954148</v>
+        <v>0.2806589337190684</v>
       </c>
       <c r="D642" t="s">
         <v>1259</v>
@@ -15203,7 +15203,7 @@
         <v>15</v>
       </c>
       <c r="C643">
-        <v>0.2720783336877807</v>
+        <v>0.3389726408126501</v>
       </c>
       <c r="D643" t="s">
         <v>1259</v>
@@ -15220,7 +15220,7 @@
         <v>15</v>
       </c>
       <c r="C644">
-        <v>0.2268079677148513</v>
+        <v>0.287455373196221</v>
       </c>
       <c r="D644" t="s">
         <v>1259</v>
@@ -15234,10 +15234,10 @@
         <v>1310</v>
       </c>
       <c r="B645" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C645">
-        <v>0.2559367048804051</v>
+        <v>0.2462174825244853</v>
       </c>
       <c r="D645" t="s">
         <v>1259</v>
@@ -15254,7 +15254,7 @@
         <v>15</v>
       </c>
       <c r="C646">
-        <v>0.302340233593975</v>
+        <v>0.364796663607433</v>
       </c>
       <c r="D646" t="s">
         <v>1259</v>
@@ -15271,7 +15271,7 @@
         <v>6</v>
       </c>
       <c r="C647">
-        <v>0.2908053135072795</v>
+        <v>0.3036479444602142</v>
       </c>
       <c r="D647" t="s">
         <v>1259</v>
@@ -15288,7 +15288,7 @@
         <v>15</v>
       </c>
       <c r="C648">
-        <v>0.2425098874253842</v>
+        <v>0.3054060374661127</v>
       </c>
       <c r="D648" t="s">
         <v>1259</v>
@@ -15305,7 +15305,7 @@
         <v>15</v>
       </c>
       <c r="C649">
-        <v>0.2847068048881836</v>
+        <v>0.3510506841049136</v>
       </c>
       <c r="D649" t="s">
         <v>1259</v>
@@ -15322,7 +15322,7 @@
         <v>6</v>
       </c>
       <c r="C650">
-        <v>0.2724851214034243</v>
+        <v>0.2877237139124142</v>
       </c>
       <c r="D650" t="s">
         <v>1259</v>
@@ -15339,7 +15339,7 @@
         <v>15</v>
       </c>
       <c r="C651">
-        <v>0.2623149712659195</v>
+        <v>0.3293679373909073</v>
       </c>
       <c r="D651" t="s">
         <v>1259</v>
@@ -15371,7 +15371,7 @@
         <v>15</v>
       </c>
       <c r="B2">
-        <v>138</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -15379,7 +15379,7 @@
         <v>10</v>
       </c>
       <c r="B3">
-        <v>103</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -15387,7 +15387,7 @@
         <v>145</v>
       </c>
       <c r="B4">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -15395,7 +15395,7 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>262</v>
+        <v>275</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -15403,7 +15403,7 @@
         <v>44</v>
       </c>
       <c r="B6">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -15419,7 +15419,7 @@
         <v>1266</v>
       </c>
       <c r="B8">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:2">

--- a/frontend/data/uk_election_predictions.xlsx
+++ b/frontend/data/uk_election_predictions.xlsx
@@ -4360,7 +4360,7 @@
         <v>6</v>
       </c>
       <c r="C2">
-        <v>0.3177513979729616</v>
+        <v>0.3158298632012356</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
@@ -4377,7 +4377,7 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>0.3822886088806316</v>
+        <v>0.4170444037015363</v>
       </c>
       <c r="D3" t="s">
         <v>7</v>
@@ -4394,7 +4394,7 @@
         <v>6</v>
       </c>
       <c r="C4">
-        <v>0.4137669402890238</v>
+        <v>0.4095832248088022</v>
       </c>
       <c r="D4" t="s">
         <v>7</v>
@@ -4411,7 +4411,7 @@
         <v>15</v>
       </c>
       <c r="C5">
-        <v>0.3850388772697</v>
+        <v>0.3762127555490866</v>
       </c>
       <c r="D5" t="s">
         <v>7</v>
@@ -4428,7 +4428,7 @@
         <v>10</v>
       </c>
       <c r="C6">
-        <v>0.369139315511929</v>
+        <v>0.4035352261672355</v>
       </c>
       <c r="D6" t="s">
         <v>7</v>
@@ -4445,7 +4445,7 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>0.331339904195997</v>
+        <v>0.3271217282075017</v>
       </c>
       <c r="D7" t="s">
         <v>7</v>
@@ -4462,7 +4462,7 @@
         <v>15</v>
       </c>
       <c r="C8">
-        <v>0.3485156812299325</v>
+        <v>0.3419455909874243</v>
       </c>
       <c r="D8" t="s">
         <v>7</v>
@@ -4479,7 +4479,7 @@
         <v>15</v>
       </c>
       <c r="C9">
-        <v>0.3219436675263968</v>
+        <v>0.3176690922632786</v>
       </c>
       <c r="D9" t="s">
         <v>7</v>
@@ -4496,7 +4496,7 @@
         <v>10</v>
       </c>
       <c r="C10">
-        <v>0.3065732495472183</v>
+        <v>0.3459006041814624</v>
       </c>
       <c r="D10" t="s">
         <v>7</v>
@@ -4513,7 +4513,7 @@
         <v>15</v>
       </c>
       <c r="C11">
-        <v>0.2390731334221285</v>
+        <v>0.2334339256556266</v>
       </c>
       <c r="D11" t="s">
         <v>7</v>
@@ -4530,7 +4530,7 @@
         <v>6</v>
       </c>
       <c r="C12">
-        <v>0.4055858717063986</v>
+        <v>0.4060904401002813</v>
       </c>
       <c r="D12" t="s">
         <v>7</v>
@@ -4547,7 +4547,7 @@
         <v>15</v>
       </c>
       <c r="C13">
-        <v>0.3042740836874898</v>
+        <v>0.3009096488649104</v>
       </c>
       <c r="D13" t="s">
         <v>7</v>
@@ -4564,7 +4564,7 @@
         <v>15</v>
       </c>
       <c r="C14">
-        <v>0.3893338233574824</v>
+        <v>0.3857374691884548</v>
       </c>
       <c r="D14" t="s">
         <v>7</v>
@@ -4581,7 +4581,7 @@
         <v>10</v>
       </c>
       <c r="C15">
-        <v>0.3367846366770625</v>
+        <v>0.3747215671985894</v>
       </c>
       <c r="D15" t="s">
         <v>7</v>
@@ -4598,7 +4598,7 @@
         <v>6</v>
       </c>
       <c r="C16">
-        <v>0.3521276997982936</v>
+        <v>0.3517519406423954</v>
       </c>
       <c r="D16" t="s">
         <v>7</v>
@@ -4615,7 +4615,7 @@
         <v>15</v>
       </c>
       <c r="C17">
-        <v>0.2848509169148288</v>
+        <v>0.2792829728117687</v>
       </c>
       <c r="D17" t="s">
         <v>7</v>
@@ -4632,7 +4632,7 @@
         <v>10</v>
       </c>
       <c r="C18">
-        <v>0.2954495075615227</v>
+        <v>0.3351635031070885</v>
       </c>
       <c r="D18" t="s">
         <v>7</v>
@@ -4649,7 +4649,7 @@
         <v>44</v>
       </c>
       <c r="C19">
-        <v>0.4266081040175916</v>
+        <v>0.4140024019375394</v>
       </c>
       <c r="D19" t="s">
         <v>7</v>
@@ -4666,7 +4666,7 @@
         <v>6</v>
       </c>
       <c r="C20">
-        <v>0.4685072603721165</v>
+        <v>0.4678675852627772</v>
       </c>
       <c r="D20" t="s">
         <v>7</v>
@@ -4683,7 +4683,7 @@
         <v>10</v>
       </c>
       <c r="C21">
-        <v>0.3834230492516509</v>
+        <v>0.4136646496930757</v>
       </c>
       <c r="D21" t="s">
         <v>7</v>
@@ -4700,7 +4700,7 @@
         <v>6</v>
       </c>
       <c r="C22">
-        <v>0.3779259080982248</v>
+        <v>0.3761993168499339</v>
       </c>
       <c r="D22" t="s">
         <v>7</v>
@@ -4717,7 +4717,7 @@
         <v>6</v>
       </c>
       <c r="C23">
-        <v>0.478089320108933</v>
+        <v>0.4741726427018033</v>
       </c>
       <c r="D23" t="s">
         <v>7</v>
@@ -4734,7 +4734,7 @@
         <v>6</v>
       </c>
       <c r="C24">
-        <v>0.361556768086219</v>
+        <v>0.3691401242389403</v>
       </c>
       <c r="D24" t="s">
         <v>7</v>
@@ -4751,7 +4751,7 @@
         <v>6</v>
       </c>
       <c r="C25">
-        <v>0.6250156488544485</v>
+        <v>0.6332002844517933</v>
       </c>
       <c r="D25" t="s">
         <v>7</v>
@@ -4765,10 +4765,10 @@
         <v>58</v>
       </c>
       <c r="B26" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C26">
-        <v>0.3017749185340396</v>
+        <v>0.2977253740788202</v>
       </c>
       <c r="D26" t="s">
         <v>7</v>
@@ -4782,10 +4782,10 @@
         <v>60</v>
       </c>
       <c r="B27" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C27">
-        <v>0.2888142944367904</v>
+        <v>0.3022335968007251</v>
       </c>
       <c r="D27" t="s">
         <v>7</v>
@@ -4802,7 +4802,7 @@
         <v>6</v>
       </c>
       <c r="C28">
-        <v>0.3395525933544372</v>
+        <v>0.334852236713102</v>
       </c>
       <c r="D28" t="s">
         <v>7</v>
@@ -4819,7 +4819,7 @@
         <v>44</v>
       </c>
       <c r="C29">
-        <v>0.4280611996691047</v>
+        <v>0.4143323663316881</v>
       </c>
       <c r="D29" t="s">
         <v>7</v>
@@ -4836,7 +4836,7 @@
         <v>6</v>
       </c>
       <c r="C30">
-        <v>0.3897713621363565</v>
+        <v>0.3941533406287126</v>
       </c>
       <c r="D30" t="s">
         <v>7</v>
@@ -4853,7 +4853,7 @@
         <v>6</v>
       </c>
       <c r="C31">
-        <v>0.4667570003921129</v>
+        <v>0.4619460120617174</v>
       </c>
       <c r="D31" t="s">
         <v>7</v>
@@ -4870,7 +4870,7 @@
         <v>15</v>
       </c>
       <c r="C32">
-        <v>0.4150797994520152</v>
+        <v>0.4052856278201252</v>
       </c>
       <c r="D32" t="s">
         <v>7</v>
@@ -4887,7 +4887,7 @@
         <v>6</v>
       </c>
       <c r="C33">
-        <v>0.4166813184098438</v>
+        <v>0.4184937967995296</v>
       </c>
       <c r="D33" t="s">
         <v>7</v>
@@ -4904,7 +4904,7 @@
         <v>15</v>
       </c>
       <c r="C34">
-        <v>0.3339177740814324</v>
+        <v>0.3261048432931341</v>
       </c>
       <c r="D34" t="s">
         <v>7</v>
@@ -4921,7 +4921,7 @@
         <v>6</v>
       </c>
       <c r="C35">
-        <v>0.4645671632420837</v>
+        <v>0.4699763975383232</v>
       </c>
       <c r="D35" t="s">
         <v>7</v>
@@ -4938,7 +4938,7 @@
         <v>6</v>
       </c>
       <c r="C36">
-        <v>0.2610495202782282</v>
+        <v>0.2642206557529245</v>
       </c>
       <c r="D36" t="s">
         <v>7</v>
@@ -4955,7 +4955,7 @@
         <v>15</v>
       </c>
       <c r="C37">
-        <v>0.324733415137741</v>
+        <v>0.3157113503486791</v>
       </c>
       <c r="D37" t="s">
         <v>7</v>
@@ -4972,7 +4972,7 @@
         <v>6</v>
       </c>
       <c r="C38">
-        <v>0.3576997206119941</v>
+        <v>0.3580053093564951</v>
       </c>
       <c r="D38" t="s">
         <v>7</v>
@@ -4989,7 +4989,7 @@
         <v>6</v>
       </c>
       <c r="C39">
-        <v>0.3268810936023725</v>
+        <v>0.3271940004446663</v>
       </c>
       <c r="D39" t="s">
         <v>7</v>
@@ -5006,7 +5006,7 @@
         <v>6</v>
       </c>
       <c r="C40">
-        <v>0.5044391390868795</v>
+        <v>0.4990842907684948</v>
       </c>
       <c r="D40" t="s">
         <v>7</v>
@@ -5023,7 +5023,7 @@
         <v>15</v>
       </c>
       <c r="C41">
-        <v>0.2953775000898723</v>
+        <v>0.2878440474171817</v>
       </c>
       <c r="D41" t="s">
         <v>7</v>
@@ -5040,7 +5040,7 @@
         <v>6</v>
       </c>
       <c r="C42">
-        <v>0.5329197933876577</v>
+        <v>0.5342198938349695</v>
       </c>
       <c r="D42" t="s">
         <v>7</v>
@@ -5057,7 +5057,7 @@
         <v>15</v>
       </c>
       <c r="C43">
-        <v>0.4099366288116458</v>
+        <v>0.3972028728118709</v>
       </c>
       <c r="D43" t="s">
         <v>7</v>
@@ -5074,7 +5074,7 @@
         <v>15</v>
       </c>
       <c r="C44">
-        <v>0.4414358167626309</v>
+        <v>0.4302687431788437</v>
       </c>
       <c r="D44" t="s">
         <v>7</v>
@@ -5091,7 +5091,7 @@
         <v>6</v>
       </c>
       <c r="C45">
-        <v>0.4273475191209967</v>
+        <v>0.4272971128029849</v>
       </c>
       <c r="D45" t="s">
         <v>7</v>
@@ -5108,7 +5108,7 @@
         <v>6</v>
       </c>
       <c r="C46">
-        <v>0.4170379215983832</v>
+        <v>0.4112099297307124</v>
       </c>
       <c r="D46" t="s">
         <v>7</v>
@@ -5125,7 +5125,7 @@
         <v>15</v>
       </c>
       <c r="C47">
-        <v>0.3036730784295011</v>
+        <v>0.2979508968083778</v>
       </c>
       <c r="D47" t="s">
         <v>7</v>
@@ -5142,7 +5142,7 @@
         <v>15</v>
       </c>
       <c r="C48">
-        <v>0.4211371320304504</v>
+        <v>0.4101544563660858</v>
       </c>
       <c r="D48" t="s">
         <v>7</v>
@@ -5159,7 +5159,7 @@
         <v>15</v>
       </c>
       <c r="C49">
-        <v>0.332672869972364</v>
+        <v>0.3272678135796174</v>
       </c>
       <c r="D49" t="s">
         <v>7</v>
@@ -5176,7 +5176,7 @@
         <v>15</v>
       </c>
       <c r="C50">
-        <v>0.3723946640151131</v>
+        <v>0.3649779141397826</v>
       </c>
       <c r="D50" t="s">
         <v>7</v>
@@ -5193,7 +5193,7 @@
         <v>15</v>
       </c>
       <c r="C51">
-        <v>0.3586566036047759</v>
+        <v>0.3538810794362612</v>
       </c>
       <c r="D51" t="s">
         <v>7</v>
@@ -5210,7 +5210,7 @@
         <v>6</v>
       </c>
       <c r="C52">
-        <v>0.5225519150334679</v>
+        <v>0.5219666848692265</v>
       </c>
       <c r="D52" t="s">
         <v>7</v>
@@ -5227,7 +5227,7 @@
         <v>15</v>
       </c>
       <c r="C53">
-        <v>0.4553504960372634</v>
+        <v>0.4435455076278219</v>
       </c>
       <c r="D53" t="s">
         <v>7</v>
@@ -5244,7 +5244,7 @@
         <v>6</v>
       </c>
       <c r="C54">
-        <v>0.429698151116335</v>
+        <v>0.4232129828036665</v>
       </c>
       <c r="D54" t="s">
         <v>7</v>
@@ -5261,7 +5261,7 @@
         <v>10</v>
       </c>
       <c r="C55">
-        <v>0.2674720836440906</v>
+        <v>0.3084071327643675</v>
       </c>
       <c r="D55" t="s">
         <v>7</v>
@@ -5278,7 +5278,7 @@
         <v>10</v>
       </c>
       <c r="C56">
-        <v>0.3588373758523407</v>
+        <v>0.3971496627461939</v>
       </c>
       <c r="D56" t="s">
         <v>7</v>
@@ -5295,7 +5295,7 @@
         <v>6</v>
       </c>
       <c r="C57">
-        <v>0.5630588465036649</v>
+        <v>0.5606328969826607</v>
       </c>
       <c r="D57" t="s">
         <v>7</v>
@@ -5312,7 +5312,7 @@
         <v>6</v>
       </c>
       <c r="C58">
-        <v>0.3405618819979059</v>
+        <v>0.3398605041805914</v>
       </c>
       <c r="D58" t="s">
         <v>7</v>
@@ -5329,7 +5329,7 @@
         <v>6</v>
       </c>
       <c r="C59">
-        <v>0.3770830623050745</v>
+        <v>0.3808000382673555</v>
       </c>
       <c r="D59" t="s">
         <v>7</v>
@@ -5346,7 +5346,7 @@
         <v>6</v>
       </c>
       <c r="C60">
-        <v>0.3335419468111263</v>
+        <v>0.331093726181319</v>
       </c>
       <c r="D60" t="s">
         <v>7</v>
@@ -5363,7 +5363,7 @@
         <v>6</v>
       </c>
       <c r="C61">
-        <v>0.3931710623309639</v>
+        <v>0.3904541254044435</v>
       </c>
       <c r="D61" t="s">
         <v>7</v>
@@ -5380,7 +5380,7 @@
         <v>10</v>
       </c>
       <c r="C62">
-        <v>0.34567084856782</v>
+        <v>0.38409173061561</v>
       </c>
       <c r="D62" t="s">
         <v>7</v>
@@ -5397,7 +5397,7 @@
         <v>6</v>
       </c>
       <c r="C63">
-        <v>0.3934626543689259</v>
+        <v>0.3916019857409938</v>
       </c>
       <c r="D63" t="s">
         <v>7</v>
@@ -5411,10 +5411,10 @@
         <v>134</v>
       </c>
       <c r="B64" t="s">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="C64">
-        <v>0.2251742171408301</v>
+        <v>0.2171101312986917</v>
       </c>
       <c r="D64" t="s">
         <v>7</v>
@@ -5428,10 +5428,10 @@
         <v>136</v>
       </c>
       <c r="B65" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C65">
-        <v>0.2942482472951895</v>
+        <v>0.3343357453896617</v>
       </c>
       <c r="D65" t="s">
         <v>7</v>
@@ -5445,10 +5445,10 @@
         <v>138</v>
       </c>
       <c r="B66" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C66">
-        <v>0.3280505731616938</v>
+        <v>0.3305622871969564</v>
       </c>
       <c r="D66" t="s">
         <v>7</v>
@@ -5465,7 +5465,7 @@
         <v>15</v>
       </c>
       <c r="C67">
-        <v>0.3483205437453036</v>
+        <v>0.3412152827432141</v>
       </c>
       <c r="D67" t="s">
         <v>7</v>
@@ -5482,7 +5482,7 @@
         <v>6</v>
       </c>
       <c r="C68">
-        <v>0.3353712974152576</v>
+        <v>0.3361653849620436</v>
       </c>
       <c r="D68" t="s">
         <v>7</v>
@@ -5499,7 +5499,7 @@
         <v>145</v>
       </c>
       <c r="C69">
-        <v>0.5099338211860865</v>
+        <v>0.4920359085785033</v>
       </c>
       <c r="D69" t="s">
         <v>7</v>
@@ -5516,7 +5516,7 @@
         <v>145</v>
       </c>
       <c r="C70">
-        <v>0.4624613446015777</v>
+        <v>0.4470149162551847</v>
       </c>
       <c r="D70" t="s">
         <v>7</v>
@@ -5533,7 +5533,7 @@
         <v>6</v>
       </c>
       <c r="C71">
-        <v>0.5027631421569684</v>
+        <v>0.5045796357270991</v>
       </c>
       <c r="D71" t="s">
         <v>7</v>
@@ -5550,7 +5550,7 @@
         <v>6</v>
       </c>
       <c r="C72">
-        <v>0.4009667907789304</v>
+        <v>0.4045537161238438</v>
       </c>
       <c r="D72" t="s">
         <v>7</v>
@@ -5567,7 +5567,7 @@
         <v>6</v>
       </c>
       <c r="C73">
-        <v>0.5353513871718116</v>
+        <v>0.53502623039927</v>
       </c>
       <c r="D73" t="s">
         <v>7</v>
@@ -5584,7 +5584,7 @@
         <v>6</v>
       </c>
       <c r="C74">
-        <v>0.5181991891948154</v>
+        <v>0.5212676224270958</v>
       </c>
       <c r="D74" t="s">
         <v>7</v>
@@ -5601,7 +5601,7 @@
         <v>10</v>
       </c>
       <c r="C75">
-        <v>0.2846022320059888</v>
+        <v>0.3245871751855626</v>
       </c>
       <c r="D75" t="s">
         <v>7</v>
@@ -5618,7 +5618,7 @@
         <v>10</v>
       </c>
       <c r="C76">
-        <v>0.3249482004824814</v>
+        <v>0.3656065436594801</v>
       </c>
       <c r="D76" t="s">
         <v>7</v>
@@ -5635,7 +5635,7 @@
         <v>10</v>
       </c>
       <c r="C77">
-        <v>0.3120826786182517</v>
+        <v>0.3516877558864219</v>
       </c>
       <c r="D77" t="s">
         <v>7</v>
@@ -5652,7 +5652,7 @@
         <v>10</v>
       </c>
       <c r="C78">
-        <v>0.4204544375090389</v>
+        <v>0.4569795710170764</v>
       </c>
       <c r="D78" t="s">
         <v>7</v>
@@ -5666,10 +5666,10 @@
         <v>165</v>
       </c>
       <c r="B79" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C79">
-        <v>0.2740414878838242</v>
+        <v>0.2916008254186891</v>
       </c>
       <c r="D79" t="s">
         <v>7</v>
@@ -5686,7 +5686,7 @@
         <v>10</v>
       </c>
       <c r="C80">
-        <v>0.3533033205049024</v>
+        <v>0.389934579094351</v>
       </c>
       <c r="D80" t="s">
         <v>7</v>
@@ -5703,7 +5703,7 @@
         <v>15</v>
       </c>
       <c r="C81">
-        <v>0.3005895488572687</v>
+        <v>0.2963947130938034</v>
       </c>
       <c r="D81" t="s">
         <v>7</v>
@@ -5720,7 +5720,7 @@
         <v>10</v>
       </c>
       <c r="C82">
-        <v>0.414837313563022</v>
+        <v>0.454365533690675</v>
       </c>
       <c r="D82" t="s">
         <v>7</v>
@@ -5737,7 +5737,7 @@
         <v>6</v>
       </c>
       <c r="C83">
-        <v>0.4229069046608408</v>
+        <v>0.4183828911842116</v>
       </c>
       <c r="D83" t="s">
         <v>7</v>
@@ -5751,10 +5751,10 @@
         <v>175</v>
       </c>
       <c r="B84" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C84">
-        <v>0.2941939288809385</v>
+        <v>0.3158659165682873</v>
       </c>
       <c r="D84" t="s">
         <v>7</v>
@@ -5771,7 +5771,7 @@
         <v>15</v>
       </c>
       <c r="C85">
-        <v>0.306730940958134</v>
+        <v>0.2999045532539021</v>
       </c>
       <c r="D85" t="s">
         <v>7</v>
@@ -5788,7 +5788,7 @@
         <v>6</v>
       </c>
       <c r="C86">
-        <v>0.3406293251035752</v>
+        <v>0.3410712452777739</v>
       </c>
       <c r="D86" t="s">
         <v>7</v>
@@ -5805,7 +5805,7 @@
         <v>6</v>
       </c>
       <c r="C87">
-        <v>0.3124293931316601</v>
+        <v>0.3108570030357116</v>
       </c>
       <c r="D87" t="s">
         <v>7</v>
@@ -5822,7 +5822,7 @@
         <v>6</v>
       </c>
       <c r="C88">
-        <v>0.2944485797123317</v>
+        <v>0.3008513567791751</v>
       </c>
       <c r="D88" t="s">
         <v>7</v>
@@ -5836,10 +5836,10 @@
         <v>185</v>
       </c>
       <c r="B89" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C89">
-        <v>0.3050371186895044</v>
+        <v>0.3153123502042979</v>
       </c>
       <c r="D89" t="s">
         <v>7</v>
@@ -5856,7 +5856,7 @@
         <v>10</v>
       </c>
       <c r="C90">
-        <v>0.2389255510983078</v>
+        <v>0.278376763944689</v>
       </c>
       <c r="D90" t="s">
         <v>7</v>
@@ -5873,7 +5873,7 @@
         <v>6</v>
       </c>
       <c r="C91">
-        <v>0.2870329309210982</v>
+        <v>0.2854119227649111</v>
       </c>
       <c r="D91" t="s">
         <v>7</v>
@@ -5887,10 +5887,10 @@
         <v>191</v>
       </c>
       <c r="B92" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C92">
-        <v>0.2846769468156784</v>
+        <v>0.283998589182451</v>
       </c>
       <c r="D92" t="s">
         <v>7</v>
@@ -5907,7 +5907,7 @@
         <v>15</v>
       </c>
       <c r="C93">
-        <v>0.3662967803745927</v>
+        <v>0.3605716367605927</v>
       </c>
       <c r="D93" t="s">
         <v>7</v>
@@ -5924,7 +5924,7 @@
         <v>6</v>
       </c>
       <c r="C94">
-        <v>0.32130490892417</v>
+        <v>0.3225850693748327</v>
       </c>
       <c r="D94" t="s">
         <v>7</v>
@@ -5938,10 +5938,10 @@
         <v>197</v>
       </c>
       <c r="B95" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C95">
-        <v>0.3283365869324532</v>
+        <v>0.3242343661727223</v>
       </c>
       <c r="D95" t="s">
         <v>7</v>
@@ -5958,7 +5958,7 @@
         <v>15</v>
       </c>
       <c r="C96">
-        <v>0.3381753039610108</v>
+        <v>0.3299536822213698</v>
       </c>
       <c r="D96" t="s">
         <v>7</v>
@@ -5975,7 +5975,7 @@
         <v>44</v>
       </c>
       <c r="C97">
-        <v>0.3192041741053191</v>
+        <v>0.3063782837690256</v>
       </c>
       <c r="D97" t="s">
         <v>7</v>
@@ -5992,7 +5992,7 @@
         <v>44</v>
       </c>
       <c r="C98">
-        <v>0.3169082187984161</v>
+        <v>0.3021456994419835</v>
       </c>
       <c r="D98" t="s">
         <v>7</v>
@@ -6009,7 +6009,7 @@
         <v>6</v>
       </c>
       <c r="C99">
-        <v>0.4684943365759415</v>
+        <v>0.4669213869724081</v>
       </c>
       <c r="D99" t="s">
         <v>7</v>
@@ -6026,7 +6026,7 @@
         <v>44</v>
       </c>
       <c r="C100">
-        <v>0.3883177966375701</v>
+        <v>0.3744290778268876</v>
       </c>
       <c r="D100" t="s">
         <v>7</v>
@@ -6043,7 +6043,7 @@
         <v>44</v>
       </c>
       <c r="C101">
-        <v>0.3765801580972891</v>
+        <v>0.3591232810452637</v>
       </c>
       <c r="D101" t="s">
         <v>7</v>
@@ -6060,7 +6060,7 @@
         <v>6</v>
       </c>
       <c r="C102">
-        <v>0.4943945950765775</v>
+        <v>0.4923628710996007</v>
       </c>
       <c r="D102" t="s">
         <v>7</v>
@@ -6077,7 +6077,7 @@
         <v>6</v>
       </c>
       <c r="C103">
-        <v>0.3737724968675789</v>
+        <v>0.3705809805454315</v>
       </c>
       <c r="D103" t="s">
         <v>7</v>
@@ -6094,7 +6094,7 @@
         <v>15</v>
       </c>
       <c r="C104">
-        <v>0.3867741018758274</v>
+        <v>0.3781518470000996</v>
       </c>
       <c r="D104" t="s">
         <v>7</v>
@@ -6111,7 +6111,7 @@
         <v>44</v>
       </c>
       <c r="C105">
-        <v>0.3148237138688294</v>
+        <v>0.2975620835049208</v>
       </c>
       <c r="D105" t="s">
         <v>7</v>
@@ -6128,7 +6128,7 @@
         <v>10</v>
       </c>
       <c r="C106">
-        <v>0.376287075335497</v>
+        <v>0.4107787019743085</v>
       </c>
       <c r="D106" t="s">
         <v>7</v>
@@ -6142,10 +6142,10 @@
         <v>221</v>
       </c>
       <c r="B107" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="C107">
-        <v>0.3096826262045743</v>
+        <v>0.339398832051066</v>
       </c>
       <c r="D107" t="s">
         <v>7</v>
@@ -6162,7 +6162,7 @@
         <v>6</v>
       </c>
       <c r="C108">
-        <v>0.4140143513231161</v>
+        <v>0.4086691278940307</v>
       </c>
       <c r="D108" t="s">
         <v>7</v>
@@ -6193,10 +6193,10 @@
         <v>228</v>
       </c>
       <c r="B110" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C110">
-        <v>0.303822970275554</v>
+        <v>0.3069865223145256</v>
       </c>
       <c r="D110" t="s">
         <v>7</v>
@@ -6213,7 +6213,7 @@
         <v>6</v>
       </c>
       <c r="C111">
-        <v>0.5115797017547364</v>
+        <v>0.5063824324583864</v>
       </c>
       <c r="D111" t="s">
         <v>7</v>
@@ -6230,7 +6230,7 @@
         <v>6</v>
       </c>
       <c r="C112">
-        <v>0.4175684350127324</v>
+        <v>0.4186542606363458</v>
       </c>
       <c r="D112" t="s">
         <v>7</v>
@@ -6247,7 +6247,7 @@
         <v>15</v>
       </c>
       <c r="C113">
-        <v>0.5003901328474587</v>
+        <v>0.4884709770417798</v>
       </c>
       <c r="D113" t="s">
         <v>7</v>
@@ -6264,7 +6264,7 @@
         <v>6</v>
       </c>
       <c r="C114">
-        <v>0.6421153357630042</v>
+        <v>0.6477941427026814</v>
       </c>
       <c r="D114" t="s">
         <v>7</v>
@@ -6281,7 +6281,7 @@
         <v>6</v>
       </c>
       <c r="C115">
-        <v>0.3092666554854256</v>
+        <v>0.3094937421584268</v>
       </c>
       <c r="D115" t="s">
         <v>7</v>
@@ -6298,7 +6298,7 @@
         <v>6</v>
       </c>
       <c r="C116">
-        <v>0.4348713223213781</v>
+        <v>0.4263199580293469</v>
       </c>
       <c r="D116" t="s">
         <v>7</v>
@@ -6315,7 +6315,7 @@
         <v>10</v>
       </c>
       <c r="C117">
-        <v>0.2875513573273098</v>
+        <v>0.3260002603677044</v>
       </c>
       <c r="D117" t="s">
         <v>7</v>
@@ -6332,7 +6332,7 @@
         <v>10</v>
       </c>
       <c r="C118">
-        <v>0.3382072798096959</v>
+        <v>0.371437016231991</v>
       </c>
       <c r="D118" t="s">
         <v>7</v>
@@ -6349,7 +6349,7 @@
         <v>6</v>
       </c>
       <c r="C119">
-        <v>0.3107844297630665</v>
+        <v>0.3061960186400475</v>
       </c>
       <c r="D119" t="s">
         <v>7</v>
@@ -6366,7 +6366,7 @@
         <v>10</v>
       </c>
       <c r="C120">
-        <v>0.3572798416672965</v>
+        <v>0.3943749735764723</v>
       </c>
       <c r="D120" t="s">
         <v>7</v>
@@ -6383,7 +6383,7 @@
         <v>226</v>
       </c>
       <c r="C121">
-        <v>0.4048284965792949</v>
+        <v>0.4040086278973045</v>
       </c>
       <c r="D121" t="s">
         <v>7</v>
@@ -6400,7 +6400,7 @@
         <v>15</v>
       </c>
       <c r="C122">
-        <v>0.3046279190528884</v>
+        <v>0.298781164913996</v>
       </c>
       <c r="D122" t="s">
         <v>7</v>
@@ -6414,10 +6414,10 @@
         <v>254</v>
       </c>
       <c r="B123" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C123">
-        <v>0.2845936181567129</v>
+        <v>0.2803206082614191</v>
       </c>
       <c r="D123" t="s">
         <v>7</v>
@@ -6434,7 +6434,7 @@
         <v>15</v>
       </c>
       <c r="C124">
-        <v>0.4082541664942054</v>
+        <v>0.3975906367149994</v>
       </c>
       <c r="D124" t="s">
         <v>7</v>
@@ -6448,10 +6448,10 @@
         <v>258</v>
       </c>
       <c r="B125" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C125">
-        <v>0.2959417105482513</v>
+        <v>0.3090927798555571</v>
       </c>
       <c r="D125" t="s">
         <v>7</v>
@@ -6465,10 +6465,10 @@
         <v>260</v>
       </c>
       <c r="B126" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C126">
-        <v>0.3386205879591305</v>
+        <v>0.367252484345717</v>
       </c>
       <c r="D126" t="s">
         <v>7</v>
@@ -6485,7 +6485,7 @@
         <v>6</v>
       </c>
       <c r="C127">
-        <v>0.5113549568973127</v>
+        <v>0.5051115066762557</v>
       </c>
       <c r="D127" t="s">
         <v>7</v>
@@ -6502,7 +6502,7 @@
         <v>15</v>
       </c>
       <c r="C128">
-        <v>0.4290813396586111</v>
+        <v>0.4213460711332955</v>
       </c>
       <c r="D128" t="s">
         <v>7</v>
@@ -6519,7 +6519,7 @@
         <v>15</v>
       </c>
       <c r="C129">
-        <v>0.3055911094442256</v>
+        <v>0.297957435812113</v>
       </c>
       <c r="D129" t="s">
         <v>7</v>
@@ -6536,7 +6536,7 @@
         <v>15</v>
       </c>
       <c r="C130">
-        <v>0.3828352180975345</v>
+        <v>0.373087228647617</v>
       </c>
       <c r="D130" t="s">
         <v>7</v>
@@ -6553,7 +6553,7 @@
         <v>10</v>
       </c>
       <c r="C131">
-        <v>0.2770284333725027</v>
+        <v>0.3173892475413256</v>
       </c>
       <c r="D131" t="s">
         <v>7</v>
@@ -6570,7 +6570,7 @@
         <v>6</v>
       </c>
       <c r="C132">
-        <v>0.4021724122612851</v>
+        <v>0.3950769398664344</v>
       </c>
       <c r="D132" t="s">
         <v>7</v>
@@ -6587,7 +6587,7 @@
         <v>15</v>
       </c>
       <c r="C133">
-        <v>0.3364521188805053</v>
+        <v>0.3311400498398224</v>
       </c>
       <c r="D133" t="s">
         <v>7</v>
@@ -6604,7 +6604,7 @@
         <v>6</v>
       </c>
       <c r="C134">
-        <v>0.3914624631820178</v>
+        <v>0.3860928008867358</v>
       </c>
       <c r="D134" t="s">
         <v>7</v>
@@ -6621,7 +6621,7 @@
         <v>6</v>
       </c>
       <c r="C135">
-        <v>0.4114796982456557</v>
+        <v>0.4115340140731483</v>
       </c>
       <c r="D135" t="s">
         <v>7</v>
@@ -6638,7 +6638,7 @@
         <v>44</v>
       </c>
       <c r="C136">
-        <v>0.3166184396374957</v>
+        <v>0.3046706258117919</v>
       </c>
       <c r="D136" t="s">
         <v>7</v>
@@ -6655,7 +6655,7 @@
         <v>6</v>
       </c>
       <c r="C137">
-        <v>0.3980871829605155</v>
+        <v>0.3983031429159632</v>
       </c>
       <c r="D137" t="s">
         <v>7</v>
@@ -6672,7 +6672,7 @@
         <v>6</v>
       </c>
       <c r="C138">
-        <v>0.3320418601882254</v>
+        <v>0.32870032156868</v>
       </c>
       <c r="D138" t="s">
         <v>7</v>
@@ -6689,7 +6689,7 @@
         <v>6</v>
       </c>
       <c r="C139">
-        <v>0.4182490808040034</v>
+        <v>0.4155515158684819</v>
       </c>
       <c r="D139" t="s">
         <v>7</v>
@@ -6706,7 +6706,7 @@
         <v>44</v>
       </c>
       <c r="C140">
-        <v>0.3906918434655675</v>
+        <v>0.3728304478999824</v>
       </c>
       <c r="D140" t="s">
         <v>7</v>
@@ -6723,7 +6723,7 @@
         <v>6</v>
       </c>
       <c r="C141">
-        <v>0.3394030309081547</v>
+        <v>0.3366007474821912</v>
       </c>
       <c r="D141" t="s">
         <v>7</v>
@@ -6740,7 +6740,7 @@
         <v>10</v>
       </c>
       <c r="C142">
-        <v>0.3818599159088267</v>
+        <v>0.415940987793596</v>
       </c>
       <c r="D142" t="s">
         <v>7</v>
@@ -6757,7 +6757,7 @@
         <v>6</v>
       </c>
       <c r="C143">
-        <v>0.3744531260966947</v>
+        <v>0.374839127865511</v>
       </c>
       <c r="D143" t="s">
         <v>7</v>
@@ -6774,7 +6774,7 @@
         <v>6</v>
       </c>
       <c r="C144">
-        <v>0.6177557817988265</v>
+        <v>0.6252919250698538</v>
       </c>
       <c r="D144" t="s">
         <v>7</v>
@@ -6791,7 +6791,7 @@
         <v>6</v>
       </c>
       <c r="C145">
-        <v>0.3085202191613176</v>
+        <v>0.3071229613573984</v>
       </c>
       <c r="D145" t="s">
         <v>7</v>
@@ -6808,7 +6808,7 @@
         <v>6</v>
       </c>
       <c r="C146">
-        <v>0.4254187313468136</v>
+        <v>0.4227903018144512</v>
       </c>
       <c r="D146" t="s">
         <v>7</v>
@@ -6825,7 +6825,7 @@
         <v>6</v>
       </c>
       <c r="C147">
-        <v>0.4739806979672494</v>
+        <v>0.4704530052423444</v>
       </c>
       <c r="D147" t="s">
         <v>7</v>
@@ -6842,7 +6842,7 @@
         <v>6</v>
       </c>
       <c r="C148">
-        <v>0.3168482097594877</v>
+        <v>0.3172681052493492</v>
       </c>
       <c r="D148" t="s">
         <v>7</v>
@@ -6859,7 +6859,7 @@
         <v>10</v>
       </c>
       <c r="C149">
-        <v>0.3773518676769389</v>
+        <v>0.4142195572282715</v>
       </c>
       <c r="D149" t="s">
         <v>7</v>
@@ -6876,7 +6876,7 @@
         <v>6</v>
       </c>
       <c r="C150">
-        <v>0.3719862901818265</v>
+        <v>0.3729043145002347</v>
       </c>
       <c r="D150" t="s">
         <v>7</v>
@@ -6893,7 +6893,7 @@
         <v>10</v>
       </c>
       <c r="C151">
-        <v>0.2513699073921489</v>
+        <v>0.2909802423281161</v>
       </c>
       <c r="D151" t="s">
         <v>7</v>
@@ -6910,7 +6910,7 @@
         <v>6</v>
       </c>
       <c r="C152">
-        <v>0.6822032151879841</v>
+        <v>0.68550176959695</v>
       </c>
       <c r="D152" t="s">
         <v>7</v>
@@ -6927,7 +6927,7 @@
         <v>10</v>
       </c>
       <c r="C153">
-        <v>0.3219643299205065</v>
+        <v>0.3571220808184837</v>
       </c>
       <c r="D153" t="s">
         <v>7</v>
@@ -6944,7 +6944,7 @@
         <v>44</v>
       </c>
       <c r="C154">
-        <v>0.3157355539161525</v>
+        <v>0.3010104823930287</v>
       </c>
       <c r="D154" t="s">
         <v>7</v>
@@ -6961,7 +6961,7 @@
         <v>6</v>
       </c>
       <c r="C155">
-        <v>0.3158143589548416</v>
+        <v>0.3149471208050237</v>
       </c>
       <c r="D155" t="s">
         <v>7</v>
@@ -6978,7 +6978,7 @@
         <v>10</v>
       </c>
       <c r="C156">
-        <v>0.3272434704953649</v>
+        <v>0.3638920577525225</v>
       </c>
       <c r="D156" t="s">
         <v>7</v>
@@ -6995,7 +6995,7 @@
         <v>6</v>
       </c>
       <c r="C157">
-        <v>0.4072142892427044</v>
+        <v>0.4034754009752538</v>
       </c>
       <c r="D157" t="s">
         <v>7</v>
@@ -7012,7 +7012,7 @@
         <v>44</v>
       </c>
       <c r="C158">
-        <v>0.3601013160075043</v>
+        <v>0.343338386124305</v>
       </c>
       <c r="D158" t="s">
         <v>7</v>
@@ -7029,7 +7029,7 @@
         <v>44</v>
       </c>
       <c r="C159">
-        <v>0.3650535693323411</v>
+        <v>0.3531117085060427</v>
       </c>
       <c r="D159" t="s">
         <v>7</v>
@@ -7046,7 +7046,7 @@
         <v>6</v>
       </c>
       <c r="C160">
-        <v>0.3949632887230734</v>
+        <v>0.3924645385822331</v>
       </c>
       <c r="D160" t="s">
         <v>7</v>
@@ -7063,7 +7063,7 @@
         <v>6</v>
       </c>
       <c r="C161">
-        <v>0.4329949319204694</v>
+        <v>0.430339755858315</v>
       </c>
       <c r="D161" t="s">
         <v>7</v>
@@ -7080,7 +7080,7 @@
         <v>6</v>
       </c>
       <c r="C162">
-        <v>0.4897276408028025</v>
+        <v>0.4843006112206148</v>
       </c>
       <c r="D162" t="s">
         <v>7</v>
@@ -7097,7 +7097,7 @@
         <v>44</v>
       </c>
       <c r="C163">
-        <v>0.4262015870734005</v>
+        <v>0.414634221450184</v>
       </c>
       <c r="D163" t="s">
         <v>7</v>
@@ -7114,7 +7114,7 @@
         <v>10</v>
       </c>
       <c r="C164">
-        <v>0.3331506870166411</v>
+        <v>0.3693453648931869</v>
       </c>
       <c r="D164" t="s">
         <v>7</v>
@@ -7131,7 +7131,7 @@
         <v>10</v>
       </c>
       <c r="C165">
-        <v>0.3836779244800037</v>
+        <v>0.4234384233801173</v>
       </c>
       <c r="D165" t="s">
         <v>7</v>
@@ -7148,7 +7148,7 @@
         <v>10</v>
       </c>
       <c r="C166">
-        <v>0.2877130334392995</v>
+        <v>0.3234231659963002</v>
       </c>
       <c r="D166" t="s">
         <v>7</v>
@@ -7165,7 +7165,7 @@
         <v>6</v>
       </c>
       <c r="C167">
-        <v>0.3764108886808609</v>
+        <v>0.374160986755515</v>
       </c>
       <c r="D167" t="s">
         <v>7</v>
@@ -7182,7 +7182,7 @@
         <v>6</v>
       </c>
       <c r="C168">
-        <v>0.6177969729671817</v>
+        <v>0.6149777064392979</v>
       </c>
       <c r="D168" t="s">
         <v>7</v>
@@ -7196,10 +7196,10 @@
         <v>346</v>
       </c>
       <c r="B169" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="C169">
-        <v>0.3153492975298122</v>
+        <v>0.3314088255243869</v>
       </c>
       <c r="D169" t="s">
         <v>7</v>
@@ -7216,7 +7216,7 @@
         <v>6</v>
       </c>
       <c r="C170">
-        <v>0.401317873824064</v>
+        <v>0.4006396258060142</v>
       </c>
       <c r="D170" t="s">
         <v>7</v>
@@ -7233,7 +7233,7 @@
         <v>6</v>
       </c>
       <c r="C171">
-        <v>0.2724642343405217</v>
+        <v>0.2727639647416724</v>
       </c>
       <c r="D171" t="s">
         <v>7</v>
@@ -7247,10 +7247,10 @@
         <v>352</v>
       </c>
       <c r="B172" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C172">
-        <v>0.415866582904903</v>
+        <v>0.429963517076091</v>
       </c>
       <c r="D172" t="s">
         <v>7</v>
@@ -7264,10 +7264,10 @@
         <v>354</v>
       </c>
       <c r="B173" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="C173">
-        <v>0.3035205145367715</v>
+        <v>0.3067824588764613</v>
       </c>
       <c r="D173" t="s">
         <v>7</v>
@@ -7284,7 +7284,7 @@
         <v>6</v>
       </c>
       <c r="C174">
-        <v>0.3245760785718852</v>
+        <v>0.321915360335224</v>
       </c>
       <c r="D174" t="s">
         <v>7</v>
@@ -7301,7 +7301,7 @@
         <v>15</v>
       </c>
       <c r="C175">
-        <v>0.303135478480608</v>
+        <v>0.2983056186518726</v>
       </c>
       <c r="D175" t="s">
         <v>7</v>
@@ -7318,7 +7318,7 @@
         <v>6</v>
       </c>
       <c r="C176">
-        <v>0.4307307974385401</v>
+        <v>0.4256815055180311</v>
       </c>
       <c r="D176" t="s">
         <v>7</v>
@@ -7335,7 +7335,7 @@
         <v>6</v>
       </c>
       <c r="C177">
-        <v>0.5271747731254864</v>
+        <v>0.5207686039431421</v>
       </c>
       <c r="D177" t="s">
         <v>7</v>
@@ -7352,7 +7352,7 @@
         <v>15</v>
       </c>
       <c r="C178">
-        <v>0.4016327007184258</v>
+        <v>0.3910155722464447</v>
       </c>
       <c r="D178" t="s">
         <v>7</v>
@@ -7369,7 +7369,7 @@
         <v>15</v>
       </c>
       <c r="C179">
-        <v>0.3095684621960773</v>
+        <v>0.3040726435683931</v>
       </c>
       <c r="D179" t="s">
         <v>7</v>
@@ -7386,7 +7386,7 @@
         <v>44</v>
       </c>
       <c r="C180">
-        <v>0.3224676143293874</v>
+        <v>0.3093552012087581</v>
       </c>
       <c r="D180" t="s">
         <v>7</v>
@@ -7403,7 +7403,7 @@
         <v>6</v>
       </c>
       <c r="C181">
-        <v>0.3405057323282793</v>
+        <v>0.3369832048967492</v>
       </c>
       <c r="D181" t="s">
         <v>7</v>
@@ -7417,10 +7417,10 @@
         <v>372</v>
       </c>
       <c r="B182" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C182">
-        <v>0.2810305532600089</v>
+        <v>0.3150957023246092</v>
       </c>
       <c r="D182" t="s">
         <v>7</v>
@@ -7437,7 +7437,7 @@
         <v>6</v>
       </c>
       <c r="C183">
-        <v>0.326870159390351</v>
+        <v>0.3278757066912501</v>
       </c>
       <c r="D183" t="s">
         <v>7</v>
@@ -7454,7 +7454,7 @@
         <v>6</v>
       </c>
       <c r="C184">
-        <v>0.3694114175357649</v>
+        <v>0.3672380224508587</v>
       </c>
       <c r="D184" t="s">
         <v>7</v>
@@ -7468,10 +7468,10 @@
         <v>378</v>
       </c>
       <c r="B185" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C185">
-        <v>0.3367474205751546</v>
+        <v>0.3712001492929879</v>
       </c>
       <c r="D185" t="s">
         <v>7</v>
@@ -7488,7 +7488,7 @@
         <v>44</v>
       </c>
       <c r="C186">
-        <v>0.3802798823873389</v>
+        <v>0.3633580716858676</v>
       </c>
       <c r="D186" t="s">
         <v>7</v>
@@ -7502,10 +7502,10 @@
         <v>382</v>
       </c>
       <c r="B187" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C187">
-        <v>0.2461859225994922</v>
+        <v>0.2664328586774437</v>
       </c>
       <c r="D187" t="s">
         <v>7</v>
@@ -7519,10 +7519,10 @@
         <v>384</v>
       </c>
       <c r="B188" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="C188">
-        <v>0.3780185907557829</v>
+        <v>0.4041146345757582</v>
       </c>
       <c r="D188" t="s">
         <v>7</v>
@@ -7536,10 +7536,10 @@
         <v>386</v>
       </c>
       <c r="B189" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C189">
-        <v>0.3475952887549523</v>
+        <v>0.3473210256989374</v>
       </c>
       <c r="D189" t="s">
         <v>7</v>
@@ -7556,7 +7556,7 @@
         <v>6</v>
       </c>
       <c r="C190">
-        <v>0.3180228111410904</v>
+        <v>0.3193924204754062</v>
       </c>
       <c r="D190" t="s">
         <v>7</v>
@@ -7573,7 +7573,7 @@
         <v>10</v>
       </c>
       <c r="C191">
-        <v>0.309428755408372</v>
+        <v>0.3496760636175043</v>
       </c>
       <c r="D191" t="s">
         <v>7</v>
@@ -7590,7 +7590,7 @@
         <v>15</v>
       </c>
       <c r="C192">
-        <v>0.4057802189475063</v>
+        <v>0.398699759549437</v>
       </c>
       <c r="D192" t="s">
         <v>7</v>
@@ -7607,7 +7607,7 @@
         <v>15</v>
       </c>
       <c r="C193">
-        <v>0.4285209953712673</v>
+        <v>0.4190832174006298</v>
       </c>
       <c r="D193" t="s">
         <v>7</v>
@@ -7624,7 +7624,7 @@
         <v>15</v>
       </c>
       <c r="C194">
-        <v>0.3686609637516772</v>
+        <v>0.3604983926365258</v>
       </c>
       <c r="D194" t="s">
         <v>7</v>
@@ -7641,7 +7641,7 @@
         <v>226</v>
       </c>
       <c r="C195">
-        <v>0.4940064828599474</v>
+        <v>0.4876899733181512</v>
       </c>
       <c r="D195" t="s">
         <v>7</v>
@@ -7658,7 +7658,7 @@
         <v>6</v>
       </c>
       <c r="C196">
-        <v>0.3918014892957586</v>
+        <v>0.3972904642317303</v>
       </c>
       <c r="D196" t="s">
         <v>7</v>
@@ -7675,7 +7675,7 @@
         <v>10</v>
       </c>
       <c r="C197">
-        <v>0.2917913163421734</v>
+        <v>0.3311162167895405</v>
       </c>
       <c r="D197" t="s">
         <v>7</v>
@@ -7692,7 +7692,7 @@
         <v>6</v>
       </c>
       <c r="C198">
-        <v>0.5256327350992031</v>
+        <v>0.5259810096392274</v>
       </c>
       <c r="D198" t="s">
         <v>7</v>
@@ -7709,7 +7709,7 @@
         <v>6</v>
       </c>
       <c r="C199">
-        <v>0.6115906448939207</v>
+        <v>0.6198264278794132</v>
       </c>
       <c r="D199" t="s">
         <v>7</v>
@@ -7726,7 +7726,7 @@
         <v>15</v>
       </c>
       <c r="C200">
-        <v>0.3253947992303289</v>
+        <v>0.3202709246438011</v>
       </c>
       <c r="D200" t="s">
         <v>7</v>
@@ -7743,7 +7743,7 @@
         <v>15</v>
       </c>
       <c r="C201">
-        <v>0.3164486756910976</v>
+        <v>0.3121292170182082</v>
       </c>
       <c r="D201" t="s">
         <v>7</v>
@@ -7760,7 +7760,7 @@
         <v>10</v>
       </c>
       <c r="C202">
-        <v>0.3314031218730466</v>
+        <v>0.3704550283872084</v>
       </c>
       <c r="D202" t="s">
         <v>7</v>
@@ -7777,7 +7777,7 @@
         <v>6</v>
       </c>
       <c r="C203">
-        <v>0.5569423179388862</v>
+        <v>0.5577578251440909</v>
       </c>
       <c r="D203" t="s">
         <v>7</v>
@@ -7794,7 +7794,7 @@
         <v>6</v>
       </c>
       <c r="C204">
-        <v>0.4940017422872954</v>
+        <v>0.4934779618703716</v>
       </c>
       <c r="D204" t="s">
         <v>7</v>
@@ -7811,7 +7811,7 @@
         <v>10</v>
       </c>
       <c r="C205">
-        <v>0.4193690743303607</v>
+        <v>0.4522510663045292</v>
       </c>
       <c r="D205" t="s">
         <v>7</v>
@@ -7828,7 +7828,7 @@
         <v>15</v>
       </c>
       <c r="C206">
-        <v>0.3529230057255753</v>
+        <v>0.3475846140146978</v>
       </c>
       <c r="D206" t="s">
         <v>7</v>
@@ -7845,7 +7845,7 @@
         <v>44</v>
       </c>
       <c r="C207">
-        <v>0.5282577329304537</v>
+        <v>0.5224378534638913</v>
       </c>
       <c r="D207" t="s">
         <v>7</v>
@@ -7859,10 +7859,10 @@
         <v>424</v>
       </c>
       <c r="B208" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="C208">
-        <v>0.3572759760765802</v>
+        <v>0.3495590788583915</v>
       </c>
       <c r="D208" t="s">
         <v>7</v>
@@ -7879,7 +7879,7 @@
         <v>10</v>
       </c>
       <c r="C209">
-        <v>0.5259310527921848</v>
+        <v>0.5539482067201438</v>
       </c>
       <c r="D209" t="s">
         <v>7</v>
@@ -7896,7 +7896,7 @@
         <v>6</v>
       </c>
       <c r="C210">
-        <v>0.4466958233959494</v>
+        <v>0.4436187924380666</v>
       </c>
       <c r="D210" t="s">
         <v>7</v>
@@ -7913,7 +7913,7 @@
         <v>15</v>
       </c>
       <c r="C211">
-        <v>0.4714768015058112</v>
+        <v>0.4598179975738328</v>
       </c>
       <c r="D211" t="s">
         <v>7</v>
@@ -7927,10 +7927,10 @@
         <v>432</v>
       </c>
       <c r="B212" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C212">
-        <v>0.2917362467853614</v>
+        <v>0.2901657990742273</v>
       </c>
       <c r="D212" t="s">
         <v>7</v>
@@ -7944,10 +7944,10 @@
         <v>434</v>
       </c>
       <c r="B213" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C213">
-        <v>0.3133788435937771</v>
+        <v>0.3283076796173972</v>
       </c>
       <c r="D213" t="s">
         <v>7</v>
@@ -7964,7 +7964,7 @@
         <v>15</v>
       </c>
       <c r="C214">
-        <v>0.3781438197087224</v>
+        <v>0.3684209688975205</v>
       </c>
       <c r="D214" t="s">
         <v>7</v>
@@ -7981,7 +7981,7 @@
         <v>10</v>
       </c>
       <c r="C215">
-        <v>0.495149041724007</v>
+        <v>0.5198819693236149</v>
       </c>
       <c r="D215" t="s">
         <v>7</v>
@@ -7998,7 +7998,7 @@
         <v>15</v>
       </c>
       <c r="C216">
-        <v>0.338315915425655</v>
+        <v>0.3301753915636213</v>
       </c>
       <c r="D216" t="s">
         <v>7</v>
@@ -8012,10 +8012,10 @@
         <v>442</v>
       </c>
       <c r="B217" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C217">
-        <v>0.2930836282664133</v>
+        <v>0.3283930235443833</v>
       </c>
       <c r="D217" t="s">
         <v>7</v>
@@ -8029,10 +8029,10 @@
         <v>444</v>
       </c>
       <c r="B218" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C218">
-        <v>0.3587380409352858</v>
+        <v>0.3697425342593207</v>
       </c>
       <c r="D218" t="s">
         <v>7</v>
@@ -8049,7 +8049,7 @@
         <v>44</v>
       </c>
       <c r="C219">
-        <v>0.4726411646955317</v>
+        <v>0.4568289938723162</v>
       </c>
       <c r="D219" t="s">
         <v>7</v>
@@ -8066,7 +8066,7 @@
         <v>15</v>
       </c>
       <c r="C220">
-        <v>0.3058139042412027</v>
+        <v>0.300018805300597</v>
       </c>
       <c r="D220" t="s">
         <v>7</v>
@@ -8083,7 +8083,7 @@
         <v>15</v>
       </c>
       <c r="C221">
-        <v>0.3823375173213545</v>
+        <v>0.3757100335338037</v>
       </c>
       <c r="D221" t="s">
         <v>7</v>
@@ -8097,10 +8097,10 @@
         <v>452</v>
       </c>
       <c r="B222" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C222">
-        <v>0.3202899837374809</v>
+        <v>0.3254059236278634</v>
       </c>
       <c r="D222" t="s">
         <v>7</v>
@@ -8117,7 +8117,7 @@
         <v>10</v>
       </c>
       <c r="C223">
-        <v>0.4647425536398484</v>
+        <v>0.4914735108101537</v>
       </c>
       <c r="D223" t="s">
         <v>7</v>
@@ -8134,7 +8134,7 @@
         <v>10</v>
       </c>
       <c r="C224">
-        <v>0.2789032247660559</v>
+        <v>0.3173977671514253</v>
       </c>
       <c r="D224" t="s">
         <v>7</v>
@@ -8151,7 +8151,7 @@
         <v>15</v>
       </c>
       <c r="C225">
-        <v>0.361512320193079</v>
+        <v>0.3559120937766239</v>
       </c>
       <c r="D225" t="s">
         <v>7</v>
@@ -8168,7 +8168,7 @@
         <v>6</v>
       </c>
       <c r="C226">
-        <v>0.5116396741165794</v>
+        <v>0.5098137015120904</v>
       </c>
       <c r="D226" t="s">
         <v>7</v>
@@ -8185,7 +8185,7 @@
         <v>10</v>
       </c>
       <c r="C227">
-        <v>0.2996521498530782</v>
+        <v>0.3400511379078193</v>
       </c>
       <c r="D227" t="s">
         <v>7</v>
@@ -8202,7 +8202,7 @@
         <v>6</v>
       </c>
       <c r="C228">
-        <v>0.5088798597204086</v>
+        <v>0.5095839703224546</v>
       </c>
       <c r="D228" t="s">
         <v>7</v>
@@ -8219,7 +8219,7 @@
         <v>6</v>
       </c>
       <c r="C229">
-        <v>0.5793449328941894</v>
+        <v>0.586917746010712</v>
       </c>
       <c r="D229" t="s">
         <v>7</v>
@@ -8236,7 +8236,7 @@
         <v>44</v>
       </c>
       <c r="C230">
-        <v>0.3317428947097051</v>
+        <v>0.314472946438428</v>
       </c>
       <c r="D230" t="s">
         <v>7</v>
@@ -8253,7 +8253,7 @@
         <v>6</v>
       </c>
       <c r="C231">
-        <v>0.3363027572203622</v>
+        <v>0.3308645659122954</v>
       </c>
       <c r="D231" t="s">
         <v>7</v>
@@ -8270,7 +8270,7 @@
         <v>6</v>
       </c>
       <c r="C232">
-        <v>0.6099239196103653</v>
+        <v>0.6097752633871738</v>
       </c>
       <c r="D232" t="s">
         <v>7</v>
@@ -8287,7 +8287,7 @@
         <v>44</v>
       </c>
       <c r="C233">
-        <v>0.3962686908673368</v>
+        <v>0.3804090853199393</v>
       </c>
       <c r="D233" t="s">
         <v>7</v>
@@ -8304,7 +8304,7 @@
         <v>6</v>
       </c>
       <c r="C234">
-        <v>0.4489134774039293</v>
+        <v>0.4452354951613074</v>
       </c>
       <c r="D234" t="s">
         <v>7</v>
@@ -8321,7 +8321,7 @@
         <v>6</v>
       </c>
       <c r="C235">
-        <v>0.5203567356573355</v>
+        <v>0.5204457984181673</v>
       </c>
       <c r="D235" t="s">
         <v>7</v>
@@ -8338,7 +8338,7 @@
         <v>6</v>
       </c>
       <c r="C236">
-        <v>0.308221623413592</v>
+        <v>0.3112369701523505</v>
       </c>
       <c r="D236" t="s">
         <v>7</v>
@@ -8355,7 +8355,7 @@
         <v>6</v>
       </c>
       <c r="C237">
-        <v>0.3281612415324567</v>
+        <v>0.3254542244177857</v>
       </c>
       <c r="D237" t="s">
         <v>7</v>
@@ -8372,7 +8372,7 @@
         <v>6</v>
       </c>
       <c r="C238">
-        <v>0.376065400153703</v>
+        <v>0.3734090214134132</v>
       </c>
       <c r="D238" t="s">
         <v>7</v>
@@ -8389,7 +8389,7 @@
         <v>6</v>
       </c>
       <c r="C239">
-        <v>0.4666542902291647</v>
+        <v>0.4598640750088599</v>
       </c>
       <c r="D239" t="s">
         <v>7</v>
@@ -8406,7 +8406,7 @@
         <v>226</v>
       </c>
       <c r="C240">
-        <v>0.3522967028147929</v>
+        <v>0.3508895557533616</v>
       </c>
       <c r="D240" t="s">
         <v>7</v>
@@ -8420,10 +8420,10 @@
         <v>490</v>
       </c>
       <c r="B241" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C241">
-        <v>0.2323183949910056</v>
+        <v>0.269976002812368</v>
       </c>
       <c r="D241" t="s">
         <v>7</v>
@@ -8440,7 +8440,7 @@
         <v>6</v>
       </c>
       <c r="C242">
-        <v>0.3419814192782404</v>
+        <v>0.3397682845941056</v>
       </c>
       <c r="D242" t="s">
         <v>7</v>
@@ -8457,7 +8457,7 @@
         <v>15</v>
       </c>
       <c r="C243">
-        <v>0.5006799575697565</v>
+        <v>0.4879686533189083</v>
       </c>
       <c r="D243" t="s">
         <v>7</v>
@@ -8474,7 +8474,7 @@
         <v>226</v>
       </c>
       <c r="C244">
-        <v>0.4771018800278814</v>
+        <v>0.4728841549886199</v>
       </c>
       <c r="D244" t="s">
         <v>7</v>
@@ -8491,7 +8491,7 @@
         <v>6</v>
       </c>
       <c r="C245">
-        <v>0.6452899008851005</v>
+        <v>0.650770054746319</v>
       </c>
       <c r="D245" t="s">
         <v>7</v>
@@ -8508,7 +8508,7 @@
         <v>6</v>
       </c>
       <c r="C246">
-        <v>0.4636217166248545</v>
+        <v>0.4667013084043142</v>
       </c>
       <c r="D246" t="s">
         <v>7</v>
@@ -8525,7 +8525,7 @@
         <v>6</v>
       </c>
       <c r="C247">
-        <v>0.4263025802786948</v>
+        <v>0.419936227851554</v>
       </c>
       <c r="D247" t="s">
         <v>7</v>
@@ -8542,7 +8542,7 @@
         <v>10</v>
       </c>
       <c r="C248">
-        <v>0.2911544830091955</v>
+        <v>0.3288582378464036</v>
       </c>
       <c r="D248" t="s">
         <v>7</v>
@@ -8559,7 +8559,7 @@
         <v>6</v>
       </c>
       <c r="C249">
-        <v>0.4490593135708703</v>
+        <v>0.4475787588455902</v>
       </c>
       <c r="D249" t="s">
         <v>7</v>
@@ -8576,7 +8576,7 @@
         <v>15</v>
       </c>
       <c r="C250">
-        <v>0.3193572902584206</v>
+        <v>0.3131450154531511</v>
       </c>
       <c r="D250" t="s">
         <v>7</v>
@@ -8593,7 +8593,7 @@
         <v>44</v>
       </c>
       <c r="C251">
-        <v>0.4920765672140364</v>
+        <v>0.4805005547154459</v>
       </c>
       <c r="D251" t="s">
         <v>7</v>
@@ -8610,7 +8610,7 @@
         <v>6</v>
       </c>
       <c r="C252">
-        <v>0.4295100346662291</v>
+        <v>0.4287034562494008</v>
       </c>
       <c r="D252" t="s">
         <v>7</v>
@@ -8627,7 +8627,7 @@
         <v>6</v>
       </c>
       <c r="C253">
-        <v>0.3797643571126112</v>
+        <v>0.3795066996673866</v>
       </c>
       <c r="D253" t="s">
         <v>7</v>
@@ -8644,7 +8644,7 @@
         <v>6</v>
       </c>
       <c r="C254">
-        <v>0.5130304667892039</v>
+        <v>0.5065138976750919</v>
       </c>
       <c r="D254" t="s">
         <v>7</v>
@@ -8661,7 +8661,7 @@
         <v>15</v>
       </c>
       <c r="C255">
-        <v>0.4526973403610122</v>
+        <v>0.443975833309654</v>
       </c>
       <c r="D255" t="s">
         <v>7</v>
@@ -8678,7 +8678,7 @@
         <v>6</v>
       </c>
       <c r="C256">
-        <v>0.6102906084632975</v>
+        <v>0.6080754660427045</v>
       </c>
       <c r="D256" t="s">
         <v>7</v>
@@ -8695,7 +8695,7 @@
         <v>6</v>
       </c>
       <c r="C257">
-        <v>0.4252869864910019</v>
+        <v>0.4248739900860602</v>
       </c>
       <c r="D257" t="s">
         <v>7</v>
@@ -8712,7 +8712,7 @@
         <v>6</v>
       </c>
       <c r="C258">
-        <v>0.5207193197792143</v>
+        <v>0.5292200994606695</v>
       </c>
       <c r="D258" t="s">
         <v>7</v>
@@ -8726,10 +8726,10 @@
         <v>526</v>
       </c>
       <c r="B259" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C259">
-        <v>0.2999551002181531</v>
+        <v>0.2957559548144028</v>
       </c>
       <c r="D259" t="s">
         <v>7</v>
@@ -8746,7 +8746,7 @@
         <v>6</v>
       </c>
       <c r="C260">
-        <v>0.4551250714572553</v>
+        <v>0.4514914915825632</v>
       </c>
       <c r="D260" t="s">
         <v>7</v>
@@ -8763,7 +8763,7 @@
         <v>6</v>
       </c>
       <c r="C261">
-        <v>0.5042220771703753</v>
+        <v>0.5010434164412489</v>
       </c>
       <c r="D261" t="s">
         <v>7</v>
@@ -8780,7 +8780,7 @@
         <v>6</v>
       </c>
       <c r="C262">
-        <v>0.4430022555391789</v>
+        <v>0.4477981772738125</v>
       </c>
       <c r="D262" t="s">
         <v>7</v>
@@ -8797,7 +8797,7 @@
         <v>6</v>
       </c>
       <c r="C263">
-        <v>0.4794056890398446</v>
+        <v>0.4776680923274867</v>
       </c>
       <c r="D263" t="s">
         <v>7</v>
@@ -8814,7 +8814,7 @@
         <v>6</v>
       </c>
       <c r="C264">
-        <v>0.4612502472942309</v>
+        <v>0.4585566080296707</v>
       </c>
       <c r="D264" t="s">
         <v>7</v>
@@ -8831,7 +8831,7 @@
         <v>6</v>
       </c>
       <c r="C265">
-        <v>0.3606790444548494</v>
+        <v>0.3620312193776954</v>
       </c>
       <c r="D265" t="s">
         <v>7</v>
@@ -8848,7 +8848,7 @@
         <v>6</v>
       </c>
       <c r="C266">
-        <v>0.413266941272524</v>
+        <v>0.4125033463316551</v>
       </c>
       <c r="D266" t="s">
         <v>7</v>
@@ -8865,7 +8865,7 @@
         <v>6</v>
       </c>
       <c r="C267">
-        <v>0.2898857341600403</v>
+        <v>0.2900911535747839</v>
       </c>
       <c r="D267" t="s">
         <v>7</v>
@@ -8882,7 +8882,7 @@
         <v>6</v>
       </c>
       <c r="C268">
-        <v>0.4677622630388396</v>
+        <v>0.4674674117069709</v>
       </c>
       <c r="D268" t="s">
         <v>7</v>
@@ -8899,7 +8899,7 @@
         <v>44</v>
       </c>
       <c r="C269">
-        <v>0.3608027024625819</v>
+        <v>0.3478357561828685</v>
       </c>
       <c r="D269" t="s">
         <v>7</v>
@@ -8916,7 +8916,7 @@
         <v>6</v>
       </c>
       <c r="C270">
-        <v>0.5532464640751245</v>
+        <v>0.5546228366108412</v>
       </c>
       <c r="D270" t="s">
         <v>7</v>
@@ -8933,7 +8933,7 @@
         <v>6</v>
       </c>
       <c r="C271">
-        <v>0.5606967991198075</v>
+        <v>0.5671076441565982</v>
       </c>
       <c r="D271" t="s">
         <v>7</v>
@@ -8950,7 +8950,7 @@
         <v>6</v>
       </c>
       <c r="C272">
-        <v>0.4015826491170143</v>
+        <v>0.4022624200839399</v>
       </c>
       <c r="D272" t="s">
         <v>7</v>
@@ -8967,7 +8967,7 @@
         <v>6</v>
       </c>
       <c r="C273">
-        <v>0.5499409857298471</v>
+        <v>0.5505033689212446</v>
       </c>
       <c r="D273" t="s">
         <v>7</v>
@@ -8984,7 +8984,7 @@
         <v>15</v>
       </c>
       <c r="C274">
-        <v>0.3623086791294109</v>
+        <v>0.3535804806460833</v>
       </c>
       <c r="D274" t="s">
         <v>7</v>
@@ -8998,10 +8998,10 @@
         <v>558</v>
       </c>
       <c r="B275" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C275">
-        <v>0.2430331853213277</v>
+        <v>0.2709112905959883</v>
       </c>
       <c r="D275" t="s">
         <v>7</v>
@@ -9018,7 +9018,7 @@
         <v>6</v>
       </c>
       <c r="C276">
-        <v>0.3338660101859057</v>
+        <v>0.3323300528353696</v>
       </c>
       <c r="D276" t="s">
         <v>7</v>
@@ -9035,7 +9035,7 @@
         <v>6</v>
       </c>
       <c r="C277">
-        <v>0.3906582368052031</v>
+        <v>0.3964910972052848</v>
       </c>
       <c r="D277" t="s">
         <v>7</v>
@@ -9052,7 +9052,7 @@
         <v>6</v>
       </c>
       <c r="C278">
-        <v>0.4568775256297566</v>
+        <v>0.4537396925068726</v>
       </c>
       <c r="D278" t="s">
         <v>7</v>
@@ -9069,7 +9069,7 @@
         <v>6</v>
       </c>
       <c r="C279">
-        <v>0.5639298152217527</v>
+        <v>0.5729455637864586</v>
       </c>
       <c r="D279" t="s">
         <v>7</v>
@@ -9086,7 +9086,7 @@
         <v>6</v>
       </c>
       <c r="C280">
-        <v>0.5062276776398805</v>
+        <v>0.5090396115947469</v>
       </c>
       <c r="D280" t="s">
         <v>7</v>
@@ -9103,7 +9103,7 @@
         <v>6</v>
       </c>
       <c r="C281">
-        <v>0.4181681675248892</v>
+        <v>0.4117389490402136</v>
       </c>
       <c r="D281" t="s">
         <v>7</v>
@@ -9120,7 +9120,7 @@
         <v>15</v>
       </c>
       <c r="C282">
-        <v>0.3703709320976004</v>
+        <v>0.3644025268586457</v>
       </c>
       <c r="D282" t="s">
         <v>7</v>
@@ -9137,7 +9137,7 @@
         <v>6</v>
       </c>
       <c r="C283">
-        <v>0.3655257933063339</v>
+        <v>0.3598628497108494</v>
       </c>
       <c r="D283" t="s">
         <v>7</v>
@@ -9154,7 +9154,7 @@
         <v>6</v>
       </c>
       <c r="C284">
-        <v>0.3489132415633993</v>
+        <v>0.3494730976146233</v>
       </c>
       <c r="D284" t="s">
         <v>7</v>
@@ -9168,10 +9168,10 @@
         <v>578</v>
       </c>
       <c r="B285" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C285">
-        <v>0.2503689210790596</v>
+        <v>0.2645807223796351</v>
       </c>
       <c r="D285" t="s">
         <v>7</v>
@@ -9188,7 +9188,7 @@
         <v>6</v>
       </c>
       <c r="C286">
-        <v>0.3146019568205206</v>
+        <v>0.313041379974872</v>
       </c>
       <c r="D286" t="s">
         <v>7</v>
@@ -9205,7 +9205,7 @@
         <v>44</v>
       </c>
       <c r="C287">
-        <v>0.4658178817547965</v>
+        <v>0.4547122588386457</v>
       </c>
       <c r="D287" t="s">
         <v>7</v>
@@ -9222,7 +9222,7 @@
         <v>6</v>
       </c>
       <c r="C288">
-        <v>0.2915861578446677</v>
+        <v>0.2920858150028525</v>
       </c>
       <c r="D288" t="s">
         <v>7</v>
@@ -9239,7 +9239,7 @@
         <v>6</v>
       </c>
       <c r="C289">
-        <v>0.3868899424053717</v>
+        <v>0.3850034022574416</v>
       </c>
       <c r="D289" t="s">
         <v>7</v>
@@ -9256,7 +9256,7 @@
         <v>15</v>
       </c>
       <c r="C290">
-        <v>0.3214170076002224</v>
+        <v>0.3153763449791123</v>
       </c>
       <c r="D290" t="s">
         <v>7</v>
@@ -9273,7 +9273,7 @@
         <v>6</v>
       </c>
       <c r="C291">
-        <v>0.4470887575383654</v>
+        <v>0.4528147063404485</v>
       </c>
       <c r="D291" t="s">
         <v>7</v>
@@ -9290,7 +9290,7 @@
         <v>145</v>
       </c>
       <c r="C292">
-        <v>0.4317491058314316</v>
+        <v>0.4147849531296718</v>
       </c>
       <c r="D292" t="s">
         <v>7</v>
@@ -9307,7 +9307,7 @@
         <v>6</v>
       </c>
       <c r="C293">
-        <v>0.6244506001415259</v>
+        <v>0.6324100861989473</v>
       </c>
       <c r="D293" t="s">
         <v>7</v>
@@ -9324,7 +9324,7 @@
         <v>15</v>
       </c>
       <c r="C294">
-        <v>0.4089960194674507</v>
+        <v>0.3996355251140249</v>
       </c>
       <c r="D294" t="s">
         <v>7</v>
@@ -9341,7 +9341,7 @@
         <v>10</v>
       </c>
       <c r="C295">
-        <v>0.3145493860791583</v>
+        <v>0.3523120850116416</v>
       </c>
       <c r="D295" t="s">
         <v>7</v>
@@ -9358,7 +9358,7 @@
         <v>15</v>
       </c>
       <c r="C296">
-        <v>0.31647002386855</v>
+        <v>0.3103039735596185</v>
       </c>
       <c r="D296" t="s">
         <v>7</v>
@@ -9375,7 +9375,7 @@
         <v>10</v>
       </c>
       <c r="C297">
-        <v>0.4461867059106271</v>
+        <v>0.4807373160734532</v>
       </c>
       <c r="D297" t="s">
         <v>7</v>
@@ -9392,7 +9392,7 @@
         <v>10</v>
       </c>
       <c r="C298">
-        <v>0.3786389595772517</v>
+        <v>0.4200955987668332</v>
       </c>
       <c r="D298" t="s">
         <v>7</v>
@@ -9406,10 +9406,10 @@
         <v>606</v>
       </c>
       <c r="B299" t="s">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="C299">
-        <v>0.2614565070052689</v>
+        <v>0.2524775006484014</v>
       </c>
       <c r="D299" t="s">
         <v>7</v>
@@ -9426,7 +9426,7 @@
         <v>10</v>
       </c>
       <c r="C300">
-        <v>0.3069831753375744</v>
+        <v>0.3455403646262921</v>
       </c>
       <c r="D300" t="s">
         <v>7</v>
@@ -9443,7 +9443,7 @@
         <v>6</v>
       </c>
       <c r="C301">
-        <v>0.3772454891940416</v>
+        <v>0.3747488225476935</v>
       </c>
       <c r="D301" t="s">
         <v>7</v>
@@ -9460,7 +9460,7 @@
         <v>44</v>
       </c>
       <c r="C302">
-        <v>0.4647148423079107</v>
+        <v>0.4499423980233307</v>
       </c>
       <c r="D302" t="s">
         <v>7</v>
@@ -9477,7 +9477,7 @@
         <v>10</v>
       </c>
       <c r="C303">
-        <v>0.297020710519695</v>
+        <v>0.3354929241022565</v>
       </c>
       <c r="D303" t="s">
         <v>7</v>
@@ -9491,10 +9491,10 @@
         <v>616</v>
       </c>
       <c r="B304" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C304">
-        <v>0.2845574363802308</v>
+        <v>0.3216877582690376</v>
       </c>
       <c r="D304" t="s">
         <v>7</v>
@@ -9511,7 +9511,7 @@
         <v>44</v>
       </c>
       <c r="C305">
-        <v>0.3920697688182801</v>
+        <v>0.3778045767895376</v>
       </c>
       <c r="D305" t="s">
         <v>7</v>
@@ -9528,7 +9528,7 @@
         <v>15</v>
       </c>
       <c r="C306">
-        <v>0.4327029435863228</v>
+        <v>0.4242393695327802</v>
       </c>
       <c r="D306" t="s">
         <v>7</v>
@@ -9545,7 +9545,7 @@
         <v>6</v>
       </c>
       <c r="C307">
-        <v>0.4448386609192092</v>
+        <v>0.4365555623360072</v>
       </c>
       <c r="D307" t="s">
         <v>7</v>
@@ -9562,7 +9562,7 @@
         <v>6</v>
       </c>
       <c r="C308">
-        <v>0.411670927673743</v>
+        <v>0.4084385285716082</v>
       </c>
       <c r="D308" t="s">
         <v>7</v>
@@ -9579,7 +9579,7 @@
         <v>6</v>
       </c>
       <c r="C309">
-        <v>0.2937885960814636</v>
+        <v>0.2920834437777971</v>
       </c>
       <c r="D309" t="s">
         <v>7</v>
@@ -9596,7 +9596,7 @@
         <v>6</v>
       </c>
       <c r="C310">
-        <v>0.4315434292576864</v>
+        <v>0.4337616798969857</v>
       </c>
       <c r="D310" t="s">
         <v>7</v>
@@ -9613,7 +9613,7 @@
         <v>15</v>
       </c>
       <c r="C311">
-        <v>0.3540259463510645</v>
+        <v>0.3479273220095984</v>
       </c>
       <c r="D311" t="s">
         <v>7</v>
@@ -9630,7 +9630,7 @@
         <v>15</v>
       </c>
       <c r="C312">
-        <v>0.2768119430270821</v>
+        <v>0.2708021174766714</v>
       </c>
       <c r="D312" t="s">
         <v>7</v>
@@ -9647,7 +9647,7 @@
         <v>44</v>
       </c>
       <c r="C313">
-        <v>0.3012457618750705</v>
+        <v>0.2874787165647144</v>
       </c>
       <c r="D313" t="s">
         <v>7</v>
@@ -9661,10 +9661,10 @@
         <v>636</v>
       </c>
       <c r="B314" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C314">
-        <v>0.2995085983059964</v>
+        <v>0.3248328094408092</v>
       </c>
       <c r="D314" t="s">
         <v>7</v>
@@ -9681,7 +9681,7 @@
         <v>44</v>
       </c>
       <c r="C315">
-        <v>0.4962980691585901</v>
+        <v>0.4883754289138955</v>
       </c>
       <c r="D315" t="s">
         <v>7</v>
@@ -9698,7 +9698,7 @@
         <v>6</v>
       </c>
       <c r="C316">
-        <v>0.4037849190072293</v>
+        <v>0.4055371276178646</v>
       </c>
       <c r="D316" t="s">
         <v>7</v>
@@ -9715,7 +9715,7 @@
         <v>6</v>
       </c>
       <c r="C317">
-        <v>0.5463630362204773</v>
+        <v>0.5489745976485709</v>
       </c>
       <c r="D317" t="s">
         <v>7</v>
@@ -9732,7 +9732,7 @@
         <v>6</v>
       </c>
       <c r="C318">
-        <v>0.5759136010683347</v>
+        <v>0.5784795385262173</v>
       </c>
       <c r="D318" t="s">
         <v>7</v>
@@ -9749,7 +9749,7 @@
         <v>6</v>
       </c>
       <c r="C319">
-        <v>0.363716438702583</v>
+        <v>0.3614309916785954</v>
       </c>
       <c r="D319" t="s">
         <v>7</v>
@@ -9763,10 +9763,10 @@
         <v>648</v>
       </c>
       <c r="B320" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C320">
-        <v>0.2863753170948884</v>
+        <v>0.295698953892377</v>
       </c>
       <c r="D320" t="s">
         <v>7</v>
@@ -9783,7 +9783,7 @@
         <v>6</v>
       </c>
       <c r="C321">
-        <v>0.3686780475055504</v>
+        <v>0.3642276397662745</v>
       </c>
       <c r="D321" t="s">
         <v>7</v>
@@ -9800,7 +9800,7 @@
         <v>6</v>
       </c>
       <c r="C322">
-        <v>0.3930228852079471</v>
+        <v>0.3925672748425564</v>
       </c>
       <c r="D322" t="s">
         <v>7</v>
@@ -9817,7 +9817,7 @@
         <v>10</v>
       </c>
       <c r="C323">
-        <v>0.3032407914181701</v>
+        <v>0.3437570586634285</v>
       </c>
       <c r="D323" t="s">
         <v>7</v>
@@ -9834,7 +9834,7 @@
         <v>44</v>
       </c>
       <c r="C324">
-        <v>0.3945970107533279</v>
+        <v>0.3804065056232418</v>
       </c>
       <c r="D324" t="s">
         <v>7</v>
@@ -9851,7 +9851,7 @@
         <v>6</v>
       </c>
       <c r="C325">
-        <v>0.2353620251354855</v>
+        <v>0.2356224070171135</v>
       </c>
       <c r="D325" t="s">
         <v>7</v>
@@ -9868,7 +9868,7 @@
         <v>44</v>
       </c>
       <c r="C326">
-        <v>0.3568842267624615</v>
+        <v>0.3413757341335001</v>
       </c>
       <c r="D326" t="s">
         <v>7</v>
@@ -9885,7 +9885,7 @@
         <v>44</v>
       </c>
       <c r="C327">
-        <v>0.3159347296001412</v>
+        <v>0.2987498098239033</v>
       </c>
       <c r="D327" t="s">
         <v>7</v>
@@ -9902,7 +9902,7 @@
         <v>6</v>
       </c>
       <c r="C328">
-        <v>0.2895979869722479</v>
+        <v>0.2904675178505768</v>
       </c>
       <c r="D328" t="s">
         <v>7</v>
@@ -9916,10 +9916,10 @@
         <v>666</v>
       </c>
       <c r="B329" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C329">
-        <v>0.3050517502872068</v>
+        <v>0.3122871886463582</v>
       </c>
       <c r="D329" t="s">
         <v>7</v>
@@ -9936,7 +9936,7 @@
         <v>15</v>
       </c>
       <c r="C330">
-        <v>0.3207628518523722</v>
+        <v>0.3128123261310653</v>
       </c>
       <c r="D330" t="s">
         <v>7</v>
@@ -9950,10 +9950,10 @@
         <v>670</v>
       </c>
       <c r="B331" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C331">
-        <v>0.3625476441132194</v>
+        <v>0.3844592891868911</v>
       </c>
       <c r="D331" t="s">
         <v>7</v>
@@ -9970,7 +9970,7 @@
         <v>10</v>
       </c>
       <c r="C332">
-        <v>0.3314768216021105</v>
+        <v>0.3703700780292697</v>
       </c>
       <c r="D332" t="s">
         <v>7</v>
@@ -9987,7 +9987,7 @@
         <v>6</v>
       </c>
       <c r="C333">
-        <v>0.498785131249303</v>
+        <v>0.497302666525147</v>
       </c>
       <c r="D333" t="s">
         <v>7</v>
@@ -10004,7 +10004,7 @@
         <v>15</v>
       </c>
       <c r="C334">
-        <v>0.3109644642924358</v>
+        <v>0.3016694107581541</v>
       </c>
       <c r="D334" t="s">
         <v>7</v>
@@ -10021,7 +10021,7 @@
         <v>15</v>
       </c>
       <c r="C335">
-        <v>0.3602587934751963</v>
+        <v>0.35162694260983</v>
       </c>
       <c r="D335" t="s">
         <v>7</v>
@@ -10038,7 +10038,7 @@
         <v>10</v>
       </c>
       <c r="C336">
-        <v>0.2964386002610418</v>
+        <v>0.3371514135705274</v>
       </c>
       <c r="D336" t="s">
         <v>7</v>
@@ -10055,7 +10055,7 @@
         <v>44</v>
       </c>
       <c r="C337">
-        <v>0.4241081538787879</v>
+        <v>0.4090382703850409</v>
       </c>
       <c r="D337" t="s">
         <v>7</v>
@@ -10072,7 +10072,7 @@
         <v>6</v>
       </c>
       <c r="C338">
-        <v>0.3059839463585597</v>
+        <v>0.3029896507449228</v>
       </c>
       <c r="D338" t="s">
         <v>7</v>
@@ -10089,7 +10089,7 @@
         <v>15</v>
       </c>
       <c r="C339">
-        <v>0.4488125767406623</v>
+        <v>0.4368703040143213</v>
       </c>
       <c r="D339" t="s">
         <v>7</v>
@@ -10106,7 +10106,7 @@
         <v>15</v>
       </c>
       <c r="C340">
-        <v>0.3092850089601737</v>
+        <v>0.3025823773188602</v>
       </c>
       <c r="D340" t="s">
         <v>7</v>
@@ -10123,7 +10123,7 @@
         <v>6</v>
       </c>
       <c r="C341">
-        <v>0.3199619604131295</v>
+        <v>0.3176665607114111</v>
       </c>
       <c r="D341" t="s">
         <v>7</v>
@@ -10140,7 +10140,7 @@
         <v>10</v>
       </c>
       <c r="C342">
-        <v>0.2599200427163789</v>
+        <v>0.2997969228385018</v>
       </c>
       <c r="D342" t="s">
         <v>7</v>
@@ -10157,7 +10157,7 @@
         <v>10</v>
       </c>
       <c r="C343">
-        <v>0.3626864552144133</v>
+        <v>0.4007831953457259</v>
       </c>
       <c r="D343" t="s">
         <v>7</v>
@@ -10171,10 +10171,10 @@
         <v>696</v>
       </c>
       <c r="B344" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C344">
-        <v>0.2636954719468262</v>
+        <v>0.2661619623036122</v>
       </c>
       <c r="D344" t="s">
         <v>7</v>
@@ -10191,7 +10191,7 @@
         <v>6</v>
       </c>
       <c r="C345">
-        <v>0.388883225275534</v>
+        <v>0.3860233925178349</v>
       </c>
       <c r="D345" t="s">
         <v>7</v>
@@ -10205,10 +10205,10 @@
         <v>700</v>
       </c>
       <c r="B346" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C346">
-        <v>0.309315977886474</v>
+        <v>0.3481786625922345</v>
       </c>
       <c r="D346" t="s">
         <v>7</v>
@@ -10225,7 +10225,7 @@
         <v>15</v>
       </c>
       <c r="C347">
-        <v>0.353117337830763</v>
+        <v>0.347702657098271</v>
       </c>
       <c r="D347" t="s">
         <v>7</v>
@@ -10242,7 +10242,7 @@
         <v>6</v>
       </c>
       <c r="C348">
-        <v>0.3696405409763551</v>
+        <v>0.3720000885758864</v>
       </c>
       <c r="D348" t="s">
         <v>7</v>
@@ -10259,7 +10259,7 @@
         <v>6</v>
       </c>
       <c r="C349">
-        <v>0.513983737280778</v>
+        <v>0.5197846889563319</v>
       </c>
       <c r="D349" t="s">
         <v>7</v>
@@ -10276,7 +10276,7 @@
         <v>15</v>
       </c>
       <c r="C350">
-        <v>0.3576146477649211</v>
+        <v>0.3488719914905639</v>
       </c>
       <c r="D350" t="s">
         <v>7</v>
@@ -10290,10 +10290,10 @@
         <v>710</v>
       </c>
       <c r="B351" t="s">
-        <v>145</v>
+        <v>15</v>
       </c>
       <c r="C351">
-        <v>0.235790518634051</v>
+        <v>0.2176045848341975</v>
       </c>
       <c r="D351" t="s">
         <v>7</v>
@@ -10310,7 +10310,7 @@
         <v>15</v>
       </c>
       <c r="C352">
-        <v>0.4040108579419713</v>
+        <v>0.3934393287978882</v>
       </c>
       <c r="D352" t="s">
         <v>7</v>
@@ -10327,7 +10327,7 @@
         <v>10</v>
       </c>
       <c r="C353">
-        <v>0.3581954370321566</v>
+        <v>0.3951806262299788</v>
       </c>
       <c r="D353" t="s">
         <v>7</v>
@@ -10344,7 +10344,7 @@
         <v>6</v>
       </c>
       <c r="C354">
-        <v>0.3049797225403081</v>
+        <v>0.3034596214015366</v>
       </c>
       <c r="D354" t="s">
         <v>7</v>
@@ -10361,7 +10361,7 @@
         <v>6</v>
       </c>
       <c r="C355">
-        <v>0.3969309993503536</v>
+        <v>0.3986534145306802</v>
       </c>
       <c r="D355" t="s">
         <v>7</v>
@@ -10378,7 +10378,7 @@
         <v>6</v>
       </c>
       <c r="C356">
-        <v>0.3407877361791164</v>
+        <v>0.3380822780293535</v>
       </c>
       <c r="D356" t="s">
         <v>7</v>
@@ -10395,7 +10395,7 @@
         <v>6</v>
       </c>
       <c r="C357">
-        <v>0.4255386120104166</v>
+        <v>0.4245321215717899</v>
       </c>
       <c r="D357" t="s">
         <v>7</v>
@@ -10412,7 +10412,7 @@
         <v>6</v>
       </c>
       <c r="C358">
-        <v>0.3629317565929992</v>
+        <v>0.3665752255594775</v>
       </c>
       <c r="D358" t="s">
         <v>7</v>
@@ -10429,7 +10429,7 @@
         <v>44</v>
       </c>
       <c r="C359">
-        <v>0.4462201855437908</v>
+        <v>0.4356235926214044</v>
       </c>
       <c r="D359" t="s">
         <v>7</v>
@@ -10446,7 +10446,7 @@
         <v>6</v>
       </c>
       <c r="C360">
-        <v>0.5033708441126752</v>
+        <v>0.511203262600149</v>
       </c>
       <c r="D360" t="s">
         <v>7</v>
@@ -10463,7 +10463,7 @@
         <v>15</v>
       </c>
       <c r="C361">
-        <v>0.3103602430659022</v>
+        <v>0.3053546882497893</v>
       </c>
       <c r="D361" t="s">
         <v>7</v>
@@ -10480,7 +10480,7 @@
         <v>6</v>
       </c>
       <c r="C362">
-        <v>0.3852494574372063</v>
+        <v>0.3823230052040431</v>
       </c>
       <c r="D362" t="s">
         <v>7</v>
@@ -10497,7 +10497,7 @@
         <v>6</v>
       </c>
       <c r="C363">
-        <v>0.3070595943506313</v>
+        <v>0.3045775689334734</v>
       </c>
       <c r="D363" t="s">
         <v>7</v>
@@ -10514,7 +10514,7 @@
         <v>10</v>
       </c>
       <c r="C364">
-        <v>0.2898821486936167</v>
+        <v>0.3294291407550929</v>
       </c>
       <c r="D364" t="s">
         <v>7</v>
@@ -10531,7 +10531,7 @@
         <v>15</v>
       </c>
       <c r="C365">
-        <v>0.3239092996795535</v>
+        <v>0.318595990836043</v>
       </c>
       <c r="D365" t="s">
         <v>7</v>
@@ -10548,7 +10548,7 @@
         <v>15</v>
       </c>
       <c r="C366">
-        <v>0.2760018428062074</v>
+        <v>0.2699595557704939</v>
       </c>
       <c r="D366" t="s">
         <v>7</v>
@@ -10565,7 +10565,7 @@
         <v>6</v>
       </c>
       <c r="C367">
-        <v>0.3701468544137403</v>
+        <v>0.3745690451921381</v>
       </c>
       <c r="D367" t="s">
         <v>7</v>
@@ -10582,7 +10582,7 @@
         <v>15</v>
       </c>
       <c r="C368">
-        <v>0.3657060461591357</v>
+        <v>0.3571800647067478</v>
       </c>
       <c r="D368" t="s">
         <v>7</v>
@@ -10599,7 +10599,7 @@
         <v>6</v>
       </c>
       <c r="C369">
-        <v>0.5508193368647804</v>
+        <v>0.5516073154480963</v>
       </c>
       <c r="D369" t="s">
         <v>7</v>
@@ -10616,7 +10616,7 @@
         <v>15</v>
       </c>
       <c r="C370">
-        <v>0.346873274461757</v>
+        <v>0.3406151055685691</v>
       </c>
       <c r="D370" t="s">
         <v>7</v>
@@ -10633,7 +10633,7 @@
         <v>6</v>
       </c>
       <c r="C371">
-        <v>0.4953715652262097</v>
+        <v>0.4963157689670968</v>
       </c>
       <c r="D371" t="s">
         <v>7</v>
@@ -10650,7 +10650,7 @@
         <v>6</v>
       </c>
       <c r="C372">
-        <v>0.3980059874345931</v>
+        <v>0.3971596105542878</v>
       </c>
       <c r="D372" t="s">
         <v>7</v>
@@ -10667,7 +10667,7 @@
         <v>6</v>
       </c>
       <c r="C373">
-        <v>0.4663199570988534</v>
+        <v>0.4619233287214545</v>
       </c>
       <c r="D373" t="s">
         <v>7</v>
@@ -10684,7 +10684,7 @@
         <v>6</v>
       </c>
       <c r="C374">
-        <v>0.5158360648798389</v>
+        <v>0.5196878220721087</v>
       </c>
       <c r="D374" t="s">
         <v>7</v>
@@ -10701,7 +10701,7 @@
         <v>6</v>
       </c>
       <c r="C375">
-        <v>0.4955184215924993</v>
+        <v>0.4955066343623892</v>
       </c>
       <c r="D375" t="s">
         <v>7</v>
@@ -10718,7 +10718,7 @@
         <v>15</v>
       </c>
       <c r="C376">
-        <v>0.3633245181856611</v>
+        <v>0.3544426930154435</v>
       </c>
       <c r="D376" t="s">
         <v>7</v>
@@ -10735,7 +10735,7 @@
         <v>6</v>
       </c>
       <c r="C377">
-        <v>0.5056865726655022</v>
+        <v>0.5077492670741895</v>
       </c>
       <c r="D377" t="s">
         <v>7</v>
@@ -10752,7 +10752,7 @@
         <v>6</v>
       </c>
       <c r="C378">
-        <v>0.3363320361311882</v>
+        <v>0.333740518037141</v>
       </c>
       <c r="D378" t="s">
         <v>7</v>
@@ -10769,7 +10769,7 @@
         <v>6</v>
       </c>
       <c r="C379">
-        <v>0.348918908483048</v>
+        <v>0.3460467747833555</v>
       </c>
       <c r="D379" t="s">
         <v>7</v>
@@ -10786,7 +10786,7 @@
         <v>6</v>
       </c>
       <c r="C380">
-        <v>0.3983738653560592</v>
+        <v>0.3959269424844753</v>
       </c>
       <c r="D380" t="s">
         <v>7</v>
@@ -10803,7 +10803,7 @@
         <v>10</v>
       </c>
       <c r="C381">
-        <v>0.4594241133485151</v>
+        <v>0.4932532901732231</v>
       </c>
       <c r="D381" t="s">
         <v>7</v>
@@ -10820,7 +10820,7 @@
         <v>6</v>
       </c>
       <c r="C382">
-        <v>0.3536359205544146</v>
+        <v>0.3504624302153623</v>
       </c>
       <c r="D382" t="s">
         <v>7</v>
@@ -10837,7 +10837,7 @@
         <v>10</v>
       </c>
       <c r="C383">
-        <v>0.3532667150252892</v>
+        <v>0.3900461620724764</v>
       </c>
       <c r="D383" t="s">
         <v>7</v>
@@ -10854,7 +10854,7 @@
         <v>44</v>
       </c>
       <c r="C384">
-        <v>0.4290164798473723</v>
+        <v>0.4180858424687868</v>
       </c>
       <c r="D384" t="s">
         <v>7</v>
@@ -10871,7 +10871,7 @@
         <v>6</v>
       </c>
       <c r="C385">
-        <v>0.426095480826498</v>
+        <v>0.4247957748907084</v>
       </c>
       <c r="D385" t="s">
         <v>7</v>
@@ -10885,10 +10885,10 @@
         <v>780</v>
       </c>
       <c r="B386" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C386">
-        <v>0.3065141044439668</v>
+        <v>0.3050672215164482</v>
       </c>
       <c r="D386" t="s">
         <v>7</v>
@@ -10905,7 +10905,7 @@
         <v>10</v>
       </c>
       <c r="C387">
-        <v>0.402668245199555</v>
+        <v>0.4316418949826951</v>
       </c>
       <c r="D387" t="s">
         <v>7</v>
@@ -10919,10 +10919,10 @@
         <v>784</v>
       </c>
       <c r="B388" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="C388">
-        <v>0.2774931476960985</v>
+        <v>0.2683457678163202</v>
       </c>
       <c r="D388" t="s">
         <v>7</v>
@@ -10939,7 +10939,7 @@
         <v>6</v>
       </c>
       <c r="C389">
-        <v>0.3839907038671397</v>
+        <v>0.3819918884232045</v>
       </c>
       <c r="D389" t="s">
         <v>7</v>
@@ -10956,7 +10956,7 @@
         <v>15</v>
       </c>
       <c r="C390">
-        <v>0.3390748354355828</v>
+        <v>0.3308178730906043</v>
       </c>
       <c r="D390" t="s">
         <v>7</v>
@@ -10973,7 +10973,7 @@
         <v>15</v>
       </c>
       <c r="C391">
-        <v>0.349082384357114</v>
+        <v>0.3456669499888304</v>
       </c>
       <c r="D391" t="s">
         <v>7</v>
@@ -10990,7 +10990,7 @@
         <v>10</v>
       </c>
       <c r="C392">
-        <v>0.3068823898419369</v>
+        <v>0.3476963549269781</v>
       </c>
       <c r="D392" t="s">
         <v>7</v>
@@ -11007,7 +11007,7 @@
         <v>10</v>
       </c>
       <c r="C393">
-        <v>0.3704367171497558</v>
+        <v>0.4032055482890283</v>
       </c>
       <c r="D393" t="s">
         <v>7</v>
@@ -11024,7 +11024,7 @@
         <v>15</v>
       </c>
       <c r="C394">
-        <v>0.3728561045939273</v>
+        <v>0.3655351157687693</v>
       </c>
       <c r="D394" t="s">
         <v>7</v>
@@ -11041,7 +11041,7 @@
         <v>10</v>
       </c>
       <c r="C395">
-        <v>0.4052078357104421</v>
+        <v>0.4377684078431449</v>
       </c>
       <c r="D395" t="s">
         <v>7</v>
@@ -11058,7 +11058,7 @@
         <v>6</v>
       </c>
       <c r="C396">
-        <v>0.4142476926055175</v>
+        <v>0.4089714416600206</v>
       </c>
       <c r="D396" t="s">
         <v>7</v>
@@ -11075,7 +11075,7 @@
         <v>10</v>
       </c>
       <c r="C397">
-        <v>0.3265848531495993</v>
+        <v>0.3634638456785183</v>
       </c>
       <c r="D397" t="s">
         <v>7</v>
@@ -11092,7 +11092,7 @@
         <v>6</v>
       </c>
       <c r="C398">
-        <v>0.5171753097355651</v>
+        <v>0.5259846379554584</v>
       </c>
       <c r="D398" t="s">
         <v>7</v>
@@ -11109,7 +11109,7 @@
         <v>15</v>
       </c>
       <c r="C399">
-        <v>0.359110174201243</v>
+        <v>0.3529206668680227</v>
       </c>
       <c r="D399" t="s">
         <v>7</v>
@@ -11126,7 +11126,7 @@
         <v>6</v>
       </c>
       <c r="C400">
-        <v>0.3595376531454739</v>
+        <v>0.3551220776514941</v>
       </c>
       <c r="D400" t="s">
         <v>7</v>
@@ -11143,7 +11143,7 @@
         <v>15</v>
       </c>
       <c r="C401">
-        <v>0.4491970303849152</v>
+        <v>0.4386358965097541</v>
       </c>
       <c r="D401" t="s">
         <v>7</v>
@@ -11160,7 +11160,7 @@
         <v>6</v>
       </c>
       <c r="C402">
-        <v>0.4184848925417775</v>
+        <v>0.4168266000497324</v>
       </c>
       <c r="D402" t="s">
         <v>7</v>
@@ -11177,7 +11177,7 @@
         <v>6</v>
       </c>
       <c r="C403">
-        <v>0.3209324868781458</v>
+        <v>0.3189583322935164</v>
       </c>
       <c r="D403" t="s">
         <v>7</v>
@@ -11194,7 +11194,7 @@
         <v>10</v>
       </c>
       <c r="C404">
-        <v>0.3039870382240839</v>
+        <v>0.3439018526498435</v>
       </c>
       <c r="D404" t="s">
         <v>7</v>
@@ -11211,7 +11211,7 @@
         <v>6</v>
       </c>
       <c r="C405">
-        <v>0.4425219944794893</v>
+        <v>0.4450263281443648</v>
       </c>
       <c r="D405" t="s">
         <v>7</v>
@@ -11225,10 +11225,10 @@
         <v>820</v>
       </c>
       <c r="B406" t="s">
-        <v>145</v>
+        <v>6</v>
       </c>
       <c r="C406">
-        <v>0.441771558854837</v>
+        <v>0.4328416846778186</v>
       </c>
       <c r="D406" t="s">
         <v>7</v>
@@ -11245,7 +11245,7 @@
         <v>6</v>
       </c>
       <c r="C407">
-        <v>0.4208688108277057</v>
+        <v>0.4180981905031739</v>
       </c>
       <c r="D407" t="s">
         <v>7</v>
@@ -11262,7 +11262,7 @@
         <v>6</v>
       </c>
       <c r="C408">
-        <v>0.4869595497511841</v>
+        <v>0.4875012093812901</v>
       </c>
       <c r="D408" t="s">
         <v>7</v>
@@ -11279,7 +11279,7 @@
         <v>6</v>
       </c>
       <c r="C409">
-        <v>0.5030077508215334</v>
+        <v>0.505176461975258</v>
       </c>
       <c r="D409" t="s">
         <v>7</v>
@@ -11296,7 +11296,7 @@
         <v>15</v>
       </c>
       <c r="C410">
-        <v>0.2960414899254465</v>
+        <v>0.2905111540672021</v>
       </c>
       <c r="D410" t="s">
         <v>7</v>
@@ -11313,7 +11313,7 @@
         <v>6</v>
       </c>
       <c r="C411">
-        <v>0.3465222906359068</v>
+        <v>0.3432368747437616</v>
       </c>
       <c r="D411" t="s">
         <v>7</v>
@@ -11330,7 +11330,7 @@
         <v>6</v>
       </c>
       <c r="C412">
-        <v>0.4556504430586393</v>
+        <v>0.4537856218305445</v>
       </c>
       <c r="D412" t="s">
         <v>7</v>
@@ -11347,7 +11347,7 @@
         <v>6</v>
       </c>
       <c r="C413">
-        <v>0.2827496322710187</v>
+        <v>0.2813769465039372</v>
       </c>
       <c r="D413" t="s">
         <v>7</v>
@@ -11364,7 +11364,7 @@
         <v>15</v>
       </c>
       <c r="C414">
-        <v>0.3201252396396334</v>
+        <v>0.313160858620894</v>
       </c>
       <c r="D414" t="s">
         <v>7</v>
@@ -11381,7 +11381,7 @@
         <v>15</v>
       </c>
       <c r="C415">
-        <v>0.3662716461415004</v>
+        <v>0.3599111410924816</v>
       </c>
       <c r="D415" t="s">
         <v>7</v>
@@ -11398,7 +11398,7 @@
         <v>15</v>
       </c>
       <c r="C416">
-        <v>0.4422239922013177</v>
+        <v>0.4384334471231472</v>
       </c>
       <c r="D416" t="s">
         <v>7</v>
@@ -11415,7 +11415,7 @@
         <v>6</v>
       </c>
       <c r="C417">
-        <v>0.2953305560228429</v>
+        <v>0.2988175555448305</v>
       </c>
       <c r="D417" t="s">
         <v>7</v>
@@ -11432,7 +11432,7 @@
         <v>10</v>
       </c>
       <c r="C418">
-        <v>0.2968244345907722</v>
+        <v>0.3330670421980722</v>
       </c>
       <c r="D418" t="s">
         <v>7</v>
@@ -11449,7 +11449,7 @@
         <v>15</v>
       </c>
       <c r="C419">
-        <v>0.4006120447094201</v>
+        <v>0.3916615964921287</v>
       </c>
       <c r="D419" t="s">
         <v>7</v>
@@ -11466,7 +11466,7 @@
         <v>44</v>
       </c>
       <c r="C420">
-        <v>0.4437514962128905</v>
+        <v>0.4274749604940434</v>
       </c>
       <c r="D420" t="s">
         <v>7</v>
@@ -11483,7 +11483,7 @@
         <v>44</v>
       </c>
       <c r="C421">
-        <v>0.4449266095234198</v>
+        <v>0.4298457874893293</v>
       </c>
       <c r="D421" t="s">
         <v>7</v>
@@ -11500,7 +11500,7 @@
         <v>6</v>
       </c>
       <c r="C422">
-        <v>0.3932800364445031</v>
+        <v>0.3902937783065749</v>
       </c>
       <c r="D422" t="s">
         <v>7</v>
@@ -11517,7 +11517,7 @@
         <v>44</v>
       </c>
       <c r="C423">
-        <v>0.4209390073629534</v>
+        <v>0.4062060854531462</v>
       </c>
       <c r="D423" t="s">
         <v>7</v>
@@ -11534,7 +11534,7 @@
         <v>10</v>
       </c>
       <c r="C424">
-        <v>0.3224082792125115</v>
+        <v>0.3609457515560782</v>
       </c>
       <c r="D424" t="s">
         <v>7</v>
@@ -11551,7 +11551,7 @@
         <v>6</v>
       </c>
       <c r="C425">
-        <v>0.3908717988792995</v>
+        <v>0.3882934835187191</v>
       </c>
       <c r="D425" t="s">
         <v>7</v>
@@ -11568,7 +11568,7 @@
         <v>15</v>
       </c>
       <c r="C426">
-        <v>0.3619722950799887</v>
+        <v>0.3563625995780869</v>
       </c>
       <c r="D426" t="s">
         <v>7</v>
@@ -11585,7 +11585,7 @@
         <v>6</v>
       </c>
       <c r="C427">
-        <v>0.307206403941885</v>
+        <v>0.3059492928211993</v>
       </c>
       <c r="D427" t="s">
         <v>7</v>
@@ -11602,7 +11602,7 @@
         <v>6</v>
       </c>
       <c r="C428">
-        <v>0.296362979653009</v>
+        <v>0.2954483975324781</v>
       </c>
       <c r="D428" t="s">
         <v>7</v>
@@ -11619,7 +11619,7 @@
         <v>10</v>
       </c>
       <c r="C429">
-        <v>0.3325154492541166</v>
+        <v>0.372029639199507</v>
       </c>
       <c r="D429" t="s">
         <v>7</v>
@@ -11636,7 +11636,7 @@
         <v>6</v>
       </c>
       <c r="C430">
-        <v>0.390773548704821</v>
+        <v>0.3883746439588164</v>
       </c>
       <c r="D430" t="s">
         <v>7</v>
@@ -11653,7 +11653,7 @@
         <v>6</v>
       </c>
       <c r="C431">
-        <v>0.3103960866508857</v>
+        <v>0.3096181918101741</v>
       </c>
       <c r="D431" t="s">
         <v>7</v>
@@ -11670,7 +11670,7 @@
         <v>15</v>
       </c>
       <c r="C432">
-        <v>0.3573173998451919</v>
+        <v>0.3504523320555997</v>
       </c>
       <c r="D432" t="s">
         <v>7</v>
@@ -11684,10 +11684,10 @@
         <v>874</v>
       </c>
       <c r="B433" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C433">
-        <v>0.2969301393877559</v>
+        <v>0.303685797671997</v>
       </c>
       <c r="D433" t="s">
         <v>7</v>
@@ -11704,7 +11704,7 @@
         <v>15</v>
       </c>
       <c r="C434">
-        <v>0.3682493745097581</v>
+        <v>0.3616277084661318</v>
       </c>
       <c r="D434" t="s">
         <v>7</v>
@@ -11721,7 +11721,7 @@
         <v>10</v>
       </c>
       <c r="C435">
-        <v>0.375552548115118</v>
+        <v>0.4112036072114286</v>
       </c>
       <c r="D435" t="s">
         <v>7</v>
@@ -11738,7 +11738,7 @@
         <v>15</v>
       </c>
       <c r="C436">
-        <v>0.3595062455578177</v>
+        <v>0.3544849172056468</v>
       </c>
       <c r="D436" t="s">
         <v>7</v>
@@ -11755,7 +11755,7 @@
         <v>10</v>
       </c>
       <c r="C437">
-        <v>0.3012345560384321</v>
+        <v>0.3414222253996815</v>
       </c>
       <c r="D437" t="s">
         <v>7</v>
@@ -11772,7 +11772,7 @@
         <v>15</v>
       </c>
       <c r="C438">
-        <v>0.3631267311904203</v>
+        <v>0.3574003227915734</v>
       </c>
       <c r="D438" t="s">
         <v>7</v>
@@ -11789,7 +11789,7 @@
         <v>6</v>
       </c>
       <c r="C439">
-        <v>0.4139142331339077</v>
+        <v>0.4166555048704128</v>
       </c>
       <c r="D439" t="s">
         <v>7</v>
@@ -11806,7 +11806,7 @@
         <v>10</v>
       </c>
       <c r="C440">
-        <v>0.2934081499320107</v>
+        <v>0.3330771968673975</v>
       </c>
       <c r="D440" t="s">
         <v>7</v>
@@ -11823,7 +11823,7 @@
         <v>6</v>
       </c>
       <c r="C441">
-        <v>0.3620322565712872</v>
+        <v>0.3600103359074219</v>
       </c>
       <c r="D441" t="s">
         <v>7</v>
@@ -11840,7 +11840,7 @@
         <v>6</v>
       </c>
       <c r="C442">
-        <v>0.3315831097365082</v>
+        <v>0.3316003174318093</v>
       </c>
       <c r="D442" t="s">
         <v>7</v>
@@ -11857,7 +11857,7 @@
         <v>15</v>
       </c>
       <c r="C443">
-        <v>0.3095803180311477</v>
+        <v>0.3043549905116072</v>
       </c>
       <c r="D443" t="s">
         <v>7</v>
@@ -11874,7 +11874,7 @@
         <v>10</v>
       </c>
       <c r="C444">
-        <v>0.3288333500761927</v>
+        <v>0.3654775085193007</v>
       </c>
       <c r="D444" t="s">
         <v>7</v>
@@ -11891,7 +11891,7 @@
         <v>6</v>
       </c>
       <c r="C445">
-        <v>0.3903356790911203</v>
+        <v>0.3847944898454261</v>
       </c>
       <c r="D445" t="s">
         <v>7</v>
@@ -11908,7 +11908,7 @@
         <v>44</v>
       </c>
       <c r="C446">
-        <v>0.3341611918108894</v>
+        <v>0.3234248568518121</v>
       </c>
       <c r="D446" t="s">
         <v>7</v>
@@ -11925,7 +11925,7 @@
         <v>6</v>
       </c>
       <c r="C447">
-        <v>0.2992231081618633</v>
+        <v>0.2951646403154087</v>
       </c>
       <c r="D447" t="s">
         <v>7</v>
@@ -11942,7 +11942,7 @@
         <v>6</v>
       </c>
       <c r="C448">
-        <v>0.3996519121181489</v>
+        <v>0.3985067210399059</v>
       </c>
       <c r="D448" t="s">
         <v>7</v>
@@ -11959,7 +11959,7 @@
         <v>6</v>
       </c>
       <c r="C449">
-        <v>0.4323291385311515</v>
+        <v>0.4295791654576813</v>
       </c>
       <c r="D449" t="s">
         <v>7</v>
@@ -11976,7 +11976,7 @@
         <v>44</v>
       </c>
       <c r="C450">
-        <v>0.4032082821877489</v>
+        <v>0.3874648503390166</v>
       </c>
       <c r="D450" t="s">
         <v>7</v>
@@ -11993,7 +11993,7 @@
         <v>44</v>
       </c>
       <c r="C451">
-        <v>0.3808793891628075</v>
+        <v>0.3672442893196977</v>
       </c>
       <c r="D451" t="s">
         <v>7</v>
@@ -12010,7 +12010,7 @@
         <v>6</v>
       </c>
       <c r="C452">
-        <v>0.3634855491286965</v>
+        <v>0.360832537724569</v>
       </c>
       <c r="D452" t="s">
         <v>7</v>
@@ -12027,7 +12027,7 @@
         <v>10</v>
       </c>
       <c r="C453">
-        <v>0.3420707709748624</v>
+        <v>0.3814021530360474</v>
       </c>
       <c r="D453" t="s">
         <v>7</v>
@@ -12044,7 +12044,7 @@
         <v>15</v>
       </c>
       <c r="C454">
-        <v>0.2914084827944642</v>
+        <v>0.2858882224639135</v>
       </c>
       <c r="D454" t="s">
         <v>7</v>
@@ -12061,7 +12061,7 @@
         <v>10</v>
       </c>
       <c r="C455">
-        <v>0.3351227682972485</v>
+        <v>0.376066871198504</v>
       </c>
       <c r="D455" t="s">
         <v>7</v>
@@ -12078,7 +12078,7 @@
         <v>6</v>
       </c>
       <c r="C456">
-        <v>0.4062710307165586</v>
+        <v>0.411688009008557</v>
       </c>
       <c r="D456" t="s">
         <v>7</v>
@@ -12095,7 +12095,7 @@
         <v>15</v>
       </c>
       <c r="C457">
-        <v>0.3641079581717803</v>
+        <v>0.3563520861066659</v>
       </c>
       <c r="D457" t="s">
         <v>7</v>
@@ -12112,7 +12112,7 @@
         <v>6</v>
       </c>
       <c r="C458">
-        <v>0.3716892279439142</v>
+        <v>0.3647467522538397</v>
       </c>
       <c r="D458" t="s">
         <v>7</v>
@@ -12129,7 +12129,7 @@
         <v>6</v>
       </c>
       <c r="C459">
-        <v>0.4176856972719337</v>
+        <v>0.4162889594928032</v>
       </c>
       <c r="D459" t="s">
         <v>7</v>
@@ -12146,7 +12146,7 @@
         <v>6</v>
       </c>
       <c r="C460">
-        <v>0.3680824014179211</v>
+        <v>0.3665363555588175</v>
       </c>
       <c r="D460" t="s">
         <v>7</v>
@@ -12160,10 +12160,10 @@
         <v>930</v>
       </c>
       <c r="B461" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C461">
-        <v>0.315961238965417</v>
+        <v>0.3303211577753296</v>
       </c>
       <c r="D461" t="s">
         <v>7</v>
@@ -12180,7 +12180,7 @@
         <v>6</v>
       </c>
       <c r="C462">
-        <v>0.3587641331431747</v>
+        <v>0.3529202000205535</v>
       </c>
       <c r="D462" t="s">
         <v>7</v>
@@ -12194,10 +12194,10 @@
         <v>934</v>
       </c>
       <c r="B463" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C463">
-        <v>0.2959525900253683</v>
+        <v>0.3264466458215104</v>
       </c>
       <c r="D463" t="s">
         <v>7</v>
@@ -12214,7 +12214,7 @@
         <v>6</v>
       </c>
       <c r="C464">
-        <v>0.4441405108262563</v>
+        <v>0.4502823927568196</v>
       </c>
       <c r="D464" t="s">
         <v>7</v>
@@ -12231,7 +12231,7 @@
         <v>44</v>
       </c>
       <c r="C465">
-        <v>0.3451045785823223</v>
+        <v>0.3291437608617064</v>
       </c>
       <c r="D465" t="s">
         <v>7</v>
@@ -12248,7 +12248,7 @@
         <v>6</v>
       </c>
       <c r="C466">
-        <v>0.559954498053082</v>
+        <v>0.5606403904315983</v>
       </c>
       <c r="D466" t="s">
         <v>7</v>
@@ -12265,7 +12265,7 @@
         <v>6</v>
       </c>
       <c r="C467">
-        <v>0.5070579214647533</v>
+        <v>0.5097555710745921</v>
       </c>
       <c r="D467" t="s">
         <v>7</v>
@@ -12282,7 +12282,7 @@
         <v>6</v>
       </c>
       <c r="C468">
-        <v>0.4160871566845558</v>
+        <v>0.4133916260184147</v>
       </c>
       <c r="D468" t="s">
         <v>7</v>
@@ -12299,7 +12299,7 @@
         <v>15</v>
       </c>
       <c r="C469">
-        <v>0.3036936235714265</v>
+        <v>0.2981015271936502</v>
       </c>
       <c r="D469" t="s">
         <v>7</v>
@@ -12316,7 +12316,7 @@
         <v>6</v>
       </c>
       <c r="C470">
-        <v>0.310824669641773</v>
+        <v>0.3136561122541821</v>
       </c>
       <c r="D470" t="s">
         <v>7</v>
@@ -12333,7 +12333,7 @@
         <v>44</v>
       </c>
       <c r="C471">
-        <v>0.3110792519122317</v>
+        <v>0.2953341017546705</v>
       </c>
       <c r="D471" t="s">
         <v>7</v>
@@ -12350,7 +12350,7 @@
         <v>15</v>
       </c>
       <c r="C472">
-        <v>0.319101540077665</v>
+        <v>0.3118730968811864</v>
       </c>
       <c r="D472" t="s">
         <v>7</v>
@@ -12364,10 +12364,10 @@
         <v>954</v>
       </c>
       <c r="B473" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="C473">
-        <v>0.3116884750881828</v>
+        <v>0.325257301109685</v>
       </c>
       <c r="D473" t="s">
         <v>7</v>
@@ -12381,10 +12381,10 @@
         <v>956</v>
       </c>
       <c r="B474" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C474">
-        <v>0.3389900555740918</v>
+        <v>0.3716456745646817</v>
       </c>
       <c r="D474" t="s">
         <v>7</v>
@@ -12401,7 +12401,7 @@
         <v>6</v>
       </c>
       <c r="C475">
-        <v>0.3623250780778673</v>
+        <v>0.3575972493186278</v>
       </c>
       <c r="D475" t="s">
         <v>7</v>
@@ -12418,7 +12418,7 @@
         <v>6</v>
       </c>
       <c r="C476">
-        <v>0.3538805413162479</v>
+        <v>0.3517216850170807</v>
       </c>
       <c r="D476" t="s">
         <v>7</v>
@@ -12432,10 +12432,10 @@
         <v>962</v>
       </c>
       <c r="B477" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C477">
-        <v>0.312372702103771</v>
+        <v>0.3498048564236744</v>
       </c>
       <c r="D477" t="s">
         <v>7</v>
@@ -12452,7 +12452,7 @@
         <v>6</v>
       </c>
       <c r="C478">
-        <v>0.4215618165511976</v>
+        <v>0.4174539949151669</v>
       </c>
       <c r="D478" t="s">
         <v>7</v>
@@ -12469,7 +12469,7 @@
         <v>44</v>
       </c>
       <c r="C479">
-        <v>0.4001566778067346</v>
+        <v>0.3856595671844311</v>
       </c>
       <c r="D479" t="s">
         <v>7</v>
@@ -12486,7 +12486,7 @@
         <v>6</v>
       </c>
       <c r="C480">
-        <v>0.4975446464462833</v>
+        <v>0.4951659625858403</v>
       </c>
       <c r="D480" t="s">
         <v>7</v>
@@ -12503,7 +12503,7 @@
         <v>44</v>
       </c>
       <c r="C481">
-        <v>0.3623025914536655</v>
+        <v>0.3436271924422239</v>
       </c>
       <c r="D481" t="s">
         <v>7</v>
@@ -12517,10 +12517,10 @@
         <v>972</v>
       </c>
       <c r="B482" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C482">
-        <v>0.2845303846344786</v>
+        <v>0.2957016847531889</v>
       </c>
       <c r="D482" t="s">
         <v>7</v>
@@ -12534,10 +12534,10 @@
         <v>974</v>
       </c>
       <c r="B483" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C483">
-        <v>0.2944433573754238</v>
+        <v>0.3254063779402611</v>
       </c>
       <c r="D483" t="s">
         <v>7</v>
@@ -12554,7 +12554,7 @@
         <v>44</v>
       </c>
       <c r="C484">
-        <v>0.3568733055987396</v>
+        <v>0.3399620469405203</v>
       </c>
       <c r="D484" t="s">
         <v>7</v>
@@ -12571,7 +12571,7 @@
         <v>15</v>
       </c>
       <c r="C485">
-        <v>0.3722099840685633</v>
+        <v>0.365038594226413</v>
       </c>
       <c r="D485" t="s">
         <v>7</v>
@@ -12588,7 +12588,7 @@
         <v>15</v>
       </c>
       <c r="C486">
-        <v>0.404991989599352</v>
+        <v>0.3962088606378225</v>
       </c>
       <c r="D486" t="s">
         <v>7</v>
@@ -12605,7 +12605,7 @@
         <v>44</v>
       </c>
       <c r="C487">
-        <v>0.4323359345254725</v>
+        <v>0.4143946877531354</v>
       </c>
       <c r="D487" t="s">
         <v>7</v>
@@ -12622,7 +12622,7 @@
         <v>10</v>
       </c>
       <c r="C488">
-        <v>0.2664462343663797</v>
+        <v>0.3077846537894847</v>
       </c>
       <c r="D488" t="s">
         <v>7</v>
@@ -12639,7 +12639,7 @@
         <v>6</v>
       </c>
       <c r="C489">
-        <v>0.5257863903256648</v>
+        <v>0.5248876229685931</v>
       </c>
       <c r="D489" t="s">
         <v>7</v>
@@ -12656,7 +12656,7 @@
         <v>15</v>
       </c>
       <c r="C490">
-        <v>0.3406787846767886</v>
+        <v>0.3331479638797427</v>
       </c>
       <c r="D490" t="s">
         <v>7</v>
@@ -12673,7 +12673,7 @@
         <v>6</v>
       </c>
       <c r="C491">
-        <v>0.3179583450362559</v>
+        <v>0.316825920549301</v>
       </c>
       <c r="D491" t="s">
         <v>7</v>
@@ -12690,7 +12690,7 @@
         <v>6</v>
       </c>
       <c r="C492">
-        <v>0.5090904117163787</v>
+        <v>0.5110927555767798</v>
       </c>
       <c r="D492" t="s">
         <v>7</v>
@@ -12707,7 +12707,7 @@
         <v>6</v>
       </c>
       <c r="C493">
-        <v>0.3266215192789174</v>
+        <v>0.3234779171379263</v>
       </c>
       <c r="D493" t="s">
         <v>7</v>
@@ -12724,7 +12724,7 @@
         <v>10</v>
       </c>
       <c r="C494">
-        <v>0.2893575723489397</v>
+        <v>0.3301090573585425</v>
       </c>
       <c r="D494" t="s">
         <v>7</v>
@@ -12741,7 +12741,7 @@
         <v>44</v>
       </c>
       <c r="C495">
-        <v>0.4987870886747073</v>
+        <v>0.4885001432635215</v>
       </c>
       <c r="D495" t="s">
         <v>7</v>
@@ -12758,7 +12758,7 @@
         <v>6</v>
       </c>
       <c r="C496">
-        <v>0.519834632376928</v>
+        <v>0.5183441783769024</v>
       </c>
       <c r="D496" t="s">
         <v>7</v>
@@ -12775,7 +12775,7 @@
         <v>10</v>
       </c>
       <c r="C497">
-        <v>0.3396803814981904</v>
+        <v>0.3792003975282267</v>
       </c>
       <c r="D497" t="s">
         <v>7</v>
@@ -12792,7 +12792,7 @@
         <v>6</v>
       </c>
       <c r="C498">
-        <v>0.6761671687299718</v>
+        <v>0.6856780407949887</v>
       </c>
       <c r="D498" t="s">
         <v>7</v>
@@ -12809,7 +12809,7 @@
         <v>15</v>
       </c>
       <c r="C499">
-        <v>0.3473675714186414</v>
+        <v>0.3417685369373382</v>
       </c>
       <c r="D499" t="s">
         <v>7</v>
@@ -12826,7 +12826,7 @@
         <v>6</v>
       </c>
       <c r="C500">
-        <v>0.4617075998454622</v>
+        <v>0.4567176251519505</v>
       </c>
       <c r="D500" t="s">
         <v>7</v>
@@ -12843,7 +12843,7 @@
         <v>15</v>
       </c>
       <c r="C501">
-        <v>0.4215186073404895</v>
+        <v>0.4116508942026493</v>
       </c>
       <c r="D501" t="s">
         <v>7</v>
@@ -12860,7 +12860,7 @@
         <v>6</v>
       </c>
       <c r="C502">
-        <v>0.5974032914677929</v>
+        <v>0.5999193392983247</v>
       </c>
       <c r="D502" t="s">
         <v>7</v>
@@ -12877,7 +12877,7 @@
         <v>15</v>
       </c>
       <c r="C503">
-        <v>0.3632921331179927</v>
+        <v>0.3552854428830499</v>
       </c>
       <c r="D503" t="s">
         <v>7</v>
@@ -12894,7 +12894,7 @@
         <v>15</v>
       </c>
       <c r="C504">
-        <v>0.3323556895979893</v>
+        <v>0.3267164136648908</v>
       </c>
       <c r="D504" t="s">
         <v>7</v>
@@ -12911,7 +12911,7 @@
         <v>6</v>
       </c>
       <c r="C505">
-        <v>0.4742675728342634</v>
+        <v>0.4708142439296356</v>
       </c>
       <c r="D505" t="s">
         <v>7</v>
@@ -12928,7 +12928,7 @@
         <v>15</v>
       </c>
       <c r="C506">
-        <v>0.4938964731857792</v>
+        <v>0.4837899268928352</v>
       </c>
       <c r="D506" t="s">
         <v>7</v>
@@ -12945,7 +12945,7 @@
         <v>6</v>
       </c>
       <c r="C507">
-        <v>0.3578671454418533</v>
+        <v>0.35287160294067</v>
       </c>
       <c r="D507" t="s">
         <v>7</v>
@@ -12962,7 +12962,7 @@
         <v>15</v>
       </c>
       <c r="C508">
-        <v>0.3327277441120651</v>
+        <v>0.3255222347943177</v>
       </c>
       <c r="D508" t="s">
         <v>7</v>
@@ -12979,7 +12979,7 @@
         <v>10</v>
       </c>
       <c r="C509">
-        <v>0.4636850741696669</v>
+        <v>0.497865832126888</v>
       </c>
       <c r="D509" t="s">
         <v>7</v>
@@ -12996,7 +12996,7 @@
         <v>10</v>
       </c>
       <c r="C510">
-        <v>0.3434269996685428</v>
+        <v>0.383196896333221</v>
       </c>
       <c r="D510" t="s">
         <v>7</v>
@@ -13013,7 +13013,7 @@
         <v>44</v>
       </c>
       <c r="C511">
-        <v>0.3318059001258545</v>
+        <v>0.3205450730910451</v>
       </c>
       <c r="D511" t="s">
         <v>7</v>
@@ -13030,7 +13030,7 @@
         <v>6</v>
       </c>
       <c r="C512">
-        <v>0.3245033109525624</v>
+        <v>0.3217168188825872</v>
       </c>
       <c r="D512" t="s">
         <v>7</v>
@@ -13047,7 +13047,7 @@
         <v>6</v>
       </c>
       <c r="C513">
-        <v>0.3928126810720414</v>
+        <v>0.3901969622588061</v>
       </c>
       <c r="D513" t="s">
         <v>7</v>
@@ -13064,7 +13064,7 @@
         <v>44</v>
       </c>
       <c r="C514">
-        <v>0.3851928333215255</v>
+        <v>0.3713388344733529</v>
       </c>
       <c r="D514" t="s">
         <v>7</v>
@@ -13081,7 +13081,7 @@
         <v>6</v>
       </c>
       <c r="C515">
-        <v>0.5255465895838465</v>
+        <v>0.5286874371227759</v>
       </c>
       <c r="D515" t="s">
         <v>7</v>
@@ -13098,7 +13098,7 @@
         <v>6</v>
       </c>
       <c r="C516">
-        <v>0.3183298173721873</v>
+        <v>0.317596827468401</v>
       </c>
       <c r="D516" t="s">
         <v>7</v>
@@ -13115,7 +13115,7 @@
         <v>15</v>
       </c>
       <c r="C517">
-        <v>0.3538022752668876</v>
+        <v>0.3480709747363355</v>
       </c>
       <c r="D517" t="s">
         <v>7</v>
@@ -13132,7 +13132,7 @@
         <v>10</v>
       </c>
       <c r="C518">
-        <v>0.2972484167886799</v>
+        <v>0.3385597732406303</v>
       </c>
       <c r="D518" t="s">
         <v>7</v>
@@ -13149,7 +13149,7 @@
         <v>44</v>
       </c>
       <c r="C519">
-        <v>0.5024211308031022</v>
+        <v>0.48764200902269</v>
       </c>
       <c r="D519" t="s">
         <v>7</v>
@@ -13166,7 +13166,7 @@
         <v>15</v>
       </c>
       <c r="C520">
-        <v>0.335990314202335</v>
+        <v>0.3300766972029622</v>
       </c>
       <c r="D520" t="s">
         <v>7</v>
@@ -13183,7 +13183,7 @@
         <v>10</v>
       </c>
       <c r="C521">
-        <v>0.2929376359647182</v>
+        <v>0.3320321697218283</v>
       </c>
       <c r="D521" t="s">
         <v>7</v>
@@ -13200,7 +13200,7 @@
         <v>15</v>
       </c>
       <c r="C522">
-        <v>0.3524487252497951</v>
+        <v>0.3429715529495362</v>
       </c>
       <c r="D522" t="s">
         <v>7</v>
@@ -13217,7 +13217,7 @@
         <v>6</v>
       </c>
       <c r="C523">
-        <v>0.465531796365688</v>
+        <v>0.4651644906802223</v>
       </c>
       <c r="D523" t="s">
         <v>7</v>
@@ -13234,7 +13234,7 @@
         <v>6</v>
       </c>
       <c r="C524">
-        <v>0.3195929657248891</v>
+        <v>0.3208111038048009</v>
       </c>
       <c r="D524" t="s">
         <v>7</v>
@@ -13251,7 +13251,7 @@
         <v>44</v>
       </c>
       <c r="C525">
-        <v>0.3786037708033582</v>
+        <v>0.3722295737069574</v>
       </c>
       <c r="D525" t="s">
         <v>7</v>
@@ -13268,7 +13268,7 @@
         <v>44</v>
       </c>
       <c r="C526">
-        <v>0.4851178902837471</v>
+        <v>0.4712523466236962</v>
       </c>
       <c r="D526" t="s">
         <v>7</v>
@@ -13285,7 +13285,7 @@
         <v>10</v>
       </c>
       <c r="C527">
-        <v>0.3704970276092567</v>
+        <v>0.4086306089652295</v>
       </c>
       <c r="D527" t="s">
         <v>7</v>
@@ -13302,7 +13302,7 @@
         <v>6</v>
       </c>
       <c r="C528">
-        <v>0.4773208460689147</v>
+        <v>0.472278420676218</v>
       </c>
       <c r="D528" t="s">
         <v>7</v>
@@ -13319,7 +13319,7 @@
         <v>10</v>
       </c>
       <c r="C529">
-        <v>0.3073714743039998</v>
+        <v>0.3458407721560603</v>
       </c>
       <c r="D529" t="s">
         <v>7</v>
@@ -13336,7 +13336,7 @@
         <v>44</v>
       </c>
       <c r="C530">
-        <v>0.4948554555083374</v>
+        <v>0.4799773938557699</v>
       </c>
       <c r="D530" t="s">
         <v>7</v>
@@ -13353,7 +13353,7 @@
         <v>44</v>
       </c>
       <c r="C531">
-        <v>0.5276301795658149</v>
+        <v>0.5139589162107649</v>
       </c>
       <c r="D531" t="s">
         <v>7</v>
@@ -13370,7 +13370,7 @@
         <v>10</v>
       </c>
       <c r="C532">
-        <v>0.2669254770600861</v>
+        <v>0.305035815939796</v>
       </c>
       <c r="D532" t="s">
         <v>7</v>
@@ -13387,7 +13387,7 @@
         <v>15</v>
       </c>
       <c r="C533">
-        <v>0.4851203837319838</v>
+        <v>0.4753802421229933</v>
       </c>
       <c r="D533" t="s">
         <v>7</v>
@@ -13404,7 +13404,7 @@
         <v>15</v>
       </c>
       <c r="C534">
-        <v>0.3349284041750403</v>
+        <v>0.3264240424804007</v>
       </c>
       <c r="D534" t="s">
         <v>7</v>
@@ -13421,7 +13421,7 @@
         <v>6</v>
       </c>
       <c r="C535">
-        <v>0.3362937749854033</v>
+        <v>0.3332024751475036</v>
       </c>
       <c r="D535" t="s">
         <v>7</v>
@@ -13438,7 +13438,7 @@
         <v>6</v>
       </c>
       <c r="C536">
-        <v>0.3391245663853532</v>
+        <v>0.3371406151627299</v>
       </c>
       <c r="D536" t="s">
         <v>7</v>
@@ -13455,7 +13455,7 @@
         <v>6</v>
       </c>
       <c r="C537">
-        <v>0.4105024521454541</v>
+        <v>0.4129376805909074</v>
       </c>
       <c r="D537" t="s">
         <v>7</v>
@@ -13469,10 +13469,10 @@
         <v>1084</v>
       </c>
       <c r="B538" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C538">
-        <v>0.2957197802619093</v>
+        <v>0.3096067823700727</v>
       </c>
       <c r="D538" t="s">
         <v>7</v>
@@ -13489,7 +13489,7 @@
         <v>6</v>
       </c>
       <c r="C539">
-        <v>0.3223440885510908</v>
+        <v>0.3206437613165823</v>
       </c>
       <c r="D539" t="s">
         <v>7</v>
@@ -13506,7 +13506,7 @@
         <v>15</v>
       </c>
       <c r="C540">
-        <v>0.2723726852424826</v>
+        <v>0.2679168631093865</v>
       </c>
       <c r="D540" t="s">
         <v>7</v>
@@ -13523,7 +13523,7 @@
         <v>6</v>
       </c>
       <c r="C541">
-        <v>0.4359240499389753</v>
+        <v>0.4344723254993317</v>
       </c>
       <c r="D541" t="s">
         <v>7</v>
@@ -13540,7 +13540,7 @@
         <v>44</v>
       </c>
       <c r="C542">
-        <v>0.3619748762818268</v>
+        <v>0.3441796689481475</v>
       </c>
       <c r="D542" t="s">
         <v>7</v>
@@ -13557,7 +13557,7 @@
         <v>6</v>
       </c>
       <c r="C543">
-        <v>0.443636510935222</v>
+        <v>0.447868930043232</v>
       </c>
       <c r="D543" t="s">
         <v>7</v>
@@ -13574,7 +13574,7 @@
         <v>6</v>
       </c>
       <c r="C544">
-        <v>0.4289519883795928</v>
+        <v>0.4268591318880953</v>
       </c>
       <c r="D544" t="s">
         <v>7</v>
@@ -13843,7 +13843,7 @@
         <v>1143</v>
       </c>
       <c r="C563">
-        <v>0.2805793477961462</v>
+        <v>0.2862317446366963</v>
       </c>
       <c r="D563" t="s">
         <v>1144</v>
@@ -13860,7 +13860,7 @@
         <v>1143</v>
       </c>
       <c r="C564">
-        <v>0.3226886015185672</v>
+        <v>0.3337067163596408</v>
       </c>
       <c r="D564" t="s">
         <v>1144</v>
@@ -13877,7 +13877,7 @@
         <v>1143</v>
       </c>
       <c r="C565">
-        <v>0.2735351765318364</v>
+        <v>0.2825384949951386</v>
       </c>
       <c r="D565" t="s">
         <v>1144</v>
@@ -13894,7 +13894,7 @@
         <v>1143</v>
       </c>
       <c r="C566">
-        <v>0.3414690873982061</v>
+        <v>0.3510873779285111</v>
       </c>
       <c r="D566" t="s">
         <v>1144</v>
@@ -13911,7 +13911,7 @@
         <v>1143</v>
       </c>
       <c r="C567">
-        <v>0.3956732205486582</v>
+        <v>0.4040472561001601</v>
       </c>
       <c r="D567" t="s">
         <v>1144</v>
@@ -13928,7 +13928,7 @@
         <v>1143</v>
       </c>
       <c r="C568">
-        <v>0.4057781108554573</v>
+        <v>0.4165961616066138</v>
       </c>
       <c r="D568" t="s">
         <v>1144</v>
@@ -13945,7 +13945,7 @@
         <v>1143</v>
       </c>
       <c r="C569">
-        <v>0.2699343584469736</v>
+        <v>0.2785684082060632</v>
       </c>
       <c r="D569" t="s">
         <v>1144</v>
@@ -13962,7 +13962,7 @@
         <v>1143</v>
       </c>
       <c r="C570">
-        <v>0.2927710349495408</v>
+        <v>0.3013860590590233</v>
       </c>
       <c r="D570" t="s">
         <v>1144</v>
@@ -13979,7 +13979,7 @@
         <v>1143</v>
       </c>
       <c r="C571">
-        <v>0.290648248460051</v>
+        <v>0.2996656613596876</v>
       </c>
       <c r="D571" t="s">
         <v>1144</v>
@@ -13996,7 +13996,7 @@
         <v>6</v>
       </c>
       <c r="C572">
-        <v>0.3022814677171713</v>
+        <v>0.3122827456887742</v>
       </c>
       <c r="D572" t="s">
         <v>1144</v>
@@ -14013,7 +14013,7 @@
         <v>1143</v>
       </c>
       <c r="C573">
-        <v>0.3372318552626489</v>
+        <v>0.3455994121167242</v>
       </c>
       <c r="D573" t="s">
         <v>1144</v>
@@ -14030,7 +14030,7 @@
         <v>44</v>
       </c>
       <c r="C574">
-        <v>0.3775549555757317</v>
+        <v>0.3788223979302355</v>
       </c>
       <c r="D574" t="s">
         <v>1144</v>
@@ -14047,7 +14047,7 @@
         <v>1143</v>
       </c>
       <c r="C575">
-        <v>0.3574920420765598</v>
+        <v>0.3688254934066839</v>
       </c>
       <c r="D575" t="s">
         <v>1144</v>
@@ -14064,7 +14064,7 @@
         <v>1143</v>
       </c>
       <c r="C576">
-        <v>0.3568132423250981</v>
+        <v>0.3659596468940942</v>
       </c>
       <c r="D576" t="s">
         <v>1144</v>
@@ -14081,7 +14081,7 @@
         <v>6</v>
       </c>
       <c r="C577">
-        <v>0.3615887940632187</v>
+        <v>0.3687562879055225</v>
       </c>
       <c r="D577" t="s">
         <v>1144</v>
@@ -14098,7 +14098,7 @@
         <v>1143</v>
       </c>
       <c r="C578">
-        <v>0.4079216583092571</v>
+        <v>0.4164216485283366</v>
       </c>
       <c r="D578" t="s">
         <v>1144</v>
@@ -14115,7 +14115,7 @@
         <v>1143</v>
       </c>
       <c r="C579">
-        <v>0.3592432676170801</v>
+        <v>0.3685337760048909</v>
       </c>
       <c r="D579" t="s">
         <v>1144</v>
@@ -14132,7 +14132,7 @@
         <v>1143</v>
       </c>
       <c r="C580">
-        <v>0.2855633197430203</v>
+        <v>0.2970881451683461</v>
       </c>
       <c r="D580" t="s">
         <v>1144</v>
@@ -14149,7 +14149,7 @@
         <v>1143</v>
       </c>
       <c r="C581">
-        <v>0.4590984710226226</v>
+        <v>0.4773013925199448</v>
       </c>
       <c r="D581" t="s">
         <v>1144</v>
@@ -14166,7 +14166,7 @@
         <v>1143</v>
       </c>
       <c r="C582">
-        <v>0.3073904002761048</v>
+        <v>0.3169579935121163</v>
       </c>
       <c r="D582" t="s">
         <v>1144</v>
@@ -14183,7 +14183,7 @@
         <v>1143</v>
       </c>
       <c r="C583">
-        <v>0.3857194928848706</v>
+        <v>0.3943543354667077</v>
       </c>
       <c r="D583" t="s">
         <v>1144</v>
@@ -14200,7 +14200,7 @@
         <v>1143</v>
       </c>
       <c r="C584">
-        <v>0.3072132309375001</v>
+        <v>0.3157911247862568</v>
       </c>
       <c r="D584" t="s">
         <v>1144</v>
@@ -14217,7 +14217,7 @@
         <v>1143</v>
       </c>
       <c r="C585">
-        <v>0.4129209703516483</v>
+        <v>0.4194886836909704</v>
       </c>
       <c r="D585" t="s">
         <v>1144</v>
@@ -14234,7 +14234,7 @@
         <v>1143</v>
       </c>
       <c r="C586">
-        <v>0.2922727161975859</v>
+        <v>0.2963659151006527</v>
       </c>
       <c r="D586" t="s">
         <v>1144</v>
@@ -14251,7 +14251,7 @@
         <v>6</v>
       </c>
       <c r="C587">
-        <v>0.3185620061034763</v>
+        <v>0.3296200532147451</v>
       </c>
       <c r="D587" t="s">
         <v>1144</v>
@@ -14268,7 +14268,7 @@
         <v>1143</v>
       </c>
       <c r="C588">
-        <v>0.3202880134151589</v>
+        <v>0.3255834791765406</v>
       </c>
       <c r="D588" t="s">
         <v>1144</v>
@@ -14285,7 +14285,7 @@
         <v>44</v>
       </c>
       <c r="C589">
-        <v>0.3954747404431621</v>
+        <v>0.3957538835677468</v>
       </c>
       <c r="D589" t="s">
         <v>1144</v>
@@ -14302,7 +14302,7 @@
         <v>6</v>
       </c>
       <c r="C590">
-        <v>0.4218210913926099</v>
+        <v>0.4265527841873999</v>
       </c>
       <c r="D590" t="s">
         <v>1144</v>
@@ -14319,7 +14319,7 @@
         <v>1143</v>
       </c>
       <c r="C591">
-        <v>0.5055260582908665</v>
+        <v>0.5229723864606979</v>
       </c>
       <c r="D591" t="s">
         <v>1144</v>
@@ -14336,7 +14336,7 @@
         <v>1143</v>
       </c>
       <c r="C592">
-        <v>0.365673310209782</v>
+        <v>0.366771425958945</v>
       </c>
       <c r="D592" t="s">
         <v>1144</v>
@@ -14353,7 +14353,7 @@
         <v>1143</v>
       </c>
       <c r="C593">
-        <v>0.6401762238910994</v>
+        <v>0.6601505655620831</v>
       </c>
       <c r="D593" t="s">
         <v>1144</v>
@@ -14370,7 +14370,7 @@
         <v>1143</v>
       </c>
       <c r="C594">
-        <v>0.4436973462294086</v>
+        <v>0.4545724518708138</v>
       </c>
       <c r="D594" t="s">
         <v>1144</v>
@@ -14387,7 +14387,7 @@
         <v>6</v>
       </c>
       <c r="C595">
-        <v>0.3269430634555045</v>
+        <v>0.3366118753612362</v>
       </c>
       <c r="D595" t="s">
         <v>1144</v>
@@ -14404,7 +14404,7 @@
         <v>1143</v>
       </c>
       <c r="C596">
-        <v>0.4327550014237833</v>
+        <v>0.4403687728395118</v>
       </c>
       <c r="D596" t="s">
         <v>1144</v>
@@ -14421,7 +14421,7 @@
         <v>6</v>
       </c>
       <c r="C597">
-        <v>0.3308150620577314</v>
+        <v>0.3387744418165347</v>
       </c>
       <c r="D597" t="s">
         <v>1144</v>
@@ -14438,7 +14438,7 @@
         <v>10</v>
       </c>
       <c r="C598">
-        <v>0.2367616074960175</v>
+        <v>0.2349640096444199</v>
       </c>
       <c r="D598" t="s">
         <v>1144</v>
@@ -14455,7 +14455,7 @@
         <v>1143</v>
       </c>
       <c r="C599">
-        <v>0.2526013000338156</v>
+        <v>0.2607819228599443</v>
       </c>
       <c r="D599" t="s">
         <v>1144</v>
@@ -14472,7 +14472,7 @@
         <v>1143</v>
       </c>
       <c r="C600">
-        <v>0.2776339863292266</v>
+        <v>0.2865953420694184</v>
       </c>
       <c r="D600" t="s">
         <v>1144</v>
@@ -14489,7 +14489,7 @@
         <v>1143</v>
       </c>
       <c r="C601">
-        <v>0.2634075432664323</v>
+        <v>0.2712143050140573</v>
       </c>
       <c r="D601" t="s">
         <v>1144</v>
@@ -14506,7 +14506,7 @@
         <v>1143</v>
       </c>
       <c r="C602">
-        <v>0.3577424260993998</v>
+        <v>0.3688778853799183</v>
       </c>
       <c r="D602" t="s">
         <v>1144</v>
@@ -14523,7 +14523,7 @@
         <v>1143</v>
       </c>
       <c r="C603">
-        <v>0.2883954952829639</v>
+        <v>0.2983503750865437</v>
       </c>
       <c r="D603" t="s">
         <v>1144</v>
@@ -14540,7 +14540,7 @@
         <v>6</v>
       </c>
       <c r="C604">
-        <v>0.3367664588901789</v>
+        <v>0.3468269121622588</v>
       </c>
       <c r="D604" t="s">
         <v>1144</v>
@@ -14557,7 +14557,7 @@
         <v>44</v>
       </c>
       <c r="C605">
-        <v>0.2841136840544377</v>
+        <v>0.2801934392474142</v>
       </c>
       <c r="D605" t="s">
         <v>1144</v>
@@ -14574,7 +14574,7 @@
         <v>6</v>
       </c>
       <c r="C606">
-        <v>0.334797708980002</v>
+        <v>0.3437621307486726</v>
       </c>
       <c r="D606" t="s">
         <v>1144</v>
@@ -14588,10 +14588,10 @@
         <v>1232</v>
       </c>
       <c r="B607" t="s">
-        <v>10</v>
+        <v>1143</v>
       </c>
       <c r="C607">
-        <v>0.3062364447840163</v>
+        <v>0.3160997265742783</v>
       </c>
       <c r="D607" t="s">
         <v>1144</v>
@@ -14608,7 +14608,7 @@
         <v>6</v>
       </c>
       <c r="C608">
-        <v>0.316493316642598</v>
+        <v>0.3238609991579033</v>
       </c>
       <c r="D608" t="s">
         <v>1144</v>
@@ -14625,7 +14625,7 @@
         <v>6</v>
       </c>
       <c r="C609">
-        <v>0.3312592535947746</v>
+        <v>0.3393061217939168</v>
       </c>
       <c r="D609" t="s">
         <v>1144</v>
@@ -14642,7 +14642,7 @@
         <v>1143</v>
       </c>
       <c r="C610">
-        <v>0.2641594966463437</v>
+        <v>0.2726779104213399</v>
       </c>
       <c r="D610" t="s">
         <v>1144</v>
@@ -14659,7 +14659,7 @@
         <v>44</v>
       </c>
       <c r="C611">
-        <v>0.5372130385996471</v>
+        <v>0.5389515318890323</v>
       </c>
       <c r="D611" t="s">
         <v>1144</v>
@@ -14676,7 +14676,7 @@
         <v>44</v>
       </c>
       <c r="C612">
-        <v>0.3809873455544808</v>
+        <v>0.3808023248916002</v>
       </c>
       <c r="D612" t="s">
         <v>1144</v>
@@ -14693,7 +14693,7 @@
         <v>1143</v>
       </c>
       <c r="C613">
-        <v>0.3320218097910265</v>
+        <v>0.3416115837284558</v>
       </c>
       <c r="D613" t="s">
         <v>1144</v>
@@ -14710,7 +14710,7 @@
         <v>1143</v>
       </c>
       <c r="C614">
-        <v>0.4355269863930907</v>
+        <v>0.445489694361066</v>
       </c>
       <c r="D614" t="s">
         <v>1144</v>
@@ -14727,7 +14727,7 @@
         <v>1143</v>
       </c>
       <c r="C615">
-        <v>0.337248592140817</v>
+        <v>0.3489856578919413</v>
       </c>
       <c r="D615" t="s">
         <v>1144</v>
@@ -14744,7 +14744,7 @@
         <v>1143</v>
       </c>
       <c r="C616">
-        <v>0.4215982454230516</v>
+        <v>0.4310659653265893</v>
       </c>
       <c r="D616" t="s">
         <v>1144</v>
@@ -14761,7 +14761,7 @@
         <v>1143</v>
       </c>
       <c r="C617">
-        <v>0.3488178018243955</v>
+        <v>0.3568415496179281</v>
       </c>
       <c r="D617" t="s">
         <v>1144</v>
@@ -14778,7 +14778,7 @@
         <v>10</v>
       </c>
       <c r="C618">
-        <v>0.33842893991552</v>
+        <v>0.3392729803083088</v>
       </c>
       <c r="D618" t="s">
         <v>1144</v>
@@ -14795,7 +14795,7 @@
         <v>1143</v>
       </c>
       <c r="C619">
-        <v>0.4396673522786895</v>
+        <v>0.4459808886902796</v>
       </c>
       <c r="D619" t="s">
         <v>1144</v>
@@ -14812,7 +14812,7 @@
         <v>6</v>
       </c>
       <c r="C620">
-        <v>0.3319525456876453</v>
+        <v>0.3278662904908047</v>
       </c>
       <c r="D620" t="s">
         <v>1259</v>
@@ -14829,7 +14829,7 @@
         <v>15</v>
       </c>
       <c r="C621">
-        <v>0.3504011928859856</v>
+        <v>0.3551411668606793</v>
       </c>
       <c r="D621" t="s">
         <v>1259</v>
@@ -14846,7 +14846,7 @@
         <v>6</v>
       </c>
       <c r="C622">
-        <v>0.2805348231654675</v>
+        <v>0.2765710284333049</v>
       </c>
       <c r="D622" t="s">
         <v>1259</v>
@@ -14863,7 +14863,7 @@
         <v>1266</v>
       </c>
       <c r="C623">
-        <v>0.2144867233283977</v>
+        <v>0.2191117244497651</v>
       </c>
       <c r="D623" t="s">
         <v>1259</v>
@@ -14880,7 +14880,7 @@
         <v>10</v>
       </c>
       <c r="C624">
-        <v>0.3068739601967791</v>
+        <v>0.3013174439129063</v>
       </c>
       <c r="D624" t="s">
         <v>1259</v>
@@ -14897,7 +14897,7 @@
         <v>10</v>
       </c>
       <c r="C625">
-        <v>0.2541124991815008</v>
+        <v>0.2484816907768088</v>
       </c>
       <c r="D625" t="s">
         <v>1259</v>
@@ -14914,7 +14914,7 @@
         <v>15</v>
       </c>
       <c r="C626">
-        <v>0.355596308414829</v>
+        <v>0.3608546553895554</v>
       </c>
       <c r="D626" t="s">
         <v>1259</v>
@@ -14931,7 +14931,7 @@
         <v>1266</v>
       </c>
       <c r="C627">
-        <v>0.2815415376198599</v>
+        <v>0.2859833994655254</v>
       </c>
       <c r="D627" t="s">
         <v>1259</v>
@@ -14948,7 +14948,7 @@
         <v>6</v>
       </c>
       <c r="C628">
-        <v>0.237864130896577</v>
+        <v>0.233098801377836</v>
       </c>
       <c r="D628" t="s">
         <v>1259</v>
@@ -14965,7 +14965,7 @@
         <v>6</v>
       </c>
       <c r="C629">
-        <v>0.2761093716323665</v>
+        <v>0.272837428093292</v>
       </c>
       <c r="D629" t="s">
         <v>1259</v>
@@ -14982,7 +14982,7 @@
         <v>1266</v>
       </c>
       <c r="C630">
-        <v>0.3045400551210535</v>
+        <v>0.3090337644068571</v>
       </c>
       <c r="D630" t="s">
         <v>1259</v>
@@ -14999,7 +14999,7 @@
         <v>1266</v>
       </c>
       <c r="C631">
-        <v>0.3023629207555387</v>
+        <v>0.3066884388449687</v>
       </c>
       <c r="D631" t="s">
         <v>1259</v>
@@ -15016,7 +15016,7 @@
         <v>1266</v>
       </c>
       <c r="C632">
-        <v>0.3924141789197788</v>
+        <v>0.396501369761091</v>
       </c>
       <c r="D632" t="s">
         <v>1259</v>
@@ -15033,7 +15033,7 @@
         <v>15</v>
       </c>
       <c r="C633">
-        <v>0.266199210429178</v>
+        <v>0.2705910581210036</v>
       </c>
       <c r="D633" t="s">
         <v>1259</v>
@@ -15050,7 +15050,7 @@
         <v>15</v>
       </c>
       <c r="C634">
-        <v>0.4193210875139612</v>
+        <v>0.4259419518583432</v>
       </c>
       <c r="D634" t="s">
         <v>1259</v>
@@ -15067,7 +15067,7 @@
         <v>1266</v>
       </c>
       <c r="C635">
-        <v>0.4572059829506785</v>
+        <v>0.4595439929718509</v>
       </c>
       <c r="D635" t="s">
         <v>1259</v>
@@ -15084,7 +15084,7 @@
         <v>6</v>
       </c>
       <c r="C636">
-        <v>0.3777014908825693</v>
+        <v>0.3746083195459203</v>
       </c>
       <c r="D636" t="s">
         <v>1259</v>
@@ -15101,7 +15101,7 @@
         <v>15</v>
       </c>
       <c r="C637">
-        <v>0.2959923307669016</v>
+        <v>0.3004285639190377</v>
       </c>
       <c r="D637" t="s">
         <v>1259</v>
@@ -15118,7 +15118,7 @@
         <v>1266</v>
       </c>
       <c r="C638">
-        <v>0.4226175453429617</v>
+        <v>0.4254250865066503</v>
       </c>
       <c r="D638" t="s">
         <v>1259</v>
@@ -15135,7 +15135,7 @@
         <v>10</v>
       </c>
       <c r="C639">
-        <v>0.3489875328904459</v>
+        <v>0.3433262666407025</v>
       </c>
       <c r="D639" t="s">
         <v>1259</v>
@@ -15152,7 +15152,7 @@
         <v>10</v>
       </c>
       <c r="C640">
-        <v>0.3169804919734888</v>
+        <v>0.3121835458922222</v>
       </c>
       <c r="D640" t="s">
         <v>1259</v>
@@ -15169,7 +15169,7 @@
         <v>15</v>
       </c>
       <c r="C641">
-        <v>0.271411162011699</v>
+        <v>0.2761513430518701</v>
       </c>
       <c r="D641" t="s">
         <v>1259</v>
@@ -15186,7 +15186,7 @@
         <v>1266</v>
       </c>
       <c r="C642">
-        <v>0.2806589337190684</v>
+        <v>0.2851580840514525</v>
       </c>
       <c r="D642" t="s">
         <v>1259</v>
@@ -15203,7 +15203,7 @@
         <v>15</v>
       </c>
       <c r="C643">
-        <v>0.3389726408126501</v>
+        <v>0.3442305383897116</v>
       </c>
       <c r="D643" t="s">
         <v>1259</v>
@@ -15220,7 +15220,7 @@
         <v>15</v>
       </c>
       <c r="C644">
-        <v>0.287455373196221</v>
+        <v>0.291935388459783</v>
       </c>
       <c r="D644" t="s">
         <v>1259</v>
@@ -15237,7 +15237,7 @@
         <v>15</v>
       </c>
       <c r="C645">
-        <v>0.2462174825244853</v>
+        <v>0.250413529510035</v>
       </c>
       <c r="D645" t="s">
         <v>1259</v>
@@ -15254,7 +15254,7 @@
         <v>15</v>
       </c>
       <c r="C646">
-        <v>0.364796663607433</v>
+        <v>0.3695681570748545</v>
       </c>
       <c r="D646" t="s">
         <v>1259</v>
@@ -15271,7 +15271,7 @@
         <v>6</v>
       </c>
       <c r="C647">
-        <v>0.3036479444602142</v>
+        <v>0.2993135631546125</v>
       </c>
       <c r="D647" t="s">
         <v>1259</v>
@@ -15288,7 +15288,7 @@
         <v>15</v>
       </c>
       <c r="C648">
-        <v>0.3054060374661127</v>
+        <v>0.3098350305973636</v>
       </c>
       <c r="D648" t="s">
         <v>1259</v>
@@ -15305,7 +15305,7 @@
         <v>15</v>
       </c>
       <c r="C649">
-        <v>0.3510506841049136</v>
+        <v>0.3560970724312739</v>
       </c>
       <c r="D649" t="s">
         <v>1259</v>
@@ -15322,7 +15322,7 @@
         <v>6</v>
       </c>
       <c r="C650">
-        <v>0.2877237139124142</v>
+        <v>0.2845150054340436</v>
       </c>
       <c r="D650" t="s">
         <v>1259</v>
@@ -15339,7 +15339,7 @@
         <v>15</v>
       </c>
       <c r="C651">
-        <v>0.3293679373909073</v>
+        <v>0.3341295391172087</v>
       </c>
       <c r="D651" t="s">
         <v>1259</v>
@@ -15371,7 +15371,7 @@
         <v>15</v>
       </c>
       <c r="B2">
-        <v>148</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -15379,7 +15379,7 @@
         <v>10</v>
       </c>
       <c r="B3">
-        <v>85</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -15387,7 +15387,7 @@
         <v>145</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -15395,7 +15395,7 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>275</v>
+        <v>265</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -15403,7 +15403,7 @@
         <v>44</v>
       </c>
       <c r="B6">
-        <v>67</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -15427,7 +15427,7 @@
         <v>1143</v>
       </c>
       <c r="B9">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:2">

--- a/frontend/data/uk_election_predictions.xlsx
+++ b/frontend/data/uk_election_predictions.xlsx
@@ -4360,7 +4360,7 @@
         <v>6</v>
       </c>
       <c r="C2">
-        <v>0.3158298632012356</v>
+        <v>0.3158750916302961</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
@@ -4377,7 +4377,7 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>0.4170444037015363</v>
+        <v>0.4172305728821916</v>
       </c>
       <c r="D3" t="s">
         <v>7</v>
@@ -4394,7 +4394,7 @@
         <v>6</v>
       </c>
       <c r="C4">
-        <v>0.4095832248088022</v>
+        <v>0.4096214589672389</v>
       </c>
       <c r="D4" t="s">
         <v>7</v>
@@ -4411,7 +4411,7 @@
         <v>15</v>
       </c>
       <c r="C5">
-        <v>0.3762127555490866</v>
+        <v>0.3760124726817399</v>
       </c>
       <c r="D5" t="s">
         <v>7</v>
@@ -4428,7 +4428,7 @@
         <v>10</v>
       </c>
       <c r="C6">
-        <v>0.4035352261672355</v>
+        <v>0.4037273028773024</v>
       </c>
       <c r="D6" t="s">
         <v>7</v>
@@ -4445,7 +4445,7 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>0.3271217282075017</v>
+        <v>0.3271418648375878</v>
       </c>
       <c r="D7" t="s">
         <v>7</v>
@@ -4462,7 +4462,7 @@
         <v>15</v>
       </c>
       <c r="C8">
-        <v>0.3419455909874243</v>
+        <v>0.3417685480192545</v>
       </c>
       <c r="D8" t="s">
         <v>7</v>
@@ -4479,7 +4479,7 @@
         <v>15</v>
       </c>
       <c r="C9">
-        <v>0.3176690922632786</v>
+        <v>0.3175000533364746</v>
       </c>
       <c r="D9" t="s">
         <v>7</v>
@@ -4496,7 +4496,7 @@
         <v>10</v>
       </c>
       <c r="C10">
-        <v>0.3459006041814624</v>
+        <v>0.3461120230833049</v>
       </c>
       <c r="D10" t="s">
         <v>7</v>
@@ -4513,7 +4513,7 @@
         <v>15</v>
       </c>
       <c r="C11">
-        <v>0.2334339256556266</v>
+        <v>0.233279448656726</v>
       </c>
       <c r="D11" t="s">
         <v>7</v>
@@ -4530,7 +4530,7 @@
         <v>6</v>
       </c>
       <c r="C12">
-        <v>0.4060904401002813</v>
+        <v>0.4061250229630603</v>
       </c>
       <c r="D12" t="s">
         <v>7</v>
@@ -4547,7 +4547,7 @@
         <v>15</v>
       </c>
       <c r="C13">
-        <v>0.3009096488649104</v>
+        <v>0.3007560270011409</v>
       </c>
       <c r="D13" t="s">
         <v>7</v>
@@ -4564,7 +4564,7 @@
         <v>15</v>
       </c>
       <c r="C14">
-        <v>0.3857374691884548</v>
+        <v>0.3855744851104193</v>
       </c>
       <c r="D14" t="s">
         <v>7</v>
@@ -4581,7 +4581,7 @@
         <v>10</v>
       </c>
       <c r="C15">
-        <v>0.3747215671985894</v>
+        <v>0.374920882928685</v>
       </c>
       <c r="D15" t="s">
         <v>7</v>
@@ -4598,7 +4598,7 @@
         <v>6</v>
       </c>
       <c r="C16">
-        <v>0.3517519406423954</v>
+        <v>0.3518053090422998</v>
       </c>
       <c r="D16" t="s">
         <v>7</v>
@@ -4612,10 +4612,10 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C17">
-        <v>0.2792829728117687</v>
+        <v>0.2791611310323777</v>
       </c>
       <c r="D17" t="s">
         <v>7</v>
@@ -4632,7 +4632,7 @@
         <v>10</v>
       </c>
       <c r="C18">
-        <v>0.3351635031070885</v>
+        <v>0.3353778213810027</v>
       </c>
       <c r="D18" t="s">
         <v>7</v>
@@ -4649,7 +4649,7 @@
         <v>44</v>
       </c>
       <c r="C19">
-        <v>0.4140024019375394</v>
+        <v>0.4139011130377653</v>
       </c>
       <c r="D19" t="s">
         <v>7</v>
@@ -4666,7 +4666,7 @@
         <v>6</v>
       </c>
       <c r="C20">
-        <v>0.4678675852627772</v>
+        <v>0.4678988639311091</v>
       </c>
       <c r="D20" t="s">
         <v>7</v>
@@ -4683,7 +4683,7 @@
         <v>10</v>
       </c>
       <c r="C21">
-        <v>0.4136646496930757</v>
+        <v>0.4138625308740333</v>
       </c>
       <c r="D21" t="s">
         <v>7</v>
@@ -4700,7 +4700,7 @@
         <v>6</v>
       </c>
       <c r="C22">
-        <v>0.3761993168499339</v>
+        <v>0.3762447171888225</v>
       </c>
       <c r="D22" t="s">
         <v>7</v>
@@ -4717,7 +4717,7 @@
         <v>6</v>
       </c>
       <c r="C23">
-        <v>0.4741726427018033</v>
+        <v>0.4742242835766043</v>
       </c>
       <c r="D23" t="s">
         <v>7</v>
@@ -4734,7 +4734,7 @@
         <v>6</v>
       </c>
       <c r="C24">
-        <v>0.3691401242389403</v>
+        <v>0.3692103763023497</v>
       </c>
       <c r="D24" t="s">
         <v>7</v>
@@ -4751,7 +4751,7 @@
         <v>6</v>
       </c>
       <c r="C25">
-        <v>0.6332002844517933</v>
+        <v>0.6332506697290622</v>
       </c>
       <c r="D25" t="s">
         <v>7</v>
@@ -4768,7 +4768,7 @@
         <v>6</v>
       </c>
       <c r="C26">
-        <v>0.2977253740788202</v>
+        <v>0.2977725367376293</v>
       </c>
       <c r="D26" t="s">
         <v>7</v>
@@ -4785,7 +4785,7 @@
         <v>10</v>
       </c>
       <c r="C27">
-        <v>0.3022335968007251</v>
+        <v>0.3024411061339548</v>
       </c>
       <c r="D27" t="s">
         <v>7</v>
@@ -4802,7 +4802,7 @@
         <v>6</v>
       </c>
       <c r="C28">
-        <v>0.334852236713102</v>
+        <v>0.3348949193172715</v>
       </c>
       <c r="D28" t="s">
         <v>7</v>
@@ -4819,7 +4819,7 @@
         <v>44</v>
       </c>
       <c r="C29">
-        <v>0.4143323663316881</v>
+        <v>0.4142447497096594</v>
       </c>
       <c r="D29" t="s">
         <v>7</v>
@@ -4836,7 +4836,7 @@
         <v>6</v>
       </c>
       <c r="C30">
-        <v>0.3941533406287126</v>
+        <v>0.3942084105840059</v>
       </c>
       <c r="D30" t="s">
         <v>7</v>
@@ -4853,7 +4853,7 @@
         <v>6</v>
       </c>
       <c r="C31">
-        <v>0.4619460120617174</v>
+        <v>0.4619513562142523</v>
       </c>
       <c r="D31" t="s">
         <v>7</v>
@@ -4870,7 +4870,7 @@
         <v>15</v>
       </c>
       <c r="C32">
-        <v>0.4052856278201252</v>
+        <v>0.4050945252813247</v>
       </c>
       <c r="D32" t="s">
         <v>7</v>
@@ -4887,7 +4887,7 @@
         <v>6</v>
       </c>
       <c r="C33">
-        <v>0.4184937967995296</v>
+        <v>0.4185379567160899</v>
       </c>
       <c r="D33" t="s">
         <v>7</v>
@@ -4904,7 +4904,7 @@
         <v>15</v>
       </c>
       <c r="C34">
-        <v>0.3261048432931341</v>
+        <v>0.3259183034563687</v>
       </c>
       <c r="D34" t="s">
         <v>7</v>
@@ -4921,7 +4921,7 @@
         <v>6</v>
       </c>
       <c r="C35">
-        <v>0.4699763975383232</v>
+        <v>0.4700222128382005</v>
       </c>
       <c r="D35" t="s">
         <v>7</v>
@@ -4938,7 +4938,7 @@
         <v>6</v>
       </c>
       <c r="C36">
-        <v>0.2642206557529245</v>
+        <v>0.2642634868812762</v>
       </c>
       <c r="D36" t="s">
         <v>7</v>
@@ -4955,7 +4955,7 @@
         <v>15</v>
       </c>
       <c r="C37">
-        <v>0.3157113503486791</v>
+        <v>0.3155042316096642</v>
       </c>
       <c r="D37" t="s">
         <v>7</v>
@@ -4972,7 +4972,7 @@
         <v>6</v>
       </c>
       <c r="C38">
-        <v>0.3580053093564951</v>
+        <v>0.3580454661950719</v>
       </c>
       <c r="D38" t="s">
         <v>7</v>
@@ -4989,7 +4989,7 @@
         <v>6</v>
       </c>
       <c r="C39">
-        <v>0.3271940004446663</v>
+        <v>0.3272420951602468</v>
       </c>
       <c r="D39" t="s">
         <v>7</v>
@@ -5006,7 +5006,7 @@
         <v>6</v>
       </c>
       <c r="C40">
-        <v>0.4990842907684948</v>
+        <v>0.4991188339283906</v>
       </c>
       <c r="D40" t="s">
         <v>7</v>
@@ -5023,7 +5023,7 @@
         <v>15</v>
       </c>
       <c r="C41">
-        <v>0.2878440474171817</v>
+        <v>0.2876595378969095</v>
       </c>
       <c r="D41" t="s">
         <v>7</v>
@@ -5040,7 +5040,7 @@
         <v>6</v>
       </c>
       <c r="C42">
-        <v>0.5342198938349695</v>
+        <v>0.5342465136704916</v>
       </c>
       <c r="D42" t="s">
         <v>7</v>
@@ -5057,7 +5057,7 @@
         <v>15</v>
       </c>
       <c r="C43">
-        <v>0.3972028728118709</v>
+        <v>0.3969918253337516</v>
       </c>
       <c r="D43" t="s">
         <v>7</v>
@@ -5074,7 +5074,7 @@
         <v>15</v>
       </c>
       <c r="C44">
-        <v>0.4302687431788437</v>
+        <v>0.4300611566194972</v>
       </c>
       <c r="D44" t="s">
         <v>7</v>
@@ -5091,7 +5091,7 @@
         <v>6</v>
       </c>
       <c r="C45">
-        <v>0.4272971128029849</v>
+        <v>0.4273555774760409</v>
       </c>
       <c r="D45" t="s">
         <v>7</v>
@@ -5108,7 +5108,7 @@
         <v>6</v>
       </c>
       <c r="C46">
-        <v>0.4112099297307124</v>
+        <v>0.4112255693737959</v>
       </c>
       <c r="D46" t="s">
         <v>7</v>
@@ -5125,7 +5125,7 @@
         <v>15</v>
       </c>
       <c r="C47">
-        <v>0.2979508968083778</v>
+        <v>0.2977801373040717</v>
       </c>
       <c r="D47" t="s">
         <v>7</v>
@@ -5142,7 +5142,7 @@
         <v>15</v>
       </c>
       <c r="C48">
-        <v>0.4101544563660858</v>
+        <v>0.4099501539883394</v>
       </c>
       <c r="D48" t="s">
         <v>7</v>
@@ -5159,7 +5159,7 @@
         <v>15</v>
       </c>
       <c r="C49">
-        <v>0.3272678135796174</v>
+        <v>0.3270973132291453</v>
       </c>
       <c r="D49" t="s">
         <v>7</v>
@@ -5176,7 +5176,7 @@
         <v>15</v>
       </c>
       <c r="C50">
-        <v>0.3649779141397826</v>
+        <v>0.3647721556125839</v>
       </c>
       <c r="D50" t="s">
         <v>7</v>
@@ -5193,7 +5193,7 @@
         <v>15</v>
       </c>
       <c r="C51">
-        <v>0.3538810794362612</v>
+        <v>0.3537074251982334</v>
       </c>
       <c r="D51" t="s">
         <v>7</v>
@@ -5210,7 +5210,7 @@
         <v>6</v>
       </c>
       <c r="C52">
-        <v>0.5219666848692265</v>
+        <v>0.521991681141481</v>
       </c>
       <c r="D52" t="s">
         <v>7</v>
@@ -5227,7 +5227,7 @@
         <v>15</v>
       </c>
       <c r="C53">
-        <v>0.4435455076278219</v>
+        <v>0.4433507006035885</v>
       </c>
       <c r="D53" t="s">
         <v>7</v>
@@ -5244,7 +5244,7 @@
         <v>6</v>
       </c>
       <c r="C54">
-        <v>0.4232129828036665</v>
+        <v>0.4232472581532497</v>
       </c>
       <c r="D54" t="s">
         <v>7</v>
@@ -5261,7 +5261,7 @@
         <v>10</v>
       </c>
       <c r="C55">
-        <v>0.3084071327643675</v>
+        <v>0.3086241034583719</v>
       </c>
       <c r="D55" t="s">
         <v>7</v>
@@ -5278,7 +5278,7 @@
         <v>10</v>
       </c>
       <c r="C56">
-        <v>0.3971496627461939</v>
+        <v>0.3973507805224538</v>
       </c>
       <c r="D56" t="s">
         <v>7</v>
@@ -5295,7 +5295,7 @@
         <v>6</v>
       </c>
       <c r="C57">
-        <v>0.5606328969826607</v>
+        <v>0.5606716598004159</v>
       </c>
       <c r="D57" t="s">
         <v>7</v>
@@ -5312,7 +5312,7 @@
         <v>6</v>
       </c>
       <c r="C58">
-        <v>0.3398605041805914</v>
+        <v>0.3398868426649885</v>
       </c>
       <c r="D58" t="s">
         <v>7</v>
@@ -5329,7 +5329,7 @@
         <v>6</v>
       </c>
       <c r="C59">
-        <v>0.3808000382673555</v>
+        <v>0.3808380726565327</v>
       </c>
       <c r="D59" t="s">
         <v>7</v>
@@ -5346,7 +5346,7 @@
         <v>6</v>
       </c>
       <c r="C60">
-        <v>0.331093726181319</v>
+        <v>0.331136092868879</v>
       </c>
       <c r="D60" t="s">
         <v>7</v>
@@ -5363,7 +5363,7 @@
         <v>6</v>
       </c>
       <c r="C61">
-        <v>0.3904541254044435</v>
+        <v>0.3904891446008104</v>
       </c>
       <c r="D61" t="s">
         <v>7</v>
@@ -5380,7 +5380,7 @@
         <v>10</v>
       </c>
       <c r="C62">
-        <v>0.38409173061561</v>
+        <v>0.3842725227120738</v>
       </c>
       <c r="D62" t="s">
         <v>7</v>
@@ -5397,7 +5397,7 @@
         <v>6</v>
       </c>
       <c r="C63">
-        <v>0.3916019857409938</v>
+        <v>0.3916341846579638</v>
       </c>
       <c r="D63" t="s">
         <v>7</v>
@@ -5414,7 +5414,7 @@
         <v>6</v>
       </c>
       <c r="C64">
-        <v>0.2171101312986917</v>
+        <v>0.2171592638181206</v>
       </c>
       <c r="D64" t="s">
         <v>7</v>
@@ -5431,7 +5431,7 @@
         <v>10</v>
       </c>
       <c r="C65">
-        <v>0.3343357453896617</v>
+        <v>0.3345539876119042</v>
       </c>
       <c r="D65" t="s">
         <v>7</v>
@@ -5448,7 +5448,7 @@
         <v>10</v>
       </c>
       <c r="C66">
-        <v>0.3305622871969564</v>
+        <v>0.3307796432821828</v>
       </c>
       <c r="D66" t="s">
         <v>7</v>
@@ -5465,7 +5465,7 @@
         <v>15</v>
       </c>
       <c r="C67">
-        <v>0.3412152827432141</v>
+        <v>0.3410348415667715</v>
       </c>
       <c r="D67" t="s">
         <v>7</v>
@@ -5482,7 +5482,7 @@
         <v>6</v>
       </c>
       <c r="C68">
-        <v>0.3361653849620436</v>
+        <v>0.3362067371877325</v>
       </c>
       <c r="D68" t="s">
         <v>7</v>
@@ -5499,7 +5499,7 @@
         <v>145</v>
       </c>
       <c r="C69">
-        <v>0.4920359085785033</v>
+        <v>0.4920376726018258</v>
       </c>
       <c r="D69" t="s">
         <v>7</v>
@@ -5516,7 +5516,7 @@
         <v>145</v>
       </c>
       <c r="C70">
-        <v>0.4470149162551847</v>
+        <v>0.4470188626389667</v>
       </c>
       <c r="D70" t="s">
         <v>7</v>
@@ -5533,7 +5533,7 @@
         <v>6</v>
       </c>
       <c r="C71">
-        <v>0.5045796357270991</v>
+        <v>0.5045810645406479</v>
       </c>
       <c r="D71" t="s">
         <v>7</v>
@@ -5550,7 +5550,7 @@
         <v>6</v>
       </c>
       <c r="C72">
-        <v>0.4045537161238438</v>
+        <v>0.4046181897353031</v>
       </c>
       <c r="D72" t="s">
         <v>7</v>
@@ -5567,7 +5567,7 @@
         <v>6</v>
       </c>
       <c r="C73">
-        <v>0.53502623039927</v>
+        <v>0.5350708887593716</v>
       </c>
       <c r="D73" t="s">
         <v>7</v>
@@ -5584,7 +5584,7 @@
         <v>6</v>
       </c>
       <c r="C74">
-        <v>0.5212676224270958</v>
+        <v>0.5213109747545196</v>
       </c>
       <c r="D74" t="s">
         <v>7</v>
@@ -5601,7 +5601,7 @@
         <v>10</v>
       </c>
       <c r="C75">
-        <v>0.3245871751855626</v>
+        <v>0.3248031881095777</v>
       </c>
       <c r="D75" t="s">
         <v>7</v>
@@ -5618,7 +5618,7 @@
         <v>10</v>
       </c>
       <c r="C76">
-        <v>0.3656065436594801</v>
+        <v>0.3658128553706181</v>
       </c>
       <c r="D76" t="s">
         <v>7</v>
@@ -5635,7 +5635,7 @@
         <v>10</v>
       </c>
       <c r="C77">
-        <v>0.3516877558864219</v>
+        <v>0.3519019969006175</v>
       </c>
       <c r="D77" t="s">
         <v>7</v>
@@ -5652,7 +5652,7 @@
         <v>10</v>
       </c>
       <c r="C78">
-        <v>0.4569795710170764</v>
+        <v>0.4571907153319389</v>
       </c>
       <c r="D78" t="s">
         <v>7</v>
@@ -5669,7 +5669,7 @@
         <v>10</v>
       </c>
       <c r="C79">
-        <v>0.2916008254186891</v>
+        <v>0.2918141555953317</v>
       </c>
       <c r="D79" t="s">
         <v>7</v>
@@ -5686,7 +5686,7 @@
         <v>10</v>
       </c>
       <c r="C80">
-        <v>0.389934579094351</v>
+        <v>0.3901321155632292</v>
       </c>
       <c r="D80" t="s">
         <v>7</v>
@@ -5703,7 +5703,7 @@
         <v>15</v>
       </c>
       <c r="C81">
-        <v>0.2963947130938034</v>
+        <v>0.2962319102336229</v>
       </c>
       <c r="D81" t="s">
         <v>7</v>
@@ -5720,7 +5720,7 @@
         <v>10</v>
       </c>
       <c r="C82">
-        <v>0.454365533690675</v>
+        <v>0.4545816897479437</v>
       </c>
       <c r="D82" t="s">
         <v>7</v>
@@ -5737,7 +5737,7 @@
         <v>6</v>
       </c>
       <c r="C83">
-        <v>0.4183828911842116</v>
+        <v>0.4183937060905052</v>
       </c>
       <c r="D83" t="s">
         <v>7</v>
@@ -5754,7 +5754,7 @@
         <v>10</v>
       </c>
       <c r="C84">
-        <v>0.3158659165682873</v>
+        <v>0.3160858588507656</v>
       </c>
       <c r="D84" t="s">
         <v>7</v>
@@ -5771,7 +5771,7 @@
         <v>15</v>
       </c>
       <c r="C85">
-        <v>0.2999045532539021</v>
+        <v>0.299731402472425</v>
       </c>
       <c r="D85" t="s">
         <v>7</v>
@@ -5788,7 +5788,7 @@
         <v>6</v>
       </c>
       <c r="C86">
-        <v>0.3410712452777739</v>
+        <v>0.3411243234781229</v>
       </c>
       <c r="D86" t="s">
         <v>7</v>
@@ -5805,7 +5805,7 @@
         <v>6</v>
       </c>
       <c r="C87">
-        <v>0.3108570030357116</v>
+        <v>0.3108977155187129</v>
       </c>
       <c r="D87" t="s">
         <v>7</v>
@@ -5822,7 +5822,7 @@
         <v>6</v>
       </c>
       <c r="C88">
-        <v>0.3008513567791751</v>
+        <v>0.3009052750796576</v>
       </c>
       <c r="D88" t="s">
         <v>7</v>
@@ -5839,7 +5839,7 @@
         <v>10</v>
       </c>
       <c r="C89">
-        <v>0.3153123502042979</v>
+        <v>0.3155032425814528</v>
       </c>
       <c r="D89" t="s">
         <v>7</v>
@@ -5856,7 +5856,7 @@
         <v>10</v>
       </c>
       <c r="C90">
-        <v>0.278376763944689</v>
+        <v>0.2785792775590318</v>
       </c>
       <c r="D90" t="s">
         <v>7</v>
@@ -5873,7 +5873,7 @@
         <v>6</v>
       </c>
       <c r="C91">
-        <v>0.2854119227649111</v>
+        <v>0.2854582331728598</v>
       </c>
       <c r="D91" t="s">
         <v>7</v>
@@ -5890,7 +5890,7 @@
         <v>10</v>
       </c>
       <c r="C92">
-        <v>0.283998589182451</v>
+        <v>0.284221704047108</v>
       </c>
       <c r="D92" t="s">
         <v>7</v>
@@ -5907,7 +5907,7 @@
         <v>15</v>
       </c>
       <c r="C93">
-        <v>0.3605716367605927</v>
+        <v>0.3603935763334742</v>
       </c>
       <c r="D93" t="s">
         <v>7</v>
@@ -5924,7 +5924,7 @@
         <v>6</v>
       </c>
       <c r="C94">
-        <v>0.3225850693748327</v>
+        <v>0.3226463761207925</v>
       </c>
       <c r="D94" t="s">
         <v>7</v>
@@ -5941,7 +5941,7 @@
         <v>10</v>
       </c>
       <c r="C95">
-        <v>0.3242343661727223</v>
+        <v>0.3244682683616514</v>
       </c>
       <c r="D95" t="s">
         <v>7</v>
@@ -5958,7 +5958,7 @@
         <v>15</v>
       </c>
       <c r="C96">
-        <v>0.3299536822213698</v>
+        <v>0.3297601230129829</v>
       </c>
       <c r="D96" t="s">
         <v>7</v>
@@ -5975,7 +5975,7 @@
         <v>44</v>
       </c>
       <c r="C97">
-        <v>0.3063782837690256</v>
+        <v>0.3062681895356062</v>
       </c>
       <c r="D97" t="s">
         <v>7</v>
@@ -5992,7 +5992,7 @@
         <v>44</v>
       </c>
       <c r="C98">
-        <v>0.3021456994419835</v>
+        <v>0.3020323388316731</v>
       </c>
       <c r="D98" t="s">
         <v>7</v>
@@ -6009,7 +6009,7 @@
         <v>6</v>
       </c>
       <c r="C99">
-        <v>0.4669213869724081</v>
+        <v>0.4669595041980193</v>
       </c>
       <c r="D99" t="s">
         <v>7</v>
@@ -6026,7 +6026,7 @@
         <v>44</v>
       </c>
       <c r="C100">
-        <v>0.3744290778268876</v>
+        <v>0.3743277640262537</v>
       </c>
       <c r="D100" t="s">
         <v>7</v>
@@ -6043,7 +6043,7 @@
         <v>44</v>
       </c>
       <c r="C101">
-        <v>0.3591232810452637</v>
+        <v>0.3590287669236582</v>
       </c>
       <c r="D101" t="s">
         <v>7</v>
@@ -6060,7 +6060,7 @@
         <v>6</v>
       </c>
       <c r="C102">
-        <v>0.4923628710996007</v>
+        <v>0.4924061738204196</v>
       </c>
       <c r="D102" t="s">
         <v>7</v>
@@ -6077,7 +6077,7 @@
         <v>6</v>
       </c>
       <c r="C103">
-        <v>0.3705809805454315</v>
+        <v>0.3706242578642114</v>
       </c>
       <c r="D103" t="s">
         <v>7</v>
@@ -6094,7 +6094,7 @@
         <v>15</v>
       </c>
       <c r="C104">
-        <v>0.3781518470000996</v>
+        <v>0.3779368403997101</v>
       </c>
       <c r="D104" t="s">
         <v>7</v>
@@ -6111,7 +6111,7 @@
         <v>44</v>
       </c>
       <c r="C105">
-        <v>0.2975620835049208</v>
+        <v>0.2974560085442119</v>
       </c>
       <c r="D105" t="s">
         <v>7</v>
@@ -6128,7 +6128,7 @@
         <v>10</v>
       </c>
       <c r="C106">
-        <v>0.4107787019743085</v>
+        <v>0.4109569794605678</v>
       </c>
       <c r="D106" t="s">
         <v>7</v>
@@ -6145,7 +6145,7 @@
         <v>10</v>
       </c>
       <c r="C107">
-        <v>0.339398832051066</v>
+        <v>0.3396276185127481</v>
       </c>
       <c r="D107" t="s">
         <v>7</v>
@@ -6162,7 +6162,7 @@
         <v>6</v>
       </c>
       <c r="C108">
-        <v>0.4086691278940307</v>
+        <v>0.4086781820072453</v>
       </c>
       <c r="D108" t="s">
         <v>7</v>
@@ -6196,7 +6196,7 @@
         <v>10</v>
       </c>
       <c r="C110">
-        <v>0.3069865223145256</v>
+        <v>0.307204690970856</v>
       </c>
       <c r="D110" t="s">
         <v>7</v>
@@ -6213,7 +6213,7 @@
         <v>6</v>
       </c>
       <c r="C111">
-        <v>0.5063824324583864</v>
+        <v>0.5064149297044651</v>
       </c>
       <c r="D111" t="s">
         <v>7</v>
@@ -6230,7 +6230,7 @@
         <v>6</v>
       </c>
       <c r="C112">
-        <v>0.4186542606363458</v>
+        <v>0.4187138939088344</v>
       </c>
       <c r="D112" t="s">
         <v>7</v>
@@ -6247,7 +6247,7 @@
         <v>15</v>
       </c>
       <c r="C113">
-        <v>0.4884709770417798</v>
+        <v>0.4882878752464895</v>
       </c>
       <c r="D113" t="s">
         <v>7</v>
@@ -6264,7 +6264,7 @@
         <v>6</v>
       </c>
       <c r="C114">
-        <v>0.6477941427026814</v>
+        <v>0.6478280329021556</v>
       </c>
       <c r="D114" t="s">
         <v>7</v>
@@ -6281,7 +6281,7 @@
         <v>6</v>
       </c>
       <c r="C115">
-        <v>0.3094937421584268</v>
+        <v>0.3095471261514482</v>
       </c>
       <c r="D115" t="s">
         <v>7</v>
@@ -6298,7 +6298,7 @@
         <v>6</v>
       </c>
       <c r="C116">
-        <v>0.4263199580293469</v>
+        <v>0.4263311140937783</v>
       </c>
       <c r="D116" t="s">
         <v>7</v>
@@ -6315,7 +6315,7 @@
         <v>10</v>
       </c>
       <c r="C117">
-        <v>0.3260002603677044</v>
+        <v>0.3262151839943554</v>
       </c>
       <c r="D117" t="s">
         <v>7</v>
@@ -6332,7 +6332,7 @@
         <v>10</v>
       </c>
       <c r="C118">
-        <v>0.371437016231991</v>
+        <v>0.371603608379141</v>
       </c>
       <c r="D118" t="s">
         <v>7</v>
@@ -6349,7 +6349,7 @@
         <v>6</v>
       </c>
       <c r="C119">
-        <v>0.3061960186400475</v>
+        <v>0.3062148405006058</v>
       </c>
       <c r="D119" t="s">
         <v>7</v>
@@ -6366,7 +6366,7 @@
         <v>10</v>
       </c>
       <c r="C120">
-        <v>0.3943749735764723</v>
+        <v>0.3945704846238975</v>
       </c>
       <c r="D120" t="s">
         <v>7</v>
@@ -6383,7 +6383,7 @@
         <v>226</v>
       </c>
       <c r="C121">
-        <v>0.4040086278973045</v>
+        <v>0.4040020188852858</v>
       </c>
       <c r="D121" t="s">
         <v>7</v>
@@ -6400,7 +6400,7 @@
         <v>15</v>
       </c>
       <c r="C122">
-        <v>0.298781164913996</v>
+        <v>0.2986011485931875</v>
       </c>
       <c r="D122" t="s">
         <v>7</v>
@@ -6417,7 +6417,7 @@
         <v>10</v>
       </c>
       <c r="C123">
-        <v>0.2803206082614191</v>
+        <v>0.2805335467014212</v>
       </c>
       <c r="D123" t="s">
         <v>7</v>
@@ -6434,7 +6434,7 @@
         <v>15</v>
       </c>
       <c r="C124">
-        <v>0.3975906367149994</v>
+        <v>0.3973796672227008</v>
       </c>
       <c r="D124" t="s">
         <v>7</v>
@@ -6451,7 +6451,7 @@
         <v>10</v>
       </c>
       <c r="C125">
-        <v>0.3090927798555571</v>
+        <v>0.3093046262825428</v>
       </c>
       <c r="D125" t="s">
         <v>7</v>
@@ -6468,7 +6468,7 @@
         <v>10</v>
       </c>
       <c r="C126">
-        <v>0.367252484345717</v>
+        <v>0.3674377051303651</v>
       </c>
       <c r="D126" t="s">
         <v>7</v>
@@ -6485,7 +6485,7 @@
         <v>6</v>
       </c>
       <c r="C127">
-        <v>0.5051115066762557</v>
+        <v>0.5051272082343499</v>
       </c>
       <c r="D127" t="s">
         <v>7</v>
@@ -6502,7 +6502,7 @@
         <v>15</v>
       </c>
       <c r="C128">
-        <v>0.4213460711332955</v>
+        <v>0.4211590078389102</v>
       </c>
       <c r="D128" t="s">
         <v>7</v>
@@ -6519,7 +6519,7 @@
         <v>15</v>
       </c>
       <c r="C129">
-        <v>0.297957435812113</v>
+        <v>0.2977698790689423</v>
       </c>
       <c r="D129" t="s">
         <v>7</v>
@@ -6536,7 +6536,7 @@
         <v>15</v>
       </c>
       <c r="C130">
-        <v>0.373087228647617</v>
+        <v>0.3728898877885902</v>
       </c>
       <c r="D130" t="s">
         <v>7</v>
@@ -6553,7 +6553,7 @@
         <v>10</v>
       </c>
       <c r="C131">
-        <v>0.3173892475413256</v>
+        <v>0.317599994994393</v>
       </c>
       <c r="D131" t="s">
         <v>7</v>
@@ -6570,7 +6570,7 @@
         <v>6</v>
       </c>
       <c r="C132">
-        <v>0.3950769398664344</v>
+        <v>0.3950841514323384</v>
       </c>
       <c r="D132" t="s">
         <v>7</v>
@@ -6587,7 +6587,7 @@
         <v>15</v>
       </c>
       <c r="C133">
-        <v>0.3311400498398224</v>
+        <v>0.3309702138758372</v>
       </c>
       <c r="D133" t="s">
         <v>7</v>
@@ -6604,7 +6604,7 @@
         <v>6</v>
       </c>
       <c r="C134">
-        <v>0.3860928008867358</v>
+        <v>0.3861496817019975</v>
       </c>
       <c r="D134" t="s">
         <v>7</v>
@@ -6621,7 +6621,7 @@
         <v>6</v>
       </c>
       <c r="C135">
-        <v>0.4115340140731483</v>
+        <v>0.4115825325600585</v>
       </c>
       <c r="D135" t="s">
         <v>7</v>
@@ -6638,7 +6638,7 @@
         <v>44</v>
       </c>
       <c r="C136">
-        <v>0.3046706258117919</v>
+        <v>0.3045595593335976</v>
       </c>
       <c r="D136" t="s">
         <v>7</v>
@@ -6655,7 +6655,7 @@
         <v>6</v>
       </c>
       <c r="C137">
-        <v>0.3983031429159632</v>
+        <v>0.3983278223616713</v>
       </c>
       <c r="D137" t="s">
         <v>7</v>
@@ -6672,7 +6672,7 @@
         <v>6</v>
       </c>
       <c r="C138">
-        <v>0.32870032156868</v>
+        <v>0.328743021665892</v>
       </c>
       <c r="D138" t="s">
         <v>7</v>
@@ -6689,7 +6689,7 @@
         <v>6</v>
       </c>
       <c r="C139">
-        <v>0.4155515158684819</v>
+        <v>0.4155945514927545</v>
       </c>
       <c r="D139" t="s">
         <v>7</v>
@@ -6706,7 +6706,7 @@
         <v>44</v>
       </c>
       <c r="C140">
-        <v>0.3728304478999824</v>
+        <v>0.3727404225766068</v>
       </c>
       <c r="D140" t="s">
         <v>7</v>
@@ -6723,7 +6723,7 @@
         <v>6</v>
       </c>
       <c r="C141">
-        <v>0.3366007474821912</v>
+        <v>0.3366462875829464</v>
       </c>
       <c r="D141" t="s">
         <v>7</v>
@@ -6740,7 +6740,7 @@
         <v>10</v>
       </c>
       <c r="C142">
-        <v>0.415940987793596</v>
+        <v>0.4161472528743987</v>
       </c>
       <c r="D142" t="s">
         <v>7</v>
@@ -6757,7 +6757,7 @@
         <v>6</v>
       </c>
       <c r="C143">
-        <v>0.374839127865511</v>
+        <v>0.3748839912079522</v>
       </c>
       <c r="D143" t="s">
         <v>7</v>
@@ -6774,7 +6774,7 @@
         <v>6</v>
       </c>
       <c r="C144">
-        <v>0.6252919250698538</v>
+        <v>0.6253298555327625</v>
       </c>
       <c r="D144" t="s">
         <v>7</v>
@@ -6791,7 +6791,7 @@
         <v>6</v>
       </c>
       <c r="C145">
-        <v>0.3071229613573984</v>
+        <v>0.3071638686153961</v>
       </c>
       <c r="D145" t="s">
         <v>7</v>
@@ -6808,7 +6808,7 @@
         <v>6</v>
       </c>
       <c r="C146">
-        <v>0.4227903018144512</v>
+        <v>0.4228321452366873</v>
       </c>
       <c r="D146" t="s">
         <v>7</v>
@@ -6825,7 +6825,7 @@
         <v>6</v>
       </c>
       <c r="C147">
-        <v>0.4704530052423444</v>
+        <v>0.4704922384946341</v>
       </c>
       <c r="D147" t="s">
         <v>7</v>
@@ -6842,7 +6842,7 @@
         <v>6</v>
       </c>
       <c r="C148">
-        <v>0.3172681052493492</v>
+        <v>0.3173058055945247</v>
       </c>
       <c r="D148" t="s">
         <v>7</v>
@@ -6859,7 +6859,7 @@
         <v>10</v>
       </c>
       <c r="C149">
-        <v>0.4142195572282715</v>
+        <v>0.41440188325174</v>
       </c>
       <c r="D149" t="s">
         <v>7</v>
@@ -6876,7 +6876,7 @@
         <v>6</v>
       </c>
       <c r="C150">
-        <v>0.3729043145002347</v>
+        <v>0.37295635314911</v>
       </c>
       <c r="D150" t="s">
         <v>7</v>
@@ -6893,7 +6893,7 @@
         <v>10</v>
       </c>
       <c r="C151">
-        <v>0.2909802423281161</v>
+        <v>0.2911850190859432</v>
       </c>
       <c r="D151" t="s">
         <v>7</v>
@@ -6910,7 +6910,7 @@
         <v>6</v>
       </c>
       <c r="C152">
-        <v>0.68550176959695</v>
+        <v>0.6854815098442254</v>
       </c>
       <c r="D152" t="s">
         <v>7</v>
@@ -6927,7 +6927,7 @@
         <v>10</v>
       </c>
       <c r="C153">
-        <v>0.3571220808184837</v>
+        <v>0.3573458709770164</v>
       </c>
       <c r="D153" t="s">
         <v>7</v>
@@ -6944,7 +6944,7 @@
         <v>44</v>
       </c>
       <c r="C154">
-        <v>0.3010104823930287</v>
+        <v>0.3009019354564765</v>
       </c>
       <c r="D154" t="s">
         <v>7</v>
@@ -6961,7 +6961,7 @@
         <v>6</v>
       </c>
       <c r="C155">
-        <v>0.3149471208050237</v>
+        <v>0.3149878441751549</v>
       </c>
       <c r="D155" t="s">
         <v>7</v>
@@ -6978,7 +6978,7 @@
         <v>10</v>
       </c>
       <c r="C156">
-        <v>0.3638920577525225</v>
+        <v>0.3641052565002296</v>
       </c>
       <c r="D156" t="s">
         <v>7</v>
@@ -6995,7 +6995,7 @@
         <v>6</v>
       </c>
       <c r="C157">
-        <v>0.4034754009752538</v>
+        <v>0.403490433487794</v>
       </c>
       <c r="D157" t="s">
         <v>7</v>
@@ -7012,7 +7012,7 @@
         <v>44</v>
       </c>
       <c r="C158">
-        <v>0.343338386124305</v>
+        <v>0.3432306219241956</v>
       </c>
       <c r="D158" t="s">
         <v>7</v>
@@ -7029,7 +7029,7 @@
         <v>44</v>
       </c>
       <c r="C159">
-        <v>0.3531117085060427</v>
+        <v>0.3530135161095824</v>
       </c>
       <c r="D159" t="s">
         <v>7</v>
@@ -7046,7 +7046,7 @@
         <v>6</v>
       </c>
       <c r="C160">
-        <v>0.3924645385822331</v>
+        <v>0.3925031161201566</v>
       </c>
       <c r="D160" t="s">
         <v>7</v>
@@ -7063,7 +7063,7 @@
         <v>6</v>
       </c>
       <c r="C161">
-        <v>0.430339755858315</v>
+        <v>0.4303852546416009</v>
       </c>
       <c r="D161" t="s">
         <v>7</v>
@@ -7080,7 +7080,7 @@
         <v>6</v>
       </c>
       <c r="C162">
-        <v>0.4843006112206148</v>
+        <v>0.4843358960395581</v>
       </c>
       <c r="D162" t="s">
         <v>7</v>
@@ -7097,7 +7097,7 @@
         <v>44</v>
       </c>
       <c r="C163">
-        <v>0.414634221450184</v>
+        <v>0.4145367679244031</v>
       </c>
       <c r="D163" t="s">
         <v>7</v>
@@ -7114,7 +7114,7 @@
         <v>10</v>
       </c>
       <c r="C164">
-        <v>0.3693453648931869</v>
+        <v>0.3695107150322886</v>
       </c>
       <c r="D164" t="s">
         <v>7</v>
@@ -7131,7 +7131,7 @@
         <v>10</v>
       </c>
       <c r="C165">
-        <v>0.4234384233801173</v>
+        <v>0.4236425497200997</v>
       </c>
       <c r="D165" t="s">
         <v>7</v>
@@ -7148,7 +7148,7 @@
         <v>10</v>
       </c>
       <c r="C166">
-        <v>0.3234231659963002</v>
+        <v>0.3236257339030049</v>
       </c>
       <c r="D166" t="s">
         <v>7</v>
@@ -7165,7 +7165,7 @@
         <v>6</v>
       </c>
       <c r="C167">
-        <v>0.374160986755515</v>
+        <v>0.3742086049729496</v>
       </c>
       <c r="D167" t="s">
         <v>7</v>
@@ -7182,7 +7182,7 @@
         <v>6</v>
       </c>
       <c r="C168">
-        <v>0.6149777064392979</v>
+        <v>0.6150106411642421</v>
       </c>
       <c r="D168" t="s">
         <v>7</v>
@@ -7199,7 +7199,7 @@
         <v>10</v>
       </c>
       <c r="C169">
-        <v>0.3314088255243869</v>
+        <v>0.3315963515899743</v>
       </c>
       <c r="D169" t="s">
         <v>7</v>
@@ -7216,7 +7216,7 @@
         <v>6</v>
       </c>
       <c r="C170">
-        <v>0.4006396258060142</v>
+        <v>0.4006943012523375</v>
       </c>
       <c r="D170" t="s">
         <v>7</v>
@@ -7233,7 +7233,7 @@
         <v>6</v>
       </c>
       <c r="C171">
-        <v>0.2727639647416724</v>
+        <v>0.2728158993850646</v>
       </c>
       <c r="D171" t="s">
         <v>7</v>
@@ -7250,7 +7250,7 @@
         <v>10</v>
       </c>
       <c r="C172">
-        <v>0.429963517076091</v>
+        <v>0.4301861626597795</v>
       </c>
       <c r="D172" t="s">
         <v>7</v>
@@ -7267,7 +7267,7 @@
         <v>10</v>
       </c>
       <c r="C173">
-        <v>0.3067824588764613</v>
+        <v>0.3069827417547709</v>
       </c>
       <c r="D173" t="s">
         <v>7</v>
@@ -7284,7 +7284,7 @@
         <v>6</v>
       </c>
       <c r="C174">
-        <v>0.321915360335224</v>
+        <v>0.3219622696067413</v>
       </c>
       <c r="D174" t="s">
         <v>7</v>
@@ -7301,7 +7301,7 @@
         <v>15</v>
       </c>
       <c r="C175">
-        <v>0.2983056186518726</v>
+        <v>0.2981447765707583</v>
       </c>
       <c r="D175" t="s">
         <v>7</v>
@@ -7318,7 +7318,7 @@
         <v>6</v>
       </c>
       <c r="C176">
-        <v>0.4256815055180311</v>
+        <v>0.4257208291041155</v>
       </c>
       <c r="D176" t="s">
         <v>7</v>
@@ -7335,7 +7335,7 @@
         <v>6</v>
       </c>
       <c r="C177">
-        <v>0.5207686039431421</v>
+        <v>0.5207966364694654</v>
       </c>
       <c r="D177" t="s">
         <v>7</v>
@@ -7352,7 +7352,7 @@
         <v>15</v>
       </c>
       <c r="C178">
-        <v>0.3910155722464447</v>
+        <v>0.3908155845559856</v>
       </c>
       <c r="D178" t="s">
         <v>7</v>
@@ -7369,7 +7369,7 @@
         <v>15</v>
       </c>
       <c r="C179">
-        <v>0.3040726435683931</v>
+        <v>0.3039038267378681</v>
       </c>
       <c r="D179" t="s">
         <v>7</v>
@@ -7386,7 +7386,7 @@
         <v>44</v>
       </c>
       <c r="C180">
-        <v>0.3093552012087581</v>
+        <v>0.3092469294013674</v>
       </c>
       <c r="D180" t="s">
         <v>7</v>
@@ -7403,7 +7403,7 @@
         <v>6</v>
       </c>
       <c r="C181">
-        <v>0.3369832048967492</v>
+        <v>0.3370273759965562</v>
       </c>
       <c r="D181" t="s">
         <v>7</v>
@@ -7420,7 +7420,7 @@
         <v>10</v>
       </c>
       <c r="C182">
-        <v>0.3150957023246092</v>
+        <v>0.3153062097867892</v>
       </c>
       <c r="D182" t="s">
         <v>7</v>
@@ -7437,7 +7437,7 @@
         <v>6</v>
       </c>
       <c r="C183">
-        <v>0.3278757066912501</v>
+        <v>0.3279283552028656</v>
       </c>
       <c r="D183" t="s">
         <v>7</v>
@@ -7454,7 +7454,7 @@
         <v>6</v>
       </c>
       <c r="C184">
-        <v>0.3672380224508587</v>
+        <v>0.3672851410429261</v>
       </c>
       <c r="D184" t="s">
         <v>7</v>
@@ -7471,7 +7471,7 @@
         <v>10</v>
       </c>
       <c r="C185">
-        <v>0.3712001492929879</v>
+        <v>0.3713803036828084</v>
       </c>
       <c r="D185" t="s">
         <v>7</v>
@@ -7488,7 +7488,7 @@
         <v>44</v>
       </c>
       <c r="C186">
-        <v>0.3633580716858676</v>
+        <v>0.3632551428773937</v>
       </c>
       <c r="D186" t="s">
         <v>7</v>
@@ -7505,7 +7505,7 @@
         <v>10</v>
       </c>
       <c r="C187">
-        <v>0.2664328586774437</v>
+        <v>0.2666468589599431</v>
       </c>
       <c r="D187" t="s">
         <v>7</v>
@@ -7522,7 +7522,7 @@
         <v>10</v>
       </c>
       <c r="C188">
-        <v>0.4041146345757582</v>
+        <v>0.4043022539197972</v>
       </c>
       <c r="D188" t="s">
         <v>7</v>
@@ -7539,7 +7539,7 @@
         <v>10</v>
       </c>
       <c r="C189">
-        <v>0.3473210256989374</v>
+        <v>0.3475212179830245</v>
       </c>
       <c r="D189" t="s">
         <v>7</v>
@@ -7556,7 +7556,7 @@
         <v>6</v>
       </c>
       <c r="C190">
-        <v>0.3193924204754062</v>
+        <v>0.3194219121535341</v>
       </c>
       <c r="D190" t="s">
         <v>7</v>
@@ -7573,7 +7573,7 @@
         <v>10</v>
       </c>
       <c r="C191">
-        <v>0.3496760636175043</v>
+        <v>0.3498963904582731</v>
       </c>
       <c r="D191" t="s">
         <v>7</v>
@@ -7590,7 +7590,7 @@
         <v>15</v>
       </c>
       <c r="C192">
-        <v>0.398699759549437</v>
+        <v>0.3985213438528357</v>
       </c>
       <c r="D192" t="s">
         <v>7</v>
@@ -7607,7 +7607,7 @@
         <v>15</v>
       </c>
       <c r="C193">
-        <v>0.4190832174006298</v>
+        <v>0.4189053263938315</v>
       </c>
       <c r="D193" t="s">
         <v>7</v>
@@ -7624,7 +7624,7 @@
         <v>15</v>
       </c>
       <c r="C194">
-        <v>0.3604983926365258</v>
+        <v>0.3602988950017231</v>
       </c>
       <c r="D194" t="s">
         <v>7</v>
@@ -7641,7 +7641,7 @@
         <v>226</v>
       </c>
       <c r="C195">
-        <v>0.4876899733181512</v>
+        <v>0.4876948436150666</v>
       </c>
       <c r="D195" t="s">
         <v>7</v>
@@ -7658,7 +7658,7 @@
         <v>6</v>
       </c>
       <c r="C196">
-        <v>0.3972904642317303</v>
+        <v>0.397352910218861</v>
       </c>
       <c r="D196" t="s">
         <v>7</v>
@@ -7675,7 +7675,7 @@
         <v>10</v>
       </c>
       <c r="C197">
-        <v>0.3311162167895405</v>
+        <v>0.3313368505677494</v>
       </c>
       <c r="D197" t="s">
         <v>7</v>
@@ -7692,7 +7692,7 @@
         <v>6</v>
       </c>
       <c r="C198">
-        <v>0.5259810096392274</v>
+        <v>0.5259849140997427</v>
       </c>
       <c r="D198" t="s">
         <v>7</v>
@@ -7709,7 +7709,7 @@
         <v>6</v>
       </c>
       <c r="C199">
-        <v>0.6198264278794132</v>
+        <v>0.6198655938653765</v>
       </c>
       <c r="D199" t="s">
         <v>7</v>
@@ -7726,7 +7726,7 @@
         <v>15</v>
       </c>
       <c r="C200">
-        <v>0.3202709246438011</v>
+        <v>0.3200997819819573</v>
       </c>
       <c r="D200" t="s">
         <v>7</v>
@@ -7743,7 +7743,7 @@
         <v>15</v>
       </c>
       <c r="C201">
-        <v>0.3121292170182082</v>
+        <v>0.3119689467489691</v>
       </c>
       <c r="D201" t="s">
         <v>7</v>
@@ -7760,7 +7760,7 @@
         <v>10</v>
       </c>
       <c r="C202">
-        <v>0.3704550283872084</v>
+        <v>0.3706752094597894</v>
       </c>
       <c r="D202" t="s">
         <v>7</v>
@@ -7777,7 +7777,7 @@
         <v>6</v>
       </c>
       <c r="C203">
-        <v>0.5577578251440909</v>
+        <v>0.5577967472348307</v>
       </c>
       <c r="D203" t="s">
         <v>7</v>
@@ -7794,7 +7794,7 @@
         <v>6</v>
       </c>
       <c r="C204">
-        <v>0.4934779618703716</v>
+        <v>0.4935176810108449</v>
       </c>
       <c r="D204" t="s">
         <v>7</v>
@@ -7811,7 +7811,7 @@
         <v>10</v>
       </c>
       <c r="C205">
-        <v>0.4522510663045292</v>
+        <v>0.4524538914960979</v>
       </c>
       <c r="D205" t="s">
         <v>7</v>
@@ -7828,7 +7828,7 @@
         <v>15</v>
       </c>
       <c r="C206">
-        <v>0.3475846140146978</v>
+        <v>0.3474082894455316</v>
       </c>
       <c r="D206" t="s">
         <v>7</v>
@@ -7845,7 +7845,7 @@
         <v>44</v>
       </c>
       <c r="C207">
-        <v>0.5224378534638913</v>
+        <v>0.5223916900359824</v>
       </c>
       <c r="D207" t="s">
         <v>7</v>
@@ -7862,7 +7862,7 @@
         <v>10</v>
       </c>
       <c r="C208">
-        <v>0.3495590788583915</v>
+        <v>0.349775881726774</v>
       </c>
       <c r="D208" t="s">
         <v>7</v>
@@ -7879,7 +7879,7 @@
         <v>10</v>
       </c>
       <c r="C209">
-        <v>0.5539482067201438</v>
+        <v>0.5540935968920363</v>
       </c>
       <c r="D209" t="s">
         <v>7</v>
@@ -7896,7 +7896,7 @@
         <v>6</v>
       </c>
       <c r="C210">
-        <v>0.4436187924380666</v>
+        <v>0.4436557348994326</v>
       </c>
       <c r="D210" t="s">
         <v>7</v>
@@ -7913,7 +7913,7 @@
         <v>15</v>
       </c>
       <c r="C211">
-        <v>0.4598179975738328</v>
+        <v>0.4596190445075198</v>
       </c>
       <c r="D211" t="s">
         <v>7</v>
@@ -7930,7 +7930,7 @@
         <v>10</v>
       </c>
       <c r="C212">
-        <v>0.2901657990742273</v>
+        <v>0.2903848094194069</v>
       </c>
       <c r="D212" t="s">
         <v>7</v>
@@ -7947,7 +7947,7 @@
         <v>10</v>
       </c>
       <c r="C213">
-        <v>0.3283076796173972</v>
+        <v>0.3285330114357485</v>
       </c>
       <c r="D213" t="s">
         <v>7</v>
@@ -7964,7 +7964,7 @@
         <v>15</v>
       </c>
       <c r="C214">
-        <v>0.3684209688975205</v>
+        <v>0.368225607786905</v>
       </c>
       <c r="D214" t="s">
         <v>7</v>
@@ -7981,7 +7981,7 @@
         <v>10</v>
       </c>
       <c r="C215">
-        <v>0.5198819693236149</v>
+        <v>0.5199946643189131</v>
       </c>
       <c r="D215" t="s">
         <v>7</v>
@@ -7998,7 +7998,7 @@
         <v>15</v>
       </c>
       <c r="C216">
-        <v>0.3301753915636213</v>
+        <v>0.3300072259854918</v>
       </c>
       <c r="D216" t="s">
         <v>7</v>
@@ -8015,7 +8015,7 @@
         <v>10</v>
       </c>
       <c r="C217">
-        <v>0.3283930235443833</v>
+        <v>0.3286213185113728</v>
       </c>
       <c r="D217" t="s">
         <v>7</v>
@@ -8032,7 +8032,7 @@
         <v>10</v>
       </c>
       <c r="C218">
-        <v>0.3697425342593207</v>
+        <v>0.3699225608053016</v>
       </c>
       <c r="D218" t="s">
         <v>7</v>
@@ -8049,7 +8049,7 @@
         <v>44</v>
       </c>
       <c r="C219">
-        <v>0.4568289938723162</v>
+        <v>0.4567566060103629</v>
       </c>
       <c r="D219" t="s">
         <v>7</v>
@@ -8066,7 +8066,7 @@
         <v>15</v>
       </c>
       <c r="C220">
-        <v>0.300018805300597</v>
+        <v>0.2998494527999482</v>
       </c>
       <c r="D220" t="s">
         <v>7</v>
@@ -8083,7 +8083,7 @@
         <v>15</v>
       </c>
       <c r="C221">
-        <v>0.3757100335338037</v>
+        <v>0.3755365900476916</v>
       </c>
       <c r="D221" t="s">
         <v>7</v>
@@ -8100,7 +8100,7 @@
         <v>10</v>
       </c>
       <c r="C222">
-        <v>0.3254059236278634</v>
+        <v>0.3256179394527048</v>
       </c>
       <c r="D222" t="s">
         <v>7</v>
@@ -8117,7 +8117,7 @@
         <v>10</v>
       </c>
       <c r="C223">
-        <v>0.4914735108101537</v>
+        <v>0.4916017964309926</v>
       </c>
       <c r="D223" t="s">
         <v>7</v>
@@ -8134,7 +8134,7 @@
         <v>10</v>
       </c>
       <c r="C224">
-        <v>0.3173977671514253</v>
+        <v>0.3175977909587966</v>
       </c>
       <c r="D224" t="s">
         <v>7</v>
@@ -8151,7 +8151,7 @@
         <v>15</v>
       </c>
       <c r="C225">
-        <v>0.3559120937766239</v>
+        <v>0.355710684772941</v>
       </c>
       <c r="D225" t="s">
         <v>7</v>
@@ -8168,7 +8168,7 @@
         <v>6</v>
       </c>
       <c r="C226">
-        <v>0.5098137015120904</v>
+        <v>0.5098558094040082</v>
       </c>
       <c r="D226" t="s">
         <v>7</v>
@@ -8185,7 +8185,7 @@
         <v>10</v>
       </c>
       <c r="C227">
-        <v>0.3400511379078193</v>
+        <v>0.3402708333816193</v>
       </c>
       <c r="D227" t="s">
         <v>7</v>
@@ -8202,7 +8202,7 @@
         <v>6</v>
       </c>
       <c r="C228">
-        <v>0.5095839703224546</v>
+        <v>0.5096666150562001</v>
       </c>
       <c r="D228" t="s">
         <v>7</v>
@@ -8219,7 +8219,7 @@
         <v>6</v>
       </c>
       <c r="C229">
-        <v>0.586917746010712</v>
+        <v>0.5869695173244037</v>
       </c>
       <c r="D229" t="s">
         <v>7</v>
@@ -8236,7 +8236,7 @@
         <v>44</v>
       </c>
       <c r="C230">
-        <v>0.314472946438428</v>
+        <v>0.3143634279980685</v>
       </c>
       <c r="D230" t="s">
         <v>7</v>
@@ -8253,7 +8253,7 @@
         <v>6</v>
       </c>
       <c r="C231">
-        <v>0.3308645659122954</v>
+        <v>0.3309048943425693</v>
       </c>
       <c r="D231" t="s">
         <v>7</v>
@@ -8270,7 +8270,7 @@
         <v>6</v>
       </c>
       <c r="C232">
-        <v>0.6097752633871738</v>
+        <v>0.609806910007668</v>
       </c>
       <c r="D232" t="s">
         <v>7</v>
@@ -8287,7 +8287,7 @@
         <v>44</v>
       </c>
       <c r="C233">
-        <v>0.3804090853199393</v>
+        <v>0.3803083588821951</v>
       </c>
       <c r="D233" t="s">
         <v>7</v>
@@ -8304,7 +8304,7 @@
         <v>6</v>
       </c>
       <c r="C234">
-        <v>0.4452354951613074</v>
+        <v>0.4452532161403751</v>
       </c>
       <c r="D234" t="s">
         <v>7</v>
@@ -8321,7 +8321,7 @@
         <v>6</v>
       </c>
       <c r="C235">
-        <v>0.5204457984181673</v>
+        <v>0.5204748547363988</v>
       </c>
       <c r="D235" t="s">
         <v>7</v>
@@ -8338,7 +8338,7 @@
         <v>6</v>
       </c>
       <c r="C236">
-        <v>0.3112369701523505</v>
+        <v>0.3112944095678405</v>
       </c>
       <c r="D236" t="s">
         <v>7</v>
@@ -8355,7 +8355,7 @@
         <v>6</v>
       </c>
       <c r="C237">
-        <v>0.3254542244177857</v>
+        <v>0.3255041924281766</v>
       </c>
       <c r="D237" t="s">
         <v>7</v>
@@ -8372,7 +8372,7 @@
         <v>6</v>
       </c>
       <c r="C238">
-        <v>0.3734090214134132</v>
+        <v>0.3734264486235567</v>
       </c>
       <c r="D238" t="s">
         <v>7</v>
@@ -8389,7 +8389,7 @@
         <v>6</v>
       </c>
       <c r="C239">
-        <v>0.4598640750088599</v>
+        <v>0.4598985968203674</v>
       </c>
       <c r="D239" t="s">
         <v>7</v>
@@ -8406,7 +8406,7 @@
         <v>226</v>
       </c>
       <c r="C240">
-        <v>0.3508895557533616</v>
+        <v>0.3508750481198449</v>
       </c>
       <c r="D240" t="s">
         <v>7</v>
@@ -8423,7 +8423,7 @@
         <v>10</v>
       </c>
       <c r="C241">
-        <v>0.269976002812368</v>
+        <v>0.2702014474003883</v>
       </c>
       <c r="D241" t="s">
         <v>7</v>
@@ -8440,7 +8440,7 @@
         <v>6</v>
       </c>
       <c r="C242">
-        <v>0.3397682845941056</v>
+        <v>0.3398097766157385</v>
       </c>
       <c r="D242" t="s">
         <v>7</v>
@@ -8457,7 +8457,7 @@
         <v>15</v>
       </c>
       <c r="C243">
-        <v>0.4879686533189083</v>
+        <v>0.4877598077355441</v>
       </c>
       <c r="D243" t="s">
         <v>7</v>
@@ -8474,7 +8474,7 @@
         <v>226</v>
       </c>
       <c r="C244">
-        <v>0.4728841549886199</v>
+        <v>0.4728371520755983</v>
       </c>
       <c r="D244" t="s">
         <v>7</v>
@@ -8491,7 +8491,7 @@
         <v>6</v>
       </c>
       <c r="C245">
-        <v>0.650770054746319</v>
+        <v>0.65081428977905</v>
       </c>
       <c r="D245" t="s">
         <v>7</v>
@@ -8508,7 +8508,7 @@
         <v>6</v>
       </c>
       <c r="C246">
-        <v>0.4667013084043142</v>
+        <v>0.4667635832177167</v>
       </c>
       <c r="D246" t="s">
         <v>7</v>
@@ -8525,7 +8525,7 @@
         <v>6</v>
       </c>
       <c r="C247">
-        <v>0.419936227851554</v>
+        <v>0.4199672474976888</v>
       </c>
       <c r="D247" t="s">
         <v>7</v>
@@ -8542,7 +8542,7 @@
         <v>10</v>
       </c>
       <c r="C248">
-        <v>0.3288582378464036</v>
+        <v>0.3290617548138802</v>
       </c>
       <c r="D248" t="s">
         <v>7</v>
@@ -8559,7 +8559,7 @@
         <v>6</v>
       </c>
       <c r="C249">
-        <v>0.4475787588455902</v>
+        <v>0.447621384986058</v>
       </c>
       <c r="D249" t="s">
         <v>7</v>
@@ -8576,7 +8576,7 @@
         <v>15</v>
       </c>
       <c r="C250">
-        <v>0.3131450154531511</v>
+        <v>0.3129666575902855</v>
       </c>
       <c r="D250" t="s">
         <v>7</v>
@@ -8593,7 +8593,7 @@
         <v>44</v>
       </c>
       <c r="C251">
-        <v>0.4805005547154459</v>
+        <v>0.4804261793244737</v>
       </c>
       <c r="D251" t="s">
         <v>7</v>
@@ -8610,7 +8610,7 @@
         <v>6</v>
       </c>
       <c r="C252">
-        <v>0.4287034562494008</v>
+        <v>0.4287692698783986</v>
       </c>
       <c r="D252" t="s">
         <v>7</v>
@@ -8627,7 +8627,7 @@
         <v>6</v>
       </c>
       <c r="C253">
-        <v>0.3795066996673866</v>
+        <v>0.3795565665945869</v>
       </c>
       <c r="D253" t="s">
         <v>7</v>
@@ -8644,7 +8644,7 @@
         <v>6</v>
       </c>
       <c r="C254">
-        <v>0.5065138976750919</v>
+        <v>0.5065610833141485</v>
       </c>
       <c r="D254" t="s">
         <v>7</v>
@@ -8661,7 +8661,7 @@
         <v>15</v>
       </c>
       <c r="C255">
-        <v>0.443975833309654</v>
+        <v>0.4437598464367363</v>
       </c>
       <c r="D255" t="s">
         <v>7</v>
@@ -8678,7 +8678,7 @@
         <v>6</v>
       </c>
       <c r="C256">
-        <v>0.6080754660427045</v>
+        <v>0.6080766524201341</v>
       </c>
       <c r="D256" t="s">
         <v>7</v>
@@ -8695,7 +8695,7 @@
         <v>6</v>
       </c>
       <c r="C257">
-        <v>0.4248739900860602</v>
+        <v>0.4249197561162011</v>
       </c>
       <c r="D257" t="s">
         <v>7</v>
@@ -8712,7 +8712,7 @@
         <v>6</v>
       </c>
       <c r="C258">
-        <v>0.5292200994606695</v>
+        <v>0.529280319363115</v>
       </c>
       <c r="D258" t="s">
         <v>7</v>
@@ -8729,7 +8729,7 @@
         <v>6</v>
       </c>
       <c r="C259">
-        <v>0.2957559548144028</v>
+        <v>0.2957785310832267</v>
       </c>
       <c r="D259" t="s">
         <v>7</v>
@@ -8746,7 +8746,7 @@
         <v>6</v>
       </c>
       <c r="C260">
-        <v>0.4514914915825632</v>
+        <v>0.4514977521541865</v>
       </c>
       <c r="D260" t="s">
         <v>7</v>
@@ -8763,7 +8763,7 @@
         <v>6</v>
       </c>
       <c r="C261">
-        <v>0.5010434164412489</v>
+        <v>0.5010860645073553</v>
       </c>
       <c r="D261" t="s">
         <v>7</v>
@@ -8780,7 +8780,7 @@
         <v>6</v>
       </c>
       <c r="C262">
-        <v>0.4477981772738125</v>
+        <v>0.4478489379716189</v>
       </c>
       <c r="D262" t="s">
         <v>7</v>
@@ -8797,7 +8797,7 @@
         <v>6</v>
       </c>
       <c r="C263">
-        <v>0.4776680923274867</v>
+        <v>0.4777106254914819</v>
       </c>
       <c r="D263" t="s">
         <v>7</v>
@@ -8814,7 +8814,7 @@
         <v>6</v>
       </c>
       <c r="C264">
-        <v>0.4585566080296707</v>
+        <v>0.4585712085471118</v>
       </c>
       <c r="D264" t="s">
         <v>7</v>
@@ -8831,7 +8831,7 @@
         <v>6</v>
       </c>
       <c r="C265">
-        <v>0.3620312193776954</v>
+        <v>0.3620689568234249</v>
       </c>
       <c r="D265" t="s">
         <v>7</v>
@@ -8848,7 +8848,7 @@
         <v>6</v>
       </c>
       <c r="C266">
-        <v>0.4125033463316551</v>
+        <v>0.4125403999083336</v>
       </c>
       <c r="D266" t="s">
         <v>7</v>
@@ -8865,7 +8865,7 @@
         <v>6</v>
       </c>
       <c r="C267">
-        <v>0.2900911535747839</v>
+        <v>0.2901382802972959</v>
       </c>
       <c r="D267" t="s">
         <v>7</v>
@@ -8882,7 +8882,7 @@
         <v>6</v>
       </c>
       <c r="C268">
-        <v>0.4674674117069709</v>
+        <v>0.4675297326835262</v>
       </c>
       <c r="D268" t="s">
         <v>7</v>
@@ -8899,7 +8899,7 @@
         <v>44</v>
       </c>
       <c r="C269">
-        <v>0.3478357561828685</v>
+        <v>0.3477321159604124</v>
       </c>
       <c r="D269" t="s">
         <v>7</v>
@@ -8916,7 +8916,7 @@
         <v>6</v>
       </c>
       <c r="C270">
-        <v>0.5546228366108412</v>
+        <v>0.5546453758137778</v>
       </c>
       <c r="D270" t="s">
         <v>7</v>
@@ -8933,7 +8933,7 @@
         <v>6</v>
       </c>
       <c r="C271">
-        <v>0.5671076441565982</v>
+        <v>0.5671463265124537</v>
       </c>
       <c r="D271" t="s">
         <v>7</v>
@@ -8950,7 +8950,7 @@
         <v>6</v>
       </c>
       <c r="C272">
-        <v>0.4022624200839399</v>
+        <v>0.4023049974648862</v>
       </c>
       <c r="D272" t="s">
         <v>7</v>
@@ -8967,7 +8967,7 @@
         <v>6</v>
       </c>
       <c r="C273">
-        <v>0.5505033689212446</v>
+        <v>0.5505573909906667</v>
       </c>
       <c r="D273" t="s">
         <v>7</v>
@@ -8984,7 +8984,7 @@
         <v>15</v>
       </c>
       <c r="C274">
-        <v>0.3535804806460833</v>
+        <v>0.3534092180518709</v>
       </c>
       <c r="D274" t="s">
         <v>7</v>
@@ -9001,7 +9001,7 @@
         <v>10</v>
       </c>
       <c r="C275">
-        <v>0.2709112905959883</v>
+        <v>0.2711153059839895</v>
       </c>
       <c r="D275" t="s">
         <v>7</v>
@@ -9018,7 +9018,7 @@
         <v>6</v>
       </c>
       <c r="C276">
-        <v>0.3323300528353696</v>
+        <v>0.3323720101875601</v>
       </c>
       <c r="D276" t="s">
         <v>7</v>
@@ -9035,7 +9035,7 @@
         <v>6</v>
       </c>
       <c r="C277">
-        <v>0.3964910972052848</v>
+        <v>0.3965443889570791</v>
       </c>
       <c r="D277" t="s">
         <v>7</v>
@@ -9052,7 +9052,7 @@
         <v>6</v>
       </c>
       <c r="C278">
-        <v>0.4537396925068726</v>
+        <v>0.4537653092004412</v>
       </c>
       <c r="D278" t="s">
         <v>7</v>
@@ -9069,7 +9069,7 @@
         <v>6</v>
       </c>
       <c r="C279">
-        <v>0.5729455637864586</v>
+        <v>0.5730123313903677</v>
       </c>
       <c r="D279" t="s">
         <v>7</v>
@@ -9086,7 +9086,7 @@
         <v>6</v>
       </c>
       <c r="C280">
-        <v>0.5090396115947469</v>
+        <v>0.5090987795517588</v>
       </c>
       <c r="D280" t="s">
         <v>7</v>
@@ -9103,7 +9103,7 @@
         <v>6</v>
       </c>
       <c r="C281">
-        <v>0.4117389490402136</v>
+        <v>0.4117751331643119</v>
       </c>
       <c r="D281" t="s">
         <v>7</v>
@@ -9120,7 +9120,7 @@
         <v>15</v>
       </c>
       <c r="C282">
-        <v>0.3644025268586457</v>
+        <v>0.36422735662484</v>
       </c>
       <c r="D282" t="s">
         <v>7</v>
@@ -9137,7 +9137,7 @@
         <v>6</v>
       </c>
       <c r="C283">
-        <v>0.3598628497108494</v>
+        <v>0.3598807386659951</v>
       </c>
       <c r="D283" t="s">
         <v>7</v>
@@ -9154,7 +9154,7 @@
         <v>6</v>
       </c>
       <c r="C284">
-        <v>0.3494730976146233</v>
+        <v>0.3495258447783943</v>
       </c>
       <c r="D284" t="s">
         <v>7</v>
@@ -9171,7 +9171,7 @@
         <v>10</v>
       </c>
       <c r="C285">
-        <v>0.2645807223796351</v>
+        <v>0.2647580123484087</v>
       </c>
       <c r="D285" t="s">
         <v>7</v>
@@ -9188,7 +9188,7 @@
         <v>6</v>
       </c>
       <c r="C286">
-        <v>0.313041379974872</v>
+        <v>0.3130828627710331</v>
       </c>
       <c r="D286" t="s">
         <v>7</v>
@@ -9205,7 +9205,7 @@
         <v>44</v>
       </c>
       <c r="C287">
-        <v>0.4547122588386457</v>
+        <v>0.4546383690506665</v>
       </c>
       <c r="D287" t="s">
         <v>7</v>
@@ -9222,7 +9222,7 @@
         <v>6</v>
       </c>
       <c r="C288">
-        <v>0.2920858150028525</v>
+        <v>0.292136073961054</v>
       </c>
       <c r="D288" t="s">
         <v>7</v>
@@ -9239,7 +9239,7 @@
         <v>6</v>
       </c>
       <c r="C289">
-        <v>0.3850034022574416</v>
+        <v>0.3850521685445955</v>
       </c>
       <c r="D289" t="s">
         <v>7</v>
@@ -9256,7 +9256,7 @@
         <v>15</v>
       </c>
       <c r="C290">
-        <v>0.3153763449791123</v>
+        <v>0.3152092281061221</v>
       </c>
       <c r="D290" t="s">
         <v>7</v>
@@ -9273,7 +9273,7 @@
         <v>6</v>
       </c>
       <c r="C291">
-        <v>0.4528147063404485</v>
+        <v>0.4528700627120865</v>
       </c>
       <c r="D291" t="s">
         <v>7</v>
@@ -9290,7 +9290,7 @@
         <v>145</v>
       </c>
       <c r="C292">
-        <v>0.4147849531296718</v>
+        <v>0.414793173055129</v>
       </c>
       <c r="D292" t="s">
         <v>7</v>
@@ -9307,7 +9307,7 @@
         <v>6</v>
       </c>
       <c r="C293">
-        <v>0.6324100861989473</v>
+        <v>0.6324562399616352</v>
       </c>
       <c r="D293" t="s">
         <v>7</v>
@@ -9324,7 +9324,7 @@
         <v>15</v>
       </c>
       <c r="C294">
-        <v>0.3996355251140249</v>
+        <v>0.3994341138156789</v>
       </c>
       <c r="D294" t="s">
         <v>7</v>
@@ -9341,7 +9341,7 @@
         <v>10</v>
       </c>
       <c r="C295">
-        <v>0.3523120850116416</v>
+        <v>0.3525385591116728</v>
       </c>
       <c r="D295" t="s">
         <v>7</v>
@@ -9358,7 +9358,7 @@
         <v>15</v>
       </c>
       <c r="C296">
-        <v>0.3103039735596185</v>
+        <v>0.3101319861299852</v>
       </c>
       <c r="D296" t="s">
         <v>7</v>
@@ -9375,7 +9375,7 @@
         <v>10</v>
       </c>
       <c r="C297">
-        <v>0.4807373160734532</v>
+        <v>0.4809445272049341</v>
       </c>
       <c r="D297" t="s">
         <v>7</v>
@@ -9392,7 +9392,7 @@
         <v>10</v>
       </c>
       <c r="C298">
-        <v>0.4200955987668332</v>
+        <v>0.4203211766388632</v>
       </c>
       <c r="D298" t="s">
         <v>7</v>
@@ -9409,7 +9409,7 @@
         <v>6</v>
       </c>
       <c r="C299">
-        <v>0.2524775006484014</v>
+        <v>0.2525275085242315</v>
       </c>
       <c r="D299" t="s">
         <v>7</v>
@@ -9426,7 +9426,7 @@
         <v>10</v>
       </c>
       <c r="C300">
-        <v>0.3455403646262921</v>
+        <v>0.3457330786706065</v>
       </c>
       <c r="D300" t="s">
         <v>7</v>
@@ -9443,7 +9443,7 @@
         <v>6</v>
       </c>
       <c r="C301">
-        <v>0.3747488225476935</v>
+        <v>0.374796308749854</v>
       </c>
       <c r="D301" t="s">
         <v>7</v>
@@ -9460,7 +9460,7 @@
         <v>44</v>
       </c>
       <c r="C302">
-        <v>0.4499423980233307</v>
+        <v>0.4498639441849994</v>
       </c>
       <c r="D302" t="s">
         <v>7</v>
@@ -9477,7 +9477,7 @@
         <v>10</v>
       </c>
       <c r="C303">
-        <v>0.3354929241022565</v>
+        <v>0.3357070198129143</v>
       </c>
       <c r="D303" t="s">
         <v>7</v>
@@ -9494,7 +9494,7 @@
         <v>10</v>
       </c>
       <c r="C304">
-        <v>0.3216877582690376</v>
+        <v>0.3219079767844323</v>
       </c>
       <c r="D304" t="s">
         <v>7</v>
@@ -9511,7 +9511,7 @@
         <v>44</v>
       </c>
       <c r="C305">
-        <v>0.3778045767895376</v>
+        <v>0.3777082407553171</v>
       </c>
       <c r="D305" t="s">
         <v>7</v>
@@ -9528,7 +9528,7 @@
         <v>15</v>
       </c>
       <c r="C306">
-        <v>0.4242393695327802</v>
+        <v>0.4240596334073203</v>
       </c>
       <c r="D306" t="s">
         <v>7</v>
@@ -9545,7 +9545,7 @@
         <v>6</v>
       </c>
       <c r="C307">
-        <v>0.4365555623360072</v>
+        <v>0.4365900647086667</v>
       </c>
       <c r="D307" t="s">
         <v>7</v>
@@ -9562,7 +9562,7 @@
         <v>6</v>
       </c>
       <c r="C308">
-        <v>0.4084385285716082</v>
+        <v>0.4084740061893299</v>
       </c>
       <c r="D308" t="s">
         <v>7</v>
@@ -9579,7 +9579,7 @@
         <v>6</v>
       </c>
       <c r="C309">
-        <v>0.2920834437777971</v>
+        <v>0.2921327744706865</v>
       </c>
       <c r="D309" t="s">
         <v>7</v>
@@ -9596,7 +9596,7 @@
         <v>6</v>
       </c>
       <c r="C310">
-        <v>0.4337616798969857</v>
+        <v>0.4338250681571506</v>
       </c>
       <c r="D310" t="s">
         <v>7</v>
@@ -9613,7 +9613,7 @@
         <v>15</v>
       </c>
       <c r="C311">
-        <v>0.3479273220095984</v>
+        <v>0.3477327182526064</v>
       </c>
       <c r="D311" t="s">
         <v>7</v>
@@ -9630,7 +9630,7 @@
         <v>15</v>
       </c>
       <c r="C312">
-        <v>0.2708021174766714</v>
+        <v>0.2706394046624557</v>
       </c>
       <c r="D312" t="s">
         <v>7</v>
@@ -9647,7 +9647,7 @@
         <v>44</v>
       </c>
       <c r="C313">
-        <v>0.2874787165647144</v>
+        <v>0.287370407743457</v>
       </c>
       <c r="D313" t="s">
         <v>7</v>
@@ -9664,7 +9664,7 @@
         <v>10</v>
       </c>
       <c r="C314">
-        <v>0.3248328094408092</v>
+        <v>0.3250439135133066</v>
       </c>
       <c r="D314" t="s">
         <v>7</v>
@@ -9681,7 +9681,7 @@
         <v>44</v>
       </c>
       <c r="C315">
-        <v>0.4883754289138955</v>
+        <v>0.4883115976894868</v>
       </c>
       <c r="D315" t="s">
         <v>7</v>
@@ -9698,7 +9698,7 @@
         <v>6</v>
       </c>
       <c r="C316">
-        <v>0.4055371276178646</v>
+        <v>0.4055949695332535</v>
       </c>
       <c r="D316" t="s">
         <v>7</v>
@@ -9715,7 +9715,7 @@
         <v>6</v>
       </c>
       <c r="C317">
-        <v>0.5489745976485709</v>
+        <v>0.5490350181408492</v>
       </c>
       <c r="D317" t="s">
         <v>7</v>
@@ -9732,7 +9732,7 @@
         <v>6</v>
       </c>
       <c r="C318">
-        <v>0.5784795385262173</v>
+        <v>0.5785395088991326</v>
       </c>
       <c r="D318" t="s">
         <v>7</v>
@@ -9749,7 +9749,7 @@
         <v>6</v>
       </c>
       <c r="C319">
-        <v>0.3614309916785954</v>
+        <v>0.361478844952316</v>
       </c>
       <c r="D319" t="s">
         <v>7</v>
@@ -9766,7 +9766,7 @@
         <v>10</v>
       </c>
       <c r="C320">
-        <v>0.295698953892377</v>
+        <v>0.2959217611185436</v>
       </c>
       <c r="D320" t="s">
         <v>7</v>
@@ -9783,7 +9783,7 @@
         <v>6</v>
       </c>
       <c r="C321">
-        <v>0.3642276397662745</v>
+        <v>0.3642419198591766</v>
       </c>
       <c r="D321" t="s">
         <v>7</v>
@@ -9800,7 +9800,7 @@
         <v>6</v>
       </c>
       <c r="C322">
-        <v>0.3925672748425564</v>
+        <v>0.3926201961377123</v>
       </c>
       <c r="D322" t="s">
         <v>7</v>
@@ -9817,7 +9817,7 @@
         <v>10</v>
       </c>
       <c r="C323">
-        <v>0.3437570586634285</v>
+        <v>0.3439760893357556</v>
       </c>
       <c r="D323" t="s">
         <v>7</v>
@@ -9834,7 +9834,7 @@
         <v>44</v>
       </c>
       <c r="C324">
-        <v>0.3804065056232418</v>
+        <v>0.3803089202655562</v>
       </c>
       <c r="D324" t="s">
         <v>7</v>
@@ -9851,7 +9851,7 @@
         <v>6</v>
       </c>
       <c r="C325">
-        <v>0.2356224070171135</v>
+        <v>0.2356707564721991</v>
       </c>
       <c r="D325" t="s">
         <v>7</v>
@@ -9868,7 +9868,7 @@
         <v>44</v>
       </c>
       <c r="C326">
-        <v>0.3413757341335001</v>
+        <v>0.3412742220266851</v>
       </c>
       <c r="D326" t="s">
         <v>7</v>
@@ -9885,7 +9885,7 @@
         <v>44</v>
       </c>
       <c r="C327">
-        <v>0.2987498098239033</v>
+        <v>0.2986428417011702</v>
       </c>
       <c r="D327" t="s">
         <v>7</v>
@@ -9902,7 +9902,7 @@
         <v>6</v>
       </c>
       <c r="C328">
-        <v>0.2904675178505768</v>
+        <v>0.2905223787049353</v>
       </c>
       <c r="D328" t="s">
         <v>7</v>
@@ -9919,7 +9919,7 @@
         <v>10</v>
       </c>
       <c r="C329">
-        <v>0.3122871886463582</v>
+        <v>0.312506700721436</v>
       </c>
       <c r="D329" t="s">
         <v>7</v>
@@ -9936,7 +9936,7 @@
         <v>15</v>
       </c>
       <c r="C330">
-        <v>0.3128123261310653</v>
+        <v>0.3126188384613264</v>
       </c>
       <c r="D330" t="s">
         <v>7</v>
@@ -9953,7 +9953,7 @@
         <v>10</v>
       </c>
       <c r="C331">
-        <v>0.3844592891868911</v>
+        <v>0.3846870667603166</v>
       </c>
       <c r="D331" t="s">
         <v>7</v>
@@ -9970,7 +9970,7 @@
         <v>10</v>
       </c>
       <c r="C332">
-        <v>0.3703700780292697</v>
+        <v>0.3705801004067801</v>
       </c>
       <c r="D332" t="s">
         <v>7</v>
@@ -9987,7 +9987,7 @@
         <v>6</v>
       </c>
       <c r="C333">
-        <v>0.497302666525147</v>
+        <v>0.497348018354944</v>
       </c>
       <c r="D333" t="s">
         <v>7</v>
@@ -10004,7 +10004,7 @@
         <v>15</v>
       </c>
       <c r="C334">
-        <v>0.3016694107581541</v>
+        <v>0.3014857413977949</v>
       </c>
       <c r="D334" t="s">
         <v>7</v>
@@ -10021,7 +10021,7 @@
         <v>15</v>
       </c>
       <c r="C335">
-        <v>0.35162694260983</v>
+        <v>0.3514610589405885</v>
       </c>
       <c r="D335" t="s">
         <v>7</v>
@@ -10038,7 +10038,7 @@
         <v>10</v>
       </c>
       <c r="C336">
-        <v>0.3371514135705274</v>
+        <v>0.3373635306006987</v>
       </c>
       <c r="D336" t="s">
         <v>7</v>
@@ -10055,7 +10055,7 @@
         <v>44</v>
       </c>
       <c r="C337">
-        <v>0.4090382703850409</v>
+        <v>0.408943161499743</v>
       </c>
       <c r="D337" t="s">
         <v>7</v>
@@ -10072,7 +10072,7 @@
         <v>6</v>
       </c>
       <c r="C338">
-        <v>0.3029896507449228</v>
+        <v>0.3030380819949579</v>
       </c>
       <c r="D338" t="s">
         <v>7</v>
@@ -10089,7 +10089,7 @@
         <v>15</v>
       </c>
       <c r="C339">
-        <v>0.4368703040143213</v>
+        <v>0.4366736494941975</v>
       </c>
       <c r="D339" t="s">
         <v>7</v>
@@ -10106,7 +10106,7 @@
         <v>15</v>
       </c>
       <c r="C340">
-        <v>0.3025823773188602</v>
+        <v>0.3024015870868682</v>
       </c>
       <c r="D340" t="s">
         <v>7</v>
@@ -10123,7 +10123,7 @@
         <v>6</v>
       </c>
       <c r="C341">
-        <v>0.3176665607114111</v>
+        <v>0.3177198319901043</v>
       </c>
       <c r="D341" t="s">
         <v>7</v>
@@ -10140,7 +10140,7 @@
         <v>10</v>
       </c>
       <c r="C342">
-        <v>0.2997969228385018</v>
+        <v>0.3000141563826407</v>
       </c>
       <c r="D342" t="s">
         <v>7</v>
@@ -10157,7 +10157,7 @@
         <v>10</v>
       </c>
       <c r="C343">
-        <v>0.4007831953457259</v>
+        <v>0.4009582202532314</v>
       </c>
       <c r="D343" t="s">
         <v>7</v>
@@ -10174,7 +10174,7 @@
         <v>10</v>
       </c>
       <c r="C344">
-        <v>0.2661619623036122</v>
+        <v>0.2663721765532291</v>
       </c>
       <c r="D344" t="s">
         <v>7</v>
@@ -10191,7 +10191,7 @@
         <v>6</v>
       </c>
       <c r="C345">
-        <v>0.3860233925178349</v>
+        <v>0.3860636618419953</v>
       </c>
       <c r="D345" t="s">
         <v>7</v>
@@ -10208,7 +10208,7 @@
         <v>10</v>
       </c>
       <c r="C346">
-        <v>0.3481786625922345</v>
+        <v>0.3483857149963979</v>
       </c>
       <c r="D346" t="s">
         <v>7</v>
@@ -10225,7 +10225,7 @@
         <v>15</v>
       </c>
       <c r="C347">
-        <v>0.347702657098271</v>
+        <v>0.3475255253597092</v>
       </c>
       <c r="D347" t="s">
         <v>7</v>
@@ -10242,7 +10242,7 @@
         <v>6</v>
       </c>
       <c r="C348">
-        <v>0.3720000885758864</v>
+        <v>0.3720502658018329</v>
       </c>
       <c r="D348" t="s">
         <v>7</v>
@@ -10259,7 +10259,7 @@
         <v>6</v>
       </c>
       <c r="C349">
-        <v>0.5197846889563319</v>
+        <v>0.5198386745070536</v>
       </c>
       <c r="D349" t="s">
         <v>7</v>
@@ -10276,7 +10276,7 @@
         <v>15</v>
       </c>
       <c r="C350">
-        <v>0.3488719914905639</v>
+        <v>0.3486752013252857</v>
       </c>
       <c r="D350" t="s">
         <v>7</v>
@@ -10293,7 +10293,7 @@
         <v>15</v>
       </c>
       <c r="C351">
-        <v>0.2176045848341975</v>
+        <v>0.217442240899363</v>
       </c>
       <c r="D351" t="s">
         <v>7</v>
@@ -10310,7 +10310,7 @@
         <v>15</v>
       </c>
       <c r="C352">
-        <v>0.3934393287978882</v>
+        <v>0.3932320209806808</v>
       </c>
       <c r="D352" t="s">
         <v>7</v>
@@ -10327,7 +10327,7 @@
         <v>10</v>
       </c>
       <c r="C353">
-        <v>0.3951806262299788</v>
+        <v>0.3953919142353359</v>
       </c>
       <c r="D353" t="s">
         <v>7</v>
@@ -10344,7 +10344,7 @@
         <v>6</v>
       </c>
       <c r="C354">
-        <v>0.3034596214015366</v>
+        <v>0.303499536305088</v>
       </c>
       <c r="D354" t="s">
         <v>7</v>
@@ -10361,7 +10361,7 @@
         <v>6</v>
       </c>
       <c r="C355">
-        <v>0.3986534145306802</v>
+        <v>0.3987051554164194</v>
       </c>
       <c r="D355" t="s">
         <v>7</v>
@@ -10378,7 +10378,7 @@
         <v>6</v>
       </c>
       <c r="C356">
-        <v>0.3380822780293535</v>
+        <v>0.3381291899673458</v>
       </c>
       <c r="D356" t="s">
         <v>7</v>
@@ -10395,7 +10395,7 @@
         <v>6</v>
       </c>
       <c r="C357">
-        <v>0.4245321215717899</v>
+        <v>0.4245897808027935</v>
       </c>
       <c r="D357" t="s">
         <v>7</v>
@@ -10412,7 +10412,7 @@
         <v>6</v>
       </c>
       <c r="C358">
-        <v>0.3665752255594775</v>
+        <v>0.3666211952182046</v>
       </c>
       <c r="D358" t="s">
         <v>7</v>
@@ -10429,7 +10429,7 @@
         <v>44</v>
       </c>
       <c r="C359">
-        <v>0.4356235926214044</v>
+        <v>0.4355407349635795</v>
       </c>
       <c r="D359" t="s">
         <v>7</v>
@@ -10446,7 +10446,7 @@
         <v>6</v>
       </c>
       <c r="C360">
-        <v>0.511203262600149</v>
+        <v>0.511257537550998</v>
       </c>
       <c r="D360" t="s">
         <v>7</v>
@@ -10463,7 +10463,7 @@
         <v>15</v>
       </c>
       <c r="C361">
-        <v>0.3053546882497893</v>
+        <v>0.3051866993622734</v>
       </c>
       <c r="D361" t="s">
         <v>7</v>
@@ -10480,7 +10480,7 @@
         <v>6</v>
       </c>
       <c r="C362">
-        <v>0.3823230052040431</v>
+        <v>0.3823718184112247</v>
       </c>
       <c r="D362" t="s">
         <v>7</v>
@@ -10497,7 +10497,7 @@
         <v>6</v>
       </c>
       <c r="C363">
-        <v>0.3045775689334734</v>
+        <v>0.3046224497891882</v>
       </c>
       <c r="D363" t="s">
         <v>7</v>
@@ -10514,7 +10514,7 @@
         <v>10</v>
       </c>
       <c r="C364">
-        <v>0.3294291407550929</v>
+        <v>0.3296222241898156</v>
       </c>
       <c r="D364" t="s">
         <v>7</v>
@@ -10531,7 +10531,7 @@
         <v>15</v>
       </c>
       <c r="C365">
-        <v>0.318595990836043</v>
+        <v>0.3184211602783286</v>
       </c>
       <c r="D365" t="s">
         <v>7</v>
@@ -10548,7 +10548,7 @@
         <v>15</v>
       </c>
       <c r="C366">
-        <v>0.2699595557704939</v>
+        <v>0.2697873317763119</v>
       </c>
       <c r="D366" t="s">
         <v>7</v>
@@ -10565,7 +10565,7 @@
         <v>6</v>
       </c>
       <c r="C367">
-        <v>0.3745690451921381</v>
+        <v>0.374632061843878</v>
       </c>
       <c r="D367" t="s">
         <v>7</v>
@@ -10582,7 +10582,7 @@
         <v>15</v>
       </c>
       <c r="C368">
-        <v>0.3571800647067478</v>
+        <v>0.357008469434623</v>
       </c>
       <c r="D368" t="s">
         <v>7</v>
@@ -10599,7 +10599,7 @@
         <v>6</v>
       </c>
       <c r="C369">
-        <v>0.5516073154480963</v>
+        <v>0.5516381386522433</v>
       </c>
       <c r="D369" t="s">
         <v>7</v>
@@ -10616,7 +10616,7 @@
         <v>15</v>
       </c>
       <c r="C370">
-        <v>0.3406151055685691</v>
+        <v>0.3404415045937713</v>
       </c>
       <c r="D370" t="s">
         <v>7</v>
@@ -10633,7 +10633,7 @@
         <v>6</v>
       </c>
       <c r="C371">
-        <v>0.4963157689670968</v>
+        <v>0.4963704759002959</v>
       </c>
       <c r="D371" t="s">
         <v>7</v>
@@ -10650,7 +10650,7 @@
         <v>6</v>
       </c>
       <c r="C372">
-        <v>0.3971596105542878</v>
+        <v>0.397204869546413</v>
       </c>
       <c r="D372" t="s">
         <v>7</v>
@@ -10667,7 +10667,7 @@
         <v>6</v>
       </c>
       <c r="C373">
-        <v>0.4619233287214545</v>
+        <v>0.461957710716437</v>
       </c>
       <c r="D373" t="s">
         <v>7</v>
@@ -10684,7 +10684,7 @@
         <v>6</v>
       </c>
       <c r="C374">
-        <v>0.5196878220721087</v>
+        <v>0.5197374230143047</v>
       </c>
       <c r="D374" t="s">
         <v>7</v>
@@ -10701,7 +10701,7 @@
         <v>6</v>
       </c>
       <c r="C375">
-        <v>0.4955066343623892</v>
+        <v>0.4955569226181429</v>
       </c>
       <c r="D375" t="s">
         <v>7</v>
@@ -10718,7 +10718,7 @@
         <v>15</v>
       </c>
       <c r="C376">
-        <v>0.3544426930154435</v>
+        <v>0.3542716523879114</v>
       </c>
       <c r="D376" t="s">
         <v>7</v>
@@ -10735,7 +10735,7 @@
         <v>6</v>
       </c>
       <c r="C377">
-        <v>0.5077492670741895</v>
+        <v>0.5077999644627443</v>
       </c>
       <c r="D377" t="s">
         <v>7</v>
@@ -10752,7 +10752,7 @@
         <v>6</v>
       </c>
       <c r="C378">
-        <v>0.333740518037141</v>
+        <v>0.3337866942832225</v>
       </c>
       <c r="D378" t="s">
         <v>7</v>
@@ -10769,7 +10769,7 @@
         <v>6</v>
       </c>
       <c r="C379">
-        <v>0.3460467747833555</v>
+        <v>0.3460903928409897</v>
       </c>
       <c r="D379" t="s">
         <v>7</v>
@@ -10786,7 +10786,7 @@
         <v>6</v>
       </c>
       <c r="C380">
-        <v>0.3959269424844753</v>
+        <v>0.3959765303746913</v>
       </c>
       <c r="D380" t="s">
         <v>7</v>
@@ -10803,7 +10803,7 @@
         <v>10</v>
       </c>
       <c r="C381">
-        <v>0.4932532901732231</v>
+        <v>0.493452434211698</v>
       </c>
       <c r="D381" t="s">
         <v>7</v>
@@ -10820,7 +10820,7 @@
         <v>6</v>
       </c>
       <c r="C382">
-        <v>0.3504624302153623</v>
+        <v>0.3505047890900696</v>
       </c>
       <c r="D382" t="s">
         <v>7</v>
@@ -10837,7 +10837,7 @@
         <v>10</v>
       </c>
       <c r="C383">
-        <v>0.3900461620724764</v>
+        <v>0.3902415881706195</v>
       </c>
       <c r="D383" t="s">
         <v>7</v>
@@ -10854,7 +10854,7 @@
         <v>44</v>
       </c>
       <c r="C384">
-        <v>0.4180858424687868</v>
+        <v>0.4180015904506967</v>
       </c>
       <c r="D384" t="s">
         <v>7</v>
@@ -10871,7 +10871,7 @@
         <v>6</v>
       </c>
       <c r="C385">
-        <v>0.4247957748907084</v>
+        <v>0.4248477897702412</v>
       </c>
       <c r="D385" t="s">
         <v>7</v>
@@ -10888,7 +10888,7 @@
         <v>10</v>
       </c>
       <c r="C386">
-        <v>0.3050672215164482</v>
+        <v>0.3052823568529727</v>
       </c>
       <c r="D386" t="s">
         <v>7</v>
@@ -10905,7 +10905,7 @@
         <v>10</v>
       </c>
       <c r="C387">
-        <v>0.4316418949826951</v>
+        <v>0.4318048580190839</v>
       </c>
       <c r="D387" t="s">
         <v>7</v>
@@ -10922,7 +10922,7 @@
         <v>10</v>
       </c>
       <c r="C388">
-        <v>0.2683457678163202</v>
+        <v>0.2685319197903051</v>
       </c>
       <c r="D388" t="s">
         <v>7</v>
@@ -10939,7 +10939,7 @@
         <v>6</v>
       </c>
       <c r="C389">
-        <v>0.3819918884232045</v>
+        <v>0.3820400523138598</v>
       </c>
       <c r="D389" t="s">
         <v>7</v>
@@ -10956,7 +10956,7 @@
         <v>15</v>
       </c>
       <c r="C390">
-        <v>0.3308178730906043</v>
+        <v>0.3306157527071439</v>
       </c>
       <c r="D390" t="s">
         <v>7</v>
@@ -10973,7 +10973,7 @@
         <v>15</v>
       </c>
       <c r="C391">
-        <v>0.3456669499888304</v>
+        <v>0.3454813205763599</v>
       </c>
       <c r="D391" t="s">
         <v>7</v>
@@ -10990,7 +10990,7 @@
         <v>10</v>
       </c>
       <c r="C392">
-        <v>0.3476963549269781</v>
+        <v>0.3479099032320183</v>
       </c>
       <c r="D392" t="s">
         <v>7</v>
@@ -11007,7 +11007,7 @@
         <v>10</v>
       </c>
       <c r="C393">
-        <v>0.4032055482890283</v>
+        <v>0.4034050299002815</v>
       </c>
       <c r="D393" t="s">
         <v>7</v>
@@ -11024,7 +11024,7 @@
         <v>15</v>
       </c>
       <c r="C394">
-        <v>0.3655351157687693</v>
+        <v>0.3653336418172703</v>
       </c>
       <c r="D394" t="s">
         <v>7</v>
@@ -11041,7 +11041,7 @@
         <v>10</v>
       </c>
       <c r="C395">
-        <v>0.4377684078431449</v>
+        <v>0.4379517495927557</v>
       </c>
       <c r="D395" t="s">
         <v>7</v>
@@ -11058,7 +11058,7 @@
         <v>6</v>
       </c>
       <c r="C396">
-        <v>0.4089714416600206</v>
+        <v>0.4090192618195433</v>
       </c>
       <c r="D396" t="s">
         <v>7</v>
@@ -11075,7 +11075,7 @@
         <v>10</v>
       </c>
       <c r="C397">
-        <v>0.3634638456785183</v>
+        <v>0.3636680339565198</v>
       </c>
       <c r="D397" t="s">
         <v>7</v>
@@ -11092,7 +11092,7 @@
         <v>6</v>
       </c>
       <c r="C398">
-        <v>0.5259846379554584</v>
+        <v>0.5260456120980714</v>
       </c>
       <c r="D398" t="s">
         <v>7</v>
@@ -11109,7 +11109,7 @@
         <v>15</v>
       </c>
       <c r="C399">
-        <v>0.3529206668680227</v>
+        <v>0.3527595112984498</v>
       </c>
       <c r="D399" t="s">
         <v>7</v>
@@ -11126,7 +11126,7 @@
         <v>6</v>
       </c>
       <c r="C400">
-        <v>0.3551220776514941</v>
+        <v>0.3551665666922437</v>
       </c>
       <c r="D400" t="s">
         <v>7</v>
@@ -11143,7 +11143,7 @@
         <v>15</v>
       </c>
       <c r="C401">
-        <v>0.4386358965097541</v>
+        <v>0.4384568604560116</v>
       </c>
       <c r="D401" t="s">
         <v>7</v>
@@ -11160,7 +11160,7 @@
         <v>6</v>
       </c>
       <c r="C402">
-        <v>0.4168266000497324</v>
+        <v>0.4168810954633874</v>
       </c>
       <c r="D402" t="s">
         <v>7</v>
@@ -11177,7 +11177,7 @@
         <v>6</v>
       </c>
       <c r="C403">
-        <v>0.3189583322935164</v>
+        <v>0.3190015833512393</v>
       </c>
       <c r="D403" t="s">
         <v>7</v>
@@ -11194,7 +11194,7 @@
         <v>10</v>
       </c>
       <c r="C404">
-        <v>0.3439018526498435</v>
+        <v>0.3441329600567073</v>
       </c>
       <c r="D404" t="s">
         <v>7</v>
@@ -11211,7 +11211,7 @@
         <v>6</v>
       </c>
       <c r="C405">
-        <v>0.4450263281443648</v>
+        <v>0.4450573736839637</v>
       </c>
       <c r="D405" t="s">
         <v>7</v>
@@ -11228,7 +11228,7 @@
         <v>6</v>
       </c>
       <c r="C406">
-        <v>0.4328416846778186</v>
+        <v>0.4328555701340731</v>
       </c>
       <c r="D406" t="s">
         <v>7</v>
@@ -11245,7 +11245,7 @@
         <v>6</v>
       </c>
       <c r="C407">
-        <v>0.4180981905031739</v>
+        <v>0.4181517975421166</v>
       </c>
       <c r="D407" t="s">
         <v>7</v>
@@ -11262,7 +11262,7 @@
         <v>6</v>
       </c>
       <c r="C408">
-        <v>0.4875012093812901</v>
+        <v>0.487547385831099</v>
       </c>
       <c r="D408" t="s">
         <v>7</v>
@@ -11279,7 +11279,7 @@
         <v>6</v>
       </c>
       <c r="C409">
-        <v>0.505176461975258</v>
+        <v>0.5052388834134643</v>
       </c>
       <c r="D409" t="s">
         <v>7</v>
@@ -11296,7 +11296,7 @@
         <v>15</v>
       </c>
       <c r="C410">
-        <v>0.2905111540672021</v>
+        <v>0.2903387713155478</v>
       </c>
       <c r="D410" t="s">
         <v>7</v>
@@ -11313,7 +11313,7 @@
         <v>6</v>
       </c>
       <c r="C411">
-        <v>0.3432368747437616</v>
+        <v>0.3432776308862663</v>
       </c>
       <c r="D411" t="s">
         <v>7</v>
@@ -11330,7 +11330,7 @@
         <v>6</v>
       </c>
       <c r="C412">
-        <v>0.4537856218305445</v>
+        <v>0.4538521238513653</v>
       </c>
       <c r="D412" t="s">
         <v>7</v>
@@ -11347,7 +11347,7 @@
         <v>6</v>
       </c>
       <c r="C413">
-        <v>0.2813769465039372</v>
+        <v>0.2814185038459897</v>
       </c>
       <c r="D413" t="s">
         <v>7</v>
@@ -11364,7 +11364,7 @@
         <v>15</v>
       </c>
       <c r="C414">
-        <v>0.313160858620894</v>
+        <v>0.3129865122412654</v>
       </c>
       <c r="D414" t="s">
         <v>7</v>
@@ -11381,7 +11381,7 @@
         <v>15</v>
       </c>
       <c r="C415">
-        <v>0.3599111410924816</v>
+        <v>0.3597455872842099</v>
       </c>
       <c r="D415" t="s">
         <v>7</v>
@@ -11398,7 +11398,7 @@
         <v>15</v>
       </c>
       <c r="C416">
-        <v>0.4384334471231472</v>
+        <v>0.4382866180182896</v>
       </c>
       <c r="D416" t="s">
         <v>7</v>
@@ -11415,7 +11415,7 @@
         <v>6</v>
       </c>
       <c r="C417">
-        <v>0.2988175555448305</v>
+        <v>0.2988721124135199</v>
       </c>
       <c r="D417" t="s">
         <v>7</v>
@@ -11432,7 +11432,7 @@
         <v>10</v>
       </c>
       <c r="C418">
-        <v>0.3330670421980722</v>
+        <v>0.3332791719098562</v>
       </c>
       <c r="D418" t="s">
         <v>7</v>
@@ -11449,7 +11449,7 @@
         <v>15</v>
       </c>
       <c r="C419">
-        <v>0.3916615964921287</v>
+        <v>0.391458790501867</v>
       </c>
       <c r="D419" t="s">
         <v>7</v>
@@ -11466,7 +11466,7 @@
         <v>44</v>
       </c>
       <c r="C420">
-        <v>0.4274749604940434</v>
+        <v>0.4273989720851753</v>
       </c>
       <c r="D420" t="s">
         <v>7</v>
@@ -11483,7 +11483,7 @@
         <v>44</v>
       </c>
       <c r="C421">
-        <v>0.4298457874893293</v>
+        <v>0.4297521206349555</v>
       </c>
       <c r="D421" t="s">
         <v>7</v>
@@ -11500,7 +11500,7 @@
         <v>6</v>
       </c>
       <c r="C422">
-        <v>0.3902937783065749</v>
+        <v>0.3903438258184407</v>
       </c>
       <c r="D422" t="s">
         <v>7</v>
@@ -11517,7 +11517,7 @@
         <v>44</v>
       </c>
       <c r="C423">
-        <v>0.4062060854531462</v>
+        <v>0.4061112800315016</v>
       </c>
       <c r="D423" t="s">
         <v>7</v>
@@ -11534,7 +11534,7 @@
         <v>10</v>
       </c>
       <c r="C424">
-        <v>0.3609457515560782</v>
+        <v>0.3611705179549649</v>
       </c>
       <c r="D424" t="s">
         <v>7</v>
@@ -11551,7 +11551,7 @@
         <v>6</v>
       </c>
       <c r="C425">
-        <v>0.3882934835187191</v>
+        <v>0.3883419777017316</v>
       </c>
       <c r="D425" t="s">
         <v>7</v>
@@ -11568,7 +11568,7 @@
         <v>15</v>
       </c>
       <c r="C426">
-        <v>0.3563625995780869</v>
+        <v>0.3561982753949714</v>
       </c>
       <c r="D426" t="s">
         <v>7</v>
@@ -11585,7 +11585,7 @@
         <v>6</v>
       </c>
       <c r="C427">
-        <v>0.3059492928211993</v>
+        <v>0.3060010209015112</v>
       </c>
       <c r="D427" t="s">
         <v>7</v>
@@ -11602,7 +11602,7 @@
         <v>6</v>
       </c>
       <c r="C428">
-        <v>0.2954483975324781</v>
+        <v>0.2955010183358314</v>
       </c>
       <c r="D428" t="s">
         <v>7</v>
@@ -11619,7 +11619,7 @@
         <v>10</v>
       </c>
       <c r="C429">
-        <v>0.372029639199507</v>
+        <v>0.3722274003195551</v>
       </c>
       <c r="D429" t="s">
         <v>7</v>
@@ -11636,7 +11636,7 @@
         <v>6</v>
       </c>
       <c r="C430">
-        <v>0.3883746439588164</v>
+        <v>0.3884275709829573</v>
       </c>
       <c r="D430" t="s">
         <v>7</v>
@@ -11653,7 +11653,7 @@
         <v>6</v>
       </c>
       <c r="C431">
-        <v>0.3096181918101741</v>
+        <v>0.3096450925963197</v>
       </c>
       <c r="D431" t="s">
         <v>7</v>
@@ -11670,7 +11670,7 @@
         <v>15</v>
       </c>
       <c r="C432">
-        <v>0.3504523320555997</v>
+        <v>0.3502839273117483</v>
       </c>
       <c r="D432" t="s">
         <v>7</v>
@@ -11687,7 +11687,7 @@
         <v>10</v>
       </c>
       <c r="C433">
-        <v>0.303685797671997</v>
+        <v>0.3038932546475513</v>
       </c>
       <c r="D433" t="s">
         <v>7</v>
@@ -11704,7 +11704,7 @@
         <v>15</v>
       </c>
       <c r="C434">
-        <v>0.3616277084661318</v>
+        <v>0.3614518649233464</v>
       </c>
       <c r="D434" t="s">
         <v>7</v>
@@ -11721,7 +11721,7 @@
         <v>10</v>
       </c>
       <c r="C435">
-        <v>0.4112036072114286</v>
+        <v>0.4114018918154311</v>
       </c>
       <c r="D435" t="s">
         <v>7</v>
@@ -11738,7 +11738,7 @@
         <v>15</v>
       </c>
       <c r="C436">
-        <v>0.3544849172056468</v>
+        <v>0.3543190554741206</v>
       </c>
       <c r="D436" t="s">
         <v>7</v>
@@ -11755,7 +11755,7 @@
         <v>10</v>
       </c>
       <c r="C437">
-        <v>0.3414222253996815</v>
+        <v>0.3416394008431627</v>
       </c>
       <c r="D437" t="s">
         <v>7</v>
@@ -11772,7 +11772,7 @@
         <v>15</v>
       </c>
       <c r="C438">
-        <v>0.3574003227915734</v>
+        <v>0.3572074610477305</v>
       </c>
       <c r="D438" t="s">
         <v>7</v>
@@ -11789,7 +11789,7 @@
         <v>6</v>
       </c>
       <c r="C439">
-        <v>0.4166555048704128</v>
+        <v>0.4167029258630305</v>
       </c>
       <c r="D439" t="s">
         <v>7</v>
@@ -11806,7 +11806,7 @@
         <v>10</v>
       </c>
       <c r="C440">
-        <v>0.3330771968673975</v>
+        <v>0.3332813404045279</v>
       </c>
       <c r="D440" t="s">
         <v>7</v>
@@ -11823,7 +11823,7 @@
         <v>6</v>
       </c>
       <c r="C441">
-        <v>0.3600103359074219</v>
+        <v>0.3600613893972875</v>
       </c>
       <c r="D441" t="s">
         <v>7</v>
@@ -11840,7 +11840,7 @@
         <v>6</v>
       </c>
       <c r="C442">
-        <v>0.3316003174318093</v>
+        <v>0.3316360817217719</v>
       </c>
       <c r="D442" t="s">
         <v>7</v>
@@ -11857,7 +11857,7 @@
         <v>15</v>
       </c>
       <c r="C443">
-        <v>0.3043549905116072</v>
+        <v>0.304186431786743</v>
       </c>
       <c r="D443" t="s">
         <v>7</v>
@@ -11874,7 +11874,7 @@
         <v>10</v>
       </c>
       <c r="C444">
-        <v>0.3654775085193007</v>
+        <v>0.3657043595403644</v>
       </c>
       <c r="D444" t="s">
         <v>7</v>
@@ -11891,7 +11891,7 @@
         <v>6</v>
       </c>
       <c r="C445">
-        <v>0.3847944898454261</v>
+        <v>0.3848088269615906</v>
       </c>
       <c r="D445" t="s">
         <v>7</v>
@@ -11908,7 +11908,7 @@
         <v>44</v>
       </c>
       <c r="C446">
-        <v>0.3234248568518121</v>
+        <v>0.3233198989418533</v>
       </c>
       <c r="D446" t="s">
         <v>7</v>
@@ -11925,7 +11925,7 @@
         <v>6</v>
       </c>
       <c r="C447">
-        <v>0.2951646403154087</v>
+        <v>0.2952132251665474</v>
       </c>
       <c r="D447" t="s">
         <v>7</v>
@@ -11942,7 +11942,7 @@
         <v>6</v>
       </c>
       <c r="C448">
-        <v>0.3985067210399059</v>
+        <v>0.3985542417230479</v>
       </c>
       <c r="D448" t="s">
         <v>7</v>
@@ -11959,7 +11959,7 @@
         <v>6</v>
       </c>
       <c r="C449">
-        <v>0.4295791654576813</v>
+        <v>0.4296286049173068</v>
       </c>
       <c r="D449" t="s">
         <v>7</v>
@@ -11976,7 +11976,7 @@
         <v>44</v>
       </c>
       <c r="C450">
-        <v>0.3874648503390166</v>
+        <v>0.3873663032938461</v>
       </c>
       <c r="D450" t="s">
         <v>7</v>
@@ -11993,7 +11993,7 @@
         <v>44</v>
       </c>
       <c r="C451">
-        <v>0.3672442893196977</v>
+        <v>0.3671422971092899</v>
       </c>
       <c r="D451" t="s">
         <v>7</v>
@@ -12010,7 +12010,7 @@
         <v>6</v>
       </c>
       <c r="C452">
-        <v>0.360832537724569</v>
+        <v>0.3608788208664604</v>
       </c>
       <c r="D452" t="s">
         <v>7</v>
@@ -12027,7 +12027,7 @@
         <v>10</v>
       </c>
       <c r="C453">
-        <v>0.3814021530360474</v>
+        <v>0.3816133666747105</v>
       </c>
       <c r="D453" t="s">
         <v>7</v>
@@ -12044,7 +12044,7 @@
         <v>15</v>
       </c>
       <c r="C454">
-        <v>0.2858882224639135</v>
+        <v>0.2857180383288314</v>
       </c>
       <c r="D454" t="s">
         <v>7</v>
@@ -12061,7 +12061,7 @@
         <v>10</v>
       </c>
       <c r="C455">
-        <v>0.376066871198504</v>
+        <v>0.3762870842286603</v>
       </c>
       <c r="D455" t="s">
         <v>7</v>
@@ -12078,7 +12078,7 @@
         <v>6</v>
       </c>
       <c r="C456">
-        <v>0.411688009008557</v>
+        <v>0.4117523115620636</v>
       </c>
       <c r="D456" t="s">
         <v>7</v>
@@ -12095,7 +12095,7 @@
         <v>15</v>
       </c>
       <c r="C457">
-        <v>0.3563520861066659</v>
+        <v>0.356169324790543</v>
       </c>
       <c r="D457" t="s">
         <v>7</v>
@@ -12112,7 +12112,7 @@
         <v>6</v>
       </c>
       <c r="C458">
-        <v>0.3647467522538397</v>
+        <v>0.3647580188805091</v>
       </c>
       <c r="D458" t="s">
         <v>7</v>
@@ -12129,7 +12129,7 @@
         <v>6</v>
       </c>
       <c r="C459">
-        <v>0.4162889594928032</v>
+        <v>0.4163337407601138</v>
       </c>
       <c r="D459" t="s">
         <v>7</v>
@@ -12146,7 +12146,7 @@
         <v>6</v>
       </c>
       <c r="C460">
-        <v>0.3665363555588175</v>
+        <v>0.3665605949461752</v>
       </c>
       <c r="D460" t="s">
         <v>7</v>
@@ -12163,7 +12163,7 @@
         <v>10</v>
       </c>
       <c r="C461">
-        <v>0.3303211577753296</v>
+        <v>0.3305016194009775</v>
       </c>
       <c r="D461" t="s">
         <v>7</v>
@@ -12180,7 +12180,7 @@
         <v>6</v>
       </c>
       <c r="C462">
-        <v>0.3529202000205535</v>
+        <v>0.3529671050984876</v>
       </c>
       <c r="D462" t="s">
         <v>7</v>
@@ -12197,7 +12197,7 @@
         <v>10</v>
       </c>
       <c r="C463">
-        <v>0.3264466458215104</v>
+        <v>0.3266646652790628</v>
       </c>
       <c r="D463" t="s">
         <v>7</v>
@@ -12214,7 +12214,7 @@
         <v>6</v>
       </c>
       <c r="C464">
-        <v>0.4502823927568196</v>
+        <v>0.4503373684049048</v>
       </c>
       <c r="D464" t="s">
         <v>7</v>
@@ -12231,7 +12231,7 @@
         <v>44</v>
       </c>
       <c r="C465">
-        <v>0.3291437608617064</v>
+        <v>0.3290429438850233</v>
       </c>
       <c r="D465" t="s">
         <v>7</v>
@@ -12248,7 +12248,7 @@
         <v>6</v>
       </c>
       <c r="C466">
-        <v>0.5606403904315983</v>
+        <v>0.5606726212320018</v>
       </c>
       <c r="D466" t="s">
         <v>7</v>
@@ -12265,7 +12265,7 @@
         <v>6</v>
       </c>
       <c r="C467">
-        <v>0.5097555710745921</v>
+        <v>0.5098024472520204</v>
       </c>
       <c r="D467" t="s">
         <v>7</v>
@@ -12282,7 +12282,7 @@
         <v>6</v>
       </c>
       <c r="C468">
-        <v>0.4133916260184147</v>
+        <v>0.4134466886524675</v>
       </c>
       <c r="D468" t="s">
         <v>7</v>
@@ -12299,7 +12299,7 @@
         <v>15</v>
       </c>
       <c r="C469">
-        <v>0.2981015271936502</v>
+        <v>0.2979319885624729</v>
       </c>
       <c r="D469" t="s">
         <v>7</v>
@@ -12316,7 +12316,7 @@
         <v>6</v>
       </c>
       <c r="C470">
-        <v>0.3136561122541821</v>
+        <v>0.3137125852121121</v>
       </c>
       <c r="D470" t="s">
         <v>7</v>
@@ -12333,7 +12333,7 @@
         <v>44</v>
       </c>
       <c r="C471">
-        <v>0.2953341017546705</v>
+        <v>0.2952206386425444</v>
       </c>
       <c r="D471" t="s">
         <v>7</v>
@@ -12350,7 +12350,7 @@
         <v>15</v>
       </c>
       <c r="C472">
-        <v>0.3118730968811864</v>
+        <v>0.3117070949850211</v>
       </c>
       <c r="D472" t="s">
         <v>7</v>
@@ -12367,7 +12367,7 @@
         <v>10</v>
       </c>
       <c r="C473">
-        <v>0.325257301109685</v>
+        <v>0.3254560714312048</v>
       </c>
       <c r="D473" t="s">
         <v>7</v>
@@ -12384,7 +12384,7 @@
         <v>10</v>
       </c>
       <c r="C474">
-        <v>0.3716456745646817</v>
+        <v>0.37183721945543</v>
       </c>
       <c r="D474" t="s">
         <v>7</v>
@@ -12401,7 +12401,7 @@
         <v>6</v>
       </c>
       <c r="C475">
-        <v>0.3575972493186278</v>
+        <v>0.3576367117469069</v>
       </c>
       <c r="D475" t="s">
         <v>7</v>
@@ -12418,7 +12418,7 @@
         <v>6</v>
       </c>
       <c r="C476">
-        <v>0.3517216850170807</v>
+        <v>0.351764894464824</v>
       </c>
       <c r="D476" t="s">
         <v>7</v>
@@ -12435,7 +12435,7 @@
         <v>10</v>
       </c>
       <c r="C477">
-        <v>0.3498048564236744</v>
+        <v>0.3499917852268019</v>
       </c>
       <c r="D477" t="s">
         <v>7</v>
@@ -12452,7 +12452,7 @@
         <v>6</v>
       </c>
       <c r="C478">
-        <v>0.4174539949151669</v>
+        <v>0.41749621094902</v>
       </c>
       <c r="D478" t="s">
         <v>7</v>
@@ -12469,7 +12469,7 @@
         <v>44</v>
       </c>
       <c r="C479">
-        <v>0.3856595671844311</v>
+        <v>0.3855545762839881</v>
       </c>
       <c r="D479" t="s">
         <v>7</v>
@@ -12486,7 +12486,7 @@
         <v>6</v>
       </c>
       <c r="C480">
-        <v>0.4951659625858403</v>
+        <v>0.4952122438038706</v>
       </c>
       <c r="D480" t="s">
         <v>7</v>
@@ -12503,7 +12503,7 @@
         <v>44</v>
       </c>
       <c r="C481">
-        <v>0.3436271924422239</v>
+        <v>0.3435296073868833</v>
       </c>
       <c r="D481" t="s">
         <v>7</v>
@@ -12520,7 +12520,7 @@
         <v>10</v>
       </c>
       <c r="C482">
-        <v>0.2957016847531889</v>
+        <v>0.2959151003079767</v>
       </c>
       <c r="D482" t="s">
         <v>7</v>
@@ -12537,7 +12537,7 @@
         <v>10</v>
       </c>
       <c r="C483">
-        <v>0.3254063779402611</v>
+        <v>0.3256314313617998</v>
       </c>
       <c r="D483" t="s">
         <v>7</v>
@@ -12554,7 +12554,7 @@
         <v>44</v>
       </c>
       <c r="C484">
-        <v>0.3399620469405203</v>
+        <v>0.3398541637547737</v>
       </c>
       <c r="D484" t="s">
         <v>7</v>
@@ -12571,7 +12571,7 @@
         <v>15</v>
       </c>
       <c r="C485">
-        <v>0.365038594226413</v>
+        <v>0.3648369109132513</v>
       </c>
       <c r="D485" t="s">
         <v>7</v>
@@ -12588,7 +12588,7 @@
         <v>15</v>
       </c>
       <c r="C486">
-        <v>0.3962088606378225</v>
+        <v>0.3960183116275673</v>
       </c>
       <c r="D486" t="s">
         <v>7</v>
@@ -12605,7 +12605,7 @@
         <v>44</v>
       </c>
       <c r="C487">
-        <v>0.4143946877531354</v>
+        <v>0.4143104321378043</v>
       </c>
       <c r="D487" t="s">
         <v>7</v>
@@ -12622,7 +12622,7 @@
         <v>10</v>
       </c>
       <c r="C488">
-        <v>0.3077846537894847</v>
+        <v>0.307994996470679</v>
       </c>
       <c r="D488" t="s">
         <v>7</v>
@@ -12639,7 +12639,7 @@
         <v>6</v>
       </c>
       <c r="C489">
-        <v>0.5248876229685931</v>
+        <v>0.5249089351409065</v>
       </c>
       <c r="D489" t="s">
         <v>7</v>
@@ -12656,7 +12656,7 @@
         <v>15</v>
       </c>
       <c r="C490">
-        <v>0.3331479638797427</v>
+        <v>0.3329815996494197</v>
       </c>
       <c r="D490" t="s">
         <v>7</v>
@@ -12673,7 +12673,7 @@
         <v>6</v>
       </c>
       <c r="C491">
-        <v>0.316825920549301</v>
+        <v>0.3168825123747923</v>
       </c>
       <c r="D491" t="s">
         <v>7</v>
@@ -12690,7 +12690,7 @@
         <v>6</v>
       </c>
       <c r="C492">
-        <v>0.5110927555767798</v>
+        <v>0.5110957064584629</v>
       </c>
       <c r="D492" t="s">
         <v>7</v>
@@ -12707,7 +12707,7 @@
         <v>6</v>
       </c>
       <c r="C493">
-        <v>0.3234779171379263</v>
+        <v>0.323527375830341</v>
       </c>
       <c r="D493" t="s">
         <v>7</v>
@@ -12724,7 +12724,7 @@
         <v>10</v>
       </c>
       <c r="C494">
-        <v>0.3301090573585425</v>
+        <v>0.3303449538684555</v>
       </c>
       <c r="D494" t="s">
         <v>7</v>
@@ -12741,7 +12741,7 @@
         <v>44</v>
       </c>
       <c r="C495">
-        <v>0.4885001432635215</v>
+        <v>0.4884329530713543</v>
       </c>
       <c r="D495" t="s">
         <v>7</v>
@@ -12758,7 +12758,7 @@
         <v>6</v>
       </c>
       <c r="C496">
-        <v>0.5183441783769024</v>
+        <v>0.5183991529202365</v>
       </c>
       <c r="D496" t="s">
         <v>7</v>
@@ -12775,7 +12775,7 @@
         <v>10</v>
       </c>
       <c r="C497">
-        <v>0.3792003975282267</v>
+        <v>0.3793927963972554</v>
       </c>
       <c r="D497" t="s">
         <v>7</v>
@@ -12792,7 +12792,7 @@
         <v>6</v>
       </c>
       <c r="C498">
-        <v>0.6856780407949887</v>
+        <v>0.6857203333963072</v>
       </c>
       <c r="D498" t="s">
         <v>7</v>
@@ -12809,7 +12809,7 @@
         <v>15</v>
       </c>
       <c r="C499">
-        <v>0.3417685369373382</v>
+        <v>0.3415934167334314</v>
       </c>
       <c r="D499" t="s">
         <v>7</v>
@@ -12826,7 +12826,7 @@
         <v>6</v>
       </c>
       <c r="C500">
-        <v>0.4567176251519505</v>
+        <v>0.4567329461978528</v>
       </c>
       <c r="D500" t="s">
         <v>7</v>
@@ -12843,7 +12843,7 @@
         <v>15</v>
       </c>
       <c r="C501">
-        <v>0.4116508942026493</v>
+        <v>0.4114613320242083</v>
       </c>
       <c r="D501" t="s">
         <v>7</v>
@@ -12860,7 +12860,7 @@
         <v>6</v>
       </c>
       <c r="C502">
-        <v>0.5999193392983247</v>
+        <v>0.5999147020206985</v>
       </c>
       <c r="D502" t="s">
         <v>7</v>
@@ -12877,7 +12877,7 @@
         <v>15</v>
       </c>
       <c r="C503">
-        <v>0.3552854428830499</v>
+        <v>0.3550800494949607</v>
       </c>
       <c r="D503" t="s">
         <v>7</v>
@@ -12894,7 +12894,7 @@
         <v>15</v>
       </c>
       <c r="C504">
-        <v>0.3267164136648908</v>
+        <v>0.3265369308939668</v>
       </c>
       <c r="D504" t="s">
         <v>7</v>
@@ -12911,7 +12911,7 @@
         <v>6</v>
       </c>
       <c r="C505">
-        <v>0.4708142439296356</v>
+        <v>0.4708503177092222</v>
       </c>
       <c r="D505" t="s">
         <v>7</v>
@@ -12928,7 +12928,7 @@
         <v>15</v>
       </c>
       <c r="C506">
-        <v>0.4837899268928352</v>
+        <v>0.4836087917785527</v>
       </c>
       <c r="D506" t="s">
         <v>7</v>
@@ -12945,7 +12945,7 @@
         <v>6</v>
       </c>
       <c r="C507">
-        <v>0.35287160294067</v>
+        <v>0.3529142349474733</v>
       </c>
       <c r="D507" t="s">
         <v>7</v>
@@ -12962,7 +12962,7 @@
         <v>15</v>
       </c>
       <c r="C508">
-        <v>0.3255222347943177</v>
+        <v>0.3253367213824494</v>
       </c>
       <c r="D508" t="s">
         <v>7</v>
@@ -12979,7 +12979,7 @@
         <v>10</v>
       </c>
       <c r="C509">
-        <v>0.497865832126888</v>
+        <v>0.4980679944269725</v>
       </c>
       <c r="D509" t="s">
         <v>7</v>
@@ -12996,7 +12996,7 @@
         <v>10</v>
       </c>
       <c r="C510">
-        <v>0.383196896333221</v>
+        <v>0.3833766997888259</v>
       </c>
       <c r="D510" t="s">
         <v>7</v>
@@ -13013,7 +13013,7 @@
         <v>44</v>
       </c>
       <c r="C511">
-        <v>0.3205450730910451</v>
+        <v>0.3204460988599924</v>
       </c>
       <c r="D511" t="s">
         <v>7</v>
@@ -13030,7 +13030,7 @@
         <v>6</v>
       </c>
       <c r="C512">
-        <v>0.3217168188825872</v>
+        <v>0.3217603566382825</v>
       </c>
       <c r="D512" t="s">
         <v>7</v>
@@ -13047,7 +13047,7 @@
         <v>6</v>
       </c>
       <c r="C513">
-        <v>0.3901969622588061</v>
+        <v>0.3902119249822659</v>
       </c>
       <c r="D513" t="s">
         <v>7</v>
@@ -13064,7 +13064,7 @@
         <v>44</v>
       </c>
       <c r="C514">
-        <v>0.3713388344733529</v>
+        <v>0.3712445706303139</v>
       </c>
       <c r="D514" t="s">
         <v>7</v>
@@ -13081,7 +13081,7 @@
         <v>6</v>
       </c>
       <c r="C515">
-        <v>0.5286874371227759</v>
+        <v>0.5287324782597118</v>
       </c>
       <c r="D515" t="s">
         <v>7</v>
@@ -13098,7 +13098,7 @@
         <v>6</v>
       </c>
       <c r="C516">
-        <v>0.317596827468401</v>
+        <v>0.3176471387892337</v>
       </c>
       <c r="D516" t="s">
         <v>7</v>
@@ -13115,7 +13115,7 @@
         <v>15</v>
       </c>
       <c r="C517">
-        <v>0.3480709747363355</v>
+        <v>0.3478961233331934</v>
       </c>
       <c r="D517" t="s">
         <v>7</v>
@@ -13132,7 +13132,7 @@
         <v>10</v>
       </c>
       <c r="C518">
-        <v>0.3385597732406303</v>
+        <v>0.3387869634587967</v>
       </c>
       <c r="D518" t="s">
         <v>7</v>
@@ -13149,7 +13149,7 @@
         <v>44</v>
       </c>
       <c r="C519">
-        <v>0.48764200902269</v>
+        <v>0.4875783557439063</v>
       </c>
       <c r="D519" t="s">
         <v>7</v>
@@ -13166,7 +13166,7 @@
         <v>15</v>
       </c>
       <c r="C520">
-        <v>0.3300766972029622</v>
+        <v>0.3298999353132537</v>
       </c>
       <c r="D520" t="s">
         <v>7</v>
@@ -13183,7 +13183,7 @@
         <v>10</v>
       </c>
       <c r="C521">
-        <v>0.3320321697218283</v>
+        <v>0.3322287326961316</v>
       </c>
       <c r="D521" t="s">
         <v>7</v>
@@ -13200,7 +13200,7 @@
         <v>15</v>
       </c>
       <c r="C522">
-        <v>0.3429715529495362</v>
+        <v>0.3427706467721077</v>
       </c>
       <c r="D522" t="s">
         <v>7</v>
@@ -13217,7 +13217,7 @@
         <v>6</v>
       </c>
       <c r="C523">
-        <v>0.4651644906802223</v>
+        <v>0.4652202857578324</v>
       </c>
       <c r="D523" t="s">
         <v>7</v>
@@ -13234,7 +13234,7 @@
         <v>6</v>
       </c>
       <c r="C524">
-        <v>0.3208111038048009</v>
+        <v>0.320857136311452</v>
       </c>
       <c r="D524" t="s">
         <v>7</v>
@@ -13251,7 +13251,7 @@
         <v>44</v>
       </c>
       <c r="C525">
-        <v>0.3722295737069574</v>
+        <v>0.372139507891448</v>
       </c>
       <c r="D525" t="s">
         <v>7</v>
@@ -13268,7 +13268,7 @@
         <v>44</v>
       </c>
       <c r="C526">
-        <v>0.4712523466236962</v>
+        <v>0.4711688933211267</v>
       </c>
       <c r="D526" t="s">
         <v>7</v>
@@ -13285,7 +13285,7 @@
         <v>10</v>
       </c>
       <c r="C527">
-        <v>0.4086306089652295</v>
+        <v>0.4088283547231956</v>
       </c>
       <c r="D527" t="s">
         <v>7</v>
@@ -13302,7 +13302,7 @@
         <v>6</v>
       </c>
       <c r="C528">
-        <v>0.472278420676218</v>
+        <v>0.4723099078950535</v>
       </c>
       <c r="D528" t="s">
         <v>7</v>
@@ -13319,7 +13319,7 @@
         <v>10</v>
       </c>
       <c r="C529">
-        <v>0.3458407721560603</v>
+        <v>0.3460559663629523</v>
       </c>
       <c r="D529" t="s">
         <v>7</v>
@@ -13336,7 +13336,7 @@
         <v>44</v>
       </c>
       <c r="C530">
-        <v>0.4799773938557699</v>
+        <v>0.4799081537353074</v>
       </c>
       <c r="D530" t="s">
         <v>7</v>
@@ -13353,7 +13353,7 @@
         <v>44</v>
       </c>
       <c r="C531">
-        <v>0.5139589162107649</v>
+        <v>0.5139018245237993</v>
       </c>
       <c r="D531" t="s">
         <v>7</v>
@@ -13370,7 +13370,7 @@
         <v>10</v>
       </c>
       <c r="C532">
-        <v>0.305035815939796</v>
+        <v>0.3052502563947118</v>
       </c>
       <c r="D532" t="s">
         <v>7</v>
@@ -13387,7 +13387,7 @@
         <v>15</v>
       </c>
       <c r="C533">
-        <v>0.4753802421229933</v>
+        <v>0.4752072334982426</v>
       </c>
       <c r="D533" t="s">
         <v>7</v>
@@ -13404,7 +13404,7 @@
         <v>15</v>
       </c>
       <c r="C534">
-        <v>0.3264240424804007</v>
+        <v>0.3262212385260762</v>
       </c>
       <c r="D534" t="s">
         <v>7</v>
@@ -13421,7 +13421,7 @@
         <v>6</v>
       </c>
       <c r="C535">
-        <v>0.3332024751475036</v>
+        <v>0.3332464112693503</v>
       </c>
       <c r="D535" t="s">
         <v>7</v>
@@ -13438,7 +13438,7 @@
         <v>6</v>
       </c>
       <c r="C536">
-        <v>0.3371406151627299</v>
+        <v>0.337188596055896</v>
       </c>
       <c r="D536" t="s">
         <v>7</v>
@@ -13455,7 +13455,7 @@
         <v>6</v>
       </c>
       <c r="C537">
-        <v>0.4129376805909074</v>
+        <v>0.4130003453365363</v>
       </c>
       <c r="D537" t="s">
         <v>7</v>
@@ -13472,7 +13472,7 @@
         <v>10</v>
       </c>
       <c r="C538">
-        <v>0.3096067823700727</v>
+        <v>0.3098247918056154</v>
       </c>
       <c r="D538" t="s">
         <v>7</v>
@@ -13489,7 +13489,7 @@
         <v>6</v>
       </c>
       <c r="C539">
-        <v>0.3206437613165823</v>
+        <v>0.3206885646404748</v>
       </c>
       <c r="D539" t="s">
         <v>7</v>
@@ -13503,10 +13503,10 @@
         <v>1088</v>
       </c>
       <c r="B540" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C540">
-        <v>0.2679168631093865</v>
+        <v>0.2679220890717738</v>
       </c>
       <c r="D540" t="s">
         <v>7</v>
@@ -13523,7 +13523,7 @@
         <v>6</v>
       </c>
       <c r="C541">
-        <v>0.4344723254993317</v>
+        <v>0.4344914782238027</v>
       </c>
       <c r="D541" t="s">
         <v>7</v>
@@ -13540,7 +13540,7 @@
         <v>44</v>
       </c>
       <c r="C542">
-        <v>0.3441796689481475</v>
+        <v>0.3440715839574824</v>
       </c>
       <c r="D542" t="s">
         <v>7</v>
@@ -13557,7 +13557,7 @@
         <v>6</v>
       </c>
       <c r="C543">
-        <v>0.447868930043232</v>
+        <v>0.4479096114122122</v>
       </c>
       <c r="D543" t="s">
         <v>7</v>
@@ -13574,7 +13574,7 @@
         <v>6</v>
       </c>
       <c r="C544">
-        <v>0.4268591318880953</v>
+        <v>0.4269150466488079</v>
       </c>
       <c r="D544" t="s">
         <v>7</v>
@@ -13843,7 +13843,7 @@
         <v>1143</v>
       </c>
       <c r="C563">
-        <v>0.2862317446366963</v>
+        <v>0.2865285111941168</v>
       </c>
       <c r="D563" t="s">
         <v>1144</v>
@@ -13860,7 +13860,7 @@
         <v>1143</v>
       </c>
       <c r="C564">
-        <v>0.3337067163596408</v>
+        <v>0.3339874309238164</v>
       </c>
       <c r="D564" t="s">
         <v>1144</v>
@@ -13877,7 +13877,7 @@
         <v>1143</v>
       </c>
       <c r="C565">
-        <v>0.2825384949951386</v>
+        <v>0.2828721453114191</v>
       </c>
       <c r="D565" t="s">
         <v>1144</v>
@@ -13894,7 +13894,7 @@
         <v>1143</v>
       </c>
       <c r="C566">
-        <v>0.3510873779285111</v>
+        <v>0.3514174809195016</v>
       </c>
       <c r="D566" t="s">
         <v>1144</v>
@@ -13911,7 +13911,7 @@
         <v>1143</v>
       </c>
       <c r="C567">
-        <v>0.4040472561001601</v>
+        <v>0.4043560811426221</v>
       </c>
       <c r="D567" t="s">
         <v>1144</v>
@@ -13928,7 +13928,7 @@
         <v>1143</v>
       </c>
       <c r="C568">
-        <v>0.4165961616066138</v>
+        <v>0.416972381564808</v>
       </c>
       <c r="D568" t="s">
         <v>1144</v>
@@ -13945,7 +13945,7 @@
         <v>1143</v>
       </c>
       <c r="C569">
-        <v>0.2785684082060632</v>
+        <v>0.278861381828963</v>
       </c>
       <c r="D569" t="s">
         <v>1144</v>
@@ -13962,7 +13962,7 @@
         <v>1143</v>
       </c>
       <c r="C570">
-        <v>0.3013860590590233</v>
+        <v>0.3017031666022623</v>
       </c>
       <c r="D570" t="s">
         <v>1144</v>
@@ -13979,7 +13979,7 @@
         <v>1143</v>
       </c>
       <c r="C571">
-        <v>0.2996656613596876</v>
+        <v>0.2999826817944883</v>
       </c>
       <c r="D571" t="s">
         <v>1144</v>
@@ -13996,7 +13996,7 @@
         <v>6</v>
       </c>
       <c r="C572">
-        <v>0.3122827456887742</v>
+        <v>0.3122559465192276</v>
       </c>
       <c r="D572" t="s">
         <v>1144</v>
@@ -14013,7 +14013,7 @@
         <v>1143</v>
       </c>
       <c r="C573">
-        <v>0.3455994121167242</v>
+        <v>0.3459385868255951</v>
       </c>
       <c r="D573" t="s">
         <v>1144</v>
@@ -14030,7 +14030,7 @@
         <v>44</v>
       </c>
       <c r="C574">
-        <v>0.3788223979302355</v>
+        <v>0.378643135692091</v>
       </c>
       <c r="D574" t="s">
         <v>1144</v>
@@ -14047,7 +14047,7 @@
         <v>1143</v>
       </c>
       <c r="C575">
-        <v>0.3688254934066839</v>
+        <v>0.3691610948781308</v>
       </c>
       <c r="D575" t="s">
         <v>1144</v>
@@ -14064,7 +14064,7 @@
         <v>1143</v>
       </c>
       <c r="C576">
-        <v>0.3659596468940942</v>
+        <v>0.3662971392040494</v>
       </c>
       <c r="D576" t="s">
         <v>1144</v>
@@ -14081,7 +14081,7 @@
         <v>6</v>
       </c>
       <c r="C577">
-        <v>0.3687562879055225</v>
+        <v>0.3686225924718544</v>
       </c>
       <c r="D577" t="s">
         <v>1144</v>
@@ -14098,7 +14098,7 @@
         <v>1143</v>
       </c>
       <c r="C578">
-        <v>0.4164216485283366</v>
+        <v>0.4167835681629807</v>
       </c>
       <c r="D578" t="s">
         <v>1144</v>
@@ -14115,7 +14115,7 @@
         <v>1143</v>
       </c>
       <c r="C579">
-        <v>0.3685337760048909</v>
+        <v>0.368898979892718</v>
       </c>
       <c r="D579" t="s">
         <v>1144</v>
@@ -14132,7 +14132,7 @@
         <v>1143</v>
       </c>
       <c r="C580">
-        <v>0.2970881451683461</v>
+        <v>0.2973895616542105</v>
       </c>
       <c r="D580" t="s">
         <v>1144</v>
@@ -14149,7 +14149,7 @@
         <v>1143</v>
       </c>
       <c r="C581">
-        <v>0.4773013925199448</v>
+        <v>0.4775904620545537</v>
       </c>
       <c r="D581" t="s">
         <v>1144</v>
@@ -14166,7 +14166,7 @@
         <v>1143</v>
       </c>
       <c r="C582">
-        <v>0.3169579935121163</v>
+        <v>0.3172739456699379</v>
       </c>
       <c r="D582" t="s">
         <v>1144</v>
@@ -14183,7 +14183,7 @@
         <v>1143</v>
       </c>
       <c r="C583">
-        <v>0.3943543354667077</v>
+        <v>0.3946426741141454</v>
       </c>
       <c r="D583" t="s">
         <v>1144</v>
@@ -14200,7 +14200,7 @@
         <v>1143</v>
       </c>
       <c r="C584">
-        <v>0.3157911247862568</v>
+        <v>0.316080871932035</v>
       </c>
       <c r="D584" t="s">
         <v>1144</v>
@@ -14217,7 +14217,7 @@
         <v>1143</v>
       </c>
       <c r="C585">
-        <v>0.4194886836909704</v>
+        <v>0.4198479906612609</v>
       </c>
       <c r="D585" t="s">
         <v>1144</v>
@@ -14234,7 +14234,7 @@
         <v>1143</v>
       </c>
       <c r="C586">
-        <v>0.2963659151006527</v>
+        <v>0.2966380962597527</v>
       </c>
       <c r="D586" t="s">
         <v>1144</v>
@@ -14251,7 +14251,7 @@
         <v>6</v>
       </c>
       <c r="C587">
-        <v>0.3296200532147451</v>
+        <v>0.3296072117146631</v>
       </c>
       <c r="D587" t="s">
         <v>1144</v>
@@ -14268,7 +14268,7 @@
         <v>1143</v>
       </c>
       <c r="C588">
-        <v>0.3255834791765406</v>
+        <v>0.3258780344804819</v>
       </c>
       <c r="D588" t="s">
         <v>1144</v>
@@ -14285,7 +14285,7 @@
         <v>44</v>
       </c>
       <c r="C589">
-        <v>0.3957538835677468</v>
+        <v>0.395583460929522</v>
       </c>
       <c r="D589" t="s">
         <v>1144</v>
@@ -14302,7 +14302,7 @@
         <v>6</v>
       </c>
       <c r="C590">
-        <v>0.4265527841873999</v>
+        <v>0.4264305278055339</v>
       </c>
       <c r="D590" t="s">
         <v>1144</v>
@@ -14319,7 +14319,7 @@
         <v>1143</v>
       </c>
       <c r="C591">
-        <v>0.5229723864606979</v>
+        <v>0.5232861714079698</v>
       </c>
       <c r="D591" t="s">
         <v>1144</v>
@@ -14336,7 +14336,7 @@
         <v>1143</v>
       </c>
       <c r="C592">
-        <v>0.366771425958945</v>
+        <v>0.3671092438643882</v>
       </c>
       <c r="D592" t="s">
         <v>1144</v>
@@ -14353,7 +14353,7 @@
         <v>1143</v>
       </c>
       <c r="C593">
-        <v>0.6601505655620831</v>
+        <v>0.6604298792217997</v>
       </c>
       <c r="D593" t="s">
         <v>1144</v>
@@ -14370,7 +14370,7 @@
         <v>1143</v>
       </c>
       <c r="C594">
-        <v>0.4545724518708138</v>
+        <v>0.4549221969708119</v>
       </c>
       <c r="D594" t="s">
         <v>1144</v>
@@ -14387,7 +14387,7 @@
         <v>6</v>
       </c>
       <c r="C595">
-        <v>0.3366118753612362</v>
+        <v>0.3365713467580632</v>
       </c>
       <c r="D595" t="s">
         <v>1144</v>
@@ -14404,7 +14404,7 @@
         <v>1143</v>
       </c>
       <c r="C596">
-        <v>0.4403687728395118</v>
+        <v>0.440715214153251</v>
       </c>
       <c r="D596" t="s">
         <v>1144</v>
@@ -14421,7 +14421,7 @@
         <v>6</v>
       </c>
       <c r="C597">
-        <v>0.3387744418165347</v>
+        <v>0.3386436516515572</v>
       </c>
       <c r="D597" t="s">
         <v>1144</v>
@@ -14438,7 +14438,7 @@
         <v>10</v>
       </c>
       <c r="C598">
-        <v>0.2349640096444199</v>
+        <v>0.2350696594842309</v>
       </c>
       <c r="D598" t="s">
         <v>1144</v>
@@ -14455,7 +14455,7 @@
         <v>1143</v>
       </c>
       <c r="C599">
-        <v>0.2607819228599443</v>
+        <v>0.2610651933945889</v>
       </c>
       <c r="D599" t="s">
         <v>1144</v>
@@ -14472,7 +14472,7 @@
         <v>1143</v>
       </c>
       <c r="C600">
-        <v>0.2865953420694184</v>
+        <v>0.2868728206048362</v>
       </c>
       <c r="D600" t="s">
         <v>1144</v>
@@ -14489,7 +14489,7 @@
         <v>1143</v>
       </c>
       <c r="C601">
-        <v>0.2712143050140573</v>
+        <v>0.2715044257637401</v>
       </c>
       <c r="D601" t="s">
         <v>1144</v>
@@ -14506,7 +14506,7 @@
         <v>1143</v>
       </c>
       <c r="C602">
-        <v>0.3688778853799183</v>
+        <v>0.3692534940030507</v>
       </c>
       <c r="D602" t="s">
         <v>1144</v>
@@ -14523,7 +14523,7 @@
         <v>1143</v>
       </c>
       <c r="C603">
-        <v>0.2983503750865437</v>
+        <v>0.2986593688687957</v>
       </c>
       <c r="D603" t="s">
         <v>1144</v>
@@ -14540,7 +14540,7 @@
         <v>6</v>
       </c>
       <c r="C604">
-        <v>0.3468269121622588</v>
+        <v>0.3467080003355819</v>
       </c>
       <c r="D604" t="s">
         <v>1144</v>
@@ -14557,7 +14557,7 @@
         <v>44</v>
       </c>
       <c r="C605">
-        <v>0.2801934392474142</v>
+        <v>0.2800703919991974</v>
       </c>
       <c r="D605" t="s">
         <v>1144</v>
@@ -14574,7 +14574,7 @@
         <v>6</v>
       </c>
       <c r="C606">
-        <v>0.3437621307486726</v>
+        <v>0.3436490912262617</v>
       </c>
       <c r="D606" t="s">
         <v>1144</v>
@@ -14591,7 +14591,7 @@
         <v>1143</v>
       </c>
       <c r="C607">
-        <v>0.3160997265742783</v>
+        <v>0.3163889512953308</v>
       </c>
       <c r="D607" t="s">
         <v>1144</v>
@@ -14608,7 +14608,7 @@
         <v>6</v>
       </c>
       <c r="C608">
-        <v>0.3238609991579033</v>
+        <v>0.3236963165065845</v>
       </c>
       <c r="D608" t="s">
         <v>1144</v>
@@ -14625,7 +14625,7 @@
         <v>6</v>
       </c>
       <c r="C609">
-        <v>0.3393061217939168</v>
+        <v>0.3391774988580925</v>
       </c>
       <c r="D609" t="s">
         <v>1144</v>
@@ -14642,7 +14642,7 @@
         <v>1143</v>
       </c>
       <c r="C610">
-        <v>0.2726779104213399</v>
+        <v>0.2729780037803216</v>
       </c>
       <c r="D610" t="s">
         <v>1144</v>
@@ -14659,7 +14659,7 @@
         <v>44</v>
       </c>
       <c r="C611">
-        <v>0.5389515318890323</v>
+        <v>0.5388467831689995</v>
       </c>
       <c r="D611" t="s">
         <v>1144</v>
@@ -14676,7 +14676,7 @@
         <v>44</v>
       </c>
       <c r="C612">
-        <v>0.3808023248916002</v>
+        <v>0.3807404865749753</v>
       </c>
       <c r="D612" t="s">
         <v>1144</v>
@@ -14693,7 +14693,7 @@
         <v>1143</v>
       </c>
       <c r="C613">
-        <v>0.3416115837284558</v>
+        <v>0.3419520005963805</v>
       </c>
       <c r="D613" t="s">
         <v>1144</v>
@@ -14710,7 +14710,7 @@
         <v>1143</v>
       </c>
       <c r="C614">
-        <v>0.445489694361066</v>
+        <v>0.4458582165764014</v>
       </c>
       <c r="D614" t="s">
         <v>1144</v>
@@ -14727,7 +14727,7 @@
         <v>1143</v>
       </c>
       <c r="C615">
-        <v>0.3489856578919413</v>
+        <v>0.3492784724364053</v>
       </c>
       <c r="D615" t="s">
         <v>1144</v>
@@ -14744,7 +14744,7 @@
         <v>1143</v>
       </c>
       <c r="C616">
-        <v>0.4310659653265893</v>
+        <v>0.4313512875114154</v>
       </c>
       <c r="D616" t="s">
         <v>1144</v>
@@ -14761,7 +14761,7 @@
         <v>1143</v>
       </c>
       <c r="C617">
-        <v>0.3568415496179281</v>
+        <v>0.3571567164381891</v>
       </c>
       <c r="D617" t="s">
         <v>1144</v>
@@ -14778,7 +14778,7 @@
         <v>10</v>
       </c>
       <c r="C618">
-        <v>0.3392729803083088</v>
+        <v>0.33930915671825</v>
       </c>
       <c r="D618" t="s">
         <v>1144</v>
@@ -14795,7 +14795,7 @@
         <v>1143</v>
       </c>
       <c r="C619">
-        <v>0.4459808886902796</v>
+        <v>0.4462944994357868</v>
       </c>
       <c r="D619" t="s">
         <v>1144</v>
@@ -14812,7 +14812,7 @@
         <v>6</v>
       </c>
       <c r="C620">
-        <v>0.3278662904908047</v>
+        <v>0.327838706255678</v>
       </c>
       <c r="D620" t="s">
         <v>1259</v>
@@ -14829,7 +14829,7 @@
         <v>15</v>
       </c>
       <c r="C621">
-        <v>0.3551411668606793</v>
+        <v>0.3546101422023398</v>
       </c>
       <c r="D621" t="s">
         <v>1259</v>
@@ -14846,7 +14846,7 @@
         <v>6</v>
       </c>
       <c r="C622">
-        <v>0.2765710284333049</v>
+        <v>0.2765414860679696</v>
       </c>
       <c r="D622" t="s">
         <v>1259</v>
@@ -14863,7 +14863,7 @@
         <v>1266</v>
       </c>
       <c r="C623">
-        <v>0.2191117244497651</v>
+        <v>0.2195260848268209</v>
       </c>
       <c r="D623" t="s">
         <v>1259</v>
@@ -14880,7 +14880,7 @@
         <v>10</v>
       </c>
       <c r="C624">
-        <v>0.3013174439129063</v>
+        <v>0.3012827392581843</v>
       </c>
       <c r="D624" t="s">
         <v>1259</v>
@@ -14897,7 +14897,7 @@
         <v>10</v>
       </c>
       <c r="C625">
-        <v>0.2484816907768088</v>
+        <v>0.2483885027536836</v>
       </c>
       <c r="D625" t="s">
         <v>1259</v>
@@ -14914,7 +14914,7 @@
         <v>15</v>
       </c>
       <c r="C626">
-        <v>0.3608546553895554</v>
+        <v>0.3603009123828729</v>
       </c>
       <c r="D626" t="s">
         <v>1259</v>
@@ -14931,7 +14931,7 @@
         <v>1266</v>
       </c>
       <c r="C627">
-        <v>0.2859833994655254</v>
+        <v>0.2864388349466772</v>
       </c>
       <c r="D627" t="s">
         <v>1259</v>
@@ -14948,7 +14948,7 @@
         <v>6</v>
       </c>
       <c r="C628">
-        <v>0.233098801377836</v>
+        <v>0.2329797822499295</v>
       </c>
       <c r="D628" t="s">
         <v>1259</v>
@@ -14965,7 +14965,7 @@
         <v>6</v>
       </c>
       <c r="C629">
-        <v>0.272837428093292</v>
+        <v>0.2727677869853829</v>
       </c>
       <c r="D629" t="s">
         <v>1259</v>
@@ -14982,7 +14982,7 @@
         <v>1266</v>
       </c>
       <c r="C630">
-        <v>0.3090337644068571</v>
+        <v>0.3095066910545931</v>
       </c>
       <c r="D630" t="s">
         <v>1259</v>
@@ -14999,7 +14999,7 @@
         <v>1266</v>
       </c>
       <c r="C631">
-        <v>0.3066884388449687</v>
+        <v>0.3071006368244846</v>
       </c>
       <c r="D631" t="s">
         <v>1259</v>
@@ -15016,7 +15016,7 @@
         <v>1266</v>
       </c>
       <c r="C632">
-        <v>0.396501369761091</v>
+        <v>0.3970017550027115</v>
       </c>
       <c r="D632" t="s">
         <v>1259</v>
@@ -15033,7 +15033,7 @@
         <v>15</v>
       </c>
       <c r="C633">
-        <v>0.2705910581210036</v>
+        <v>0.2700895497368387</v>
       </c>
       <c r="D633" t="s">
         <v>1259</v>
@@ -15050,7 +15050,7 @@
         <v>15</v>
       </c>
       <c r="C634">
-        <v>0.4259419518583432</v>
+        <v>0.425560222265739</v>
       </c>
       <c r="D634" t="s">
         <v>1259</v>
@@ -15067,7 +15067,7 @@
         <v>1266</v>
       </c>
       <c r="C635">
-        <v>0.4595439929718509</v>
+        <v>0.460028709054074</v>
       </c>
       <c r="D635" t="s">
         <v>1259</v>
@@ -15084,7 +15084,7 @@
         <v>6</v>
       </c>
       <c r="C636">
-        <v>0.3746083195459203</v>
+        <v>0.3745972168681952</v>
       </c>
       <c r="D636" t="s">
         <v>1259</v>
@@ -15101,7 +15101,7 @@
         <v>15</v>
       </c>
       <c r="C637">
-        <v>0.3004285639190377</v>
+        <v>0.2999316228030968</v>
       </c>
       <c r="D637" t="s">
         <v>1259</v>
@@ -15118,7 +15118,7 @@
         <v>1266</v>
       </c>
       <c r="C638">
-        <v>0.4254250865066503</v>
+        <v>0.4256926247246307</v>
       </c>
       <c r="D638" t="s">
         <v>1259</v>
@@ -15135,7 +15135,7 @@
         <v>10</v>
       </c>
       <c r="C639">
-        <v>0.3433262666407025</v>
+        <v>0.3433022002984534</v>
       </c>
       <c r="D639" t="s">
         <v>1259</v>
@@ -15152,7 +15152,7 @@
         <v>10</v>
       </c>
       <c r="C640">
-        <v>0.3121835458922222</v>
+        <v>0.3120986368406384</v>
       </c>
       <c r="D640" t="s">
         <v>1259</v>
@@ -15169,7 +15169,7 @@
         <v>15</v>
       </c>
       <c r="C641">
-        <v>0.2761513430518701</v>
+        <v>0.275672472911778</v>
       </c>
       <c r="D641" t="s">
         <v>1259</v>
@@ -15186,7 +15186,7 @@
         <v>1266</v>
       </c>
       <c r="C642">
-        <v>0.2851580840514525</v>
+        <v>0.285644092319161</v>
       </c>
       <c r="D642" t="s">
         <v>1259</v>
@@ -15203,7 +15203,7 @@
         <v>15</v>
       </c>
       <c r="C643">
-        <v>0.3442305383897116</v>
+        <v>0.3437100119396257</v>
       </c>
       <c r="D643" t="s">
         <v>1259</v>
@@ -15220,7 +15220,7 @@
         <v>15</v>
       </c>
       <c r="C644">
-        <v>0.291935388459783</v>
+        <v>0.2914450730017736</v>
       </c>
       <c r="D644" t="s">
         <v>1259</v>
@@ -15237,7 +15237,7 @@
         <v>15</v>
       </c>
       <c r="C645">
-        <v>0.250413529510035</v>
+        <v>0.2499514734199365</v>
       </c>
       <c r="D645" t="s">
         <v>1259</v>
@@ -15254,7 +15254,7 @@
         <v>15</v>
       </c>
       <c r="C646">
-        <v>0.3695681570748545</v>
+        <v>0.3690748629684756</v>
       </c>
       <c r="D646" t="s">
         <v>1259</v>
@@ -15271,7 +15271,7 @@
         <v>6</v>
       </c>
       <c r="C647">
-        <v>0.2993135631546125</v>
+        <v>0.2992509391881946</v>
       </c>
       <c r="D647" t="s">
         <v>1259</v>
@@ -15288,7 +15288,7 @@
         <v>15</v>
       </c>
       <c r="C648">
-        <v>0.3098350305973636</v>
+        <v>0.3093236047485535</v>
       </c>
       <c r="D648" t="s">
         <v>1259</v>
@@ -15305,7 +15305,7 @@
         <v>15</v>
       </c>
       <c r="C649">
-        <v>0.3560970724312739</v>
+        <v>0.355576724583402</v>
       </c>
       <c r="D649" t="s">
         <v>1259</v>
@@ -15322,7 +15322,7 @@
         <v>6</v>
       </c>
       <c r="C650">
-        <v>0.2845150054340436</v>
+        <v>0.2844631870191548</v>
       </c>
       <c r="D650" t="s">
         <v>1259</v>
@@ -15339,7 +15339,7 @@
         <v>15</v>
       </c>
       <c r="C651">
-        <v>0.3341295391172087</v>
+        <v>0.3335918913220633</v>
       </c>
       <c r="D651" t="s">
         <v>1259</v>
@@ -15371,7 +15371,7 @@
         <v>15</v>
       </c>
       <c r="B2">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -15379,7 +15379,7 @@
         <v>10</v>
       </c>
       <c r="B3">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:2">

--- a/frontend/data/uk_election_predictions.xlsx
+++ b/frontend/data/uk_election_predictions.xlsx
@@ -35,27 +35,27 @@
     <t>aldershot</t>
   </si>
   <si>
+    <t>Conservative</t>
+  </si>
+  <si>
+    <t>England</t>
+  </si>
+  <si>
+    <t>E14001063</t>
+  </si>
+  <si>
+    <t>aldridge-brownhills</t>
+  </si>
+  <si>
+    <t>E14001064</t>
+  </si>
+  <si>
+    <t>altrincham and sale west</t>
+  </si>
+  <si>
     <t>Labour</t>
   </si>
   <si>
-    <t>England</t>
-  </si>
-  <si>
-    <t>E14001063</t>
-  </si>
-  <si>
-    <t>aldridge-brownhills</t>
-  </si>
-  <si>
-    <t>Conservative</t>
-  </si>
-  <si>
-    <t>E14001064</t>
-  </si>
-  <si>
-    <t>altrincham and sale west</t>
-  </si>
-  <si>
     <t>E14001065</t>
   </si>
   <si>
@@ -3446,16 +3446,16 @@
     <t>aberdeen north</t>
   </si>
   <si>
+    <t>Scotland</t>
+  </si>
+  <si>
+    <t>S14000060</t>
+  </si>
+  <si>
+    <t>aberdeen south</t>
+  </si>
+  <si>
     <t>Scottish National Party (SNP)</t>
-  </si>
-  <si>
-    <t>Scotland</t>
-  </si>
-  <si>
-    <t>S14000060</t>
-  </si>
-  <si>
-    <t>aberdeen south</t>
   </si>
   <si>
     <t>S14000061</t>
@@ -4360,7 +4360,7 @@
         <v>6</v>
       </c>
       <c r="C2">
-        <v>0.3158750916302961</v>
+        <v>0.3089361890270064</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
@@ -4374,27 +4374,27 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3">
+        <v>0.4239419994104246</v>
+      </c>
+      <c r="D3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" t="s">
         <v>10</v>
-      </c>
-      <c r="C3">
-        <v>0.4172305728821916</v>
-      </c>
-      <c r="D3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C4">
-        <v>0.4096214589672389</v>
+        <v>0.4041092028102727</v>
       </c>
       <c r="D4" t="s">
         <v>7</v>
@@ -4411,7 +4411,7 @@
         <v>15</v>
       </c>
       <c r="C5">
-        <v>0.3760124726817399</v>
+        <v>0.3776338725442422</v>
       </c>
       <c r="D5" t="s">
         <v>7</v>
@@ -4425,10 +4425,10 @@
         <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>0.4037273028773024</v>
+        <v>0.4029138480718916</v>
       </c>
       <c r="D6" t="s">
         <v>7</v>
@@ -4442,10 +4442,10 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C7">
-        <v>0.3271418648375878</v>
+        <v>0.3267657874505037</v>
       </c>
       <c r="D7" t="s">
         <v>7</v>
@@ -4462,7 +4462,7 @@
         <v>15</v>
       </c>
       <c r="C8">
-        <v>0.3417685480192545</v>
+        <v>0.3394647709705603</v>
       </c>
       <c r="D8" t="s">
         <v>7</v>
@@ -4479,7 +4479,7 @@
         <v>15</v>
       </c>
       <c r="C9">
-        <v>0.3175000533364746</v>
+        <v>0.3164046736507709</v>
       </c>
       <c r="D9" t="s">
         <v>7</v>
@@ -4493,10 +4493,10 @@
         <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C10">
-        <v>0.3461120230833049</v>
+        <v>0.3534427058878392</v>
       </c>
       <c r="D10" t="s">
         <v>7</v>
@@ -4513,7 +4513,7 @@
         <v>15</v>
       </c>
       <c r="C11">
-        <v>0.233279448656726</v>
+        <v>0.2321970610160016</v>
       </c>
       <c r="D11" t="s">
         <v>7</v>
@@ -4527,10 +4527,10 @@
         <v>29</v>
       </c>
       <c r="B12" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C12">
-        <v>0.4061250229630603</v>
+        <v>0.4076041132940694</v>
       </c>
       <c r="D12" t="s">
         <v>7</v>
@@ -4547,7 +4547,7 @@
         <v>15</v>
       </c>
       <c r="C13">
-        <v>0.3007560270011409</v>
+        <v>0.2998339533963955</v>
       </c>
       <c r="D13" t="s">
         <v>7</v>
@@ -4564,7 +4564,7 @@
         <v>15</v>
       </c>
       <c r="C14">
-        <v>0.3855744851104193</v>
+        <v>0.3845917348789192</v>
       </c>
       <c r="D14" t="s">
         <v>7</v>
@@ -4578,10 +4578,10 @@
         <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C15">
-        <v>0.374920882928685</v>
+        <v>0.3786686288650424</v>
       </c>
       <c r="D15" t="s">
         <v>7</v>
@@ -4595,10 +4595,10 @@
         <v>37</v>
       </c>
       <c r="B16" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C16">
-        <v>0.3518053090422998</v>
+        <v>0.3466480686112843</v>
       </c>
       <c r="D16" t="s">
         <v>7</v>
@@ -4612,10 +4612,10 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C17">
-        <v>0.2791611310323777</v>
+        <v>0.2872286865785014</v>
       </c>
       <c r="D17" t="s">
         <v>7</v>
@@ -4629,10 +4629,10 @@
         <v>41</v>
       </c>
       <c r="B18" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C18">
-        <v>0.3353778213810027</v>
+        <v>0.3388249669557636</v>
       </c>
       <c r="D18" t="s">
         <v>7</v>
@@ -4649,7 +4649,7 @@
         <v>44</v>
       </c>
       <c r="C19">
-        <v>0.4139011130377653</v>
+        <v>0.4205724607029313</v>
       </c>
       <c r="D19" t="s">
         <v>7</v>
@@ -4663,10 +4663,10 @@
         <v>46</v>
       </c>
       <c r="B20" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C20">
-        <v>0.4678988639311091</v>
+        <v>0.4546565518194737</v>
       </c>
       <c r="D20" t="s">
         <v>7</v>
@@ -4680,10 +4680,10 @@
         <v>48</v>
       </c>
       <c r="B21" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C21">
-        <v>0.4138625308740333</v>
+        <v>0.411808702421012</v>
       </c>
       <c r="D21" t="s">
         <v>7</v>
@@ -4697,10 +4697,10 @@
         <v>50</v>
       </c>
       <c r="B22" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C22">
-        <v>0.3762447171888225</v>
+        <v>0.3700704246641553</v>
       </c>
       <c r="D22" t="s">
         <v>7</v>
@@ -4714,10 +4714,10 @@
         <v>52</v>
       </c>
       <c r="B23" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C23">
-        <v>0.4742242835766043</v>
+        <v>0.4609682391635985</v>
       </c>
       <c r="D23" t="s">
         <v>7</v>
@@ -4731,10 +4731,10 @@
         <v>54</v>
       </c>
       <c r="B24" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C24">
-        <v>0.3692103763023497</v>
+        <v>0.3556398850061476</v>
       </c>
       <c r="D24" t="s">
         <v>7</v>
@@ -4748,10 +4748,10 @@
         <v>56</v>
       </c>
       <c r="B25" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C25">
-        <v>0.6332506697290622</v>
+        <v>0.6216335437310239</v>
       </c>
       <c r="D25" t="s">
         <v>7</v>
@@ -4765,10 +4765,10 @@
         <v>58</v>
       </c>
       <c r="B26" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C26">
-        <v>0.2977725367376293</v>
+        <v>0.2901439505620627</v>
       </c>
       <c r="D26" t="s">
         <v>7</v>
@@ -4782,10 +4782,10 @@
         <v>60</v>
       </c>
       <c r="B27" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C27">
-        <v>0.3024411061339548</v>
+        <v>0.3100446797202301</v>
       </c>
       <c r="D27" t="s">
         <v>7</v>
@@ -4799,10 +4799,10 @@
         <v>62</v>
       </c>
       <c r="B28" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C28">
-        <v>0.3348949193172715</v>
+        <v>0.3239707257194963</v>
       </c>
       <c r="D28" t="s">
         <v>7</v>
@@ -4819,7 +4819,7 @@
         <v>44</v>
       </c>
       <c r="C29">
-        <v>0.4142447497096594</v>
+        <v>0.4200935343725836</v>
       </c>
       <c r="D29" t="s">
         <v>7</v>
@@ -4833,10 +4833,10 @@
         <v>66</v>
       </c>
       <c r="B30" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C30">
-        <v>0.3942084105840059</v>
+        <v>0.3912339886155048</v>
       </c>
       <c r="D30" t="s">
         <v>7</v>
@@ -4850,10 +4850,10 @@
         <v>68</v>
       </c>
       <c r="B31" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C31">
-        <v>0.4619513562142523</v>
+        <v>0.4605120136826356</v>
       </c>
       <c r="D31" t="s">
         <v>7</v>
@@ -4870,7 +4870,7 @@
         <v>15</v>
       </c>
       <c r="C32">
-        <v>0.4050945252813247</v>
+        <v>0.406398644337622</v>
       </c>
       <c r="D32" t="s">
         <v>7</v>
@@ -4884,10 +4884,10 @@
         <v>72</v>
       </c>
       <c r="B33" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C33">
-        <v>0.4185379567160899</v>
+        <v>0.4150870054199206</v>
       </c>
       <c r="D33" t="s">
         <v>7</v>
@@ -4904,7 +4904,7 @@
         <v>15</v>
       </c>
       <c r="C34">
-        <v>0.3259183034563687</v>
+        <v>0.3274515813018074</v>
       </c>
       <c r="D34" t="s">
         <v>7</v>
@@ -4918,10 +4918,10 @@
         <v>76</v>
       </c>
       <c r="B35" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C35">
-        <v>0.4700222128382005</v>
+        <v>0.4676710924625198</v>
       </c>
       <c r="D35" t="s">
         <v>7</v>
@@ -4935,10 +4935,10 @@
         <v>78</v>
       </c>
       <c r="B36" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C36">
-        <v>0.2642634868812762</v>
+        <v>0.2593734862987884</v>
       </c>
       <c r="D36" t="s">
         <v>7</v>
@@ -4955,7 +4955,7 @@
         <v>15</v>
       </c>
       <c r="C37">
-        <v>0.3155042316096642</v>
+        <v>0.316296777209943</v>
       </c>
       <c r="D37" t="s">
         <v>7</v>
@@ -4969,10 +4969,10 @@
         <v>82</v>
       </c>
       <c r="B38" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C38">
-        <v>0.3580454661950719</v>
+        <v>0.3514283498905464</v>
       </c>
       <c r="D38" t="s">
         <v>7</v>
@@ -4986,10 +4986,10 @@
         <v>84</v>
       </c>
       <c r="B39" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C39">
-        <v>0.3272420951602468</v>
+        <v>0.322815747752313</v>
       </c>
       <c r="D39" t="s">
         <v>7</v>
@@ -5003,10 +5003,10 @@
         <v>86</v>
       </c>
       <c r="B40" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C40">
-        <v>0.4991188339283906</v>
+        <v>0.4935175079684386</v>
       </c>
       <c r="D40" t="s">
         <v>7</v>
@@ -5020,10 +5020,10 @@
         <v>88</v>
       </c>
       <c r="B41" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C41">
-        <v>0.2876595378969095</v>
+        <v>0.2988619667608612</v>
       </c>
       <c r="D41" t="s">
         <v>7</v>
@@ -5037,10 +5037,10 @@
         <v>90</v>
       </c>
       <c r="B42" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C42">
-        <v>0.5342465136704916</v>
+        <v>0.5345587892554764</v>
       </c>
       <c r="D42" t="s">
         <v>7</v>
@@ -5057,7 +5057,7 @@
         <v>15</v>
       </c>
       <c r="C43">
-        <v>0.3969918253337516</v>
+        <v>0.3930335051288815</v>
       </c>
       <c r="D43" t="s">
         <v>7</v>
@@ -5074,7 +5074,7 @@
         <v>15</v>
       </c>
       <c r="C44">
-        <v>0.4300611566194972</v>
+        <v>0.4309291839402182</v>
       </c>
       <c r="D44" t="s">
         <v>7</v>
@@ -5088,10 +5088,10 @@
         <v>96</v>
       </c>
       <c r="B45" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C45">
-        <v>0.4273555774760409</v>
+        <v>0.4219584861650154</v>
       </c>
       <c r="D45" t="s">
         <v>7</v>
@@ -5105,10 +5105,10 @@
         <v>98</v>
       </c>
       <c r="B46" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C46">
-        <v>0.4112255693737959</v>
+        <v>0.4096429268681686</v>
       </c>
       <c r="D46" t="s">
         <v>7</v>
@@ -5125,7 +5125,7 @@
         <v>15</v>
       </c>
       <c r="C47">
-        <v>0.2977801373040717</v>
+        <v>0.2953464576464722</v>
       </c>
       <c r="D47" t="s">
         <v>7</v>
@@ -5142,7 +5142,7 @@
         <v>15</v>
       </c>
       <c r="C48">
-        <v>0.4099501539883394</v>
+        <v>0.4107673869722708</v>
       </c>
       <c r="D48" t="s">
         <v>7</v>
@@ -5159,7 +5159,7 @@
         <v>15</v>
       </c>
       <c r="C49">
-        <v>0.3270973132291453</v>
+        <v>0.3256510092007087</v>
       </c>
       <c r="D49" t="s">
         <v>7</v>
@@ -5176,7 +5176,7 @@
         <v>15</v>
       </c>
       <c r="C50">
-        <v>0.3647721556125839</v>
+        <v>0.3654136442313836</v>
       </c>
       <c r="D50" t="s">
         <v>7</v>
@@ -5193,7 +5193,7 @@
         <v>15</v>
       </c>
       <c r="C51">
-        <v>0.3537074251982334</v>
+        <v>0.3520448794201434</v>
       </c>
       <c r="D51" t="s">
         <v>7</v>
@@ -5207,10 +5207,10 @@
         <v>110</v>
       </c>
       <c r="B52" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C52">
-        <v>0.521991681141481</v>
+        <v>0.5217939925913709</v>
       </c>
       <c r="D52" t="s">
         <v>7</v>
@@ -5227,7 +5227,7 @@
         <v>15</v>
       </c>
       <c r="C53">
-        <v>0.4433507006035885</v>
+        <v>0.4448075024690321</v>
       </c>
       <c r="D53" t="s">
         <v>7</v>
@@ -5241,10 +5241,10 @@
         <v>114</v>
       </c>
       <c r="B54" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C54">
-        <v>0.4232472581532497</v>
+        <v>0.4115338619376534</v>
       </c>
       <c r="D54" t="s">
         <v>7</v>
@@ -5258,10 +5258,10 @@
         <v>116</v>
       </c>
       <c r="B55" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C55">
-        <v>0.3086241034583719</v>
+        <v>0.311373099780354</v>
       </c>
       <c r="D55" t="s">
         <v>7</v>
@@ -5275,10 +5275,10 @@
         <v>118</v>
       </c>
       <c r="B56" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C56">
-        <v>0.3973507805224538</v>
+        <v>0.4052380212400331</v>
       </c>
       <c r="D56" t="s">
         <v>7</v>
@@ -5292,10 +5292,10 @@
         <v>120</v>
       </c>
       <c r="B57" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C57">
-        <v>0.5606716598004159</v>
+        <v>0.5559918970011678</v>
       </c>
       <c r="D57" t="s">
         <v>7</v>
@@ -5309,10 +5309,10 @@
         <v>122</v>
       </c>
       <c r="B58" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C58">
-        <v>0.3398868426649885</v>
+        <v>0.3390541829800454</v>
       </c>
       <c r="D58" t="s">
         <v>7</v>
@@ -5326,10 +5326,10 @@
         <v>124</v>
       </c>
       <c r="B59" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C59">
-        <v>0.3808380726565327</v>
+        <v>0.3793136334753959</v>
       </c>
       <c r="D59" t="s">
         <v>7</v>
@@ -5343,10 +5343,10 @@
         <v>126</v>
       </c>
       <c r="B60" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C60">
-        <v>0.331136092868879</v>
+        <v>0.3250573434045577</v>
       </c>
       <c r="D60" t="s">
         <v>7</v>
@@ -5360,10 +5360,10 @@
         <v>128</v>
       </c>
       <c r="B61" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C61">
-        <v>0.3904891446008104</v>
+        <v>0.3857339822555611</v>
       </c>
       <c r="D61" t="s">
         <v>7</v>
@@ -5377,10 +5377,10 @@
         <v>130</v>
       </c>
       <c r="B62" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C62">
-        <v>0.3842725227120738</v>
+        <v>0.3859060290596675</v>
       </c>
       <c r="D62" t="s">
         <v>7</v>
@@ -5394,10 +5394,10 @@
         <v>132</v>
       </c>
       <c r="B63" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C63">
-        <v>0.3916341846579638</v>
+        <v>0.3863504905310944</v>
       </c>
       <c r="D63" t="s">
         <v>7</v>
@@ -5411,10 +5411,10 @@
         <v>134</v>
       </c>
       <c r="B64" t="s">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="C64">
-        <v>0.2171592638181206</v>
+        <v>0.2264391393869829</v>
       </c>
       <c r="D64" t="s">
         <v>7</v>
@@ -5428,10 +5428,10 @@
         <v>136</v>
       </c>
       <c r="B65" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C65">
-        <v>0.3345539876119042</v>
+        <v>0.3422859589209933</v>
       </c>
       <c r="D65" t="s">
         <v>7</v>
@@ -5445,10 +5445,10 @@
         <v>138</v>
       </c>
       <c r="B66" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C66">
-        <v>0.3307796432821828</v>
+        <v>0.3391698967485272</v>
       </c>
       <c r="D66" t="s">
         <v>7</v>
@@ -5465,7 +5465,7 @@
         <v>15</v>
       </c>
       <c r="C67">
-        <v>0.3410348415667715</v>
+        <v>0.3382369480450507</v>
       </c>
       <c r="D67" t="s">
         <v>7</v>
@@ -5479,10 +5479,10 @@
         <v>142</v>
       </c>
       <c r="B68" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C68">
-        <v>0.3362067371877325</v>
+        <v>0.330194130912436</v>
       </c>
       <c r="D68" t="s">
         <v>7</v>
@@ -5499,7 +5499,7 @@
         <v>145</v>
       </c>
       <c r="C69">
-        <v>0.4920376726018258</v>
+        <v>0.4875564351619477</v>
       </c>
       <c r="D69" t="s">
         <v>7</v>
@@ -5516,7 +5516,7 @@
         <v>145</v>
       </c>
       <c r="C70">
-        <v>0.4470188626389667</v>
+        <v>0.4436873200723312</v>
       </c>
       <c r="D70" t="s">
         <v>7</v>
@@ -5530,10 +5530,10 @@
         <v>149</v>
       </c>
       <c r="B71" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C71">
-        <v>0.5045810645406479</v>
+        <v>0.496831361499494</v>
       </c>
       <c r="D71" t="s">
         <v>7</v>
@@ -5547,10 +5547,10 @@
         <v>151</v>
       </c>
       <c r="B72" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C72">
-        <v>0.4046181897353031</v>
+        <v>0.3941306982800571</v>
       </c>
       <c r="D72" t="s">
         <v>7</v>
@@ -5564,10 +5564,10 @@
         <v>153</v>
       </c>
       <c r="B73" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C73">
-        <v>0.5350708887593716</v>
+        <v>0.52190071998596</v>
       </c>
       <c r="D73" t="s">
         <v>7</v>
@@ -5581,10 +5581,10 @@
         <v>155</v>
       </c>
       <c r="B74" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C74">
-        <v>0.5213109747545196</v>
+        <v>0.5154012914376723</v>
       </c>
       <c r="D74" t="s">
         <v>7</v>
@@ -5598,10 +5598,10 @@
         <v>157</v>
       </c>
       <c r="B75" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C75">
-        <v>0.3248031881095777</v>
+        <v>0.3314367917668221</v>
       </c>
       <c r="D75" t="s">
         <v>7</v>
@@ -5615,10 +5615,10 @@
         <v>159</v>
       </c>
       <c r="B76" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C76">
-        <v>0.3658128553706181</v>
+        <v>0.3699147370448828</v>
       </c>
       <c r="D76" t="s">
         <v>7</v>
@@ -5632,10 +5632,10 @@
         <v>161</v>
       </c>
       <c r="B77" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C77">
-        <v>0.3519019969006175</v>
+        <v>0.3546318682881281</v>
       </c>
       <c r="D77" t="s">
         <v>7</v>
@@ -5649,10 +5649,10 @@
         <v>163</v>
       </c>
       <c r="B78" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C78">
-        <v>0.4571907153319389</v>
+        <v>0.4654403920238682</v>
       </c>
       <c r="D78" t="s">
         <v>7</v>
@@ -5666,10 +5666,10 @@
         <v>165</v>
       </c>
       <c r="B79" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C79">
-        <v>0.2918141555953317</v>
+        <v>0.3001009705346404</v>
       </c>
       <c r="D79" t="s">
         <v>7</v>
@@ -5683,10 +5683,10 @@
         <v>167</v>
       </c>
       <c r="B80" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C80">
-        <v>0.3901321155632292</v>
+        <v>0.3975238246630193</v>
       </c>
       <c r="D80" t="s">
         <v>7</v>
@@ -5703,7 +5703,7 @@
         <v>15</v>
       </c>
       <c r="C81">
-        <v>0.2962319102336229</v>
+        <v>0.2953560341197214</v>
       </c>
       <c r="D81" t="s">
         <v>7</v>
@@ -5717,10 +5717,10 @@
         <v>171</v>
       </c>
       <c r="B82" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C82">
-        <v>0.4545816897479437</v>
+        <v>0.4575591628501349</v>
       </c>
       <c r="D82" t="s">
         <v>7</v>
@@ -5734,10 +5734,10 @@
         <v>173</v>
       </c>
       <c r="B83" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C83">
-        <v>0.4183937060905052</v>
+        <v>0.4127952240236872</v>
       </c>
       <c r="D83" t="s">
         <v>7</v>
@@ -5751,10 +5751,10 @@
         <v>175</v>
       </c>
       <c r="B84" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C84">
-        <v>0.3160858588507656</v>
+        <v>0.3241977745892953</v>
       </c>
       <c r="D84" t="s">
         <v>7</v>
@@ -5771,7 +5771,7 @@
         <v>15</v>
       </c>
       <c r="C85">
-        <v>0.299731402472425</v>
+        <v>0.2954832569492601</v>
       </c>
       <c r="D85" t="s">
         <v>7</v>
@@ -5785,10 +5785,10 @@
         <v>179</v>
       </c>
       <c r="B86" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C86">
-        <v>0.3411243234781229</v>
+        <v>0.3346911119576672</v>
       </c>
       <c r="D86" t="s">
         <v>7</v>
@@ -5802,10 +5802,10 @@
         <v>181</v>
       </c>
       <c r="B87" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C87">
-        <v>0.3108977155187129</v>
+        <v>0.3071346216264821</v>
       </c>
       <c r="D87" t="s">
         <v>7</v>
@@ -5819,10 +5819,10 @@
         <v>183</v>
       </c>
       <c r="B88" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C88">
-        <v>0.3009052750796576</v>
+        <v>0.2882946692011581</v>
       </c>
       <c r="D88" t="s">
         <v>7</v>
@@ -5836,10 +5836,10 @@
         <v>185</v>
       </c>
       <c r="B89" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C89">
-        <v>0.3155032425814528</v>
+        <v>0.3258071734888688</v>
       </c>
       <c r="D89" t="s">
         <v>7</v>
@@ -5853,10 +5853,10 @@
         <v>187</v>
       </c>
       <c r="B90" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C90">
-        <v>0.2785792775590318</v>
+        <v>0.2870808161900931</v>
       </c>
       <c r="D90" t="s">
         <v>7</v>
@@ -5873,7 +5873,7 @@
         <v>6</v>
       </c>
       <c r="C91">
-        <v>0.2854582331728598</v>
+        <v>0.2929857738989522</v>
       </c>
       <c r="D91" t="s">
         <v>7</v>
@@ -5887,10 +5887,10 @@
         <v>191</v>
       </c>
       <c r="B92" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C92">
-        <v>0.284221704047108</v>
+        <v>0.2898490290082375</v>
       </c>
       <c r="D92" t="s">
         <v>7</v>
@@ -5907,7 +5907,7 @@
         <v>15</v>
       </c>
       <c r="C93">
-        <v>0.3603935763334742</v>
+        <v>0.3582027052370604</v>
       </c>
       <c r="D93" t="s">
         <v>7</v>
@@ -5921,10 +5921,10 @@
         <v>195</v>
       </c>
       <c r="B94" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C94">
-        <v>0.3226463761207925</v>
+        <v>0.3141971396070826</v>
       </c>
       <c r="D94" t="s">
         <v>7</v>
@@ -5938,10 +5938,10 @@
         <v>197</v>
       </c>
       <c r="B95" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C95">
-        <v>0.3244682683616514</v>
+        <v>0.3319865518250765</v>
       </c>
       <c r="D95" t="s">
         <v>7</v>
@@ -5958,7 +5958,7 @@
         <v>15</v>
       </c>
       <c r="C96">
-        <v>0.3297601230129829</v>
+        <v>0.330468618675236</v>
       </c>
       <c r="D96" t="s">
         <v>7</v>
@@ -5975,7 +5975,7 @@
         <v>44</v>
       </c>
       <c r="C97">
-        <v>0.3062681895356062</v>
+        <v>0.3161172472968449</v>
       </c>
       <c r="D97" t="s">
         <v>7</v>
@@ -5992,7 +5992,7 @@
         <v>44</v>
       </c>
       <c r="C98">
-        <v>0.3020323388316731</v>
+        <v>0.3116542110284386</v>
       </c>
       <c r="D98" t="s">
         <v>7</v>
@@ -6006,10 +6006,10 @@
         <v>205</v>
       </c>
       <c r="B99" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C99">
-        <v>0.4669595041980193</v>
+        <v>0.4527336764165985</v>
       </c>
       <c r="D99" t="s">
         <v>7</v>
@@ -6026,7 +6026,7 @@
         <v>44</v>
       </c>
       <c r="C100">
-        <v>0.3743277640262537</v>
+        <v>0.380587737752518</v>
       </c>
       <c r="D100" t="s">
         <v>7</v>
@@ -6043,7 +6043,7 @@
         <v>44</v>
       </c>
       <c r="C101">
-        <v>0.3590287669236582</v>
+        <v>0.3658804856142956</v>
       </c>
       <c r="D101" t="s">
         <v>7</v>
@@ -6057,10 +6057,10 @@
         <v>211</v>
       </c>
       <c r="B102" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C102">
-        <v>0.4924061738204196</v>
+        <v>0.483091520138685</v>
       </c>
       <c r="D102" t="s">
         <v>7</v>
@@ -6074,10 +6074,10 @@
         <v>213</v>
       </c>
       <c r="B103" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C103">
-        <v>0.3706242578642114</v>
+        <v>0.3655350351310906</v>
       </c>
       <c r="D103" t="s">
         <v>7</v>
@@ -6094,7 +6094,7 @@
         <v>15</v>
       </c>
       <c r="C104">
-        <v>0.3779368403997101</v>
+        <v>0.3783275940075863</v>
       </c>
       <c r="D104" t="s">
         <v>7</v>
@@ -6111,7 +6111,7 @@
         <v>44</v>
       </c>
       <c r="C105">
-        <v>0.2974560085442119</v>
+        <v>0.3068977231529376</v>
       </c>
       <c r="D105" t="s">
         <v>7</v>
@@ -6125,10 +6125,10 @@
         <v>219</v>
       </c>
       <c r="B106" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C106">
-        <v>0.4109569794605678</v>
+        <v>0.4133314417842037</v>
       </c>
       <c r="D106" t="s">
         <v>7</v>
@@ -6142,10 +6142,10 @@
         <v>221</v>
       </c>
       <c r="B107" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C107">
-        <v>0.3396276185127481</v>
+        <v>0.3395682913411763</v>
       </c>
       <c r="D107" t="s">
         <v>7</v>
@@ -6159,10 +6159,10 @@
         <v>223</v>
       </c>
       <c r="B108" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C108">
-        <v>0.4086781820072453</v>
+        <v>0.4031811188174734</v>
       </c>
       <c r="D108" t="s">
         <v>7</v>
@@ -6193,10 +6193,10 @@
         <v>228</v>
       </c>
       <c r="B110" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C110">
-        <v>0.307204690970856</v>
+        <v>0.3146503559350151</v>
       </c>
       <c r="D110" t="s">
         <v>7</v>
@@ -6210,10 +6210,10 @@
         <v>230</v>
       </c>
       <c r="B111" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C111">
-        <v>0.5064149297044651</v>
+        <v>0.4925985454099738</v>
       </c>
       <c r="D111" t="s">
         <v>7</v>
@@ -6227,10 +6227,10 @@
         <v>232</v>
       </c>
       <c r="B112" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C112">
-        <v>0.4187138939088344</v>
+        <v>0.4110824903994398</v>
       </c>
       <c r="D112" t="s">
         <v>7</v>
@@ -6247,7 +6247,7 @@
         <v>15</v>
       </c>
       <c r="C113">
-        <v>0.4882878752464895</v>
+        <v>0.4905862451934004</v>
       </c>
       <c r="D113" t="s">
         <v>7</v>
@@ -6261,10 +6261,10 @@
         <v>236</v>
       </c>
       <c r="B114" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C114">
-        <v>0.6478280329021556</v>
+        <v>0.6357992518414292</v>
       </c>
       <c r="D114" t="s">
         <v>7</v>
@@ -6278,10 +6278,10 @@
         <v>238</v>
       </c>
       <c r="B115" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C115">
-        <v>0.3095471261514482</v>
+        <v>0.3023651038277281</v>
       </c>
       <c r="D115" t="s">
         <v>7</v>
@@ -6295,10 +6295,10 @@
         <v>240</v>
       </c>
       <c r="B116" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C116">
-        <v>0.4263311140937783</v>
+        <v>0.4219262202546338</v>
       </c>
       <c r="D116" t="s">
         <v>7</v>
@@ -6312,10 +6312,10 @@
         <v>242</v>
       </c>
       <c r="B117" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C117">
-        <v>0.3262151839943554</v>
+        <v>0.3289014561802077</v>
       </c>
       <c r="D117" t="s">
         <v>7</v>
@@ -6329,10 +6329,10 @@
         <v>244</v>
       </c>
       <c r="B118" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C118">
-        <v>0.371603608379141</v>
+        <v>0.3841110196040773</v>
       </c>
       <c r="D118" t="s">
         <v>7</v>
@@ -6346,10 +6346,10 @@
         <v>246</v>
       </c>
       <c r="B119" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C119">
-        <v>0.3062148405006058</v>
+        <v>0.3056840953028916</v>
       </c>
       <c r="D119" t="s">
         <v>7</v>
@@ -6363,10 +6363,10 @@
         <v>248</v>
       </c>
       <c r="B120" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C120">
-        <v>0.3945704846238975</v>
+        <v>0.4038345450098044</v>
       </c>
       <c r="D120" t="s">
         <v>7</v>
@@ -6383,7 +6383,7 @@
         <v>226</v>
       </c>
       <c r="C121">
-        <v>0.4040020188852858</v>
+        <v>0.3919252745247332</v>
       </c>
       <c r="D121" t="s">
         <v>7</v>
@@ -6400,7 +6400,7 @@
         <v>15</v>
       </c>
       <c r="C122">
-        <v>0.2986011485931875</v>
+        <v>0.297154099181397</v>
       </c>
       <c r="D122" t="s">
         <v>7</v>
@@ -6414,10 +6414,10 @@
         <v>254</v>
       </c>
       <c r="B123" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C123">
-        <v>0.2805335467014212</v>
+        <v>0.288969586567</v>
       </c>
       <c r="D123" t="s">
         <v>7</v>
@@ -6434,7 +6434,7 @@
         <v>15</v>
       </c>
       <c r="C124">
-        <v>0.3973796672227008</v>
+        <v>0.3982371077787633</v>
       </c>
       <c r="D124" t="s">
         <v>7</v>
@@ -6448,10 +6448,10 @@
         <v>258</v>
       </c>
       <c r="B125" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C125">
-        <v>0.3093046262825428</v>
+        <v>0.317294049704288</v>
       </c>
       <c r="D125" t="s">
         <v>7</v>
@@ -6465,10 +6465,10 @@
         <v>260</v>
       </c>
       <c r="B126" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C126">
-        <v>0.3674377051303651</v>
+        <v>0.3700894566887373</v>
       </c>
       <c r="D126" t="s">
         <v>7</v>
@@ -6482,10 +6482,10 @@
         <v>262</v>
       </c>
       <c r="B127" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C127">
-        <v>0.5051272082343499</v>
+        <v>0.4930912707997198</v>
       </c>
       <c r="D127" t="s">
         <v>7</v>
@@ -6502,7 +6502,7 @@
         <v>15</v>
       </c>
       <c r="C128">
-        <v>0.4211590078389102</v>
+        <v>0.42393076457509</v>
       </c>
       <c r="D128" t="s">
         <v>7</v>
@@ -6516,10 +6516,10 @@
         <v>266</v>
       </c>
       <c r="B129" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C129">
-        <v>0.2977698790689423</v>
+        <v>0.3065694278588164</v>
       </c>
       <c r="D129" t="s">
         <v>7</v>
@@ -6536,7 +6536,7 @@
         <v>15</v>
       </c>
       <c r="C130">
-        <v>0.3728898877885902</v>
+        <v>0.373537611066851</v>
       </c>
       <c r="D130" t="s">
         <v>7</v>
@@ -6550,10 +6550,10 @@
         <v>270</v>
       </c>
       <c r="B131" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C131">
-        <v>0.317599994994393</v>
+        <v>0.3248249580656742</v>
       </c>
       <c r="D131" t="s">
         <v>7</v>
@@ -6567,10 +6567,10 @@
         <v>272</v>
       </c>
       <c r="B132" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C132">
-        <v>0.3950841514323384</v>
+        <v>0.3854551274377275</v>
       </c>
       <c r="D132" t="s">
         <v>7</v>
@@ -6587,7 +6587,7 @@
         <v>15</v>
       </c>
       <c r="C133">
-        <v>0.3309702138758372</v>
+        <v>0.3293111251325738</v>
       </c>
       <c r="D133" t="s">
         <v>7</v>
@@ -6601,10 +6601,10 @@
         <v>276</v>
       </c>
       <c r="B134" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C134">
-        <v>0.3861496817019975</v>
+        <v>0.3741459464469846</v>
       </c>
       <c r="D134" t="s">
         <v>7</v>
@@ -6618,10 +6618,10 @@
         <v>278</v>
       </c>
       <c r="B135" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C135">
-        <v>0.4115825325600585</v>
+        <v>0.4058459461332418</v>
       </c>
       <c r="D135" t="s">
         <v>7</v>
@@ -6638,7 +6638,7 @@
         <v>44</v>
       </c>
       <c r="C136">
-        <v>0.3045595593335976</v>
+        <v>0.318438263932938</v>
       </c>
       <c r="D136" t="s">
         <v>7</v>
@@ -6652,10 +6652,10 @@
         <v>282</v>
       </c>
       <c r="B137" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C137">
-        <v>0.3983278223616713</v>
+        <v>0.395076628076451</v>
       </c>
       <c r="D137" t="s">
         <v>7</v>
@@ -6669,10 +6669,10 @@
         <v>284</v>
       </c>
       <c r="B138" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C138">
-        <v>0.328743021665892</v>
+        <v>0.322777715353354</v>
       </c>
       <c r="D138" t="s">
         <v>7</v>
@@ -6686,10 +6686,10 @@
         <v>286</v>
       </c>
       <c r="B139" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C139">
-        <v>0.4155945514927545</v>
+        <v>0.4112141671000881</v>
       </c>
       <c r="D139" t="s">
         <v>7</v>
@@ -6706,7 +6706,7 @@
         <v>44</v>
       </c>
       <c r="C140">
-        <v>0.3727404225766068</v>
+        <v>0.3789730015184242</v>
       </c>
       <c r="D140" t="s">
         <v>7</v>
@@ -6720,10 +6720,10 @@
         <v>290</v>
       </c>
       <c r="B141" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C141">
-        <v>0.3366462875829464</v>
+        <v>0.3303814238611743</v>
       </c>
       <c r="D141" t="s">
         <v>7</v>
@@ -6737,10 +6737,10 @@
         <v>292</v>
       </c>
       <c r="B142" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C142">
-        <v>0.4161472528743987</v>
+        <v>0.4170088771159847</v>
       </c>
       <c r="D142" t="s">
         <v>7</v>
@@ -6754,10 +6754,10 @@
         <v>294</v>
       </c>
       <c r="B143" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C143">
-        <v>0.3748839912079522</v>
+        <v>0.3700113834773755</v>
       </c>
       <c r="D143" t="s">
         <v>7</v>
@@ -6771,10 +6771,10 @@
         <v>296</v>
       </c>
       <c r="B144" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C144">
-        <v>0.6253298555327625</v>
+        <v>0.6139111706767413</v>
       </c>
       <c r="D144" t="s">
         <v>7</v>
@@ -6791,7 +6791,7 @@
         <v>6</v>
       </c>
       <c r="C145">
-        <v>0.3071638686153961</v>
+        <v>0.3096824277482824</v>
       </c>
       <c r="D145" t="s">
         <v>7</v>
@@ -6805,10 +6805,10 @@
         <v>300</v>
       </c>
       <c r="B146" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C146">
-        <v>0.4228321452366873</v>
+        <v>0.4165280354759018</v>
       </c>
       <c r="D146" t="s">
         <v>7</v>
@@ -6822,10 +6822,10 @@
         <v>302</v>
       </c>
       <c r="B147" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C147">
-        <v>0.4704922384946341</v>
+        <v>0.4634111937585345</v>
       </c>
       <c r="D147" t="s">
         <v>7</v>
@@ -6842,7 +6842,7 @@
         <v>6</v>
       </c>
       <c r="C148">
-        <v>0.3173058055945247</v>
+        <v>0.3123050992762109</v>
       </c>
       <c r="D148" t="s">
         <v>7</v>
@@ -6856,10 +6856,10 @@
         <v>306</v>
       </c>
       <c r="B149" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C149">
-        <v>0.41440188325174</v>
+        <v>0.4164312930699521</v>
       </c>
       <c r="D149" t="s">
         <v>7</v>
@@ -6873,10 +6873,10 @@
         <v>308</v>
       </c>
       <c r="B150" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C150">
-        <v>0.37295635314911</v>
+        <v>0.3703531189368181</v>
       </c>
       <c r="D150" t="s">
         <v>7</v>
@@ -6890,10 +6890,10 @@
         <v>310</v>
       </c>
       <c r="B151" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C151">
-        <v>0.2911850190859432</v>
+        <v>0.2982647963566956</v>
       </c>
       <c r="D151" t="s">
         <v>7</v>
@@ -6907,10 +6907,10 @@
         <v>312</v>
       </c>
       <c r="B152" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C152">
-        <v>0.6854815098442254</v>
+        <v>0.6755258994720322</v>
       </c>
       <c r="D152" t="s">
         <v>7</v>
@@ -6924,10 +6924,10 @@
         <v>314</v>
       </c>
       <c r="B153" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C153">
-        <v>0.3573458709770164</v>
+        <v>0.3571509981121045</v>
       </c>
       <c r="D153" t="s">
         <v>7</v>
@@ -6944,7 +6944,7 @@
         <v>44</v>
       </c>
       <c r="C154">
-        <v>0.3009019354564765</v>
+        <v>0.310209728695125</v>
       </c>
       <c r="D154" t="s">
         <v>7</v>
@@ -6958,10 +6958,10 @@
         <v>318</v>
       </c>
       <c r="B155" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C155">
-        <v>0.3149878441751549</v>
+        <v>0.3106131947894918</v>
       </c>
       <c r="D155" t="s">
         <v>7</v>
@@ -6975,10 +6975,10 @@
         <v>320</v>
       </c>
       <c r="B156" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C156">
-        <v>0.3641052565002296</v>
+        <v>0.3661321478512945</v>
       </c>
       <c r="D156" t="s">
         <v>7</v>
@@ -6992,10 +6992,10 @@
         <v>322</v>
       </c>
       <c r="B157" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C157">
-        <v>0.403490433487794</v>
+        <v>0.3985216450901836</v>
       </c>
       <c r="D157" t="s">
         <v>7</v>
@@ -7012,7 +7012,7 @@
         <v>44</v>
       </c>
       <c r="C158">
-        <v>0.3432306219241956</v>
+        <v>0.3562145985905591</v>
       </c>
       <c r="D158" t="s">
         <v>7</v>
@@ -7029,7 +7029,7 @@
         <v>44</v>
       </c>
       <c r="C159">
-        <v>0.3530135161095824</v>
+        <v>0.3668403050418066</v>
       </c>
       <c r="D159" t="s">
         <v>7</v>
@@ -7043,10 +7043,10 @@
         <v>328</v>
       </c>
       <c r="B160" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C160">
-        <v>0.3925031161201566</v>
+        <v>0.3867282818303553</v>
       </c>
       <c r="D160" t="s">
         <v>7</v>
@@ -7060,10 +7060,10 @@
         <v>330</v>
       </c>
       <c r="B161" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C161">
-        <v>0.4303852546416009</v>
+        <v>0.4235124378836009</v>
       </c>
       <c r="D161" t="s">
         <v>7</v>
@@ -7077,10 +7077,10 @@
         <v>332</v>
       </c>
       <c r="B162" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C162">
-        <v>0.4843358960395581</v>
+        <v>0.4789207006287615</v>
       </c>
       <c r="D162" t="s">
         <v>7</v>
@@ -7097,7 +7097,7 @@
         <v>44</v>
       </c>
       <c r="C163">
-        <v>0.4145367679244031</v>
+        <v>0.4238647745165507</v>
       </c>
       <c r="D163" t="s">
         <v>7</v>
@@ -7111,10 +7111,10 @@
         <v>336</v>
       </c>
       <c r="B164" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C164">
-        <v>0.3695107150322886</v>
+        <v>0.3805253370642712</v>
       </c>
       <c r="D164" t="s">
         <v>7</v>
@@ -7128,10 +7128,10 @@
         <v>338</v>
       </c>
       <c r="B165" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C165">
-        <v>0.4236425497200997</v>
+        <v>0.4304144426322573</v>
       </c>
       <c r="D165" t="s">
         <v>7</v>
@@ -7145,10 +7145,10 @@
         <v>340</v>
       </c>
       <c r="B166" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C166">
-        <v>0.3236257339030049</v>
+        <v>0.324406743724562</v>
       </c>
       <c r="D166" t="s">
         <v>7</v>
@@ -7162,10 +7162,10 @@
         <v>342</v>
       </c>
       <c r="B167" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C167">
-        <v>0.3742086049729496</v>
+        <v>0.3679957202474127</v>
       </c>
       <c r="D167" t="s">
         <v>7</v>
@@ -7179,10 +7179,10 @@
         <v>344</v>
       </c>
       <c r="B168" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C168">
-        <v>0.6150106411642421</v>
+        <v>0.6029641600788604</v>
       </c>
       <c r="D168" t="s">
         <v>7</v>
@@ -7196,10 +7196,10 @@
         <v>346</v>
       </c>
       <c r="B169" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C169">
-        <v>0.3315963515899743</v>
+        <v>0.3319421001088503</v>
       </c>
       <c r="D169" t="s">
         <v>7</v>
@@ -7213,10 +7213,10 @@
         <v>348</v>
       </c>
       <c r="B170" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C170">
-        <v>0.4006943012523375</v>
+        <v>0.3882854580707736</v>
       </c>
       <c r="D170" t="s">
         <v>7</v>
@@ -7230,10 +7230,10 @@
         <v>350</v>
       </c>
       <c r="B171" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C171">
-        <v>0.2728158993850646</v>
+        <v>0.2649887088475221</v>
       </c>
       <c r="D171" t="s">
         <v>7</v>
@@ -7247,10 +7247,10 @@
         <v>352</v>
       </c>
       <c r="B172" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C172">
-        <v>0.4301861626597795</v>
+        <v>0.4324987684988992</v>
       </c>
       <c r="D172" t="s">
         <v>7</v>
@@ -7264,10 +7264,10 @@
         <v>354</v>
       </c>
       <c r="B173" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C173">
-        <v>0.3069827417547709</v>
+        <v>0.3118539929789926</v>
       </c>
       <c r="D173" t="s">
         <v>7</v>
@@ -7284,7 +7284,7 @@
         <v>6</v>
       </c>
       <c r="C174">
-        <v>0.3219622696067413</v>
+        <v>0.3156690523752907</v>
       </c>
       <c r="D174" t="s">
         <v>7</v>
@@ -7301,7 +7301,7 @@
         <v>15</v>
       </c>
       <c r="C175">
-        <v>0.2981447765707583</v>
+        <v>0.2969311791829523</v>
       </c>
       <c r="D175" t="s">
         <v>7</v>
@@ -7315,10 +7315,10 @@
         <v>360</v>
       </c>
       <c r="B176" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C176">
-        <v>0.4257208291041155</v>
+        <v>0.4140382510536716</v>
       </c>
       <c r="D176" t="s">
         <v>7</v>
@@ -7332,10 +7332,10 @@
         <v>362</v>
       </c>
       <c r="B177" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C177">
-        <v>0.5207966364694654</v>
+        <v>0.5076271383222238</v>
       </c>
       <c r="D177" t="s">
         <v>7</v>
@@ -7352,7 +7352,7 @@
         <v>15</v>
       </c>
       <c r="C178">
-        <v>0.3908155845559856</v>
+        <v>0.3917641570466525</v>
       </c>
       <c r="D178" t="s">
         <v>7</v>
@@ -7369,7 +7369,7 @@
         <v>15</v>
       </c>
       <c r="C179">
-        <v>0.3039038267378681</v>
+        <v>0.3023685317276503</v>
       </c>
       <c r="D179" t="s">
         <v>7</v>
@@ -7386,7 +7386,7 @@
         <v>44</v>
       </c>
       <c r="C180">
-        <v>0.3092469294013674</v>
+        <v>0.3228136922406105</v>
       </c>
       <c r="D180" t="s">
         <v>7</v>
@@ -7403,7 +7403,7 @@
         <v>6</v>
       </c>
       <c r="C181">
-        <v>0.3370273759965562</v>
+        <v>0.3420660582925992</v>
       </c>
       <c r="D181" t="s">
         <v>7</v>
@@ -7417,10 +7417,10 @@
         <v>372</v>
       </c>
       <c r="B182" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C182">
-        <v>0.3153062097867892</v>
+        <v>0.3231323396080082</v>
       </c>
       <c r="D182" t="s">
         <v>7</v>
@@ -7434,10 +7434,10 @@
         <v>374</v>
       </c>
       <c r="B183" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C183">
-        <v>0.3279283552028656</v>
+        <v>0.3221780888269346</v>
       </c>
       <c r="D183" t="s">
         <v>7</v>
@@ -7451,10 +7451,10 @@
         <v>376</v>
       </c>
       <c r="B184" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C184">
-        <v>0.3672851410429261</v>
+        <v>0.3606439941129837</v>
       </c>
       <c r="D184" t="s">
         <v>7</v>
@@ -7468,10 +7468,10 @@
         <v>378</v>
       </c>
       <c r="B185" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C185">
-        <v>0.3713803036828084</v>
+        <v>0.383266512840537</v>
       </c>
       <c r="D185" t="s">
         <v>7</v>
@@ -7488,7 +7488,7 @@
         <v>44</v>
       </c>
       <c r="C186">
-        <v>0.3632551428773937</v>
+        <v>0.3758399667683893</v>
       </c>
       <c r="D186" t="s">
         <v>7</v>
@@ -7502,10 +7502,10 @@
         <v>382</v>
       </c>
       <c r="B187" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C187">
-        <v>0.2666468589599431</v>
+        <v>0.2740835232358662</v>
       </c>
       <c r="D187" t="s">
         <v>7</v>
@@ -7519,10 +7519,10 @@
         <v>384</v>
       </c>
       <c r="B188" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C188">
-        <v>0.4043022539197972</v>
+        <v>0.4020488380636786</v>
       </c>
       <c r="D188" t="s">
         <v>7</v>
@@ -7536,10 +7536,10 @@
         <v>386</v>
       </c>
       <c r="B189" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C189">
-        <v>0.3475212179830245</v>
+        <v>0.351108972399523</v>
       </c>
       <c r="D189" t="s">
         <v>7</v>
@@ -7553,10 +7553,10 @@
         <v>388</v>
       </c>
       <c r="B190" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C190">
-        <v>0.3194219121535341</v>
+        <v>0.3189423429184208</v>
       </c>
       <c r="D190" t="s">
         <v>7</v>
@@ -7570,10 +7570,10 @@
         <v>390</v>
       </c>
       <c r="B191" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C191">
-        <v>0.3498963904582731</v>
+        <v>0.3572512354173196</v>
       </c>
       <c r="D191" t="s">
         <v>7</v>
@@ -7590,7 +7590,7 @@
         <v>15</v>
       </c>
       <c r="C192">
-        <v>0.3985213438528357</v>
+        <v>0.3952942128039468</v>
       </c>
       <c r="D192" t="s">
         <v>7</v>
@@ -7607,7 +7607,7 @@
         <v>15</v>
       </c>
       <c r="C193">
-        <v>0.4189053263938315</v>
+        <v>0.4207534592886891</v>
       </c>
       <c r="D193" t="s">
         <v>7</v>
@@ -7624,7 +7624,7 @@
         <v>15</v>
       </c>
       <c r="C194">
-        <v>0.3602988950017231</v>
+        <v>0.3611133707764278</v>
       </c>
       <c r="D194" t="s">
         <v>7</v>
@@ -7641,7 +7641,7 @@
         <v>226</v>
       </c>
       <c r="C195">
-        <v>0.4876948436150666</v>
+        <v>0.4805555899282046</v>
       </c>
       <c r="D195" t="s">
         <v>7</v>
@@ -7655,10 +7655,10 @@
         <v>400</v>
       </c>
       <c r="B196" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C196">
-        <v>0.397352910218861</v>
+        <v>0.3893448544353938</v>
       </c>
       <c r="D196" t="s">
         <v>7</v>
@@ -7672,10 +7672,10 @@
         <v>402</v>
       </c>
       <c r="B197" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C197">
-        <v>0.3313368505677494</v>
+        <v>0.3363439892618814</v>
       </c>
       <c r="D197" t="s">
         <v>7</v>
@@ -7689,10 +7689,10 @@
         <v>404</v>
       </c>
       <c r="B198" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C198">
-        <v>0.5259849140997427</v>
+        <v>0.5250913022696641</v>
       </c>
       <c r="D198" t="s">
         <v>7</v>
@@ -7706,10 +7706,10 @@
         <v>406</v>
       </c>
       <c r="B199" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C199">
-        <v>0.6198655938653765</v>
+        <v>0.6090576680160146</v>
       </c>
       <c r="D199" t="s">
         <v>7</v>
@@ -7723,10 +7723,10 @@
         <v>408</v>
       </c>
       <c r="B200" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C200">
-        <v>0.3200997819819573</v>
+        <v>0.3238718047220134</v>
       </c>
       <c r="D200" t="s">
         <v>7</v>
@@ -7743,7 +7743,7 @@
         <v>15</v>
       </c>
       <c r="C201">
-        <v>0.3119689467489691</v>
+        <v>0.3110074423081757</v>
       </c>
       <c r="D201" t="s">
         <v>7</v>
@@ -7757,10 +7757,10 @@
         <v>412</v>
       </c>
       <c r="B202" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C202">
-        <v>0.3706752094597894</v>
+        <v>0.3768181205767128</v>
       </c>
       <c r="D202" t="s">
         <v>7</v>
@@ -7774,10 +7774,10 @@
         <v>414</v>
       </c>
       <c r="B203" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C203">
-        <v>0.5577967472348307</v>
+        <v>0.545019131233511</v>
       </c>
       <c r="D203" t="s">
         <v>7</v>
@@ -7791,10 +7791,10 @@
         <v>416</v>
       </c>
       <c r="B204" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C204">
-        <v>0.4935176810108449</v>
+        <v>0.4871472232359261</v>
       </c>
       <c r="D204" t="s">
         <v>7</v>
@@ -7808,10 +7808,10 @@
         <v>418</v>
       </c>
       <c r="B205" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C205">
-        <v>0.4524538914960979</v>
+        <v>0.4529004704231175</v>
       </c>
       <c r="D205" t="s">
         <v>7</v>
@@ -7828,7 +7828,7 @@
         <v>15</v>
       </c>
       <c r="C206">
-        <v>0.3474082894455316</v>
+        <v>0.3459583984910837</v>
       </c>
       <c r="D206" t="s">
         <v>7</v>
@@ -7845,7 +7845,7 @@
         <v>44</v>
       </c>
       <c r="C207">
-        <v>0.5223916900359824</v>
+        <v>0.525014847445017</v>
       </c>
       <c r="D207" t="s">
         <v>7</v>
@@ -7859,10 +7859,10 @@
         <v>424</v>
       </c>
       <c r="B208" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C208">
-        <v>0.349775881726774</v>
+        <v>0.3491440762669842</v>
       </c>
       <c r="D208" t="s">
         <v>7</v>
@@ -7876,10 +7876,10 @@
         <v>426</v>
       </c>
       <c r="B209" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C209">
-        <v>0.5540935968920363</v>
+        <v>0.5591809022034547</v>
       </c>
       <c r="D209" t="s">
         <v>7</v>
@@ -7893,10 +7893,10 @@
         <v>428</v>
       </c>
       <c r="B210" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C210">
-        <v>0.4436557348994326</v>
+        <v>0.430154122076351</v>
       </c>
       <c r="D210" t="s">
         <v>7</v>
@@ -7913,7 +7913,7 @@
         <v>15</v>
       </c>
       <c r="C211">
-        <v>0.4596190445075198</v>
+        <v>0.4610431633404332</v>
       </c>
       <c r="D211" t="s">
         <v>7</v>
@@ -7927,10 +7927,10 @@
         <v>432</v>
       </c>
       <c r="B212" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C212">
-        <v>0.2903848094194069</v>
+        <v>0.297700045340252</v>
       </c>
       <c r="D212" t="s">
         <v>7</v>
@@ -7944,10 +7944,10 @@
         <v>434</v>
       </c>
       <c r="B213" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C213">
-        <v>0.3285330114357485</v>
+        <v>0.3372333962843071</v>
       </c>
       <c r="D213" t="s">
         <v>7</v>
@@ -7964,7 +7964,7 @@
         <v>15</v>
       </c>
       <c r="C214">
-        <v>0.368225607786905</v>
+        <v>0.3686238658534763</v>
       </c>
       <c r="D214" t="s">
         <v>7</v>
@@ -7978,10 +7978,10 @@
         <v>438</v>
       </c>
       <c r="B215" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C215">
-        <v>0.5199946643189131</v>
+        <v>0.5293467249721576</v>
       </c>
       <c r="D215" t="s">
         <v>7</v>
@@ -7998,7 +7998,7 @@
         <v>15</v>
       </c>
       <c r="C216">
-        <v>0.3300072259854918</v>
+        <v>0.326166220131468</v>
       </c>
       <c r="D216" t="s">
         <v>7</v>
@@ -8012,10 +8012,10 @@
         <v>442</v>
       </c>
       <c r="B217" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C217">
-        <v>0.3286213185113728</v>
+        <v>0.3356798173357969</v>
       </c>
       <c r="D217" t="s">
         <v>7</v>
@@ -8029,10 +8029,10 @@
         <v>444</v>
       </c>
       <c r="B218" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C218">
-        <v>0.3699225608053016</v>
+        <v>0.3726034258854494</v>
       </c>
       <c r="D218" t="s">
         <v>7</v>
@@ -8049,7 +8049,7 @@
         <v>44</v>
       </c>
       <c r="C219">
-        <v>0.4567566060103629</v>
+        <v>0.4600069042488924</v>
       </c>
       <c r="D219" t="s">
         <v>7</v>
@@ -8063,10 +8063,10 @@
         <v>448</v>
       </c>
       <c r="B220" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C220">
-        <v>0.2998494527999482</v>
+        <v>0.300470037053787</v>
       </c>
       <c r="D220" t="s">
         <v>7</v>
@@ -8083,7 +8083,7 @@
         <v>15</v>
       </c>
       <c r="C221">
-        <v>0.3755365900476916</v>
+        <v>0.3732605312279292</v>
       </c>
       <c r="D221" t="s">
         <v>7</v>
@@ -8097,10 +8097,10 @@
         <v>452</v>
       </c>
       <c r="B222" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C222">
-        <v>0.3256179394527048</v>
+        <v>0.3304458792688951</v>
       </c>
       <c r="D222" t="s">
         <v>7</v>
@@ -8114,10 +8114,10 @@
         <v>454</v>
       </c>
       <c r="B223" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C223">
-        <v>0.4916017964309926</v>
+        <v>0.4955663073052685</v>
       </c>
       <c r="D223" t="s">
         <v>7</v>
@@ -8131,10 +8131,10 @@
         <v>456</v>
       </c>
       <c r="B224" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C224">
-        <v>0.3175977909587966</v>
+        <v>0.3253723015059947</v>
       </c>
       <c r="D224" t="s">
         <v>7</v>
@@ -8151,7 +8151,7 @@
         <v>15</v>
       </c>
       <c r="C225">
-        <v>0.355710684772941</v>
+        <v>0.3547865234927187</v>
       </c>
       <c r="D225" t="s">
         <v>7</v>
@@ -8165,10 +8165,10 @@
         <v>460</v>
       </c>
       <c r="B226" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C226">
-        <v>0.5098558094040082</v>
+        <v>0.4989632808565369</v>
       </c>
       <c r="D226" t="s">
         <v>7</v>
@@ -8182,10 +8182,10 @@
         <v>462</v>
       </c>
       <c r="B227" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C227">
-        <v>0.3402708333816193</v>
+        <v>0.3439745747638348</v>
       </c>
       <c r="D227" t="s">
         <v>7</v>
@@ -8199,10 +8199,10 @@
         <v>464</v>
       </c>
       <c r="B228" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C228">
-        <v>0.5096666150562001</v>
+        <v>0.4960476624231919</v>
       </c>
       <c r="D228" t="s">
         <v>7</v>
@@ -8216,10 +8216,10 @@
         <v>466</v>
       </c>
       <c r="B229" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C229">
-        <v>0.5869695173244037</v>
+        <v>0.5740146128197484</v>
       </c>
       <c r="D229" t="s">
         <v>7</v>
@@ -8236,7 +8236,7 @@
         <v>44</v>
       </c>
       <c r="C230">
-        <v>0.3143634279980685</v>
+        <v>0.3232419777951397</v>
       </c>
       <c r="D230" t="s">
         <v>7</v>
@@ -8253,7 +8253,7 @@
         <v>6</v>
       </c>
       <c r="C231">
-        <v>0.3309048943425693</v>
+        <v>0.3325102397728656</v>
       </c>
       <c r="D231" t="s">
         <v>7</v>
@@ -8267,10 +8267,10 @@
         <v>472</v>
       </c>
       <c r="B232" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C232">
-        <v>0.609806910007668</v>
+        <v>0.5961901385703038</v>
       </c>
       <c r="D232" t="s">
         <v>7</v>
@@ -8287,7 +8287,7 @@
         <v>44</v>
       </c>
       <c r="C233">
-        <v>0.3803083588821951</v>
+        <v>0.3921532301576182</v>
       </c>
       <c r="D233" t="s">
         <v>7</v>
@@ -8301,10 +8301,10 @@
         <v>476</v>
       </c>
       <c r="B234" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C234">
-        <v>0.4452532161403751</v>
+        <v>0.4442591991261273</v>
       </c>
       <c r="D234" t="s">
         <v>7</v>
@@ -8318,10 +8318,10 @@
         <v>478</v>
       </c>
       <c r="B235" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C235">
-        <v>0.5204748547363988</v>
+        <v>0.5141795336025841</v>
       </c>
       <c r="D235" t="s">
         <v>7</v>
@@ -8335,10 +8335,10 @@
         <v>480</v>
       </c>
       <c r="B236" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C236">
-        <v>0.3112944095678405</v>
+        <v>0.3043959123424687</v>
       </c>
       <c r="D236" t="s">
         <v>7</v>
@@ -8352,10 +8352,10 @@
         <v>482</v>
       </c>
       <c r="B237" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C237">
-        <v>0.3255041924281766</v>
+        <v>0.3139800576799208</v>
       </c>
       <c r="D237" t="s">
         <v>7</v>
@@ -8369,10 +8369,10 @@
         <v>484</v>
       </c>
       <c r="B238" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C238">
-        <v>0.3734264486235567</v>
+        <v>0.3725061754414346</v>
       </c>
       <c r="D238" t="s">
         <v>7</v>
@@ -8386,10 +8386,10 @@
         <v>486</v>
       </c>
       <c r="B239" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C239">
-        <v>0.4598985968203674</v>
+        <v>0.4478244417033663</v>
       </c>
       <c r="D239" t="s">
         <v>7</v>
@@ -8406,7 +8406,7 @@
         <v>226</v>
       </c>
       <c r="C240">
-        <v>0.3508750481198449</v>
+        <v>0.3363554272917126</v>
       </c>
       <c r="D240" t="s">
         <v>7</v>
@@ -8420,10 +8420,10 @@
         <v>490</v>
       </c>
       <c r="B241" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C241">
-        <v>0.2702014474003883</v>
+        <v>0.2771312473870947</v>
       </c>
       <c r="D241" t="s">
         <v>7</v>
@@ -8437,10 +8437,10 @@
         <v>492</v>
       </c>
       <c r="B242" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C242">
-        <v>0.3398097766157385</v>
+        <v>0.3344103253860502</v>
       </c>
       <c r="D242" t="s">
         <v>7</v>
@@ -8457,7 +8457,7 @@
         <v>15</v>
       </c>
       <c r="C243">
-        <v>0.4877598077355441</v>
+        <v>0.4894561831172544</v>
       </c>
       <c r="D243" t="s">
         <v>7</v>
@@ -8474,7 +8474,7 @@
         <v>226</v>
       </c>
       <c r="C244">
-        <v>0.4728371520755983</v>
+        <v>0.4690826283287785</v>
       </c>
       <c r="D244" t="s">
         <v>7</v>
@@ -8488,10 +8488,10 @@
         <v>498</v>
       </c>
       <c r="B245" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C245">
-        <v>0.65081428977905</v>
+        <v>0.6388834121511222</v>
       </c>
       <c r="D245" t="s">
         <v>7</v>
@@ -8505,10 +8505,10 @@
         <v>500</v>
       </c>
       <c r="B246" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C246">
-        <v>0.4667635832177167</v>
+        <v>0.4632827918000617</v>
       </c>
       <c r="D246" t="s">
         <v>7</v>
@@ -8522,10 +8522,10 @@
         <v>502</v>
       </c>
       <c r="B247" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C247">
-        <v>0.4199672474976888</v>
+        <v>0.4086384268150137</v>
       </c>
       <c r="D247" t="s">
         <v>7</v>
@@ -8539,10 +8539,10 @@
         <v>504</v>
       </c>
       <c r="B248" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C248">
-        <v>0.3290617548138802</v>
+        <v>0.3347139154425993</v>
       </c>
       <c r="D248" t="s">
         <v>7</v>
@@ -8556,10 +8556,10 @@
         <v>506</v>
       </c>
       <c r="B249" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C249">
-        <v>0.447621384986058</v>
+        <v>0.4399463396498191</v>
       </c>
       <c r="D249" t="s">
         <v>7</v>
@@ -8576,7 +8576,7 @@
         <v>15</v>
       </c>
       <c r="C250">
-        <v>0.3129666575902855</v>
+        <v>0.3108943649895647</v>
       </c>
       <c r="D250" t="s">
         <v>7</v>
@@ -8593,7 +8593,7 @@
         <v>44</v>
       </c>
       <c r="C251">
-        <v>0.4804261793244737</v>
+        <v>0.4828932584431646</v>
       </c>
       <c r="D251" t="s">
         <v>7</v>
@@ -8607,10 +8607,10 @@
         <v>512</v>
       </c>
       <c r="B252" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C252">
-        <v>0.4287692698783986</v>
+        <v>0.4219148622878776</v>
       </c>
       <c r="D252" t="s">
         <v>7</v>
@@ -8624,10 +8624,10 @@
         <v>514</v>
       </c>
       <c r="B253" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C253">
-        <v>0.3795565665945869</v>
+        <v>0.3745798689777225</v>
       </c>
       <c r="D253" t="s">
         <v>7</v>
@@ -8641,10 +8641,10 @@
         <v>516</v>
       </c>
       <c r="B254" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C254">
-        <v>0.5065610833141485</v>
+        <v>0.4956924595813771</v>
       </c>
       <c r="D254" t="s">
         <v>7</v>
@@ -8661,7 +8661,7 @@
         <v>15</v>
       </c>
       <c r="C255">
-        <v>0.4437598464367363</v>
+        <v>0.4438909051870091</v>
       </c>
       <c r="D255" t="s">
         <v>7</v>
@@ -8675,10 +8675,10 @@
         <v>520</v>
       </c>
       <c r="B256" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C256">
-        <v>0.6080766524201341</v>
+        <v>0.6087668283538009</v>
       </c>
       <c r="D256" t="s">
         <v>7</v>
@@ -8692,10 +8692,10 @@
         <v>522</v>
       </c>
       <c r="B257" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C257">
-        <v>0.4249197561162011</v>
+        <v>0.4183369032543381</v>
       </c>
       <c r="D257" t="s">
         <v>7</v>
@@ -8709,10 +8709,10 @@
         <v>524</v>
       </c>
       <c r="B258" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C258">
-        <v>0.529280319363115</v>
+        <v>0.516755238693733</v>
       </c>
       <c r="D258" t="s">
         <v>7</v>
@@ -8726,10 +8726,10 @@
         <v>526</v>
       </c>
       <c r="B259" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C259">
-        <v>0.2957785310832267</v>
+        <v>0.2945920911980119</v>
       </c>
       <c r="D259" t="s">
         <v>7</v>
@@ -8743,10 +8743,10 @@
         <v>528</v>
       </c>
       <c r="B260" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C260">
-        <v>0.4514977521541865</v>
+        <v>0.4427673260424204</v>
       </c>
       <c r="D260" t="s">
         <v>7</v>
@@ -8760,10 +8760,10 @@
         <v>530</v>
       </c>
       <c r="B261" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C261">
-        <v>0.5010860645073553</v>
+        <v>0.4888573304692178</v>
       </c>
       <c r="D261" t="s">
         <v>7</v>
@@ -8777,10 +8777,10 @@
         <v>532</v>
       </c>
       <c r="B262" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C262">
-        <v>0.4478489379716189</v>
+        <v>0.4431848308489289</v>
       </c>
       <c r="D262" t="s">
         <v>7</v>
@@ -8794,10 +8794,10 @@
         <v>534</v>
       </c>
       <c r="B263" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C263">
-        <v>0.4777106254914819</v>
+        <v>0.4727052627242979</v>
       </c>
       <c r="D263" t="s">
         <v>7</v>
@@ -8811,10 +8811,10 @@
         <v>536</v>
       </c>
       <c r="B264" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C264">
-        <v>0.4585712085471118</v>
+        <v>0.4560859743915858</v>
       </c>
       <c r="D264" t="s">
         <v>7</v>
@@ -8828,10 +8828,10 @@
         <v>538</v>
       </c>
       <c r="B265" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C265">
-        <v>0.3620689568234249</v>
+        <v>0.3577478590607062</v>
       </c>
       <c r="D265" t="s">
         <v>7</v>
@@ -8845,10 +8845,10 @@
         <v>540</v>
       </c>
       <c r="B266" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C266">
-        <v>0.4125403999083336</v>
+        <v>0.4094555758836149</v>
       </c>
       <c r="D266" t="s">
         <v>7</v>
@@ -8862,10 +8862,10 @@
         <v>542</v>
       </c>
       <c r="B267" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C267">
-        <v>0.2901382802972959</v>
+        <v>0.2854732998867289</v>
       </c>
       <c r="D267" t="s">
         <v>7</v>
@@ -8879,10 +8879,10 @@
         <v>544</v>
       </c>
       <c r="B268" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C268">
-        <v>0.4675297326835262</v>
+        <v>0.4620145993075376</v>
       </c>
       <c r="D268" t="s">
         <v>7</v>
@@ -8899,7 +8899,7 @@
         <v>44</v>
       </c>
       <c r="C269">
-        <v>0.3477321159604124</v>
+        <v>0.3616701276519387</v>
       </c>
       <c r="D269" t="s">
         <v>7</v>
@@ -8913,10 +8913,10 @@
         <v>548</v>
       </c>
       <c r="B270" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C270">
-        <v>0.5546453758137778</v>
+        <v>0.5424573513620763</v>
       </c>
       <c r="D270" t="s">
         <v>7</v>
@@ -8930,10 +8930,10 @@
         <v>550</v>
       </c>
       <c r="B271" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C271">
-        <v>0.5671463265124537</v>
+        <v>0.5552207054010903</v>
       </c>
       <c r="D271" t="s">
         <v>7</v>
@@ -8947,10 +8947,10 @@
         <v>552</v>
       </c>
       <c r="B272" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C272">
-        <v>0.4023049974648862</v>
+        <v>0.3949784079602809</v>
       </c>
       <c r="D272" t="s">
         <v>7</v>
@@ -8964,10 +8964,10 @@
         <v>554</v>
       </c>
       <c r="B273" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C273">
-        <v>0.5505573909906667</v>
+        <v>0.5378209354970783</v>
       </c>
       <c r="D273" t="s">
         <v>7</v>
@@ -8984,7 +8984,7 @@
         <v>15</v>
       </c>
       <c r="C274">
-        <v>0.3534092180518709</v>
+        <v>0.3459801749803365</v>
       </c>
       <c r="D274" t="s">
         <v>7</v>
@@ -8998,10 +8998,10 @@
         <v>558</v>
       </c>
       <c r="B275" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C275">
-        <v>0.2711153059839895</v>
+        <v>0.2799615587568567</v>
       </c>
       <c r="D275" t="s">
         <v>7</v>
@@ -9015,10 +9015,10 @@
         <v>560</v>
       </c>
       <c r="B276" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C276">
-        <v>0.3323720101875601</v>
+        <v>0.3288146300284943</v>
       </c>
       <c r="D276" t="s">
         <v>7</v>
@@ -9032,10 +9032,10 @@
         <v>562</v>
       </c>
       <c r="B277" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C277">
-        <v>0.3965443889570791</v>
+        <v>0.393093540731229</v>
       </c>
       <c r="D277" t="s">
         <v>7</v>
@@ -9049,10 +9049,10 @@
         <v>564</v>
       </c>
       <c r="B278" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C278">
-        <v>0.4537653092004412</v>
+        <v>0.4547408734503038</v>
       </c>
       <c r="D278" t="s">
         <v>7</v>
@@ -9066,10 +9066,10 @@
         <v>566</v>
       </c>
       <c r="B279" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C279">
-        <v>0.5730123313903677</v>
+        <v>0.5594984869500769</v>
       </c>
       <c r="D279" t="s">
         <v>7</v>
@@ -9083,10 +9083,10 @@
         <v>568</v>
       </c>
       <c r="B280" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C280">
-        <v>0.5090987795517588</v>
+        <v>0.5075583053011297</v>
       </c>
       <c r="D280" t="s">
         <v>7</v>
@@ -9100,10 +9100,10 @@
         <v>570</v>
       </c>
       <c r="B281" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C281">
-        <v>0.4117751331643119</v>
+        <v>0.4000032660882443</v>
       </c>
       <c r="D281" t="s">
         <v>7</v>
@@ -9120,7 +9120,7 @@
         <v>15</v>
       </c>
       <c r="C282">
-        <v>0.36422735662484</v>
+        <v>0.3619094526791173</v>
       </c>
       <c r="D282" t="s">
         <v>7</v>
@@ -9134,10 +9134,10 @@
         <v>574</v>
       </c>
       <c r="B283" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C283">
-        <v>0.3598807386659951</v>
+        <v>0.3585060966853886</v>
       </c>
       <c r="D283" t="s">
         <v>7</v>
@@ -9151,10 +9151,10 @@
         <v>576</v>
       </c>
       <c r="B284" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C284">
-        <v>0.3495258447783943</v>
+        <v>0.3424898239964088</v>
       </c>
       <c r="D284" t="s">
         <v>7</v>
@@ -9168,10 +9168,10 @@
         <v>578</v>
       </c>
       <c r="B285" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C285">
-        <v>0.2647580123484087</v>
+        <v>0.2758562475742407</v>
       </c>
       <c r="D285" t="s">
         <v>7</v>
@@ -9185,10 +9185,10 @@
         <v>580</v>
       </c>
       <c r="B286" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C286">
-        <v>0.3130828627710331</v>
+        <v>0.3075003878695524</v>
       </c>
       <c r="D286" t="s">
         <v>7</v>
@@ -9205,7 +9205,7 @@
         <v>44</v>
       </c>
       <c r="C287">
-        <v>0.4546383690506665</v>
+        <v>0.4577307774082736</v>
       </c>
       <c r="D287" t="s">
         <v>7</v>
@@ -9219,10 +9219,10 @@
         <v>584</v>
       </c>
       <c r="B288" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C288">
-        <v>0.292136073961054</v>
+        <v>0.2842558035868035</v>
       </c>
       <c r="D288" t="s">
         <v>7</v>
@@ -9236,10 +9236,10 @@
         <v>586</v>
       </c>
       <c r="B289" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C289">
-        <v>0.3850521685445955</v>
+        <v>0.3805903261546035</v>
       </c>
       <c r="D289" t="s">
         <v>7</v>
@@ -9253,10 +9253,10 @@
         <v>588</v>
       </c>
       <c r="B290" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C290">
-        <v>0.3152092281061221</v>
+        <v>0.3142537434840742</v>
       </c>
       <c r="D290" t="s">
         <v>7</v>
@@ -9270,10 +9270,10 @@
         <v>590</v>
       </c>
       <c r="B291" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C291">
-        <v>0.4528700627120865</v>
+        <v>0.4475573889342771</v>
       </c>
       <c r="D291" t="s">
         <v>7</v>
@@ -9290,7 +9290,7 @@
         <v>145</v>
       </c>
       <c r="C292">
-        <v>0.414793173055129</v>
+        <v>0.4188178531073534</v>
       </c>
       <c r="D292" t="s">
         <v>7</v>
@@ -9304,10 +9304,10 @@
         <v>594</v>
       </c>
       <c r="B293" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C293">
-        <v>0.6324562399616352</v>
+        <v>0.6199535925483386</v>
       </c>
       <c r="D293" t="s">
         <v>7</v>
@@ -9324,7 +9324,7 @@
         <v>15</v>
       </c>
       <c r="C294">
-        <v>0.3994341138156789</v>
+        <v>0.4006998119628482</v>
       </c>
       <c r="D294" t="s">
         <v>7</v>
@@ -9338,10 +9338,10 @@
         <v>598</v>
       </c>
       <c r="B295" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C295">
-        <v>0.3525385591116728</v>
+        <v>0.357556431388483</v>
       </c>
       <c r="D295" t="s">
         <v>7</v>
@@ -9358,7 +9358,7 @@
         <v>15</v>
       </c>
       <c r="C296">
-        <v>0.3101319861299852</v>
+        <v>0.3072856354710736</v>
       </c>
       <c r="D296" t="s">
         <v>7</v>
@@ -9372,10 +9372,10 @@
         <v>602</v>
       </c>
       <c r="B297" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C297">
-        <v>0.4809445272049341</v>
+        <v>0.4834244125491446</v>
       </c>
       <c r="D297" t="s">
         <v>7</v>
@@ -9389,10 +9389,10 @@
         <v>604</v>
       </c>
       <c r="B298" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C298">
-        <v>0.4203211766388632</v>
+        <v>0.4224353090087663</v>
       </c>
       <c r="D298" t="s">
         <v>7</v>
@@ -9406,10 +9406,10 @@
         <v>606</v>
       </c>
       <c r="B299" t="s">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="C299">
-        <v>0.2525275085242315</v>
+        <v>0.2596400393061148</v>
       </c>
       <c r="D299" t="s">
         <v>7</v>
@@ -9423,10 +9423,10 @@
         <v>608</v>
       </c>
       <c r="B300" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C300">
-        <v>0.3457330786706065</v>
+        <v>0.3549201831746485</v>
       </c>
       <c r="D300" t="s">
         <v>7</v>
@@ -9440,10 +9440,10 @@
         <v>610</v>
       </c>
       <c r="B301" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C301">
-        <v>0.374796308749854</v>
+        <v>0.3676509654455384</v>
       </c>
       <c r="D301" t="s">
         <v>7</v>
@@ -9460,7 +9460,7 @@
         <v>44</v>
       </c>
       <c r="C302">
-        <v>0.4498639441849994</v>
+        <v>0.4539550398077981</v>
       </c>
       <c r="D302" t="s">
         <v>7</v>
@@ -9474,10 +9474,10 @@
         <v>614</v>
       </c>
       <c r="B303" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C303">
-        <v>0.3357070198129143</v>
+        <v>0.3395507508774431</v>
       </c>
       <c r="D303" t="s">
         <v>7</v>
@@ -9491,10 +9491,10 @@
         <v>616</v>
       </c>
       <c r="B304" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C304">
-        <v>0.3219079767844323</v>
+        <v>0.3302793622772512</v>
       </c>
       <c r="D304" t="s">
         <v>7</v>
@@ -9511,7 +9511,7 @@
         <v>44</v>
       </c>
       <c r="C305">
-        <v>0.3777082407553171</v>
+        <v>0.3899101467867369</v>
       </c>
       <c r="D305" t="s">
         <v>7</v>
@@ -9528,7 +9528,7 @@
         <v>15</v>
       </c>
       <c r="C306">
-        <v>0.4240596334073203</v>
+        <v>0.4260592303994008</v>
       </c>
       <c r="D306" t="s">
         <v>7</v>
@@ -9542,10 +9542,10 @@
         <v>622</v>
       </c>
       <c r="B307" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C307">
-        <v>0.4365900647086667</v>
+        <v>0.4256617247791599</v>
       </c>
       <c r="D307" t="s">
         <v>7</v>
@@ -9559,10 +9559,10 @@
         <v>624</v>
       </c>
       <c r="B308" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C308">
-        <v>0.4084740061893299</v>
+        <v>0.4026787325556452</v>
       </c>
       <c r="D308" t="s">
         <v>7</v>
@@ -9576,10 +9576,10 @@
         <v>626</v>
       </c>
       <c r="B309" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C309">
-        <v>0.2921327744706865</v>
+        <v>0.2850741120128562</v>
       </c>
       <c r="D309" t="s">
         <v>7</v>
@@ -9593,10 +9593,10 @@
         <v>628</v>
       </c>
       <c r="B310" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C310">
-        <v>0.4338250681571506</v>
+        <v>0.4195818717609271</v>
       </c>
       <c r="D310" t="s">
         <v>7</v>
@@ -9613,7 +9613,7 @@
         <v>15</v>
       </c>
       <c r="C311">
-        <v>0.3477327182526064</v>
+        <v>0.3471516841970048</v>
       </c>
       <c r="D311" t="s">
         <v>7</v>
@@ -9630,7 +9630,7 @@
         <v>15</v>
       </c>
       <c r="C312">
-        <v>0.2706394046624557</v>
+        <v>0.2684067613133689</v>
       </c>
       <c r="D312" t="s">
         <v>7</v>
@@ -9647,7 +9647,7 @@
         <v>44</v>
       </c>
       <c r="C313">
-        <v>0.287370407743457</v>
+        <v>0.3013203362121963</v>
       </c>
       <c r="D313" t="s">
         <v>7</v>
@@ -9661,10 +9661,10 @@
         <v>636</v>
       </c>
       <c r="B314" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C314">
-        <v>0.3250439135133066</v>
+        <v>0.3325296493460294</v>
       </c>
       <c r="D314" t="s">
         <v>7</v>
@@ -9681,7 +9681,7 @@
         <v>44</v>
       </c>
       <c r="C315">
-        <v>0.4883115976894868</v>
+        <v>0.4925793111776408</v>
       </c>
       <c r="D315" t="s">
         <v>7</v>
@@ -9695,10 +9695,10 @@
         <v>640</v>
       </c>
       <c r="B316" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C316">
-        <v>0.4055949695332535</v>
+        <v>0.4006215411480921</v>
       </c>
       <c r="D316" t="s">
         <v>7</v>
@@ -9712,10 +9712,10 @@
         <v>642</v>
       </c>
       <c r="B317" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C317">
-        <v>0.5490350181408492</v>
+        <v>0.5429454594963393</v>
       </c>
       <c r="D317" t="s">
         <v>7</v>
@@ -9729,10 +9729,10 @@
         <v>644</v>
       </c>
       <c r="B318" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C318">
-        <v>0.5785395088991326</v>
+        <v>0.565797919966618</v>
       </c>
       <c r="D318" t="s">
         <v>7</v>
@@ -9746,10 +9746,10 @@
         <v>646</v>
       </c>
       <c r="B319" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C319">
-        <v>0.361478844952316</v>
+        <v>0.3551841405255953</v>
       </c>
       <c r="D319" t="s">
         <v>7</v>
@@ -9763,10 +9763,10 @@
         <v>648</v>
       </c>
       <c r="B320" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C320">
-        <v>0.2959217611185436</v>
+        <v>0.3023756815398353</v>
       </c>
       <c r="D320" t="s">
         <v>7</v>
@@ -9780,10 +9780,10 @@
         <v>650</v>
       </c>
       <c r="B321" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C321">
-        <v>0.3642419198591766</v>
+        <v>0.3599395599942822</v>
       </c>
       <c r="D321" t="s">
         <v>7</v>
@@ -9797,10 +9797,10 @@
         <v>652</v>
       </c>
       <c r="B322" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C322">
-        <v>0.3926201961377123</v>
+        <v>0.3882002755807427</v>
       </c>
       <c r="D322" t="s">
         <v>7</v>
@@ -9814,10 +9814,10 @@
         <v>654</v>
       </c>
       <c r="B323" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C323">
-        <v>0.3439760893357556</v>
+        <v>0.3485196695504432</v>
       </c>
       <c r="D323" t="s">
         <v>7</v>
@@ -9834,7 +9834,7 @@
         <v>44</v>
       </c>
       <c r="C324">
-        <v>0.3803089202655562</v>
+        <v>0.3936611525956747</v>
       </c>
       <c r="D324" t="s">
         <v>7</v>
@@ -9851,7 +9851,7 @@
         <v>6</v>
       </c>
       <c r="C325">
-        <v>0.2356707564721991</v>
+        <v>0.2336239379331035</v>
       </c>
       <c r="D325" t="s">
         <v>7</v>
@@ -9868,7 +9868,7 @@
         <v>44</v>
       </c>
       <c r="C326">
-        <v>0.3412742220266851</v>
+        <v>0.3533378653295376</v>
       </c>
       <c r="D326" t="s">
         <v>7</v>
@@ -9885,7 +9885,7 @@
         <v>44</v>
       </c>
       <c r="C327">
-        <v>0.2986428417011702</v>
+        <v>0.3077809733377868</v>
       </c>
       <c r="D327" t="s">
         <v>7</v>
@@ -9899,10 +9899,10 @@
         <v>664</v>
       </c>
       <c r="B328" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C328">
-        <v>0.2905223787049353</v>
+        <v>0.2848862094758736</v>
       </c>
       <c r="D328" t="s">
         <v>7</v>
@@ -9916,10 +9916,10 @@
         <v>666</v>
       </c>
       <c r="B329" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C329">
-        <v>0.312506700721436</v>
+        <v>0.3212302222272556</v>
       </c>
       <c r="D329" t="s">
         <v>7</v>
@@ -9936,7 +9936,7 @@
         <v>15</v>
       </c>
       <c r="C330">
-        <v>0.3126188384613264</v>
+        <v>0.3130824383530552</v>
       </c>
       <c r="D330" t="s">
         <v>7</v>
@@ -9950,10 +9950,10 @@
         <v>670</v>
       </c>
       <c r="B331" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C331">
-        <v>0.3846870667603166</v>
+        <v>0.3910052068664205</v>
       </c>
       <c r="D331" t="s">
         <v>7</v>
@@ -9967,10 +9967,10 @@
         <v>672</v>
       </c>
       <c r="B332" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C332">
-        <v>0.3705801004067801</v>
+        <v>0.3762960749987268</v>
       </c>
       <c r="D332" t="s">
         <v>7</v>
@@ -9984,10 +9984,10 @@
         <v>674</v>
       </c>
       <c r="B333" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C333">
-        <v>0.497348018354944</v>
+        <v>0.484750216697777</v>
       </c>
       <c r="D333" t="s">
         <v>7</v>
@@ -10004,7 +10004,7 @@
         <v>15</v>
       </c>
       <c r="C334">
-        <v>0.3014857413977949</v>
+        <v>0.2991063036072676</v>
       </c>
       <c r="D334" t="s">
         <v>7</v>
@@ -10021,7 +10021,7 @@
         <v>15</v>
       </c>
       <c r="C335">
-        <v>0.3514610589405885</v>
+        <v>0.347300905356385</v>
       </c>
       <c r="D335" t="s">
         <v>7</v>
@@ -10035,10 +10035,10 @@
         <v>680</v>
       </c>
       <c r="B336" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C336">
-        <v>0.3373635306006987</v>
+        <v>0.3460645671138828</v>
       </c>
       <c r="D336" t="s">
         <v>7</v>
@@ -10055,7 +10055,7 @@
         <v>44</v>
       </c>
       <c r="C337">
-        <v>0.408943161499743</v>
+        <v>0.4218911064221688</v>
       </c>
       <c r="D337" t="s">
         <v>7</v>
@@ -10069,10 +10069,10 @@
         <v>684</v>
       </c>
       <c r="B338" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C338">
-        <v>0.3030380819949579</v>
+        <v>0.2909934874983195</v>
       </c>
       <c r="D338" t="s">
         <v>7</v>
@@ -10089,7 +10089,7 @@
         <v>15</v>
       </c>
       <c r="C339">
-        <v>0.4366736494941975</v>
+        <v>0.4370923483794991</v>
       </c>
       <c r="D339" t="s">
         <v>7</v>
@@ -10106,7 +10106,7 @@
         <v>15</v>
       </c>
       <c r="C340">
-        <v>0.3024015870868682</v>
+        <v>0.3008967809590951</v>
       </c>
       <c r="D340" t="s">
         <v>7</v>
@@ -10120,10 +10120,10 @@
         <v>690</v>
       </c>
       <c r="B341" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C341">
-        <v>0.3177198319901043</v>
+        <v>0.3051780100951938</v>
       </c>
       <c r="D341" t="s">
         <v>7</v>
@@ -10137,10 +10137,10 @@
         <v>692</v>
       </c>
       <c r="B342" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C342">
-        <v>0.3000141563826407</v>
+        <v>0.3022323148549867</v>
       </c>
       <c r="D342" t="s">
         <v>7</v>
@@ -10154,10 +10154,10 @@
         <v>694</v>
       </c>
       <c r="B343" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C343">
-        <v>0.4009582202532314</v>
+        <v>0.4113955091076755</v>
       </c>
       <c r="D343" t="s">
         <v>7</v>
@@ -10171,10 +10171,10 @@
         <v>696</v>
       </c>
       <c r="B344" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C344">
-        <v>0.2663721765532291</v>
+        <v>0.2732624548485608</v>
       </c>
       <c r="D344" t="s">
         <v>7</v>
@@ -10188,10 +10188,10 @@
         <v>698</v>
       </c>
       <c r="B345" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C345">
-        <v>0.3860636618419953</v>
+        <v>0.3806545877931447</v>
       </c>
       <c r="D345" t="s">
         <v>7</v>
@@ -10205,10 +10205,10 @@
         <v>700</v>
       </c>
       <c r="B346" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C346">
-        <v>0.3483857149963979</v>
+        <v>0.3523514588037165</v>
       </c>
       <c r="D346" t="s">
         <v>7</v>
@@ -10225,7 +10225,7 @@
         <v>15</v>
       </c>
       <c r="C347">
-        <v>0.3475255253597092</v>
+        <v>0.3459034512894915</v>
       </c>
       <c r="D347" t="s">
         <v>7</v>
@@ -10239,10 +10239,10 @@
         <v>704</v>
       </c>
       <c r="B348" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C348">
-        <v>0.3720502658018329</v>
+        <v>0.3658817296205562</v>
       </c>
       <c r="D348" t="s">
         <v>7</v>
@@ -10256,10 +10256,10 @@
         <v>706</v>
       </c>
       <c r="B349" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C349">
-        <v>0.5198386745070536</v>
+        <v>0.5113369403429094</v>
       </c>
       <c r="D349" t="s">
         <v>7</v>
@@ -10276,7 +10276,7 @@
         <v>15</v>
       </c>
       <c r="C350">
-        <v>0.3486752013252857</v>
+        <v>0.3497997773538578</v>
       </c>
       <c r="D350" t="s">
         <v>7</v>
@@ -10293,7 +10293,7 @@
         <v>15</v>
       </c>
       <c r="C351">
-        <v>0.217442240899363</v>
+        <v>0.2168681280929442</v>
       </c>
       <c r="D351" t="s">
         <v>7</v>
@@ -10310,7 +10310,7 @@
         <v>15</v>
       </c>
       <c r="C352">
-        <v>0.3932320209806808</v>
+        <v>0.3942294636502503</v>
       </c>
       <c r="D352" t="s">
         <v>7</v>
@@ -10324,10 +10324,10 @@
         <v>714</v>
       </c>
       <c r="B353" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C353">
-        <v>0.3953919142353359</v>
+        <v>0.3989168737801188</v>
       </c>
       <c r="D353" t="s">
         <v>7</v>
@@ -10341,10 +10341,10 @@
         <v>716</v>
       </c>
       <c r="B354" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C354">
-        <v>0.303499536305088</v>
+        <v>0.2993481333617596</v>
       </c>
       <c r="D354" t="s">
         <v>7</v>
@@ -10358,10 +10358,10 @@
         <v>718</v>
       </c>
       <c r="B355" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C355">
-        <v>0.3987051554164194</v>
+        <v>0.3944097967724159</v>
       </c>
       <c r="D355" t="s">
         <v>7</v>
@@ -10375,10 +10375,10 @@
         <v>720</v>
       </c>
       <c r="B356" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C356">
-        <v>0.3381291899673458</v>
+        <v>0.3308231228779561</v>
       </c>
       <c r="D356" t="s">
         <v>7</v>
@@ -10392,10 +10392,10 @@
         <v>722</v>
       </c>
       <c r="B357" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C357">
-        <v>0.4245897808027935</v>
+        <v>0.4182045952453424</v>
       </c>
       <c r="D357" t="s">
         <v>7</v>
@@ -10409,10 +10409,10 @@
         <v>724</v>
       </c>
       <c r="B358" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C358">
-        <v>0.3666211952182046</v>
+        <v>0.3595376544776399</v>
       </c>
       <c r="D358" t="s">
         <v>7</v>
@@ -10429,7 +10429,7 @@
         <v>44</v>
       </c>
       <c r="C359">
-        <v>0.4355407349635795</v>
+        <v>0.4401090816331542</v>
       </c>
       <c r="D359" t="s">
         <v>7</v>
@@ -10443,10 +10443,10 @@
         <v>728</v>
       </c>
       <c r="B360" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C360">
-        <v>0.511257537550998</v>
+        <v>0.5003279260691016</v>
       </c>
       <c r="D360" t="s">
         <v>7</v>
@@ -10463,7 +10463,7 @@
         <v>15</v>
       </c>
       <c r="C361">
-        <v>0.3051866993622734</v>
+        <v>0.3032200747112017</v>
       </c>
       <c r="D361" t="s">
         <v>7</v>
@@ -10477,10 +10477,10 @@
         <v>732</v>
       </c>
       <c r="B362" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C362">
-        <v>0.3823718184112247</v>
+        <v>0.3754521946613957</v>
       </c>
       <c r="D362" t="s">
         <v>7</v>
@@ -10497,7 +10497,7 @@
         <v>6</v>
       </c>
       <c r="C363">
-        <v>0.3046224497891882</v>
+        <v>0.3071607398924736</v>
       </c>
       <c r="D363" t="s">
         <v>7</v>
@@ -10511,10 +10511,10 @@
         <v>736</v>
       </c>
       <c r="B364" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C364">
-        <v>0.3296222241898156</v>
+        <v>0.3385464332722383</v>
       </c>
       <c r="D364" t="s">
         <v>7</v>
@@ -10531,7 +10531,7 @@
         <v>15</v>
       </c>
       <c r="C365">
-        <v>0.3184211602783286</v>
+        <v>0.3162930342314425</v>
       </c>
       <c r="D365" t="s">
         <v>7</v>
@@ -10548,7 +10548,7 @@
         <v>15</v>
       </c>
       <c r="C366">
-        <v>0.2697873317763119</v>
+        <v>0.2687311122966826</v>
       </c>
       <c r="D366" t="s">
         <v>7</v>
@@ -10562,10 +10562,10 @@
         <v>742</v>
       </c>
       <c r="B367" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C367">
-        <v>0.374632061843878</v>
+        <v>0.3717428342243341</v>
       </c>
       <c r="D367" t="s">
         <v>7</v>
@@ -10582,7 +10582,7 @@
         <v>15</v>
       </c>
       <c r="C368">
-        <v>0.357008469434623</v>
+        <v>0.3493174297076012</v>
       </c>
       <c r="D368" t="s">
         <v>7</v>
@@ -10596,10 +10596,10 @@
         <v>746</v>
       </c>
       <c r="B369" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C369">
-        <v>0.5516381386522433</v>
+        <v>0.5458181764633021</v>
       </c>
       <c r="D369" t="s">
         <v>7</v>
@@ -10616,7 +10616,7 @@
         <v>15</v>
       </c>
       <c r="C370">
-        <v>0.3404415045937713</v>
+        <v>0.3383379722867129</v>
       </c>
       <c r="D370" t="s">
         <v>7</v>
@@ -10630,10 +10630,10 @@
         <v>750</v>
       </c>
       <c r="B371" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C371">
-        <v>0.4963704759002959</v>
+        <v>0.4825482647440731</v>
       </c>
       <c r="D371" t="s">
         <v>7</v>
@@ -10647,10 +10647,10 @@
         <v>752</v>
       </c>
       <c r="B372" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C372">
-        <v>0.397204869546413</v>
+        <v>0.3932615644587441</v>
       </c>
       <c r="D372" t="s">
         <v>7</v>
@@ -10664,10 +10664,10 @@
         <v>754</v>
       </c>
       <c r="B373" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C373">
-        <v>0.461957710716437</v>
+        <v>0.4483682344733102</v>
       </c>
       <c r="D373" t="s">
         <v>7</v>
@@ -10681,10 +10681,10 @@
         <v>756</v>
       </c>
       <c r="B374" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C374">
-        <v>0.5197374230143047</v>
+        <v>0.513295182725667</v>
       </c>
       <c r="D374" t="s">
         <v>7</v>
@@ -10698,10 +10698,10 @@
         <v>758</v>
       </c>
       <c r="B375" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C375">
-        <v>0.4955569226181429</v>
+        <v>0.4905781773404378</v>
       </c>
       <c r="D375" t="s">
         <v>7</v>
@@ -10715,10 +10715,10 @@
         <v>760</v>
       </c>
       <c r="B376" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C376">
-        <v>0.3542716523879114</v>
+        <v>0.3545779070167907</v>
       </c>
       <c r="D376" t="s">
         <v>7</v>
@@ -10732,10 +10732,10 @@
         <v>762</v>
       </c>
       <c r="B377" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C377">
-        <v>0.5077999644627443</v>
+        <v>0.4997925706575624</v>
       </c>
       <c r="D377" t="s">
         <v>7</v>
@@ -10749,10 +10749,10 @@
         <v>764</v>
       </c>
       <c r="B378" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C378">
-        <v>0.3337866942832225</v>
+        <v>0.3269445402126762</v>
       </c>
       <c r="D378" t="s">
         <v>7</v>
@@ -10766,10 +10766,10 @@
         <v>766</v>
       </c>
       <c r="B379" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C379">
-        <v>0.3460903928409897</v>
+        <v>0.3396331969999503</v>
       </c>
       <c r="D379" t="s">
         <v>7</v>
@@ -10783,10 +10783,10 @@
         <v>768</v>
       </c>
       <c r="B380" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C380">
-        <v>0.3959765303746913</v>
+        <v>0.3887400956623545</v>
       </c>
       <c r="D380" t="s">
         <v>7</v>
@@ -10800,10 +10800,10 @@
         <v>770</v>
       </c>
       <c r="B381" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C381">
-        <v>0.493452434211698</v>
+        <v>0.4935159194345329</v>
       </c>
       <c r="D381" t="s">
         <v>7</v>
@@ -10817,10 +10817,10 @@
         <v>772</v>
       </c>
       <c r="B382" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C382">
-        <v>0.3505047890900696</v>
+        <v>0.3455362254958698</v>
       </c>
       <c r="D382" t="s">
         <v>7</v>
@@ -10834,10 +10834,10 @@
         <v>774</v>
       </c>
       <c r="B383" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C383">
-        <v>0.3902415881706195</v>
+        <v>0.3992409181471723</v>
       </c>
       <c r="D383" t="s">
         <v>7</v>
@@ -10854,7 +10854,7 @@
         <v>44</v>
       </c>
       <c r="C384">
-        <v>0.4180015904506967</v>
+        <v>0.4227498718322691</v>
       </c>
       <c r="D384" t="s">
         <v>7</v>
@@ -10868,10 +10868,10 @@
         <v>778</v>
       </c>
       <c r="B385" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C385">
-        <v>0.4248477897702412</v>
+        <v>0.4200713651258565</v>
       </c>
       <c r="D385" t="s">
         <v>7</v>
@@ -10885,10 +10885,10 @@
         <v>780</v>
       </c>
       <c r="B386" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C386">
-        <v>0.3052823568529727</v>
+        <v>0.3145921705773721</v>
       </c>
       <c r="D386" t="s">
         <v>7</v>
@@ -10902,10 +10902,10 @@
         <v>782</v>
       </c>
       <c r="B387" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C387">
-        <v>0.4318048580190839</v>
+        <v>0.4382885054553811</v>
       </c>
       <c r="D387" t="s">
         <v>7</v>
@@ -10919,10 +10919,10 @@
         <v>784</v>
       </c>
       <c r="B388" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="C388">
-        <v>0.2685319197903051</v>
+        <v>0.2782036358348184</v>
       </c>
       <c r="D388" t="s">
         <v>7</v>
@@ -10936,10 +10936,10 @@
         <v>786</v>
       </c>
       <c r="B389" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C389">
-        <v>0.3820400523138598</v>
+        <v>0.3760384152508029</v>
       </c>
       <c r="D389" t="s">
         <v>7</v>
@@ -10956,7 +10956,7 @@
         <v>15</v>
       </c>
       <c r="C390">
-        <v>0.3306157527071439</v>
+        <v>0.3313069112834445</v>
       </c>
       <c r="D390" t="s">
         <v>7</v>
@@ -10973,7 +10973,7 @@
         <v>15</v>
       </c>
       <c r="C391">
-        <v>0.3454813205763599</v>
+        <v>0.345183358938561</v>
       </c>
       <c r="D391" t="s">
         <v>7</v>
@@ -10987,10 +10987,10 @@
         <v>792</v>
       </c>
       <c r="B392" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C392">
-        <v>0.3479099032320183</v>
+        <v>0.3532917582670004</v>
       </c>
       <c r="D392" t="s">
         <v>7</v>
@@ -11004,10 +11004,10 @@
         <v>794</v>
       </c>
       <c r="B393" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C393">
-        <v>0.4034050299002815</v>
+        <v>0.4029283702134476</v>
       </c>
       <c r="D393" t="s">
         <v>7</v>
@@ -11024,7 +11024,7 @@
         <v>15</v>
       </c>
       <c r="C394">
-        <v>0.3653336418172703</v>
+        <v>0.3660020206065805</v>
       </c>
       <c r="D394" t="s">
         <v>7</v>
@@ -11038,10 +11038,10 @@
         <v>798</v>
       </c>
       <c r="B395" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C395">
-        <v>0.4379517495927557</v>
+        <v>0.4390788171634048</v>
       </c>
       <c r="D395" t="s">
         <v>7</v>
@@ -11055,10 +11055,10 @@
         <v>800</v>
       </c>
       <c r="B396" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C396">
-        <v>0.4090192618195433</v>
+        <v>0.3964417190211114</v>
       </c>
       <c r="D396" t="s">
         <v>7</v>
@@ -11072,10 +11072,10 @@
         <v>802</v>
       </c>
       <c r="B397" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C397">
-        <v>0.3636680339565198</v>
+        <v>0.3650872277457678</v>
       </c>
       <c r="D397" t="s">
         <v>7</v>
@@ -11089,10 +11089,10 @@
         <v>804</v>
       </c>
       <c r="B398" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C398">
-        <v>0.5260456120980714</v>
+        <v>0.5148057034701986</v>
       </c>
       <c r="D398" t="s">
         <v>7</v>
@@ -11109,7 +11109,7 @@
         <v>15</v>
       </c>
       <c r="C399">
-        <v>0.3527595112984498</v>
+        <v>0.3501960805337617</v>
       </c>
       <c r="D399" t="s">
         <v>7</v>
@@ -11123,10 +11123,10 @@
         <v>808</v>
       </c>
       <c r="B400" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C400">
-        <v>0.3551665666922437</v>
+        <v>0.3467497965359735</v>
       </c>
       <c r="D400" t="s">
         <v>7</v>
@@ -11143,7 +11143,7 @@
         <v>15</v>
       </c>
       <c r="C401">
-        <v>0.4384568604560116</v>
+        <v>0.4402282382292482</v>
       </c>
       <c r="D401" t="s">
         <v>7</v>
@@ -11157,10 +11157,10 @@
         <v>812</v>
       </c>
       <c r="B402" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C402">
-        <v>0.4168810954633874</v>
+        <v>0.4097211630199757</v>
       </c>
       <c r="D402" t="s">
         <v>7</v>
@@ -11174,10 +11174,10 @@
         <v>814</v>
       </c>
       <c r="B403" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C403">
-        <v>0.3190015833512393</v>
+        <v>0.3144254950591202</v>
       </c>
       <c r="D403" t="s">
         <v>7</v>
@@ -11191,10 +11191,10 @@
         <v>816</v>
       </c>
       <c r="B404" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C404">
-        <v>0.3441329600567073</v>
+        <v>0.3490398919563341</v>
       </c>
       <c r="D404" t="s">
         <v>7</v>
@@ -11208,10 +11208,10 @@
         <v>818</v>
       </c>
       <c r="B405" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C405">
-        <v>0.4450573736839637</v>
+        <v>0.4453783393072623</v>
       </c>
       <c r="D405" t="s">
         <v>7</v>
@@ -11225,10 +11225,10 @@
         <v>820</v>
       </c>
       <c r="B406" t="s">
-        <v>6</v>
+        <v>145</v>
       </c>
       <c r="C406">
-        <v>0.4328555701340731</v>
+        <v>0.4268739360398142</v>
       </c>
       <c r="D406" t="s">
         <v>7</v>
@@ -11242,10 +11242,10 @@
         <v>822</v>
       </c>
       <c r="B407" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C407">
-        <v>0.4181517975421166</v>
+        <v>0.4044980000393313</v>
       </c>
       <c r="D407" t="s">
         <v>7</v>
@@ -11259,10 +11259,10 @@
         <v>824</v>
       </c>
       <c r="B408" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C408">
-        <v>0.487547385831099</v>
+        <v>0.4824627541167594</v>
       </c>
       <c r="D408" t="s">
         <v>7</v>
@@ -11276,10 +11276,10 @@
         <v>826</v>
       </c>
       <c r="B409" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C409">
-        <v>0.5052388834134643</v>
+        <v>0.5011347762132599</v>
       </c>
       <c r="D409" t="s">
         <v>7</v>
@@ -11296,7 +11296,7 @@
         <v>15</v>
       </c>
       <c r="C410">
-        <v>0.2903387713155478</v>
+        <v>0.2886651867493523</v>
       </c>
       <c r="D410" t="s">
         <v>7</v>
@@ -11310,10 +11310,10 @@
         <v>830</v>
       </c>
       <c r="B411" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C411">
-        <v>0.3432776308862663</v>
+        <v>0.3371149505657562</v>
       </c>
       <c r="D411" t="s">
         <v>7</v>
@@ -11327,10 +11327,10 @@
         <v>832</v>
       </c>
       <c r="B412" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C412">
-        <v>0.4538521238513653</v>
+        <v>0.4401572893666832</v>
       </c>
       <c r="D412" t="s">
         <v>7</v>
@@ -11347,7 +11347,7 @@
         <v>6</v>
       </c>
       <c r="C413">
-        <v>0.2814185038459897</v>
+        <v>0.2811139899718828</v>
       </c>
       <c r="D413" t="s">
         <v>7</v>
@@ -11364,7 +11364,7 @@
         <v>15</v>
       </c>
       <c r="C414">
-        <v>0.3129865122412654</v>
+        <v>0.3098683928718262</v>
       </c>
       <c r="D414" t="s">
         <v>7</v>
@@ -11378,10 +11378,10 @@
         <v>838</v>
       </c>
       <c r="B415" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C415">
-        <v>0.3597455872842099</v>
+        <v>0.3631181204971604</v>
       </c>
       <c r="D415" t="s">
         <v>7</v>
@@ -11398,7 +11398,7 @@
         <v>15</v>
       </c>
       <c r="C416">
-        <v>0.4382866180182896</v>
+        <v>0.4357009267161114</v>
       </c>
       <c r="D416" t="s">
         <v>7</v>
@@ -11412,10 +11412,10 @@
         <v>842</v>
       </c>
       <c r="B417" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C417">
-        <v>0.2988721124135199</v>
+        <v>0.2942190953270828</v>
       </c>
       <c r="D417" t="s">
         <v>7</v>
@@ -11429,10 +11429,10 @@
         <v>844</v>
       </c>
       <c r="B418" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C418">
-        <v>0.3332791719098562</v>
+        <v>0.3340377788963301</v>
       </c>
       <c r="D418" t="s">
         <v>7</v>
@@ -11449,7 +11449,7 @@
         <v>15</v>
       </c>
       <c r="C419">
-        <v>0.391458790501867</v>
+        <v>0.3924944231808148</v>
       </c>
       <c r="D419" t="s">
         <v>7</v>
@@ -11466,7 +11466,7 @@
         <v>44</v>
       </c>
       <c r="C420">
-        <v>0.4273989720851753</v>
+        <v>0.4314424703151867</v>
       </c>
       <c r="D420" t="s">
         <v>7</v>
@@ -11483,7 +11483,7 @@
         <v>44</v>
       </c>
       <c r="C421">
-        <v>0.4297521206349555</v>
+        <v>0.4392213991812861</v>
       </c>
       <c r="D421" t="s">
         <v>7</v>
@@ -11497,10 +11497,10 @@
         <v>852</v>
       </c>
       <c r="B422" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C422">
-        <v>0.3903438258184407</v>
+        <v>0.381219750734441</v>
       </c>
       <c r="D422" t="s">
         <v>7</v>
@@ -11517,7 +11517,7 @@
         <v>44</v>
       </c>
       <c r="C423">
-        <v>0.4061112800315016</v>
+        <v>0.4188747143759381</v>
       </c>
       <c r="D423" t="s">
         <v>7</v>
@@ -11531,10 +11531,10 @@
         <v>856</v>
       </c>
       <c r="B424" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C424">
-        <v>0.3611705179549649</v>
+        <v>0.3635013377620491</v>
       </c>
       <c r="D424" t="s">
         <v>7</v>
@@ -11548,10 +11548,10 @@
         <v>858</v>
       </c>
       <c r="B425" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C425">
-        <v>0.3883419777017316</v>
+        <v>0.3824238952397113</v>
       </c>
       <c r="D425" t="s">
         <v>7</v>
@@ -11568,7 +11568,7 @@
         <v>15</v>
       </c>
       <c r="C426">
-        <v>0.3561982753949714</v>
+        <v>0.3541967379038762</v>
       </c>
       <c r="D426" t="s">
         <v>7</v>
@@ -11582,10 +11582,10 @@
         <v>862</v>
       </c>
       <c r="B427" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C427">
-        <v>0.3060010209015112</v>
+        <v>0.296209926082169</v>
       </c>
       <c r="D427" t="s">
         <v>7</v>
@@ -11599,10 +11599,10 @@
         <v>864</v>
       </c>
       <c r="B428" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C428">
-        <v>0.2955010183358314</v>
+        <v>0.2887054238617824</v>
       </c>
       <c r="D428" t="s">
         <v>7</v>
@@ -11616,10 +11616,10 @@
         <v>866</v>
       </c>
       <c r="B429" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C429">
-        <v>0.3722274003195551</v>
+        <v>0.3797035656886627</v>
       </c>
       <c r="D429" t="s">
         <v>7</v>
@@ -11633,10 +11633,10 @@
         <v>868</v>
       </c>
       <c r="B430" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C430">
-        <v>0.3884275709829573</v>
+        <v>0.3766621547847255</v>
       </c>
       <c r="D430" t="s">
         <v>7</v>
@@ -11650,10 +11650,10 @@
         <v>870</v>
       </c>
       <c r="B431" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C431">
-        <v>0.3096450925963197</v>
+        <v>0.3097234988632968</v>
       </c>
       <c r="D431" t="s">
         <v>7</v>
@@ -11670,7 +11670,7 @@
         <v>15</v>
       </c>
       <c r="C432">
-        <v>0.3502839273117483</v>
+        <v>0.3470912443336482</v>
       </c>
       <c r="D432" t="s">
         <v>7</v>
@@ -11684,10 +11684,10 @@
         <v>874</v>
       </c>
       <c r="B433" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C433">
-        <v>0.3038932546475513</v>
+        <v>0.3105590910670639</v>
       </c>
       <c r="D433" t="s">
         <v>7</v>
@@ -11704,7 +11704,7 @@
         <v>15</v>
       </c>
       <c r="C434">
-        <v>0.3614518649233464</v>
+        <v>0.3582997836909294</v>
       </c>
       <c r="D434" t="s">
         <v>7</v>
@@ -11718,10 +11718,10 @@
         <v>878</v>
       </c>
       <c r="B435" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C435">
-        <v>0.4114018918154311</v>
+        <v>0.4173199908012859</v>
       </c>
       <c r="D435" t="s">
         <v>7</v>
@@ -11738,7 +11738,7 @@
         <v>15</v>
       </c>
       <c r="C436">
-        <v>0.3543190554741206</v>
+        <v>0.3529526680094827</v>
       </c>
       <c r="D436" t="s">
         <v>7</v>
@@ -11752,10 +11752,10 @@
         <v>882</v>
       </c>
       <c r="B437" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C437">
-        <v>0.3416394008431627</v>
+        <v>0.3488232223500442</v>
       </c>
       <c r="D437" t="s">
         <v>7</v>
@@ -11772,7 +11772,7 @@
         <v>15</v>
       </c>
       <c r="C438">
-        <v>0.3572074610477305</v>
+        <v>0.3556642988668989</v>
       </c>
       <c r="D438" t="s">
         <v>7</v>
@@ -11786,10 +11786,10 @@
         <v>886</v>
       </c>
       <c r="B439" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C439">
-        <v>0.4167029258630305</v>
+        <v>0.4102850844272984</v>
       </c>
       <c r="D439" t="s">
         <v>7</v>
@@ -11803,10 +11803,10 @@
         <v>888</v>
       </c>
       <c r="B440" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C440">
-        <v>0.3332813404045279</v>
+        <v>0.342469169631205</v>
       </c>
       <c r="D440" t="s">
         <v>7</v>
@@ -11820,10 +11820,10 @@
         <v>890</v>
       </c>
       <c r="B441" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C441">
-        <v>0.3600613893972875</v>
+        <v>0.3487432370455419</v>
       </c>
       <c r="D441" t="s">
         <v>7</v>
@@ -11837,10 +11837,10 @@
         <v>892</v>
       </c>
       <c r="B442" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C442">
-        <v>0.3316360817217719</v>
+        <v>0.3261393871954462</v>
       </c>
       <c r="D442" t="s">
         <v>7</v>
@@ -11857,7 +11857,7 @@
         <v>15</v>
       </c>
       <c r="C443">
-        <v>0.304186431786743</v>
+        <v>0.3020020218200828</v>
       </c>
       <c r="D443" t="s">
         <v>7</v>
@@ -11871,10 +11871,10 @@
         <v>896</v>
       </c>
       <c r="B444" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C444">
-        <v>0.3657043595403644</v>
+        <v>0.3661036917703137</v>
       </c>
       <c r="D444" t="s">
         <v>7</v>
@@ -11888,10 +11888,10 @@
         <v>898</v>
       </c>
       <c r="B445" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C445">
-        <v>0.3848088269615906</v>
+        <v>0.3820191656059362</v>
       </c>
       <c r="D445" t="s">
         <v>7</v>
@@ -11908,7 +11908,7 @@
         <v>44</v>
       </c>
       <c r="C446">
-        <v>0.3233198989418533</v>
+        <v>0.331460862660215</v>
       </c>
       <c r="D446" t="s">
         <v>7</v>
@@ -11925,7 +11925,7 @@
         <v>6</v>
       </c>
       <c r="C447">
-        <v>0.2952132251665474</v>
+        <v>0.2943067786662789</v>
       </c>
       <c r="D447" t="s">
         <v>7</v>
@@ -11939,10 +11939,10 @@
         <v>904</v>
       </c>
       <c r="B448" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C448">
-        <v>0.3985542417230479</v>
+        <v>0.3922889339711307</v>
       </c>
       <c r="D448" t="s">
         <v>7</v>
@@ -11956,10 +11956,10 @@
         <v>906</v>
       </c>
       <c r="B449" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C449">
-        <v>0.4296286049173068</v>
+        <v>0.422234800797579</v>
       </c>
       <c r="D449" t="s">
         <v>7</v>
@@ -11976,7 +11976,7 @@
         <v>44</v>
       </c>
       <c r="C450">
-        <v>0.3873663032938461</v>
+        <v>0.3999660009788307</v>
       </c>
       <c r="D450" t="s">
         <v>7</v>
@@ -11993,7 +11993,7 @@
         <v>44</v>
       </c>
       <c r="C451">
-        <v>0.3671422971092899</v>
+        <v>0.3742902336685707</v>
       </c>
       <c r="D451" t="s">
         <v>7</v>
@@ -12007,10 +12007,10 @@
         <v>912</v>
       </c>
       <c r="B452" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C452">
-        <v>0.3608788208664604</v>
+        <v>0.3541974257183759</v>
       </c>
       <c r="D452" t="s">
         <v>7</v>
@@ -12024,10 +12024,10 @@
         <v>914</v>
       </c>
       <c r="B453" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C453">
-        <v>0.3816133666747105</v>
+        <v>0.3872783288642929</v>
       </c>
       <c r="D453" t="s">
         <v>7</v>
@@ -12044,7 +12044,7 @@
         <v>15</v>
       </c>
       <c r="C454">
-        <v>0.2857180383288314</v>
+        <v>0.2848404685368386</v>
       </c>
       <c r="D454" t="s">
         <v>7</v>
@@ -12058,10 +12058,10 @@
         <v>918</v>
       </c>
       <c r="B455" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C455">
-        <v>0.3762870842286603</v>
+        <v>0.3848679464717468</v>
       </c>
       <c r="D455" t="s">
         <v>7</v>
@@ -12075,10 +12075,10 @@
         <v>920</v>
       </c>
       <c r="B456" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C456">
-        <v>0.4117523115620636</v>
+        <v>0.4022640123238438</v>
       </c>
       <c r="D456" t="s">
         <v>7</v>
@@ -12095,7 +12095,7 @@
         <v>15</v>
       </c>
       <c r="C457">
-        <v>0.356169324790543</v>
+        <v>0.3575213283608206</v>
       </c>
       <c r="D457" t="s">
         <v>7</v>
@@ -12109,10 +12109,10 @@
         <v>924</v>
       </c>
       <c r="B458" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C458">
-        <v>0.3647580188805091</v>
+        <v>0.3553125467396773</v>
       </c>
       <c r="D458" t="s">
         <v>7</v>
@@ -12126,10 +12126,10 @@
         <v>926</v>
       </c>
       <c r="B459" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C459">
-        <v>0.4163337407601138</v>
+        <v>0.410195273937341</v>
       </c>
       <c r="D459" t="s">
         <v>7</v>
@@ -12143,10 +12143,10 @@
         <v>928</v>
       </c>
       <c r="B460" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C460">
-        <v>0.3665605949461752</v>
+        <v>0.3659315851297602</v>
       </c>
       <c r="D460" t="s">
         <v>7</v>
@@ -12160,10 +12160,10 @@
         <v>930</v>
       </c>
       <c r="B461" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C461">
-        <v>0.3305016194009775</v>
+        <v>0.3418178316506956</v>
       </c>
       <c r="D461" t="s">
         <v>7</v>
@@ -12177,10 +12177,10 @@
         <v>932</v>
       </c>
       <c r="B462" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C462">
-        <v>0.3529671050984876</v>
+        <v>0.3414016032376475</v>
       </c>
       <c r="D462" t="s">
         <v>7</v>
@@ -12194,10 +12194,10 @@
         <v>934</v>
       </c>
       <c r="B463" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C463">
-        <v>0.3266646652790628</v>
+        <v>0.3332596090386848</v>
       </c>
       <c r="D463" t="s">
         <v>7</v>
@@ -12211,10 +12211,10 @@
         <v>936</v>
       </c>
       <c r="B464" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C464">
-        <v>0.4503373684049048</v>
+        <v>0.4372217103975827</v>
       </c>
       <c r="D464" t="s">
         <v>7</v>
@@ -12231,7 +12231,7 @@
         <v>44</v>
       </c>
       <c r="C465">
-        <v>0.3290429438850233</v>
+        <v>0.3365869344021591</v>
       </c>
       <c r="D465" t="s">
         <v>7</v>
@@ -12245,10 +12245,10 @@
         <v>940</v>
       </c>
       <c r="B466" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C466">
-        <v>0.5606726212320018</v>
+        <v>0.5484018408091574</v>
       </c>
       <c r="D466" t="s">
         <v>7</v>
@@ -12262,10 +12262,10 @@
         <v>942</v>
       </c>
       <c r="B467" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C467">
-        <v>0.5098024472520204</v>
+        <v>0.5062639188669167</v>
       </c>
       <c r="D467" t="s">
         <v>7</v>
@@ -12279,10 +12279,10 @@
         <v>944</v>
       </c>
       <c r="B468" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C468">
-        <v>0.4134466886524675</v>
+        <v>0.4002872450265423</v>
       </c>
       <c r="D468" t="s">
         <v>7</v>
@@ -12299,7 +12299,7 @@
         <v>15</v>
       </c>
       <c r="C469">
-        <v>0.2979319885624729</v>
+        <v>0.2954826016268713</v>
       </c>
       <c r="D469" t="s">
         <v>7</v>
@@ -12313,10 +12313,10 @@
         <v>948</v>
       </c>
       <c r="B470" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C470">
-        <v>0.3137125852121121</v>
+        <v>0.3091633733193918</v>
       </c>
       <c r="D470" t="s">
         <v>7</v>
@@ -12333,7 +12333,7 @@
         <v>44</v>
       </c>
       <c r="C471">
-        <v>0.2952206386425444</v>
+        <v>0.3064928215567844</v>
       </c>
       <c r="D471" t="s">
         <v>7</v>
@@ -12350,7 +12350,7 @@
         <v>15</v>
       </c>
       <c r="C472">
-        <v>0.3117070949850211</v>
+        <v>0.3087858268005206</v>
       </c>
       <c r="D472" t="s">
         <v>7</v>
@@ -12364,10 +12364,10 @@
         <v>954</v>
       </c>
       <c r="B473" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C473">
-        <v>0.3254560714312048</v>
+        <v>0.3257085584260569</v>
       </c>
       <c r="D473" t="s">
         <v>7</v>
@@ -12381,10 +12381,10 @@
         <v>956</v>
       </c>
       <c r="B474" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C474">
-        <v>0.37183721945543</v>
+        <v>0.3755296331962198</v>
       </c>
       <c r="D474" t="s">
         <v>7</v>
@@ -12398,10 +12398,10 @@
         <v>958</v>
       </c>
       <c r="B475" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C475">
-        <v>0.3576367117469069</v>
+        <v>0.3466779966447449</v>
       </c>
       <c r="D475" t="s">
         <v>7</v>
@@ -12415,10 +12415,10 @@
         <v>960</v>
       </c>
       <c r="B476" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C476">
-        <v>0.351764894464824</v>
+        <v>0.3459229374112741</v>
       </c>
       <c r="D476" t="s">
         <v>7</v>
@@ -12432,10 +12432,10 @@
         <v>962</v>
       </c>
       <c r="B477" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C477">
-        <v>0.3499917852268019</v>
+        <v>0.3584164346099656</v>
       </c>
       <c r="D477" t="s">
         <v>7</v>
@@ -12449,10 +12449,10 @@
         <v>964</v>
       </c>
       <c r="B478" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C478">
-        <v>0.41749621094902</v>
+        <v>0.410732442181212</v>
       </c>
       <c r="D478" t="s">
         <v>7</v>
@@ -12469,7 +12469,7 @@
         <v>44</v>
       </c>
       <c r="C479">
-        <v>0.3855545762839881</v>
+        <v>0.3961212452625692</v>
       </c>
       <c r="D479" t="s">
         <v>7</v>
@@ -12483,10 +12483,10 @@
         <v>968</v>
       </c>
       <c r="B480" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C480">
-        <v>0.4952122438038706</v>
+        <v>0.4882047987377601</v>
       </c>
       <c r="D480" t="s">
         <v>7</v>
@@ -12503,7 +12503,7 @@
         <v>44</v>
       </c>
       <c r="C481">
-        <v>0.3435296073868833</v>
+        <v>0.3509029550353161</v>
       </c>
       <c r="D481" t="s">
         <v>7</v>
@@ -12517,10 +12517,10 @@
         <v>972</v>
       </c>
       <c r="B482" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C482">
-        <v>0.2959151003079767</v>
+        <v>0.3035410706378638</v>
       </c>
       <c r="D482" t="s">
         <v>7</v>
@@ -12534,10 +12534,10 @@
         <v>974</v>
       </c>
       <c r="B483" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C483">
-        <v>0.3256314313617998</v>
+        <v>0.3324685720463726</v>
       </c>
       <c r="D483" t="s">
         <v>7</v>
@@ -12554,7 +12554,7 @@
         <v>44</v>
       </c>
       <c r="C484">
-        <v>0.3398541637547737</v>
+        <v>0.3528969508158219</v>
       </c>
       <c r="D484" t="s">
         <v>7</v>
@@ -12571,7 +12571,7 @@
         <v>15</v>
       </c>
       <c r="C485">
-        <v>0.3648369109132513</v>
+        <v>0.3659207167571105</v>
       </c>
       <c r="D485" t="s">
         <v>7</v>
@@ -12588,7 +12588,7 @@
         <v>15</v>
       </c>
       <c r="C486">
-        <v>0.3960183116275673</v>
+        <v>0.3976489380171654</v>
       </c>
       <c r="D486" t="s">
         <v>7</v>
@@ -12605,7 +12605,7 @@
         <v>44</v>
       </c>
       <c r="C487">
-        <v>0.4143104321378043</v>
+        <v>0.4202886781223146</v>
       </c>
       <c r="D487" t="s">
         <v>7</v>
@@ -12619,10 +12619,10 @@
         <v>984</v>
       </c>
       <c r="B488" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C488">
-        <v>0.307994996470679</v>
+        <v>0.3165185326749123</v>
       </c>
       <c r="D488" t="s">
         <v>7</v>
@@ -12636,10 +12636,10 @@
         <v>986</v>
       </c>
       <c r="B489" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C489">
-        <v>0.5249089351409065</v>
+        <v>0.5124983114818423</v>
       </c>
       <c r="D489" t="s">
         <v>7</v>
@@ -12656,7 +12656,7 @@
         <v>15</v>
       </c>
       <c r="C490">
-        <v>0.3329815996494197</v>
+        <v>0.3297837489248796</v>
       </c>
       <c r="D490" t="s">
         <v>7</v>
@@ -12670,10 +12670,10 @@
         <v>990</v>
       </c>
       <c r="B491" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C491">
-        <v>0.3168825123747923</v>
+        <v>0.3089986584637536</v>
       </c>
       <c r="D491" t="s">
         <v>7</v>
@@ -12687,10 +12687,10 @@
         <v>992</v>
       </c>
       <c r="B492" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C492">
-        <v>0.5110957064584629</v>
+        <v>0.5044204215795108</v>
       </c>
       <c r="D492" t="s">
         <v>7</v>
@@ -12704,10 +12704,10 @@
         <v>994</v>
       </c>
       <c r="B493" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C493">
-        <v>0.323527375830341</v>
+        <v>0.3112720883490302</v>
       </c>
       <c r="D493" t="s">
         <v>7</v>
@@ -12721,10 +12721,10 @@
         <v>996</v>
       </c>
       <c r="B494" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C494">
-        <v>0.3303449538684555</v>
+        <v>0.3332665810918839</v>
       </c>
       <c r="D494" t="s">
         <v>7</v>
@@ -12741,7 +12741,7 @@
         <v>44</v>
       </c>
       <c r="C495">
-        <v>0.4884329530713543</v>
+        <v>0.490724584940085</v>
       </c>
       <c r="D495" t="s">
         <v>7</v>
@@ -12755,10 +12755,10 @@
         <v>1000</v>
       </c>
       <c r="B496" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C496">
-        <v>0.5183991529202365</v>
+        <v>0.5121451052477821</v>
       </c>
       <c r="D496" t="s">
         <v>7</v>
@@ -12772,10 +12772,10 @@
         <v>1002</v>
       </c>
       <c r="B497" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C497">
-        <v>0.3793927963972554</v>
+        <v>0.3877018107643418</v>
       </c>
       <c r="D497" t="s">
         <v>7</v>
@@ -12789,10 +12789,10 @@
         <v>1004</v>
       </c>
       <c r="B498" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C498">
-        <v>0.6857203333963072</v>
+        <v>0.6740567144897142</v>
       </c>
       <c r="D498" t="s">
         <v>7</v>
@@ -12809,7 +12809,7 @@
         <v>15</v>
       </c>
       <c r="C499">
-        <v>0.3415934167334314</v>
+        <v>0.3390848062383568</v>
       </c>
       <c r="D499" t="s">
         <v>7</v>
@@ -12823,10 +12823,10 @@
         <v>1008</v>
       </c>
       <c r="B500" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C500">
-        <v>0.4567329461978528</v>
+        <v>0.454538655240101</v>
       </c>
       <c r="D500" t="s">
         <v>7</v>
@@ -12843,7 +12843,7 @@
         <v>15</v>
       </c>
       <c r="C501">
-        <v>0.4114613320242083</v>
+        <v>0.4132117194598846</v>
       </c>
       <c r="D501" t="s">
         <v>7</v>
@@ -12857,10 +12857,10 @@
         <v>1012</v>
       </c>
       <c r="B502" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C502">
-        <v>0.5999147020206985</v>
+        <v>0.5987536998773402</v>
       </c>
       <c r="D502" t="s">
         <v>7</v>
@@ -12877,7 +12877,7 @@
         <v>15</v>
       </c>
       <c r="C503">
-        <v>0.3550800494949607</v>
+        <v>0.3565400296051159</v>
       </c>
       <c r="D503" t="s">
         <v>7</v>
@@ -12894,7 +12894,7 @@
         <v>15</v>
       </c>
       <c r="C504">
-        <v>0.3265369308939668</v>
+        <v>0.3245983527946168</v>
       </c>
       <c r="D504" t="s">
         <v>7</v>
@@ -12908,10 +12908,10 @@
         <v>1018</v>
       </c>
       <c r="B505" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C505">
-        <v>0.4708503177092222</v>
+        <v>0.4645211191793697</v>
       </c>
       <c r="D505" t="s">
         <v>7</v>
@@ -12928,7 +12928,7 @@
         <v>15</v>
       </c>
       <c r="C506">
-        <v>0.4836087917785527</v>
+        <v>0.4863910226891323</v>
       </c>
       <c r="D506" t="s">
         <v>7</v>
@@ -12942,10 +12942,10 @@
         <v>1022</v>
       </c>
       <c r="B507" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C507">
-        <v>0.3529142349474733</v>
+        <v>0.341220896291039</v>
       </c>
       <c r="D507" t="s">
         <v>7</v>
@@ -12962,7 +12962,7 @@
         <v>15</v>
       </c>
       <c r="C508">
-        <v>0.3253367213824494</v>
+        <v>0.324352338993503</v>
       </c>
       <c r="D508" t="s">
         <v>7</v>
@@ -12976,10 +12976,10 @@
         <v>1026</v>
       </c>
       <c r="B509" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C509">
-        <v>0.4980679944269725</v>
+        <v>0.5006996036216135</v>
       </c>
       <c r="D509" t="s">
         <v>7</v>
@@ -12993,10 +12993,10 @@
         <v>1028</v>
       </c>
       <c r="B510" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C510">
-        <v>0.3833766997888259</v>
+        <v>0.3923261354332524</v>
       </c>
       <c r="D510" t="s">
         <v>7</v>
@@ -13013,7 +13013,7 @@
         <v>44</v>
       </c>
       <c r="C511">
-        <v>0.3204460988599924</v>
+        <v>0.3346644415766576</v>
       </c>
       <c r="D511" t="s">
         <v>7</v>
@@ -13027,10 +13027,10 @@
         <v>1032</v>
       </c>
       <c r="B512" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C512">
-        <v>0.3217603566382825</v>
+        <v>0.3160488332310641</v>
       </c>
       <c r="D512" t="s">
         <v>7</v>
@@ -13044,10 +13044,10 @@
         <v>1034</v>
       </c>
       <c r="B513" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C513">
-        <v>0.3902119249822659</v>
+        <v>0.385330142560689</v>
       </c>
       <c r="D513" t="s">
         <v>7</v>
@@ -13064,7 +13064,7 @@
         <v>44</v>
       </c>
       <c r="C514">
-        <v>0.3712445706303139</v>
+        <v>0.3838097865849493</v>
       </c>
       <c r="D514" t="s">
         <v>7</v>
@@ -13078,10 +13078,10 @@
         <v>1038</v>
       </c>
       <c r="B515" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C515">
-        <v>0.5287324782597118</v>
+        <v>0.5193103774051421</v>
       </c>
       <c r="D515" t="s">
         <v>7</v>
@@ -13095,10 +13095,10 @@
         <v>1040</v>
       </c>
       <c r="B516" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C516">
-        <v>0.3176471387892337</v>
+        <v>0.3121629498301982</v>
       </c>
       <c r="D516" t="s">
         <v>7</v>
@@ -13115,7 +13115,7 @@
         <v>15</v>
       </c>
       <c r="C517">
-        <v>0.3478961233331934</v>
+        <v>0.3455129024719174</v>
       </c>
       <c r="D517" t="s">
         <v>7</v>
@@ -13129,10 +13129,10 @@
         <v>1044</v>
       </c>
       <c r="B518" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C518">
-        <v>0.3387869634587967</v>
+        <v>0.3459531992159799</v>
       </c>
       <c r="D518" t="s">
         <v>7</v>
@@ -13149,7 +13149,7 @@
         <v>44</v>
       </c>
       <c r="C519">
-        <v>0.4875783557439063</v>
+        <v>0.4894358989815615</v>
       </c>
       <c r="D519" t="s">
         <v>7</v>
@@ -13166,7 +13166,7 @@
         <v>15</v>
       </c>
       <c r="C520">
-        <v>0.3298999353132537</v>
+        <v>0.32799840723622</v>
       </c>
       <c r="D520" t="s">
         <v>7</v>
@@ -13180,10 +13180,10 @@
         <v>1050</v>
       </c>
       <c r="B521" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C521">
-        <v>0.3322287326961316</v>
+        <v>0.3403328706977611</v>
       </c>
       <c r="D521" t="s">
         <v>7</v>
@@ -13200,7 +13200,7 @@
         <v>15</v>
       </c>
       <c r="C522">
-        <v>0.3427706467721077</v>
+        <v>0.3433240404051616</v>
       </c>
       <c r="D522" t="s">
         <v>7</v>
@@ -13214,10 +13214,10 @@
         <v>1054</v>
       </c>
       <c r="B523" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C523">
-        <v>0.4652202857578324</v>
+        <v>0.4616499238514787</v>
       </c>
       <c r="D523" t="s">
         <v>7</v>
@@ -13231,10 +13231,10 @@
         <v>1056</v>
       </c>
       <c r="B524" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C524">
-        <v>0.320857136311452</v>
+        <v>0.3169878636537494</v>
       </c>
       <c r="D524" t="s">
         <v>7</v>
@@ -13251,7 +13251,7 @@
         <v>44</v>
       </c>
       <c r="C525">
-        <v>0.372139507891448</v>
+        <v>0.3803981991830894</v>
       </c>
       <c r="D525" t="s">
         <v>7</v>
@@ -13268,7 +13268,7 @@
         <v>44</v>
       </c>
       <c r="C526">
-        <v>0.4711688933211267</v>
+        <v>0.4799840235304881</v>
       </c>
       <c r="D526" t="s">
         <v>7</v>
@@ -13282,10 +13282,10 @@
         <v>1062</v>
       </c>
       <c r="B527" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C527">
-        <v>0.4088283547231956</v>
+        <v>0.4170070128906602</v>
       </c>
       <c r="D527" t="s">
         <v>7</v>
@@ -13299,10 +13299,10 @@
         <v>1064</v>
       </c>
       <c r="B528" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C528">
-        <v>0.4723099078950535</v>
+        <v>0.4597743583875652</v>
       </c>
       <c r="D528" t="s">
         <v>7</v>
@@ -13316,10 +13316,10 @@
         <v>1066</v>
       </c>
       <c r="B529" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C529">
-        <v>0.3460559663629523</v>
+        <v>0.3497113082503594</v>
       </c>
       <c r="D529" t="s">
         <v>7</v>
@@ -13336,7 +13336,7 @@
         <v>44</v>
       </c>
       <c r="C530">
-        <v>0.4799081537353074</v>
+        <v>0.4832502157499432</v>
       </c>
       <c r="D530" t="s">
         <v>7</v>
@@ -13353,7 +13353,7 @@
         <v>44</v>
       </c>
       <c r="C531">
-        <v>0.5139018245237993</v>
+        <v>0.514652676017043</v>
       </c>
       <c r="D531" t="s">
         <v>7</v>
@@ -13367,10 +13367,10 @@
         <v>1072</v>
       </c>
       <c r="B532" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C532">
-        <v>0.3052502563947118</v>
+        <v>0.3066483447215016</v>
       </c>
       <c r="D532" t="s">
         <v>7</v>
@@ -13387,7 +13387,7 @@
         <v>15</v>
       </c>
       <c r="C533">
-        <v>0.4752072334982426</v>
+        <v>0.4781232897753587</v>
       </c>
       <c r="D533" t="s">
         <v>7</v>
@@ -13404,7 +13404,7 @@
         <v>15</v>
       </c>
       <c r="C534">
-        <v>0.3262212385260762</v>
+        <v>0.3272733158320389</v>
       </c>
       <c r="D534" t="s">
         <v>7</v>
@@ -13418,10 +13418,10 @@
         <v>1078</v>
       </c>
       <c r="B535" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C535">
-        <v>0.3332464112693503</v>
+        <v>0.3272721822527869</v>
       </c>
       <c r="D535" t="s">
         <v>7</v>
@@ -13435,10 +13435,10 @@
         <v>1080</v>
       </c>
       <c r="B536" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C536">
-        <v>0.337188596055896</v>
+        <v>0.3303766598300278</v>
       </c>
       <c r="D536" t="s">
         <v>7</v>
@@ -13452,10 +13452,10 @@
         <v>1082</v>
       </c>
       <c r="B537" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C537">
-        <v>0.4130003453365363</v>
+        <v>0.4068357590774516</v>
       </c>
       <c r="D537" t="s">
         <v>7</v>
@@ -13469,10 +13469,10 @@
         <v>1084</v>
       </c>
       <c r="B538" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C538">
-        <v>0.3098247918056154</v>
+        <v>0.3179356414673124</v>
       </c>
       <c r="D538" t="s">
         <v>7</v>
@@ -13486,10 +13486,10 @@
         <v>1086</v>
       </c>
       <c r="B539" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C539">
-        <v>0.3206885646404748</v>
+        <v>0.3144731173034122</v>
       </c>
       <c r="D539" t="s">
         <v>7</v>
@@ -13503,10 +13503,10 @@
         <v>1088</v>
       </c>
       <c r="B540" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C540">
-        <v>0.2679220890717738</v>
+        <v>0.2763437715584581</v>
       </c>
       <c r="D540" t="s">
         <v>7</v>
@@ -13520,10 +13520,10 @@
         <v>1090</v>
       </c>
       <c r="B541" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C541">
-        <v>0.4344914782238027</v>
+        <v>0.4321349612742895</v>
       </c>
       <c r="D541" t="s">
         <v>7</v>
@@ -13540,7 +13540,7 @@
         <v>44</v>
       </c>
       <c r="C542">
-        <v>0.3440715839574824</v>
+        <v>0.3573806662849626</v>
       </c>
       <c r="D542" t="s">
         <v>7</v>
@@ -13554,10 +13554,10 @@
         <v>1094</v>
       </c>
       <c r="B543" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C543">
-        <v>0.4479096114122122</v>
+        <v>0.4353219235819677</v>
       </c>
       <c r="D543" t="s">
         <v>7</v>
@@ -13571,10 +13571,10 @@
         <v>1096</v>
       </c>
       <c r="B544" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C544">
-        <v>0.4269150466488079</v>
+        <v>0.4133475971449067</v>
       </c>
       <c r="D544" t="s">
         <v>7</v>
@@ -13840,30 +13840,30 @@
         <v>1142</v>
       </c>
       <c r="B563" t="s">
+        <v>12</v>
+      </c>
+      <c r="C563">
+        <v>0.27879179341987</v>
+      </c>
+      <c r="D563" t="s">
         <v>1143</v>
       </c>
-      <c r="C563">
-        <v>0.2865285111941168</v>
-      </c>
-      <c r="D563" t="s">
+      <c r="E563" t="s">
         <v>1144</v>
-      </c>
-      <c r="E563" t="s">
-        <v>1145</v>
       </c>
     </row>
     <row r="564" spans="1:5">
       <c r="A564" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B564" t="s">
         <v>1146</v>
       </c>
-      <c r="B564" t="s">
+      <c r="C564">
+        <v>0.3239249580582771</v>
+      </c>
+      <c r="D564" t="s">
         <v>1143</v>
-      </c>
-      <c r="C564">
-        <v>0.3339874309238164</v>
-      </c>
-      <c r="D564" t="s">
-        <v>1144</v>
       </c>
       <c r="E564" t="s">
         <v>1147</v>
@@ -13874,13 +13874,13 @@
         <v>1148</v>
       </c>
       <c r="B565" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C565">
+        <v>0.2646874841175051</v>
+      </c>
+      <c r="D565" t="s">
         <v>1143</v>
-      </c>
-      <c r="C565">
-        <v>0.2828721453114191</v>
-      </c>
-      <c r="D565" t="s">
-        <v>1144</v>
       </c>
       <c r="E565" t="s">
         <v>1149</v>
@@ -13891,13 +13891,13 @@
         <v>1150</v>
       </c>
       <c r="B566" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C566">
+        <v>0.328114384096285</v>
+      </c>
+      <c r="D566" t="s">
         <v>1143</v>
-      </c>
-      <c r="C566">
-        <v>0.3514174809195016</v>
-      </c>
-      <c r="D566" t="s">
-        <v>1144</v>
       </c>
       <c r="E566" t="s">
         <v>1151</v>
@@ -13908,13 +13908,13 @@
         <v>1152</v>
       </c>
       <c r="B567" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C567">
+        <v>0.3814741478164655</v>
+      </c>
+      <c r="D567" t="s">
         <v>1143</v>
-      </c>
-      <c r="C567">
-        <v>0.4043560811426221</v>
-      </c>
-      <c r="D567" t="s">
-        <v>1144</v>
       </c>
       <c r="E567" t="s">
         <v>1153</v>
@@ -13925,13 +13925,13 @@
         <v>1154</v>
       </c>
       <c r="B568" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C568">
+        <v>0.3953370068743307</v>
+      </c>
+      <c r="D568" t="s">
         <v>1143</v>
-      </c>
-      <c r="C568">
-        <v>0.416972381564808</v>
-      </c>
-      <c r="D568" t="s">
-        <v>1144</v>
       </c>
       <c r="E568" t="s">
         <v>1155</v>
@@ -13942,13 +13942,13 @@
         <v>1156</v>
       </c>
       <c r="B569" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C569">
+        <v>0.2622990327257377</v>
+      </c>
+      <c r="D569" t="s">
         <v>1143</v>
-      </c>
-      <c r="C569">
-        <v>0.278861381828963</v>
-      </c>
-      <c r="D569" t="s">
-        <v>1144</v>
       </c>
       <c r="E569" t="s">
         <v>1157</v>
@@ -13959,13 +13959,13 @@
         <v>1158</v>
       </c>
       <c r="B570" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C570">
+        <v>0.2853634376069786</v>
+      </c>
+      <c r="D570" t="s">
         <v>1143</v>
-      </c>
-      <c r="C570">
-        <v>0.3017031666022623</v>
-      </c>
-      <c r="D570" t="s">
-        <v>1144</v>
       </c>
       <c r="E570" t="s">
         <v>1159</v>
@@ -13976,13 +13976,13 @@
         <v>1160</v>
       </c>
       <c r="B571" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C571">
+        <v>0.2827409217116091</v>
+      </c>
+      <c r="D571" t="s">
         <v>1143</v>
-      </c>
-      <c r="C571">
-        <v>0.2999826817944883</v>
-      </c>
-      <c r="D571" t="s">
-        <v>1144</v>
       </c>
       <c r="E571" t="s">
         <v>1161</v>
@@ -13993,13 +13993,13 @@
         <v>1162</v>
       </c>
       <c r="B572" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C572">
-        <v>0.3122559465192276</v>
+        <v>0.3446257030204877</v>
       </c>
       <c r="D572" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E572" t="s">
         <v>1163</v>
@@ -14010,13 +14010,13 @@
         <v>1164</v>
       </c>
       <c r="B573" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C573">
+        <v>0.3265096672591629</v>
+      </c>
+      <c r="D573" t="s">
         <v>1143</v>
-      </c>
-      <c r="C573">
-        <v>0.3459385868255951</v>
-      </c>
-      <c r="D573" t="s">
-        <v>1144</v>
       </c>
       <c r="E573" t="s">
         <v>1165</v>
@@ -14030,10 +14030,10 @@
         <v>44</v>
       </c>
       <c r="C574">
-        <v>0.378643135692091</v>
+        <v>0.3814268878392177</v>
       </c>
       <c r="D574" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E574" t="s">
         <v>1167</v>
@@ -14044,13 +14044,13 @@
         <v>1168</v>
       </c>
       <c r="B575" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C575">
+        <v>0.345816121665159</v>
+      </c>
+      <c r="D575" t="s">
         <v>1143</v>
-      </c>
-      <c r="C575">
-        <v>0.3691610948781308</v>
-      </c>
-      <c r="D575" t="s">
-        <v>1144</v>
       </c>
       <c r="E575" t="s">
         <v>1169</v>
@@ -14061,13 +14061,13 @@
         <v>1170</v>
       </c>
       <c r="B576" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C576">
+        <v>0.343709260421431</v>
+      </c>
+      <c r="D576" t="s">
         <v>1143</v>
-      </c>
-      <c r="C576">
-        <v>0.3662971392040494</v>
-      </c>
-      <c r="D576" t="s">
-        <v>1144</v>
       </c>
       <c r="E576" t="s">
         <v>1171</v>
@@ -14078,13 +14078,13 @@
         <v>1172</v>
       </c>
       <c r="B577" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C577">
-        <v>0.3686225924718544</v>
+        <v>0.3928711837409645</v>
       </c>
       <c r="D577" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E577" t="s">
         <v>1173</v>
@@ -14095,13 +14095,13 @@
         <v>1174</v>
       </c>
       <c r="B578" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C578">
+        <v>0.4002391507901918</v>
+      </c>
+      <c r="D578" t="s">
         <v>1143</v>
-      </c>
-      <c r="C578">
-        <v>0.4167835681629807</v>
-      </c>
-      <c r="D578" t="s">
-        <v>1144</v>
       </c>
       <c r="E578" t="s">
         <v>1175</v>
@@ -14112,13 +14112,13 @@
         <v>1176</v>
       </c>
       <c r="B579" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C579">
+        <v>0.3467561412074572</v>
+      </c>
+      <c r="D579" t="s">
         <v>1143</v>
-      </c>
-      <c r="C579">
-        <v>0.368898979892718</v>
-      </c>
-      <c r="D579" t="s">
-        <v>1144</v>
       </c>
       <c r="E579" t="s">
         <v>1177</v>
@@ -14129,13 +14129,13 @@
         <v>1178</v>
       </c>
       <c r="B580" t="s">
+        <v>6</v>
+      </c>
+      <c r="C580">
+        <v>0.3087481541854679</v>
+      </c>
+      <c r="D580" t="s">
         <v>1143</v>
-      </c>
-      <c r="C580">
-        <v>0.2973895616542105</v>
-      </c>
-      <c r="D580" t="s">
-        <v>1144</v>
       </c>
       <c r="E580" t="s">
         <v>1179</v>
@@ -14146,13 +14146,13 @@
         <v>1180</v>
       </c>
       <c r="B581" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C581">
+        <v>0.4572131491064606</v>
+      </c>
+      <c r="D581" t="s">
         <v>1143</v>
-      </c>
-      <c r="C581">
-        <v>0.4775904620545537</v>
-      </c>
-      <c r="D581" t="s">
-        <v>1144</v>
       </c>
       <c r="E581" t="s">
         <v>1181</v>
@@ -14163,13 +14163,13 @@
         <v>1182</v>
       </c>
       <c r="B582" t="s">
+        <v>12</v>
+      </c>
+      <c r="C582">
+        <v>0.3029628013100104</v>
+      </c>
+      <c r="D582" t="s">
         <v>1143</v>
-      </c>
-      <c r="C582">
-        <v>0.3172739456699379</v>
-      </c>
-      <c r="D582" t="s">
-        <v>1144</v>
       </c>
       <c r="E582" t="s">
         <v>1183</v>
@@ -14180,13 +14180,13 @@
         <v>1184</v>
       </c>
       <c r="B583" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C583">
+        <v>0.37355807069213</v>
+      </c>
+      <c r="D583" t="s">
         <v>1143</v>
-      </c>
-      <c r="C583">
-        <v>0.3946426741141454</v>
-      </c>
-      <c r="D583" t="s">
-        <v>1144</v>
       </c>
       <c r="E583" t="s">
         <v>1185</v>
@@ -14197,13 +14197,13 @@
         <v>1186</v>
       </c>
       <c r="B584" t="s">
+        <v>12</v>
+      </c>
+      <c r="C584">
+        <v>0.3109826823751518</v>
+      </c>
+      <c r="D584" t="s">
         <v>1143</v>
-      </c>
-      <c r="C584">
-        <v>0.316080871932035</v>
-      </c>
-      <c r="D584" t="s">
-        <v>1144</v>
       </c>
       <c r="E584" t="s">
         <v>1187</v>
@@ -14214,13 +14214,13 @@
         <v>1188</v>
       </c>
       <c r="B585" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C585">
+        <v>0.4014137622534586</v>
+      </c>
+      <c r="D585" t="s">
         <v>1143</v>
-      </c>
-      <c r="C585">
-        <v>0.4198479906612609</v>
-      </c>
-      <c r="D585" t="s">
-        <v>1144</v>
       </c>
       <c r="E585" t="s">
         <v>1189</v>
@@ -14231,13 +14231,13 @@
         <v>1190</v>
       </c>
       <c r="B586" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C586">
+        <v>0.2794613597048632</v>
+      </c>
+      <c r="D586" t="s">
         <v>1143</v>
-      </c>
-      <c r="C586">
-        <v>0.2966380962597527</v>
-      </c>
-      <c r="D586" t="s">
-        <v>1144</v>
       </c>
       <c r="E586" t="s">
         <v>1191</v>
@@ -14248,13 +14248,13 @@
         <v>1192</v>
       </c>
       <c r="B587" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C587">
-        <v>0.3296072117146631</v>
+        <v>0.3523544611256467</v>
       </c>
       <c r="D587" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E587" t="s">
         <v>1193</v>
@@ -14265,13 +14265,13 @@
         <v>1194</v>
       </c>
       <c r="B588" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C588">
+        <v>0.3039355909611097</v>
+      </c>
+      <c r="D588" t="s">
         <v>1143</v>
-      </c>
-      <c r="C588">
-        <v>0.3258780344804819</v>
-      </c>
-      <c r="D588" t="s">
-        <v>1144</v>
       </c>
       <c r="E588" t="s">
         <v>1195</v>
@@ -14285,10 +14285,10 @@
         <v>44</v>
       </c>
       <c r="C589">
-        <v>0.395583460929522</v>
+        <v>0.4041037129378175</v>
       </c>
       <c r="D589" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E589" t="s">
         <v>1197</v>
@@ -14299,13 +14299,13 @@
         <v>1198</v>
       </c>
       <c r="B590" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C590">
-        <v>0.4264305278055339</v>
+        <v>0.4484440023434808</v>
       </c>
       <c r="D590" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E590" t="s">
         <v>1199</v>
@@ -14316,13 +14316,13 @@
         <v>1200</v>
       </c>
       <c r="B591" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C591">
+        <v>0.5324168853157348</v>
+      </c>
+      <c r="D591" t="s">
         <v>1143</v>
-      </c>
-      <c r="C591">
-        <v>0.5232861714079698</v>
-      </c>
-      <c r="D591" t="s">
-        <v>1144</v>
       </c>
       <c r="E591" t="s">
         <v>1201</v>
@@ -14333,13 +14333,13 @@
         <v>1202</v>
       </c>
       <c r="B592" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C592">
+        <v>0.3415313299300413</v>
+      </c>
+      <c r="D592" t="s">
         <v>1143</v>
-      </c>
-      <c r="C592">
-        <v>0.3671092438643882</v>
-      </c>
-      <c r="D592" t="s">
-        <v>1144</v>
       </c>
       <c r="E592" t="s">
         <v>1203</v>
@@ -14350,13 +14350,13 @@
         <v>1204</v>
       </c>
       <c r="B593" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C593">
+        <v>0.6574734429186216</v>
+      </c>
+      <c r="D593" t="s">
         <v>1143</v>
-      </c>
-      <c r="C593">
-        <v>0.6604298792217997</v>
-      </c>
-      <c r="D593" t="s">
-        <v>1144</v>
       </c>
       <c r="E593" t="s">
         <v>1205</v>
@@ -14367,13 +14367,13 @@
         <v>1206</v>
       </c>
       <c r="B594" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C594">
+        <v>0.430820818582851</v>
+      </c>
+      <c r="D594" t="s">
         <v>1143</v>
-      </c>
-      <c r="C594">
-        <v>0.4549221969708119</v>
-      </c>
-      <c r="D594" t="s">
-        <v>1144</v>
       </c>
       <c r="E594" t="s">
         <v>1207</v>
@@ -14384,13 +14384,13 @@
         <v>1208</v>
       </c>
       <c r="B595" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C595">
-        <v>0.3365713467580632</v>
+        <v>0.3693323003894664</v>
       </c>
       <c r="D595" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E595" t="s">
         <v>1209</v>
@@ -14401,13 +14401,13 @@
         <v>1210</v>
       </c>
       <c r="B596" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C596">
+        <v>0.4144082144456794</v>
+      </c>
+      <c r="D596" t="s">
         <v>1143</v>
-      </c>
-      <c r="C596">
-        <v>0.440715214153251</v>
-      </c>
-      <c r="D596" t="s">
-        <v>1144</v>
       </c>
       <c r="E596" t="s">
         <v>1211</v>
@@ -14418,13 +14418,13 @@
         <v>1212</v>
       </c>
       <c r="B597" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C597">
-        <v>0.3386436516515572</v>
+        <v>0.3677889676473683</v>
       </c>
       <c r="D597" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E597" t="s">
         <v>1213</v>
@@ -14435,13 +14435,13 @@
         <v>1214</v>
       </c>
       <c r="B598" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C598">
-        <v>0.2350696594842309</v>
+        <v>0.2497307928150381</v>
       </c>
       <c r="D598" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E598" t="s">
         <v>1215</v>
@@ -14452,13 +14452,13 @@
         <v>1216</v>
       </c>
       <c r="B599" t="s">
+        <v>12</v>
+      </c>
+      <c r="C599">
+        <v>0.2795831780705831</v>
+      </c>
+      <c r="D599" t="s">
         <v>1143</v>
-      </c>
-      <c r="C599">
-        <v>0.2610651933945889</v>
-      </c>
-      <c r="D599" t="s">
-        <v>1144</v>
       </c>
       <c r="E599" t="s">
         <v>1217</v>
@@ -14469,13 +14469,13 @@
         <v>1218</v>
       </c>
       <c r="B600" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C600">
+        <v>0.2694980140305447</v>
+      </c>
+      <c r="D600" t="s">
         <v>1143</v>
-      </c>
-      <c r="C600">
-        <v>0.2868728206048362</v>
-      </c>
-      <c r="D600" t="s">
-        <v>1144</v>
       </c>
       <c r="E600" t="s">
         <v>1219</v>
@@ -14486,13 +14486,13 @@
         <v>1220</v>
       </c>
       <c r="B601" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C601">
+        <v>0.2558575056851942</v>
+      </c>
+      <c r="D601" t="s">
         <v>1143</v>
-      </c>
-      <c r="C601">
-        <v>0.2715044257637401</v>
-      </c>
-      <c r="D601" t="s">
-        <v>1144</v>
       </c>
       <c r="E601" t="s">
         <v>1221</v>
@@ -14503,13 +14503,13 @@
         <v>1222</v>
       </c>
       <c r="B602" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C602">
+        <v>0.3454317876177139</v>
+      </c>
+      <c r="D602" t="s">
         <v>1143</v>
-      </c>
-      <c r="C602">
-        <v>0.3692534940030507</v>
-      </c>
-      <c r="D602" t="s">
-        <v>1144</v>
       </c>
       <c r="E602" t="s">
         <v>1223</v>
@@ -14520,13 +14520,13 @@
         <v>1224</v>
       </c>
       <c r="B603" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C603">
+        <v>0.2807612943435618</v>
+      </c>
+      <c r="D603" t="s">
         <v>1143</v>
-      </c>
-      <c r="C603">
-        <v>0.2986593688687957</v>
-      </c>
-      <c r="D603" t="s">
-        <v>1144</v>
       </c>
       <c r="E603" t="s">
         <v>1225</v>
@@ -14537,13 +14537,13 @@
         <v>1226</v>
       </c>
       <c r="B604" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C604">
-        <v>0.3467080003355819</v>
+        <v>0.3712521734837993</v>
       </c>
       <c r="D604" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E604" t="s">
         <v>1227</v>
@@ -14557,10 +14557,10 @@
         <v>44</v>
       </c>
       <c r="C605">
-        <v>0.2800703919991974</v>
+        <v>0.2715879372725378</v>
       </c>
       <c r="D605" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E605" t="s">
         <v>1229</v>
@@ -14571,13 +14571,13 @@
         <v>1230</v>
       </c>
       <c r="B606" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C606">
-        <v>0.3436490912262617</v>
+        <v>0.3765226506346622</v>
       </c>
       <c r="D606" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E606" t="s">
         <v>1231</v>
@@ -14588,13 +14588,13 @@
         <v>1232</v>
       </c>
       <c r="B607" t="s">
+        <v>6</v>
+      </c>
+      <c r="C607">
+        <v>0.325044004041226</v>
+      </c>
+      <c r="D607" t="s">
         <v>1143</v>
-      </c>
-      <c r="C607">
-        <v>0.3163889512953308</v>
-      </c>
-      <c r="D607" t="s">
-        <v>1144</v>
       </c>
       <c r="E607" t="s">
         <v>1233</v>
@@ -14605,13 +14605,13 @@
         <v>1234</v>
       </c>
       <c r="B608" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C608">
-        <v>0.3236963165065845</v>
+        <v>0.3488294823410722</v>
       </c>
       <c r="D608" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E608" t="s">
         <v>1235</v>
@@ -14622,13 +14622,13 @@
         <v>1236</v>
       </c>
       <c r="B609" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C609">
-        <v>0.3391774988580925</v>
+        <v>0.3619710251521469</v>
       </c>
       <c r="D609" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E609" t="s">
         <v>1237</v>
@@ -14639,13 +14639,13 @@
         <v>1238</v>
       </c>
       <c r="B610" t="s">
+        <v>12</v>
+      </c>
+      <c r="C610">
+        <v>0.2985730827949721</v>
+      </c>
+      <c r="D610" t="s">
         <v>1143</v>
-      </c>
-      <c r="C610">
-        <v>0.2729780037803216</v>
-      </c>
-      <c r="D610" t="s">
-        <v>1144</v>
       </c>
       <c r="E610" t="s">
         <v>1239</v>
@@ -14659,10 +14659,10 @@
         <v>44</v>
       </c>
       <c r="C611">
-        <v>0.5388467831689995</v>
+        <v>0.5409530656282712</v>
       </c>
       <c r="D611" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E611" t="s">
         <v>1241</v>
@@ -14676,10 +14676,10 @@
         <v>44</v>
       </c>
       <c r="C612">
-        <v>0.3807404865749753</v>
+        <v>0.3749469117602584</v>
       </c>
       <c r="D612" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E612" t="s">
         <v>1243</v>
@@ -14690,13 +14690,13 @@
         <v>1244</v>
       </c>
       <c r="B613" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C613">
+        <v>0.320688516645652</v>
+      </c>
+      <c r="D613" t="s">
         <v>1143</v>
-      </c>
-      <c r="C613">
-        <v>0.3419520005963805</v>
-      </c>
-      <c r="D613" t="s">
-        <v>1144</v>
       </c>
       <c r="E613" t="s">
         <v>1245</v>
@@ -14707,13 +14707,13 @@
         <v>1246</v>
       </c>
       <c r="B614" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C614">
+        <v>0.4218295463281418</v>
+      </c>
+      <c r="D614" t="s">
         <v>1143</v>
-      </c>
-      <c r="C614">
-        <v>0.4458582165764014</v>
-      </c>
-      <c r="D614" t="s">
-        <v>1144</v>
       </c>
       <c r="E614" t="s">
         <v>1247</v>
@@ -14724,13 +14724,13 @@
         <v>1248</v>
       </c>
       <c r="B615" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C615">
+        <v>0.3380208456119674</v>
+      </c>
+      <c r="D615" t="s">
         <v>1143</v>
-      </c>
-      <c r="C615">
-        <v>0.3492784724364053</v>
-      </c>
-      <c r="D615" t="s">
-        <v>1144</v>
       </c>
       <c r="E615" t="s">
         <v>1249</v>
@@ -14741,13 +14741,13 @@
         <v>1250</v>
       </c>
       <c r="B616" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C616">
+        <v>0.4086418852777425</v>
+      </c>
+      <c r="D616" t="s">
         <v>1143</v>
-      </c>
-      <c r="C616">
-        <v>0.4313512875114154</v>
-      </c>
-      <c r="D616" t="s">
-        <v>1144</v>
       </c>
       <c r="E616" t="s">
         <v>1251</v>
@@ -14758,13 +14758,13 @@
         <v>1252</v>
       </c>
       <c r="B617" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C617">
+        <v>0.3376930789676206</v>
+      </c>
+      <c r="D617" t="s">
         <v>1143</v>
-      </c>
-      <c r="C617">
-        <v>0.3571567164381891</v>
-      </c>
-      <c r="D617" t="s">
-        <v>1144</v>
       </c>
       <c r="E617" t="s">
         <v>1253</v>
@@ -14775,13 +14775,13 @@
         <v>1254</v>
       </c>
       <c r="B618" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C618">
-        <v>0.33930915671825</v>
+        <v>0.3638839849201608</v>
       </c>
       <c r="D618" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E618" t="s">
         <v>1255</v>
@@ -14792,13 +14792,13 @@
         <v>1256</v>
       </c>
       <c r="B619" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C619">
+        <v>0.4295936363309433</v>
+      </c>
+      <c r="D619" t="s">
         <v>1143</v>
-      </c>
-      <c r="C619">
-        <v>0.4462944994357868</v>
-      </c>
-      <c r="D619" t="s">
-        <v>1144</v>
       </c>
       <c r="E619" t="s">
         <v>1257</v>
@@ -14809,10 +14809,10 @@
         <v>1258</v>
       </c>
       <c r="B620" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C620">
-        <v>0.327838706255678</v>
+        <v>0.3278662904908047</v>
       </c>
       <c r="D620" t="s">
         <v>1259</v>
@@ -14829,7 +14829,7 @@
         <v>15</v>
       </c>
       <c r="C621">
-        <v>0.3546101422023398</v>
+        <v>0.3551411668606793</v>
       </c>
       <c r="D621" t="s">
         <v>1259</v>
@@ -14843,10 +14843,10 @@
         <v>1263</v>
       </c>
       <c r="B622" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C622">
-        <v>0.2765414860679696</v>
+        <v>0.2765710284333049</v>
       </c>
       <c r="D622" t="s">
         <v>1259</v>
@@ -14863,7 +14863,7 @@
         <v>1266</v>
       </c>
       <c r="C623">
-        <v>0.2195260848268209</v>
+        <v>0.2191117244497651</v>
       </c>
       <c r="D623" t="s">
         <v>1259</v>
@@ -14877,10 +14877,10 @@
         <v>1268</v>
       </c>
       <c r="B624" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C624">
-        <v>0.3012827392581843</v>
+        <v>0.3013174439129063</v>
       </c>
       <c r="D624" t="s">
         <v>1259</v>
@@ -14894,10 +14894,10 @@
         <v>1270</v>
       </c>
       <c r="B625" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C625">
-        <v>0.2483885027536836</v>
+        <v>0.2484816907768088</v>
       </c>
       <c r="D625" t="s">
         <v>1259</v>
@@ -14914,7 +14914,7 @@
         <v>15</v>
       </c>
       <c r="C626">
-        <v>0.3603009123828729</v>
+        <v>0.3608546553895554</v>
       </c>
       <c r="D626" t="s">
         <v>1259</v>
@@ -14931,7 +14931,7 @@
         <v>1266</v>
       </c>
       <c r="C627">
-        <v>0.2864388349466772</v>
+        <v>0.2859833994655254</v>
       </c>
       <c r="D627" t="s">
         <v>1259</v>
@@ -14945,10 +14945,10 @@
         <v>1276</v>
       </c>
       <c r="B628" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C628">
-        <v>0.2329797822499295</v>
+        <v>0.233098801377836</v>
       </c>
       <c r="D628" t="s">
         <v>1259</v>
@@ -14962,10 +14962,10 @@
         <v>1278</v>
       </c>
       <c r="B629" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C629">
-        <v>0.2727677869853829</v>
+        <v>0.272837428093292</v>
       </c>
       <c r="D629" t="s">
         <v>1259</v>
@@ -14982,7 +14982,7 @@
         <v>1266</v>
       </c>
       <c r="C630">
-        <v>0.3095066910545931</v>
+        <v>0.3090337644068571</v>
       </c>
       <c r="D630" t="s">
         <v>1259</v>
@@ -14999,7 +14999,7 @@
         <v>1266</v>
       </c>
       <c r="C631">
-        <v>0.3071006368244846</v>
+        <v>0.3066884388449687</v>
       </c>
       <c r="D631" t="s">
         <v>1259</v>
@@ -15016,7 +15016,7 @@
         <v>1266</v>
       </c>
       <c r="C632">
-        <v>0.3970017550027115</v>
+        <v>0.396501369761091</v>
       </c>
       <c r="D632" t="s">
         <v>1259</v>
@@ -15033,7 +15033,7 @@
         <v>15</v>
       </c>
       <c r="C633">
-        <v>0.2700895497368387</v>
+        <v>0.2705910581210036</v>
       </c>
       <c r="D633" t="s">
         <v>1259</v>
@@ -15050,7 +15050,7 @@
         <v>15</v>
       </c>
       <c r="C634">
-        <v>0.425560222265739</v>
+        <v>0.4259419518583432</v>
       </c>
       <c r="D634" t="s">
         <v>1259</v>
@@ -15067,7 +15067,7 @@
         <v>1266</v>
       </c>
       <c r="C635">
-        <v>0.460028709054074</v>
+        <v>0.4595439929718509</v>
       </c>
       <c r="D635" t="s">
         <v>1259</v>
@@ -15081,10 +15081,10 @@
         <v>1292</v>
       </c>
       <c r="B636" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C636">
-        <v>0.3745972168681952</v>
+        <v>0.3746083195459203</v>
       </c>
       <c r="D636" t="s">
         <v>1259</v>
@@ -15101,7 +15101,7 @@
         <v>15</v>
       </c>
       <c r="C637">
-        <v>0.2999316228030968</v>
+        <v>0.3004285639190377</v>
       </c>
       <c r="D637" t="s">
         <v>1259</v>
@@ -15118,7 +15118,7 @@
         <v>1266</v>
       </c>
       <c r="C638">
-        <v>0.4256926247246307</v>
+        <v>0.4254250865066503</v>
       </c>
       <c r="D638" t="s">
         <v>1259</v>
@@ -15132,10 +15132,10 @@
         <v>1298</v>
       </c>
       <c r="B639" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C639">
-        <v>0.3433022002984534</v>
+        <v>0.3433262666407025</v>
       </c>
       <c r="D639" t="s">
         <v>1259</v>
@@ -15149,10 +15149,10 @@
         <v>1300</v>
       </c>
       <c r="B640" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C640">
-        <v>0.3120986368406384</v>
+        <v>0.3121835458922222</v>
       </c>
       <c r="D640" t="s">
         <v>1259</v>
@@ -15169,7 +15169,7 @@
         <v>15</v>
       </c>
       <c r="C641">
-        <v>0.275672472911778</v>
+        <v>0.2761513430518701</v>
       </c>
       <c r="D641" t="s">
         <v>1259</v>
@@ -15186,7 +15186,7 @@
         <v>1266</v>
       </c>
       <c r="C642">
-        <v>0.285644092319161</v>
+        <v>0.2851580840514525</v>
       </c>
       <c r="D642" t="s">
         <v>1259</v>
@@ -15203,7 +15203,7 @@
         <v>15</v>
       </c>
       <c r="C643">
-        <v>0.3437100119396257</v>
+        <v>0.3442305383897116</v>
       </c>
       <c r="D643" t="s">
         <v>1259</v>
@@ -15220,7 +15220,7 @@
         <v>15</v>
       </c>
       <c r="C644">
-        <v>0.2914450730017736</v>
+        <v>0.291935388459783</v>
       </c>
       <c r="D644" t="s">
         <v>1259</v>
@@ -15237,7 +15237,7 @@
         <v>15</v>
       </c>
       <c r="C645">
-        <v>0.2499514734199365</v>
+        <v>0.250413529510035</v>
       </c>
       <c r="D645" t="s">
         <v>1259</v>
@@ -15254,7 +15254,7 @@
         <v>15</v>
       </c>
       <c r="C646">
-        <v>0.3690748629684756</v>
+        <v>0.3695681570748545</v>
       </c>
       <c r="D646" t="s">
         <v>1259</v>
@@ -15268,10 +15268,10 @@
         <v>1314</v>
       </c>
       <c r="B647" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C647">
-        <v>0.2992509391881946</v>
+        <v>0.2993135631546125</v>
       </c>
       <c r="D647" t="s">
         <v>1259</v>
@@ -15288,7 +15288,7 @@
         <v>15</v>
       </c>
       <c r="C648">
-        <v>0.3093236047485535</v>
+        <v>0.3098350305973636</v>
       </c>
       <c r="D648" t="s">
         <v>1259</v>
@@ -15305,7 +15305,7 @@
         <v>15</v>
       </c>
       <c r="C649">
-        <v>0.355576724583402</v>
+        <v>0.3560970724312739</v>
       </c>
       <c r="D649" t="s">
         <v>1259</v>
@@ -15319,10 +15319,10 @@
         <v>1320</v>
       </c>
       <c r="B650" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C650">
-        <v>0.2844631870191548</v>
+        <v>0.2845150054340436</v>
       </c>
       <c r="D650" t="s">
         <v>1259</v>
@@ -15339,7 +15339,7 @@
         <v>15</v>
       </c>
       <c r="C651">
-        <v>0.3335918913220633</v>
+        <v>0.3341295391172087</v>
       </c>
       <c r="D651" t="s">
         <v>1259</v>
@@ -15371,15 +15371,15 @@
         <v>15</v>
       </c>
       <c r="B2">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B3">
-        <v>134</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -15387,15 +15387,15 @@
         <v>145</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B5">
-        <v>265</v>
+        <v>255</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -15403,7 +15403,7 @@
         <v>44</v>
       </c>
       <c r="B6">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -15424,10 +15424,10 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>1143</v>
+        <v>1146</v>
       </c>
       <c r="B9">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:2">

--- a/frontend/data/uk_election_predictions.xlsx
+++ b/frontend/data/uk_election_predictions.xlsx
@@ -35,25 +35,25 @@
     <t>aldershot</t>
   </si>
   <si>
+    <t>Labour</t>
+  </si>
+  <si>
+    <t>England</t>
+  </si>
+  <si>
+    <t>E14001063</t>
+  </si>
+  <si>
+    <t>aldridge-brownhills</t>
+  </si>
+  <si>
     <t>Conservative</t>
   </si>
   <si>
-    <t>England</t>
-  </si>
-  <si>
-    <t>E14001063</t>
-  </si>
-  <si>
-    <t>aldridge-brownhills</t>
-  </si>
-  <si>
     <t>E14001064</t>
   </si>
   <si>
     <t>altrincham and sale west</t>
-  </si>
-  <si>
-    <t>Labour</t>
   </si>
   <si>
     <t>E14001065</t>
@@ -4360,7 +4360,7 @@
         <v>6</v>
       </c>
       <c r="C2">
-        <v>0.3089361890270064</v>
+        <v>0.3289653833422099</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
@@ -4374,27 +4374,27 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C3">
-        <v>0.4239419994104246</v>
+        <v>0.4260047694844682</v>
       </c>
       <c r="D3" t="s">
         <v>7</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C4">
-        <v>0.4041092028102727</v>
+        <v>0.423111830868948</v>
       </c>
       <c r="D4" t="s">
         <v>7</v>
@@ -4411,7 +4411,7 @@
         <v>15</v>
       </c>
       <c r="C5">
-        <v>0.3776338725442422</v>
+        <v>0.3565970282414205</v>
       </c>
       <c r="D5" t="s">
         <v>7</v>
@@ -4425,10 +4425,10 @@
         <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C6">
-        <v>0.4029138480718916</v>
+        <v>0.406845424576544</v>
       </c>
       <c r="D6" t="s">
         <v>7</v>
@@ -4442,10 +4442,10 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C7">
-        <v>0.3267657874505037</v>
+        <v>0.3432546551195295</v>
       </c>
       <c r="D7" t="s">
         <v>7</v>
@@ -4459,10 +4459,10 @@
         <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C8">
-        <v>0.3394647709705603</v>
+        <v>0.3256093424790764</v>
       </c>
       <c r="D8" t="s">
         <v>7</v>
@@ -4476,10 +4476,10 @@
         <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C9">
-        <v>0.3164046736507709</v>
+        <v>0.3096630845860979</v>
       </c>
       <c r="D9" t="s">
         <v>7</v>
@@ -4493,10 +4493,10 @@
         <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C10">
-        <v>0.3534427058878392</v>
+        <v>0.3564925710245171</v>
       </c>
       <c r="D10" t="s">
         <v>7</v>
@@ -4510,10 +4510,10 @@
         <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C11">
-        <v>0.2321970610160016</v>
+        <v>0.2240690076675117</v>
       </c>
       <c r="D11" t="s">
         <v>7</v>
@@ -4527,10 +4527,10 @@
         <v>29</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C12">
-        <v>0.4076041132940694</v>
+        <v>0.4234417739132951</v>
       </c>
       <c r="D12" t="s">
         <v>7</v>
@@ -4544,10 +4544,10 @@
         <v>31</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C13">
-        <v>0.2998339533963955</v>
+        <v>0.2958450291265594</v>
       </c>
       <c r="D13" t="s">
         <v>7</v>
@@ -4564,7 +4564,7 @@
         <v>15</v>
       </c>
       <c r="C14">
-        <v>0.3845917348789192</v>
+        <v>0.3662865321668959</v>
       </c>
       <c r="D14" t="s">
         <v>7</v>
@@ -4578,10 +4578,10 @@
         <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C15">
-        <v>0.3786686288650424</v>
+        <v>0.3799754354473133</v>
       </c>
       <c r="D15" t="s">
         <v>7</v>
@@ -4595,10 +4595,10 @@
         <v>37</v>
       </c>
       <c r="B16" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C16">
-        <v>0.3466480686112843</v>
+        <v>0.3657404419142363</v>
       </c>
       <c r="D16" t="s">
         <v>7</v>
@@ -4612,10 +4612,10 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C17">
-        <v>0.2872286865785014</v>
+        <v>0.2893976115276043</v>
       </c>
       <c r="D17" t="s">
         <v>7</v>
@@ -4629,10 +4629,10 @@
         <v>41</v>
       </c>
       <c r="B18" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C18">
-        <v>0.3388249669557636</v>
+        <v>0.3411388495056361</v>
       </c>
       <c r="D18" t="s">
         <v>7</v>
@@ -4649,7 +4649,7 @@
         <v>44</v>
       </c>
       <c r="C19">
-        <v>0.4205724607029313</v>
+        <v>0.4136611159512015</v>
       </c>
       <c r="D19" t="s">
         <v>7</v>
@@ -4663,10 +4663,10 @@
         <v>46</v>
       </c>
       <c r="B20" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C20">
-        <v>0.4546565518194737</v>
+        <v>0.4717344398318465</v>
       </c>
       <c r="D20" t="s">
         <v>7</v>
@@ -4680,10 +4680,10 @@
         <v>48</v>
       </c>
       <c r="B21" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C21">
-        <v>0.411808702421012</v>
+        <v>0.4194217705746495</v>
       </c>
       <c r="D21" t="s">
         <v>7</v>
@@ -4697,10 +4697,10 @@
         <v>50</v>
       </c>
       <c r="B22" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C22">
-        <v>0.3700704246641553</v>
+        <v>0.3897540327054654</v>
       </c>
       <c r="D22" t="s">
         <v>7</v>
@@ -4714,10 +4714,10 @@
         <v>52</v>
       </c>
       <c r="B23" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C23">
-        <v>0.4609682391635985</v>
+        <v>0.4810130225302497</v>
       </c>
       <c r="D23" t="s">
         <v>7</v>
@@ -4731,10 +4731,10 @@
         <v>54</v>
       </c>
       <c r="B24" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C24">
-        <v>0.3556398850061476</v>
+        <v>0.3741380109991789</v>
       </c>
       <c r="D24" t="s">
         <v>7</v>
@@ -4748,10 +4748,10 @@
         <v>56</v>
       </c>
       <c r="B25" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C25">
-        <v>0.6216335437310239</v>
+        <v>0.6337603634468535</v>
       </c>
       <c r="D25" t="s">
         <v>7</v>
@@ -4765,10 +4765,10 @@
         <v>58</v>
       </c>
       <c r="B26" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C26">
-        <v>0.2901439505620627</v>
+        <v>0.308190526707846</v>
       </c>
       <c r="D26" t="s">
         <v>7</v>
@@ -4782,10 +4782,10 @@
         <v>60</v>
       </c>
       <c r="B27" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C27">
-        <v>0.3100446797202301</v>
+        <v>0.312092986081799</v>
       </c>
       <c r="D27" t="s">
         <v>7</v>
@@ -4799,10 +4799,10 @@
         <v>62</v>
       </c>
       <c r="B28" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C28">
-        <v>0.3239707257194963</v>
+        <v>0.344666363099958</v>
       </c>
       <c r="D28" t="s">
         <v>7</v>
@@ -4819,7 +4819,7 @@
         <v>44</v>
       </c>
       <c r="C29">
-        <v>0.4200935343725836</v>
+        <v>0.413232979939163</v>
       </c>
       <c r="D29" t="s">
         <v>7</v>
@@ -4833,10 +4833,10 @@
         <v>66</v>
       </c>
       <c r="B30" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C30">
-        <v>0.3912339886155048</v>
+        <v>0.409318230724802</v>
       </c>
       <c r="D30" t="s">
         <v>7</v>
@@ -4850,10 +4850,10 @@
         <v>68</v>
       </c>
       <c r="B31" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C31">
-        <v>0.4605120136826356</v>
+        <v>0.4769115341553035</v>
       </c>
       <c r="D31" t="s">
         <v>7</v>
@@ -4870,7 +4870,7 @@
         <v>15</v>
       </c>
       <c r="C32">
-        <v>0.406398644337622</v>
+        <v>0.3872553057308337</v>
       </c>
       <c r="D32" t="s">
         <v>7</v>
@@ -4884,10 +4884,10 @@
         <v>72</v>
       </c>
       <c r="B33" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C33">
-        <v>0.4150870054199206</v>
+        <v>0.4300422494952387</v>
       </c>
       <c r="D33" t="s">
         <v>7</v>
@@ -4904,7 +4904,7 @@
         <v>15</v>
       </c>
       <c r="C34">
-        <v>0.3274515813018074</v>
+        <v>0.3076457062738653</v>
       </c>
       <c r="D34" t="s">
         <v>7</v>
@@ -4918,10 +4918,10 @@
         <v>76</v>
       </c>
       <c r="B35" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C35">
-        <v>0.4676710924625198</v>
+        <v>0.4821046331957373</v>
       </c>
       <c r="D35" t="s">
         <v>7</v>
@@ -4935,10 +4935,10 @@
         <v>78</v>
       </c>
       <c r="B36" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C36">
-        <v>0.2593734862987884</v>
+        <v>0.2770559376605885</v>
       </c>
       <c r="D36" t="s">
         <v>7</v>
@@ -4952,10 +4952,10 @@
         <v>80</v>
       </c>
       <c r="B37" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C37">
-        <v>0.316296777209943</v>
+        <v>0.3162225434615302</v>
       </c>
       <c r="D37" t="s">
         <v>7</v>
@@ -4969,10 +4969,10 @@
         <v>82</v>
       </c>
       <c r="B38" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C38">
-        <v>0.3514283498905464</v>
+        <v>0.3710788830906041</v>
       </c>
       <c r="D38" t="s">
         <v>7</v>
@@ -4986,10 +4986,10 @@
         <v>84</v>
       </c>
       <c r="B39" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C39">
-        <v>0.322815747752313</v>
+        <v>0.3424041983721556</v>
       </c>
       <c r="D39" t="s">
         <v>7</v>
@@ -5003,10 +5003,10 @@
         <v>86</v>
       </c>
       <c r="B40" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C40">
-        <v>0.4935175079684386</v>
+        <v>0.5121342766135777</v>
       </c>
       <c r="D40" t="s">
         <v>7</v>
@@ -5020,10 +5020,10 @@
         <v>88</v>
       </c>
       <c r="B41" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C41">
-        <v>0.2988619667608612</v>
+        <v>0.2985749574772059</v>
       </c>
       <c r="D41" t="s">
         <v>7</v>
@@ -5037,10 +5037,10 @@
         <v>90</v>
       </c>
       <c r="B42" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C42">
-        <v>0.5345587892554764</v>
+        <v>0.5506843111599619</v>
       </c>
       <c r="D42" t="s">
         <v>7</v>
@@ -5057,7 +5057,7 @@
         <v>15</v>
       </c>
       <c r="C43">
-        <v>0.3930335051288815</v>
+        <v>0.3720740728955613</v>
       </c>
       <c r="D43" t="s">
         <v>7</v>
@@ -5074,7 +5074,7 @@
         <v>15</v>
       </c>
       <c r="C44">
-        <v>0.4309291839402182</v>
+        <v>0.4101146116200795</v>
       </c>
       <c r="D44" t="s">
         <v>7</v>
@@ -5088,10 +5088,10 @@
         <v>96</v>
       </c>
       <c r="B45" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C45">
-        <v>0.4219584861650154</v>
+        <v>0.4425601809325658</v>
       </c>
       <c r="D45" t="s">
         <v>7</v>
@@ -5105,10 +5105,10 @@
         <v>98</v>
       </c>
       <c r="B46" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C46">
-        <v>0.4096429268681686</v>
+        <v>0.4273378615207259</v>
       </c>
       <c r="D46" t="s">
         <v>7</v>
@@ -5125,7 +5125,7 @@
         <v>15</v>
       </c>
       <c r="C47">
-        <v>0.2953464576464722</v>
+        <v>0.2773919733715783</v>
       </c>
       <c r="D47" t="s">
         <v>7</v>
@@ -5142,7 +5142,7 @@
         <v>15</v>
       </c>
       <c r="C48">
-        <v>0.4107673869722708</v>
+        <v>0.3904939937984963</v>
       </c>
       <c r="D48" t="s">
         <v>7</v>
@@ -5159,7 +5159,7 @@
         <v>15</v>
       </c>
       <c r="C49">
-        <v>0.3256510092007087</v>
+        <v>0.3073512002380215</v>
       </c>
       <c r="D49" t="s">
         <v>7</v>
@@ -5176,7 +5176,7 @@
         <v>15</v>
       </c>
       <c r="C50">
-        <v>0.3654136442313836</v>
+        <v>0.3449151389579794</v>
       </c>
       <c r="D50" t="s">
         <v>7</v>
@@ -5193,7 +5193,7 @@
         <v>15</v>
       </c>
       <c r="C51">
-        <v>0.3520448794201434</v>
+        <v>0.3331181886681006</v>
       </c>
       <c r="D51" t="s">
         <v>7</v>
@@ -5207,10 +5207,10 @@
         <v>110</v>
       </c>
       <c r="B52" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C52">
-        <v>0.5217939925913709</v>
+        <v>0.5382623564005196</v>
       </c>
       <c r="D52" t="s">
         <v>7</v>
@@ -5227,7 +5227,7 @@
         <v>15</v>
       </c>
       <c r="C53">
-        <v>0.4448075024690321</v>
+        <v>0.4262023795561595</v>
       </c>
       <c r="D53" t="s">
         <v>7</v>
@@ -5241,10 +5241,10 @@
         <v>114</v>
       </c>
       <c r="B54" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C54">
-        <v>0.4115338619376534</v>
+        <v>0.4309446137952609</v>
       </c>
       <c r="D54" t="s">
         <v>7</v>
@@ -5258,10 +5258,10 @@
         <v>116</v>
       </c>
       <c r="B55" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C55">
-        <v>0.311373099780354</v>
+        <v>0.3139768421080206</v>
       </c>
       <c r="D55" t="s">
         <v>7</v>
@@ -5275,10 +5275,10 @@
         <v>118</v>
       </c>
       <c r="B56" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C56">
-        <v>0.4052380212400331</v>
+        <v>0.4072231668587288</v>
       </c>
       <c r="D56" t="s">
         <v>7</v>
@@ -5292,10 +5292,10 @@
         <v>120</v>
       </c>
       <c r="B57" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C57">
-        <v>0.5559918970011678</v>
+        <v>0.573109050019448</v>
       </c>
       <c r="D57" t="s">
         <v>7</v>
@@ -5309,10 +5309,10 @@
         <v>122</v>
       </c>
       <c r="B58" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C58">
-        <v>0.3390541829800454</v>
+        <v>0.355903450697221</v>
       </c>
       <c r="D58" t="s">
         <v>7</v>
@@ -5326,10 +5326,10 @@
         <v>124</v>
       </c>
       <c r="B59" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C59">
-        <v>0.3793136334753959</v>
+        <v>0.3931508489512807</v>
       </c>
       <c r="D59" t="s">
         <v>7</v>
@@ -5343,10 +5343,10 @@
         <v>126</v>
       </c>
       <c r="B60" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C60">
-        <v>0.3250573434045577</v>
+        <v>0.3452998540101524</v>
       </c>
       <c r="D60" t="s">
         <v>7</v>
@@ -5360,10 +5360,10 @@
         <v>128</v>
       </c>
       <c r="B61" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C61">
-        <v>0.3857339822555611</v>
+        <v>0.4028038127745576</v>
       </c>
       <c r="D61" t="s">
         <v>7</v>
@@ -5377,10 +5377,10 @@
         <v>130</v>
       </c>
       <c r="B62" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C62">
-        <v>0.3859060290596675</v>
+        <v>0.3856606121239725</v>
       </c>
       <c r="D62" t="s">
         <v>7</v>
@@ -5394,10 +5394,10 @@
         <v>132</v>
       </c>
       <c r="B63" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C63">
-        <v>0.3863504905310944</v>
+        <v>0.4037334279396249</v>
       </c>
       <c r="D63" t="s">
         <v>7</v>
@@ -5411,10 +5411,10 @@
         <v>134</v>
       </c>
       <c r="B64" t="s">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="C64">
-        <v>0.2264391393869829</v>
+        <v>0.227800192906883</v>
       </c>
       <c r="D64" t="s">
         <v>7</v>
@@ -5428,10 +5428,10 @@
         <v>136</v>
       </c>
       <c r="B65" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C65">
-        <v>0.3422859589209933</v>
+        <v>0.3451964425452142</v>
       </c>
       <c r="D65" t="s">
         <v>7</v>
@@ -5445,10 +5445,10 @@
         <v>138</v>
       </c>
       <c r="B66" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C66">
-        <v>0.3391698967485272</v>
+        <v>0.3419393748500511</v>
       </c>
       <c r="D66" t="s">
         <v>7</v>
@@ -5465,7 +5465,7 @@
         <v>15</v>
       </c>
       <c r="C67">
-        <v>0.3382369480450507</v>
+        <v>0.3197423008616184</v>
       </c>
       <c r="D67" t="s">
         <v>7</v>
@@ -5479,10 +5479,10 @@
         <v>142</v>
       </c>
       <c r="B68" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C68">
-        <v>0.330194130912436</v>
+        <v>0.3490469699094162</v>
       </c>
       <c r="D68" t="s">
         <v>7</v>
@@ -5499,7 +5499,7 @@
         <v>145</v>
       </c>
       <c r="C69">
-        <v>0.4875564351619477</v>
+        <v>0.4913619127718122</v>
       </c>
       <c r="D69" t="s">
         <v>7</v>
@@ -5516,7 +5516,7 @@
         <v>145</v>
       </c>
       <c r="C70">
-        <v>0.4436873200723312</v>
+        <v>0.4463973204564242</v>
       </c>
       <c r="D70" t="s">
         <v>7</v>
@@ -5530,10 +5530,10 @@
         <v>149</v>
       </c>
       <c r="B71" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C71">
-        <v>0.496831361499494</v>
+        <v>0.5077699877020571</v>
       </c>
       <c r="D71" t="s">
         <v>7</v>
@@ -5547,10 +5547,10 @@
         <v>151</v>
       </c>
       <c r="B72" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C72">
-        <v>0.3941306982800571</v>
+        <v>0.4149869950640694</v>
       </c>
       <c r="D72" t="s">
         <v>7</v>
@@ -5564,10 +5564,10 @@
         <v>153</v>
       </c>
       <c r="B73" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C73">
-        <v>0.52190071998596</v>
+        <v>0.5392628207795375</v>
       </c>
       <c r="D73" t="s">
         <v>7</v>
@@ -5581,10 +5581,10 @@
         <v>155</v>
       </c>
       <c r="B74" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C74">
-        <v>0.5154012914376723</v>
+        <v>0.532164411356876</v>
       </c>
       <c r="D74" t="s">
         <v>7</v>
@@ -5598,10 +5598,10 @@
         <v>157</v>
       </c>
       <c r="B75" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C75">
-        <v>0.3314367917668221</v>
+        <v>0.3345262925952142</v>
       </c>
       <c r="D75" t="s">
         <v>7</v>
@@ -5615,10 +5615,10 @@
         <v>159</v>
       </c>
       <c r="B76" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C76">
-        <v>0.3699147370448828</v>
+        <v>0.3715336071935639</v>
       </c>
       <c r="D76" t="s">
         <v>7</v>
@@ -5632,10 +5632,10 @@
         <v>161</v>
       </c>
       <c r="B77" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C77">
-        <v>0.3546318682881281</v>
+        <v>0.3582238989682636</v>
       </c>
       <c r="D77" t="s">
         <v>7</v>
@@ -5649,10 +5649,10 @@
         <v>163</v>
       </c>
       <c r="B78" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C78">
-        <v>0.4654403920238682</v>
+        <v>0.4705601169301538</v>
       </c>
       <c r="D78" t="s">
         <v>7</v>
@@ -5666,10 +5666,10 @@
         <v>165</v>
       </c>
       <c r="B79" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C79">
-        <v>0.3001009705346404</v>
+        <v>0.301978347784832</v>
       </c>
       <c r="D79" t="s">
         <v>7</v>
@@ -5683,10 +5683,10 @@
         <v>167</v>
       </c>
       <c r="B80" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C80">
-        <v>0.3975238246630193</v>
+        <v>0.400469586813911</v>
       </c>
       <c r="D80" t="s">
         <v>7</v>
@@ -5700,10 +5700,10 @@
         <v>169</v>
       </c>
       <c r="B81" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C81">
-        <v>0.2953560341197214</v>
+        <v>0.3002484428599494</v>
       </c>
       <c r="D81" t="s">
         <v>7</v>
@@ -5717,10 +5717,10 @@
         <v>171</v>
       </c>
       <c r="B82" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C82">
-        <v>0.4575591628501349</v>
+        <v>0.4620168995588939</v>
       </c>
       <c r="D82" t="s">
         <v>7</v>
@@ -5734,10 +5734,10 @@
         <v>173</v>
       </c>
       <c r="B83" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C83">
-        <v>0.4127952240236872</v>
+        <v>0.4332106198591876</v>
       </c>
       <c r="D83" t="s">
         <v>7</v>
@@ -5751,10 +5751,10 @@
         <v>175</v>
       </c>
       <c r="B84" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C84">
-        <v>0.3241977745892953</v>
+        <v>0.3264640578512697</v>
       </c>
       <c r="D84" t="s">
         <v>7</v>
@@ -5771,7 +5771,7 @@
         <v>15</v>
       </c>
       <c r="C85">
-        <v>0.2954832569492601</v>
+        <v>0.2786103604584534</v>
       </c>
       <c r="D85" t="s">
         <v>7</v>
@@ -5785,10 +5785,10 @@
         <v>179</v>
       </c>
       <c r="B86" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C86">
-        <v>0.3346911119576672</v>
+        <v>0.3547546741739843</v>
       </c>
       <c r="D86" t="s">
         <v>7</v>
@@ -5802,10 +5802,10 @@
         <v>181</v>
       </c>
       <c r="B87" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C87">
-        <v>0.3071346216264821</v>
+        <v>0.3253231109460152</v>
       </c>
       <c r="D87" t="s">
         <v>7</v>
@@ -5819,10 +5819,10 @@
         <v>183</v>
       </c>
       <c r="B88" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C88">
-        <v>0.2882946692011581</v>
+        <v>0.3060524953786663</v>
       </c>
       <c r="D88" t="s">
         <v>7</v>
@@ -5836,10 +5836,10 @@
         <v>185</v>
       </c>
       <c r="B89" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C89">
-        <v>0.3258071734888688</v>
+        <v>0.3261694608505095</v>
       </c>
       <c r="D89" t="s">
         <v>7</v>
@@ -5853,10 +5853,10 @@
         <v>187</v>
       </c>
       <c r="B90" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C90">
-        <v>0.2870808161900931</v>
+        <v>0.2889142790543868</v>
       </c>
       <c r="D90" t="s">
         <v>7</v>
@@ -5873,7 +5873,7 @@
         <v>6</v>
       </c>
       <c r="C91">
-        <v>0.2929857738989522</v>
+        <v>0.2987984715708097</v>
       </c>
       <c r="D91" t="s">
         <v>7</v>
@@ -5887,10 +5887,10 @@
         <v>191</v>
       </c>
       <c r="B92" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C92">
-        <v>0.2898490290082375</v>
+        <v>0.2955893612618058</v>
       </c>
       <c r="D92" t="s">
         <v>7</v>
@@ -5907,7 +5907,7 @@
         <v>15</v>
       </c>
       <c r="C93">
-        <v>0.3582027052370604</v>
+        <v>0.3391844692093606</v>
       </c>
       <c r="D93" t="s">
         <v>7</v>
@@ -5921,10 +5921,10 @@
         <v>195</v>
       </c>
       <c r="B94" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C94">
-        <v>0.3141971396070826</v>
+        <v>0.3350451502054578</v>
       </c>
       <c r="D94" t="s">
         <v>7</v>
@@ -5938,10 +5938,10 @@
         <v>197</v>
       </c>
       <c r="B95" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C95">
-        <v>0.3319865518250765</v>
+        <v>0.3354734362274315</v>
       </c>
       <c r="D95" t="s">
         <v>7</v>
@@ -5958,7 +5958,7 @@
         <v>15</v>
       </c>
       <c r="C96">
-        <v>0.330468618675236</v>
+        <v>0.3101704480078056</v>
       </c>
       <c r="D96" t="s">
         <v>7</v>
@@ -5975,7 +5975,7 @@
         <v>44</v>
       </c>
       <c r="C97">
-        <v>0.3161172472968449</v>
+        <v>0.3060298534746905</v>
       </c>
       <c r="D97" t="s">
         <v>7</v>
@@ -5989,10 +5989,10 @@
         <v>203</v>
       </c>
       <c r="B98" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="C98">
-        <v>0.3116542110284386</v>
+        <v>0.3070263953398138</v>
       </c>
       <c r="D98" t="s">
         <v>7</v>
@@ -6006,10 +6006,10 @@
         <v>205</v>
       </c>
       <c r="B99" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C99">
-        <v>0.4527336764165985</v>
+        <v>0.4698609246571516</v>
       </c>
       <c r="D99" t="s">
         <v>7</v>
@@ -6026,7 +6026,7 @@
         <v>44</v>
       </c>
       <c r="C100">
-        <v>0.380587737752518</v>
+        <v>0.3728587957328225</v>
       </c>
       <c r="D100" t="s">
         <v>7</v>
@@ -6043,7 +6043,7 @@
         <v>44</v>
       </c>
       <c r="C101">
-        <v>0.3658804856142956</v>
+        <v>0.3605635465166732</v>
       </c>
       <c r="D101" t="s">
         <v>7</v>
@@ -6057,10 +6057,10 @@
         <v>211</v>
       </c>
       <c r="B102" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C102">
-        <v>0.483091520138685</v>
+        <v>0.5019454405679098</v>
       </c>
       <c r="D102" t="s">
         <v>7</v>
@@ -6074,10 +6074,10 @@
         <v>213</v>
       </c>
       <c r="B103" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C103">
-        <v>0.3655350351310906</v>
+        <v>0.3842621069102828</v>
       </c>
       <c r="D103" t="s">
         <v>7</v>
@@ -6094,7 +6094,7 @@
         <v>15</v>
       </c>
       <c r="C104">
-        <v>0.3783275940075863</v>
+        <v>0.3569475086617354</v>
       </c>
       <c r="D104" t="s">
         <v>7</v>
@@ -6111,7 +6111,7 @@
         <v>44</v>
       </c>
       <c r="C105">
-        <v>0.3068977231529376</v>
+        <v>0.2999070733962252</v>
       </c>
       <c r="D105" t="s">
         <v>7</v>
@@ -6125,10 +6125,10 @@
         <v>219</v>
       </c>
       <c r="B106" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C106">
-        <v>0.4133314417842037</v>
+        <v>0.4138561447555889</v>
       </c>
       <c r="D106" t="s">
         <v>7</v>
@@ -6142,10 +6142,10 @@
         <v>221</v>
       </c>
       <c r="B107" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C107">
-        <v>0.3395682913411763</v>
+        <v>0.3475512372579904</v>
       </c>
       <c r="D107" t="s">
         <v>7</v>
@@ -6159,10 +6159,10 @@
         <v>223</v>
       </c>
       <c r="B108" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C108">
-        <v>0.4031811188174734</v>
+        <v>0.4229213330721038</v>
       </c>
       <c r="D108" t="s">
         <v>7</v>
@@ -6193,10 +6193,10 @@
         <v>228</v>
       </c>
       <c r="B110" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C110">
-        <v>0.3146503559350151</v>
+        <v>0.3181160901395911</v>
       </c>
       <c r="D110" t="s">
         <v>7</v>
@@ -6210,10 +6210,10 @@
         <v>230</v>
       </c>
       <c r="B111" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C111">
-        <v>0.4925985454099738</v>
+        <v>0.5090225160682184</v>
       </c>
       <c r="D111" t="s">
         <v>7</v>
@@ -6227,10 +6227,10 @@
         <v>232</v>
       </c>
       <c r="B112" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C112">
-        <v>0.4110824903994398</v>
+        <v>0.4314096618133605</v>
       </c>
       <c r="D112" t="s">
         <v>7</v>
@@ -6247,7 +6247,7 @@
         <v>15</v>
       </c>
       <c r="C113">
-        <v>0.4905862451934004</v>
+        <v>0.473639313147446</v>
       </c>
       <c r="D113" t="s">
         <v>7</v>
@@ -6261,10 +6261,10 @@
         <v>236</v>
       </c>
       <c r="B114" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C114">
-        <v>0.6357992518414292</v>
+        <v>0.6466043203737389</v>
       </c>
       <c r="D114" t="s">
         <v>7</v>
@@ -6278,10 +6278,10 @@
         <v>238</v>
       </c>
       <c r="B115" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C115">
-        <v>0.3023651038277281</v>
+        <v>0.3232923263606644</v>
       </c>
       <c r="D115" t="s">
         <v>7</v>
@@ -6295,10 +6295,10 @@
         <v>240</v>
       </c>
       <c r="B116" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C116">
-        <v>0.4219262202546338</v>
+        <v>0.4406464666364502</v>
       </c>
       <c r="D116" t="s">
         <v>7</v>
@@ -6312,10 +6312,10 @@
         <v>242</v>
       </c>
       <c r="B117" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C117">
-        <v>0.3289014561802077</v>
+        <v>0.3321244179281112</v>
       </c>
       <c r="D117" t="s">
         <v>7</v>
@@ -6329,10 +6329,10 @@
         <v>244</v>
       </c>
       <c r="B118" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C118">
-        <v>0.3841110196040773</v>
+        <v>0.3843352721152164</v>
       </c>
       <c r="D118" t="s">
         <v>7</v>
@@ -6346,10 +6346,10 @@
         <v>246</v>
       </c>
       <c r="B119" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C119">
-        <v>0.3056840953028916</v>
+        <v>0.3218905598097479</v>
       </c>
       <c r="D119" t="s">
         <v>7</v>
@@ -6363,10 +6363,10 @@
         <v>248</v>
       </c>
       <c r="B120" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C120">
-        <v>0.4038345450098044</v>
+        <v>0.4058079394277698</v>
       </c>
       <c r="D120" t="s">
         <v>7</v>
@@ -6383,7 +6383,7 @@
         <v>226</v>
       </c>
       <c r="C121">
-        <v>0.3919252745247332</v>
+        <v>0.3912411493133269</v>
       </c>
       <c r="D121" t="s">
         <v>7</v>
@@ -6397,10 +6397,10 @@
         <v>252</v>
       </c>
       <c r="B122" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C122">
-        <v>0.297154099181397</v>
+        <v>0.3067568296958493</v>
       </c>
       <c r="D122" t="s">
         <v>7</v>
@@ -6414,10 +6414,10 @@
         <v>254</v>
       </c>
       <c r="B123" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C123">
-        <v>0.288969586567</v>
+        <v>0.2908652168189803</v>
       </c>
       <c r="D123" t="s">
         <v>7</v>
@@ -6434,7 +6434,7 @@
         <v>15</v>
       </c>
       <c r="C124">
-        <v>0.3982371077787633</v>
+        <v>0.3768026473755218</v>
       </c>
       <c r="D124" t="s">
         <v>7</v>
@@ -6448,10 +6448,10 @@
         <v>258</v>
       </c>
       <c r="B125" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C125">
-        <v>0.317294049704288</v>
+        <v>0.3190248169732125</v>
       </c>
       <c r="D125" t="s">
         <v>7</v>
@@ -6465,10 +6465,10 @@
         <v>260</v>
       </c>
       <c r="B126" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C126">
-        <v>0.3700894566887373</v>
+        <v>0.3703107726708325</v>
       </c>
       <c r="D126" t="s">
         <v>7</v>
@@ -6482,10 +6482,10 @@
         <v>262</v>
       </c>
       <c r="B127" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C127">
-        <v>0.4930912707997198</v>
+        <v>0.5086117879717563</v>
       </c>
       <c r="D127" t="s">
         <v>7</v>
@@ -6502,7 +6502,7 @@
         <v>15</v>
       </c>
       <c r="C128">
-        <v>0.42393076457509</v>
+        <v>0.4038897505618919</v>
       </c>
       <c r="D128" t="s">
         <v>7</v>
@@ -6516,10 +6516,10 @@
         <v>266</v>
       </c>
       <c r="B129" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C129">
-        <v>0.3065694278588164</v>
+        <v>0.3062255242801446</v>
       </c>
       <c r="D129" t="s">
         <v>7</v>
@@ -6536,7 +6536,7 @@
         <v>15</v>
       </c>
       <c r="C130">
-        <v>0.373537611066851</v>
+        <v>0.3534646188656872</v>
       </c>
       <c r="D130" t="s">
         <v>7</v>
@@ -6550,10 +6550,10 @@
         <v>270</v>
       </c>
       <c r="B131" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C131">
-        <v>0.3248249580656742</v>
+        <v>0.3269267702015947</v>
       </c>
       <c r="D131" t="s">
         <v>7</v>
@@ -6567,10 +6567,10 @@
         <v>272</v>
       </c>
       <c r="B132" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C132">
-        <v>0.3854551274377275</v>
+        <v>0.4048614213227024</v>
       </c>
       <c r="D132" t="s">
         <v>7</v>
@@ -6587,7 +6587,7 @@
         <v>15</v>
       </c>
       <c r="C133">
-        <v>0.3293111251325738</v>
+        <v>0.3111467895549171</v>
       </c>
       <c r="D133" t="s">
         <v>7</v>
@@ -6601,10 +6601,10 @@
         <v>276</v>
       </c>
       <c r="B134" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C134">
-        <v>0.3741459464469846</v>
+        <v>0.3962152433078411</v>
       </c>
       <c r="D134" t="s">
         <v>7</v>
@@ -6618,10 +6618,10 @@
         <v>278</v>
       </c>
       <c r="B135" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C135">
-        <v>0.4058459461332418</v>
+        <v>0.4247593337130838</v>
       </c>
       <c r="D135" t="s">
         <v>7</v>
@@ -6638,7 +6638,7 @@
         <v>44</v>
       </c>
       <c r="C136">
-        <v>0.318438263932938</v>
+        <v>0.3074596167191818</v>
       </c>
       <c r="D136" t="s">
         <v>7</v>
@@ -6652,10 +6652,10 @@
         <v>282</v>
       </c>
       <c r="B137" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C137">
-        <v>0.395076628076451</v>
+        <v>0.41475699110013</v>
       </c>
       <c r="D137" t="s">
         <v>7</v>
@@ -6669,10 +6669,10 @@
         <v>284</v>
       </c>
       <c r="B138" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C138">
-        <v>0.322777715353354</v>
+        <v>0.3432286228847704</v>
       </c>
       <c r="D138" t="s">
         <v>7</v>
@@ -6686,10 +6686,10 @@
         <v>286</v>
       </c>
       <c r="B139" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C139">
-        <v>0.4112141671000881</v>
+        <v>0.430946398014495</v>
       </c>
       <c r="D139" t="s">
         <v>7</v>
@@ -6706,7 +6706,7 @@
         <v>44</v>
       </c>
       <c r="C140">
-        <v>0.3789730015184242</v>
+        <v>0.3748651183300223</v>
       </c>
       <c r="D140" t="s">
         <v>7</v>
@@ -6720,10 +6720,10 @@
         <v>290</v>
       </c>
       <c r="B141" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C141">
-        <v>0.3303814238611743</v>
+        <v>0.3511509590037827</v>
       </c>
       <c r="D141" t="s">
         <v>7</v>
@@ -6737,10 +6737,10 @@
         <v>292</v>
       </c>
       <c r="B142" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C142">
-        <v>0.4170088771159847</v>
+        <v>0.4217512545072261</v>
       </c>
       <c r="D142" t="s">
         <v>7</v>
@@ -6754,10 +6754,10 @@
         <v>294</v>
       </c>
       <c r="B143" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C143">
-        <v>0.3700113834773755</v>
+        <v>0.3893688272772886</v>
       </c>
       <c r="D143" t="s">
         <v>7</v>
@@ -6771,10 +6771,10 @@
         <v>296</v>
       </c>
       <c r="B144" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C144">
-        <v>0.6139111706767413</v>
+        <v>0.6247838976070993</v>
       </c>
       <c r="D144" t="s">
         <v>7</v>
@@ -6791,7 +6791,7 @@
         <v>6</v>
       </c>
       <c r="C145">
-        <v>0.3096824277482824</v>
+        <v>0.3205951989670599</v>
       </c>
       <c r="D145" t="s">
         <v>7</v>
@@ -6805,10 +6805,10 @@
         <v>300</v>
       </c>
       <c r="B146" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C146">
-        <v>0.4165280354759018</v>
+        <v>0.4351361035190289</v>
       </c>
       <c r="D146" t="s">
         <v>7</v>
@@ -6822,10 +6822,10 @@
         <v>302</v>
       </c>
       <c r="B147" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C147">
-        <v>0.4634111937585345</v>
+        <v>0.4826534147936326</v>
       </c>
       <c r="D147" t="s">
         <v>7</v>
@@ -6842,7 +6842,7 @@
         <v>6</v>
       </c>
       <c r="C148">
-        <v>0.3123050992762109</v>
+        <v>0.3281353343915556</v>
       </c>
       <c r="D148" t="s">
         <v>7</v>
@@ -6856,10 +6856,10 @@
         <v>306</v>
       </c>
       <c r="B149" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C149">
-        <v>0.4164312930699521</v>
+        <v>0.4166954612798233</v>
       </c>
       <c r="D149" t="s">
         <v>7</v>
@@ -6873,10 +6873,10 @@
         <v>308</v>
       </c>
       <c r="B150" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C150">
-        <v>0.3703531189368181</v>
+        <v>0.38910228598503</v>
       </c>
       <c r="D150" t="s">
         <v>7</v>
@@ -6890,10 +6890,10 @@
         <v>310</v>
       </c>
       <c r="B151" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C151">
-        <v>0.2982647963566956</v>
+        <v>0.3007797986731844</v>
       </c>
       <c r="D151" t="s">
         <v>7</v>
@@ -6907,10 +6907,10 @@
         <v>312</v>
       </c>
       <c r="B152" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C152">
-        <v>0.6755258994720322</v>
+        <v>0.6842104135934368</v>
       </c>
       <c r="D152" t="s">
         <v>7</v>
@@ -6924,10 +6924,10 @@
         <v>314</v>
       </c>
       <c r="B153" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C153">
-        <v>0.3571509981121045</v>
+        <v>0.3649306306493701</v>
       </c>
       <c r="D153" t="s">
         <v>7</v>
@@ -6944,7 +6944,7 @@
         <v>44</v>
       </c>
       <c r="C154">
-        <v>0.310209728695125</v>
+        <v>0.3006572274196644</v>
       </c>
       <c r="D154" t="s">
         <v>7</v>
@@ -6958,10 +6958,10 @@
         <v>318</v>
       </c>
       <c r="B155" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C155">
-        <v>0.3106131947894918</v>
+        <v>0.3294663603922149</v>
       </c>
       <c r="D155" t="s">
         <v>7</v>
@@ -6975,10 +6975,10 @@
         <v>320</v>
       </c>
       <c r="B156" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C156">
-        <v>0.3661321478512945</v>
+        <v>0.370092389188025</v>
       </c>
       <c r="D156" t="s">
         <v>7</v>
@@ -6992,10 +6992,10 @@
         <v>322</v>
       </c>
       <c r="B157" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C157">
-        <v>0.3985216450901836</v>
+        <v>0.419183584671653</v>
       </c>
       <c r="D157" t="s">
         <v>7</v>
@@ -7012,7 +7012,7 @@
         <v>44</v>
       </c>
       <c r="C158">
-        <v>0.3562145985905591</v>
+        <v>0.3490976143621561</v>
       </c>
       <c r="D158" t="s">
         <v>7</v>
@@ -7029,7 +7029,7 @@
         <v>44</v>
       </c>
       <c r="C159">
-        <v>0.3668403050418066</v>
+        <v>0.3583246366318928</v>
       </c>
       <c r="D159" t="s">
         <v>7</v>
@@ -7043,10 +7043,10 @@
         <v>328</v>
       </c>
       <c r="B160" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C160">
-        <v>0.3867282818303553</v>
+        <v>0.4055001839859372</v>
       </c>
       <c r="D160" t="s">
         <v>7</v>
@@ -7060,10 +7060,10 @@
         <v>330</v>
       </c>
       <c r="B161" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C161">
-        <v>0.4235124378836009</v>
+        <v>0.4440576132162777</v>
       </c>
       <c r="D161" t="s">
         <v>7</v>
@@ -7077,10 +7077,10 @@
         <v>332</v>
       </c>
       <c r="B162" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C162">
-        <v>0.4789207006287615</v>
+        <v>0.4974120547478548</v>
       </c>
       <c r="D162" t="s">
         <v>7</v>
@@ -7097,7 +7097,7 @@
         <v>44</v>
       </c>
       <c r="C163">
-        <v>0.4238647745165507</v>
+        <v>0.4161268014486749</v>
       </c>
       <c r="D163" t="s">
         <v>7</v>
@@ -7111,10 +7111,10 @@
         <v>336</v>
       </c>
       <c r="B164" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C164">
-        <v>0.3805253370642712</v>
+        <v>0.3784611490704823</v>
       </c>
       <c r="D164" t="s">
         <v>7</v>
@@ -7128,10 +7128,10 @@
         <v>338</v>
       </c>
       <c r="B165" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C165">
-        <v>0.4304144426322573</v>
+        <v>0.4321350297241994</v>
       </c>
       <c r="D165" t="s">
         <v>7</v>
@@ -7145,10 +7145,10 @@
         <v>340</v>
       </c>
       <c r="B166" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C166">
-        <v>0.324406743724562</v>
+        <v>0.3285275400866587</v>
       </c>
       <c r="D166" t="s">
         <v>7</v>
@@ -7162,10 +7162,10 @@
         <v>342</v>
       </c>
       <c r="B167" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C167">
-        <v>0.3679957202474127</v>
+        <v>0.388339973785072</v>
       </c>
       <c r="D167" t="s">
         <v>7</v>
@@ -7179,10 +7179,10 @@
         <v>344</v>
       </c>
       <c r="B168" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C168">
-        <v>0.6029641600788604</v>
+        <v>0.6179527611850931</v>
       </c>
       <c r="D168" t="s">
         <v>7</v>
@@ -7196,10 +7196,10 @@
         <v>346</v>
       </c>
       <c r="B169" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C169">
-        <v>0.3319421001088503</v>
+        <v>0.3357087035627654</v>
       </c>
       <c r="D169" t="s">
         <v>7</v>
@@ -7213,10 +7213,10 @@
         <v>348</v>
       </c>
       <c r="B170" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C170">
-        <v>0.3882854580707736</v>
+        <v>0.4092941889225901</v>
       </c>
       <c r="D170" t="s">
         <v>7</v>
@@ -7230,10 +7230,10 @@
         <v>350</v>
       </c>
       <c r="B171" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C171">
-        <v>0.2649887088475221</v>
+        <v>0.2847466045575704</v>
       </c>
       <c r="D171" t="s">
         <v>7</v>
@@ -7247,10 +7247,10 @@
         <v>352</v>
       </c>
       <c r="B172" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C172">
-        <v>0.4324987684988992</v>
+        <v>0.439461211162863</v>
       </c>
       <c r="D172" t="s">
         <v>7</v>
@@ -7264,10 +7264,10 @@
         <v>354</v>
       </c>
       <c r="B173" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C173">
-        <v>0.3118539929789926</v>
+        <v>0.3156394978394135</v>
       </c>
       <c r="D173" t="s">
         <v>7</v>
@@ -7284,7 +7284,7 @@
         <v>6</v>
       </c>
       <c r="C174">
-        <v>0.3156690523752907</v>
+        <v>0.3351786435473981</v>
       </c>
       <c r="D174" t="s">
         <v>7</v>
@@ -7301,7 +7301,7 @@
         <v>15</v>
       </c>
       <c r="C175">
-        <v>0.2969311791829523</v>
+        <v>0.2795298143947709</v>
       </c>
       <c r="D175" t="s">
         <v>7</v>
@@ -7315,10 +7315,10 @@
         <v>360</v>
       </c>
       <c r="B176" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C176">
-        <v>0.4140382510536716</v>
+        <v>0.434175156762933</v>
       </c>
       <c r="D176" t="s">
         <v>7</v>
@@ -7332,10 +7332,10 @@
         <v>362</v>
       </c>
       <c r="B177" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C177">
-        <v>0.5076271383222238</v>
+        <v>0.5240989602416791</v>
       </c>
       <c r="D177" t="s">
         <v>7</v>
@@ -7352,7 +7352,7 @@
         <v>15</v>
       </c>
       <c r="C178">
-        <v>0.3917641570466525</v>
+        <v>0.3719230125424597</v>
       </c>
       <c r="D178" t="s">
         <v>7</v>
@@ -7366,10 +7366,10 @@
         <v>366</v>
       </c>
       <c r="B179" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C179">
-        <v>0.3023685317276503</v>
+        <v>0.2875695018213156</v>
       </c>
       <c r="D179" t="s">
         <v>7</v>
@@ -7386,7 +7386,7 @@
         <v>44</v>
       </c>
       <c r="C180">
-        <v>0.3228136922406105</v>
+        <v>0.313321839181619</v>
       </c>
       <c r="D180" t="s">
         <v>7</v>
@@ -7403,7 +7403,7 @@
         <v>6</v>
       </c>
       <c r="C181">
-        <v>0.3420660582925992</v>
+        <v>0.3508454813422085</v>
       </c>
       <c r="D181" t="s">
         <v>7</v>
@@ -7417,10 +7417,10 @@
         <v>372</v>
       </c>
       <c r="B182" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C182">
-        <v>0.3231323396080082</v>
+        <v>0.3261355665076192</v>
       </c>
       <c r="D182" t="s">
         <v>7</v>
@@ -7434,10 +7434,10 @@
         <v>374</v>
       </c>
       <c r="B183" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C183">
-        <v>0.3221780888269346</v>
+        <v>0.3421427242105084</v>
       </c>
       <c r="D183" t="s">
         <v>7</v>
@@ -7451,10 +7451,10 @@
         <v>376</v>
       </c>
       <c r="B184" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C184">
-        <v>0.3606439941129837</v>
+        <v>0.3814421545929628</v>
       </c>
       <c r="D184" t="s">
         <v>7</v>
@@ -7468,10 +7468,10 @@
         <v>378</v>
       </c>
       <c r="B185" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C185">
-        <v>0.383266512840537</v>
+        <v>0.3832239167464059</v>
       </c>
       <c r="D185" t="s">
         <v>7</v>
@@ -7488,7 +7488,7 @@
         <v>44</v>
       </c>
       <c r="C186">
-        <v>0.3758399667683893</v>
+        <v>0.3695059330192038</v>
       </c>
       <c r="D186" t="s">
         <v>7</v>
@@ -7502,10 +7502,10 @@
         <v>382</v>
       </c>
       <c r="B187" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C187">
-        <v>0.2740835232358662</v>
+        <v>0.2765957014387327</v>
       </c>
       <c r="D187" t="s">
         <v>7</v>
@@ -7519,10 +7519,10 @@
         <v>384</v>
       </c>
       <c r="B188" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C188">
-        <v>0.4020488380636786</v>
+        <v>0.4100765076072995</v>
       </c>
       <c r="D188" t="s">
         <v>7</v>
@@ -7539,7 +7539,7 @@
         <v>6</v>
       </c>
       <c r="C189">
-        <v>0.351108972399523</v>
+        <v>0.3536640563296798</v>
       </c>
       <c r="D189" t="s">
         <v>7</v>
@@ -7553,10 +7553,10 @@
         <v>388</v>
       </c>
       <c r="B190" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C190">
-        <v>0.3189423429184208</v>
+        <v>0.3350125911115217</v>
       </c>
       <c r="D190" t="s">
         <v>7</v>
@@ -7570,10 +7570,10 @@
         <v>390</v>
       </c>
       <c r="B191" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C191">
-        <v>0.3572512354173196</v>
+        <v>0.3608851274397162</v>
       </c>
       <c r="D191" t="s">
         <v>7</v>
@@ -7590,7 +7590,7 @@
         <v>15</v>
       </c>
       <c r="C192">
-        <v>0.3952942128039468</v>
+        <v>0.3772205994110407</v>
       </c>
       <c r="D192" t="s">
         <v>7</v>
@@ -7607,7 +7607,7 @@
         <v>15</v>
       </c>
       <c r="C193">
-        <v>0.4207534592886891</v>
+        <v>0.4031094425831283</v>
       </c>
       <c r="D193" t="s">
         <v>7</v>
@@ -7621,10 +7621,10 @@
         <v>396</v>
       </c>
       <c r="B194" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C194">
-        <v>0.3611133707764278</v>
+        <v>0.362211884022788</v>
       </c>
       <c r="D194" t="s">
         <v>7</v>
@@ -7641,7 +7641,7 @@
         <v>226</v>
       </c>
       <c r="C195">
-        <v>0.4805555899282046</v>
+        <v>0.4831853068180252</v>
       </c>
       <c r="D195" t="s">
         <v>7</v>
@@ -7655,10 +7655,10 @@
         <v>400</v>
       </c>
       <c r="B196" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C196">
-        <v>0.3893448544353938</v>
+        <v>0.4087741212249478</v>
       </c>
       <c r="D196" t="s">
         <v>7</v>
@@ -7672,10 +7672,10 @@
         <v>402</v>
       </c>
       <c r="B197" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C197">
-        <v>0.3363439892618814</v>
+        <v>0.3415855573289717</v>
       </c>
       <c r="D197" t="s">
         <v>7</v>
@@ -7689,10 +7689,10 @@
         <v>404</v>
       </c>
       <c r="B198" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C198">
-        <v>0.5250913022696641</v>
+        <v>0.53646444020937</v>
       </c>
       <c r="D198" t="s">
         <v>7</v>
@@ -7706,10 +7706,10 @@
         <v>406</v>
       </c>
       <c r="B199" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C199">
-        <v>0.6090576680160146</v>
+        <v>0.6191580508885444</v>
       </c>
       <c r="D199" t="s">
         <v>7</v>
@@ -7723,10 +7723,10 @@
         <v>408</v>
       </c>
       <c r="B200" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C200">
-        <v>0.3238718047220134</v>
+        <v>0.3257933343291731</v>
       </c>
       <c r="D200" t="s">
         <v>7</v>
@@ -7743,7 +7743,7 @@
         <v>15</v>
       </c>
       <c r="C201">
-        <v>0.3110074423081757</v>
+        <v>0.2933250245177096</v>
       </c>
       <c r="D201" t="s">
         <v>7</v>
@@ -7757,10 +7757,10 @@
         <v>412</v>
       </c>
       <c r="B202" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C202">
-        <v>0.3768181205767128</v>
+        <v>0.3817277012969252</v>
       </c>
       <c r="D202" t="s">
         <v>7</v>
@@ -7774,10 +7774,10 @@
         <v>414</v>
       </c>
       <c r="B203" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C203">
-        <v>0.545019131233511</v>
+        <v>0.5609590026594351</v>
       </c>
       <c r="D203" t="s">
         <v>7</v>
@@ -7791,10 +7791,10 @@
         <v>416</v>
       </c>
       <c r="B204" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C204">
-        <v>0.4871472232359261</v>
+        <v>0.5051643468406526</v>
       </c>
       <c r="D204" t="s">
         <v>7</v>
@@ -7808,10 +7808,10 @@
         <v>418</v>
       </c>
       <c r="B205" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C205">
-        <v>0.4529004704231175</v>
+        <v>0.4579855861788087</v>
       </c>
       <c r="D205" t="s">
         <v>7</v>
@@ -7828,7 +7828,7 @@
         <v>15</v>
       </c>
       <c r="C206">
-        <v>0.3459583984910837</v>
+        <v>0.3268949932865443</v>
       </c>
       <c r="D206" t="s">
         <v>7</v>
@@ -7845,7 +7845,7 @@
         <v>44</v>
       </c>
       <c r="C207">
-        <v>0.525014847445017</v>
+        <v>0.5189438079331452</v>
       </c>
       <c r="D207" t="s">
         <v>7</v>
@@ -7859,10 +7859,10 @@
         <v>424</v>
       </c>
       <c r="B208" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C208">
-        <v>0.3491440762669842</v>
+        <v>0.3573812202719416</v>
       </c>
       <c r="D208" t="s">
         <v>7</v>
@@ -7876,10 +7876,10 @@
         <v>426</v>
       </c>
       <c r="B209" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C209">
-        <v>0.5591809022034547</v>
+        <v>0.5606496647820907</v>
       </c>
       <c r="D209" t="s">
         <v>7</v>
@@ -7893,10 +7893,10 @@
         <v>428</v>
       </c>
       <c r="B210" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C210">
-        <v>0.430154122076351</v>
+        <v>0.4485989242400502</v>
       </c>
       <c r="D210" t="s">
         <v>7</v>
@@ -7913,7 +7913,7 @@
         <v>15</v>
       </c>
       <c r="C211">
-        <v>0.4610431633404332</v>
+        <v>0.4417869252203848</v>
       </c>
       <c r="D211" t="s">
         <v>7</v>
@@ -7927,10 +7927,10 @@
         <v>432</v>
       </c>
       <c r="B212" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C212">
-        <v>0.297700045340252</v>
+        <v>0.3006853289284446</v>
       </c>
       <c r="D212" t="s">
         <v>7</v>
@@ -7944,10 +7944,10 @@
         <v>434</v>
       </c>
       <c r="B213" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C213">
-        <v>0.3372333962843071</v>
+        <v>0.3394240325933338</v>
       </c>
       <c r="D213" t="s">
         <v>7</v>
@@ -7961,10 +7961,10 @@
         <v>436</v>
       </c>
       <c r="B214" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C214">
-        <v>0.3686238658534763</v>
+        <v>0.351812588397646</v>
       </c>
       <c r="D214" t="s">
         <v>7</v>
@@ -7978,10 +7978,10 @@
         <v>438</v>
       </c>
       <c r="B215" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C215">
-        <v>0.5293467249721576</v>
+        <v>0.5264630343441175</v>
       </c>
       <c r="D215" t="s">
         <v>7</v>
@@ -7998,7 +7998,7 @@
         <v>15</v>
       </c>
       <c r="C216">
-        <v>0.326166220131468</v>
+        <v>0.3102631614449942</v>
       </c>
       <c r="D216" t="s">
         <v>7</v>
@@ -8012,10 +8012,10 @@
         <v>442</v>
       </c>
       <c r="B217" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C217">
-        <v>0.3356798173357969</v>
+        <v>0.3396653888796702</v>
       </c>
       <c r="D217" t="s">
         <v>7</v>
@@ -8029,10 +8029,10 @@
         <v>444</v>
       </c>
       <c r="B218" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C218">
-        <v>0.3726034258854494</v>
+        <v>0.3722468476918996</v>
       </c>
       <c r="D218" t="s">
         <v>7</v>
@@ -8049,7 +8049,7 @@
         <v>44</v>
       </c>
       <c r="C219">
-        <v>0.4600069042488924</v>
+        <v>0.4574170471202713</v>
       </c>
       <c r="D219" t="s">
         <v>7</v>
@@ -8063,10 +8063,10 @@
         <v>448</v>
       </c>
       <c r="B220" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C220">
-        <v>0.300470037053787</v>
+        <v>0.3042085380514488</v>
       </c>
       <c r="D220" t="s">
         <v>7</v>
@@ -8083,7 +8083,7 @@
         <v>15</v>
       </c>
       <c r="C221">
-        <v>0.3732605312279292</v>
+        <v>0.3554640604922192</v>
       </c>
       <c r="D221" t="s">
         <v>7</v>
@@ -8097,10 +8097,10 @@
         <v>452</v>
       </c>
       <c r="B222" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C222">
-        <v>0.3304458792688951</v>
+        <v>0.3317842240772516</v>
       </c>
       <c r="D222" t="s">
         <v>7</v>
@@ -8114,10 +8114,10 @@
         <v>454</v>
       </c>
       <c r="B223" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C223">
-        <v>0.4955663073052685</v>
+        <v>0.4959446494107327</v>
       </c>
       <c r="D223" t="s">
         <v>7</v>
@@ -8131,10 +8131,10 @@
         <v>456</v>
       </c>
       <c r="B224" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C224">
-        <v>0.3253723015059947</v>
+        <v>0.327080707466623</v>
       </c>
       <c r="D224" t="s">
         <v>7</v>
@@ -8151,7 +8151,7 @@
         <v>15</v>
       </c>
       <c r="C225">
-        <v>0.3547865234927187</v>
+        <v>0.3354962203943647</v>
       </c>
       <c r="D225" t="s">
         <v>7</v>
@@ -8165,10 +8165,10 @@
         <v>460</v>
       </c>
       <c r="B226" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C226">
-        <v>0.4989632808565369</v>
+        <v>0.5171776701807875</v>
       </c>
       <c r="D226" t="s">
         <v>7</v>
@@ -8182,10 +8182,10 @@
         <v>462</v>
       </c>
       <c r="B227" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C227">
-        <v>0.3439745747638348</v>
+        <v>0.3481423650625157</v>
       </c>
       <c r="D227" t="s">
         <v>7</v>
@@ -8199,10 +8199,10 @@
         <v>464</v>
       </c>
       <c r="B228" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C228">
-        <v>0.4960476624231919</v>
+        <v>0.5161079354827416</v>
       </c>
       <c r="D228" t="s">
         <v>7</v>
@@ -8216,10 +8216,10 @@
         <v>466</v>
       </c>
       <c r="B229" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C229">
-        <v>0.5740146128197484</v>
+        <v>0.5874459860693126</v>
       </c>
       <c r="D229" t="s">
         <v>7</v>
@@ -8236,7 +8236,7 @@
         <v>44</v>
       </c>
       <c r="C230">
-        <v>0.3232419777951397</v>
+        <v>0.3171594280760494</v>
       </c>
       <c r="D230" t="s">
         <v>7</v>
@@ -8253,7 +8253,7 @@
         <v>6</v>
       </c>
       <c r="C231">
-        <v>0.3325102397728656</v>
+        <v>0.3410909033707503</v>
       </c>
       <c r="D231" t="s">
         <v>7</v>
@@ -8267,10 +8267,10 @@
         <v>472</v>
       </c>
       <c r="B232" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C232">
-        <v>0.5961901385703038</v>
+        <v>0.609365013524596</v>
       </c>
       <c r="D232" t="s">
         <v>7</v>
@@ -8287,7 +8287,7 @@
         <v>44</v>
       </c>
       <c r="C233">
-        <v>0.3921532301576182</v>
+        <v>0.3860159720731177</v>
       </c>
       <c r="D233" t="s">
         <v>7</v>
@@ -8301,10 +8301,10 @@
         <v>476</v>
       </c>
       <c r="B234" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C234">
-        <v>0.4442591991261273</v>
+        <v>0.4618443155014605</v>
       </c>
       <c r="D234" t="s">
         <v>7</v>
@@ -8318,10 +8318,10 @@
         <v>478</v>
       </c>
       <c r="B235" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C235">
-        <v>0.5141795336025841</v>
+        <v>0.5300367711377891</v>
       </c>
       <c r="D235" t="s">
         <v>7</v>
@@ -8335,10 +8335,10 @@
         <v>480</v>
       </c>
       <c r="B236" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C236">
-        <v>0.3043959123424687</v>
+        <v>0.3242981636722224</v>
       </c>
       <c r="D236" t="s">
         <v>7</v>
@@ -8352,10 +8352,10 @@
         <v>482</v>
       </c>
       <c r="B237" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C237">
-        <v>0.3139800576799208</v>
+        <v>0.3346642094397786</v>
       </c>
       <c r="D237" t="s">
         <v>7</v>
@@ -8369,10 +8369,10 @@
         <v>484</v>
       </c>
       <c r="B238" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C238">
-        <v>0.3725061754414346</v>
+        <v>0.3892350758702786</v>
       </c>
       <c r="D238" t="s">
         <v>7</v>
@@ -8386,10 +8386,10 @@
         <v>486</v>
       </c>
       <c r="B239" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C239">
-        <v>0.4478244417033663</v>
+        <v>0.4669847543540107</v>
       </c>
       <c r="D239" t="s">
         <v>7</v>
@@ -8406,7 +8406,7 @@
         <v>226</v>
       </c>
       <c r="C240">
-        <v>0.3363554272917126</v>
+        <v>0.3353764116884409</v>
       </c>
       <c r="D240" t="s">
         <v>7</v>
@@ -8420,10 +8420,10 @@
         <v>490</v>
       </c>
       <c r="B241" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C241">
-        <v>0.2771312473870947</v>
+        <v>0.2797571757364561</v>
       </c>
       <c r="D241" t="s">
         <v>7</v>
@@ -8437,10 +8437,10 @@
         <v>492</v>
       </c>
       <c r="B242" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C242">
-        <v>0.3344103253860502</v>
+        <v>0.3546344249653504</v>
       </c>
       <c r="D242" t="s">
         <v>7</v>
@@ -8457,7 +8457,7 @@
         <v>15</v>
       </c>
       <c r="C243">
-        <v>0.4894561831172544</v>
+        <v>0.4693799188925705</v>
       </c>
       <c r="D243" t="s">
         <v>7</v>
@@ -8474,7 +8474,7 @@
         <v>226</v>
       </c>
       <c r="C244">
-        <v>0.4690826283287785</v>
+        <v>0.4648085988000742</v>
       </c>
       <c r="D244" t="s">
         <v>7</v>
@@ -8488,10 +8488,10 @@
         <v>498</v>
       </c>
       <c r="B245" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C245">
-        <v>0.6388834121511222</v>
+        <v>0.6511455044507365</v>
       </c>
       <c r="D245" t="s">
         <v>7</v>
@@ -8505,10 +8505,10 @@
         <v>500</v>
       </c>
       <c r="B246" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C246">
-        <v>0.4632827918000617</v>
+        <v>0.4824319779662805</v>
       </c>
       <c r="D246" t="s">
         <v>7</v>
@@ -8522,10 +8522,10 @@
         <v>502</v>
       </c>
       <c r="B247" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C247">
-        <v>0.4086384268150137</v>
+        <v>0.427746539384419</v>
       </c>
       <c r="D247" t="s">
         <v>7</v>
@@ -8539,10 +8539,10 @@
         <v>504</v>
       </c>
       <c r="B248" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C248">
-        <v>0.3347139154425993</v>
+        <v>0.3382408955522707</v>
       </c>
       <c r="D248" t="s">
         <v>7</v>
@@ -8556,10 +8556,10 @@
         <v>506</v>
       </c>
       <c r="B249" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C249">
-        <v>0.4399463396498191</v>
+        <v>0.4593540044113102</v>
       </c>
       <c r="D249" t="s">
         <v>7</v>
@@ -8573,10 +8573,10 @@
         <v>508</v>
       </c>
       <c r="B250" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C250">
-        <v>0.3108943649895647</v>
+        <v>0.2964418015451242</v>
       </c>
       <c r="D250" t="s">
         <v>7</v>
@@ -8593,7 +8593,7 @@
         <v>44</v>
       </c>
       <c r="C251">
-        <v>0.4828932584431646</v>
+        <v>0.477760954499133</v>
       </c>
       <c r="D251" t="s">
         <v>7</v>
@@ -8607,10 +8607,10 @@
         <v>512</v>
       </c>
       <c r="B252" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C252">
-        <v>0.4219148622878776</v>
+        <v>0.4432589558683434</v>
       </c>
       <c r="D252" t="s">
         <v>7</v>
@@ -8624,10 +8624,10 @@
         <v>514</v>
       </c>
       <c r="B253" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C253">
-        <v>0.3745798689777225</v>
+        <v>0.39455671086058</v>
       </c>
       <c r="D253" t="s">
         <v>7</v>
@@ -8641,10 +8641,10 @@
         <v>516</v>
       </c>
       <c r="B254" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C254">
-        <v>0.4956924595813771</v>
+        <v>0.5158104646809606</v>
       </c>
       <c r="D254" t="s">
         <v>7</v>
@@ -8661,7 +8661,7 @@
         <v>15</v>
       </c>
       <c r="C255">
-        <v>0.4438909051870091</v>
+        <v>0.4228135072682143</v>
       </c>
       <c r="D255" t="s">
         <v>7</v>
@@ -8675,10 +8675,10 @@
         <v>520</v>
       </c>
       <c r="B256" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C256">
-        <v>0.6087668283538009</v>
+        <v>0.6203731677394234</v>
       </c>
       <c r="D256" t="s">
         <v>7</v>
@@ -8692,10 +8692,10 @@
         <v>522</v>
       </c>
       <c r="B257" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C257">
-        <v>0.4183369032543381</v>
+        <v>0.437951278681427</v>
       </c>
       <c r="D257" t="s">
         <v>7</v>
@@ -8709,10 +8709,10 @@
         <v>524</v>
       </c>
       <c r="B258" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C258">
-        <v>0.516755238693733</v>
+        <v>0.531812593191024</v>
       </c>
       <c r="D258" t="s">
         <v>7</v>
@@ -8726,10 +8726,10 @@
         <v>526</v>
       </c>
       <c r="B259" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C259">
-        <v>0.2945920911980119</v>
+        <v>0.311116915253339</v>
       </c>
       <c r="D259" t="s">
         <v>7</v>
@@ -8743,10 +8743,10 @@
         <v>528</v>
       </c>
       <c r="B260" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C260">
-        <v>0.4427673260424204</v>
+        <v>0.4624084580267258</v>
       </c>
       <c r="D260" t="s">
         <v>7</v>
@@ -8760,10 +8760,10 @@
         <v>530</v>
       </c>
       <c r="B261" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C261">
-        <v>0.4888573304692178</v>
+        <v>0.5077915478263925</v>
       </c>
       <c r="D261" t="s">
         <v>7</v>
@@ -8777,10 +8777,10 @@
         <v>532</v>
       </c>
       <c r="B262" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C262">
-        <v>0.4431848308489289</v>
+        <v>0.460253688099852</v>
       </c>
       <c r="D262" t="s">
         <v>7</v>
@@ -8794,10 +8794,10 @@
         <v>534</v>
       </c>
       <c r="B263" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C263">
-        <v>0.4727052627242979</v>
+        <v>0.4918043517631351</v>
       </c>
       <c r="D263" t="s">
         <v>7</v>
@@ -8811,10 +8811,10 @@
         <v>536</v>
       </c>
       <c r="B264" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C264">
-        <v>0.4560859743915858</v>
+        <v>0.4736164758561264</v>
       </c>
       <c r="D264" t="s">
         <v>7</v>
@@ -8828,10 +8828,10 @@
         <v>538</v>
       </c>
       <c r="B265" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C265">
-        <v>0.3577478590607062</v>
+        <v>0.375102710035347</v>
       </c>
       <c r="D265" t="s">
         <v>7</v>
@@ -8845,10 +8845,10 @@
         <v>540</v>
       </c>
       <c r="B266" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C266">
-        <v>0.4094555758836149</v>
+        <v>0.4264457347139144</v>
       </c>
       <c r="D266" t="s">
         <v>7</v>
@@ -8862,10 +8862,10 @@
         <v>542</v>
       </c>
       <c r="B267" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C267">
-        <v>0.2854732998867289</v>
+        <v>0.3042461937906263</v>
       </c>
       <c r="D267" t="s">
         <v>7</v>
@@ -8879,10 +8879,10 @@
         <v>544</v>
       </c>
       <c r="B268" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C268">
-        <v>0.4620145993075376</v>
+        <v>0.4825597439060587</v>
       </c>
       <c r="D268" t="s">
         <v>7</v>
@@ -8899,7 +8899,7 @@
         <v>44</v>
       </c>
       <c r="C269">
-        <v>0.3616701276519387</v>
+        <v>0.3518510552084041</v>
       </c>
       <c r="D269" t="s">
         <v>7</v>
@@ -8913,10 +8913,10 @@
         <v>548</v>
       </c>
       <c r="B270" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C270">
-        <v>0.5424573513620763</v>
+        <v>0.55624032776037</v>
       </c>
       <c r="D270" t="s">
         <v>7</v>
@@ -8930,10 +8930,10 @@
         <v>550</v>
       </c>
       <c r="B271" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C271">
-        <v>0.5552207054010903</v>
+        <v>0.5677110229479347</v>
       </c>
       <c r="D271" t="s">
         <v>7</v>
@@ -8947,10 +8947,10 @@
         <v>552</v>
       </c>
       <c r="B272" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C272">
-        <v>0.3949784079602809</v>
+        <v>0.4143518888015238</v>
       </c>
       <c r="D272" t="s">
         <v>7</v>
@@ -8964,10 +8964,10 @@
         <v>554</v>
       </c>
       <c r="B273" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C273">
-        <v>0.5378209354970783</v>
+        <v>0.5556941476773948</v>
       </c>
       <c r="D273" t="s">
         <v>7</v>
@@ -8981,10 +8981,10 @@
         <v>556</v>
       </c>
       <c r="B274" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C274">
-        <v>0.3459801749803365</v>
+        <v>0.3307354419558324</v>
       </c>
       <c r="D274" t="s">
         <v>7</v>
@@ -8998,10 +8998,10 @@
         <v>558</v>
       </c>
       <c r="B275" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C275">
-        <v>0.2799615587568567</v>
+        <v>0.2814313682886532</v>
       </c>
       <c r="D275" t="s">
         <v>7</v>
@@ -9015,10 +9015,10 @@
         <v>560</v>
       </c>
       <c r="B276" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C276">
-        <v>0.3288146300284943</v>
+        <v>0.3461093101905831</v>
       </c>
       <c r="D276" t="s">
         <v>7</v>
@@ -9032,10 +9032,10 @@
         <v>562</v>
       </c>
       <c r="B277" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C277">
-        <v>0.393093540731229</v>
+        <v>0.4094992312803502</v>
       </c>
       <c r="D277" t="s">
         <v>7</v>
@@ -9049,10 +9049,10 @@
         <v>564</v>
       </c>
       <c r="B278" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C278">
-        <v>0.4547408734503038</v>
+        <v>0.4708683656421307</v>
       </c>
       <c r="D278" t="s">
         <v>7</v>
@@ -9066,10 +9066,10 @@
         <v>566</v>
       </c>
       <c r="B279" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C279">
-        <v>0.5594984869500769</v>
+        <v>0.574145002789877</v>
       </c>
       <c r="D279" t="s">
         <v>7</v>
@@ -9083,10 +9083,10 @@
         <v>568</v>
       </c>
       <c r="B280" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C280">
-        <v>0.5075583053011297</v>
+        <v>0.5241912940733453</v>
       </c>
       <c r="D280" t="s">
         <v>7</v>
@@ -9100,10 +9100,10 @@
         <v>570</v>
       </c>
       <c r="B281" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C281">
-        <v>0.4000032660882443</v>
+        <v>0.4195606868626256</v>
       </c>
       <c r="D281" t="s">
         <v>7</v>
@@ -9120,7 +9120,7 @@
         <v>15</v>
       </c>
       <c r="C282">
-        <v>0.3619094526791173</v>
+        <v>0.3434420398784382</v>
       </c>
       <c r="D282" t="s">
         <v>7</v>
@@ -9134,10 +9134,10 @@
         <v>574</v>
       </c>
       <c r="B283" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C283">
-        <v>0.3585060966853886</v>
+        <v>0.37621175696775</v>
       </c>
       <c r="D283" t="s">
         <v>7</v>
@@ -9151,10 +9151,10 @@
         <v>576</v>
       </c>
       <c r="B284" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C284">
-        <v>0.3424898239964088</v>
+        <v>0.3632266211049573</v>
       </c>
       <c r="D284" t="s">
         <v>7</v>
@@ -9168,10 +9168,10 @@
         <v>578</v>
       </c>
       <c r="B285" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C285">
-        <v>0.2758562475742407</v>
+        <v>0.2757513127782407</v>
       </c>
       <c r="D285" t="s">
         <v>7</v>
@@ -9185,10 +9185,10 @@
         <v>580</v>
       </c>
       <c r="B286" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C286">
-        <v>0.3075003878695524</v>
+        <v>0.3270151361818072</v>
       </c>
       <c r="D286" t="s">
         <v>7</v>
@@ -9205,7 +9205,7 @@
         <v>44</v>
       </c>
       <c r="C287">
-        <v>0.4577307774082736</v>
+        <v>0.4513202807134823</v>
       </c>
       <c r="D287" t="s">
         <v>7</v>
@@ -9219,10 +9219,10 @@
         <v>584</v>
       </c>
       <c r="B288" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C288">
-        <v>0.2842558035868035</v>
+        <v>0.3045551463237746</v>
       </c>
       <c r="D288" t="s">
         <v>7</v>
@@ -9236,10 +9236,10 @@
         <v>586</v>
       </c>
       <c r="B289" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C289">
-        <v>0.3805903261546035</v>
+        <v>0.4007222683292734</v>
       </c>
       <c r="D289" t="s">
         <v>7</v>
@@ -9253,10 +9253,10 @@
         <v>588</v>
       </c>
       <c r="B290" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C290">
-        <v>0.3142537434840742</v>
+        <v>0.3179754714216725</v>
       </c>
       <c r="D290" t="s">
         <v>7</v>
@@ -9270,10 +9270,10 @@
         <v>590</v>
       </c>
       <c r="B291" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C291">
-        <v>0.4475573889342771</v>
+        <v>0.4642135168400575</v>
       </c>
       <c r="D291" t="s">
         <v>7</v>
@@ -9290,7 +9290,7 @@
         <v>145</v>
       </c>
       <c r="C292">
-        <v>0.4188178531073534</v>
+        <v>0.4223742718145638</v>
       </c>
       <c r="D292" t="s">
         <v>7</v>
@@ -9304,10 +9304,10 @@
         <v>594</v>
       </c>
       <c r="B293" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C293">
-        <v>0.6199535925483386</v>
+        <v>0.6313562498790707</v>
       </c>
       <c r="D293" t="s">
         <v>7</v>
@@ -9324,7 +9324,7 @@
         <v>15</v>
       </c>
       <c r="C294">
-        <v>0.4006998119628482</v>
+        <v>0.3797989632767214</v>
       </c>
       <c r="D294" t="s">
         <v>7</v>
@@ -9338,10 +9338,10 @@
         <v>598</v>
       </c>
       <c r="B295" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C295">
-        <v>0.357556431388483</v>
+        <v>0.3649637200899256</v>
       </c>
       <c r="D295" t="s">
         <v>7</v>
@@ -9355,10 +9355,10 @@
         <v>600</v>
       </c>
       <c r="B296" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C296">
-        <v>0.3072856354710736</v>
+        <v>0.2939237355783472</v>
       </c>
       <c r="D296" t="s">
         <v>7</v>
@@ -9372,10 +9372,10 @@
         <v>602</v>
       </c>
       <c r="B297" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C297">
-        <v>0.4834244125491446</v>
+        <v>0.4903581788114826</v>
       </c>
       <c r="D297" t="s">
         <v>7</v>
@@ -9389,10 +9389,10 @@
         <v>604</v>
       </c>
       <c r="B298" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C298">
-        <v>0.4224353090087663</v>
+        <v>0.4272627097051143</v>
       </c>
       <c r="D298" t="s">
         <v>7</v>
@@ -9406,10 +9406,10 @@
         <v>606</v>
       </c>
       <c r="B299" t="s">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="C299">
-        <v>0.2596400393061148</v>
+        <v>0.2593123927049661</v>
       </c>
       <c r="D299" t="s">
         <v>7</v>
@@ -9423,10 +9423,10 @@
         <v>608</v>
       </c>
       <c r="B300" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C300">
-        <v>0.3549201831746485</v>
+        <v>0.355457925678787</v>
       </c>
       <c r="D300" t="s">
         <v>7</v>
@@ -9440,10 +9440,10 @@
         <v>610</v>
       </c>
       <c r="B301" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C301">
-        <v>0.3676509654455384</v>
+        <v>0.3884141719133472</v>
       </c>
       <c r="D301" t="s">
         <v>7</v>
@@ -9460,7 +9460,7 @@
         <v>44</v>
       </c>
       <c r="C302">
-        <v>0.4539550398077981</v>
+        <v>0.4496518115934375</v>
       </c>
       <c r="D302" t="s">
         <v>7</v>
@@ -9474,10 +9474,10 @@
         <v>614</v>
       </c>
       <c r="B303" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C303">
-        <v>0.3395507508774431</v>
+        <v>0.3421450741318135</v>
       </c>
       <c r="D303" t="s">
         <v>7</v>
@@ -9491,10 +9491,10 @@
         <v>616</v>
       </c>
       <c r="B304" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C304">
-        <v>0.3302793622772512</v>
+        <v>0.3319468028171157</v>
       </c>
       <c r="D304" t="s">
         <v>7</v>
@@ -9511,7 +9511,7 @@
         <v>44</v>
       </c>
       <c r="C305">
-        <v>0.3899101467867369</v>
+        <v>0.3831170633426291</v>
       </c>
       <c r="D305" t="s">
         <v>7</v>
@@ -9528,7 +9528,7 @@
         <v>15</v>
       </c>
       <c r="C306">
-        <v>0.4260592303994008</v>
+        <v>0.4074496138411706</v>
       </c>
       <c r="D306" t="s">
         <v>7</v>
@@ -9542,10 +9542,10 @@
         <v>622</v>
       </c>
       <c r="B307" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C307">
-        <v>0.4256617247791599</v>
+        <v>0.4455674266997934</v>
       </c>
       <c r="D307" t="s">
         <v>7</v>
@@ -9559,10 +9559,10 @@
         <v>624</v>
       </c>
       <c r="B308" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C308">
-        <v>0.4026787325556452</v>
+        <v>0.4213911785485803</v>
       </c>
       <c r="D308" t="s">
         <v>7</v>
@@ -9576,10 +9576,10 @@
         <v>626</v>
       </c>
       <c r="B309" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C309">
-        <v>0.2850741120128562</v>
+        <v>0.3050131718500049</v>
       </c>
       <c r="D309" t="s">
         <v>7</v>
@@ -9593,10 +9593,10 @@
         <v>628</v>
       </c>
       <c r="B310" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C310">
-        <v>0.4195818717609271</v>
+        <v>0.4389372548880359</v>
       </c>
       <c r="D310" t="s">
         <v>7</v>
@@ -9613,7 +9613,7 @@
         <v>15</v>
       </c>
       <c r="C311">
-        <v>0.3471516841970048</v>
+        <v>0.3285281188247275</v>
       </c>
       <c r="D311" t="s">
         <v>7</v>
@@ -9630,7 +9630,7 @@
         <v>15</v>
       </c>
       <c r="C312">
-        <v>0.2684067613133689</v>
+        <v>0.2516064514552738</v>
       </c>
       <c r="D312" t="s">
         <v>7</v>
@@ -9647,7 +9647,7 @@
         <v>44</v>
       </c>
       <c r="C313">
-        <v>0.3013203362121963</v>
+        <v>0.2913256162707525</v>
       </c>
       <c r="D313" t="s">
         <v>7</v>
@@ -9661,10 +9661,10 @@
         <v>636</v>
       </c>
       <c r="B314" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C314">
-        <v>0.3325296493460294</v>
+        <v>0.3341118900629933</v>
       </c>
       <c r="D314" t="s">
         <v>7</v>
@@ -9681,7 +9681,7 @@
         <v>44</v>
       </c>
       <c r="C315">
-        <v>0.4925793111776408</v>
+        <v>0.4860038797996393</v>
       </c>
       <c r="D315" t="s">
         <v>7</v>
@@ -9695,10 +9695,10 @@
         <v>640</v>
       </c>
       <c r="B316" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C316">
-        <v>0.4006215411480921</v>
+        <v>0.4207261620930255</v>
       </c>
       <c r="D316" t="s">
         <v>7</v>
@@ -9712,10 +9712,10 @@
         <v>642</v>
       </c>
       <c r="B317" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C317">
-        <v>0.5429454594963393</v>
+        <v>0.5616600622029742</v>
       </c>
       <c r="D317" t="s">
         <v>7</v>
@@ -9729,10 +9729,10 @@
         <v>644</v>
       </c>
       <c r="B318" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C318">
-        <v>0.565797919966618</v>
+        <v>0.5829244381933757</v>
       </c>
       <c r="D318" t="s">
         <v>7</v>
@@ -9746,10 +9746,10 @@
         <v>646</v>
       </c>
       <c r="B319" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C319">
-        <v>0.3551841405255953</v>
+        <v>0.375896330497547</v>
       </c>
       <c r="D319" t="s">
         <v>7</v>
@@ -9763,10 +9763,10 @@
         <v>648</v>
       </c>
       <c r="B320" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C320">
-        <v>0.3023756815398353</v>
+        <v>0.3068238821089315</v>
       </c>
       <c r="D320" t="s">
         <v>7</v>
@@ -9780,10 +9780,10 @@
         <v>650</v>
       </c>
       <c r="B321" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C321">
-        <v>0.3599395599942822</v>
+        <v>0.3797330614233719</v>
       </c>
       <c r="D321" t="s">
         <v>7</v>
@@ -9797,10 +9797,10 @@
         <v>652</v>
       </c>
       <c r="B322" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C322">
-        <v>0.3882002755807427</v>
+        <v>0.4084007005751528</v>
       </c>
       <c r="D322" t="s">
         <v>7</v>
@@ -9814,10 +9814,10 @@
         <v>654</v>
       </c>
       <c r="B323" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C323">
-        <v>0.3485196695504432</v>
+        <v>0.3524212944026122</v>
       </c>
       <c r="D323" t="s">
         <v>7</v>
@@ -9834,7 +9834,7 @@
         <v>44</v>
       </c>
       <c r="C324">
-        <v>0.3936611525956747</v>
+        <v>0.3859997785064447</v>
       </c>
       <c r="D324" t="s">
         <v>7</v>
@@ -9851,7 +9851,7 @@
         <v>6</v>
       </c>
       <c r="C325">
-        <v>0.2336239379331035</v>
+        <v>0.2476521724699391</v>
       </c>
       <c r="D325" t="s">
         <v>7</v>
@@ -9868,7 +9868,7 @@
         <v>44</v>
       </c>
       <c r="C326">
-        <v>0.3533378653295376</v>
+        <v>0.3464660771427366</v>
       </c>
       <c r="D326" t="s">
         <v>7</v>
@@ -9882,10 +9882,10 @@
         <v>662</v>
       </c>
       <c r="B327" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="C327">
-        <v>0.3077809733377868</v>
+        <v>0.3008723891414887</v>
       </c>
       <c r="D327" t="s">
         <v>7</v>
@@ -9899,10 +9899,10 @@
         <v>664</v>
       </c>
       <c r="B328" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C328">
-        <v>0.2848862094758736</v>
+        <v>0.3046175705044445</v>
       </c>
       <c r="D328" t="s">
         <v>7</v>
@@ -9916,10 +9916,10 @@
         <v>666</v>
       </c>
       <c r="B329" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C329">
-        <v>0.3212302222272556</v>
+        <v>0.3245007004223342</v>
       </c>
       <c r="D329" t="s">
         <v>7</v>
@@ -9933,10 +9933,10 @@
         <v>668</v>
       </c>
       <c r="B330" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C330">
-        <v>0.3130824383530552</v>
+        <v>0.3105972038029944</v>
       </c>
       <c r="D330" t="s">
         <v>7</v>
@@ -9950,10 +9950,10 @@
         <v>670</v>
       </c>
       <c r="B331" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C331">
-        <v>0.3910052068664205</v>
+        <v>0.398913490774229</v>
       </c>
       <c r="D331" t="s">
         <v>7</v>
@@ -9967,10 +9967,10 @@
         <v>672</v>
       </c>
       <c r="B332" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C332">
-        <v>0.3762960749987268</v>
+        <v>0.3799230204419501</v>
       </c>
       <c r="D332" t="s">
         <v>7</v>
@@ -9984,10 +9984,10 @@
         <v>674</v>
       </c>
       <c r="B333" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C333">
-        <v>0.484750216697777</v>
+        <v>0.5035488270907091</v>
       </c>
       <c r="D333" t="s">
         <v>7</v>
@@ -10001,10 +10001,10 @@
         <v>676</v>
       </c>
       <c r="B334" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C334">
-        <v>0.2991063036072676</v>
+        <v>0.291295869120158</v>
       </c>
       <c r="D334" t="s">
         <v>7</v>
@@ -10021,7 +10021,7 @@
         <v>15</v>
       </c>
       <c r="C335">
-        <v>0.347300905356385</v>
+        <v>0.3321349120548036</v>
       </c>
       <c r="D335" t="s">
         <v>7</v>
@@ -10035,10 +10035,10 @@
         <v>680</v>
       </c>
       <c r="B336" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C336">
-        <v>0.3460645671138828</v>
+        <v>0.3476945402382672</v>
       </c>
       <c r="D336" t="s">
         <v>7</v>
@@ -10055,7 +10055,7 @@
         <v>44</v>
       </c>
       <c r="C337">
-        <v>0.4218911064221688</v>
+        <v>0.4155718561044428</v>
       </c>
       <c r="D337" t="s">
         <v>7</v>
@@ -10069,10 +10069,10 @@
         <v>684</v>
       </c>
       <c r="B338" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C338">
-        <v>0.2909934874983195</v>
+        <v>0.3108727373820458</v>
       </c>
       <c r="D338" t="s">
         <v>7</v>
@@ -10089,7 +10089,7 @@
         <v>15</v>
       </c>
       <c r="C339">
-        <v>0.4370923483794991</v>
+        <v>0.4182575462315499</v>
       </c>
       <c r="D339" t="s">
         <v>7</v>
@@ -10106,7 +10106,7 @@
         <v>15</v>
       </c>
       <c r="C340">
-        <v>0.3008967809590951</v>
+        <v>0.281682295188981</v>
       </c>
       <c r="D340" t="s">
         <v>7</v>
@@ -10120,10 +10120,10 @@
         <v>690</v>
       </c>
       <c r="B341" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C341">
-        <v>0.3051780100951938</v>
+        <v>0.3255034629576644</v>
       </c>
       <c r="D341" t="s">
         <v>7</v>
@@ -10137,10 +10137,10 @@
         <v>692</v>
       </c>
       <c r="B342" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C342">
-        <v>0.3022323148549867</v>
+        <v>0.3055693620627097</v>
       </c>
       <c r="D342" t="s">
         <v>7</v>
@@ -10154,10 +10154,10 @@
         <v>694</v>
       </c>
       <c r="B343" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C343">
-        <v>0.4113955091076755</v>
+        <v>0.4133124295915993</v>
       </c>
       <c r="D343" t="s">
         <v>7</v>
@@ -10171,10 +10171,10 @@
         <v>696</v>
       </c>
       <c r="B344" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C344">
-        <v>0.2732624548485608</v>
+        <v>0.2766386364489009</v>
       </c>
       <c r="D344" t="s">
         <v>7</v>
@@ -10188,10 +10188,10 @@
         <v>698</v>
       </c>
       <c r="B345" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C345">
-        <v>0.3806545877931447</v>
+        <v>0.4005486788087232</v>
       </c>
       <c r="D345" t="s">
         <v>7</v>
@@ -10205,10 +10205,10 @@
         <v>700</v>
       </c>
       <c r="B346" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C346">
-        <v>0.3523514588037165</v>
+        <v>0.353593514915826</v>
       </c>
       <c r="D346" t="s">
         <v>7</v>
@@ -10225,7 +10225,7 @@
         <v>15</v>
       </c>
       <c r="C347">
-        <v>0.3459034512894915</v>
+        <v>0.3268070004859198</v>
       </c>
       <c r="D347" t="s">
         <v>7</v>
@@ -10239,10 +10239,10 @@
         <v>704</v>
       </c>
       <c r="B348" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C348">
-        <v>0.3658817296205562</v>
+        <v>0.385178938137101</v>
       </c>
       <c r="D348" t="s">
         <v>7</v>
@@ -10256,10 +10256,10 @@
         <v>706</v>
       </c>
       <c r="B349" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C349">
-        <v>0.5113369403429094</v>
+        <v>0.5263096150552639</v>
       </c>
       <c r="D349" t="s">
         <v>7</v>
@@ -10276,7 +10276,7 @@
         <v>15</v>
       </c>
       <c r="C350">
-        <v>0.3497997773538578</v>
+        <v>0.3292553585894153</v>
       </c>
       <c r="D350" t="s">
         <v>7</v>
@@ -10290,10 +10290,10 @@
         <v>710</v>
       </c>
       <c r="B351" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C351">
-        <v>0.2168681280929442</v>
+        <v>0.2198971959502281</v>
       </c>
       <c r="D351" t="s">
         <v>7</v>
@@ -10310,7 +10310,7 @@
         <v>15</v>
       </c>
       <c r="C352">
-        <v>0.3942294636502503</v>
+        <v>0.3734590418079319</v>
       </c>
       <c r="D352" t="s">
         <v>7</v>
@@ -10324,10 +10324,10 @@
         <v>714</v>
       </c>
       <c r="B353" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C353">
-        <v>0.3989168737801188</v>
+        <v>0.4020863370578426</v>
       </c>
       <c r="D353" t="s">
         <v>7</v>
@@ -10341,10 +10341,10 @@
         <v>716</v>
       </c>
       <c r="B354" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C354">
-        <v>0.2993481333617596</v>
+        <v>0.3177447867261351</v>
       </c>
       <c r="D354" t="s">
         <v>7</v>
@@ -10358,10 +10358,10 @@
         <v>718</v>
       </c>
       <c r="B355" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C355">
-        <v>0.3944097967724159</v>
+        <v>0.4138311054171007</v>
       </c>
       <c r="D355" t="s">
         <v>7</v>
@@ -10375,10 +10375,10 @@
         <v>720</v>
       </c>
       <c r="B356" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C356">
-        <v>0.3308231228779561</v>
+        <v>0.3516527670174905</v>
       </c>
       <c r="D356" t="s">
         <v>7</v>
@@ -10392,10 +10392,10 @@
         <v>722</v>
       </c>
       <c r="B357" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C357">
-        <v>0.4182045952453424</v>
+        <v>0.43959281515981</v>
       </c>
       <c r="D357" t="s">
         <v>7</v>
@@ -10409,10 +10409,10 @@
         <v>724</v>
       </c>
       <c r="B358" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C358">
-        <v>0.3595376544776399</v>
+        <v>0.3776059532039719</v>
       </c>
       <c r="D358" t="s">
         <v>7</v>
@@ -10429,7 +10429,7 @@
         <v>44</v>
       </c>
       <c r="C359">
-        <v>0.4401090816331542</v>
+        <v>0.432147104108058</v>
       </c>
       <c r="D359" t="s">
         <v>7</v>
@@ -10443,10 +10443,10 @@
         <v>728</v>
       </c>
       <c r="B360" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C360">
-        <v>0.5003279260691016</v>
+        <v>0.5147878481541579</v>
       </c>
       <c r="D360" t="s">
         <v>7</v>
@@ -10460,10 +10460,10 @@
         <v>730</v>
       </c>
       <c r="B361" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C361">
-        <v>0.3032200747112017</v>
+        <v>0.2856865014246219</v>
       </c>
       <c r="D361" t="s">
         <v>7</v>
@@ -10477,10 +10477,10 @@
         <v>732</v>
       </c>
       <c r="B362" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C362">
-        <v>0.3754521946613957</v>
+        <v>0.396004107132908</v>
       </c>
       <c r="D362" t="s">
         <v>7</v>
@@ -10497,7 +10497,7 @@
         <v>6</v>
       </c>
       <c r="C363">
-        <v>0.3071607398924736</v>
+        <v>0.318345576846174</v>
       </c>
       <c r="D363" t="s">
         <v>7</v>
@@ -10511,10 +10511,10 @@
         <v>736</v>
       </c>
       <c r="B364" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C364">
-        <v>0.3385464332722383</v>
+        <v>0.3389494474688206</v>
       </c>
       <c r="D364" t="s">
         <v>7</v>
@@ -10528,10 +10528,10 @@
         <v>738</v>
       </c>
       <c r="B365" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C365">
-        <v>0.3162930342314425</v>
+        <v>0.2995542506028574</v>
       </c>
       <c r="D365" t="s">
         <v>7</v>
@@ -10545,10 +10545,10 @@
         <v>740</v>
       </c>
       <c r="B366" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C366">
-        <v>0.2687311122966826</v>
+        <v>0.272945675102132</v>
       </c>
       <c r="D366" t="s">
         <v>7</v>
@@ -10562,10 +10562,10 @@
         <v>742</v>
       </c>
       <c r="B367" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C367">
-        <v>0.3717428342243341</v>
+        <v>0.3903414842104247</v>
       </c>
       <c r="D367" t="s">
         <v>7</v>
@@ -10582,7 +10582,7 @@
         <v>15</v>
       </c>
       <c r="C368">
-        <v>0.3493174297076012</v>
+        <v>0.3324320596831159</v>
       </c>
       <c r="D368" t="s">
         <v>7</v>
@@ -10596,10 +10596,10 @@
         <v>746</v>
       </c>
       <c r="B369" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C369">
-        <v>0.5458181764633021</v>
+        <v>0.5609243650258485</v>
       </c>
       <c r="D369" t="s">
         <v>7</v>
@@ -10616,7 +10616,7 @@
         <v>15</v>
       </c>
       <c r="C370">
-        <v>0.3383379722867129</v>
+        <v>0.3202304435215778</v>
       </c>
       <c r="D370" t="s">
         <v>7</v>
@@ -10630,10 +10630,10 @@
         <v>750</v>
       </c>
       <c r="B371" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C371">
-        <v>0.4825482647440731</v>
+        <v>0.5011885393846285</v>
       </c>
       <c r="D371" t="s">
         <v>7</v>
@@ -10647,10 +10647,10 @@
         <v>752</v>
       </c>
       <c r="B372" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C372">
-        <v>0.3932615644587441</v>
+        <v>0.4120201150462778</v>
       </c>
       <c r="D372" t="s">
         <v>7</v>
@@ -10664,10 +10664,10 @@
         <v>754</v>
       </c>
       <c r="B373" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C373">
-        <v>0.4483682344733102</v>
+        <v>0.4660941424857311</v>
       </c>
       <c r="D373" t="s">
         <v>7</v>
@@ -10681,10 +10681,10 @@
         <v>756</v>
       </c>
       <c r="B374" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C374">
-        <v>0.513295182725667</v>
+        <v>0.5299178224051443</v>
       </c>
       <c r="D374" t="s">
         <v>7</v>
@@ -10698,10 +10698,10 @@
         <v>758</v>
       </c>
       <c r="B375" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C375">
-        <v>0.4905781773404378</v>
+        <v>0.509826715689798</v>
       </c>
       <c r="D375" t="s">
         <v>7</v>
@@ -10715,10 +10715,10 @@
         <v>760</v>
       </c>
       <c r="B376" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C376">
-        <v>0.3545779070167907</v>
+        <v>0.3592248739509881</v>
       </c>
       <c r="D376" t="s">
         <v>7</v>
@@ -10732,10 +10732,10 @@
         <v>762</v>
       </c>
       <c r="B377" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C377">
-        <v>0.4997925706575624</v>
+        <v>0.5173805544599029</v>
       </c>
       <c r="D377" t="s">
         <v>7</v>
@@ -10749,10 +10749,10 @@
         <v>764</v>
       </c>
       <c r="B378" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C378">
-        <v>0.3269445402126762</v>
+        <v>0.3473180590943401</v>
       </c>
       <c r="D378" t="s">
         <v>7</v>
@@ -10766,10 +10766,10 @@
         <v>766</v>
       </c>
       <c r="B379" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C379">
-        <v>0.3396331969999503</v>
+        <v>0.3596159725410774</v>
       </c>
       <c r="D379" t="s">
         <v>7</v>
@@ -10783,10 +10783,10 @@
         <v>768</v>
       </c>
       <c r="B380" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C380">
-        <v>0.3887400956623545</v>
+        <v>0.4097150494556605</v>
       </c>
       <c r="D380" t="s">
         <v>7</v>
@@ -10800,10 +10800,10 @@
         <v>770</v>
       </c>
       <c r="B381" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C381">
-        <v>0.4935159194345329</v>
+        <v>0.4984080100951949</v>
       </c>
       <c r="D381" t="s">
         <v>7</v>
@@ -10817,10 +10817,10 @@
         <v>772</v>
       </c>
       <c r="B382" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C382">
-        <v>0.3455362254958698</v>
+        <v>0.3647024743172205</v>
       </c>
       <c r="D382" t="s">
         <v>7</v>
@@ -10834,10 +10834,10 @@
         <v>774</v>
       </c>
       <c r="B383" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C383">
-        <v>0.3992409181471723</v>
+        <v>0.401474065281487</v>
       </c>
       <c r="D383" t="s">
         <v>7</v>
@@ -10854,7 +10854,7 @@
         <v>44</v>
       </c>
       <c r="C384">
-        <v>0.4227498718322691</v>
+        <v>0.4145857816141802</v>
       </c>
       <c r="D384" t="s">
         <v>7</v>
@@ -10868,10 +10868,10 @@
         <v>778</v>
       </c>
       <c r="B385" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C385">
-        <v>0.4200713651258565</v>
+        <v>0.4397960532214739</v>
       </c>
       <c r="D385" t="s">
         <v>7</v>
@@ -10885,10 +10885,10 @@
         <v>780</v>
       </c>
       <c r="B386" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C386">
-        <v>0.3145921705773721</v>
+        <v>0.3162831420677857</v>
       </c>
       <c r="D386" t="s">
         <v>7</v>
@@ -10902,10 +10902,10 @@
         <v>782</v>
       </c>
       <c r="B387" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C387">
-        <v>0.4382885054553811</v>
+        <v>0.438847931293578</v>
       </c>
       <c r="D387" t="s">
         <v>7</v>
@@ -10919,10 +10919,10 @@
         <v>784</v>
       </c>
       <c r="B388" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="C388">
-        <v>0.2782036358348184</v>
+        <v>0.2774897855728563</v>
       </c>
       <c r="D388" t="s">
         <v>7</v>
@@ -10936,10 +10936,10 @@
         <v>786</v>
       </c>
       <c r="B389" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C389">
-        <v>0.3760384152508029</v>
+        <v>0.3965839997667663</v>
       </c>
       <c r="D389" t="s">
         <v>7</v>
@@ -10956,7 +10956,7 @@
         <v>15</v>
       </c>
       <c r="C390">
-        <v>0.3313069112834445</v>
+        <v>0.3103284084885004</v>
       </c>
       <c r="D390" t="s">
         <v>7</v>
@@ -10970,10 +10970,10 @@
         <v>790</v>
       </c>
       <c r="B391" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C391">
-        <v>0.345183358938561</v>
+        <v>0.3612525103914231</v>
       </c>
       <c r="D391" t="s">
         <v>7</v>
@@ -10987,10 +10987,10 @@
         <v>792</v>
       </c>
       <c r="B392" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C392">
-        <v>0.3532917582670004</v>
+        <v>0.3557271528328959</v>
       </c>
       <c r="D392" t="s">
         <v>7</v>
@@ -11004,10 +11004,10 @@
         <v>794</v>
       </c>
       <c r="B393" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C393">
-        <v>0.4029283702134476</v>
+        <v>0.4081855794325344</v>
       </c>
       <c r="D393" t="s">
         <v>7</v>
@@ -11024,7 +11024,7 @@
         <v>15</v>
       </c>
       <c r="C394">
-        <v>0.3660020206065805</v>
+        <v>0.3458912237713959</v>
       </c>
       <c r="D394" t="s">
         <v>7</v>
@@ -11038,10 +11038,10 @@
         <v>798</v>
       </c>
       <c r="B395" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C395">
-        <v>0.4390788171634048</v>
+        <v>0.4413653805148</v>
       </c>
       <c r="D395" t="s">
         <v>7</v>
@@ -11055,10 +11055,10 @@
         <v>800</v>
       </c>
       <c r="B396" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C396">
-        <v>0.3964417190211114</v>
+        <v>0.4172689636474265</v>
       </c>
       <c r="D396" t="s">
         <v>7</v>
@@ -11072,10 +11072,10 @@
         <v>802</v>
       </c>
       <c r="B397" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C397">
-        <v>0.3650872277457678</v>
+        <v>0.3681564602714705</v>
       </c>
       <c r="D397" t="s">
         <v>7</v>
@@ -11089,10 +11089,10 @@
         <v>804</v>
       </c>
       <c r="B398" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C398">
-        <v>0.5148057034701986</v>
+        <v>0.5303406165731562</v>
       </c>
       <c r="D398" t="s">
         <v>7</v>
@@ -11109,7 +11109,7 @@
         <v>15</v>
       </c>
       <c r="C399">
-        <v>0.3501960805337617</v>
+        <v>0.3339652929728653</v>
       </c>
       <c r="D399" t="s">
         <v>7</v>
@@ -11123,10 +11123,10 @@
         <v>808</v>
       </c>
       <c r="B400" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C400">
-        <v>0.3467497965359735</v>
+        <v>0.3676980791261886</v>
       </c>
       <c r="D400" t="s">
         <v>7</v>
@@ -11143,7 +11143,7 @@
         <v>15</v>
       </c>
       <c r="C401">
-        <v>0.4402282382292482</v>
+        <v>0.4231735789427519</v>
       </c>
       <c r="D401" t="s">
         <v>7</v>
@@ -11157,10 +11157,10 @@
         <v>812</v>
       </c>
       <c r="B402" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C402">
-        <v>0.4097211630199757</v>
+        <v>0.4298689787592774</v>
       </c>
       <c r="D402" t="s">
         <v>7</v>
@@ -11174,10 +11174,10 @@
         <v>814</v>
       </c>
       <c r="B403" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C403">
-        <v>0.3144254950591202</v>
+        <v>0.3335510938873685</v>
       </c>
       <c r="D403" t="s">
         <v>7</v>
@@ -11191,10 +11191,10 @@
         <v>816</v>
       </c>
       <c r="B404" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C404">
-        <v>0.3490398919563341</v>
+        <v>0.3558305956351188</v>
       </c>
       <c r="D404" t="s">
         <v>7</v>
@@ -11208,10 +11208,10 @@
         <v>818</v>
       </c>
       <c r="B405" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C405">
-        <v>0.4453783393072623</v>
+        <v>0.4616758954172872</v>
       </c>
       <c r="D405" t="s">
         <v>7</v>
@@ -11225,10 +11225,10 @@
         <v>820</v>
       </c>
       <c r="B406" t="s">
-        <v>145</v>
+        <v>6</v>
       </c>
       <c r="C406">
-        <v>0.4268739360398142</v>
+        <v>0.4383890952628081</v>
       </c>
       <c r="D406" t="s">
         <v>7</v>
@@ -11242,10 +11242,10 @@
         <v>822</v>
       </c>
       <c r="B407" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C407">
-        <v>0.4044980000393313</v>
+        <v>0.4237105703202882</v>
       </c>
       <c r="D407" t="s">
         <v>7</v>
@@ -11259,10 +11259,10 @@
         <v>824</v>
       </c>
       <c r="B408" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C408">
-        <v>0.4824627541167594</v>
+        <v>0.5007125384691642</v>
       </c>
       <c r="D408" t="s">
         <v>7</v>
@@ -11276,10 +11276,10 @@
         <v>826</v>
       </c>
       <c r="B409" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C409">
-        <v>0.5011347762132599</v>
+        <v>0.5187414359297987</v>
       </c>
       <c r="D409" t="s">
         <v>7</v>
@@ -11293,10 +11293,10 @@
         <v>828</v>
       </c>
       <c r="B410" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C410">
-        <v>0.2886651867493523</v>
+        <v>0.2793017101308404</v>
       </c>
       <c r="D410" t="s">
         <v>7</v>
@@ -11310,10 +11310,10 @@
         <v>830</v>
       </c>
       <c r="B411" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C411">
-        <v>0.3371149505657562</v>
+        <v>0.3574297683268172</v>
       </c>
       <c r="D411" t="s">
         <v>7</v>
@@ -11327,10 +11327,10 @@
         <v>832</v>
       </c>
       <c r="B412" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C412">
-        <v>0.4401572893666832</v>
+        <v>0.4610453651723681</v>
       </c>
       <c r="D412" t="s">
         <v>7</v>
@@ -11347,7 +11347,7 @@
         <v>6</v>
       </c>
       <c r="C413">
-        <v>0.2811139899718828</v>
+        <v>0.2952135205387721</v>
       </c>
       <c r="D413" t="s">
         <v>7</v>
@@ -11364,7 +11364,7 @@
         <v>15</v>
       </c>
       <c r="C414">
-        <v>0.3098683928718262</v>
+        <v>0.2921585742393087</v>
       </c>
       <c r="D414" t="s">
         <v>7</v>
@@ -11378,10 +11378,10 @@
         <v>838</v>
       </c>
       <c r="B415" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C415">
-        <v>0.3631181204971604</v>
+        <v>0.3672266962512292</v>
       </c>
       <c r="D415" t="s">
         <v>7</v>
@@ -11398,7 +11398,7 @@
         <v>15</v>
       </c>
       <c r="C416">
-        <v>0.4357009267161114</v>
+        <v>0.423223874584187</v>
       </c>
       <c r="D416" t="s">
         <v>7</v>
@@ -11412,10 +11412,10 @@
         <v>842</v>
       </c>
       <c r="B417" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C417">
-        <v>0.2942190953270828</v>
+        <v>0.3130685163953121</v>
       </c>
       <c r="D417" t="s">
         <v>7</v>
@@ -11429,10 +11429,10 @@
         <v>844</v>
       </c>
       <c r="B418" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C418">
-        <v>0.3340377788963301</v>
+        <v>0.3390684567351993</v>
       </c>
       <c r="D418" t="s">
         <v>7</v>
@@ -11449,7 +11449,7 @@
         <v>15</v>
       </c>
       <c r="C419">
-        <v>0.3924944231808148</v>
+        <v>0.371848759776974</v>
       </c>
       <c r="D419" t="s">
         <v>7</v>
@@ -11466,7 +11466,7 @@
         <v>44</v>
       </c>
       <c r="C420">
-        <v>0.4314424703151867</v>
+        <v>0.4285759824704768</v>
       </c>
       <c r="D420" t="s">
         <v>7</v>
@@ -11483,7 +11483,7 @@
         <v>44</v>
       </c>
       <c r="C421">
-        <v>0.4392213991812861</v>
+        <v>0.4352790924440437</v>
       </c>
       <c r="D421" t="s">
         <v>7</v>
@@ -11497,10 +11497,10 @@
         <v>852</v>
       </c>
       <c r="B422" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C422">
-        <v>0.381219750734441</v>
+        <v>0.4025913169062175</v>
       </c>
       <c r="D422" t="s">
         <v>7</v>
@@ -11517,7 +11517,7 @@
         <v>44</v>
       </c>
       <c r="C423">
-        <v>0.4188747143759381</v>
+        <v>0.4121641001691528</v>
       </c>
       <c r="D423" t="s">
         <v>7</v>
@@ -11531,10 +11531,10 @@
         <v>856</v>
       </c>
       <c r="B424" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C424">
-        <v>0.3635013377620491</v>
+        <v>0.3681703140290443</v>
       </c>
       <c r="D424" t="s">
         <v>7</v>
@@ -11548,10 +11548,10 @@
         <v>858</v>
       </c>
       <c r="B425" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C425">
-        <v>0.3824238952397113</v>
+        <v>0.4029588985456579</v>
       </c>
       <c r="D425" t="s">
         <v>7</v>
@@ -11565,10 +11565,10 @@
         <v>860</v>
       </c>
       <c r="B426" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C426">
-        <v>0.3541967379038762</v>
+        <v>0.3371648779973476</v>
       </c>
       <c r="D426" t="s">
         <v>7</v>
@@ -11582,10 +11582,10 @@
         <v>862</v>
       </c>
       <c r="B427" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C427">
-        <v>0.296209926082169</v>
+        <v>0.3174175736732505</v>
       </c>
       <c r="D427" t="s">
         <v>7</v>
@@ -11599,10 +11599,10 @@
         <v>864</v>
       </c>
       <c r="B428" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C428">
-        <v>0.2887054238617824</v>
+        <v>0.3090929453806241</v>
       </c>
       <c r="D428" t="s">
         <v>7</v>
@@ -11616,10 +11616,10 @@
         <v>866</v>
       </c>
       <c r="B429" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C429">
-        <v>0.3797035656886627</v>
+        <v>0.3807431423732258</v>
       </c>
       <c r="D429" t="s">
         <v>7</v>
@@ -11633,10 +11633,10 @@
         <v>868</v>
       </c>
       <c r="B430" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C430">
-        <v>0.3766621547847255</v>
+        <v>0.3985532546955</v>
       </c>
       <c r="D430" t="s">
         <v>7</v>
@@ -11650,10 +11650,10 @@
         <v>870</v>
       </c>
       <c r="B431" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C431">
-        <v>0.3097234988632968</v>
+        <v>0.3256055445958998</v>
       </c>
       <c r="D431" t="s">
         <v>7</v>
@@ -11670,7 +11670,7 @@
         <v>15</v>
       </c>
       <c r="C432">
-        <v>0.3470912443336482</v>
+        <v>0.3302996269841959</v>
       </c>
       <c r="D432" t="s">
         <v>7</v>
@@ -11684,10 +11684,10 @@
         <v>874</v>
       </c>
       <c r="B433" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C433">
-        <v>0.3105590910670639</v>
+        <v>0.3128056691296099</v>
       </c>
       <c r="D433" t="s">
         <v>7</v>
@@ -11704,7 +11704,7 @@
         <v>15</v>
       </c>
       <c r="C434">
-        <v>0.3582997836909294</v>
+        <v>0.3402497271052948</v>
       </c>
       <c r="D434" t="s">
         <v>7</v>
@@ -11718,10 +11718,10 @@
         <v>878</v>
       </c>
       <c r="B435" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C435">
-        <v>0.4173199908012859</v>
+        <v>0.4211936782971066</v>
       </c>
       <c r="D435" t="s">
         <v>7</v>
@@ -11738,7 +11738,7 @@
         <v>15</v>
       </c>
       <c r="C436">
-        <v>0.3529526680094827</v>
+        <v>0.3351417427237318</v>
       </c>
       <c r="D436" t="s">
         <v>7</v>
@@ -11752,10 +11752,10 @@
         <v>882</v>
       </c>
       <c r="B437" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C437">
-        <v>0.3488232223500442</v>
+        <v>0.3520017066706759</v>
       </c>
       <c r="D437" t="s">
         <v>7</v>
@@ -11772,7 +11772,7 @@
         <v>15</v>
       </c>
       <c r="C438">
-        <v>0.3556642988668989</v>
+        <v>0.3344300741938477</v>
       </c>
       <c r="D438" t="s">
         <v>7</v>
@@ -11786,10 +11786,10 @@
         <v>886</v>
       </c>
       <c r="B439" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C439">
-        <v>0.4102850844272984</v>
+        <v>0.4289842751371972</v>
       </c>
       <c r="D439" t="s">
         <v>7</v>
@@ -11803,10 +11803,10 @@
         <v>888</v>
       </c>
       <c r="B440" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C440">
-        <v>0.342469169631205</v>
+        <v>0.3442450995624102</v>
       </c>
       <c r="D440" t="s">
         <v>7</v>
@@ -11820,10 +11820,10 @@
         <v>890</v>
       </c>
       <c r="B441" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C441">
-        <v>0.3487432370455419</v>
+        <v>0.370109676394752</v>
       </c>
       <c r="D441" t="s">
         <v>7</v>
@@ -11837,10 +11837,10 @@
         <v>892</v>
       </c>
       <c r="B442" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C442">
-        <v>0.3261393871954462</v>
+        <v>0.3441410622169255</v>
       </c>
       <c r="D442" t="s">
         <v>7</v>
@@ -11854,10 +11854,10 @@
         <v>894</v>
       </c>
       <c r="B443" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C443">
-        <v>0.3020020218200828</v>
+        <v>0.2893030580264312</v>
       </c>
       <c r="D443" t="s">
         <v>7</v>
@@ -11871,10 +11871,10 @@
         <v>896</v>
       </c>
       <c r="B444" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C444">
-        <v>0.3661036917703137</v>
+        <v>0.3730230723228786</v>
       </c>
       <c r="D444" t="s">
         <v>7</v>
@@ -11888,10 +11888,10 @@
         <v>898</v>
       </c>
       <c r="B445" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C445">
-        <v>0.3820191656059362</v>
+        <v>0.4001739237338046</v>
       </c>
       <c r="D445" t="s">
         <v>7</v>
@@ -11908,7 +11908,7 @@
         <v>44</v>
       </c>
       <c r="C446">
-        <v>0.331460862660215</v>
+        <v>0.3203829433351694</v>
       </c>
       <c r="D446" t="s">
         <v>7</v>
@@ -11925,7 +11925,7 @@
         <v>6</v>
       </c>
       <c r="C447">
-        <v>0.2943067786662789</v>
+        <v>0.3054111934828411</v>
       </c>
       <c r="D447" t="s">
         <v>7</v>
@@ -11939,10 +11939,10 @@
         <v>904</v>
       </c>
       <c r="B448" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C448">
-        <v>0.3922889339711307</v>
+        <v>0.4125546932941145</v>
       </c>
       <c r="D448" t="s">
         <v>7</v>
@@ -11956,10 +11956,10 @@
         <v>906</v>
       </c>
       <c r="B449" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C449">
-        <v>0.422234800797579</v>
+        <v>0.4423819714439057</v>
       </c>
       <c r="D449" t="s">
         <v>7</v>
@@ -11976,7 +11976,7 @@
         <v>44</v>
       </c>
       <c r="C450">
-        <v>0.3999660009788307</v>
+        <v>0.3935677311009899</v>
       </c>
       <c r="D450" t="s">
         <v>7</v>
@@ -11993,7 +11993,7 @@
         <v>44</v>
       </c>
       <c r="C451">
-        <v>0.3742902336685707</v>
+        <v>0.3661265757613624</v>
       </c>
       <c r="D451" t="s">
         <v>7</v>
@@ -12007,10 +12007,10 @@
         <v>912</v>
       </c>
       <c r="B452" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C452">
-        <v>0.3541974257183759</v>
+        <v>0.3749886016874734</v>
       </c>
       <c r="D452" t="s">
         <v>7</v>
@@ -12024,10 +12024,10 @@
         <v>914</v>
       </c>
       <c r="B453" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C453">
-        <v>0.3872783288642929</v>
+        <v>0.3904133070126878</v>
       </c>
       <c r="D453" t="s">
         <v>7</v>
@@ -12044,7 +12044,7 @@
         <v>15</v>
       </c>
       <c r="C454">
-        <v>0.2848404685368386</v>
+        <v>0.2663624826447448</v>
       </c>
       <c r="D454" t="s">
         <v>7</v>
@@ -12058,10 +12058,10 @@
         <v>918</v>
       </c>
       <c r="B455" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C455">
-        <v>0.3848679464717468</v>
+        <v>0.3881264357815991</v>
       </c>
       <c r="D455" t="s">
         <v>7</v>
@@ -12075,10 +12075,10 @@
         <v>920</v>
       </c>
       <c r="B456" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C456">
-        <v>0.4022640123238438</v>
+        <v>0.4218294633182448</v>
       </c>
       <c r="D456" t="s">
         <v>7</v>
@@ -12095,7 +12095,7 @@
         <v>15</v>
       </c>
       <c r="C457">
-        <v>0.3575213283608206</v>
+        <v>0.3383193013911983</v>
       </c>
       <c r="D457" t="s">
         <v>7</v>
@@ -12109,10 +12109,10 @@
         <v>924</v>
       </c>
       <c r="B458" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C458">
-        <v>0.3553125467396773</v>
+        <v>0.3756449050647295</v>
       </c>
       <c r="D458" t="s">
         <v>7</v>
@@ -12126,10 +12126,10 @@
         <v>926</v>
       </c>
       <c r="B459" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C459">
-        <v>0.410195273937341</v>
+        <v>0.430521040988619</v>
       </c>
       <c r="D459" t="s">
         <v>7</v>
@@ -12143,10 +12143,10 @@
         <v>928</v>
       </c>
       <c r="B460" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C460">
-        <v>0.3659315851297602</v>
+        <v>0.3830014630818599</v>
       </c>
       <c r="D460" t="s">
         <v>7</v>
@@ -12160,10 +12160,10 @@
         <v>930</v>
       </c>
       <c r="B461" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C461">
-        <v>0.3418178316506956</v>
+        <v>0.3411269550129695</v>
       </c>
       <c r="D461" t="s">
         <v>7</v>
@@ -12177,10 +12177,10 @@
         <v>932</v>
       </c>
       <c r="B462" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C462">
-        <v>0.3414016032376475</v>
+        <v>0.3623829986698393</v>
       </c>
       <c r="D462" t="s">
         <v>7</v>
@@ -12194,10 +12194,10 @@
         <v>934</v>
       </c>
       <c r="B463" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C463">
-        <v>0.3332596090386848</v>
+        <v>0.3350003506447781</v>
       </c>
       <c r="D463" t="s">
         <v>7</v>
@@ -12211,10 +12211,10 @@
         <v>936</v>
       </c>
       <c r="B464" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C464">
-        <v>0.4372217103975827</v>
+        <v>0.4546964862099072</v>
       </c>
       <c r="D464" t="s">
         <v>7</v>
@@ -12228,10 +12228,10 @@
         <v>938</v>
       </c>
       <c r="B465" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="C465">
-        <v>0.3365869344021591</v>
+        <v>0.3337243009434443</v>
       </c>
       <c r="D465" t="s">
         <v>7</v>
@@ -12245,10 +12245,10 @@
         <v>940</v>
       </c>
       <c r="B466" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C466">
-        <v>0.5484018408091574</v>
+        <v>0.5636285624058959</v>
       </c>
       <c r="D466" t="s">
         <v>7</v>
@@ -12262,10 +12262,10 @@
         <v>942</v>
       </c>
       <c r="B467" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C467">
-        <v>0.5062639188669167</v>
+        <v>0.5229133540466075</v>
       </c>
       <c r="D467" t="s">
         <v>7</v>
@@ -12279,10 +12279,10 @@
         <v>944</v>
       </c>
       <c r="B468" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C468">
-        <v>0.4002872450265423</v>
+        <v>0.421273225580398</v>
       </c>
       <c r="D468" t="s">
         <v>7</v>
@@ -12296,10 +12296,10 @@
         <v>946</v>
       </c>
       <c r="B469" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C469">
-        <v>0.2954826016268713</v>
+        <v>0.2956148112779658</v>
       </c>
       <c r="D469" t="s">
         <v>7</v>
@@ -12313,10 +12313,10 @@
         <v>948</v>
       </c>
       <c r="B470" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C470">
-        <v>0.3091633733193918</v>
+        <v>0.3286848580451875</v>
       </c>
       <c r="D470" t="s">
         <v>7</v>
@@ -12333,7 +12333,7 @@
         <v>44</v>
       </c>
       <c r="C471">
-        <v>0.3064928215567844</v>
+        <v>0.2985705574643817</v>
       </c>
       <c r="D471" t="s">
         <v>7</v>
@@ -12350,7 +12350,7 @@
         <v>15</v>
       </c>
       <c r="C472">
-        <v>0.3087858268005206</v>
+        <v>0.2924524345477012</v>
       </c>
       <c r="D472" t="s">
         <v>7</v>
@@ -12364,10 +12364,10 @@
         <v>954</v>
       </c>
       <c r="B473" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C473">
-        <v>0.3257085584260569</v>
+        <v>0.3300138626250277</v>
       </c>
       <c r="D473" t="s">
         <v>7</v>
@@ -12381,10 +12381,10 @@
         <v>956</v>
       </c>
       <c r="B474" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C474">
-        <v>0.3755296331962198</v>
+        <v>0.3763547545030688</v>
       </c>
       <c r="D474" t="s">
         <v>7</v>
@@ -12398,10 +12398,10 @@
         <v>958</v>
       </c>
       <c r="B475" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C475">
-        <v>0.3466779966447449</v>
+        <v>0.366995330710093</v>
       </c>
       <c r="D475" t="s">
         <v>7</v>
@@ -12415,10 +12415,10 @@
         <v>960</v>
       </c>
       <c r="B476" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C476">
-        <v>0.3459229374112741</v>
+        <v>0.3659850838512184</v>
       </c>
       <c r="D476" t="s">
         <v>7</v>
@@ -12432,10 +12432,10 @@
         <v>962</v>
       </c>
       <c r="B477" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C477">
-        <v>0.3584164346099656</v>
+        <v>0.3601364174646608</v>
       </c>
       <c r="D477" t="s">
         <v>7</v>
@@ -12449,10 +12449,10 @@
         <v>964</v>
       </c>
       <c r="B478" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C478">
-        <v>0.410732442181212</v>
+        <v>0.4297430179328033</v>
       </c>
       <c r="D478" t="s">
         <v>7</v>
@@ -12469,7 +12469,7 @@
         <v>44</v>
       </c>
       <c r="C479">
-        <v>0.3961212452625692</v>
+        <v>0.3898719285703695</v>
       </c>
       <c r="D479" t="s">
         <v>7</v>
@@ -12483,10 +12483,10 @@
         <v>968</v>
       </c>
       <c r="B480" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C480">
-        <v>0.4882047987377601</v>
+        <v>0.5077160329341599</v>
       </c>
       <c r="D480" t="s">
         <v>7</v>
@@ -12500,10 +12500,10 @@
         <v>970</v>
       </c>
       <c r="B481" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="C481">
-        <v>0.3509029550353161</v>
+        <v>0.3470222046437242</v>
       </c>
       <c r="D481" t="s">
         <v>7</v>
@@ -12517,10 +12517,10 @@
         <v>972</v>
       </c>
       <c r="B482" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C482">
-        <v>0.3035410706378638</v>
+        <v>0.3056844111447325</v>
       </c>
       <c r="D482" t="s">
         <v>7</v>
@@ -12534,10 +12534,10 @@
         <v>974</v>
       </c>
       <c r="B483" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C483">
-        <v>0.3324685720463726</v>
+        <v>0.3366730886793209</v>
       </c>
       <c r="D483" t="s">
         <v>7</v>
@@ -12554,7 +12554,7 @@
         <v>44</v>
       </c>
       <c r="C484">
-        <v>0.3528969508158219</v>
+        <v>0.3460087375036862</v>
       </c>
       <c r="D484" t="s">
         <v>7</v>
@@ -12571,7 +12571,7 @@
         <v>15</v>
       </c>
       <c r="C485">
-        <v>0.3659207167571105</v>
+        <v>0.3449986945826742</v>
       </c>
       <c r="D485" t="s">
         <v>7</v>
@@ -12588,7 +12588,7 @@
         <v>15</v>
       </c>
       <c r="C486">
-        <v>0.3976489380171654</v>
+        <v>0.37787187593894</v>
       </c>
       <c r="D486" t="s">
         <v>7</v>
@@ -12605,7 +12605,7 @@
         <v>44</v>
       </c>
       <c r="C487">
-        <v>0.4202886781223146</v>
+        <v>0.4172531369874979</v>
       </c>
       <c r="D487" t="s">
         <v>7</v>
@@ -12619,10 +12619,10 @@
         <v>984</v>
       </c>
       <c r="B488" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C488">
-        <v>0.3165185326749123</v>
+        <v>0.3183370368684694</v>
       </c>
       <c r="D488" t="s">
         <v>7</v>
@@ -12636,10 +12636,10 @@
         <v>986</v>
       </c>
       <c r="B489" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C489">
-        <v>0.5124983114818423</v>
+        <v>0.5275286409506488</v>
       </c>
       <c r="D489" t="s">
         <v>7</v>
@@ -12656,7 +12656,7 @@
         <v>15</v>
       </c>
       <c r="C490">
-        <v>0.3297837489248796</v>
+        <v>0.3137033397372489</v>
       </c>
       <c r="D490" t="s">
         <v>7</v>
@@ -12670,10 +12670,10 @@
         <v>990</v>
       </c>
       <c r="B491" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C491">
-        <v>0.3089986584637536</v>
+        <v>0.3301431920913931</v>
       </c>
       <c r="D491" t="s">
         <v>7</v>
@@ -12687,10 +12687,10 @@
         <v>992</v>
       </c>
       <c r="B492" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C492">
-        <v>0.5044204215795108</v>
+        <v>0.514040355132703</v>
       </c>
       <c r="D492" t="s">
         <v>7</v>
@@ -12704,10 +12704,10 @@
         <v>994</v>
       </c>
       <c r="B493" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C493">
-        <v>0.3112720883490302</v>
+        <v>0.3317449116168437</v>
       </c>
       <c r="D493" t="s">
         <v>7</v>
@@ -12721,10 +12721,10 @@
         <v>996</v>
       </c>
       <c r="B494" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C494">
-        <v>0.3332665810918839</v>
+        <v>0.3418383383762884</v>
       </c>
       <c r="D494" t="s">
         <v>7</v>
@@ -12741,7 +12741,7 @@
         <v>44</v>
       </c>
       <c r="C495">
-        <v>0.490724584940085</v>
+        <v>0.4850737226924509</v>
       </c>
       <c r="D495" t="s">
         <v>7</v>
@@ -12755,10 +12755,10 @@
         <v>1000</v>
       </c>
       <c r="B496" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C496">
-        <v>0.5121451052477821</v>
+        <v>0.5313116910243985</v>
       </c>
       <c r="D496" t="s">
         <v>7</v>
@@ -12772,10 +12772,10 @@
         <v>1002</v>
       </c>
       <c r="B497" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C497">
-        <v>0.3877018107643418</v>
+        <v>0.3877565499357977</v>
       </c>
       <c r="D497" t="s">
         <v>7</v>
@@ -12789,10 +12789,10 @@
         <v>1004</v>
       </c>
       <c r="B498" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C498">
-        <v>0.6740567144897142</v>
+        <v>0.6832679466156888</v>
       </c>
       <c r="D498" t="s">
         <v>7</v>
@@ -12809,7 +12809,7 @@
         <v>15</v>
       </c>
       <c r="C499">
-        <v>0.3390848062383568</v>
+        <v>0.3205367195094202</v>
       </c>
       <c r="D499" t="s">
         <v>7</v>
@@ -12823,10 +12823,10 @@
         <v>1008</v>
       </c>
       <c r="B500" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C500">
-        <v>0.454538655240101</v>
+        <v>0.472155839555514</v>
       </c>
       <c r="D500" t="s">
         <v>7</v>
@@ -12843,7 +12843,7 @@
         <v>15</v>
       </c>
       <c r="C501">
-        <v>0.4132117194598846</v>
+        <v>0.3943464463636471</v>
       </c>
       <c r="D501" t="s">
         <v>7</v>
@@ -12857,10 +12857,10 @@
         <v>1012</v>
       </c>
       <c r="B502" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C502">
-        <v>0.5987536998773402</v>
+        <v>0.6100030845100392</v>
       </c>
       <c r="D502" t="s">
         <v>7</v>
@@ -12874,10 +12874,10 @@
         <v>1014</v>
       </c>
       <c r="B503" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C503">
-        <v>0.3565400296051159</v>
+        <v>0.33644308048219</v>
       </c>
       <c r="D503" t="s">
         <v>7</v>
@@ -12894,7 +12894,7 @@
         <v>15</v>
       </c>
       <c r="C504">
-        <v>0.3245983527946168</v>
+        <v>0.3052931184908297</v>
       </c>
       <c r="D504" t="s">
         <v>7</v>
@@ -12908,10 +12908,10 @@
         <v>1018</v>
       </c>
       <c r="B505" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C505">
-        <v>0.4645211191793697</v>
+        <v>0.4830849151814429</v>
       </c>
       <c r="D505" t="s">
         <v>7</v>
@@ -12928,7 +12928,7 @@
         <v>15</v>
       </c>
       <c r="C506">
-        <v>0.4863910226891323</v>
+        <v>0.4685011613236778</v>
       </c>
       <c r="D506" t="s">
         <v>7</v>
@@ -12942,10 +12942,10 @@
         <v>1022</v>
       </c>
       <c r="B507" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C507">
-        <v>0.341220896291039</v>
+        <v>0.3613212137181485</v>
       </c>
       <c r="D507" t="s">
         <v>7</v>
@@ -12962,7 +12962,7 @@
         <v>15</v>
       </c>
       <c r="C508">
-        <v>0.324352338993503</v>
+        <v>0.3045772046375209</v>
       </c>
       <c r="D508" t="s">
         <v>7</v>
@@ -12976,10 +12976,10 @@
         <v>1026</v>
       </c>
       <c r="B509" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C509">
-        <v>0.5006996036216135</v>
+        <v>0.5067775604549954</v>
       </c>
       <c r="D509" t="s">
         <v>7</v>
@@ -12993,10 +12993,10 @@
         <v>1028</v>
       </c>
       <c r="B510" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C510">
-        <v>0.3923261354332524</v>
+        <v>0.3940962279929187</v>
       </c>
       <c r="D510" t="s">
         <v>7</v>
@@ -13013,7 +13013,7 @@
         <v>44</v>
       </c>
       <c r="C511">
-        <v>0.3346644415766576</v>
+        <v>0.3246197845981337</v>
       </c>
       <c r="D511" t="s">
         <v>7</v>
@@ -13027,10 +13027,10 @@
         <v>1032</v>
       </c>
       <c r="B512" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C512">
-        <v>0.3160488332310641</v>
+        <v>0.3356932426077056</v>
       </c>
       <c r="D512" t="s">
         <v>7</v>
@@ -13044,10 +13044,10 @@
         <v>1034</v>
       </c>
       <c r="B513" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C513">
-        <v>0.385330142560689</v>
+        <v>0.4053013243203978</v>
       </c>
       <c r="D513" t="s">
         <v>7</v>
@@ -13064,7 +13064,7 @@
         <v>44</v>
       </c>
       <c r="C514">
-        <v>0.3838097865849493</v>
+        <v>0.3766931240722334</v>
       </c>
       <c r="D514" t="s">
         <v>7</v>
@@ -13078,10 +13078,10 @@
         <v>1038</v>
       </c>
       <c r="B515" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C515">
-        <v>0.5193103774051421</v>
+        <v>0.5352753379323867</v>
       </c>
       <c r="D515" t="s">
         <v>7</v>
@@ -13095,10 +13095,10 @@
         <v>1040</v>
       </c>
       <c r="B516" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C516">
-        <v>0.3121629498301982</v>
+        <v>0.332377852195855</v>
       </c>
       <c r="D516" t="s">
         <v>7</v>
@@ -13115,7 +13115,7 @@
         <v>15</v>
       </c>
       <c r="C517">
-        <v>0.3455129024719174</v>
+        <v>0.3269856622399843</v>
       </c>
       <c r="D517" t="s">
         <v>7</v>
@@ -13129,10 +13129,10 @@
         <v>1044</v>
       </c>
       <c r="B518" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C518">
-        <v>0.3459531992159799</v>
+        <v>0.3505031305585941</v>
       </c>
       <c r="D518" t="s">
         <v>7</v>
@@ -13149,7 +13149,7 @@
         <v>44</v>
       </c>
       <c r="C519">
-        <v>0.4894358989815615</v>
+        <v>0.4875769378763033</v>
       </c>
       <c r="D519" t="s">
         <v>7</v>
@@ -13166,7 +13166,7 @@
         <v>15</v>
       </c>
       <c r="C520">
-        <v>0.32799840723622</v>
+        <v>0.3092082256528178</v>
       </c>
       <c r="D520" t="s">
         <v>7</v>
@@ -13180,10 +13180,10 @@
         <v>1050</v>
       </c>
       <c r="B521" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C521">
-        <v>0.3403328706977611</v>
+        <v>0.3414308552419872</v>
       </c>
       <c r="D521" t="s">
         <v>7</v>
@@ -13200,7 +13200,7 @@
         <v>15</v>
       </c>
       <c r="C522">
-        <v>0.3433240404051616</v>
+        <v>0.3226532985142193</v>
       </c>
       <c r="D522" t="s">
         <v>7</v>
@@ -13214,10 +13214,10 @@
         <v>1054</v>
       </c>
       <c r="B523" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C523">
-        <v>0.4616499238514787</v>
+        <v>0.4804447301690321</v>
       </c>
       <c r="D523" t="s">
         <v>7</v>
@@ -13231,10 +13231,10 @@
         <v>1056</v>
       </c>
       <c r="B524" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C524">
-        <v>0.3169878636537494</v>
+        <v>0.3357694340079835</v>
       </c>
       <c r="D524" t="s">
         <v>7</v>
@@ -13251,7 +13251,7 @@
         <v>44</v>
       </c>
       <c r="C525">
-        <v>0.3803981991830894</v>
+        <v>0.3689307311093062</v>
       </c>
       <c r="D525" t="s">
         <v>7</v>
@@ -13268,7 +13268,7 @@
         <v>44</v>
       </c>
       <c r="C526">
-        <v>0.4799840235304881</v>
+        <v>0.4764825795390087</v>
       </c>
       <c r="D526" t="s">
         <v>7</v>
@@ -13282,10 +13282,10 @@
         <v>1062</v>
       </c>
       <c r="B527" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C527">
-        <v>0.4170070128906602</v>
+        <v>0.4184176151221148</v>
       </c>
       <c r="D527" t="s">
         <v>7</v>
@@ -13299,10 +13299,10 @@
         <v>1064</v>
       </c>
       <c r="B528" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C528">
-        <v>0.4597743583875652</v>
+        <v>0.4780153548811785</v>
       </c>
       <c r="D528" t="s">
         <v>7</v>
@@ -13316,10 +13316,10 @@
         <v>1066</v>
       </c>
       <c r="B529" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C529">
-        <v>0.3497113082503594</v>
+        <v>0.3525318444186028</v>
       </c>
       <c r="D529" t="s">
         <v>7</v>
@@ -13336,7 +13336,7 @@
         <v>44</v>
       </c>
       <c r="C530">
-        <v>0.4832502157499432</v>
+        <v>0.4805975800105688</v>
       </c>
       <c r="D530" t="s">
         <v>7</v>
@@ -13353,7 +13353,7 @@
         <v>44</v>
       </c>
       <c r="C531">
-        <v>0.514652676017043</v>
+        <v>0.5132803242087696</v>
       </c>
       <c r="D531" t="s">
         <v>7</v>
@@ -13367,10 +13367,10 @@
         <v>1072</v>
       </c>
       <c r="B532" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C532">
-        <v>0.3066483447215016</v>
+        <v>0.310898269435666</v>
       </c>
       <c r="D532" t="s">
         <v>7</v>
@@ -13387,7 +13387,7 @@
         <v>15</v>
       </c>
       <c r="C533">
-        <v>0.4781232897753587</v>
+        <v>0.4615460609724146</v>
       </c>
       <c r="D533" t="s">
         <v>7</v>
@@ -13401,10 +13401,10 @@
         <v>1076</v>
       </c>
       <c r="B534" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C534">
-        <v>0.3272733158320389</v>
+        <v>0.3136332239813024</v>
       </c>
       <c r="D534" t="s">
         <v>7</v>
@@ -13418,10 +13418,10 @@
         <v>1078</v>
       </c>
       <c r="B535" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C535">
-        <v>0.3272721822527869</v>
+        <v>0.3476124355041556</v>
       </c>
       <c r="D535" t="s">
         <v>7</v>
@@ -13435,10 +13435,10 @@
         <v>1080</v>
       </c>
       <c r="B536" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C536">
-        <v>0.3303766598300278</v>
+        <v>0.3515235680032729</v>
       </c>
       <c r="D536" t="s">
         <v>7</v>
@@ -13452,10 +13452,10 @@
         <v>1082</v>
       </c>
       <c r="B537" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C537">
-        <v>0.4068357590774516</v>
+        <v>0.4275681597574219</v>
       </c>
       <c r="D537" t="s">
         <v>7</v>
@@ -13469,10 +13469,10 @@
         <v>1084</v>
       </c>
       <c r="B538" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C538">
-        <v>0.3179356414673124</v>
+        <v>0.3200355269532008</v>
       </c>
       <c r="D538" t="s">
         <v>7</v>
@@ -13486,10 +13486,10 @@
         <v>1086</v>
       </c>
       <c r="B539" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C539">
-        <v>0.3144731173034122</v>
+        <v>0.3347277396727026</v>
       </c>
       <c r="D539" t="s">
         <v>7</v>
@@ -13503,10 +13503,10 @@
         <v>1088</v>
       </c>
       <c r="B540" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C540">
-        <v>0.2763437715584581</v>
+        <v>0.2782634543001677</v>
       </c>
       <c r="D540" t="s">
         <v>7</v>
@@ -13520,10 +13520,10 @@
         <v>1090</v>
       </c>
       <c r="B541" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C541">
-        <v>0.4321349612742895</v>
+        <v>0.4506651563983798</v>
       </c>
       <c r="D541" t="s">
         <v>7</v>
@@ -13540,7 +13540,7 @@
         <v>44</v>
       </c>
       <c r="C542">
-        <v>0.3573806662849626</v>
+        <v>0.3509180933117227</v>
       </c>
       <c r="D542" t="s">
         <v>7</v>
@@ -13554,10 +13554,10 @@
         <v>1094</v>
       </c>
       <c r="B543" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C543">
-        <v>0.4353219235819677</v>
+        <v>0.4517790651555583</v>
       </c>
       <c r="D543" t="s">
         <v>7</v>
@@ -13571,10 +13571,10 @@
         <v>1096</v>
       </c>
       <c r="B544" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C544">
-        <v>0.4133475971449067</v>
+        <v>0.4339133479987508</v>
       </c>
       <c r="D544" t="s">
         <v>7</v>
@@ -13840,10 +13840,10 @@
         <v>1142</v>
       </c>
       <c r="B563" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C563">
-        <v>0.27879179341987</v>
+        <v>0.2728134722765461</v>
       </c>
       <c r="D563" t="s">
         <v>1143</v>
@@ -13860,7 +13860,7 @@
         <v>1146</v>
       </c>
       <c r="C564">
-        <v>0.3239249580582771</v>
+        <v>0.3041773017477934</v>
       </c>
       <c r="D564" t="s">
         <v>1143</v>
@@ -13877,7 +13877,7 @@
         <v>1146</v>
       </c>
       <c r="C565">
-        <v>0.2646874841175051</v>
+        <v>0.2499532089170535</v>
       </c>
       <c r="D565" t="s">
         <v>1143</v>
@@ -13894,7 +13894,7 @@
         <v>1146</v>
       </c>
       <c r="C566">
-        <v>0.328114384096285</v>
+        <v>0.3109378194064201</v>
       </c>
       <c r="D566" t="s">
         <v>1143</v>
@@ -13911,7 +13911,7 @@
         <v>1146</v>
       </c>
       <c r="C567">
-        <v>0.3814741478164655</v>
+        <v>0.3641729185127462</v>
       </c>
       <c r="D567" t="s">
         <v>1143</v>
@@ -13928,7 +13928,7 @@
         <v>1146</v>
       </c>
       <c r="C568">
-        <v>0.3953370068743307</v>
+        <v>0.3737976253058301</v>
       </c>
       <c r="D568" t="s">
         <v>1143</v>
@@ -13945,7 +13945,7 @@
         <v>1146</v>
       </c>
       <c r="C569">
-        <v>0.2622990327257377</v>
+        <v>0.2463234718054413</v>
       </c>
       <c r="D569" t="s">
         <v>1143</v>
@@ -13962,7 +13962,7 @@
         <v>1146</v>
       </c>
       <c r="C570">
-        <v>0.2853634376069786</v>
+        <v>0.2681458194004742</v>
       </c>
       <c r="D570" t="s">
         <v>1143</v>
@@ -13979,7 +13979,7 @@
         <v>1146</v>
       </c>
       <c r="C571">
-        <v>0.2827409217116091</v>
+        <v>0.2657968026438128</v>
       </c>
       <c r="D571" t="s">
         <v>1143</v>
@@ -13993,10 +13993,10 @@
         <v>1162</v>
       </c>
       <c r="B572" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C572">
-        <v>0.3446257030204877</v>
+        <v>0.3397300491503483</v>
       </c>
       <c r="D572" t="s">
         <v>1143</v>
@@ -14013,7 +14013,7 @@
         <v>1146</v>
       </c>
       <c r="C573">
-        <v>0.3265096672591629</v>
+        <v>0.3077053444243202</v>
       </c>
       <c r="D573" t="s">
         <v>1143</v>
@@ -14030,7 +14030,7 @@
         <v>44</v>
       </c>
       <c r="C574">
-        <v>0.3814268878392177</v>
+        <v>0.38858728836375</v>
       </c>
       <c r="D574" t="s">
         <v>1143</v>
@@ -14047,7 +14047,7 @@
         <v>1146</v>
       </c>
       <c r="C575">
-        <v>0.345816121665159</v>
+        <v>0.3268584053710282</v>
       </c>
       <c r="D575" t="s">
         <v>1143</v>
@@ -14064,7 +14064,7 @@
         <v>1146</v>
       </c>
       <c r="C576">
-        <v>0.343709260421431</v>
+        <v>0.3259447851474023</v>
       </c>
       <c r="D576" t="s">
         <v>1143</v>
@@ -14078,10 +14078,10 @@
         <v>1172</v>
       </c>
       <c r="B577" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C577">
-        <v>0.3928711837409645</v>
+        <v>0.3926893162705831</v>
       </c>
       <c r="D577" t="s">
         <v>1143</v>
@@ -14098,7 +14098,7 @@
         <v>1146</v>
       </c>
       <c r="C578">
-        <v>0.4002391507901918</v>
+        <v>0.3796416893384154</v>
       </c>
       <c r="D578" t="s">
         <v>1143</v>
@@ -14115,7 +14115,7 @@
         <v>1146</v>
       </c>
       <c r="C579">
-        <v>0.3467561412074572</v>
+        <v>0.3275683423083785</v>
       </c>
       <c r="D579" t="s">
         <v>1143</v>
@@ -14129,10 +14129,10 @@
         <v>1178</v>
       </c>
       <c r="B580" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C580">
-        <v>0.3087481541854679</v>
+        <v>0.3060074448658934</v>
       </c>
       <c r="D580" t="s">
         <v>1143</v>
@@ -14149,7 +14149,7 @@
         <v>1146</v>
       </c>
       <c r="C581">
-        <v>0.4572131491064606</v>
+        <v>0.4326379968014321</v>
       </c>
       <c r="D581" t="s">
         <v>1143</v>
@@ -14163,10 +14163,10 @@
         <v>1182</v>
       </c>
       <c r="B582" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C582">
-        <v>0.3029628013100104</v>
+        <v>0.3019148792571923</v>
       </c>
       <c r="D582" t="s">
         <v>1143</v>
@@ -14183,7 +14183,7 @@
         <v>1146</v>
       </c>
       <c r="C583">
-        <v>0.37355807069213</v>
+        <v>0.3562865943908382</v>
       </c>
       <c r="D583" t="s">
         <v>1143</v>
@@ -14197,10 +14197,10 @@
         <v>1186</v>
       </c>
       <c r="B584" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C584">
-        <v>0.3109826823751518</v>
+        <v>0.3117871835772504</v>
       </c>
       <c r="D584" t="s">
         <v>1143</v>
@@ -14217,7 +14217,7 @@
         <v>1146</v>
       </c>
       <c r="C585">
-        <v>0.4014137622534586</v>
+        <v>0.3814079069264508</v>
       </c>
       <c r="D585" t="s">
         <v>1143</v>
@@ -14231,10 +14231,10 @@
         <v>1190</v>
       </c>
       <c r="B586" t="s">
-        <v>1146</v>
+        <v>6</v>
       </c>
       <c r="C586">
-        <v>0.2794613597048632</v>
+        <v>0.2672775792719544</v>
       </c>
       <c r="D586" t="s">
         <v>1143</v>
@@ -14248,10 +14248,10 @@
         <v>1192</v>
       </c>
       <c r="B587" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C587">
-        <v>0.3523544611256467</v>
+        <v>0.3477822179417158</v>
       </c>
       <c r="D587" t="s">
         <v>1143</v>
@@ -14268,7 +14268,7 @@
         <v>1146</v>
       </c>
       <c r="C588">
-        <v>0.3039355909611097</v>
+        <v>0.2874024045794803</v>
       </c>
       <c r="D588" t="s">
         <v>1143</v>
@@ -14285,7 +14285,7 @@
         <v>44</v>
       </c>
       <c r="C589">
-        <v>0.4041037129378175</v>
+        <v>0.4119808517453742</v>
       </c>
       <c r="D589" t="s">
         <v>1143</v>
@@ -14299,10 +14299,10 @@
         <v>1198</v>
       </c>
       <c r="B590" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C590">
-        <v>0.4484440023434808</v>
+        <v>0.4509875791124231</v>
       </c>
       <c r="D590" t="s">
         <v>1143</v>
@@ -14319,7 +14319,7 @@
         <v>1146</v>
       </c>
       <c r="C591">
-        <v>0.5324168853157348</v>
+        <v>0.509352313313134</v>
       </c>
       <c r="D591" t="s">
         <v>1143</v>
@@ -14336,7 +14336,7 @@
         <v>1146</v>
       </c>
       <c r="C592">
-        <v>0.3415313299300413</v>
+        <v>0.3262632226443293</v>
       </c>
       <c r="D592" t="s">
         <v>1143</v>
@@ -14353,7 +14353,7 @@
         <v>1146</v>
       </c>
       <c r="C593">
-        <v>0.6574734429186216</v>
+        <v>0.6382627427551794</v>
       </c>
       <c r="D593" t="s">
         <v>1143</v>
@@ -14370,7 +14370,7 @@
         <v>1146</v>
       </c>
       <c r="C594">
-        <v>0.430820818582851</v>
+        <v>0.4087171080078558</v>
       </c>
       <c r="D594" t="s">
         <v>1143</v>
@@ -14384,10 +14384,10 @@
         <v>1208</v>
       </c>
       <c r="B595" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C595">
-        <v>0.3693323003894664</v>
+        <v>0.3653837604135975</v>
       </c>
       <c r="D595" t="s">
         <v>1143</v>
@@ -14404,7 +14404,7 @@
         <v>1146</v>
       </c>
       <c r="C596">
-        <v>0.4144082144456794</v>
+        <v>0.3939845974778586</v>
       </c>
       <c r="D596" t="s">
         <v>1143</v>
@@ -14418,10 +14418,10 @@
         <v>1212</v>
       </c>
       <c r="B597" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C597">
-        <v>0.3677889676473683</v>
+        <v>0.3680865003769195</v>
       </c>
       <c r="D597" t="s">
         <v>1143</v>
@@ -14435,10 +14435,10 @@
         <v>1214</v>
       </c>
       <c r="B598" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C598">
-        <v>0.2497307928150381</v>
+        <v>0.2471317623871156</v>
       </c>
       <c r="D598" t="s">
         <v>1143</v>
@@ -14452,10 +14452,10 @@
         <v>1216</v>
       </c>
       <c r="B599" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C599">
-        <v>0.2795831780705831</v>
+        <v>0.275925548117749</v>
       </c>
       <c r="D599" t="s">
         <v>1143</v>
@@ -14472,7 +14472,7 @@
         <v>1146</v>
       </c>
       <c r="C600">
-        <v>0.2694980140305447</v>
+        <v>0.2538916754907527</v>
       </c>
       <c r="D600" t="s">
         <v>1143</v>
@@ -14489,7 +14489,7 @@
         <v>1146</v>
       </c>
       <c r="C601">
-        <v>0.2558575056851942</v>
+        <v>0.2401522778714379</v>
       </c>
       <c r="D601" t="s">
         <v>1143</v>
@@ -14506,7 +14506,7 @@
         <v>1146</v>
       </c>
       <c r="C602">
-        <v>0.3454317876177139</v>
+        <v>0.3258980834030497</v>
       </c>
       <c r="D602" t="s">
         <v>1143</v>
@@ -14523,7 +14523,7 @@
         <v>1146</v>
       </c>
       <c r="C603">
-        <v>0.2807612943435618</v>
+        <v>0.2632865341364541</v>
       </c>
       <c r="D603" t="s">
         <v>1143</v>
@@ -14537,10 +14537,10 @@
         <v>1226</v>
       </c>
       <c r="B604" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C604">
-        <v>0.3712521734837993</v>
+        <v>0.3673174353646165</v>
       </c>
       <c r="D604" t="s">
         <v>1143</v>
@@ -14557,7 +14557,7 @@
         <v>44</v>
       </c>
       <c r="C605">
-        <v>0.2715879372725378</v>
+        <v>0.279479667571571</v>
       </c>
       <c r="D605" t="s">
         <v>1143</v>
@@ -14571,10 +14571,10 @@
         <v>1230</v>
       </c>
       <c r="B606" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C606">
-        <v>0.3765226506346622</v>
+        <v>0.3752882635458198</v>
       </c>
       <c r="D606" t="s">
         <v>1143</v>
@@ -14588,10 +14588,10 @@
         <v>1232</v>
       </c>
       <c r="B607" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C607">
-        <v>0.325044004041226</v>
+        <v>0.3252122748965556</v>
       </c>
       <c r="D607" t="s">
         <v>1143</v>
@@ -14605,10 +14605,10 @@
         <v>1234</v>
       </c>
       <c r="B608" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C608">
-        <v>0.3488294823410722</v>
+        <v>0.3479982079893791</v>
       </c>
       <c r="D608" t="s">
         <v>1143</v>
@@ -14622,10 +14622,10 @@
         <v>1236</v>
       </c>
       <c r="B609" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C609">
-        <v>0.3619710251521469</v>
+        <v>0.362546888560262</v>
       </c>
       <c r="D609" t="s">
         <v>1143</v>
@@ -14639,10 +14639,10 @@
         <v>1238</v>
       </c>
       <c r="B610" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C610">
-        <v>0.2985730827949721</v>
+        <v>0.295853565193556</v>
       </c>
       <c r="D610" t="s">
         <v>1143</v>
@@ -14659,7 +14659,7 @@
         <v>44</v>
       </c>
       <c r="C611">
-        <v>0.5409530656282712</v>
+        <v>0.54508482339619</v>
       </c>
       <c r="D611" t="s">
         <v>1143</v>
@@ -14676,7 +14676,7 @@
         <v>44</v>
       </c>
       <c r="C612">
-        <v>0.3749469117602584</v>
+        <v>0.3785308684608637</v>
       </c>
       <c r="D612" t="s">
         <v>1143</v>
@@ -14693,7 +14693,7 @@
         <v>1146</v>
       </c>
       <c r="C613">
-        <v>0.320688516645652</v>
+        <v>0.3022799315491516</v>
       </c>
       <c r="D613" t="s">
         <v>1143</v>
@@ -14710,7 +14710,7 @@
         <v>1146</v>
       </c>
       <c r="C614">
-        <v>0.4218295463281418</v>
+        <v>0.4007794584166884</v>
       </c>
       <c r="D614" t="s">
         <v>1143</v>
@@ -14724,10 +14724,10 @@
         <v>1248</v>
       </c>
       <c r="B615" t="s">
-        <v>1146</v>
+        <v>10</v>
       </c>
       <c r="C615">
-        <v>0.3380208456119674</v>
+        <v>0.3367317044226123</v>
       </c>
       <c r="D615" t="s">
         <v>1143</v>
@@ -14744,7 +14744,7 @@
         <v>1146</v>
       </c>
       <c r="C616">
-        <v>0.4086418852777425</v>
+        <v>0.3898219142094663</v>
       </c>
       <c r="D616" t="s">
         <v>1143</v>
@@ -14761,7 +14761,7 @@
         <v>1146</v>
       </c>
       <c r="C617">
-        <v>0.3376930789676206</v>
+        <v>0.3193346406490536</v>
       </c>
       <c r="D617" t="s">
         <v>1143</v>
@@ -14775,10 +14775,10 @@
         <v>1254</v>
       </c>
       <c r="B618" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C618">
-        <v>0.3638839849201608</v>
+        <v>0.3617804984927424</v>
       </c>
       <c r="D618" t="s">
         <v>1143</v>
@@ -14795,7 +14795,7 @@
         <v>1146</v>
       </c>
       <c r="C619">
-        <v>0.4295936363309433</v>
+        <v>0.4125160211791412</v>
       </c>
       <c r="D619" t="s">
         <v>1143</v>
@@ -14809,7 +14809,7 @@
         <v>1258</v>
       </c>
       <c r="B620" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C620">
         <v>0.3278662904908047</v>
@@ -14843,7 +14843,7 @@
         <v>1263</v>
       </c>
       <c r="B622" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C622">
         <v>0.2765710284333049</v>
@@ -14877,7 +14877,7 @@
         <v>1268</v>
       </c>
       <c r="B624" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C624">
         <v>0.3013174439129063</v>
@@ -14894,7 +14894,7 @@
         <v>1270</v>
       </c>
       <c r="B625" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C625">
         <v>0.2484816907768088</v>
@@ -14945,7 +14945,7 @@
         <v>1276</v>
       </c>
       <c r="B628" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C628">
         <v>0.233098801377836</v>
@@ -14962,7 +14962,7 @@
         <v>1278</v>
       </c>
       <c r="B629" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C629">
         <v>0.272837428093292</v>
@@ -15081,7 +15081,7 @@
         <v>1292</v>
       </c>
       <c r="B636" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C636">
         <v>0.3746083195459203</v>
@@ -15132,7 +15132,7 @@
         <v>1298</v>
       </c>
       <c r="B639" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C639">
         <v>0.3433262666407025</v>
@@ -15149,7 +15149,7 @@
         <v>1300</v>
       </c>
       <c r="B640" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C640">
         <v>0.3121835458922222</v>
@@ -15268,7 +15268,7 @@
         <v>1314</v>
       </c>
       <c r="B647" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C647">
         <v>0.2993135631546125</v>
@@ -15319,7 +15319,7 @@
         <v>1320</v>
       </c>
       <c r="B650" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C650">
         <v>0.2845150054340436</v>
@@ -15371,15 +15371,15 @@
         <v>15</v>
       </c>
       <c r="B2">
-        <v>113</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B3">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -15387,15 +15387,15 @@
         <v>145</v>
       </c>
       <c r="B4">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5">
-        <v>255</v>
+        <v>290</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -15403,7 +15403,7 @@
         <v>44</v>
       </c>
       <c r="B6">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -15427,7 +15427,7 @@
         <v>1146</v>
       </c>
       <c r="B9">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:2">
